--- a/Documentation/LHO - M5 - JournalPlanif.xlsx
+++ b/Documentation/LHO - M5 - JournalPlanif.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>date</t>
   </si>
@@ -312,6 +312,12 @@
   </si>
   <si>
     <t xml:space="preserve">Commencement du support de présentation. Ajout du model et de la base de travail. Ajout des différentes polices utilisés.</t>
+  </si>
+  <si>
+    <t>02.06.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation des différents composants du projet</t>
   </si>
   <si>
     <t>Phases</t>
@@ -384,9 +390,6 @@
   </si>
   <si>
     <t>01.06.2026</t>
-  </si>
-  <si>
-    <t>02.06.2026</t>
   </si>
   <si>
     <t>08.06.2026</t>
@@ -1556,7 +1559,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="179">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1604,6 +1607,12 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3707,8 +3716,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E68">
-  <autoFilter ref="B2:E68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E69">
+  <autoFilter ref="B2:E69"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -4272,7 +4281,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.019687192387618943</v>
+        <v>0.018474802422251874</v>
       </c>
       <c r="J3" s="12" t="str">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -4305,7 +4314,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.019687192387618943</v>
+        <v>0.018474802422251874</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -4338,7 +4347,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.062342775894126658</v>
+        <v>0.0585035410037976</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -4371,7 +4380,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.11156075686317402</v>
+        <v>0.10469054705942729</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -4400,11 +4409,11 @@
       </c>
       <c r="H7" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>46</v>
+        <v>55.5</v>
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.3018702832768238</v>
+        <v>0.34178384481165969</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -4412,7 +4421,7 @@
       </c>
       <c r="K7" s="13">
         <f/>
-        <v>46</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="8" ht="28.5">
@@ -4437,7 +4446,7 @@
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.46921141857158483</v>
+        <v>0.44031612439700302</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -4470,7 +4479,7 @@
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.015640380619052829</v>
+        <v>0.014677204146566767</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -4499,11 +4508,11 @@
       </c>
       <c r="H10" s="16">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0</v>
+        <v>0.0030791337370419791</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -4526,7 +4535,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>152.38333333333333</v>
+        <v>162.38333333333333</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -5300,7 +5309,7 @@
         <v>46160</v>
       </c>
       <c r="C66" s="21">
-        <v>0.10416666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>12</v>
@@ -5314,7 +5323,7 @@
         <v>46161</v>
       </c>
       <c r="C67" s="21">
-        <v>0.083333333333333329</v>
+        <v>0.14583333333333334</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>12</v>
@@ -5333,85 +5342,93 @@
       <c r="D68" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E68" s="22" t="s">
+      <c r="E68" s="8" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="20"/>
-      <c r="C69" s="23"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="8"/>
+      <c r="B69" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" s="24" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="20"/>
-      <c r="C70" s="23"/>
+      <c r="C70" s="25"/>
       <c r="D70" s="7"/>
       <c r="E70" s="8"/>
     </row>
     <row r="71">
       <c r="B71" s="20"/>
-      <c r="C71" s="23"/>
+      <c r="C71" s="25"/>
       <c r="D71" s="7"/>
       <c r="E71" s="8"/>
     </row>
     <row r="72">
       <c r="B72" s="20"/>
-      <c r="C72" s="23"/>
+      <c r="C72" s="25"/>
       <c r="D72" s="7"/>
       <c r="E72" s="8"/>
     </row>
     <row r="73">
       <c r="B73" s="20"/>
-      <c r="C73" s="23"/>
+      <c r="C73" s="25"/>
       <c r="D73" s="7"/>
       <c r="E73" s="8"/>
     </row>
     <row r="74">
       <c r="B74" s="20"/>
-      <c r="C74" s="23"/>
+      <c r="C74" s="25"/>
       <c r="D74" s="7"/>
       <c r="E74" s="8"/>
     </row>
     <row r="75">
       <c r="B75" s="20"/>
-      <c r="C75" s="23"/>
+      <c r="C75" s="25"/>
       <c r="D75" s="7"/>
       <c r="E75" s="8"/>
     </row>
     <row r="76">
       <c r="B76" s="7"/>
-      <c r="C76" s="23"/>
+      <c r="C76" s="25"/>
       <c r="D76" s="7"/>
       <c r="E76" s="8"/>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
-      <c r="C77" s="23"/>
+      <c r="C77" s="25"/>
       <c r="D77" s="7"/>
       <c r="E77" s="8"/>
     </row>
     <row r="78">
       <c r="B78" s="7"/>
-      <c r="C78" s="23"/>
+      <c r="C78" s="25"/>
       <c r="D78" s="7"/>
       <c r="E78" s="8"/>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
-      <c r="C79" s="23"/>
+      <c r="C79" s="25"/>
       <c r="D79" s="7"/>
       <c r="E79" s="8"/>
     </row>
     <row r="80">
       <c r="B80" s="7"/>
-      <c r="C80" s="23"/>
+      <c r="C80" s="25"/>
       <c r="D80" s="7"/>
       <c r="E80" s="8"/>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
-      <c r="C81" s="23"/>
+      <c r="C81" s="25"/>
       <c r="D81" s="7"/>
       <c r="E81" s="8"/>
     </row>
@@ -5431,7 +5448,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{0004003C-0028-4F8D-AFC5-00D2000100C9}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{002500AD-0070-46AA-93D9-00FC000200AB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -5463,1787 +5480,1787 @@
       <c r="C1"/>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="str">
+      <c r="A2" s="26" t="str">
         <f t="array" ref="A2:A38">_xlfn.UNIQUE(Journal[date])</f>
         <v>20.01.2026</v>
       </c>
-      <c r="B2" s="25">
+      <c r="B2" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A2,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="str">
+      <c r="A3" s="26" t="str">
         <f/>
         <v>27.01.2026</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C3"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="str">
+      <c r="A4" s="26" t="str">
         <f/>
         <v>30.01.2026</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C4"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="str">
+      <c r="A5" s="26" t="str">
         <f/>
         <v>03.02.2026</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C5"/>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="26" t="str">
         <f/>
         <v>04.02.2026</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C6"/>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="str">
+      <c r="A7" s="26" t="str">
         <f/>
         <v>06.02.2026</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C7"/>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="str">
+      <c r="A8" s="26" t="str">
         <f/>
         <v>08.02.2026</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
       <c r="C8"/>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="str">
+      <c r="A9" s="26" t="str">
         <f/>
         <v>09.02.2026</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0.041666666666666664</v>
       </c>
       <c r="C9"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="str">
+      <c r="A10" s="26" t="str">
         <f/>
         <v>10.02.2026</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0.29166666666666663</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="str">
+      <c r="A11" s="26" t="str">
         <f/>
         <v>12.02.2026</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="str">
+      <c r="A12" s="26" t="str">
         <f/>
         <v>13.02.2026</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0.0625</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="str">
+      <c r="A13" s="26" t="str">
         <f/>
         <v>24.02.2026</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0.125</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="str">
+      <c r="A14" s="26" t="str">
         <f/>
         <v>03.03.2026</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="str">
+      <c r="A15" s="26" t="str">
         <f/>
         <v>05.03.2026</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="24">
+      <c r="A16" s="26">
         <f/>
         <v>46087</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="24">
+      <c r="A17" s="26">
         <f/>
         <v>46088</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0.25</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="24">
+      <c r="A18" s="26">
         <f/>
         <v>46091</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="24">
+      <c r="A19" s="26">
         <f/>
         <v>46093</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="24">
+      <c r="A20" s="26">
         <f/>
         <v>46095</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="24">
+      <c r="A21" s="26">
         <f/>
         <v>46096</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="24">
+      <c r="A22" s="26">
         <f/>
         <v>46097</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="24">
+      <c r="A23" s="26">
         <f/>
         <v>46098</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="24">
+      <c r="A24" s="26">
         <f/>
         <v>46099</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="24">
+      <c r="A25" s="26">
         <f/>
         <v>46100</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="C25"/>
-      <c r="F25" s="26"/>
+      <c r="F25" s="28"/>
     </row>
     <row r="26">
-      <c r="A26" s="24">
+      <c r="A26" s="26">
         <f/>
         <v>46102</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24">
+      <c r="A27" s="26">
         <f/>
         <v>46103</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24">
+      <c r="A28" s="26">
         <f/>
         <v>46104</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0.013888888888888888</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0.013888888888888888</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24">
+      <c r="A29" s="26">
         <f/>
         <v>46117</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24">
+      <c r="A30" s="26">
         <f/>
         <v>46118</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24">
+      <c r="A31" s="26">
         <f/>
         <v>46119</v>
       </c>
-      <c r="B31" s="25">
+      <c r="B31" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24">
+      <c r="A32" s="26">
         <f/>
         <v>46122</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24">
+      <c r="A33" s="26">
         <f/>
         <v>46133</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24">
+      <c r="A34" s="26">
         <f/>
         <v>46134</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24">
+      <c r="A35" s="26">
         <f/>
         <v>46135</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0.041666666666666664</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24">
+      <c r="A36" s="26">
         <f/>
         <v>46136</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24">
+      <c r="A37" s="26">
         <f/>
         <v>46137</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24">
+      <c r="A38" s="26">
         <f/>
         <v>46140</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0.18958333333333333</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24"/>
-      <c r="C39" s="27">
+      <c r="A39" s="26"/>
+      <c r="C39" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24"/>
-      <c r="B40" s="25" t="str">
+      <c r="A40" s="26"/>
+      <c r="B40" s="27" t="str">
         <f t="shared" ref="B40:B103" si="0">IF(C40&gt;0,C40,"")</f>
         <v/>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24"/>
-      <c r="B41" s="25" t="str">
+      <c r="A41" s="26"/>
+      <c r="B41" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28"/>
-      <c r="B42" s="25" t="str">
+      <c r="A42" s="30"/>
+      <c r="B42" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28"/>
-      <c r="B43" s="25" t="str">
+      <c r="A43" s="30"/>
+      <c r="B43" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28"/>
-      <c r="B44" s="25" t="str">
+      <c r="A44" s="30"/>
+      <c r="B44" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28"/>
-      <c r="B45" s="25" t="str">
+      <c r="A45" s="30"/>
+      <c r="B45" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="28"/>
-      <c r="B46" s="25" t="str">
+      <c r="A46" s="30"/>
+      <c r="B46" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29"/>
-      <c r="B47" s="25" t="str">
+      <c r="A47" s="31"/>
+      <c r="B47" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29"/>
-      <c r="B48" s="25" t="str">
+      <c r="A48" s="31"/>
+      <c r="B48" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29"/>
-      <c r="B49" s="25" t="str">
+      <c r="A49" s="31"/>
+      <c r="B49" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29"/>
-      <c r="B50" s="25" t="str">
+      <c r="A50" s="31"/>
+      <c r="B50" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29"/>
-      <c r="B51" s="25" t="str">
+      <c r="A51" s="31"/>
+      <c r="B51" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29"/>
-      <c r="B52" s="25" t="str">
+      <c r="A52" s="31"/>
+      <c r="B52" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29"/>
-      <c r="B53" s="25" t="str">
+      <c r="A53" s="31"/>
+      <c r="B53" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29"/>
-      <c r="B54" s="25" t="str">
+      <c r="A54" s="31"/>
+      <c r="B54" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29"/>
-      <c r="B55" s="25" t="str">
+      <c r="A55" s="31"/>
+      <c r="B55" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29"/>
-      <c r="B56" s="25" t="str">
+      <c r="A56" s="31"/>
+      <c r="B56" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29"/>
-      <c r="B57" s="25" t="str">
+      <c r="A57" s="31"/>
+      <c r="B57" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29"/>
-      <c r="B58" s="25" t="str">
+      <c r="A58" s="31"/>
+      <c r="B58" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29"/>
-      <c r="B59" s="25" t="str">
+      <c r="A59" s="31"/>
+      <c r="B59" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29"/>
-      <c r="B60" s="25" t="str">
+      <c r="A60" s="31"/>
+      <c r="B60" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29"/>
-      <c r="B61" s="25" t="str">
+      <c r="A61" s="31"/>
+      <c r="B61" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29"/>
-      <c r="B62" s="25" t="str">
+      <c r="A62" s="31"/>
+      <c r="B62" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29"/>
-      <c r="B63" s="25" t="str">
+      <c r="A63" s="31"/>
+      <c r="B63" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29"/>
-      <c r="B64" s="25" t="str">
+      <c r="A64" s="31"/>
+      <c r="B64" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29"/>
-      <c r="B65" s="25" t="str">
+      <c r="A65" s="31"/>
+      <c r="B65" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29"/>
-      <c r="B66" s="25" t="str">
+      <c r="A66" s="31"/>
+      <c r="B66" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29"/>
-      <c r="B67" s="25" t="str">
+      <c r="A67" s="31"/>
+      <c r="B67" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29"/>
-      <c r="B68" s="25" t="str">
+      <c r="A68" s="31"/>
+      <c r="B68" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29"/>
-      <c r="B69" s="25" t="str">
+      <c r="A69" s="31"/>
+      <c r="B69" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29"/>
-      <c r="B70" s="25" t="str">
+      <c r="A70" s="31"/>
+      <c r="B70" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29"/>
-      <c r="B71" s="25" t="str">
+      <c r="A71" s="31"/>
+      <c r="B71" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29"/>
-      <c r="B72" s="25" t="str">
+      <c r="A72" s="31"/>
+      <c r="B72" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29"/>
-      <c r="B73" s="25" t="str">
+      <c r="A73" s="31"/>
+      <c r="B73" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29"/>
-      <c r="B74" s="25" t="str">
+      <c r="A74" s="31"/>
+      <c r="B74" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29"/>
-      <c r="B75" s="25" t="str">
+      <c r="A75" s="31"/>
+      <c r="B75" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29"/>
-      <c r="B76" s="25" t="str">
+      <c r="A76" s="31"/>
+      <c r="B76" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29"/>
-      <c r="B77" s="25" t="str">
+      <c r="A77" s="31"/>
+      <c r="B77" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29"/>
-      <c r="B78" s="25" t="str">
+      <c r="A78" s="31"/>
+      <c r="B78" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29"/>
-      <c r="B79" s="25" t="str">
+      <c r="A79" s="31"/>
+      <c r="B79" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29"/>
-      <c r="B80" s="25" t="str">
+      <c r="A80" s="31"/>
+      <c r="B80" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29"/>
-      <c r="B81" s="25" t="str">
+      <c r="A81" s="31"/>
+      <c r="B81" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29"/>
-      <c r="B82" s="25" t="str">
+      <c r="A82" s="31"/>
+      <c r="B82" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29"/>
-      <c r="B83" s="25" t="str">
+      <c r="A83" s="31"/>
+      <c r="B83" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29"/>
-      <c r="B84" s="25" t="str">
+      <c r="A84" s="31"/>
+      <c r="B84" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29"/>
-      <c r="B85" s="25" t="str">
+      <c r="A85" s="31"/>
+      <c r="B85" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="29"/>
-      <c r="B86" s="25" t="str">
+      <c r="A86" s="31"/>
+      <c r="B86" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29"/>
-      <c r="B87" s="25" t="str">
+      <c r="A87" s="31"/>
+      <c r="B87" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29"/>
-      <c r="B88" s="25" t="str">
+      <c r="A88" s="31"/>
+      <c r="B88" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29"/>
-      <c r="B89" s="25" t="str">
+      <c r="A89" s="31"/>
+      <c r="B89" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29"/>
-      <c r="B90" s="25" t="str">
+      <c r="A90" s="31"/>
+      <c r="B90" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29"/>
-      <c r="B91" s="25" t="str">
+      <c r="A91" s="31"/>
+      <c r="B91" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="29"/>
-      <c r="B92" s="25" t="str">
+      <c r="A92" s="31"/>
+      <c r="B92" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29"/>
-      <c r="B93" s="25" t="str">
+      <c r="A93" s="31"/>
+      <c r="B93" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="29"/>
-      <c r="B94" s="25" t="str">
+      <c r="A94" s="31"/>
+      <c r="B94" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29"/>
-      <c r="B95" s="25" t="str">
+      <c r="A95" s="31"/>
+      <c r="B95" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="29"/>
-      <c r="B96" s="25" t="str">
+      <c r="A96" s="31"/>
+      <c r="B96" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29"/>
-      <c r="B97" s="25" t="str">
+      <c r="A97" s="31"/>
+      <c r="B97" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="29"/>
-      <c r="B98" s="25" t="str">
+      <c r="A98" s="31"/>
+      <c r="B98" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="29"/>
-      <c r="B99" s="25" t="str">
+      <c r="A99" s="31"/>
+      <c r="B99" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="29"/>
-      <c r="B100" s="25" t="str">
+      <c r="A100" s="31"/>
+      <c r="B100" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29"/>
-      <c r="B101" s="25" t="str">
+      <c r="A101" s="31"/>
+      <c r="B101" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="29"/>
-      <c r="B102" s="25" t="str">
+      <c r="A102" s="31"/>
+      <c r="B102" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="29"/>
-      <c r="B103" s="25" t="str">
+      <c r="A103" s="31"/>
+      <c r="B103" s="27" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="29"/>
-      <c r="B104" s="25" t="str">
+      <c r="A104" s="31"/>
+      <c r="B104" s="27" t="str">
         <f t="shared" ref="B104:B114" si="1">IF(C104&gt;0,C104,"")</f>
         <v/>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="29"/>
-      <c r="B105" s="25" t="str">
+      <c r="A105" s="31"/>
+      <c r="B105" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29"/>
-      <c r="B106" s="25" t="str">
+      <c r="A106" s="31"/>
+      <c r="B106" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="29"/>
-      <c r="B107" s="25" t="str">
+      <c r="A107" s="31"/>
+      <c r="B107" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="29"/>
-      <c r="B108" s="25" t="str">
+      <c r="A108" s="31"/>
+      <c r="B108" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="29"/>
-      <c r="B109" s="25" t="str">
+      <c r="A109" s="31"/>
+      <c r="B109" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="29"/>
-      <c r="B110" s="25" t="str">
+      <c r="A110" s="31"/>
+      <c r="B110" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="29"/>
-      <c r="B111" s="25" t="str">
+      <c r="A111" s="31"/>
+      <c r="B111" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="29"/>
-      <c r="B112" s="25" t="str">
+      <c r="A112" s="31"/>
+      <c r="B112" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="29"/>
-      <c r="B113" s="25" t="str">
+      <c r="A113" s="31"/>
+      <c r="B113" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="29"/>
-      <c r="B114" s="25" t="str">
+      <c r="A114" s="31"/>
+      <c r="B114" s="27" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="29"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="27"/>
+      <c r="A115" s="31"/>
+      <c r="B115" s="31"/>
+      <c r="C115" s="29"/>
     </row>
     <row r="116">
-      <c r="A116" s="29"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="27"/>
+      <c r="A116" s="31"/>
+      <c r="B116" s="31"/>
+      <c r="C116" s="29"/>
     </row>
     <row r="117">
-      <c r="A117" s="29"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="27"/>
+      <c r="A117" s="31"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118">
-      <c r="A118" s="29"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="27"/>
+      <c r="A118" s="31"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="29"/>
     </row>
     <row r="119">
-      <c r="A119" s="29"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="27"/>
+      <c r="A119" s="31"/>
+      <c r="B119" s="31"/>
+      <c r="C119" s="29"/>
     </row>
     <row r="120">
-      <c r="A120" s="29"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="27"/>
+      <c r="A120" s="31"/>
+      <c r="B120" s="31"/>
+      <c r="C120" s="29"/>
     </row>
     <row r="121">
-      <c r="A121" s="29"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="27"/>
+      <c r="A121" s="31"/>
+      <c r="B121" s="31"/>
+      <c r="C121" s="29"/>
     </row>
     <row r="122">
-      <c r="A122" s="29"/>
-      <c r="B122" s="29"/>
-      <c r="C122" s="27"/>
+      <c r="A122" s="31"/>
+      <c r="B122" s="31"/>
+      <c r="C122" s="29"/>
     </row>
     <row r="123">
-      <c r="A123" s="29"/>
-      <c r="B123" s="29"/>
-      <c r="C123" s="27"/>
+      <c r="A123" s="31"/>
+      <c r="B123" s="31"/>
+      <c r="C123" s="29"/>
     </row>
     <row r="124">
-      <c r="A124" s="29"/>
-      <c r="B124" s="29"/>
-      <c r="C124" s="27"/>
+      <c r="A124" s="31"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="29"/>
     </row>
     <row r="125">
-      <c r="A125" s="29"/>
-      <c r="B125" s="29"/>
-      <c r="C125" s="27"/>
+      <c r="A125" s="31"/>
+      <c r="B125" s="31"/>
+      <c r="C125" s="29"/>
     </row>
     <row r="126">
-      <c r="A126" s="29"/>
-      <c r="B126" s="29"/>
-      <c r="C126" s="27"/>
+      <c r="A126" s="31"/>
+      <c r="B126" s="31"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127">
-      <c r="A127" s="29"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="27"/>
+      <c r="A127" s="31"/>
+      <c r="B127" s="31"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128">
-      <c r="A128" s="29"/>
-      <c r="B128" s="29"/>
-      <c r="C128" s="27"/>
+      <c r="A128" s="31"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="29"/>
     </row>
     <row r="129">
-      <c r="A129" s="29"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="27"/>
+      <c r="A129" s="31"/>
+      <c r="B129" s="31"/>
+      <c r="C129" s="29"/>
     </row>
     <row r="130">
-      <c r="A130" s="29"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="27"/>
+      <c r="A130" s="31"/>
+      <c r="B130" s="31"/>
+      <c r="C130" s="29"/>
     </row>
     <row r="131">
-      <c r="A131" s="29"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="27"/>
+      <c r="A131" s="31"/>
+      <c r="B131" s="31"/>
+      <c r="C131" s="29"/>
     </row>
     <row r="132">
-      <c r="A132" s="29"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="27"/>
+      <c r="A132" s="31"/>
+      <c r="B132" s="31"/>
+      <c r="C132" s="29"/>
     </row>
     <row r="133">
-      <c r="A133" s="29"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="27"/>
+      <c r="A133" s="31"/>
+      <c r="B133" s="31"/>
+      <c r="C133" s="29"/>
     </row>
     <row r="134">
-      <c r="A134" s="29"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="27"/>
+      <c r="A134" s="31"/>
+      <c r="B134" s="31"/>
+      <c r="C134" s="29"/>
     </row>
     <row r="135">
-      <c r="A135" s="29"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="27"/>
+      <c r="A135" s="31"/>
+      <c r="B135" s="31"/>
+      <c r="C135" s="29"/>
     </row>
     <row r="136">
-      <c r="A136" s="29"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="27"/>
+      <c r="A136" s="31"/>
+      <c r="B136" s="31"/>
+      <c r="C136" s="29"/>
     </row>
     <row r="137">
-      <c r="A137" s="29"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="27"/>
+      <c r="A137" s="31"/>
+      <c r="B137" s="31"/>
+      <c r="C137" s="29"/>
     </row>
     <row r="138">
-      <c r="A138" s="29"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="27"/>
+      <c r="A138" s="31"/>
+      <c r="B138" s="31"/>
+      <c r="C138" s="29"/>
     </row>
     <row r="139">
-      <c r="A139" s="29"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="27"/>
+      <c r="A139" s="31"/>
+      <c r="B139" s="31"/>
+      <c r="C139" s="29"/>
     </row>
     <row r="140">
-      <c r="A140" s="29"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="27"/>
+      <c r="A140" s="31"/>
+      <c r="B140" s="31"/>
+      <c r="C140" s="29"/>
     </row>
     <row r="141">
-      <c r="A141" s="29"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="27"/>
+      <c r="A141" s="31"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="29"/>
     </row>
     <row r="142">
-      <c r="A142" s="29"/>
-      <c r="B142" s="29"/>
-      <c r="C142" s="27"/>
+      <c r="A142" s="31"/>
+      <c r="B142" s="31"/>
+      <c r="C142" s="29"/>
     </row>
     <row r="143">
-      <c r="A143" s="29"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="27"/>
+      <c r="A143" s="31"/>
+      <c r="B143" s="31"/>
+      <c r="C143" s="29"/>
     </row>
     <row r="144">
-      <c r="A144" s="29"/>
-      <c r="B144" s="29"/>
-      <c r="C144" s="27"/>
+      <c r="A144" s="31"/>
+      <c r="B144" s="31"/>
+      <c r="C144" s="29"/>
     </row>
     <row r="145">
-      <c r="A145" s="29"/>
-      <c r="B145" s="29"/>
-      <c r="C145" s="27"/>
+      <c r="A145" s="31"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="29"/>
     </row>
     <row r="146">
-      <c r="A146" s="29"/>
-      <c r="B146" s="29"/>
-      <c r="C146" s="27"/>
+      <c r="A146" s="31"/>
+      <c r="B146" s="31"/>
+      <c r="C146" s="29"/>
     </row>
     <row r="147">
-      <c r="A147" s="29"/>
-      <c r="B147" s="29"/>
-      <c r="C147" s="27"/>
+      <c r="A147" s="31"/>
+      <c r="B147" s="31"/>
+      <c r="C147" s="29"/>
     </row>
     <row r="148">
-      <c r="A148" s="29"/>
-      <c r="B148" s="29"/>
-      <c r="C148" s="27"/>
+      <c r="A148" s="31"/>
+      <c r="B148" s="31"/>
+      <c r="C148" s="29"/>
     </row>
     <row r="149">
-      <c r="A149" s="29"/>
-      <c r="B149" s="29"/>
-      <c r="C149" s="27"/>
+      <c r="A149" s="31"/>
+      <c r="B149" s="31"/>
+      <c r="C149" s="29"/>
     </row>
     <row r="150">
-      <c r="A150" s="29"/>
-      <c r="B150" s="29"/>
-      <c r="C150" s="27"/>
+      <c r="A150" s="31"/>
+      <c r="B150" s="31"/>
+      <c r="C150" s="29"/>
     </row>
     <row r="151">
-      <c r="A151" s="29"/>
-      <c r="B151" s="29"/>
-      <c r="C151" s="27"/>
+      <c r="A151" s="31"/>
+      <c r="B151" s="31"/>
+      <c r="C151" s="29"/>
     </row>
     <row r="152">
-      <c r="A152" s="29"/>
-      <c r="B152" s="29"/>
-      <c r="C152" s="27"/>
+      <c r="A152" s="31"/>
+      <c r="B152" s="31"/>
+      <c r="C152" s="29"/>
     </row>
     <row r="153">
-      <c r="A153" s="29"/>
-      <c r="B153" s="29"/>
-      <c r="C153" s="27"/>
+      <c r="A153" s="31"/>
+      <c r="B153" s="31"/>
+      <c r="C153" s="29"/>
     </row>
     <row r="154">
-      <c r="A154" s="29"/>
-      <c r="B154" s="29"/>
-      <c r="C154" s="27"/>
+      <c r="A154" s="31"/>
+      <c r="B154" s="31"/>
+      <c r="C154" s="29"/>
     </row>
     <row r="155">
-      <c r="A155" s="29"/>
-      <c r="B155" s="29"/>
-      <c r="C155" s="27"/>
+      <c r="A155" s="31"/>
+      <c r="B155" s="31"/>
+      <c r="C155" s="29"/>
     </row>
     <row r="156">
-      <c r="A156" s="29"/>
-      <c r="B156" s="29"/>
-      <c r="C156" s="27"/>
+      <c r="A156" s="31"/>
+      <c r="B156" s="31"/>
+      <c r="C156" s="29"/>
     </row>
     <row r="157">
-      <c r="A157" s="29"/>
-      <c r="B157" s="29"/>
-      <c r="C157" s="27"/>
+      <c r="A157" s="31"/>
+      <c r="B157" s="31"/>
+      <c r="C157" s="29"/>
     </row>
     <row r="158">
-      <c r="A158" s="29"/>
-      <c r="B158" s="29"/>
-      <c r="C158" s="27"/>
+      <c r="A158" s="31"/>
+      <c r="B158" s="31"/>
+      <c r="C158" s="29"/>
     </row>
     <row r="159">
-      <c r="A159" s="29"/>
-      <c r="B159" s="29"/>
+      <c r="A159" s="31"/>
+      <c r="B159" s="31"/>
     </row>
     <row r="160">
-      <c r="A160" s="29"/>
-      <c r="B160" s="29"/>
+      <c r="A160" s="31"/>
+      <c r="B160" s="31"/>
     </row>
     <row r="161">
-      <c r="A161" s="29"/>
-      <c r="B161" s="29"/>
+      <c r="A161" s="31"/>
+      <c r="B161" s="31"/>
     </row>
     <row r="162">
-      <c r="A162" s="29"/>
-      <c r="B162" s="29"/>
+      <c r="A162" s="31"/>
+      <c r="B162" s="31"/>
     </row>
     <row r="163">
-      <c r="A163" s="29"/>
-      <c r="B163" s="29"/>
+      <c r="A163" s="31"/>
+      <c r="B163" s="31"/>
     </row>
     <row r="164">
-      <c r="A164" s="29"/>
-      <c r="B164" s="29"/>
+      <c r="A164" s="31"/>
+      <c r="B164" s="31"/>
     </row>
     <row r="165">
-      <c r="A165" s="29"/>
-      <c r="B165" s="29"/>
+      <c r="A165" s="31"/>
+      <c r="B165" s="31"/>
     </row>
     <row r="166">
-      <c r="A166" s="29"/>
-      <c r="B166" s="29"/>
+      <c r="A166" s="31"/>
+      <c r="B166" s="31"/>
     </row>
     <row r="167">
-      <c r="A167" s="29"/>
-      <c r="B167" s="29"/>
+      <c r="A167" s="31"/>
+      <c r="B167" s="31"/>
     </row>
     <row r="168">
-      <c r="A168" s="29"/>
-      <c r="B168" s="29"/>
+      <c r="A168" s="31"/>
+      <c r="B168" s="31"/>
     </row>
     <row r="169">
-      <c r="A169" s="29"/>
-      <c r="B169" s="29"/>
+      <c r="A169" s="31"/>
+      <c r="B169" s="31"/>
     </row>
     <row r="170">
-      <c r="A170" s="29"/>
-      <c r="B170" s="29"/>
+      <c r="A170" s="31"/>
+      <c r="B170" s="31"/>
     </row>
     <row r="171">
-      <c r="A171" s="29"/>
-      <c r="B171" s="29"/>
+      <c r="A171" s="31"/>
+      <c r="B171" s="31"/>
     </row>
     <row r="172">
-      <c r="A172" s="29"/>
-      <c r="B172" s="29"/>
+      <c r="A172" s="31"/>
+      <c r="B172" s="31"/>
     </row>
     <row r="173">
-      <c r="A173" s="29"/>
-      <c r="B173" s="29"/>
+      <c r="A173" s="31"/>
+      <c r="B173" s="31"/>
     </row>
     <row r="174">
-      <c r="A174" s="29"/>
-      <c r="B174" s="29"/>
+      <c r="A174" s="31"/>
+      <c r="B174" s="31"/>
     </row>
     <row r="175">
-      <c r="A175" s="29"/>
-      <c r="B175" s="29"/>
+      <c r="A175" s="31"/>
+      <c r="B175" s="31"/>
     </row>
     <row r="176">
-      <c r="A176" s="29"/>
-      <c r="B176" s="29"/>
+      <c r="A176" s="31"/>
+      <c r="B176" s="31"/>
     </row>
     <row r="177">
-      <c r="A177" s="29"/>
-      <c r="B177" s="29"/>
+      <c r="A177" s="31"/>
+      <c r="B177" s="31"/>
     </row>
     <row r="178">
-      <c r="A178" s="29"/>
-      <c r="B178" s="29"/>
+      <c r="A178" s="31"/>
+      <c r="B178" s="31"/>
     </row>
     <row r="179">
-      <c r="A179" s="29"/>
-      <c r="B179" s="29"/>
+      <c r="A179" s="31"/>
+      <c r="B179" s="31"/>
     </row>
     <row r="180">
-      <c r="A180" s="29"/>
-      <c r="B180" s="29"/>
+      <c r="A180" s="31"/>
+      <c r="B180" s="31"/>
     </row>
     <row r="181">
-      <c r="A181" s="29"/>
-      <c r="B181" s="29"/>
+      <c r="A181" s="31"/>
+      <c r="B181" s="31"/>
     </row>
     <row r="182">
-      <c r="A182" s="29"/>
-      <c r="B182" s="29"/>
+      <c r="A182" s="31"/>
+      <c r="B182" s="31"/>
     </row>
     <row r="183">
-      <c r="A183" s="29"/>
-      <c r="B183" s="29"/>
+      <c r="A183" s="31"/>
+      <c r="B183" s="31"/>
     </row>
     <row r="184">
-      <c r="A184" s="29"/>
-      <c r="B184" s="29"/>
+      <c r="A184" s="31"/>
+      <c r="B184" s="31"/>
     </row>
     <row r="185">
-      <c r="A185" s="29"/>
-      <c r="B185" s="29"/>
+      <c r="A185" s="31"/>
+      <c r="B185" s="31"/>
     </row>
     <row r="186">
-      <c r="A186" s="29"/>
-      <c r="B186" s="29"/>
+      <c r="A186" s="31"/>
+      <c r="B186" s="31"/>
     </row>
     <row r="187">
-      <c r="A187" s="29"/>
-      <c r="B187" s="29"/>
+      <c r="A187" s="31"/>
+      <c r="B187" s="31"/>
     </row>
     <row r="188">
-      <c r="A188" s="29"/>
-      <c r="B188" s="29"/>
+      <c r="A188" s="31"/>
+      <c r="B188" s="31"/>
     </row>
     <row r="189">
-      <c r="A189" s="29"/>
-      <c r="B189" s="29"/>
+      <c r="A189" s="31"/>
+      <c r="B189" s="31"/>
     </row>
     <row r="190">
-      <c r="A190" s="29"/>
-      <c r="B190" s="29"/>
+      <c r="A190" s="31"/>
+      <c r="B190" s="31"/>
     </row>
     <row r="191">
-      <c r="A191" s="29"/>
-      <c r="B191" s="29"/>
+      <c r="A191" s="31"/>
+      <c r="B191" s="31"/>
     </row>
     <row r="192">
-      <c r="A192" s="29"/>
-      <c r="B192" s="29"/>
+      <c r="A192" s="31"/>
+      <c r="B192" s="31"/>
     </row>
     <row r="193">
-      <c r="A193" s="29"/>
-      <c r="B193" s="29"/>
+      <c r="A193" s="31"/>
+      <c r="B193" s="31"/>
     </row>
     <row r="194">
-      <c r="A194" s="29"/>
-      <c r="B194" s="29"/>
+      <c r="A194" s="31"/>
+      <c r="B194" s="31"/>
     </row>
     <row r="195">
-      <c r="A195" s="29"/>
-      <c r="B195" s="29"/>
+      <c r="A195" s="31"/>
+      <c r="B195" s="31"/>
     </row>
     <row r="196">
-      <c r="A196" s="29"/>
-      <c r="B196" s="29"/>
+      <c r="A196" s="31"/>
+      <c r="B196" s="31"/>
     </row>
     <row r="197">
-      <c r="A197" s="29"/>
-      <c r="B197" s="29"/>
+      <c r="A197" s="31"/>
+      <c r="B197" s="31"/>
     </row>
     <row r="198">
-      <c r="A198" s="29"/>
-      <c r="B198" s="29"/>
+      <c r="A198" s="31"/>
+      <c r="B198" s="31"/>
     </row>
     <row r="199">
-      <c r="A199" s="29"/>
-      <c r="B199" s="29"/>
+      <c r="A199" s="31"/>
+      <c r="B199" s="31"/>
     </row>
     <row r="200">
-      <c r="A200" s="29"/>
-      <c r="B200" s="29"/>
+      <c r="A200" s="31"/>
+      <c r="B200" s="31"/>
     </row>
     <row r="201">
-      <c r="A201" s="29"/>
-      <c r="B201" s="29"/>
+      <c r="A201" s="31"/>
+      <c r="B201" s="31"/>
     </row>
     <row r="202">
-      <c r="A202" s="29"/>
-      <c r="B202" s="29"/>
+      <c r="A202" s="31"/>
+      <c r="B202" s="31"/>
     </row>
     <row r="203">
-      <c r="A203" s="29"/>
-      <c r="B203" s="29"/>
+      <c r="A203" s="31"/>
+      <c r="B203" s="31"/>
     </row>
     <row r="204">
-      <c r="A204" s="29"/>
-      <c r="B204" s="29"/>
+      <c r="A204" s="31"/>
+      <c r="B204" s="31"/>
     </row>
     <row r="205">
-      <c r="A205" s="29"/>
-      <c r="B205" s="29"/>
+      <c r="A205" s="31"/>
+      <c r="B205" s="31"/>
     </row>
     <row r="206">
-      <c r="A206" s="29"/>
-      <c r="B206" s="29"/>
+      <c r="A206" s="31"/>
+      <c r="B206" s="31"/>
     </row>
     <row r="207">
-      <c r="A207" s="29"/>
-      <c r="B207" s="29"/>
+      <c r="A207" s="31"/>
+      <c r="B207" s="31"/>
     </row>
     <row r="208">
-      <c r="A208" s="29"/>
-      <c r="B208" s="29"/>
+      <c r="A208" s="31"/>
+      <c r="B208" s="31"/>
     </row>
     <row r="209">
-      <c r="A209" s="29"/>
-      <c r="B209" s="29"/>
+      <c r="A209" s="31"/>
+      <c r="B209" s="31"/>
     </row>
     <row r="210">
-      <c r="A210" s="29"/>
-      <c r="B210" s="29"/>
+      <c r="A210" s="31"/>
+      <c r="B210" s="31"/>
     </row>
     <row r="211">
-      <c r="A211" s="29"/>
-      <c r="B211" s="29"/>
+      <c r="A211" s="31"/>
+      <c r="B211" s="31"/>
     </row>
     <row r="212">
-      <c r="A212" s="29"/>
-      <c r="B212" s="29"/>
+      <c r="A212" s="31"/>
+      <c r="B212" s="31"/>
     </row>
     <row r="213">
-      <c r="A213" s="29"/>
-      <c r="B213" s="29"/>
+      <c r="A213" s="31"/>
+      <c r="B213" s="31"/>
     </row>
     <row r="214">
-      <c r="A214" s="29"/>
-      <c r="B214" s="29"/>
+      <c r="A214" s="31"/>
+      <c r="B214" s="31"/>
     </row>
     <row r="215">
-      <c r="A215" s="29"/>
-      <c r="B215" s="29"/>
+      <c r="A215" s="31"/>
+      <c r="B215" s="31"/>
     </row>
     <row r="216">
-      <c r="A216" s="29"/>
-      <c r="B216" s="29"/>
+      <c r="A216" s="31"/>
+      <c r="B216" s="31"/>
     </row>
     <row r="217">
-      <c r="A217" s="29"/>
-      <c r="B217" s="29"/>
+      <c r="A217" s="31"/>
+      <c r="B217" s="31"/>
     </row>
     <row r="218">
-      <c r="A218" s="29"/>
-      <c r="B218" s="29"/>
+      <c r="A218" s="31"/>
+      <c r="B218" s="31"/>
     </row>
     <row r="219">
-      <c r="A219" s="29"/>
-      <c r="B219" s="29"/>
+      <c r="A219" s="31"/>
+      <c r="B219" s="31"/>
     </row>
     <row r="220">
-      <c r="A220" s="29"/>
-      <c r="B220" s="29"/>
+      <c r="A220" s="31"/>
+      <c r="B220" s="31"/>
     </row>
     <row r="221">
-      <c r="A221" s="29"/>
-      <c r="B221" s="29"/>
+      <c r="A221" s="31"/>
+      <c r="B221" s="31"/>
     </row>
     <row r="222">
-      <c r="A222" s="29"/>
-      <c r="B222" s="29"/>
+      <c r="A222" s="31"/>
+      <c r="B222" s="31"/>
     </row>
     <row r="223">
-      <c r="A223" s="29"/>
-      <c r="B223" s="29"/>
+      <c r="A223" s="31"/>
+      <c r="B223" s="31"/>
     </row>
     <row r="224">
-      <c r="A224" s="29"/>
-      <c r="B224" s="29"/>
+      <c r="A224" s="31"/>
+      <c r="B224" s="31"/>
     </row>
     <row r="225">
-      <c r="A225" s="29"/>
-      <c r="B225" s="29"/>
+      <c r="A225" s="31"/>
+      <c r="B225" s="31"/>
     </row>
     <row r="226">
-      <c r="A226" s="29"/>
-      <c r="B226" s="29"/>
+      <c r="A226" s="31"/>
+      <c r="B226" s="31"/>
     </row>
     <row r="227">
-      <c r="A227" s="29"/>
-      <c r="B227" s="29"/>
+      <c r="A227" s="31"/>
+      <c r="B227" s="31"/>
     </row>
     <row r="228">
-      <c r="A228" s="29"/>
-      <c r="B228" s="29"/>
+      <c r="A228" s="31"/>
+      <c r="B228" s="31"/>
     </row>
     <row r="229">
-      <c r="A229" s="29"/>
-      <c r="B229" s="29"/>
+      <c r="A229" s="31"/>
+      <c r="B229" s="31"/>
     </row>
     <row r="230">
-      <c r="A230" s="29"/>
-      <c r="B230" s="29"/>
+      <c r="A230" s="31"/>
+      <c r="B230" s="31"/>
     </row>
     <row r="231">
-      <c r="A231" s="29"/>
-      <c r="B231" s="29"/>
+      <c r="A231" s="31"/>
+      <c r="B231" s="31"/>
     </row>
     <row r="232">
-      <c r="A232" s="29"/>
-      <c r="B232" s="29"/>
+      <c r="A232" s="31"/>
+      <c r="B232" s="31"/>
     </row>
     <row r="233">
-      <c r="A233" s="29"/>
-      <c r="B233" s="29"/>
+      <c r="A233" s="31"/>
+      <c r="B233" s="31"/>
     </row>
     <row r="234">
-      <c r="A234" s="29"/>
-      <c r="B234" s="29"/>
+      <c r="A234" s="31"/>
+      <c r="B234" s="31"/>
     </row>
     <row r="235">
-      <c r="A235" s="29"/>
-      <c r="B235" s="29"/>
+      <c r="A235" s="31"/>
+      <c r="B235" s="31"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -7261,2034 +7278,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="30" width="6"/>
+    <col customWidth="1" min="12" max="12" style="32" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="30" width="6"/>
+    <col customWidth="1" min="23" max="23" style="32" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="30" width="6"/>
+    <col customWidth="1" min="30" max="30" style="32" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="32" t="s">
+    <row r="1" s="33" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="K1" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" s="40" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="P1" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="S1" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="T1" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="U1" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="V1" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="W1" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="X1" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y1" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z1" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA1" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB1" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC1" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="AD1" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE1" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF1" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG1" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F1" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="I1" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="L1" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="M1" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="N1" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="O1" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="P1" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q1" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="R1" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="S1" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="T1" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="U1" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="V1" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="W1" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="X1" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y1" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z1" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA1" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="AB1" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="AC1" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="AD1" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE1" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="AF1" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="AG1" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="AH1" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="AI1" s="44" t="s">
+      <c r="AH1" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="AJ1" s="44" t="s">
+      <c r="AI1" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="AK1" s="41" t="s">
+      <c r="AJ1" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="AL1" s="45"/>
-      <c r="AM1" s="45"/>
-      <c r="AN1" s="45"/>
-      <c r="AO1" s="45"/>
-      <c r="AP1" s="45"/>
-      <c r="AQ1" s="45"/>
-      <c r="AR1" s="45"/>
-      <c r="AS1" s="45"/>
-      <c r="AT1" s="45"/>
-      <c r="AU1" s="45"/>
+      <c r="AK1" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="47"/>
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="47"/>
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="47"/>
+      <c r="AT1" s="47"/>
+      <c r="AU1" s="47"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="54"/>
-      <c r="AB2" s="48"/>
-      <c r="AC2" s="48"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="54"/>
-      <c r="AG2" s="48"/>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="48"/>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="46"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="55"/>
-      <c r="X3" s="48"/>
-      <c r="Y3" s="48"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="54"/>
-      <c r="AB3" s="48"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="54"/>
-      <c r="AG3" s="48"/>
-      <c r="AH3" s="48"/>
-      <c r="AI3" s="48"/>
-      <c r="AJ3" s="48"/>
-      <c r="AK3" s="48"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="50"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="55"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="50"/>
+      <c r="Y3" s="50"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="50"/>
+      <c r="AC3" s="50"/>
+      <c r="AD3" s="54"/>
+      <c r="AE3" s="55"/>
+      <c r="AF3" s="56"/>
+      <c r="AG3" s="50"/>
+      <c r="AH3" s="50"/>
+      <c r="AI3" s="50"/>
+      <c r="AJ3" s="50"/>
+      <c r="AK3" s="50"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="53"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="48"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="52"/>
-      <c r="AE4" s="53"/>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="48"/>
-      <c r="AH4" s="48"/>
-      <c r="AI4" s="48"/>
-      <c r="AJ4" s="48"/>
-      <c r="AK4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="50"/>
+      <c r="U4" s="50"/>
+      <c r="V4" s="55"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="50"/>
+      <c r="Y4" s="50"/>
+      <c r="Z4" s="55"/>
+      <c r="AA4" s="56"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="50"/>
+      <c r="AD4" s="54"/>
+      <c r="AE4" s="55"/>
+      <c r="AF4" s="56"/>
+      <c r="AG4" s="50"/>
+      <c r="AH4" s="50"/>
+      <c r="AI4" s="50"/>
+      <c r="AJ4" s="50"/>
+      <c r="AK4" s="50"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="46"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="53"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="48"/>
-      <c r="Z5" s="53"/>
-      <c r="AA5" s="54"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="48"/>
-      <c r="AD5" s="52"/>
-      <c r="AE5" s="53"/>
-      <c r="AF5" s="54"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="48"/>
-      <c r="AJ5" s="48"/>
-      <c r="AK5" s="48"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="50"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="50"/>
+      <c r="U5" s="50"/>
+      <c r="V5" s="55"/>
+      <c r="W5" s="57"/>
+      <c r="X5" s="50"/>
+      <c r="Y5" s="50"/>
+      <c r="Z5" s="55"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="50"/>
+      <c r="AC5" s="50"/>
+      <c r="AD5" s="54"/>
+      <c r="AE5" s="55"/>
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="50"/>
+      <c r="AH5" s="50"/>
+      <c r="AI5" s="50"/>
+      <c r="AJ5" s="50"/>
+      <c r="AK5" s="50"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="46"/>
-      <c r="C6" s="47" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="48"/>
-      <c r="V6" s="53"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="48"/>
-      <c r="Y6" s="48"/>
-      <c r="Z6" s="53"/>
-      <c r="AA6" s="54"/>
-      <c r="AB6" s="48"/>
-      <c r="AC6" s="48"/>
-      <c r="AD6" s="52"/>
-      <c r="AE6" s="50"/>
-      <c r="AF6" s="51"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="62"/>
-      <c r="AK6" s="62"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="50"/>
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
+      <c r="V6" s="55"/>
+      <c r="W6" s="57"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="50"/>
+      <c r="Z6" s="55"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="50"/>
+      <c r="AC6" s="50"/>
+      <c r="AD6" s="54"/>
+      <c r="AE6" s="52"/>
+      <c r="AF6" s="53"/>
+      <c r="AG6" s="64"/>
+      <c r="AH6" s="64"/>
+      <c r="AI6" s="64"/>
+      <c r="AJ6" s="64"/>
+      <c r="AK6" s="64"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="46"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="55"/>
-      <c r="X7" s="48"/>
-      <c r="Y7" s="48"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="54"/>
-      <c r="AB7" s="48"/>
-      <c r="AC7" s="48"/>
-      <c r="AD7" s="52"/>
-      <c r="AE7" s="53"/>
-      <c r="AF7" s="54"/>
-      <c r="AG7" s="48"/>
-      <c r="AH7" s="48"/>
-      <c r="AI7" s="48"/>
-      <c r="AJ7" s="48"/>
-      <c r="AK7" s="48"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="55"/>
+      <c r="W7" s="57"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="50"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="56"/>
+      <c r="AB7" s="50"/>
+      <c r="AC7" s="50"/>
+      <c r="AD7" s="54"/>
+      <c r="AE7" s="55"/>
+      <c r="AF7" s="56"/>
+      <c r="AG7" s="50"/>
+      <c r="AH7" s="50"/>
+      <c r="AI7" s="50"/>
+      <c r="AJ7" s="50"/>
+      <c r="AK7" s="50"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="46"/>
-      <c r="C8" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="62"/>
-      <c r="Q8" s="62"/>
-      <c r="R8" s="62"/>
-      <c r="S8" s="62"/>
-      <c r="T8" s="62"/>
-      <c r="U8" s="62"/>
-      <c r="V8" s="50"/>
-      <c r="W8" s="55"/>
-      <c r="X8" s="62"/>
-      <c r="Y8" s="62"/>
-      <c r="Z8" s="50"/>
-      <c r="AA8" s="51"/>
-      <c r="AB8" s="62"/>
-      <c r="AC8" s="62"/>
-      <c r="AD8" s="52"/>
-      <c r="AE8" s="50"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="62"/>
-      <c r="AH8" s="62"/>
-      <c r="AI8" s="62"/>
-      <c r="AJ8" s="62"/>
-      <c r="AK8" s="62"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="52"/>
+      <c r="W8" s="57"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="52"/>
+      <c r="AA8" s="53"/>
+      <c r="AB8" s="64"/>
+      <c r="AC8" s="64"/>
+      <c r="AD8" s="54"/>
+      <c r="AE8" s="52"/>
+      <c r="AF8" s="53"/>
+      <c r="AG8" s="64"/>
+      <c r="AH8" s="64"/>
+      <c r="AI8" s="64"/>
+      <c r="AJ8" s="64"/>
+      <c r="AK8" s="64"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="46"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="61"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="61"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="59"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="61"/>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="59"/>
-      <c r="AA9" s="60"/>
-      <c r="AB9" s="48"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="61"/>
-      <c r="AE9" s="53"/>
-      <c r="AF9" s="54"/>
-      <c r="AG9" s="48"/>
-      <c r="AH9" s="48"/>
-      <c r="AI9" s="48"/>
-      <c r="AJ9" s="48"/>
-      <c r="AK9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="50"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="50"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="61"/>
+      <c r="W9" s="57"/>
+      <c r="X9" s="63"/>
+      <c r="Y9" s="50"/>
+      <c r="Z9" s="61"/>
+      <c r="AA9" s="62"/>
+      <c r="AB9" s="50"/>
+      <c r="AC9" s="50"/>
+      <c r="AD9" s="63"/>
+      <c r="AE9" s="55"/>
+      <c r="AF9" s="56"/>
+      <c r="AG9" s="50"/>
+      <c r="AH9" s="50"/>
+      <c r="AI9" s="50"/>
+      <c r="AJ9" s="50"/>
+      <c r="AK9" s="50"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="46"/>
-      <c r="C10" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="48"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="48"/>
-      <c r="U10" s="48"/>
-      <c r="V10" s="50"/>
-      <c r="W10" s="55"/>
-      <c r="X10" s="62"/>
-      <c r="Y10" s="62"/>
-      <c r="Z10" s="50"/>
-      <c r="AA10" s="54"/>
-      <c r="AB10" s="48"/>
-      <c r="AC10" s="48"/>
-      <c r="AD10" s="52"/>
-      <c r="AE10" s="53"/>
-      <c r="AF10" s="54"/>
-      <c r="AG10" s="48"/>
-      <c r="AH10" s="48"/>
-      <c r="AI10" s="48"/>
-      <c r="AJ10" s="48"/>
-      <c r="AK10" s="48"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="52"/>
+      <c r="W10" s="57"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="52"/>
+      <c r="AA10" s="56"/>
+      <c r="AB10" s="50"/>
+      <c r="AC10" s="50"/>
+      <c r="AD10" s="54"/>
+      <c r="AE10" s="55"/>
+      <c r="AF10" s="56"/>
+      <c r="AG10" s="50"/>
+      <c r="AH10" s="50"/>
+      <c r="AI10" s="50"/>
+      <c r="AJ10" s="50"/>
+      <c r="AK10" s="50"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="46"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="48"/>
-      <c r="Q11" s="48"/>
-      <c r="R11" s="48"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="48"/>
-      <c r="U11" s="48"/>
-      <c r="V11" s="53"/>
-      <c r="W11" s="55"/>
-      <c r="X11" s="48"/>
-      <c r="Y11" s="48"/>
-      <c r="Z11" s="53"/>
-      <c r="AA11" s="54"/>
-      <c r="AB11" s="48"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="64"/>
-      <c r="AE11" s="53"/>
-      <c r="AF11" s="54"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="48"/>
-      <c r="AI11" s="48"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="48"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="50"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="55"/>
+      <c r="W11" s="57"/>
+      <c r="X11" s="50"/>
+      <c r="Y11" s="50"/>
+      <c r="Z11" s="55"/>
+      <c r="AA11" s="56"/>
+      <c r="AB11" s="50"/>
+      <c r="AC11" s="50"/>
+      <c r="AD11" s="66"/>
+      <c r="AE11" s="55"/>
+      <c r="AF11" s="56"/>
+      <c r="AG11" s="50"/>
+      <c r="AH11" s="50"/>
+      <c r="AI11" s="50"/>
+      <c r="AJ11" s="50"/>
+      <c r="AK11" s="50"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="46"/>
-      <c r="C12" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="48"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="48"/>
-      <c r="U12" s="48"/>
-      <c r="V12" s="53"/>
-      <c r="W12" s="55"/>
-      <c r="X12" s="48"/>
-      <c r="Y12" s="48"/>
-      <c r="Z12" s="53"/>
-      <c r="AA12" s="54"/>
-      <c r="AB12" s="48"/>
-      <c r="AC12" s="48"/>
-      <c r="AD12" s="52"/>
-      <c r="AE12" s="53"/>
-      <c r="AF12" s="51"/>
-      <c r="AG12" s="62"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="62"/>
-      <c r="AJ12" s="62"/>
-      <c r="AK12" s="62"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="55"/>
+      <c r="W12" s="57"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="55"/>
+      <c r="AA12" s="56"/>
+      <c r="AB12" s="50"/>
+      <c r="AC12" s="50"/>
+      <c r="AD12" s="54"/>
+      <c r="AE12" s="55"/>
+      <c r="AF12" s="53"/>
+      <c r="AG12" s="64"/>
+      <c r="AH12" s="64"/>
+      <c r="AI12" s="64"/>
+      <c r="AJ12" s="64"/>
+      <c r="AK12" s="64"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="46"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="48"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="55"/>
-      <c r="X13" s="48"/>
-      <c r="Y13" s="48"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="54"/>
-      <c r="AB13" s="48"/>
-      <c r="AC13" s="48"/>
-      <c r="AD13" s="52"/>
-      <c r="AE13" s="53"/>
-      <c r="AF13" s="54"/>
-      <c r="AG13" s="48"/>
-      <c r="AH13" s="48"/>
-      <c r="AI13" s="48"/>
-      <c r="AJ13" s="48"/>
-      <c r="AK13" s="48"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="50"/>
+      <c r="V13" s="55"/>
+      <c r="W13" s="57"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="55"/>
+      <c r="AA13" s="56"/>
+      <c r="AB13" s="50"/>
+      <c r="AC13" s="50"/>
+      <c r="AD13" s="54"/>
+      <c r="AE13" s="55"/>
+      <c r="AF13" s="56"/>
+      <c r="AG13" s="50"/>
+      <c r="AH13" s="50"/>
+      <c r="AI13" s="50"/>
+      <c r="AJ13" s="50"/>
+      <c r="AK13" s="50"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="65" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="66" t="s">
+      <c r="B14" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="68"/>
-      <c r="Q14" s="68"/>
-      <c r="R14" s="68"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="68"/>
-      <c r="U14" s="68"/>
-      <c r="V14" s="69"/>
-      <c r="W14" s="55"/>
-      <c r="X14" s="68"/>
-      <c r="Y14" s="68"/>
-      <c r="Z14" s="69"/>
-      <c r="AA14" s="67"/>
-      <c r="AB14" s="68"/>
-      <c r="AC14" s="68"/>
-      <c r="AD14" s="52"/>
-      <c r="AE14" s="69"/>
-      <c r="AF14" s="67"/>
-      <c r="AG14" s="68"/>
-      <c r="AH14" s="68"/>
-      <c r="AI14" s="68"/>
-      <c r="AJ14" s="68"/>
-      <c r="AK14" s="68"/>
+      <c r="C14" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="70"/>
+      <c r="N14" s="71"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="70"/>
+      <c r="Q14" s="70"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="70"/>
+      <c r="T14" s="70"/>
+      <c r="U14" s="70"/>
+      <c r="V14" s="71"/>
+      <c r="W14" s="57"/>
+      <c r="X14" s="70"/>
+      <c r="Y14" s="70"/>
+      <c r="Z14" s="71"/>
+      <c r="AA14" s="69"/>
+      <c r="AB14" s="70"/>
+      <c r="AC14" s="70"/>
+      <c r="AD14" s="54"/>
+      <c r="AE14" s="71"/>
+      <c r="AF14" s="69"/>
+      <c r="AG14" s="70"/>
+      <c r="AH14" s="70"/>
+      <c r="AI14" s="70"/>
+      <c r="AJ14" s="70"/>
+      <c r="AK14" s="70"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="68"/>
-      <c r="Q15" s="68"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="69"/>
-      <c r="W15" s="55"/>
-      <c r="X15" s="68"/>
-      <c r="Y15" s="68"/>
-      <c r="Z15" s="69"/>
-      <c r="AA15" s="67"/>
-      <c r="AB15" s="68"/>
-      <c r="AC15" s="68"/>
-      <c r="AD15" s="52"/>
-      <c r="AE15" s="69"/>
-      <c r="AF15" s="67"/>
-      <c r="AG15" s="68"/>
-      <c r="AH15" s="68"/>
-      <c r="AI15" s="68"/>
-      <c r="AJ15" s="68"/>
-      <c r="AK15" s="68"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
+      <c r="S15" s="70"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="70"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="57"/>
+      <c r="X15" s="70"/>
+      <c r="Y15" s="70"/>
+      <c r="Z15" s="71"/>
+      <c r="AA15" s="69"/>
+      <c r="AB15" s="70"/>
+      <c r="AC15" s="70"/>
+      <c r="AD15" s="54"/>
+      <c r="AE15" s="71"/>
+      <c r="AF15" s="69"/>
+      <c r="AG15" s="70"/>
+      <c r="AH15" s="70"/>
+      <c r="AI15" s="70"/>
+      <c r="AJ15" s="70"/>
+      <c r="AK15" s="70"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="65"/>
-      <c r="C16" s="66" t="s">
-        <v>127</v>
-      </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="68"/>
-      <c r="Q16" s="68"/>
-      <c r="R16" s="68"/>
-      <c r="S16" s="68"/>
-      <c r="T16" s="68"/>
-      <c r="U16" s="68"/>
-      <c r="V16" s="69"/>
-      <c r="W16" s="55"/>
-      <c r="X16" s="68"/>
-      <c r="Y16" s="68"/>
-      <c r="Z16" s="69"/>
-      <c r="AA16" s="67"/>
-      <c r="AB16" s="68"/>
-      <c r="AC16" s="68"/>
-      <c r="AD16" s="52"/>
-      <c r="AE16" s="69"/>
-      <c r="AF16" s="67"/>
-      <c r="AG16" s="68"/>
-      <c r="AH16" s="68"/>
-      <c r="AI16" s="68"/>
-      <c r="AJ16" s="68"/>
-      <c r="AK16" s="68"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="68" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="69"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="70"/>
+      <c r="S16" s="70"/>
+      <c r="T16" s="70"/>
+      <c r="U16" s="70"/>
+      <c r="V16" s="71"/>
+      <c r="W16" s="57"/>
+      <c r="X16" s="70"/>
+      <c r="Y16" s="70"/>
+      <c r="Z16" s="71"/>
+      <c r="AA16" s="69"/>
+      <c r="AB16" s="70"/>
+      <c r="AC16" s="70"/>
+      <c r="AD16" s="54"/>
+      <c r="AE16" s="71"/>
+      <c r="AF16" s="69"/>
+      <c r="AG16" s="70"/>
+      <c r="AH16" s="70"/>
+      <c r="AI16" s="70"/>
+      <c r="AJ16" s="70"/>
+      <c r="AK16" s="70"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="67"/>
-      <c r="P17" s="68"/>
-      <c r="Q17" s="68"/>
-      <c r="R17" s="68"/>
-      <c r="S17" s="68"/>
-      <c r="T17" s="68"/>
-      <c r="U17" s="68"/>
-      <c r="V17" s="69"/>
-      <c r="W17" s="55"/>
-      <c r="X17" s="68"/>
-      <c r="Y17" s="68"/>
-      <c r="Z17" s="69"/>
-      <c r="AA17" s="67"/>
-      <c r="AB17" s="68"/>
-      <c r="AC17" s="68"/>
-      <c r="AD17" s="52"/>
-      <c r="AE17" s="69"/>
-      <c r="AF17" s="67"/>
-      <c r="AG17" s="68"/>
-      <c r="AH17" s="68"/>
-      <c r="AI17" s="68"/>
-      <c r="AJ17" s="68"/>
-      <c r="AK17" s="68"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
+      <c r="S17" s="70"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="71"/>
+      <c r="W17" s="57"/>
+      <c r="X17" s="70"/>
+      <c r="Y17" s="70"/>
+      <c r="Z17" s="71"/>
+      <c r="AA17" s="69"/>
+      <c r="AB17" s="70"/>
+      <c r="AC17" s="70"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="71"/>
+      <c r="AF17" s="69"/>
+      <c r="AG17" s="70"/>
+      <c r="AH17" s="70"/>
+      <c r="AI17" s="70"/>
+      <c r="AJ17" s="70"/>
+      <c r="AK17" s="70"/>
       <c r="AN17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="65"/>
-      <c r="C18" s="66" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="68"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="68"/>
-      <c r="Q18" s="68"/>
-      <c r="R18" s="68"/>
-      <c r="S18" s="68"/>
-      <c r="T18" s="68"/>
-      <c r="U18" s="68"/>
-      <c r="V18" s="69"/>
-      <c r="W18" s="55"/>
-      <c r="X18" s="68"/>
-      <c r="Y18" s="68"/>
-      <c r="Z18" s="69"/>
-      <c r="AA18" s="67"/>
-      <c r="AB18" s="68"/>
-      <c r="AC18" s="68"/>
-      <c r="AD18" s="52"/>
-      <c r="AE18" s="69"/>
-      <c r="AF18" s="67"/>
-      <c r="AG18" s="68"/>
-      <c r="AH18" s="68"/>
-      <c r="AI18" s="68"/>
-      <c r="AJ18" s="68"/>
-      <c r="AK18" s="68"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="71"/>
+      <c r="O18" s="69"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="70"/>
+      <c r="R18" s="70"/>
+      <c r="S18" s="70"/>
+      <c r="T18" s="70"/>
+      <c r="U18" s="70"/>
+      <c r="V18" s="71"/>
+      <c r="W18" s="57"/>
+      <c r="X18" s="70"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="71"/>
+      <c r="AA18" s="69"/>
+      <c r="AB18" s="70"/>
+      <c r="AC18" s="70"/>
+      <c r="AD18" s="54"/>
+      <c r="AE18" s="71"/>
+      <c r="AF18" s="69"/>
+      <c r="AG18" s="70"/>
+      <c r="AH18" s="70"/>
+      <c r="AI18" s="70"/>
+      <c r="AJ18" s="70"/>
+      <c r="AK18" s="70"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="65"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="67"/>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
-      <c r="U19" s="68"/>
-      <c r="V19" s="69"/>
-      <c r="W19" s="55"/>
-      <c r="X19" s="68"/>
-      <c r="Y19" s="68"/>
-      <c r="Z19" s="69"/>
-      <c r="AA19" s="67"/>
-      <c r="AB19" s="68"/>
-      <c r="AC19" s="68"/>
-      <c r="AD19" s="52"/>
-      <c r="AE19" s="69"/>
-      <c r="AF19" s="67"/>
-      <c r="AG19" s="68"/>
-      <c r="AH19" s="68"/>
-      <c r="AI19" s="68"/>
-      <c r="AJ19" s="68"/>
-      <c r="AK19" s="68"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="69"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="70"/>
+      <c r="R19" s="70"/>
+      <c r="S19" s="70"/>
+      <c r="T19" s="70"/>
+      <c r="U19" s="70"/>
+      <c r="V19" s="71"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="70"/>
+      <c r="Y19" s="70"/>
+      <c r="Z19" s="71"/>
+      <c r="AA19" s="69"/>
+      <c r="AB19" s="70"/>
+      <c r="AC19" s="70"/>
+      <c r="AD19" s="54"/>
+      <c r="AE19" s="71"/>
+      <c r="AF19" s="69"/>
+      <c r="AG19" s="70"/>
+      <c r="AH19" s="70"/>
+      <c r="AI19" s="70"/>
+      <c r="AJ19" s="70"/>
+      <c r="AK19" s="70"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="65"/>
-      <c r="C20" s="66" t="s">
-        <v>130</v>
-      </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="68"/>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="68"/>
-      <c r="T20" s="68"/>
-      <c r="U20" s="68"/>
-      <c r="V20" s="69"/>
-      <c r="W20" s="55"/>
-      <c r="X20" s="68"/>
-      <c r="Y20" s="68"/>
-      <c r="Z20" s="69"/>
-      <c r="AA20" s="67"/>
-      <c r="AB20" s="68"/>
-      <c r="AC20" s="68"/>
-      <c r="AD20" s="52"/>
-      <c r="AE20" s="69"/>
-      <c r="AF20" s="67"/>
-      <c r="AG20" s="68"/>
-      <c r="AH20" s="68"/>
-      <c r="AI20" s="68"/>
-      <c r="AJ20" s="68"/>
-      <c r="AK20" s="68"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="71"/>
+      <c r="O20" s="69"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="70"/>
+      <c r="T20" s="70"/>
+      <c r="U20" s="70"/>
+      <c r="V20" s="71"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="70"/>
+      <c r="Y20" s="70"/>
+      <c r="Z20" s="71"/>
+      <c r="AA20" s="69"/>
+      <c r="AB20" s="70"/>
+      <c r="AC20" s="70"/>
+      <c r="AD20" s="54"/>
+      <c r="AE20" s="71"/>
+      <c r="AF20" s="69"/>
+      <c r="AG20" s="70"/>
+      <c r="AH20" s="70"/>
+      <c r="AI20" s="70"/>
+      <c r="AJ20" s="70"/>
+      <c r="AK20" s="70"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="68"/>
-      <c r="S21" s="68"/>
-      <c r="T21" s="68"/>
-      <c r="U21" s="68"/>
-      <c r="V21" s="69"/>
-      <c r="W21" s="55"/>
-      <c r="X21" s="68"/>
-      <c r="Y21" s="68"/>
-      <c r="Z21" s="69"/>
-      <c r="AA21" s="67"/>
-      <c r="AB21" s="68"/>
-      <c r="AC21" s="68"/>
-      <c r="AD21" s="52"/>
-      <c r="AE21" s="69"/>
-      <c r="AF21" s="67"/>
-      <c r="AG21" s="68"/>
-      <c r="AH21" s="68"/>
-      <c r="AI21" s="68"/>
-      <c r="AJ21" s="68"/>
-      <c r="AK21" s="68"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="69"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="70"/>
+      <c r="R21" s="70"/>
+      <c r="S21" s="70"/>
+      <c r="T21" s="70"/>
+      <c r="U21" s="70"/>
+      <c r="V21" s="71"/>
+      <c r="W21" s="57"/>
+      <c r="X21" s="70"/>
+      <c r="Y21" s="70"/>
+      <c r="Z21" s="71"/>
+      <c r="AA21" s="69"/>
+      <c r="AB21" s="70"/>
+      <c r="AC21" s="70"/>
+      <c r="AD21" s="54"/>
+      <c r="AE21" s="71"/>
+      <c r="AF21" s="69"/>
+      <c r="AG21" s="70"/>
+      <c r="AH21" s="70"/>
+      <c r="AI21" s="70"/>
+      <c r="AJ21" s="70"/>
+      <c r="AK21" s="70"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="65"/>
-      <c r="C22" s="66" t="s">
-        <v>131</v>
-      </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="68"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="67"/>
-      <c r="P22" s="68"/>
-      <c r="Q22" s="68"/>
-      <c r="R22" s="68"/>
-      <c r="S22" s="68"/>
-      <c r="T22" s="68"/>
-      <c r="U22" s="68"/>
-      <c r="V22" s="69"/>
-      <c r="W22" s="55"/>
-      <c r="X22" s="68"/>
-      <c r="Y22" s="68"/>
-      <c r="Z22" s="69"/>
-      <c r="AA22" s="67"/>
-      <c r="AB22" s="68"/>
-      <c r="AC22" s="68"/>
-      <c r="AD22" s="52"/>
-      <c r="AE22" s="69"/>
-      <c r="AF22" s="67"/>
-      <c r="AG22" s="68"/>
-      <c r="AH22" s="68"/>
-      <c r="AI22" s="68"/>
-      <c r="AJ22" s="68"/>
-      <c r="AK22" s="68"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="71"/>
+      <c r="O22" s="69"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="70"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="70"/>
+      <c r="T22" s="70"/>
+      <c r="U22" s="70"/>
+      <c r="V22" s="71"/>
+      <c r="W22" s="57"/>
+      <c r="X22" s="70"/>
+      <c r="Y22" s="70"/>
+      <c r="Z22" s="71"/>
+      <c r="AA22" s="69"/>
+      <c r="AB22" s="70"/>
+      <c r="AC22" s="70"/>
+      <c r="AD22" s="54"/>
+      <c r="AE22" s="71"/>
+      <c r="AF22" s="69"/>
+      <c r="AG22" s="70"/>
+      <c r="AH22" s="70"/>
+      <c r="AI22" s="70"/>
+      <c r="AJ22" s="70"/>
+      <c r="AK22" s="70"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="65"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="68"/>
-      <c r="Q23" s="68"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="68"/>
-      <c r="T23" s="68"/>
-      <c r="U23" s="68"/>
-      <c r="V23" s="69"/>
-      <c r="W23" s="55"/>
-      <c r="X23" s="68"/>
-      <c r="Y23" s="68"/>
-      <c r="Z23" s="69"/>
-      <c r="AA23" s="67"/>
-      <c r="AB23" s="68"/>
-      <c r="AC23" s="68"/>
-      <c r="AD23" s="52"/>
-      <c r="AE23" s="69"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="68"/>
-      <c r="AH23" s="68"/>
-      <c r="AI23" s="68"/>
-      <c r="AJ23" s="68"/>
-      <c r="AK23" s="68"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="69"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
+      <c r="S23" s="70"/>
+      <c r="T23" s="70"/>
+      <c r="U23" s="70"/>
+      <c r="V23" s="71"/>
+      <c r="W23" s="57"/>
+      <c r="X23" s="70"/>
+      <c r="Y23" s="70"/>
+      <c r="Z23" s="71"/>
+      <c r="AA23" s="69"/>
+      <c r="AB23" s="70"/>
+      <c r="AC23" s="70"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="71"/>
+      <c r="AF23" s="69"/>
+      <c r="AG23" s="70"/>
+      <c r="AH23" s="70"/>
+      <c r="AI23" s="70"/>
+      <c r="AJ23" s="70"/>
+      <c r="AK23" s="70"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="65"/>
-      <c r="C24" s="66" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="67"/>
-      <c r="P24" s="68"/>
-      <c r="Q24" s="68"/>
-      <c r="R24" s="68"/>
-      <c r="S24" s="68"/>
-      <c r="T24" s="68"/>
-      <c r="U24" s="68"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="55"/>
-      <c r="X24" s="68"/>
-      <c r="Y24" s="68"/>
-      <c r="Z24" s="69"/>
-      <c r="AA24" s="67"/>
-      <c r="AB24" s="68"/>
-      <c r="AC24" s="68"/>
-      <c r="AD24" s="52"/>
-      <c r="AE24" s="69"/>
-      <c r="AF24" s="67"/>
-      <c r="AG24" s="68"/>
-      <c r="AH24" s="68"/>
-      <c r="AI24" s="68"/>
-      <c r="AJ24" s="68"/>
-      <c r="AK24" s="68"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="68" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="71"/>
+      <c r="O24" s="69"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="70"/>
+      <c r="R24" s="70"/>
+      <c r="S24" s="70"/>
+      <c r="T24" s="70"/>
+      <c r="U24" s="70"/>
+      <c r="V24" s="71"/>
+      <c r="W24" s="57"/>
+      <c r="X24" s="70"/>
+      <c r="Y24" s="70"/>
+      <c r="Z24" s="71"/>
+      <c r="AA24" s="69"/>
+      <c r="AB24" s="70"/>
+      <c r="AC24" s="70"/>
+      <c r="AD24" s="54"/>
+      <c r="AE24" s="71"/>
+      <c r="AF24" s="69"/>
+      <c r="AG24" s="70"/>
+      <c r="AH24" s="70"/>
+      <c r="AI24" s="70"/>
+      <c r="AJ24" s="70"/>
+      <c r="AK24" s="70"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="65"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="52"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="68"/>
-      <c r="R25" s="68"/>
-      <c r="S25" s="68"/>
-      <c r="T25" s="68"/>
-      <c r="U25" s="68"/>
-      <c r="V25" s="69"/>
-      <c r="W25" s="55"/>
-      <c r="X25" s="68"/>
-      <c r="Y25" s="68"/>
-      <c r="Z25" s="69"/>
-      <c r="AA25" s="67"/>
-      <c r="AB25" s="68"/>
-      <c r="AC25" s="68"/>
-      <c r="AD25" s="52"/>
-      <c r="AE25" s="69"/>
-      <c r="AF25" s="67"/>
-      <c r="AG25" s="68"/>
-      <c r="AH25" s="68"/>
-      <c r="AI25" s="68"/>
-      <c r="AJ25" s="68"/>
-      <c r="AK25" s="68"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="69"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="70"/>
+      <c r="R25" s="70"/>
+      <c r="S25" s="70"/>
+      <c r="T25" s="70"/>
+      <c r="U25" s="70"/>
+      <c r="V25" s="71"/>
+      <c r="W25" s="57"/>
+      <c r="X25" s="70"/>
+      <c r="Y25" s="70"/>
+      <c r="Z25" s="71"/>
+      <c r="AA25" s="69"/>
+      <c r="AB25" s="70"/>
+      <c r="AC25" s="70"/>
+      <c r="AD25" s="54"/>
+      <c r="AE25" s="71"/>
+      <c r="AF25" s="69"/>
+      <c r="AG25" s="70"/>
+      <c r="AH25" s="70"/>
+      <c r="AI25" s="70"/>
+      <c r="AJ25" s="70"/>
+      <c r="AK25" s="70"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="47" t="s">
+      <c r="B26" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="48"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="48"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="53"/>
-      <c r="W26" s="55"/>
-      <c r="X26" s="48"/>
-      <c r="Y26" s="48"/>
-      <c r="Z26" s="53"/>
-      <c r="AA26" s="54"/>
-      <c r="AB26" s="48"/>
-      <c r="AC26" s="48"/>
-      <c r="AD26" s="52"/>
-      <c r="AE26" s="53"/>
-      <c r="AF26" s="54"/>
-      <c r="AG26" s="48"/>
-      <c r="AH26" s="48"/>
-      <c r="AI26" s="48"/>
-      <c r="AJ26" s="48"/>
-      <c r="AK26" s="48"/>
+      <c r="C26" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="55"/>
+      <c r="W26" s="57"/>
+      <c r="X26" s="50"/>
+      <c r="Y26" s="50"/>
+      <c r="Z26" s="55"/>
+      <c r="AA26" s="56"/>
+      <c r="AB26" s="50"/>
+      <c r="AC26" s="50"/>
+      <c r="AD26" s="54"/>
+      <c r="AE26" s="55"/>
+      <c r="AF26" s="56"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="46"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="48"/>
-      <c r="S27" s="48"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="53"/>
-      <c r="W27" s="55"/>
-      <c r="X27" s="48"/>
-      <c r="Y27" s="48"/>
-      <c r="Z27" s="53"/>
-      <c r="AA27" s="54"/>
-      <c r="AB27" s="48"/>
-      <c r="AC27" s="48"/>
-      <c r="AD27" s="52"/>
-      <c r="AE27" s="53"/>
-      <c r="AF27" s="54"/>
-      <c r="AG27" s="48"/>
-      <c r="AH27" s="48"/>
-      <c r="AI27" s="48"/>
-      <c r="AJ27" s="48"/>
-      <c r="AK27" s="48"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="50"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="55"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="50"/>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="55"/>
+      <c r="AA27" s="56"/>
+      <c r="AB27" s="50"/>
+      <c r="AC27" s="50"/>
+      <c r="AD27" s="54"/>
+      <c r="AE27" s="55"/>
+      <c r="AF27" s="56"/>
+      <c r="AG27" s="50"/>
+      <c r="AH27" s="50"/>
+      <c r="AI27" s="50"/>
+      <c r="AJ27" s="50"/>
+      <c r="AK27" s="50"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="46"/>
-      <c r="C28" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="52"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="48"/>
-      <c r="U28" s="48"/>
-      <c r="V28" s="53"/>
-      <c r="W28" s="55"/>
-      <c r="X28" s="48"/>
-      <c r="Y28" s="48"/>
-      <c r="Z28" s="53"/>
-      <c r="AA28" s="54"/>
-      <c r="AB28" s="48"/>
-      <c r="AC28" s="48"/>
-      <c r="AD28" s="52"/>
-      <c r="AE28" s="53"/>
-      <c r="AF28" s="54"/>
-      <c r="AG28" s="48"/>
-      <c r="AH28" s="48"/>
-      <c r="AI28" s="48"/>
-      <c r="AJ28" s="48"/>
-      <c r="AK28" s="48"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="56"/>
+      <c r="P28" s="50"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="50"/>
+      <c r="V28" s="55"/>
+      <c r="W28" s="57"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="55"/>
+      <c r="AA28" s="56"/>
+      <c r="AB28" s="50"/>
+      <c r="AC28" s="50"/>
+      <c r="AD28" s="54"/>
+      <c r="AE28" s="55"/>
+      <c r="AF28" s="56"/>
+      <c r="AG28" s="50"/>
+      <c r="AH28" s="50"/>
+      <c r="AI28" s="50"/>
+      <c r="AJ28" s="50"/>
+      <c r="AK28" s="50"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="46"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="48"/>
-      <c r="V29" s="53"/>
-      <c r="W29" s="55"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="53"/>
-      <c r="AA29" s="54"/>
-      <c r="AB29" s="48"/>
-      <c r="AC29" s="48"/>
-      <c r="AD29" s="52"/>
-      <c r="AE29" s="53"/>
-      <c r="AF29" s="54"/>
-      <c r="AG29" s="48"/>
-      <c r="AH29" s="48"/>
-      <c r="AI29" s="48"/>
-      <c r="AJ29" s="48"/>
-      <c r="AK29" s="48"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="50"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="50"/>
+      <c r="V29" s="55"/>
+      <c r="W29" s="57"/>
+      <c r="X29" s="50"/>
+      <c r="Y29" s="50"/>
+      <c r="Z29" s="55"/>
+      <c r="AA29" s="56"/>
+      <c r="AB29" s="50"/>
+      <c r="AC29" s="50"/>
+      <c r="AD29" s="54"/>
+      <c r="AE29" s="55"/>
+      <c r="AF29" s="56"/>
+      <c r="AG29" s="50"/>
+      <c r="AH29" s="50"/>
+      <c r="AI29" s="50"/>
+      <c r="AJ29" s="50"/>
+      <c r="AK29" s="50"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="46"/>
-      <c r="C30" s="47" t="s">
-        <v>136</v>
-      </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="62"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="54"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="48"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="48"/>
-      <c r="V30" s="53"/>
-      <c r="W30" s="55"/>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="53"/>
-      <c r="AA30" s="54"/>
-      <c r="AB30" s="48"/>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="52"/>
-      <c r="AE30" s="53"/>
-      <c r="AF30" s="54"/>
-      <c r="AG30" s="48"/>
-      <c r="AH30" s="48"/>
-      <c r="AI30" s="48"/>
-      <c r="AJ30" s="48"/>
-      <c r="AK30" s="48"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50"/>
+      <c r="S30" s="50"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="50"/>
+      <c r="V30" s="55"/>
+      <c r="W30" s="57"/>
+      <c r="X30" s="50"/>
+      <c r="Y30" s="50"/>
+      <c r="Z30" s="55"/>
+      <c r="AA30" s="56"/>
+      <c r="AB30" s="50"/>
+      <c r="AC30" s="50"/>
+      <c r="AD30" s="54"/>
+      <c r="AE30" s="55"/>
+      <c r="AF30" s="56"/>
+      <c r="AG30" s="50"/>
+      <c r="AH30" s="50"/>
+      <c r="AI30" s="50"/>
+      <c r="AJ30" s="50"/>
+      <c r="AK30" s="50"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="46"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="63"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="48"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="48"/>
-      <c r="U31" s="48"/>
-      <c r="V31" s="53"/>
-      <c r="W31" s="55"/>
-      <c r="X31" s="48"/>
-      <c r="Y31" s="48"/>
-      <c r="Z31" s="53"/>
-      <c r="AA31" s="54"/>
-      <c r="AB31" s="48"/>
-      <c r="AC31" s="48"/>
-      <c r="AD31" s="52"/>
-      <c r="AE31" s="53"/>
-      <c r="AF31" s="54"/>
-      <c r="AG31" s="48"/>
-      <c r="AH31" s="48"/>
-      <c r="AI31" s="48"/>
-      <c r="AJ31" s="48"/>
-      <c r="AK31" s="48"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="75"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="56"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="50"/>
+      <c r="V31" s="55"/>
+      <c r="W31" s="57"/>
+      <c r="X31" s="50"/>
+      <c r="Y31" s="50"/>
+      <c r="Z31" s="55"/>
+      <c r="AA31" s="56"/>
+      <c r="AB31" s="50"/>
+      <c r="AC31" s="50"/>
+      <c r="AD31" s="54"/>
+      <c r="AE31" s="55"/>
+      <c r="AF31" s="56"/>
+      <c r="AG31" s="50"/>
+      <c r="AH31" s="50"/>
+      <c r="AI31" s="50"/>
+      <c r="AJ31" s="50"/>
+      <c r="AK31" s="50"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="46"/>
-      <c r="C32" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="62"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="48"/>
-      <c r="R32" s="48"/>
-      <c r="S32" s="48"/>
-      <c r="T32" s="48"/>
-      <c r="U32" s="48"/>
-      <c r="V32" s="53"/>
-      <c r="W32" s="55"/>
-      <c r="X32" s="48"/>
-      <c r="Y32" s="48"/>
-      <c r="Z32" s="53"/>
-      <c r="AA32" s="54"/>
-      <c r="AB32" s="48"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="52"/>
-      <c r="AE32" s="53"/>
-      <c r="AF32" s="54"/>
-      <c r="AG32" s="48"/>
-      <c r="AH32" s="48"/>
-      <c r="AI32" s="48"/>
-      <c r="AJ32" s="48"/>
-      <c r="AK32" s="48"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="64"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="50"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="50"/>
+      <c r="S32" s="50"/>
+      <c r="T32" s="50"/>
+      <c r="U32" s="50"/>
+      <c r="V32" s="55"/>
+      <c r="W32" s="57"/>
+      <c r="X32" s="50"/>
+      <c r="Y32" s="50"/>
+      <c r="Z32" s="55"/>
+      <c r="AA32" s="56"/>
+      <c r="AB32" s="50"/>
+      <c r="AC32" s="50"/>
+      <c r="AD32" s="54"/>
+      <c r="AE32" s="55"/>
+      <c r="AF32" s="56"/>
+      <c r="AG32" s="50"/>
+      <c r="AH32" s="50"/>
+      <c r="AI32" s="50"/>
+      <c r="AJ32" s="50"/>
+      <c r="AK32" s="50"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="46"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="52"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="59"/>
-      <c r="O33" s="54"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="48"/>
-      <c r="R33" s="48"/>
-      <c r="S33" s="48"/>
-      <c r="T33" s="48"/>
-      <c r="U33" s="48"/>
-      <c r="V33" s="53"/>
-      <c r="W33" s="55"/>
-      <c r="X33" s="48"/>
-      <c r="Y33" s="48"/>
-      <c r="Z33" s="53"/>
-      <c r="AA33" s="54"/>
-      <c r="AB33" s="48"/>
-      <c r="AC33" s="48"/>
-      <c r="AD33" s="52"/>
-      <c r="AE33" s="53"/>
-      <c r="AF33" s="54"/>
-      <c r="AG33" s="48"/>
-      <c r="AH33" s="48"/>
-      <c r="AI33" s="48"/>
-      <c r="AJ33" s="48"/>
-      <c r="AK33" s="48"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="61"/>
+      <c r="O33" s="56"/>
+      <c r="P33" s="50"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50"/>
+      <c r="S33" s="50"/>
+      <c r="T33" s="50"/>
+      <c r="U33" s="50"/>
+      <c r="V33" s="55"/>
+      <c r="W33" s="57"/>
+      <c r="X33" s="50"/>
+      <c r="Y33" s="50"/>
+      <c r="Z33" s="55"/>
+      <c r="AA33" s="56"/>
+      <c r="AB33" s="50"/>
+      <c r="AC33" s="50"/>
+      <c r="AD33" s="54"/>
+      <c r="AE33" s="55"/>
+      <c r="AF33" s="56"/>
+      <c r="AG33" s="50"/>
+      <c r="AH33" s="50"/>
+      <c r="AI33" s="50"/>
+      <c r="AJ33" s="50"/>
+      <c r="AK33" s="50"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="65" t="s">
-        <v>138</v>
-      </c>
-      <c r="C34" s="74" t="s">
+      <c r="B34" s="67" t="s">
         <v>139</v>
       </c>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="67"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="68"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="62"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="51"/>
-      <c r="P34" s="62"/>
-      <c r="Q34" s="62"/>
-      <c r="R34" s="62"/>
-      <c r="S34" s="68"/>
-      <c r="T34" s="68"/>
-      <c r="U34" s="68"/>
-      <c r="V34" s="69"/>
-      <c r="W34" s="55"/>
-      <c r="X34" s="68"/>
-      <c r="Y34" s="68"/>
-      <c r="Z34" s="69"/>
-      <c r="AA34" s="67"/>
-      <c r="AB34" s="68"/>
-      <c r="AC34" s="68"/>
-      <c r="AD34" s="52"/>
-      <c r="AE34" s="69"/>
-      <c r="AF34" s="67"/>
-      <c r="AG34" s="68"/>
-      <c r="AH34" s="68"/>
-      <c r="AI34" s="68"/>
-      <c r="AJ34" s="68"/>
-      <c r="AK34" s="68"/>
+      <c r="C34" s="76" t="s">
+        <v>140</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="70"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="64"/>
+      <c r="N34" s="52"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="64"/>
+      <c r="S34" s="70"/>
+      <c r="T34" s="70"/>
+      <c r="U34" s="70"/>
+      <c r="V34" s="71"/>
+      <c r="W34" s="57"/>
+      <c r="X34" s="70"/>
+      <c r="Y34" s="70"/>
+      <c r="Z34" s="71"/>
+      <c r="AA34" s="69"/>
+      <c r="AB34" s="70"/>
+      <c r="AC34" s="70"/>
+      <c r="AD34" s="54"/>
+      <c r="AE34" s="71"/>
+      <c r="AF34" s="69"/>
+      <c r="AG34" s="70"/>
+      <c r="AH34" s="70"/>
+      <c r="AI34" s="70"/>
+      <c r="AJ34" s="70"/>
+      <c r="AK34" s="70"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="65"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="67"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="59"/>
-      <c r="O35" s="67"/>
-      <c r="P35" s="61"/>
-      <c r="Q35" s="68"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="76"/>
-      <c r="T35" s="57"/>
-      <c r="U35" s="68"/>
-      <c r="V35" s="69"/>
-      <c r="W35" s="55"/>
-      <c r="X35" s="68"/>
-      <c r="Y35" s="68"/>
-      <c r="Z35" s="69"/>
-      <c r="AA35" s="67"/>
-      <c r="AB35" s="68"/>
-      <c r="AC35" s="68"/>
-      <c r="AD35" s="52"/>
-      <c r="AE35" s="69"/>
-      <c r="AF35" s="67"/>
-      <c r="AG35" s="68"/>
-      <c r="AH35" s="68"/>
-      <c r="AI35" s="68"/>
-      <c r="AJ35" s="68"/>
-      <c r="AK35" s="68"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="70"/>
+      <c r="N35" s="61"/>
+      <c r="O35" s="69"/>
+      <c r="P35" s="63"/>
+      <c r="Q35" s="70"/>
+      <c r="R35" s="78"/>
+      <c r="S35" s="78"/>
+      <c r="T35" s="59"/>
+      <c r="U35" s="70"/>
+      <c r="V35" s="71"/>
+      <c r="W35" s="57"/>
+      <c r="X35" s="70"/>
+      <c r="Y35" s="70"/>
+      <c r="Z35" s="71"/>
+      <c r="AA35" s="69"/>
+      <c r="AB35" s="70"/>
+      <c r="AC35" s="70"/>
+      <c r="AD35" s="54"/>
+      <c r="AE35" s="71"/>
+      <c r="AF35" s="69"/>
+      <c r="AG35" s="70"/>
+      <c r="AH35" s="70"/>
+      <c r="AI35" s="70"/>
+      <c r="AJ35" s="70"/>
+      <c r="AK35" s="70"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="65"/>
-      <c r="C36" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="68"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="62"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="62"/>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="68"/>
-      <c r="S36" s="68"/>
-      <c r="T36" s="68"/>
-      <c r="U36" s="68"/>
-      <c r="V36" s="69"/>
-      <c r="W36" s="55"/>
-      <c r="X36" s="68"/>
-      <c r="Y36" s="68"/>
-      <c r="Z36" s="69"/>
-      <c r="AA36" s="67"/>
-      <c r="AB36" s="68"/>
-      <c r="AC36" s="68"/>
-      <c r="AD36" s="52"/>
-      <c r="AE36" s="69"/>
-      <c r="AF36" s="67"/>
-      <c r="AG36" s="68"/>
-      <c r="AH36" s="68"/>
-      <c r="AI36" s="68"/>
-      <c r="AJ36" s="68"/>
-      <c r="AK36" s="68"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="64"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="64"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="70"/>
+      <c r="S36" s="70"/>
+      <c r="T36" s="70"/>
+      <c r="U36" s="70"/>
+      <c r="V36" s="71"/>
+      <c r="W36" s="57"/>
+      <c r="X36" s="70"/>
+      <c r="Y36" s="70"/>
+      <c r="Z36" s="71"/>
+      <c r="AA36" s="69"/>
+      <c r="AB36" s="70"/>
+      <c r="AC36" s="70"/>
+      <c r="AD36" s="54"/>
+      <c r="AE36" s="71"/>
+      <c r="AF36" s="69"/>
+      <c r="AG36" s="70"/>
+      <c r="AH36" s="70"/>
+      <c r="AI36" s="70"/>
+      <c r="AJ36" s="70"/>
+      <c r="AK36" s="70"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="65"/>
-      <c r="C37" s="74"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="75"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="67"/>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="68"/>
-      <c r="R37" s="76"/>
-      <c r="S37" s="76"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="68"/>
-      <c r="V37" s="69"/>
-      <c r="W37" s="55"/>
-      <c r="X37" s="68"/>
-      <c r="Y37" s="68"/>
-      <c r="Z37" s="69"/>
-      <c r="AA37" s="67"/>
-      <c r="AB37" s="68"/>
-      <c r="AC37" s="68"/>
-      <c r="AD37" s="52"/>
-      <c r="AE37" s="69"/>
-      <c r="AF37" s="67"/>
-      <c r="AG37" s="68"/>
-      <c r="AH37" s="68"/>
-      <c r="AI37" s="68"/>
-      <c r="AJ37" s="68"/>
-      <c r="AK37" s="68"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="77"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="70"/>
+      <c r="N37" s="71"/>
+      <c r="O37" s="69"/>
+      <c r="P37" s="63"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="78"/>
+      <c r="S37" s="78"/>
+      <c r="T37" s="59"/>
+      <c r="U37" s="70"/>
+      <c r="V37" s="71"/>
+      <c r="W37" s="57"/>
+      <c r="X37" s="70"/>
+      <c r="Y37" s="70"/>
+      <c r="Z37" s="71"/>
+      <c r="AA37" s="69"/>
+      <c r="AB37" s="70"/>
+      <c r="AC37" s="70"/>
+      <c r="AD37" s="54"/>
+      <c r="AE37" s="71"/>
+      <c r="AF37" s="69"/>
+      <c r="AG37" s="70"/>
+      <c r="AH37" s="70"/>
+      <c r="AI37" s="70"/>
+      <c r="AJ37" s="70"/>
+      <c r="AK37" s="70"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="65"/>
-      <c r="C38" s="74" t="s">
-        <v>141</v>
-      </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="62"/>
-      <c r="Q38" s="62"/>
-      <c r="R38" s="62"/>
-      <c r="S38" s="62"/>
-      <c r="T38" s="62"/>
-      <c r="U38" s="62"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="55"/>
-      <c r="X38" s="62"/>
-      <c r="Y38" s="62"/>
-      <c r="Z38" s="69"/>
-      <c r="AA38" s="67"/>
-      <c r="AB38" s="68"/>
-      <c r="AC38" s="68"/>
-      <c r="AD38" s="52"/>
-      <c r="AE38" s="69"/>
-      <c r="AF38" s="67"/>
-      <c r="AG38" s="68"/>
-      <c r="AH38" s="68"/>
-      <c r="AI38" s="68"/>
-      <c r="AJ38" s="68"/>
-      <c r="AK38" s="68"/>
+      <c r="B38" s="67"/>
+      <c r="C38" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="53"/>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="64"/>
+      <c r="R38" s="64"/>
+      <c r="S38" s="64"/>
+      <c r="T38" s="64"/>
+      <c r="U38" s="64"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="57"/>
+      <c r="X38" s="64"/>
+      <c r="Y38" s="64"/>
+      <c r="Z38" s="71"/>
+      <c r="AA38" s="69"/>
+      <c r="AB38" s="70"/>
+      <c r="AC38" s="70"/>
+      <c r="AD38" s="54"/>
+      <c r="AE38" s="71"/>
+      <c r="AF38" s="69"/>
+      <c r="AG38" s="70"/>
+      <c r="AH38" s="70"/>
+      <c r="AI38" s="70"/>
+      <c r="AJ38" s="70"/>
+      <c r="AK38" s="70"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="65"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="52"/>
-      <c r="M39" s="68"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="68"/>
-      <c r="Q39" s="68"/>
-      <c r="R39" s="75"/>
-      <c r="S39" s="75"/>
-      <c r="T39" s="68"/>
-      <c r="U39" s="68"/>
-      <c r="V39" s="69"/>
-      <c r="W39" s="55"/>
-      <c r="X39" s="68"/>
-      <c r="Y39" s="68"/>
-      <c r="Z39" s="69"/>
-      <c r="AA39" s="67"/>
-      <c r="AB39" s="68"/>
-      <c r="AC39" s="68"/>
-      <c r="AD39" s="52"/>
-      <c r="AE39" s="69"/>
-      <c r="AF39" s="67"/>
-      <c r="AG39" s="68"/>
-      <c r="AH39" s="68"/>
-      <c r="AI39" s="68"/>
-      <c r="AJ39" s="68"/>
-      <c r="AK39" s="68"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="54"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="69"/>
+      <c r="P39" s="70"/>
+      <c r="Q39" s="70"/>
+      <c r="R39" s="77"/>
+      <c r="S39" s="77"/>
+      <c r="T39" s="70"/>
+      <c r="U39" s="70"/>
+      <c r="V39" s="71"/>
+      <c r="W39" s="57"/>
+      <c r="X39" s="70"/>
+      <c r="Y39" s="70"/>
+      <c r="Z39" s="71"/>
+      <c r="AA39" s="69"/>
+      <c r="AB39" s="70"/>
+      <c r="AC39" s="70"/>
+      <c r="AD39" s="54"/>
+      <c r="AE39" s="71"/>
+      <c r="AF39" s="69"/>
+      <c r="AG39" s="70"/>
+      <c r="AH39" s="70"/>
+      <c r="AI39" s="70"/>
+      <c r="AJ39" s="70"/>
+      <c r="AK39" s="70"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="65"/>
-      <c r="C40" s="74" t="s">
-        <v>142</v>
-      </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="69"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="68"/>
-      <c r="Q40" s="68"/>
-      <c r="R40" s="62"/>
-      <c r="S40" s="62"/>
-      <c r="T40" s="62"/>
-      <c r="U40" s="62"/>
-      <c r="V40" s="50"/>
-      <c r="W40" s="55"/>
-      <c r="X40" s="62"/>
-      <c r="Y40" s="62"/>
-      <c r="Z40" s="50"/>
-      <c r="AA40" s="51"/>
-      <c r="AB40" s="62"/>
-      <c r="AC40" s="62"/>
-      <c r="AD40" s="52"/>
-      <c r="AE40" s="69"/>
-      <c r="AF40" s="67"/>
-      <c r="AG40" s="68"/>
-      <c r="AH40" s="68"/>
-      <c r="AI40" s="68"/>
-      <c r="AJ40" s="68"/>
-      <c r="AK40" s="68"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="76" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="54"/>
+      <c r="M40" s="70"/>
+      <c r="N40" s="71"/>
+      <c r="O40" s="69"/>
+      <c r="P40" s="70"/>
+      <c r="Q40" s="70"/>
+      <c r="R40" s="64"/>
+      <c r="S40" s="64"/>
+      <c r="T40" s="64"/>
+      <c r="U40" s="64"/>
+      <c r="V40" s="52"/>
+      <c r="W40" s="57"/>
+      <c r="X40" s="64"/>
+      <c r="Y40" s="64"/>
+      <c r="Z40" s="52"/>
+      <c r="AA40" s="53"/>
+      <c r="AB40" s="64"/>
+      <c r="AC40" s="64"/>
+      <c r="AD40" s="54"/>
+      <c r="AE40" s="71"/>
+      <c r="AF40" s="69"/>
+      <c r="AG40" s="70"/>
+      <c r="AH40" s="70"/>
+      <c r="AI40" s="70"/>
+      <c r="AJ40" s="70"/>
+      <c r="AK40" s="70"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="65"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="52"/>
-      <c r="M41" s="68"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="68"/>
-      <c r="Q41" s="61"/>
-      <c r="R41" s="75"/>
-      <c r="S41" s="75"/>
-      <c r="T41" s="61"/>
-      <c r="U41" s="68"/>
-      <c r="V41" s="69"/>
-      <c r="W41" s="55"/>
-      <c r="X41" s="68"/>
-      <c r="Y41" s="68"/>
-      <c r="Z41" s="69"/>
-      <c r="AA41" s="67"/>
-      <c r="AB41" s="68"/>
-      <c r="AC41" s="68"/>
-      <c r="AD41" s="52"/>
-      <c r="AE41" s="69"/>
-      <c r="AF41" s="67"/>
-      <c r="AG41" s="68"/>
-      <c r="AH41" s="68"/>
-      <c r="AI41" s="68"/>
-      <c r="AJ41" s="68"/>
-      <c r="AK41" s="68"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="54"/>
+      <c r="M41" s="70"/>
+      <c r="N41" s="71"/>
+      <c r="O41" s="69"/>
+      <c r="P41" s="70"/>
+      <c r="Q41" s="63"/>
+      <c r="R41" s="77"/>
+      <c r="S41" s="77"/>
+      <c r="T41" s="63"/>
+      <c r="U41" s="70"/>
+      <c r="V41" s="71"/>
+      <c r="W41" s="57"/>
+      <c r="X41" s="70"/>
+      <c r="Y41" s="70"/>
+      <c r="Z41" s="71"/>
+      <c r="AA41" s="69"/>
+      <c r="AB41" s="70"/>
+      <c r="AC41" s="70"/>
+      <c r="AD41" s="54"/>
+      <c r="AE41" s="71"/>
+      <c r="AF41" s="69"/>
+      <c r="AG41" s="70"/>
+      <c r="AH41" s="70"/>
+      <c r="AI41" s="70"/>
+      <c r="AJ41" s="70"/>
+      <c r="AK41" s="70"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="77" t="s">
-        <v>143</v>
-      </c>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
-      <c r="L42" s="52"/>
-      <c r="M42" s="48"/>
-      <c r="N42" s="53"/>
-      <c r="O42" s="54"/>
-      <c r="P42" s="62"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="48"/>
-      <c r="S42" s="48"/>
-      <c r="T42" s="61"/>
-      <c r="U42" s="48"/>
-      <c r="V42" s="50"/>
-      <c r="W42" s="55"/>
-      <c r="X42" s="62"/>
-      <c r="Y42" s="62"/>
-      <c r="Z42" s="50"/>
-      <c r="AA42" s="51"/>
-      <c r="AB42" s="62"/>
-      <c r="AC42" s="62"/>
-      <c r="AD42" s="52"/>
-      <c r="AE42" s="53"/>
-      <c r="AF42" s="54"/>
-      <c r="AG42" s="48"/>
-      <c r="AH42" s="48"/>
-      <c r="AI42" s="48"/>
-      <c r="AJ42" s="48"/>
-      <c r="AK42" s="48"/>
+      <c r="C42" s="79" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="50"/>
+      <c r="J42" s="50"/>
+      <c r="K42" s="50"/>
+      <c r="L42" s="54"/>
+      <c r="M42" s="50"/>
+      <c r="N42" s="55"/>
+      <c r="O42" s="56"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="64"/>
+      <c r="R42" s="50"/>
+      <c r="S42" s="50"/>
+      <c r="T42" s="63"/>
+      <c r="U42" s="50"/>
+      <c r="V42" s="52"/>
+      <c r="W42" s="57"/>
+      <c r="X42" s="64"/>
+      <c r="Y42" s="64"/>
+      <c r="Z42" s="52"/>
+      <c r="AA42" s="53"/>
+      <c r="AB42" s="64"/>
+      <c r="AC42" s="64"/>
+      <c r="AD42" s="54"/>
+      <c r="AE42" s="55"/>
+      <c r="AF42" s="56"/>
+      <c r="AG42" s="50"/>
+      <c r="AH42" s="50"/>
+      <c r="AI42" s="50"/>
+      <c r="AJ42" s="50"/>
+      <c r="AK42" s="50"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="46"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="53"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
-      <c r="L43" s="52"/>
-      <c r="M43" s="48"/>
-      <c r="N43" s="53"/>
-      <c r="O43" s="54"/>
-      <c r="P43" s="48"/>
-      <c r="Q43" s="61"/>
-      <c r="R43" s="48"/>
-      <c r="S43" s="63"/>
-      <c r="T43" s="48"/>
-      <c r="U43" s="48"/>
-      <c r="V43" s="53"/>
-      <c r="W43" s="55"/>
-      <c r="X43" s="48"/>
-      <c r="Y43" s="48"/>
-      <c r="Z43" s="53"/>
-      <c r="AA43" s="54"/>
-      <c r="AB43" s="48"/>
-      <c r="AC43" s="48"/>
-      <c r="AD43" s="52"/>
-      <c r="AE43" s="53"/>
-      <c r="AF43" s="54"/>
-      <c r="AG43" s="48"/>
-      <c r="AH43" s="48"/>
-      <c r="AI43" s="48"/>
-      <c r="AJ43" s="48"/>
-      <c r="AK43" s="48"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="54"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="55"/>
+      <c r="O43" s="56"/>
+      <c r="P43" s="50"/>
+      <c r="Q43" s="63"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="65"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="50"/>
+      <c r="V43" s="55"/>
+      <c r="W43" s="57"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="50"/>
+      <c r="Z43" s="55"/>
+      <c r="AA43" s="56"/>
+      <c r="AB43" s="50"/>
+      <c r="AC43" s="50"/>
+      <c r="AD43" s="54"/>
+      <c r="AE43" s="55"/>
+      <c r="AF43" s="56"/>
+      <c r="AG43" s="50"/>
+      <c r="AH43" s="50"/>
+      <c r="AI43" s="50"/>
+      <c r="AJ43" s="50"/>
+      <c r="AK43" s="50"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="46"/>
-      <c r="C44" s="77" t="s">
-        <v>144</v>
-      </c>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="54"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
-      <c r="L44" s="52"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="53"/>
-      <c r="O44" s="54"/>
-      <c r="P44" s="62"/>
-      <c r="Q44" s="62"/>
-      <c r="R44" s="48"/>
-      <c r="S44" s="48"/>
-      <c r="T44" s="48"/>
-      <c r="U44" s="48"/>
-      <c r="V44" s="53"/>
-      <c r="W44" s="55"/>
-      <c r="X44" s="62"/>
-      <c r="Y44" s="62"/>
-      <c r="Z44" s="53"/>
-      <c r="AA44" s="54"/>
-      <c r="AB44" s="48"/>
-      <c r="AC44" s="62"/>
-      <c r="AD44" s="52"/>
-      <c r="AE44" s="50"/>
-      <c r="AF44" s="51"/>
-      <c r="AG44" s="48"/>
-      <c r="AH44" s="48"/>
-      <c r="AI44" s="62"/>
-      <c r="AJ44" s="48"/>
-      <c r="AK44" s="48"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
+      <c r="L44" s="54"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="55"/>
+      <c r="O44" s="56"/>
+      <c r="P44" s="64"/>
+      <c r="Q44" s="64"/>
+      <c r="R44" s="50"/>
+      <c r="S44" s="50"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="55"/>
+      <c r="W44" s="57"/>
+      <c r="X44" s="64"/>
+      <c r="Y44" s="64"/>
+      <c r="Z44" s="55"/>
+      <c r="AA44" s="56"/>
+      <c r="AB44" s="50"/>
+      <c r="AC44" s="64"/>
+      <c r="AD44" s="54"/>
+      <c r="AE44" s="52"/>
+      <c r="AF44" s="53"/>
+      <c r="AG44" s="50"/>
+      <c r="AH44" s="50"/>
+      <c r="AI44" s="64"/>
+      <c r="AJ44" s="50"/>
+      <c r="AK44" s="50"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="46"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="54"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="48"/>
-      <c r="N45" s="53"/>
-      <c r="O45" s="54"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="48"/>
-      <c r="R45" s="48"/>
-      <c r="S45" s="48"/>
-      <c r="T45" s="48"/>
-      <c r="U45" s="48"/>
-      <c r="V45" s="53"/>
-      <c r="W45" s="55"/>
-      <c r="X45" s="48"/>
-      <c r="Y45" s="61"/>
-      <c r="Z45" s="78"/>
-      <c r="AA45" s="54"/>
-      <c r="AB45" s="48"/>
-      <c r="AC45" s="48"/>
-      <c r="AD45" s="52"/>
-      <c r="AE45" s="53"/>
-      <c r="AF45" s="54"/>
-      <c r="AG45" s="48"/>
-      <c r="AH45" s="48"/>
-      <c r="AI45" s="48"/>
-      <c r="AJ45" s="48"/>
-      <c r="AK45" s="48"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="79"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="50"/>
+      <c r="L45" s="54"/>
+      <c r="M45" s="50"/>
+      <c r="N45" s="55"/>
+      <c r="O45" s="56"/>
+      <c r="P45" s="50"/>
+      <c r="Q45" s="50"/>
+      <c r="R45" s="50"/>
+      <c r="S45" s="50"/>
+      <c r="T45" s="50"/>
+      <c r="U45" s="50"/>
+      <c r="V45" s="55"/>
+      <c r="W45" s="57"/>
+      <c r="X45" s="50"/>
+      <c r="Y45" s="63"/>
+      <c r="Z45" s="80"/>
+      <c r="AA45" s="56"/>
+      <c r="AB45" s="50"/>
+      <c r="AC45" s="50"/>
+      <c r="AD45" s="54"/>
+      <c r="AE45" s="55"/>
+      <c r="AF45" s="56"/>
+      <c r="AG45" s="50"/>
+      <c r="AH45" s="50"/>
+      <c r="AI45" s="50"/>
+      <c r="AJ45" s="50"/>
+      <c r="AK45" s="50"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="65" t="s">
-        <v>145</v>
-      </c>
-      <c r="C46" s="66" t="s">
+      <c r="B46" s="67" t="s">
+        <v>146</v>
+      </c>
+      <c r="C46" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="67"/>
-      <c r="I46" s="68"/>
-      <c r="J46" s="68"/>
-      <c r="K46" s="68"/>
-      <c r="L46" s="52"/>
-      <c r="M46" s="68"/>
-      <c r="N46" s="69"/>
-      <c r="O46" s="67"/>
-      <c r="P46" s="68"/>
-      <c r="Q46" s="68"/>
-      <c r="R46" s="68"/>
-      <c r="S46" s="68"/>
-      <c r="T46" s="68"/>
-      <c r="U46" s="68"/>
-      <c r="V46" s="69"/>
-      <c r="W46" s="55"/>
-      <c r="X46" s="68"/>
-      <c r="Y46" s="68"/>
-      <c r="Z46" s="69"/>
-      <c r="AA46" s="67"/>
-      <c r="AB46" s="68"/>
-      <c r="AC46" s="68"/>
-      <c r="AD46" s="52"/>
-      <c r="AE46" s="69"/>
-      <c r="AF46" s="67"/>
-      <c r="AG46" s="68"/>
-      <c r="AH46" s="68"/>
-      <c r="AI46" s="68"/>
-      <c r="AJ46" s="62"/>
-      <c r="AK46" s="68"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="70"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="54"/>
+      <c r="M46" s="70"/>
+      <c r="N46" s="71"/>
+      <c r="O46" s="69"/>
+      <c r="P46" s="70"/>
+      <c r="Q46" s="70"/>
+      <c r="R46" s="70"/>
+      <c r="S46" s="70"/>
+      <c r="T46" s="70"/>
+      <c r="U46" s="70"/>
+      <c r="V46" s="71"/>
+      <c r="W46" s="57"/>
+      <c r="X46" s="70"/>
+      <c r="Y46" s="70"/>
+      <c r="Z46" s="71"/>
+      <c r="AA46" s="69"/>
+      <c r="AB46" s="70"/>
+      <c r="AC46" s="70"/>
+      <c r="AD46" s="54"/>
+      <c r="AE46" s="71"/>
+      <c r="AF46" s="69"/>
+      <c r="AG46" s="70"/>
+      <c r="AH46" s="70"/>
+      <c r="AI46" s="70"/>
+      <c r="AJ46" s="64"/>
+      <c r="AK46" s="70"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="65"/>
-      <c r="C47" s="66"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="71"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="68"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="68"/>
-      <c r="L47" s="52"/>
-      <c r="M47" s="68"/>
-      <c r="N47" s="69"/>
-      <c r="O47" s="67"/>
-      <c r="P47" s="68"/>
-      <c r="Q47" s="68"/>
-      <c r="R47" s="68"/>
-      <c r="S47" s="68"/>
-      <c r="T47" s="68"/>
-      <c r="U47" s="68"/>
-      <c r="V47" s="69"/>
-      <c r="W47" s="55"/>
-      <c r="X47" s="68"/>
-      <c r="Y47" s="68"/>
-      <c r="Z47" s="69"/>
-      <c r="AA47" s="67"/>
-      <c r="AB47" s="68"/>
-      <c r="AC47" s="68"/>
-      <c r="AD47" s="52"/>
-      <c r="AE47" s="69"/>
-      <c r="AF47" s="67"/>
-      <c r="AG47" s="68"/>
-      <c r="AH47" s="68"/>
-      <c r="AI47" s="68"/>
-      <c r="AJ47" s="68"/>
-      <c r="AK47" s="68"/>
-      <c r="AN47" s="79" t="s">
-        <v>146</v>
-      </c>
-      <c r="AO47" s="62"/>
+      <c r="B47" s="67"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="70"/>
+      <c r="N47" s="71"/>
+      <c r="O47" s="69"/>
+      <c r="P47" s="70"/>
+      <c r="Q47" s="70"/>
+      <c r="R47" s="70"/>
+      <c r="S47" s="70"/>
+      <c r="T47" s="70"/>
+      <c r="U47" s="70"/>
+      <c r="V47" s="71"/>
+      <c r="W47" s="57"/>
+      <c r="X47" s="70"/>
+      <c r="Y47" s="70"/>
+      <c r="Z47" s="71"/>
+      <c r="AA47" s="69"/>
+      <c r="AB47" s="70"/>
+      <c r="AC47" s="70"/>
+      <c r="AD47" s="54"/>
+      <c r="AE47" s="71"/>
+      <c r="AF47" s="69"/>
+      <c r="AG47" s="70"/>
+      <c r="AH47" s="70"/>
+      <c r="AI47" s="70"/>
+      <c r="AJ47" s="70"/>
+      <c r="AK47" s="70"/>
+      <c r="AN47" s="81" t="s">
+        <v>147</v>
+      </c>
+      <c r="AO47" s="64"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="65"/>
-      <c r="C48" s="66" t="s">
-        <v>147</v>
-      </c>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="71"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="67"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="68"/>
-      <c r="L48" s="52"/>
-      <c r="M48" s="68"/>
-      <c r="N48" s="69"/>
-      <c r="O48" s="67"/>
-      <c r="P48" s="68"/>
-      <c r="Q48" s="68"/>
-      <c r="R48" s="68"/>
-      <c r="S48" s="68"/>
-      <c r="T48" s="68"/>
-      <c r="U48" s="68"/>
-      <c r="V48" s="69"/>
-      <c r="W48" s="55"/>
-      <c r="X48" s="68"/>
-      <c r="Y48" s="68"/>
-      <c r="Z48" s="69"/>
-      <c r="AA48" s="67"/>
-      <c r="AB48" s="68"/>
-      <c r="AC48" s="68"/>
-      <c r="AD48" s="52"/>
-      <c r="AE48" s="69"/>
-      <c r="AF48" s="67"/>
-      <c r="AG48" s="68"/>
-      <c r="AH48" s="68"/>
-      <c r="AI48" s="68"/>
-      <c r="AJ48" s="68"/>
-      <c r="AK48" s="80"/>
-      <c r="AN48" s="79" t="s">
+      <c r="B48" s="67"/>
+      <c r="C48" s="68" t="s">
         <v>148</v>
       </c>
-      <c r="AO48" s="61"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="70"/>
+      <c r="K48" s="70"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="70"/>
+      <c r="N48" s="71"/>
+      <c r="O48" s="69"/>
+      <c r="P48" s="70"/>
+      <c r="Q48" s="70"/>
+      <c r="R48" s="70"/>
+      <c r="S48" s="70"/>
+      <c r="T48" s="70"/>
+      <c r="U48" s="70"/>
+      <c r="V48" s="71"/>
+      <c r="W48" s="57"/>
+      <c r="X48" s="70"/>
+      <c r="Y48" s="70"/>
+      <c r="Z48" s="71"/>
+      <c r="AA48" s="69"/>
+      <c r="AB48" s="70"/>
+      <c r="AC48" s="70"/>
+      <c r="AD48" s="54"/>
+      <c r="AE48" s="71"/>
+      <c r="AF48" s="69"/>
+      <c r="AG48" s="70"/>
+      <c r="AH48" s="70"/>
+      <c r="AI48" s="70"/>
+      <c r="AJ48" s="70"/>
+      <c r="AK48" s="82"/>
+      <c r="AN48" s="81" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO48" s="63"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="65"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="68"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="68"/>
-      <c r="K49" s="68"/>
-      <c r="L49" s="52"/>
-      <c r="M49" s="68"/>
-      <c r="N49" s="69"/>
-      <c r="O49" s="67"/>
-      <c r="P49" s="68"/>
-      <c r="Q49" s="68"/>
-      <c r="R49" s="68"/>
-      <c r="S49" s="68"/>
-      <c r="T49" s="68"/>
-      <c r="U49" s="68"/>
-      <c r="V49" s="69"/>
-      <c r="W49" s="55"/>
-      <c r="X49" s="68"/>
-      <c r="Y49" s="68"/>
-      <c r="Z49" s="69"/>
-      <c r="AA49" s="67"/>
-      <c r="AB49" s="68"/>
-      <c r="AC49" s="68"/>
-      <c r="AD49" s="52"/>
-      <c r="AE49" s="69"/>
-      <c r="AF49" s="67"/>
-      <c r="AG49" s="68"/>
-      <c r="AH49" s="68"/>
-      <c r="AI49" s="68"/>
-      <c r="AJ49" s="68"/>
-      <c r="AK49" s="68"/>
-      <c r="AN49" s="79" t="s">
-        <v>149</v>
-      </c>
-      <c r="AO49" s="57"/>
+      <c r="B49" s="67"/>
+      <c r="C49" s="68"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="70"/>
+      <c r="K49" s="70"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="70"/>
+      <c r="N49" s="71"/>
+      <c r="O49" s="69"/>
+      <c r="P49" s="70"/>
+      <c r="Q49" s="70"/>
+      <c r="R49" s="70"/>
+      <c r="S49" s="70"/>
+      <c r="T49" s="70"/>
+      <c r="U49" s="70"/>
+      <c r="V49" s="71"/>
+      <c r="W49" s="57"/>
+      <c r="X49" s="70"/>
+      <c r="Y49" s="70"/>
+      <c r="Z49" s="71"/>
+      <c r="AA49" s="69"/>
+      <c r="AB49" s="70"/>
+      <c r="AC49" s="70"/>
+      <c r="AD49" s="54"/>
+      <c r="AE49" s="71"/>
+      <c r="AF49" s="69"/>
+      <c r="AG49" s="70"/>
+      <c r="AH49" s="70"/>
+      <c r="AI49" s="70"/>
+      <c r="AJ49" s="70"/>
+      <c r="AK49" s="70"/>
+      <c r="AN49" s="81" t="s">
+        <v>150</v>
+      </c>
+      <c r="AO49" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -9351,801 +9368,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="81"/>
+      <c r="B1" s="83"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="82" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="83" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="84" t="s">
-        <v>150</v>
-      </c>
-      <c r="E2" s="85" t="s">
+      <c r="B2" s="84" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="86" t="s">
         <v>151</v>
       </c>
-      <c r="F2" s="86" t="s">
+      <c r="E2" s="87" t="s">
         <v>152</v>
       </c>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="86" t="s">
+      <c r="F2" s="88" t="s">
         <v>153</v>
       </c>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="86" t="s">
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="88" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="86"/>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="86" t="s">
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="S2" s="87"/>
-      <c r="AD2" s="28"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="87"/>
+      <c r="R2" s="88" t="s">
+        <v>156</v>
+      </c>
+      <c r="S2" s="89"/>
+      <c r="AD2" s="30"/>
     </row>
     <row r="3">
-      <c r="B3" s="88"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="90" t="s">
-        <v>156</v>
-      </c>
-      <c r="E3" s="91">
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="92" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="93">
         <v>4</v>
       </c>
-      <c r="F3" s="92">
+      <c r="F3" s="94">
         <v>1</v>
       </c>
-      <c r="G3" s="93">
+      <c r="G3" s="95">
         <v>2</v>
       </c>
-      <c r="H3" s="93">
+      <c r="H3" s="95">
         <v>3</v>
       </c>
-      <c r="I3" s="91">
+      <c r="I3" s="93">
         <v>4</v>
       </c>
-      <c r="J3" s="92">
+      <c r="J3" s="94">
         <v>1</v>
       </c>
-      <c r="K3" s="93">
+      <c r="K3" s="95">
         <v>2</v>
       </c>
-      <c r="L3" s="93">
+      <c r="L3" s="95">
         <v>3</v>
       </c>
-      <c r="M3" s="91">
+      <c r="M3" s="93">
         <v>4</v>
       </c>
-      <c r="N3" s="92">
+      <c r="N3" s="94">
         <v>1</v>
       </c>
-      <c r="O3" s="93">
+      <c r="O3" s="95">
         <v>2</v>
       </c>
-      <c r="P3" s="93">
+      <c r="P3" s="95">
         <v>3</v>
       </c>
-      <c r="Q3" s="91">
+      <c r="Q3" s="93">
         <v>4</v>
       </c>
-      <c r="R3" s="92">
+      <c r="R3" s="94">
         <v>1</v>
       </c>
-      <c r="S3" s="94">
+      <c r="S3" s="96">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="95" t="s">
-        <v>158</v>
-      </c>
-      <c r="C4" s="83" t="s">
+      <c r="B4" s="97" t="s">
         <v>159</v>
       </c>
-      <c r="D4" s="96"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="97"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="97"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="101"/>
+      <c r="C4" s="85" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="98"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="103"/>
       <c r="U4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="95"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="107"/>
-      <c r="L5" s="107"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="107"/>
-      <c r="P5" s="107"/>
-      <c r="Q5" s="104"/>
-      <c r="R5" s="108"/>
-      <c r="S5" s="109"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="109"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="106"/>
+      <c r="R5" s="110"/>
+      <c r="S5" s="111"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="95"/>
-      <c r="C6" s="110" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="111"/>
-      <c r="E6" s="112"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="114"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="112"/>
-      <c r="J6" s="116"/>
-      <c r="K6" s="115"/>
-      <c r="L6" s="115"/>
-      <c r="M6" s="112"/>
-      <c r="N6" s="116"/>
-      <c r="O6" s="115"/>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="112"/>
-      <c r="R6" s="116"/>
-      <c r="S6" s="117"/>
-      <c r="U6" s="118" t="s">
+      <c r="B6" s="97"/>
+      <c r="C6" s="112" t="s">
         <v>162</v>
       </c>
-      <c r="V6" s="118"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="116"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="118"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="114"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="117"/>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="114"/>
+      <c r="R6" s="118"/>
+      <c r="S6" s="119"/>
+      <c r="U6" s="120" t="s">
+        <v>163</v>
+      </c>
+      <c r="V6" s="120"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="95"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="108"/>
-      <c r="O7" s="107"/>
-      <c r="P7" s="107"/>
-      <c r="Q7" s="104"/>
-      <c r="R7" s="108"/>
-      <c r="S7" s="109"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="109"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="106"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="111"/>
       <c r="U7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="95"/>
-      <c r="C8" s="110" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" s="111"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="115"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="116"/>
-      <c r="K8" s="115"/>
-      <c r="L8" s="115"/>
-      <c r="M8" s="112"/>
-      <c r="N8" s="116"/>
-      <c r="O8" s="115"/>
-      <c r="P8" s="115"/>
-      <c r="Q8" s="112"/>
-      <c r="R8" s="116"/>
-      <c r="S8" s="117"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="112" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="113"/>
+      <c r="E8" s="114"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="114"/>
+      <c r="J8" s="118"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="117"/>
+      <c r="M8" s="114"/>
+      <c r="N8" s="118"/>
+      <c r="O8" s="117"/>
+      <c r="P8" s="117"/>
+      <c r="Q8" s="114"/>
+      <c r="R8" s="118"/>
+      <c r="S8" s="119"/>
       <c r="U8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="95"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="108"/>
-      <c r="G9" s="106"/>
-      <c r="H9" s="107"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="108"/>
-      <c r="K9" s="107"/>
-      <c r="L9" s="107"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="108"/>
-      <c r="O9" s="107"/>
-      <c r="P9" s="107"/>
-      <c r="Q9" s="104"/>
-      <c r="R9" s="108"/>
-      <c r="S9" s="109"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="110"/>
+      <c r="K9" s="109"/>
+      <c r="L9" s="109"/>
+      <c r="M9" s="106"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="109"/>
+      <c r="P9" s="109"/>
+      <c r="Q9" s="106"/>
+      <c r="R9" s="110"/>
+      <c r="S9" s="111"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="95"/>
-      <c r="C10" s="110" t="s">
-        <v>166</v>
-      </c>
-      <c r="D10" s="111"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="116"/>
-      <c r="G10" s="114"/>
-      <c r="H10" s="114"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="116"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="112"/>
-      <c r="N10" s="116"/>
-      <c r="O10" s="115"/>
-      <c r="P10" s="115"/>
-      <c r="Q10" s="112"/>
-      <c r="R10" s="116"/>
-      <c r="S10" s="117"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="112" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="113"/>
+      <c r="E10" s="114"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="116"/>
+      <c r="H10" s="116"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="118"/>
+      <c r="K10" s="117"/>
+      <c r="L10" s="117"/>
+      <c r="M10" s="114"/>
+      <c r="N10" s="118"/>
+      <c r="O10" s="117"/>
+      <c r="P10" s="117"/>
+      <c r="Q10" s="114"/>
+      <c r="R10" s="118"/>
+      <c r="S10" s="119"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="119"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="124"/>
-      <c r="H11" s="124"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="125"/>
-      <c r="L11" s="125"/>
-      <c r="M11" s="122"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="125"/>
-      <c r="P11" s="125"/>
-      <c r="Q11" s="122"/>
-      <c r="R11" s="123"/>
-      <c r="S11" s="126"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="125"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="124"/>
+      <c r="N11" s="125"/>
+      <c r="O11" s="127"/>
+      <c r="P11" s="127"/>
+      <c r="Q11" s="124"/>
+      <c r="R11" s="125"/>
+      <c r="S11" s="128"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="82" t="s">
-        <v>167</v>
-      </c>
-      <c r="C12" s="83" t="s">
+      <c r="B12" s="84" t="s">
         <v>168</v>
       </c>
-      <c r="D12" s="96"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="99"/>
-      <c r="H12" s="127"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="99"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="97"/>
-      <c r="N12" s="100"/>
-      <c r="O12" s="99"/>
-      <c r="P12" s="99"/>
-      <c r="Q12" s="97"/>
-      <c r="R12" s="100"/>
-      <c r="S12" s="101"/>
+      <c r="C12" s="85" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" s="98"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="99"/>
+      <c r="N12" s="102"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="101"/>
+      <c r="Q12" s="99"/>
+      <c r="R12" s="102"/>
+      <c r="S12" s="103"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="95"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="108"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="107"/>
-      <c r="L13" s="107"/>
-      <c r="M13" s="104"/>
-      <c r="N13" s="108"/>
-      <c r="O13" s="107"/>
-      <c r="P13" s="107"/>
-      <c r="Q13" s="104"/>
-      <c r="R13" s="108"/>
-      <c r="S13" s="109"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="109"/>
+      <c r="L13" s="109"/>
+      <c r="M13" s="106"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="109"/>
+      <c r="P13" s="109"/>
+      <c r="Q13" s="106"/>
+      <c r="R13" s="110"/>
+      <c r="S13" s="111"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="95"/>
-      <c r="C14" s="110" t="s">
-        <v>169</v>
-      </c>
-      <c r="D14" s="129"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="112"/>
-      <c r="J14" s="116"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="115"/>
-      <c r="M14" s="112"/>
-      <c r="N14" s="116"/>
-      <c r="O14" s="115"/>
-      <c r="P14" s="115"/>
-      <c r="Q14" s="112"/>
-      <c r="R14" s="116"/>
-      <c r="S14" s="117"/>
+      <c r="B14" s="97"/>
+      <c r="C14" s="112" t="s">
+        <v>170</v>
+      </c>
+      <c r="D14" s="131"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="118"/>
+      <c r="O14" s="117"/>
+      <c r="P14" s="117"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="118"/>
+      <c r="S14" s="119"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="95"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="108"/>
-      <c r="G15" s="107"/>
-      <c r="H15" s="107"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="107"/>
-      <c r="L15" s="107"/>
-      <c r="M15" s="104"/>
-      <c r="N15" s="108"/>
-      <c r="O15" s="107"/>
-      <c r="P15" s="107"/>
-      <c r="Q15" s="104"/>
-      <c r="R15" s="108"/>
-      <c r="S15" s="109"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="109"/>
+      <c r="L15" s="109"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="109"/>
+      <c r="P15" s="109"/>
+      <c r="Q15" s="106"/>
+      <c r="R15" s="110"/>
+      <c r="S15" s="111"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="95"/>
-      <c r="C16" s="110" t="s">
-        <v>170</v>
-      </c>
-      <c r="D16" s="111"/>
-      <c r="E16" s="112"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="114"/>
-      <c r="I16" s="131"/>
-      <c r="J16" s="116"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="115"/>
-      <c r="M16" s="112"/>
-      <c r="N16" s="116"/>
-      <c r="O16" s="115"/>
-      <c r="P16" s="115"/>
-      <c r="Q16" s="112"/>
-      <c r="R16" s="116"/>
-      <c r="S16" s="117"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="D16" s="113"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="116"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="118"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="114"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="117"/>
+      <c r="P16" s="117"/>
+      <c r="Q16" s="114"/>
+      <c r="R16" s="118"/>
+      <c r="S16" s="119"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="119"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="122"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="125"/>
-      <c r="H17" s="125"/>
-      <c r="I17" s="122"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="124"/>
-      <c r="L17" s="125"/>
-      <c r="M17" s="122"/>
-      <c r="N17" s="123"/>
-      <c r="O17" s="125"/>
-      <c r="P17" s="125"/>
-      <c r="Q17" s="122"/>
-      <c r="R17" s="123"/>
-      <c r="S17" s="126"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="127"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="124"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="127"/>
+      <c r="M17" s="124"/>
+      <c r="N17" s="125"/>
+      <c r="O17" s="127"/>
+      <c r="P17" s="127"/>
+      <c r="Q17" s="124"/>
+      <c r="R17" s="125"/>
+      <c r="S17" s="128"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="84" t="s">
-        <v>171</v>
-      </c>
-      <c r="C18" s="83" t="s">
+      <c r="B18" s="86" t="s">
         <v>172</v>
       </c>
-      <c r="D18" s="96"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="100"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="99"/>
-      <c r="I18" s="128"/>
-      <c r="J18" s="100"/>
-      <c r="K18" s="99"/>
-      <c r="L18" s="99"/>
-      <c r="M18" s="97"/>
-      <c r="N18" s="100"/>
-      <c r="O18" s="99"/>
-      <c r="P18" s="99"/>
-      <c r="Q18" s="97"/>
-      <c r="R18" s="100"/>
-      <c r="S18" s="101"/>
+      <c r="C18" s="85" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="98"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="101"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="101"/>
+      <c r="L18" s="101"/>
+      <c r="M18" s="99"/>
+      <c r="N18" s="102"/>
+      <c r="O18" s="101"/>
+      <c r="P18" s="101"/>
+      <c r="Q18" s="99"/>
+      <c r="R18" s="102"/>
+      <c r="S18" s="103"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="95"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="108"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="107"/>
-      <c r="M19" s="104"/>
-      <c r="N19" s="108"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="107"/>
-      <c r="Q19" s="104"/>
-      <c r="R19" s="108"/>
-      <c r="S19" s="109"/>
+      <c r="B19" s="97"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="109"/>
+      <c r="M19" s="106"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="109"/>
+      <c r="P19" s="109"/>
+      <c r="Q19" s="106"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="111"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="95"/>
-      <c r="C20" s="110" t="s">
-        <v>173</v>
-      </c>
-      <c r="D20" s="111"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="131"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="114"/>
-      <c r="M20" s="112"/>
-      <c r="N20" s="116"/>
-      <c r="O20" s="115"/>
-      <c r="P20" s="115"/>
-      <c r="Q20" s="112"/>
-      <c r="R20" s="116"/>
-      <c r="S20" s="117"/>
+      <c r="B20" s="97"/>
+      <c r="C20" s="112" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="113"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="133"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="116"/>
+      <c r="L20" s="116"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="118"/>
+      <c r="O20" s="117"/>
+      <c r="P20" s="117"/>
+      <c r="Q20" s="114"/>
+      <c r="R20" s="118"/>
+      <c r="S20" s="119"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="95"/>
-      <c r="C21" s="102"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="107"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="108"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="107"/>
-      <c r="M21" s="104"/>
-      <c r="N21" s="133"/>
-      <c r="O21" s="107"/>
-      <c r="P21" s="107"/>
-      <c r="Q21" s="104"/>
-      <c r="R21" s="108"/>
-      <c r="S21" s="109"/>
+      <c r="B21" s="97"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="106"/>
+      <c r="N21" s="135"/>
+      <c r="O21" s="109"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="106"/>
+      <c r="R21" s="110"/>
+      <c r="S21" s="111"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="95"/>
-      <c r="C22" s="110" t="s">
-        <v>174</v>
-      </c>
-      <c r="D22" s="111"/>
-      <c r="E22" s="112"/>
-      <c r="F22" s="116"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="115"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="116"/>
-      <c r="K22" s="114"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="112"/>
-      <c r="N22" s="116"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="115"/>
-      <c r="Q22" s="112"/>
-      <c r="R22" s="116"/>
-      <c r="S22" s="117"/>
+      <c r="B22" s="97"/>
+      <c r="C22" s="112" t="s">
+        <v>175</v>
+      </c>
+      <c r="D22" s="113"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="116"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="114"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="117"/>
+      <c r="P22" s="117"/>
+      <c r="Q22" s="114"/>
+      <c r="R22" s="118"/>
+      <c r="S22" s="119"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="119"/>
-      <c r="C23" s="120"/>
-      <c r="D23" s="121"/>
-      <c r="E23" s="122"/>
-      <c r="F23" s="123"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="122"/>
-      <c r="J23" s="123"/>
-      <c r="K23" s="125"/>
-      <c r="L23" s="125"/>
-      <c r="M23" s="122"/>
-      <c r="N23" s="123"/>
-      <c r="O23" s="125"/>
-      <c r="P23" s="125"/>
-      <c r="Q23" s="122"/>
-      <c r="R23" s="123"/>
-      <c r="S23" s="126"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="127"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="124"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="127"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="124"/>
+      <c r="N23" s="125"/>
+      <c r="O23" s="127"/>
+      <c r="P23" s="127"/>
+      <c r="Q23" s="124"/>
+      <c r="R23" s="125"/>
+      <c r="S23" s="128"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="84" t="s">
-        <v>175</v>
-      </c>
-      <c r="C24" s="83" t="s">
+      <c r="B24" s="86" t="s">
         <v>176</v>
       </c>
-      <c r="D24" s="96"/>
-      <c r="E24" s="97"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="99"/>
-      <c r="H24" s="99"/>
-      <c r="I24" s="97"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="99"/>
-      <c r="L24" s="99"/>
-      <c r="M24" s="128"/>
-      <c r="N24" s="98"/>
-      <c r="O24" s="127"/>
-      <c r="P24" s="127"/>
-      <c r="Q24" s="97"/>
-      <c r="R24" s="100"/>
-      <c r="S24" s="101"/>
+      <c r="C24" s="85" t="s">
+        <v>177</v>
+      </c>
+      <c r="D24" s="98"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="130"/>
+      <c r="N24" s="100"/>
+      <c r="O24" s="129"/>
+      <c r="P24" s="129"/>
+      <c r="Q24" s="99"/>
+      <c r="R24" s="102"/>
+      <c r="S24" s="103"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="95"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="107"/>
-      <c r="H25" s="107"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="108"/>
-      <c r="K25" s="107"/>
-      <c r="L25" s="107"/>
-      <c r="M25" s="104"/>
-      <c r="N25" s="108"/>
-      <c r="O25" s="107"/>
-      <c r="P25" s="107"/>
-      <c r="Q25" s="104"/>
-      <c r="R25" s="108"/>
-      <c r="S25" s="109"/>
+      <c r="B25" s="97"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="109"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="110"/>
+      <c r="O25" s="109"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="106"/>
+      <c r="R25" s="110"/>
+      <c r="S25" s="111"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="95"/>
-      <c r="C26" s="110" t="s">
-        <v>177</v>
-      </c>
-      <c r="D26" s="111"/>
-      <c r="E26" s="112"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="115"/>
-      <c r="H26" s="115"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="116"/>
-      <c r="K26" s="115"/>
-      <c r="L26" s="115"/>
-      <c r="M26" s="112"/>
-      <c r="N26" s="116"/>
-      <c r="O26" s="114"/>
-      <c r="P26" s="114"/>
-      <c r="Q26" s="112"/>
-      <c r="R26" s="116"/>
-      <c r="S26" s="117"/>
+      <c r="B26" s="97"/>
+      <c r="C26" s="112" t="s">
+        <v>178</v>
+      </c>
+      <c r="D26" s="113"/>
+      <c r="E26" s="114"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="114"/>
+      <c r="J26" s="118"/>
+      <c r="K26" s="117"/>
+      <c r="L26" s="117"/>
+      <c r="M26" s="114"/>
+      <c r="N26" s="118"/>
+      <c r="O26" s="116"/>
+      <c r="P26" s="116"/>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="118"/>
+      <c r="S26" s="119"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="95"/>
-      <c r="C27" s="102"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="108"/>
-      <c r="G27" s="107"/>
-      <c r="H27" s="107"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="108"/>
-      <c r="K27" s="107"/>
-      <c r="L27" s="107"/>
-      <c r="M27" s="104"/>
-      <c r="N27" s="108"/>
-      <c r="O27" s="107"/>
-      <c r="P27" s="107"/>
-      <c r="Q27" s="104"/>
-      <c r="R27" s="108"/>
-      <c r="S27" s="109"/>
+      <c r="B27" s="97"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="109"/>
+      <c r="L27" s="109"/>
+      <c r="M27" s="106"/>
+      <c r="N27" s="110"/>
+      <c r="O27" s="109"/>
+      <c r="P27" s="109"/>
+      <c r="Q27" s="106"/>
+      <c r="R27" s="110"/>
+      <c r="S27" s="111"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="95"/>
-      <c r="C28" s="110" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" s="111"/>
-      <c r="E28" s="112"/>
-      <c r="F28" s="116"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="112"/>
-      <c r="J28" s="116"/>
-      <c r="K28" s="115"/>
-      <c r="L28" s="115"/>
-      <c r="M28" s="112"/>
-      <c r="N28" s="116"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="114"/>
-      <c r="Q28" s="131"/>
-      <c r="R28" s="116"/>
-      <c r="S28" s="117"/>
+      <c r="B28" s="97"/>
+      <c r="C28" s="112" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="113"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="118"/>
+      <c r="K28" s="117"/>
+      <c r="L28" s="117"/>
+      <c r="M28" s="114"/>
+      <c r="N28" s="118"/>
+      <c r="O28" s="117"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="133"/>
+      <c r="R28" s="118"/>
+      <c r="S28" s="119"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="95"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="134"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="136"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="138"/>
-      <c r="I29" s="135"/>
-      <c r="J29" s="136"/>
-      <c r="K29" s="137"/>
-      <c r="L29" s="138"/>
-      <c r="M29" s="135"/>
-      <c r="N29" s="139"/>
-      <c r="O29" s="138"/>
-      <c r="P29" s="137"/>
-      <c r="Q29" s="135"/>
-      <c r="R29" s="136"/>
-      <c r="S29" s="140"/>
+      <c r="B29" s="97"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="136"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="139"/>
+      <c r="H29" s="140"/>
+      <c r="I29" s="137"/>
+      <c r="J29" s="138"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="140"/>
+      <c r="M29" s="137"/>
+      <c r="N29" s="141"/>
+      <c r="O29" s="140"/>
+      <c r="P29" s="139"/>
+      <c r="Q29" s="137"/>
+      <c r="R29" s="138"/>
+      <c r="S29" s="142"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="141" t="s">
+      <c r="B30" s="143" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="142" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" s="96"/>
-      <c r="E30" s="143"/>
-      <c r="F30" s="144"/>
-      <c r="G30" s="144"/>
-      <c r="H30" s="145"/>
-      <c r="I30" s="146"/>
-      <c r="J30" s="144"/>
-      <c r="K30" s="144"/>
-      <c r="L30" s="145"/>
-      <c r="M30" s="146"/>
-      <c r="N30" s="144"/>
-      <c r="O30" s="145"/>
-      <c r="P30" s="144"/>
-      <c r="Q30" s="146"/>
-      <c r="R30" s="144"/>
-      <c r="S30" s="147"/>
+      <c r="C30" s="144" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="98"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="146"/>
+      <c r="H30" s="147"/>
+      <c r="I30" s="148"/>
+      <c r="J30" s="146"/>
+      <c r="K30" s="146"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="148"/>
+      <c r="N30" s="146"/>
+      <c r="O30" s="147"/>
+      <c r="P30" s="146"/>
+      <c r="Q30" s="148"/>
+      <c r="R30" s="146"/>
+      <c r="S30" s="149"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="148"/>
-      <c r="C31" s="149"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="150"/>
-      <c r="F31" s="151"/>
-      <c r="G31" s="151"/>
-      <c r="H31" s="152"/>
-      <c r="I31" s="153"/>
-      <c r="J31" s="151"/>
-      <c r="K31" s="154"/>
-      <c r="L31" s="152"/>
-      <c r="M31" s="153"/>
-      <c r="N31" s="151"/>
-      <c r="O31" s="152"/>
-      <c r="P31" s="151"/>
-      <c r="Q31" s="153"/>
-      <c r="R31" s="151"/>
-      <c r="S31" s="109"/>
+      <c r="B31" s="150"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="152"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="153"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="155"/>
+      <c r="J31" s="153"/>
+      <c r="K31" s="156"/>
+      <c r="L31" s="154"/>
+      <c r="M31" s="155"/>
+      <c r="N31" s="153"/>
+      <c r="O31" s="154"/>
+      <c r="P31" s="153"/>
+      <c r="Q31" s="155"/>
+      <c r="R31" s="153"/>
+      <c r="S31" s="111"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="148"/>
-      <c r="C32" s="149" t="s">
+      <c r="B32" s="150"/>
+      <c r="C32" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="111"/>
-      <c r="E32" s="155"/>
-      <c r="F32" s="156"/>
-      <c r="G32" s="156"/>
-      <c r="H32" s="157"/>
-      <c r="I32" s="158"/>
-      <c r="J32" s="156"/>
-      <c r="K32" s="156"/>
-      <c r="L32" s="157"/>
-      <c r="M32" s="158"/>
-      <c r="N32" s="156"/>
-      <c r="O32" s="157"/>
-      <c r="P32" s="156"/>
-      <c r="Q32" s="158"/>
-      <c r="R32" s="156"/>
-      <c r="S32" s="159"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="158"/>
+      <c r="G32" s="158"/>
+      <c r="H32" s="159"/>
+      <c r="I32" s="160"/>
+      <c r="J32" s="158"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="159"/>
+      <c r="M32" s="160"/>
+      <c r="N32" s="158"/>
+      <c r="O32" s="159"/>
+      <c r="P32" s="158"/>
+      <c r="Q32" s="160"/>
+      <c r="R32" s="158"/>
+      <c r="S32" s="161"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="148"/>
-      <c r="C33" s="149"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="150"/>
-      <c r="F33" s="154"/>
-      <c r="G33" s="151"/>
-      <c r="H33" s="160"/>
-      <c r="I33" s="161"/>
-      <c r="J33" s="151"/>
-      <c r="K33" s="154"/>
-      <c r="L33" s="152"/>
-      <c r="M33" s="153"/>
-      <c r="N33" s="151"/>
-      <c r="O33" s="152"/>
-      <c r="P33" s="151"/>
-      <c r="Q33" s="153"/>
-      <c r="R33" s="151"/>
-      <c r="S33" s="109"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="151"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="152"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="153"/>
+      <c r="H33" s="162"/>
+      <c r="I33" s="163"/>
+      <c r="J33" s="153"/>
+      <c r="K33" s="156"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="155"/>
+      <c r="N33" s="153"/>
+      <c r="O33" s="154"/>
+      <c r="P33" s="153"/>
+      <c r="Q33" s="155"/>
+      <c r="R33" s="153"/>
+      <c r="S33" s="111"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="148"/>
-      <c r="C34" s="102" t="s">
-        <v>179</v>
-      </c>
-      <c r="D34" s="134"/>
-      <c r="E34" s="162"/>
-      <c r="F34" s="163"/>
-      <c r="G34" s="163"/>
-      <c r="H34" s="164"/>
-      <c r="I34" s="165"/>
-      <c r="J34" s="163"/>
-      <c r="K34" s="163"/>
-      <c r="L34" s="164"/>
-      <c r="M34" s="165"/>
-      <c r="N34" s="163"/>
-      <c r="O34" s="164"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="165"/>
-      <c r="R34" s="163"/>
-      <c r="S34" s="166"/>
-      <c r="U34" s="167"/>
-      <c r="V34" s="168" t="s">
+      <c r="B34" s="150"/>
+      <c r="C34" s="104" t="s">
         <v>180</v>
       </c>
+      <c r="D34" s="136"/>
+      <c r="E34" s="164"/>
+      <c r="F34" s="165"/>
+      <c r="G34" s="165"/>
+      <c r="H34" s="166"/>
+      <c r="I34" s="167"/>
+      <c r="J34" s="165"/>
+      <c r="K34" s="165"/>
+      <c r="L34" s="166"/>
+      <c r="M34" s="167"/>
+      <c r="N34" s="165"/>
+      <c r="O34" s="166"/>
+      <c r="P34" s="165"/>
+      <c r="Q34" s="167"/>
+      <c r="R34" s="165"/>
+      <c r="S34" s="168"/>
+      <c r="U34" s="169"/>
+      <c r="V34" s="170" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="169"/>
-      <c r="C35" s="170"/>
-      <c r="D35" s="121"/>
-      <c r="E35" s="171"/>
-      <c r="F35" s="172"/>
-      <c r="G35" s="172"/>
-      <c r="H35" s="173"/>
-      <c r="I35" s="174"/>
-      <c r="J35" s="172"/>
-      <c r="K35" s="172"/>
-      <c r="L35" s="173"/>
-      <c r="M35" s="174"/>
-      <c r="N35" s="172"/>
-      <c r="O35" s="173"/>
-      <c r="P35" s="172"/>
-      <c r="Q35" s="174"/>
-      <c r="R35" s="172"/>
-      <c r="S35" s="126"/>
-      <c r="U35" s="175"/>
-      <c r="V35" s="176" t="s">
-        <v>181</v>
+      <c r="B35" s="171"/>
+      <c r="C35" s="172"/>
+      <c r="D35" s="123"/>
+      <c r="E35" s="173"/>
+      <c r="F35" s="174"/>
+      <c r="G35" s="174"/>
+      <c r="H35" s="175"/>
+      <c r="I35" s="176"/>
+      <c r="J35" s="174"/>
+      <c r="K35" s="174"/>
+      <c r="L35" s="175"/>
+      <c r="M35" s="176"/>
+      <c r="N35" s="174"/>
+      <c r="O35" s="175"/>
+      <c r="P35" s="174"/>
+      <c r="Q35" s="176"/>
+      <c r="R35" s="174"/>
+      <c r="S35" s="128"/>
+      <c r="U35" s="177"/>
+      <c r="V35" s="178" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -10190,7 +10207,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00000000-0000-0000-0000-000000000000}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="00000000-0000-0000-0000-000000000000">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
   </ds:schemaRefs>

--- a/Documentation/LHO - M5 - JournalPlanif.xlsx
+++ b/Documentation/LHO - M5 - JournalPlanif.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <si>
     <t>date</t>
   </si>
@@ -281,46 +281,55 @@
     <t xml:space="preserve">Correction de fonctionnement + Optimisation et suppression de mem leak</t>
   </si>
   <si>
+    <t xml:space="preserve">Documentation "Proof Of Concept" du systeme de gestion des scans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction de l'accès à la BDD. Sécurisation de la connexion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction d'affichage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déplacement du modal ExportMD en composant réutilisable et ajout a NotePage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout de responsivité dans accueil, GridSplitter. Correction d'affichage du graphique donut. Suppression d'une erreur d'héritage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tests et mesures gain PoC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalisation de la documentation "Proof Of Concept" du systeme de gestion des scans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commencement du manuel utilisateur. Documentation des différents affichages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout de contenu dans le manuel utilisateur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commencement du support de présentation. Ajout du model et de la base de travail. Ajout des différentes polices utilisés.</t>
+  </si>
+  <si>
+    <t>02.06.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation des différents composants du projet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sécurisation d'une entrée utilisateur dans notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction d'affichage des document dans le menu notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test de fonctionnement global de l'application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déploiement de la première version sur Windows, Linux et MacOS. Avec Installateur universel pour windows Inno Setup.</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;-- A jour avec la BDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documentation "Proof Of Concept" du systeme de gestion des scans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correction de l'accès à la BDD. Sécurisation de la connexion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correction d'affichage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Déplacement du modal ExportMD en composant réutilisable et ajout a NotePage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajout de responsivité dans accueil, GridSplitter. Correction d'affichage du graphique donut. Suppression d'une erreur d'héritage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tests et mesures gain PoC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finalisation de la documentation "Proof Of Concept" du systeme de gestion des scans.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commencement du manuel utilisateur. Documentation des différents affichages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajout de contenu dans le manuel utilisateur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commencement du support de présentation. Ajout du model et de la base de travail. Ajout des différentes polices utilisés.</t>
-  </si>
-  <si>
-    <t>02.06.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Documentation des différents composants du projet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sécurisation d'une entrée utilisateur dans notes</t>
   </si>
   <si>
     <t xml:space="preserve">Par jour</t>
@@ -628,9 +637,9 @@
     <numFmt numFmtId="166" formatCode="0.0&quot; H&quot;;@"/>
     <numFmt numFmtId="167" formatCode="0&quot;H&quot;"/>
     <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="169" formatCode="[$-F400]h:mm:ss"/>
-    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="169" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="170" formatCode="[$-F400]h:mm:ss"/>
+    <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -1590,7 +1599,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="182">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1645,14 +1654,26 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="170" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="170" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="171" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -1924,7 +1945,7 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="169" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="left" indent="0" readingOrder="0" relativeIndent="0" shrinkToFit="0" textRotation="0" vertical="center" wrapText="0"/>
     </dxf>
     <dxf>
@@ -2264,7 +2285,7 @@
                   <c:v>55.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>71.5</c:v>
+                  <c:v>75.66666666666667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4879,8 +4900,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E70">
-  <autoFilter ref="B2:E70"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E73">
+  <autoFilter ref="B2:E73"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5444,7 +5465,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.8436955853733485e-002</v>
+        <v>1.7595307917888561e-002</v>
       </c>
       <c r="J3" s="12" t="str">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -5477,7 +5498,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.8436955853733485e-002</v>
+        <v>1.7595307917888561e-002</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -5510,7 +5531,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>5.8383693536822698e-002</v>
+        <v>5.5718475073313775e-002</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -5543,7 +5564,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.10447608317115641</v>
+        <v>9.9706744868035171e-002</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -5576,7 +5597,7 @@
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.34108368329406946</v>
+        <v>0.32551319648093835</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -5605,11 +5626,11 @@
       </c>
       <c r="H8" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>71.833333333333343</v>
+        <v>75.666666666666671</v>
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.44146266516439625</v>
+        <v>0.44379276637341147</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -5617,7 +5638,7 @@
       </c>
       <c r="K8" s="13">
         <f/>
-        <v>71.833333333333343</v>
+        <v>75.666666666666671</v>
       </c>
     </row>
     <row r="9">
@@ -5638,11 +5659,11 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>2.3833333333333333</v>
+        <v>6.3333333333333339</v>
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.4647137150466045e-002</v>
+        <v>3.714565004887585e-002</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -5650,7 +5671,7 @@
       </c>
       <c r="K9" s="14">
         <f/>
-        <v>2.3833333333333333</v>
+        <v>6.3333333333333339</v>
       </c>
     </row>
     <row r="10">
@@ -5675,7 +5696,7 @@
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>3.0728259756222474e-003</v>
+        <v>2.9325513196480934e-003</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -5698,7 +5719,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>162.71666666666667</v>
+        <v>170.50000000000003</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -6351,9 +6372,6 @@
       <c r="E57" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="G57" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="58" ht="28.5">
       <c r="B58" s="5">
@@ -6366,7 +6384,7 @@
         <v>12</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="59" ht="28.5">
@@ -6380,7 +6398,7 @@
         <v>12</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60">
@@ -6394,7 +6412,7 @@
         <v>19</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61">
@@ -6408,7 +6426,7 @@
         <v>19</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" ht="28.5">
@@ -6422,7 +6440,7 @@
         <v>19</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" ht="42.75">
@@ -6436,7 +6454,7 @@
         <v>19</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64">
@@ -6444,13 +6462,13 @@
         <v>46140</v>
       </c>
       <c r="C64" s="21">
-        <v>4.3749999999999997e-002</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" ht="28.800000000000001">
@@ -6464,7 +6482,7 @@
         <v>12</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" ht="28.800000000000001">
@@ -6478,7 +6496,7 @@
         <v>12</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67">
@@ -6492,7 +6510,7 @@
         <v>12</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" ht="28.800000000000001">
@@ -6506,12 +6524,12 @@
         <v>24</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C69" s="21">
         <v>0.125</v>
@@ -6520,7 +6538,7 @@
         <v>12</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="70">
@@ -6530,30 +6548,57 @@
       <c r="C70" s="21">
         <v>1.3888888888888888e-002</v>
       </c>
-      <c r="D70" s="22" t="s">
+      <c r="D70" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E70" s="23" t="s">
+      <c r="E70" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5">
+        <v>46177</v>
+      </c>
+      <c r="C71" s="21">
+        <v>3.4722222222222224e-002</v>
+      </c>
+      <c r="D71" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" s="23" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="5"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="8"/>
-    </row>
     <row r="72">
-      <c r="B72" s="5"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="8"/>
+      <c r="B72" s="24">
+        <v>46177</v>
+      </c>
+      <c r="C72" s="25">
+        <v>0.125</v>
+      </c>
+      <c r="D72" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="27" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="73">
-      <c r="B73" s="5"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="8"/>
+      <c r="B73" s="5">
+        <v>46177</v>
+      </c>
+      <c r="C73" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G73" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="74">
       <c r="B74" s="5"/>
@@ -6619,7 +6664,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{9126E532-4A90-4845-81CA-07333EE423A7}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{BCC6999D-ED5A-4D2A-8069-60D39E73A911}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6643,11 +6688,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -6661,47 +6706,47 @@
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24">
+      <c r="A3" s="28">
         <v>46042</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B3" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C3" s="25"/>
+      <c r="C3" s="29"/>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F3" s="26">
+        <v>104</v>
+      </c>
+      <c r="F3" s="30">
         <f t="shared" ref="F3:F8" si="0">SUMPRODUCT((MONTH($A$3:$A$152)=D3)*($A$3:$A$152&lt;&gt;"")*$B$3:$B$152)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="31">
         <f t="shared" ref="G3:G8" si="1">F3*24</f>
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24">
+      <c r="A4" s="28">
         <v>46043</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6710,22 +6755,22 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="26">
+        <v>105</v>
+      </c>
+      <c r="F4" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24">
+      <c r="A5" s="28">
         <v>46044</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6734,22 +6779,22 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F5" s="26">
+        <v>106</v>
+      </c>
+      <c r="F5" s="30">
         <f t="shared" si="0"/>
         <v>2.6805555555555558</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="31">
         <f t="shared" si="1"/>
         <v>64.333333333333343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24">
+      <c r="A6" s="28">
         <v>46045</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6758,22 +6803,22 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="26">
+        <v>107</v>
+      </c>
+      <c r="F6" s="30">
         <f t="shared" si="0"/>
-        <v>1.1687499999999997</v>
-      </c>
-      <c r="G6" s="27">
+        <v>1.2083333333333333</v>
+      </c>
+      <c r="G6" s="31">
         <f t="shared" si="1"/>
-        <v>28.049999999999994</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24">
+      <c r="A7" s="28">
         <v>46046</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6782,22 +6827,22 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="26">
+        <v>108</v>
+      </c>
+      <c r="F7" s="30">
         <f t="shared" si="0"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="31">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24">
+      <c r="A8" s="28">
         <v>46047</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6806,2071 +6851,2071 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F8" s="26">
+        <v>109</v>
+      </c>
+      <c r="F8" s="30">
         <f t="shared" si="0"/>
-        <v>1.3888888888888888e-002</v>
-      </c>
-      <c r="G8" s="27">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="G8" s="31">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>7.1666666666666661</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24">
+      <c r="A9" s="28">
         <v>46048</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
-      <c r="G9" s="27">
+      <c r="G9" s="31">
         <f>SUM(G3:G8)</f>
-        <v>99.716666666666669</v>
+        <v>107.50000000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24">
+      <c r="A10" s="28">
         <v>46049</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="24">
+      <c r="A11" s="28">
         <v>46050</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="24">
+      <c r="A12" s="28">
         <v>46051</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="24">
+      <c r="A13" s="28">
         <v>46052</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="24">
+      <c r="A14" s="28">
         <v>46053</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="24">
+      <c r="A15" s="28">
         <v>46054</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="24">
+      <c r="A16" s="28">
         <v>46055</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="24">
+      <c r="A17" s="28">
         <v>46056</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="24">
+      <c r="A18" s="28">
         <v>46057</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="24">
+      <c r="A19" s="28">
         <v>46058</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="24">
+      <c r="A20" s="28">
         <v>46059</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="24">
+      <c r="A21" s="28">
         <v>46060</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="24">
+      <c r="A22" s="28">
         <v>46061</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="24">
+      <c r="A23" s="28">
         <v>46062</v>
       </c>
-      <c r="B23" s="25">
+      <c r="B23" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="24">
+      <c r="A24" s="28">
         <v>46063</v>
       </c>
-      <c r="B24" s="25">
+      <c r="B24" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="24">
+      <c r="A25" s="28">
         <v>46064</v>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
     </row>
     <row r="26">
-      <c r="A26" s="24">
+      <c r="A26" s="28">
         <v>46065</v>
       </c>
-      <c r="B26" s="25">
+      <c r="B26" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C26"/>
-      <c r="F26" s="27"/>
+      <c r="F26" s="31"/>
     </row>
     <row r="27">
-      <c r="A27" s="24">
+      <c r="A27" s="28">
         <v>46066</v>
       </c>
-      <c r="B27" s="25">
+      <c r="B27" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24">
+      <c r="A28" s="28">
         <v>46067</v>
       </c>
-      <c r="B28" s="25">
+      <c r="B28" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24">
+      <c r="A29" s="28">
         <v>46068</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B29" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24">
+      <c r="A30" s="28">
         <v>46069</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B30" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24">
+      <c r="A31" s="28">
         <v>46070</v>
       </c>
-      <c r="B31" s="25">
+      <c r="B31" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24">
+      <c r="A32" s="28">
         <v>46071</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B32" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24">
+      <c r="A33" s="28">
         <v>46072</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B33" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24">
+      <c r="A34" s="28">
         <v>46073</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24">
+      <c r="A35" s="28">
         <v>46074</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B35" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24">
+      <c r="A36" s="28">
         <v>46075</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B36" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24">
+      <c r="A37" s="28">
         <v>46076</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B37" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24">
+      <c r="A38" s="28">
         <v>46077</v>
       </c>
-      <c r="B38" s="25">
+      <c r="B38" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24">
+      <c r="A39" s="28">
         <v>46078</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24">
+      <c r="A40" s="28">
         <v>46079</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24">
+      <c r="A41" s="28">
         <v>46080</v>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24">
+      <c r="A42" s="28">
         <v>46081</v>
       </c>
-      <c r="B42" s="25">
+      <c r="B42" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24">
+      <c r="A43" s="28">
         <v>46082</v>
       </c>
-      <c r="B43" s="25">
+      <c r="B43" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24">
+      <c r="A44" s="28">
         <v>46083</v>
       </c>
-      <c r="B44" s="25">
+      <c r="B44" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="24">
+      <c r="A45" s="28">
         <v>46084</v>
       </c>
-      <c r="B45" s="25">
+      <c r="B45" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="24">
+      <c r="A46" s="28">
         <v>46085</v>
       </c>
-      <c r="B46" s="25">
+      <c r="B46" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="24">
+      <c r="A47" s="28">
         <v>46086</v>
       </c>
-      <c r="B47" s="25">
+      <c r="B47" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="24">
+      <c r="A48" s="28">
         <v>46087</v>
       </c>
-      <c r="B48" s="25">
+      <c r="B48" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="24">
+      <c r="A49" s="28">
         <v>46088</v>
       </c>
-      <c r="B49" s="25">
+      <c r="B49" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="24">
+      <c r="A50" s="28">
         <v>46089</v>
       </c>
-      <c r="B50" s="25">
+      <c r="B50" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="24">
+      <c r="A51" s="28">
         <v>46090</v>
       </c>
-      <c r="B51" s="25">
+      <c r="B51" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="24">
+      <c r="A52" s="28">
         <v>46091</v>
       </c>
-      <c r="B52" s="25">
+      <c r="B52" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="24">
+      <c r="A53" s="28">
         <v>46092</v>
       </c>
-      <c r="B53" s="25">
+      <c r="B53" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="24">
+      <c r="A54" s="28">
         <v>46093</v>
       </c>
-      <c r="B54" s="25">
+      <c r="B54" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="24">
+      <c r="A55" s="28">
         <v>46094</v>
       </c>
-      <c r="B55" s="25">
+      <c r="B55" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="24">
+      <c r="A56" s="28">
         <v>46095</v>
       </c>
-      <c r="B56" s="25">
+      <c r="B56" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
-      <c r="C56" s="28">
+      <c r="C56" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="24">
+      <c r="A57" s="28">
         <v>46096</v>
       </c>
-      <c r="B57" s="25">
+      <c r="B57" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C57" s="28">
+      <c r="C57" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="24">
+      <c r="A58" s="28">
         <v>46097</v>
       </c>
-      <c r="B58" s="25">
+      <c r="B58" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C58" s="28">
+      <c r="C58" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="24">
+      <c r="A59" s="28">
         <v>46098</v>
       </c>
-      <c r="B59" s="25">
+      <c r="B59" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C59" s="28">
+      <c r="C59" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="24">
+      <c r="A60" s="28">
         <v>46099</v>
       </c>
-      <c r="B60" s="25">
+      <c r="B60" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C60" s="28">
+      <c r="C60" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="24">
+      <c r="A61" s="28">
         <v>46100</v>
       </c>
-      <c r="B61" s="25">
+      <c r="B61" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="C61" s="28">
+      <c r="C61" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="24">
+      <c r="A62" s="28">
         <v>46101</v>
       </c>
-      <c r="B62" s="25">
+      <c r="B62" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C62" s="28">
+      <c r="C62" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="24">
+      <c r="A63" s="28">
         <v>46102</v>
       </c>
-      <c r="B63" s="25">
+      <c r="B63" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C63" s="28">
+      <c r="C63" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="24">
+      <c r="A64" s="28">
         <v>46103</v>
       </c>
-      <c r="B64" s="25">
+      <c r="B64" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C64" s="28">
+      <c r="C64" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="24">
+      <c r="A65" s="28">
         <v>46104</v>
       </c>
-      <c r="B65" s="25">
+      <c r="B65" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
       </c>
-      <c r="C65" s="28">
+      <c r="C65" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="24">
+      <c r="A66" s="28">
         <v>46105</v>
       </c>
-      <c r="B66" s="25">
+      <c r="B66" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C66" s="28">
+      <c r="C66" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="24">
+      <c r="A67" s="28">
         <v>46106</v>
       </c>
-      <c r="B67" s="25">
+      <c r="B67" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C67" s="28">
+      <c r="C67" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24">
+      <c r="A68" s="28">
         <v>46107</v>
       </c>
-      <c r="B68" s="25">
+      <c r="B68" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="24">
+      <c r="A69" s="28">
         <v>46108</v>
       </c>
-      <c r="B69" s="25">
+      <c r="B69" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C69" s="28">
+      <c r="C69" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="24">
+      <c r="A70" s="28">
         <v>46109</v>
       </c>
-      <c r="B70" s="25">
+      <c r="B70" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C70" s="28">
+      <c r="C70" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="24">
+      <c r="A71" s="28">
         <v>46110</v>
       </c>
-      <c r="B71" s="25">
+      <c r="B71" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C71" s="28">
+      <c r="C71" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="24">
+      <c r="A72" s="28">
         <v>46111</v>
       </c>
-      <c r="B72" s="25">
+      <c r="B72" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C72" s="28">
+      <c r="C72" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="24">
+      <c r="A73" s="28">
         <v>46112</v>
       </c>
-      <c r="B73" s="25">
+      <c r="B73" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C73" s="28">
+      <c r="C73" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="24">
+      <c r="A74" s="28">
         <v>46113</v>
       </c>
-      <c r="B74" s="25">
+      <c r="B74" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C74" s="28">
+      <c r="C74" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="24">
+      <c r="A75" s="28">
         <v>46114</v>
       </c>
-      <c r="B75" s="25">
+      <c r="B75" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C75" s="28">
+      <c r="C75" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="24">
+      <c r="A76" s="28">
         <v>46115</v>
       </c>
-      <c r="B76" s="25">
+      <c r="B76" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C76" s="28">
+      <c r="C76" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="24">
+      <c r="A77" s="28">
         <v>46116</v>
       </c>
-      <c r="B77" s="25">
+      <c r="B77" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C77" s="28">
+      <c r="C77" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="24">
+      <c r="A78" s="28">
         <v>46117</v>
       </c>
-      <c r="B78" s="25">
+      <c r="B78" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C78" s="28">
+      <c r="C78" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="24">
+      <c r="A79" s="28">
         <v>46118</v>
       </c>
-      <c r="B79" s="25">
+      <c r="B79" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C79" s="28">
+      <c r="C79" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="24">
+      <c r="A80" s="28">
         <v>46119</v>
       </c>
-      <c r="B80" s="25">
+      <c r="B80" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C80" s="28">
+      <c r="C80" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="24">
+      <c r="A81" s="28">
         <v>46120</v>
       </c>
-      <c r="B81" s="25">
+      <c r="B81" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C81" s="28">
+      <c r="C81" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="24">
+      <c r="A82" s="28">
         <v>46121</v>
       </c>
-      <c r="B82" s="25">
+      <c r="B82" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C82" s="28">
+      <c r="C82" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="24">
+      <c r="A83" s="28">
         <v>46122</v>
       </c>
-      <c r="B83" s="25">
+      <c r="B83" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C83" s="28">
+      <c r="C83" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="24">
+      <c r="A84" s="28">
         <v>46123</v>
       </c>
-      <c r="B84" s="25">
+      <c r="B84" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C84" s="28">
+      <c r="C84" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="24">
+      <c r="A85" s="28">
         <v>46124</v>
       </c>
-      <c r="B85" s="25">
+      <c r="B85" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C85" s="28">
+      <c r="C85" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="24">
+      <c r="A86" s="28">
         <v>46125</v>
       </c>
-      <c r="B86" s="25">
+      <c r="B86" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C86" s="28">
+      <c r="C86" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="24">
+      <c r="A87" s="28">
         <v>46126</v>
       </c>
-      <c r="B87" s="25">
+      <c r="B87" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C87" s="28">
+      <c r="C87" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="24">
+      <c r="A88" s="28">
         <v>46127</v>
       </c>
-      <c r="B88" s="25">
+      <c r="B88" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C88" s="28">
+      <c r="C88" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="24">
+      <c r="A89" s="28">
         <v>46128</v>
       </c>
-      <c r="B89" s="25">
+      <c r="B89" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C89" s="28">
+      <c r="C89" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="24">
+      <c r="A90" s="28">
         <v>46129</v>
       </c>
-      <c r="B90" s="25">
+      <c r="B90" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C90" s="28">
+      <c r="C90" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="24">
+      <c r="A91" s="28">
         <v>46130</v>
       </c>
-      <c r="B91" s="25">
+      <c r="B91" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C91" s="28">
+      <c r="C91" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="24">
+      <c r="A92" s="28">
         <v>46131</v>
       </c>
-      <c r="B92" s="25">
+      <c r="B92" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C92" s="28">
+      <c r="C92" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="24">
+      <c r="A93" s="28">
         <v>46132</v>
       </c>
-      <c r="B93" s="25">
+      <c r="B93" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C93" s="28">
+      <c r="C93" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="24">
+      <c r="A94" s="28">
         <v>46133</v>
       </c>
-      <c r="B94" s="25">
+      <c r="B94" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="24">
+      <c r="A95" s="28">
         <v>46134</v>
       </c>
-      <c r="B95" s="25">
+      <c r="B95" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
-      <c r="C95" s="28">
+      <c r="C95" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="24">
+      <c r="A96" s="28">
         <v>46135</v>
       </c>
-      <c r="B96" s="25">
+      <c r="B96" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
-      <c r="C96" s="28">
+      <c r="C96" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="24">
+      <c r="A97" s="28">
         <v>46136</v>
       </c>
-      <c r="B97" s="25">
+      <c r="B97" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C97" s="28">
+      <c r="C97" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="24">
+      <c r="A98" s="28">
         <v>46137</v>
       </c>
-      <c r="B98" s="25">
+      <c r="B98" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C98" s="28">
+      <c r="C98" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="24">
+      <c r="A99" s="28">
         <v>46138</v>
       </c>
-      <c r="B99" s="25">
+      <c r="B99" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C99" s="28">
+      <c r="C99" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="24">
+      <c r="A100" s="28">
         <v>46139</v>
       </c>
-      <c r="B100" s="25">
+      <c r="B100" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C100" s="28">
+      <c r="C100" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="24">
+      <c r="A101" s="28">
         <v>46140</v>
       </c>
-      <c r="B101" s="25">
+      <c r="B101" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
-        <v>0.18958333333333333</v>
-      </c>
-      <c r="C101" s="28">
+        <v>0.22916666666666669</v>
+      </c>
+      <c r="C101" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
-        <v>0.18958333333333333</v>
+        <v>0.22916666666666669</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="24">
+      <c r="A102" s="28">
         <v>46141</v>
       </c>
-      <c r="B102" s="25">
+      <c r="B102" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C102" s="28">
+      <c r="C102" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="24">
+      <c r="A103" s="28">
         <v>46142</v>
       </c>
-      <c r="B103" s="25">
+      <c r="B103" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C103" s="28">
+      <c r="C103" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="24">
+      <c r="A104" s="28">
         <v>46143</v>
       </c>
-      <c r="B104" s="25">
+      <c r="B104" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C104" s="28">
+      <c r="C104" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="24">
+      <c r="A105" s="28">
         <v>46144</v>
       </c>
-      <c r="B105" s="25">
+      <c r="B105" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C105" s="28">
+      <c r="C105" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="24">
+      <c r="A106" s="28">
         <v>46145</v>
       </c>
-      <c r="B106" s="25">
+      <c r="B106" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C106" s="28">
+      <c r="C106" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="24">
+      <c r="A107" s="28">
         <v>46146</v>
       </c>
-      <c r="B107" s="25">
+      <c r="B107" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C107" s="28">
+      <c r="C107" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="24">
+      <c r="A108" s="28">
         <v>46147</v>
       </c>
-      <c r="B108" s="25">
+      <c r="B108" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C108" s="28">
+      <c r="C108" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="24">
+      <c r="A109" s="28">
         <v>46148</v>
       </c>
-      <c r="B109" s="25">
+      <c r="B109" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C109" s="28">
+      <c r="C109" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="24">
+      <c r="A110" s="28">
         <v>46149</v>
       </c>
-      <c r="B110" s="25">
+      <c r="B110" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C110" s="28">
+      <c r="C110" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="24">
+      <c r="A111" s="28">
         <v>46150</v>
       </c>
-      <c r="B111" s="25">
+      <c r="B111" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C111" s="28">
+      <c r="C111" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="24">
+      <c r="A112" s="28">
         <v>46151</v>
       </c>
-      <c r="B112" s="25">
+      <c r="B112" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C112" s="28">
+      <c r="C112" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="24">
+      <c r="A113" s="28">
         <v>46152</v>
       </c>
-      <c r="B113" s="25">
+      <c r="B113" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C113" s="28">
+      <c r="C113" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="24">
+      <c r="A114" s="28">
         <v>46153</v>
       </c>
-      <c r="B114" s="25">
+      <c r="B114" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C114" s="28">
+      <c r="C114" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="24">
+      <c r="A115" s="28">
         <v>46154</v>
       </c>
-      <c r="B115" s="25">
+      <c r="B115" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C115" s="28">
+      <c r="C115" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="24">
+      <c r="A116" s="28">
         <v>46155</v>
       </c>
-      <c r="B116" s="25">
+      <c r="B116" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A116,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C116" s="28"/>
+      <c r="C116" s="32"/>
     </row>
     <row r="117">
-      <c r="A117" s="24">
+      <c r="A117" s="28">
         <v>46156</v>
       </c>
-      <c r="B117" s="25">
+      <c r="B117" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A117,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C117" s="28"/>
+      <c r="C117" s="32"/>
     </row>
     <row r="118">
-      <c r="A118" s="24">
+      <c r="A118" s="28">
         <v>46157</v>
       </c>
-      <c r="B118" s="25">
+      <c r="B118" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A118,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C118" s="28"/>
+      <c r="C118" s="32"/>
     </row>
     <row r="119">
-      <c r="A119" s="24">
+      <c r="A119" s="28">
         <v>46158</v>
       </c>
-      <c r="B119" s="25">
+      <c r="B119" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A119,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C119" s="28"/>
+      <c r="C119" s="32"/>
     </row>
     <row r="120">
-      <c r="A120" s="24">
+      <c r="A120" s="28">
         <v>46159</v>
       </c>
-      <c r="B120" s="25">
+      <c r="B120" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A120,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C120" s="28"/>
+      <c r="C120" s="32"/>
     </row>
     <row r="121">
-      <c r="A121" s="24">
+      <c r="A121" s="28">
         <v>46160</v>
       </c>
-      <c r="B121" s="25">
+      <c r="B121" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A121,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C121" s="28"/>
+      <c r="C121" s="32"/>
     </row>
     <row r="122">
-      <c r="A122" s="24">
+      <c r="A122" s="28">
         <v>46161</v>
       </c>
-      <c r="B122" s="25">
+      <c r="B122" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A122,Journal[Temps])</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="C122" s="28"/>
+      <c r="C122" s="32"/>
     </row>
     <row r="123">
-      <c r="A123" s="24">
+      <c r="A123" s="28">
         <v>46162</v>
       </c>
-      <c r="B123" s="25">
+      <c r="B123" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A123,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C123" s="28"/>
+      <c r="C123" s="32"/>
     </row>
     <row r="124">
-      <c r="A124" s="24">
+      <c r="A124" s="28">
         <v>46163</v>
       </c>
-      <c r="B124" s="25">
+      <c r="B124" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A124,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C124" s="28"/>
+      <c r="C124" s="32"/>
     </row>
     <row r="125">
-      <c r="A125" s="24">
+      <c r="A125" s="28">
         <v>46164</v>
       </c>
-      <c r="B125" s="25">
+      <c r="B125" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A125,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C125" s="28"/>
+      <c r="C125" s="32"/>
     </row>
     <row r="126">
-      <c r="A126" s="24">
+      <c r="A126" s="28">
         <v>46165</v>
       </c>
-      <c r="B126" s="25">
+      <c r="B126" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A126,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C126" s="28"/>
+      <c r="C126" s="32"/>
     </row>
     <row r="127">
-      <c r="A127" s="24">
+      <c r="A127" s="28">
         <v>46166</v>
       </c>
-      <c r="B127" s="25">
+      <c r="B127" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A127,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C127" s="28"/>
+      <c r="C127" s="32"/>
     </row>
     <row r="128">
-      <c r="A128" s="24">
+      <c r="A128" s="28">
         <v>46167</v>
       </c>
-      <c r="B128" s="25">
+      <c r="B128" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A128,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C128" s="28"/>
+      <c r="C128" s="32"/>
     </row>
     <row r="129">
-      <c r="A129" s="24">
+      <c r="A129" s="28">
         <v>46168</v>
       </c>
-      <c r="B129" s="25">
+      <c r="B129" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A129,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C129" s="28"/>
+      <c r="C129" s="32"/>
     </row>
     <row r="130">
-      <c r="A130" s="24">
+      <c r="A130" s="28">
         <v>46169</v>
       </c>
-      <c r="B130" s="25">
+      <c r="B130" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A130,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C130" s="28"/>
+      <c r="C130" s="32"/>
     </row>
     <row r="131">
-      <c r="A131" s="24">
+      <c r="A131" s="28">
         <v>46170</v>
       </c>
-      <c r="B131" s="25">
+      <c r="B131" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A131,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C131" s="28"/>
+      <c r="C131" s="32"/>
     </row>
     <row r="132">
-      <c r="A132" s="24">
+      <c r="A132" s="28">
         <v>46171</v>
       </c>
-      <c r="B132" s="25">
+      <c r="B132" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A132,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C132" s="28"/>
+      <c r="C132" s="32"/>
     </row>
     <row r="133">
-      <c r="A133" s="24">
+      <c r="A133" s="28">
         <v>46172</v>
       </c>
-      <c r="B133" s="25">
+      <c r="B133" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A133,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C133" s="28"/>
+      <c r="C133" s="32"/>
     </row>
     <row r="134">
-      <c r="A134" s="24">
+      <c r="A134" s="28">
         <v>46173</v>
       </c>
-      <c r="B134" s="25">
+      <c r="B134" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A134,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C134" s="28"/>
+      <c r="C134" s="32"/>
     </row>
     <row r="135">
-      <c r="A135" s="24">
+      <c r="A135" s="28">
         <v>46174</v>
       </c>
-      <c r="B135" s="25">
+      <c r="B135" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A135,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C135" s="28"/>
+      <c r="C135" s="32"/>
     </row>
     <row r="136">
-      <c r="A136" s="24">
+      <c r="A136" s="28">
         <v>46175</v>
       </c>
-      <c r="B136" s="25">
+      <c r="B136" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A136,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C136" s="28"/>
+      <c r="C136" s="32"/>
     </row>
     <row r="137">
-      <c r="A137" s="24">
+      <c r="A137" s="28">
         <v>46176</v>
       </c>
-      <c r="B137" s="25">
+      <c r="B137" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A137,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C137" s="28"/>
+      <c r="C137" s="32"/>
     </row>
     <row r="138">
-      <c r="A138" s="24">
+      <c r="A138" s="28">
         <v>46177</v>
       </c>
-      <c r="B138" s="25">
+      <c r="B138" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A138,Journal[Temps])</f>
-        <v>1.3888888888888888e-002</v>
-      </c>
-      <c r="C138" s="28"/>
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="C138" s="32"/>
     </row>
     <row r="139">
-      <c r="A139" s="24">
+      <c r="A139" s="28">
         <v>46178</v>
       </c>
-      <c r="B139" s="25">
+      <c r="B139" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A139,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C139" s="28"/>
+      <c r="C139" s="32"/>
     </row>
     <row r="140">
-      <c r="A140" s="24">
+      <c r="A140" s="28">
         <v>46179</v>
       </c>
-      <c r="B140" s="25">
+      <c r="B140" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A140,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C140" s="28"/>
+      <c r="C140" s="32"/>
     </row>
     <row r="141">
-      <c r="A141" s="24">
+      <c r="A141" s="28">
         <v>46180</v>
       </c>
-      <c r="B141" s="25">
+      <c r="B141" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A141,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C141" s="28"/>
+      <c r="C141" s="32"/>
     </row>
     <row r="142">
-      <c r="A142" s="24">
+      <c r="A142" s="28">
         <v>46181</v>
       </c>
-      <c r="B142" s="25">
+      <c r="B142" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A142,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C142" s="28"/>
+      <c r="C142" s="32"/>
     </row>
     <row r="143">
-      <c r="A143" s="24">
+      <c r="A143" s="28">
         <v>46182</v>
       </c>
-      <c r="B143" s="25">
+      <c r="B143" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A143,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C143" s="28"/>
+      <c r="C143" s="32"/>
     </row>
     <row r="144">
-      <c r="A144" s="24">
+      <c r="A144" s="28">
         <v>46183</v>
       </c>
-      <c r="B144" s="25">
+      <c r="B144" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A144,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C144" s="28"/>
+      <c r="C144" s="32"/>
     </row>
     <row r="145">
-      <c r="A145" s="24">
+      <c r="A145" s="28">
         <v>46184</v>
       </c>
-      <c r="B145" s="25">
+      <c r="B145" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A145,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C145" s="28"/>
+      <c r="C145" s="32"/>
     </row>
     <row r="146">
-      <c r="A146" s="24">
+      <c r="A146" s="28">
         <v>46185</v>
       </c>
-      <c r="B146" s="25">
+      <c r="B146" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A146,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C146" s="28"/>
+      <c r="C146" s="32"/>
     </row>
     <row r="147">
-      <c r="A147" s="24">
+      <c r="A147" s="28">
         <v>46186</v>
       </c>
-      <c r="B147" s="25">
+      <c r="B147" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A147,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C147" s="28"/>
+      <c r="C147" s="32"/>
     </row>
     <row r="148">
-      <c r="A148" s="24">
+      <c r="A148" s="28">
         <v>46187</v>
       </c>
-      <c r="B148" s="25">
+      <c r="B148" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A148,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C148" s="28"/>
+      <c r="C148" s="32"/>
     </row>
     <row r="149">
-      <c r="A149" s="24">
+      <c r="A149" s="28">
         <v>46188</v>
       </c>
-      <c r="B149" s="25">
+      <c r="B149" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A149,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C149" s="28"/>
+      <c r="C149" s="32"/>
     </row>
     <row r="150">
-      <c r="A150" s="24">
+      <c r="A150" s="28">
         <v>46189</v>
       </c>
-      <c r="B150" s="25">
+      <c r="B150" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A150,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C150" s="28"/>
+      <c r="C150" s="32"/>
     </row>
     <row r="151">
-      <c r="A151" s="24">
+      <c r="A151" s="28">
         <v>46190</v>
       </c>
-      <c r="B151" s="25">
+      <c r="B151" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A151,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C151" s="28"/>
+      <c r="C151" s="32"/>
     </row>
     <row r="152">
-      <c r="A152" s="24">
+      <c r="A152" s="28">
         <v>46191</v>
       </c>
-      <c r="B152" s="25">
+      <c r="B152" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A152,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C152" s="28"/>
+      <c r="C152" s="32"/>
     </row>
     <row r="153">
-      <c r="A153" s="24"/>
-      <c r="B153" s="29"/>
-      <c r="C153" s="28"/>
+      <c r="A153" s="28"/>
+      <c r="B153" s="33"/>
+      <c r="C153" s="32"/>
     </row>
     <row r="154">
-      <c r="A154" s="24"/>
-      <c r="B154" s="29"/>
-      <c r="C154" s="28"/>
+      <c r="A154" s="28"/>
+      <c r="B154" s="33"/>
+      <c r="C154" s="32"/>
     </row>
     <row r="155">
-      <c r="A155" s="24"/>
-      <c r="B155" s="29"/>
-      <c r="C155" s="28"/>
+      <c r="A155" s="28"/>
+      <c r="B155" s="33"/>
+      <c r="C155" s="32"/>
     </row>
     <row r="156">
-      <c r="A156" s="24"/>
-      <c r="B156" s="29"/>
-      <c r="C156" s="28"/>
+      <c r="A156" s="28"/>
+      <c r="B156" s="33"/>
+      <c r="C156" s="32"/>
     </row>
     <row r="157">
-      <c r="A157" s="24"/>
-      <c r="B157" s="29"/>
-      <c r="C157" s="28"/>
+      <c r="A157" s="28"/>
+      <c r="B157" s="33"/>
+      <c r="C157" s="32"/>
     </row>
     <row r="158">
-      <c r="A158" s="24"/>
-      <c r="B158" s="29"/>
-      <c r="C158" s="28"/>
+      <c r="A158" s="28"/>
+      <c r="B158" s="33"/>
+      <c r="C158" s="32"/>
     </row>
     <row r="159">
-      <c r="A159" s="24"/>
-      <c r="B159" s="29"/>
-      <c r="C159" s="28"/>
+      <c r="A159" s="28"/>
+      <c r="B159" s="33"/>
+      <c r="C159" s="32"/>
     </row>
     <row r="160">
-      <c r="A160" s="24"/>
-      <c r="B160" s="29"/>
+      <c r="A160" s="28"/>
+      <c r="B160" s="33"/>
     </row>
     <row r="161">
-      <c r="A161" s="24"/>
-      <c r="B161" s="29"/>
+      <c r="A161" s="28"/>
+      <c r="B161" s="33"/>
     </row>
     <row r="162">
-      <c r="A162" s="24"/>
-      <c r="B162" s="29"/>
+      <c r="A162" s="28"/>
+      <c r="B162" s="33"/>
     </row>
     <row r="163">
-      <c r="A163" s="24"/>
-      <c r="B163" s="29"/>
+      <c r="A163" s="28"/>
+      <c r="B163" s="33"/>
     </row>
     <row r="164">
-      <c r="A164" s="24"/>
-      <c r="B164" s="29"/>
+      <c r="A164" s="28"/>
+      <c r="B164" s="33"/>
     </row>
     <row r="165">
-      <c r="A165" s="24"/>
-      <c r="B165" s="29"/>
+      <c r="A165" s="28"/>
+      <c r="B165" s="33"/>
     </row>
     <row r="166">
-      <c r="A166" s="24"/>
-      <c r="B166" s="29"/>
+      <c r="A166" s="28"/>
+      <c r="B166" s="33"/>
     </row>
     <row r="167">
-      <c r="A167" s="24"/>
-      <c r="B167" s="29"/>
+      <c r="A167" s="28"/>
+      <c r="B167" s="33"/>
     </row>
     <row r="168">
-      <c r="A168" s="24"/>
-      <c r="B168" s="29"/>
+      <c r="A168" s="28"/>
+      <c r="B168" s="33"/>
     </row>
     <row r="169">
-      <c r="A169" s="24"/>
-      <c r="B169" s="29"/>
+      <c r="A169" s="28"/>
+      <c r="B169" s="33"/>
     </row>
     <row r="170">
-      <c r="A170" s="24"/>
-      <c r="B170" s="29"/>
+      <c r="A170" s="28"/>
+      <c r="B170" s="33"/>
     </row>
     <row r="171">
-      <c r="A171" s="24"/>
-      <c r="B171" s="29"/>
+      <c r="A171" s="28"/>
+      <c r="B171" s="33"/>
     </row>
     <row r="172">
-      <c r="A172" s="24"/>
-      <c r="B172" s="29"/>
+      <c r="A172" s="28"/>
+      <c r="B172" s="33"/>
     </row>
     <row r="173">
-      <c r="A173" s="24"/>
-      <c r="B173" s="29"/>
+      <c r="A173" s="28"/>
+      <c r="B173" s="33"/>
     </row>
     <row r="174">
-      <c r="A174" s="24"/>
-      <c r="B174" s="29"/>
+      <c r="A174" s="28"/>
+      <c r="B174" s="33"/>
     </row>
     <row r="175">
-      <c r="A175" s="24"/>
-      <c r="B175" s="29"/>
+      <c r="A175" s="28"/>
+      <c r="B175" s="33"/>
     </row>
     <row r="176">
-      <c r="A176" s="24"/>
-      <c r="B176" s="29"/>
+      <c r="A176" s="28"/>
+      <c r="B176" s="33"/>
     </row>
     <row r="177">
-      <c r="A177" s="24"/>
-      <c r="B177" s="29"/>
+      <c r="A177" s="28"/>
+      <c r="B177" s="33"/>
     </row>
     <row r="178">
-      <c r="A178" s="24"/>
-      <c r="B178" s="29"/>
+      <c r="A178" s="28"/>
+      <c r="B178" s="33"/>
     </row>
     <row r="179">
-      <c r="A179" s="24"/>
-      <c r="B179" s="29"/>
+      <c r="A179" s="28"/>
+      <c r="B179" s="33"/>
     </row>
     <row r="180">
-      <c r="A180" s="24"/>
-      <c r="B180" s="29"/>
+      <c r="A180" s="28"/>
+      <c r="B180" s="33"/>
     </row>
     <row r="181">
-      <c r="A181" s="24"/>
-      <c r="B181" s="29"/>
+      <c r="A181" s="28"/>
+      <c r="B181" s="33"/>
     </row>
     <row r="182">
-      <c r="A182" s="24"/>
-      <c r="B182" s="29"/>
+      <c r="A182" s="28"/>
+      <c r="B182" s="33"/>
     </row>
     <row r="183">
-      <c r="A183" s="24"/>
-      <c r="B183" s="29"/>
+      <c r="A183" s="28"/>
+      <c r="B183" s="33"/>
     </row>
     <row r="184">
-      <c r="A184" s="24"/>
-      <c r="B184" s="29"/>
+      <c r="A184" s="28"/>
+      <c r="B184" s="33"/>
     </row>
     <row r="185">
-      <c r="A185" s="24"/>
-      <c r="B185" s="29"/>
+      <c r="A185" s="28"/>
+      <c r="B185" s="33"/>
     </row>
     <row r="186">
-      <c r="A186" s="24"/>
-      <c r="B186" s="29"/>
+      <c r="A186" s="28"/>
+      <c r="B186" s="33"/>
     </row>
     <row r="187">
-      <c r="A187" s="24"/>
-      <c r="B187" s="29"/>
+      <c r="A187" s="28"/>
+      <c r="B187" s="33"/>
     </row>
     <row r="188">
-      <c r="A188" s="29"/>
-      <c r="B188" s="29"/>
+      <c r="A188" s="33"/>
+      <c r="B188" s="33"/>
     </row>
     <row r="189">
-      <c r="A189" s="29"/>
-      <c r="B189" s="29"/>
+      <c r="A189" s="33"/>
+      <c r="B189" s="33"/>
     </row>
     <row r="190">
-      <c r="A190" s="29"/>
-      <c r="B190" s="29"/>
+      <c r="A190" s="33"/>
+      <c r="B190" s="33"/>
     </row>
     <row r="191">
-      <c r="A191" s="29"/>
-      <c r="B191" s="29"/>
+      <c r="A191" s="33"/>
+      <c r="B191" s="33"/>
     </row>
     <row r="192">
-      <c r="A192" s="29"/>
-      <c r="B192" s="29"/>
+      <c r="A192" s="33"/>
+      <c r="B192" s="33"/>
     </row>
     <row r="193">
-      <c r="A193" s="29"/>
-      <c r="B193" s="29"/>
+      <c r="A193" s="33"/>
+      <c r="B193" s="33"/>
     </row>
     <row r="194">
-      <c r="A194" s="29"/>
-      <c r="B194" s="29"/>
+      <c r="A194" s="33"/>
+      <c r="B194" s="33"/>
     </row>
     <row r="195">
-      <c r="A195" s="29"/>
-      <c r="B195" s="29"/>
+      <c r="A195" s="33"/>
+      <c r="B195" s="33"/>
     </row>
     <row r="196">
-      <c r="A196" s="29"/>
-      <c r="B196" s="29"/>
+      <c r="A196" s="33"/>
+      <c r="B196" s="33"/>
     </row>
     <row r="197">
-      <c r="A197" s="29"/>
-      <c r="B197" s="29"/>
+      <c r="A197" s="33"/>
+      <c r="B197" s="33"/>
     </row>
     <row r="198">
-      <c r="A198" s="29"/>
-      <c r="B198" s="29"/>
+      <c r="A198" s="33"/>
+      <c r="B198" s="33"/>
     </row>
     <row r="199">
-      <c r="A199" s="29"/>
-      <c r="B199" s="29"/>
+      <c r="A199" s="33"/>
+      <c r="B199" s="33"/>
     </row>
     <row r="200">
-      <c r="A200" s="29"/>
-      <c r="B200" s="29"/>
+      <c r="A200" s="33"/>
+      <c r="B200" s="33"/>
     </row>
     <row r="201">
-      <c r="A201" s="29"/>
-      <c r="B201" s="29"/>
+      <c r="A201" s="33"/>
+      <c r="B201" s="33"/>
     </row>
     <row r="202">
-      <c r="A202" s="29"/>
-      <c r="B202" s="29"/>
+      <c r="A202" s="33"/>
+      <c r="B202" s="33"/>
     </row>
     <row r="203">
-      <c r="A203" s="29"/>
-      <c r="B203" s="29"/>
+      <c r="A203" s="33"/>
+      <c r="B203" s="33"/>
     </row>
     <row r="204">
-      <c r="A204" s="29"/>
-      <c r="B204" s="29"/>
+      <c r="A204" s="33"/>
+      <c r="B204" s="33"/>
     </row>
     <row r="205">
-      <c r="A205" s="29"/>
-      <c r="B205" s="29"/>
+      <c r="A205" s="33"/>
+      <c r="B205" s="33"/>
     </row>
     <row r="206">
-      <c r="A206" s="29"/>
-      <c r="B206" s="29"/>
+      <c r="A206" s="33"/>
+      <c r="B206" s="33"/>
     </row>
     <row r="207">
-      <c r="A207" s="29"/>
-      <c r="B207" s="29"/>
+      <c r="A207" s="33"/>
+      <c r="B207" s="33"/>
     </row>
     <row r="208">
-      <c r="A208" s="29"/>
-      <c r="B208" s="29"/>
+      <c r="A208" s="33"/>
+      <c r="B208" s="33"/>
     </row>
     <row r="209">
-      <c r="A209" s="29"/>
-      <c r="B209" s="29"/>
+      <c r="A209" s="33"/>
+      <c r="B209" s="33"/>
     </row>
     <row r="210">
-      <c r="A210" s="29"/>
-      <c r="B210" s="29"/>
+      <c r="A210" s="33"/>
+      <c r="B210" s="33"/>
     </row>
     <row r="211">
-      <c r="A211" s="29"/>
-      <c r="B211" s="29"/>
+      <c r="A211" s="33"/>
+      <c r="B211" s="33"/>
     </row>
     <row r="212">
-      <c r="A212" s="29"/>
-      <c r="B212" s="29"/>
+      <c r="A212" s="33"/>
+      <c r="B212" s="33"/>
     </row>
     <row r="213">
-      <c r="A213" s="29"/>
-      <c r="B213" s="29"/>
+      <c r="A213" s="33"/>
+      <c r="B213" s="33"/>
     </row>
     <row r="214">
-      <c r="A214" s="29"/>
-      <c r="B214" s="29"/>
+      <c r="A214" s="33"/>
+      <c r="B214" s="33"/>
     </row>
     <row r="215">
-      <c r="A215" s="29"/>
-      <c r="B215" s="29"/>
+      <c r="A215" s="33"/>
+      <c r="B215" s="33"/>
     </row>
     <row r="216">
-      <c r="A216" s="29"/>
-      <c r="B216" s="29"/>
+      <c r="A216" s="33"/>
+      <c r="B216" s="33"/>
     </row>
     <row r="217">
-      <c r="A217" s="29"/>
-      <c r="B217" s="29"/>
+      <c r="A217" s="33"/>
+      <c r="B217" s="33"/>
     </row>
     <row r="218">
-      <c r="A218" s="29"/>
-      <c r="B218" s="29"/>
+      <c r="A218" s="33"/>
+      <c r="B218" s="33"/>
     </row>
     <row r="219">
-      <c r="A219" s="29"/>
-      <c r="B219" s="29"/>
+      <c r="A219" s="33"/>
+      <c r="B219" s="33"/>
     </row>
     <row r="220">
-      <c r="A220" s="29"/>
-      <c r="B220" s="29"/>
+      <c r="A220" s="33"/>
+      <c r="B220" s="33"/>
     </row>
     <row r="221">
-      <c r="A221" s="29"/>
-      <c r="B221" s="29"/>
+      <c r="A221" s="33"/>
+      <c r="B221" s="33"/>
     </row>
     <row r="222">
-      <c r="A222" s="29"/>
-      <c r="B222" s="29"/>
+      <c r="A222" s="33"/>
+      <c r="B222" s="33"/>
     </row>
     <row r="223">
-      <c r="A223" s="29"/>
-      <c r="B223" s="29"/>
+      <c r="A223" s="33"/>
+      <c r="B223" s="33"/>
     </row>
     <row r="224">
-      <c r="A224" s="29"/>
-      <c r="B224" s="29"/>
+      <c r="A224" s="33"/>
+      <c r="B224" s="33"/>
     </row>
     <row r="225">
-      <c r="A225" s="29"/>
-      <c r="B225" s="29"/>
+      <c r="A225" s="33"/>
+      <c r="B225" s="33"/>
     </row>
     <row r="226">
-      <c r="A226" s="29"/>
-      <c r="B226" s="29"/>
+      <c r="A226" s="33"/>
+      <c r="B226" s="33"/>
     </row>
     <row r="227">
-      <c r="A227" s="29"/>
-      <c r="B227" s="29"/>
+      <c r="A227" s="33"/>
+      <c r="B227" s="33"/>
     </row>
     <row r="228">
-      <c r="A228" s="29"/>
-      <c r="B228" s="29"/>
+      <c r="A228" s="33"/>
+      <c r="B228" s="33"/>
     </row>
     <row r="229">
-      <c r="A229" s="29"/>
-      <c r="B229" s="29"/>
+      <c r="A229" s="33"/>
+      <c r="B229" s="33"/>
     </row>
     <row r="230">
-      <c r="A230" s="29"/>
-      <c r="B230" s="29"/>
+      <c r="A230" s="33"/>
+      <c r="B230" s="33"/>
     </row>
     <row r="231">
-      <c r="A231" s="29"/>
-      <c r="B231" s="29"/>
+      <c r="A231" s="33"/>
+      <c r="B231" s="33"/>
     </row>
     <row r="232">
-      <c r="A232" s="29"/>
-      <c r="B232" s="29"/>
+      <c r="A232" s="33"/>
+      <c r="B232" s="33"/>
     </row>
     <row r="233">
-      <c r="A233" s="29"/>
-      <c r="B233" s="29"/>
+      <c r="A233" s="33"/>
+      <c r="B233" s="33"/>
     </row>
     <row r="234">
-      <c r="A234" s="29"/>
-      <c r="B234" s="29"/>
+      <c r="A234" s="33"/>
+      <c r="B234" s="33"/>
     </row>
     <row r="235">
-      <c r="A235" s="29"/>
-      <c r="B235" s="29"/>
+      <c r="A235" s="33"/>
+      <c r="B235" s="33"/>
     </row>
     <row r="236">
-      <c r="A236" s="29"/>
-      <c r="B236" s="29"/>
+      <c r="A236" s="33"/>
+      <c r="B236" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8892,2034 +8937,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="30" width="6"/>
+    <col customWidth="1" min="12" max="12" style="34" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="30" width="6"/>
+    <col customWidth="1" min="23" max="23" style="34" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="30" width="6"/>
+    <col customWidth="1" min="30" max="30" style="34" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" s="34" t="s">
+    <row r="1" s="35" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" s="35" t="s">
+      <c r="E1" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="34" t="s">
+      <c r="H1" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="L1" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="M1" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="N1" s="36" t="s">
+      <c r="K1" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="L1" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="M1" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="37" t="s">
+      <c r="O1" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="P1" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q1" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="R1" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="S1" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="T1" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="U1" s="34" t="s">
+      <c r="R1" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="V1" s="36" t="s">
+      <c r="S1" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="W1" s="39" t="s">
+      <c r="T1" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="X1" s="34" t="s">
+      <c r="U1" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="Y1" s="34" t="s">
+      <c r="V1" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="Z1" s="36" t="s">
+      <c r="W1" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="AA1" s="40" t="s">
+      <c r="X1" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="AB1" s="41" t="s">
+      <c r="Y1" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="AC1" s="41" t="s">
+      <c r="Z1" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="AD1" s="38" t="s">
+      <c r="AA1" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="AE1" s="42" t="s">
+      <c r="AB1" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="AF1" s="43" t="s">
+      <c r="AC1" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="AG1" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="AH1" s="44" t="s">
+      <c r="AD1" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="AI1" s="44" t="s">
+      <c r="AE1" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="AJ1" s="44" t="s">
+      <c r="AF1" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="AK1" s="41" t="s">
+      <c r="AG1" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH1" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="AL1" s="45"/>
-      <c r="AM1" s="45"/>
-      <c r="AN1" s="45"/>
-      <c r="AO1" s="45"/>
-      <c r="AP1" s="45"/>
-      <c r="AQ1" s="45"/>
-      <c r="AR1" s="45"/>
-      <c r="AS1" s="45"/>
-      <c r="AT1" s="45"/>
-      <c r="AU1" s="45"/>
+      <c r="AI1" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ1" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK1" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL1" s="49"/>
+      <c r="AM1" s="49"/>
+      <c r="AN1" s="49"/>
+      <c r="AO1" s="49"/>
+      <c r="AP1" s="49"/>
+      <c r="AQ1" s="49"/>
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="49"/>
+      <c r="AT1" s="49"/>
+      <c r="AU1" s="49"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="55"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="54"/>
-      <c r="AB2" s="48"/>
-      <c r="AC2" s="48"/>
-      <c r="AD2" s="52"/>
-      <c r="AE2" s="53"/>
-      <c r="AF2" s="54"/>
-      <c r="AG2" s="48"/>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="48"/>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="57"/>
+      <c r="AA2" s="58"/>
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="56"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="58"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="46"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="54"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="53"/>
-      <c r="W3" s="55"/>
-      <c r="X3" s="48"/>
-      <c r="Y3" s="48"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="54"/>
-      <c r="AB3" s="48"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="52"/>
-      <c r="AE3" s="53"/>
-      <c r="AF3" s="54"/>
-      <c r="AG3" s="48"/>
-      <c r="AH3" s="48"/>
-      <c r="AI3" s="48"/>
-      <c r="AJ3" s="48"/>
-      <c r="AK3" s="48"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="59"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="52"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="58"/>
+      <c r="AB3" s="52"/>
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="58"/>
+      <c r="AG3" s="52"/>
+      <c r="AH3" s="52"/>
+      <c r="AI3" s="52"/>
+      <c r="AJ3" s="52"/>
+      <c r="AK3" s="52"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="53"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="48"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="52"/>
-      <c r="AE4" s="53"/>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="48"/>
-      <c r="AH4" s="48"/>
-      <c r="AI4" s="48"/>
-      <c r="AJ4" s="48"/>
-      <c r="AK4" s="48"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="57"/>
+      <c r="W4" s="59"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="57"/>
+      <c r="AA4" s="58"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="57"/>
+      <c r="AF4" s="58"/>
+      <c r="AG4" s="52"/>
+      <c r="AH4" s="52"/>
+      <c r="AI4" s="52"/>
+      <c r="AJ4" s="52"/>
+      <c r="AK4" s="52"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="46"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="53"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="48"/>
-      <c r="Z5" s="53"/>
-      <c r="AA5" s="54"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="48"/>
-      <c r="AD5" s="52"/>
-      <c r="AE5" s="53"/>
-      <c r="AF5" s="54"/>
-      <c r="AG5" s="48"/>
-      <c r="AH5" s="48"/>
-      <c r="AI5" s="48"/>
-      <c r="AJ5" s="48"/>
-      <c r="AK5" s="48"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="52"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="52"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="52"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="59"/>
+      <c r="X5" s="52"/>
+      <c r="Y5" s="52"/>
+      <c r="Z5" s="57"/>
+      <c r="AA5" s="58"/>
+      <c r="AB5" s="52"/>
+      <c r="AC5" s="52"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="57"/>
+      <c r="AF5" s="58"/>
+      <c r="AG5" s="52"/>
+      <c r="AH5" s="52"/>
+      <c r="AI5" s="52"/>
+      <c r="AJ5" s="52"/>
+      <c r="AK5" s="52"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="46"/>
-      <c r="C6" s="47" t="s">
+      <c r="B6" s="50"/>
+      <c r="C6" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="53"/>
-      <c r="O6" s="54"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="48"/>
-      <c r="V6" s="53"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="48"/>
-      <c r="Y6" s="48"/>
-      <c r="Z6" s="53"/>
-      <c r="AA6" s="54"/>
-      <c r="AB6" s="48"/>
-      <c r="AC6" s="48"/>
-      <c r="AD6" s="52"/>
-      <c r="AE6" s="50"/>
-      <c r="AF6" s="51"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="62"/>
-      <c r="AJ6" s="62"/>
-      <c r="AK6" s="62"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="52"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
+      <c r="T6" s="52"/>
+      <c r="U6" s="52"/>
+      <c r="V6" s="57"/>
+      <c r="W6" s="59"/>
+      <c r="X6" s="52"/>
+      <c r="Y6" s="52"/>
+      <c r="Z6" s="57"/>
+      <c r="AA6" s="58"/>
+      <c r="AB6" s="52"/>
+      <c r="AC6" s="52"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="54"/>
+      <c r="AF6" s="55"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="46"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="48"/>
-      <c r="Q7" s="61"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
-      <c r="V7" s="53"/>
-      <c r="W7" s="55"/>
-      <c r="X7" s="48"/>
-      <c r="Y7" s="48"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="54"/>
-      <c r="AB7" s="48"/>
-      <c r="AC7" s="48"/>
-      <c r="AD7" s="52"/>
-      <c r="AE7" s="53"/>
-      <c r="AF7" s="54"/>
-      <c r="AG7" s="48"/>
-      <c r="AH7" s="48"/>
-      <c r="AI7" s="48"/>
-      <c r="AJ7" s="48"/>
-      <c r="AK7" s="48"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="52"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="57"/>
+      <c r="W7" s="59"/>
+      <c r="X7" s="52"/>
+      <c r="Y7" s="52"/>
+      <c r="Z7" s="57"/>
+      <c r="AA7" s="58"/>
+      <c r="AB7" s="52"/>
+      <c r="AC7" s="52"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="57"/>
+      <c r="AF7" s="58"/>
+      <c r="AG7" s="52"/>
+      <c r="AH7" s="52"/>
+      <c r="AI7" s="52"/>
+      <c r="AJ7" s="52"/>
+      <c r="AK7" s="52"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="46"/>
-      <c r="C8" s="47" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="52"/>
-      <c r="M8" s="62"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="62"/>
-      <c r="Q8" s="62"/>
-      <c r="R8" s="62"/>
-      <c r="S8" s="62"/>
-      <c r="T8" s="62"/>
-      <c r="U8" s="62"/>
-      <c r="V8" s="50"/>
-      <c r="W8" s="55"/>
-      <c r="X8" s="62"/>
-      <c r="Y8" s="62"/>
-      <c r="Z8" s="50"/>
-      <c r="AA8" s="51"/>
-      <c r="AB8" s="62"/>
-      <c r="AC8" s="62"/>
-      <c r="AD8" s="52"/>
-      <c r="AE8" s="50"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="62"/>
-      <c r="AH8" s="62"/>
-      <c r="AI8" s="62"/>
-      <c r="AJ8" s="62"/>
-      <c r="AK8" s="62"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="66"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="59"/>
+      <c r="X8" s="66"/>
+      <c r="Y8" s="66"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="55"/>
+      <c r="AB8" s="66"/>
+      <c r="AC8" s="66"/>
+      <c r="AD8" s="56"/>
+      <c r="AE8" s="54"/>
+      <c r="AF8" s="55"/>
+      <c r="AG8" s="66"/>
+      <c r="AH8" s="66"/>
+      <c r="AI8" s="66"/>
+      <c r="AJ8" s="66"/>
+      <c r="AK8" s="66"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="46"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="61"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="52"/>
-      <c r="M9" s="61"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="60"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="61"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="59"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="61"/>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="59"/>
-      <c r="AA9" s="60"/>
-      <c r="AB9" s="48"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="61"/>
-      <c r="AE9" s="53"/>
-      <c r="AF9" s="54"/>
-      <c r="AG9" s="48"/>
-      <c r="AH9" s="48"/>
-      <c r="AI9" s="48"/>
-      <c r="AJ9" s="48"/>
-      <c r="AK9" s="48"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="52"/>
+      <c r="Q9" s="65"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="52"/>
+      <c r="V9" s="63"/>
+      <c r="W9" s="59"/>
+      <c r="X9" s="65"/>
+      <c r="Y9" s="52"/>
+      <c r="Z9" s="63"/>
+      <c r="AA9" s="64"/>
+      <c r="AB9" s="52"/>
+      <c r="AC9" s="52"/>
+      <c r="AD9" s="65"/>
+      <c r="AE9" s="57"/>
+      <c r="AF9" s="58"/>
+      <c r="AG9" s="52"/>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="52"/>
+      <c r="AK9" s="52"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="46"/>
-      <c r="C10" s="47" t="s">
-        <v>136</v>
-      </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="48"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="52"/>
-      <c r="M10" s="48"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="48"/>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="48"/>
-      <c r="S10" s="48"/>
-      <c r="T10" s="48"/>
-      <c r="U10" s="48"/>
-      <c r="V10" s="50"/>
-      <c r="W10" s="55"/>
-      <c r="X10" s="62"/>
-      <c r="Y10" s="62"/>
-      <c r="Z10" s="50"/>
-      <c r="AA10" s="54"/>
-      <c r="AB10" s="48"/>
-      <c r="AC10" s="48"/>
-      <c r="AD10" s="52"/>
-      <c r="AE10" s="53"/>
-      <c r="AF10" s="54"/>
-      <c r="AG10" s="48"/>
-      <c r="AH10" s="48"/>
-      <c r="AI10" s="48"/>
-      <c r="AJ10" s="48"/>
-      <c r="AK10" s="48"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="58"/>
+      <c r="P10" s="52"/>
+      <c r="Q10" s="52"/>
+      <c r="R10" s="52"/>
+      <c r="S10" s="52"/>
+      <c r="T10" s="52"/>
+      <c r="U10" s="52"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="59"/>
+      <c r="X10" s="66"/>
+      <c r="Y10" s="66"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="58"/>
+      <c r="AB10" s="52"/>
+      <c r="AC10" s="52"/>
+      <c r="AD10" s="56"/>
+      <c r="AE10" s="57"/>
+      <c r="AF10" s="58"/>
+      <c r="AG10" s="52"/>
+      <c r="AH10" s="52"/>
+      <c r="AI10" s="52"/>
+      <c r="AJ10" s="52"/>
+      <c r="AK10" s="52"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="46"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="56"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="53"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="48"/>
-      <c r="Q11" s="48"/>
-      <c r="R11" s="48"/>
-      <c r="S11" s="48"/>
-      <c r="T11" s="48"/>
-      <c r="U11" s="48"/>
-      <c r="V11" s="53"/>
-      <c r="W11" s="55"/>
-      <c r="X11" s="48"/>
-      <c r="Y11" s="48"/>
-      <c r="Z11" s="53"/>
-      <c r="AA11" s="54"/>
-      <c r="AB11" s="48"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="64"/>
-      <c r="AE11" s="53"/>
-      <c r="AF11" s="54"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="48"/>
-      <c r="AI11" s="48"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="48"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="52"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
+      <c r="T11" s="52"/>
+      <c r="U11" s="52"/>
+      <c r="V11" s="57"/>
+      <c r="W11" s="59"/>
+      <c r="X11" s="52"/>
+      <c r="Y11" s="52"/>
+      <c r="Z11" s="57"/>
+      <c r="AA11" s="58"/>
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="52"/>
+      <c r="AD11" s="68"/>
+      <c r="AE11" s="57"/>
+      <c r="AF11" s="58"/>
+      <c r="AG11" s="52"/>
+      <c r="AH11" s="52"/>
+      <c r="AI11" s="52"/>
+      <c r="AJ11" s="52"/>
+      <c r="AK11" s="52"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="46"/>
-      <c r="C12" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="48"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="48"/>
-      <c r="U12" s="48"/>
-      <c r="V12" s="53"/>
-      <c r="W12" s="55"/>
-      <c r="X12" s="48"/>
-      <c r="Y12" s="48"/>
-      <c r="Z12" s="53"/>
-      <c r="AA12" s="54"/>
-      <c r="AB12" s="48"/>
-      <c r="AC12" s="48"/>
-      <c r="AD12" s="52"/>
-      <c r="AE12" s="53"/>
-      <c r="AF12" s="51"/>
-      <c r="AG12" s="62"/>
-      <c r="AH12" s="62"/>
-      <c r="AI12" s="62"/>
-      <c r="AJ12" s="62"/>
-      <c r="AK12" s="62"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="56"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="52"/>
+      <c r="Q12" s="52"/>
+      <c r="R12" s="52"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="52"/>
+      <c r="U12" s="52"/>
+      <c r="V12" s="57"/>
+      <c r="W12" s="59"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="52"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="58"/>
+      <c r="AB12" s="52"/>
+      <c r="AC12" s="52"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="55"/>
+      <c r="AG12" s="66"/>
+      <c r="AH12" s="66"/>
+      <c r="AI12" s="66"/>
+      <c r="AJ12" s="66"/>
+      <c r="AK12" s="66"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="46"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="48"/>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="52"/>
-      <c r="M13" s="48"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="48"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="48"/>
-      <c r="S13" s="48"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="48"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="55"/>
-      <c r="X13" s="48"/>
-      <c r="Y13" s="48"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="54"/>
-      <c r="AB13" s="48"/>
-      <c r="AC13" s="48"/>
-      <c r="AD13" s="52"/>
-      <c r="AE13" s="53"/>
-      <c r="AF13" s="54"/>
-      <c r="AG13" s="48"/>
-      <c r="AH13" s="48"/>
-      <c r="AI13" s="48"/>
-      <c r="AJ13" s="48"/>
-      <c r="AK13" s="48"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="52"/>
+      <c r="Q13" s="52"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="52"/>
+      <c r="U13" s="52"/>
+      <c r="V13" s="57"/>
+      <c r="W13" s="59"/>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="52"/>
+      <c r="Z13" s="57"/>
+      <c r="AA13" s="58"/>
+      <c r="AB13" s="52"/>
+      <c r="AC13" s="52"/>
+      <c r="AD13" s="56"/>
+      <c r="AE13" s="57"/>
+      <c r="AF13" s="58"/>
+      <c r="AG13" s="52"/>
+      <c r="AH13" s="52"/>
+      <c r="AI13" s="52"/>
+      <c r="AJ13" s="52"/>
+      <c r="AK13" s="52"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="65" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="66" t="s">
-        <v>139</v>
-      </c>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="69"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="68"/>
-      <c r="Q14" s="68"/>
-      <c r="R14" s="68"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="68"/>
-      <c r="U14" s="68"/>
-      <c r="V14" s="69"/>
-      <c r="W14" s="55"/>
-      <c r="X14" s="68"/>
-      <c r="Y14" s="68"/>
-      <c r="Z14" s="69"/>
-      <c r="AA14" s="67"/>
-      <c r="AB14" s="68"/>
-      <c r="AC14" s="68"/>
-      <c r="AD14" s="52"/>
-      <c r="AE14" s="69"/>
-      <c r="AF14" s="67"/>
-      <c r="AG14" s="68"/>
-      <c r="AH14" s="68"/>
-      <c r="AI14" s="68"/>
-      <c r="AJ14" s="68"/>
-      <c r="AK14" s="68"/>
+      <c r="B14" s="69" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="70" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="73"/>
+      <c r="W14" s="59"/>
+      <c r="X14" s="72"/>
+      <c r="Y14" s="72"/>
+      <c r="Z14" s="73"/>
+      <c r="AA14" s="71"/>
+      <c r="AB14" s="72"/>
+      <c r="AC14" s="72"/>
+      <c r="AD14" s="56"/>
+      <c r="AE14" s="73"/>
+      <c r="AF14" s="71"/>
+      <c r="AG14" s="72"/>
+      <c r="AH14" s="72"/>
+      <c r="AI14" s="72"/>
+      <c r="AJ14" s="72"/>
+      <c r="AK14" s="72"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="52"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="69"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="68"/>
-      <c r="Q15" s="68"/>
-      <c r="R15" s="68"/>
-      <c r="S15" s="68"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="68"/>
-      <c r="V15" s="69"/>
-      <c r="W15" s="55"/>
-      <c r="X15" s="68"/>
-      <c r="Y15" s="68"/>
-      <c r="Z15" s="69"/>
-      <c r="AA15" s="67"/>
-      <c r="AB15" s="68"/>
-      <c r="AC15" s="68"/>
-      <c r="AD15" s="52"/>
-      <c r="AE15" s="69"/>
-      <c r="AF15" s="67"/>
-      <c r="AG15" s="68"/>
-      <c r="AH15" s="68"/>
-      <c r="AI15" s="68"/>
-      <c r="AJ15" s="68"/>
-      <c r="AK15" s="68"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="72"/>
+      <c r="V15" s="73"/>
+      <c r="W15" s="59"/>
+      <c r="X15" s="72"/>
+      <c r="Y15" s="72"/>
+      <c r="Z15" s="73"/>
+      <c r="AA15" s="71"/>
+      <c r="AB15" s="72"/>
+      <c r="AC15" s="72"/>
+      <c r="AD15" s="56"/>
+      <c r="AE15" s="73"/>
+      <c r="AF15" s="71"/>
+      <c r="AG15" s="72"/>
+      <c r="AH15" s="72"/>
+      <c r="AI15" s="72"/>
+      <c r="AJ15" s="72"/>
+      <c r="AK15" s="72"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="65"/>
-      <c r="C16" s="66" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="69"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="68"/>
-      <c r="Q16" s="68"/>
-      <c r="R16" s="68"/>
-      <c r="S16" s="68"/>
-      <c r="T16" s="68"/>
-      <c r="U16" s="68"/>
-      <c r="V16" s="69"/>
-      <c r="W16" s="55"/>
-      <c r="X16" s="68"/>
-      <c r="Y16" s="68"/>
-      <c r="Z16" s="69"/>
-      <c r="AA16" s="67"/>
-      <c r="AB16" s="68"/>
-      <c r="AC16" s="68"/>
-      <c r="AD16" s="52"/>
-      <c r="AE16" s="69"/>
-      <c r="AF16" s="67"/>
-      <c r="AG16" s="68"/>
-      <c r="AH16" s="68"/>
-      <c r="AI16" s="68"/>
-      <c r="AJ16" s="68"/>
-      <c r="AK16" s="68"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="73"/>
+      <c r="W16" s="59"/>
+      <c r="X16" s="72"/>
+      <c r="Y16" s="72"/>
+      <c r="Z16" s="73"/>
+      <c r="AA16" s="71"/>
+      <c r="AB16" s="72"/>
+      <c r="AC16" s="72"/>
+      <c r="AD16" s="56"/>
+      <c r="AE16" s="73"/>
+      <c r="AF16" s="71"/>
+      <c r="AG16" s="72"/>
+      <c r="AH16" s="72"/>
+      <c r="AI16" s="72"/>
+      <c r="AJ16" s="72"/>
+      <c r="AK16" s="72"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="52"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="69"/>
-      <c r="O17" s="67"/>
-      <c r="P17" s="68"/>
-      <c r="Q17" s="68"/>
-      <c r="R17" s="68"/>
-      <c r="S17" s="68"/>
-      <c r="T17" s="68"/>
-      <c r="U17" s="68"/>
-      <c r="V17" s="69"/>
-      <c r="W17" s="55"/>
-      <c r="X17" s="68"/>
-      <c r="Y17" s="68"/>
-      <c r="Z17" s="69"/>
-      <c r="AA17" s="67"/>
-      <c r="AB17" s="68"/>
-      <c r="AC17" s="68"/>
-      <c r="AD17" s="52"/>
-      <c r="AE17" s="69"/>
-      <c r="AF17" s="67"/>
-      <c r="AG17" s="68"/>
-      <c r="AH17" s="68"/>
-      <c r="AI17" s="68"/>
-      <c r="AJ17" s="68"/>
-      <c r="AK17" s="68"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="72"/>
+      <c r="V17" s="73"/>
+      <c r="W17" s="59"/>
+      <c r="X17" s="72"/>
+      <c r="Y17" s="72"/>
+      <c r="Z17" s="73"/>
+      <c r="AA17" s="71"/>
+      <c r="AB17" s="72"/>
+      <c r="AC17" s="72"/>
+      <c r="AD17" s="56"/>
+      <c r="AE17" s="73"/>
+      <c r="AF17" s="71"/>
+      <c r="AG17" s="72"/>
+      <c r="AH17" s="72"/>
+      <c r="AI17" s="72"/>
+      <c r="AJ17" s="72"/>
+      <c r="AK17" s="72"/>
       <c r="AN17" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="65"/>
-      <c r="C18" s="66" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="52"/>
-      <c r="M18" s="68"/>
-      <c r="N18" s="69"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="68"/>
-      <c r="Q18" s="68"/>
-      <c r="R18" s="68"/>
-      <c r="S18" s="68"/>
-      <c r="T18" s="68"/>
-      <c r="U18" s="68"/>
-      <c r="V18" s="69"/>
-      <c r="W18" s="55"/>
-      <c r="X18" s="68"/>
-      <c r="Y18" s="68"/>
-      <c r="Z18" s="69"/>
-      <c r="AA18" s="67"/>
-      <c r="AB18" s="68"/>
-      <c r="AC18" s="68"/>
-      <c r="AD18" s="52"/>
-      <c r="AE18" s="69"/>
-      <c r="AF18" s="67"/>
-      <c r="AG18" s="68"/>
-      <c r="AH18" s="68"/>
-      <c r="AI18" s="68"/>
-      <c r="AJ18" s="68"/>
-      <c r="AK18" s="68"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="70" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="73"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="72"/>
+      <c r="U18" s="72"/>
+      <c r="V18" s="73"/>
+      <c r="W18" s="59"/>
+      <c r="X18" s="72"/>
+      <c r="Y18" s="72"/>
+      <c r="Z18" s="73"/>
+      <c r="AA18" s="71"/>
+      <c r="AB18" s="72"/>
+      <c r="AC18" s="72"/>
+      <c r="AD18" s="56"/>
+      <c r="AE18" s="73"/>
+      <c r="AF18" s="71"/>
+      <c r="AG18" s="72"/>
+      <c r="AH18" s="72"/>
+      <c r="AI18" s="72"/>
+      <c r="AJ18" s="72"/>
+      <c r="AK18" s="72"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="65"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="67"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="67"/>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
-      <c r="U19" s="68"/>
-      <c r="V19" s="69"/>
-      <c r="W19" s="55"/>
-      <c r="X19" s="68"/>
-      <c r="Y19" s="68"/>
-      <c r="Z19" s="69"/>
-      <c r="AA19" s="67"/>
-      <c r="AB19" s="68"/>
-      <c r="AC19" s="68"/>
-      <c r="AD19" s="52"/>
-      <c r="AE19" s="69"/>
-      <c r="AF19" s="67"/>
-      <c r="AG19" s="68"/>
-      <c r="AH19" s="68"/>
-      <c r="AI19" s="68"/>
-      <c r="AJ19" s="68"/>
-      <c r="AK19" s="68"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="73"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+      <c r="T19" s="72"/>
+      <c r="U19" s="72"/>
+      <c r="V19" s="73"/>
+      <c r="W19" s="59"/>
+      <c r="X19" s="72"/>
+      <c r="Y19" s="72"/>
+      <c r="Z19" s="73"/>
+      <c r="AA19" s="71"/>
+      <c r="AB19" s="72"/>
+      <c r="AC19" s="72"/>
+      <c r="AD19" s="56"/>
+      <c r="AE19" s="73"/>
+      <c r="AF19" s="71"/>
+      <c r="AG19" s="72"/>
+      <c r="AH19" s="72"/>
+      <c r="AI19" s="72"/>
+      <c r="AJ19" s="72"/>
+      <c r="AK19" s="72"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="65"/>
-      <c r="C20" s="66" t="s">
-        <v>143</v>
-      </c>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="52"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="69"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="68"/>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="68"/>
-      <c r="T20" s="68"/>
-      <c r="U20" s="68"/>
-      <c r="V20" s="69"/>
-      <c r="W20" s="55"/>
-      <c r="X20" s="68"/>
-      <c r="Y20" s="68"/>
-      <c r="Z20" s="69"/>
-      <c r="AA20" s="67"/>
-      <c r="AB20" s="68"/>
-      <c r="AC20" s="68"/>
-      <c r="AD20" s="52"/>
-      <c r="AE20" s="69"/>
-      <c r="AF20" s="67"/>
-      <c r="AG20" s="68"/>
-      <c r="AH20" s="68"/>
-      <c r="AI20" s="68"/>
-      <c r="AJ20" s="68"/>
-      <c r="AK20" s="68"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="73"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="72"/>
+      <c r="V20" s="73"/>
+      <c r="W20" s="59"/>
+      <c r="X20" s="72"/>
+      <c r="Y20" s="72"/>
+      <c r="Z20" s="73"/>
+      <c r="AA20" s="71"/>
+      <c r="AB20" s="72"/>
+      <c r="AC20" s="72"/>
+      <c r="AD20" s="56"/>
+      <c r="AE20" s="73"/>
+      <c r="AF20" s="71"/>
+      <c r="AG20" s="72"/>
+      <c r="AH20" s="72"/>
+      <c r="AI20" s="72"/>
+      <c r="AJ20" s="72"/>
+      <c r="AK20" s="72"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="69"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="68"/>
-      <c r="S21" s="68"/>
-      <c r="T21" s="68"/>
-      <c r="U21" s="68"/>
-      <c r="V21" s="69"/>
-      <c r="W21" s="55"/>
-      <c r="X21" s="68"/>
-      <c r="Y21" s="68"/>
-      <c r="Z21" s="69"/>
-      <c r="AA21" s="67"/>
-      <c r="AB21" s="68"/>
-      <c r="AC21" s="68"/>
-      <c r="AD21" s="52"/>
-      <c r="AE21" s="69"/>
-      <c r="AF21" s="67"/>
-      <c r="AG21" s="68"/>
-      <c r="AH21" s="68"/>
-      <c r="AI21" s="68"/>
-      <c r="AJ21" s="68"/>
-      <c r="AK21" s="68"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="73"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="72"/>
+      <c r="V21" s="73"/>
+      <c r="W21" s="59"/>
+      <c r="X21" s="72"/>
+      <c r="Y21" s="72"/>
+      <c r="Z21" s="73"/>
+      <c r="AA21" s="71"/>
+      <c r="AB21" s="72"/>
+      <c r="AC21" s="72"/>
+      <c r="AD21" s="56"/>
+      <c r="AE21" s="73"/>
+      <c r="AF21" s="71"/>
+      <c r="AG21" s="72"/>
+      <c r="AH21" s="72"/>
+      <c r="AI21" s="72"/>
+      <c r="AJ21" s="72"/>
+      <c r="AK21" s="72"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="65"/>
-      <c r="C22" s="66" t="s">
-        <v>144</v>
-      </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="52"/>
-      <c r="M22" s="68"/>
-      <c r="N22" s="69"/>
-      <c r="O22" s="67"/>
-      <c r="P22" s="68"/>
-      <c r="Q22" s="68"/>
-      <c r="R22" s="68"/>
-      <c r="S22" s="68"/>
-      <c r="T22" s="68"/>
-      <c r="U22" s="68"/>
-      <c r="V22" s="69"/>
-      <c r="W22" s="55"/>
-      <c r="X22" s="68"/>
-      <c r="Y22" s="68"/>
-      <c r="Z22" s="69"/>
-      <c r="AA22" s="67"/>
-      <c r="AB22" s="68"/>
-      <c r="AC22" s="68"/>
-      <c r="AD22" s="52"/>
-      <c r="AE22" s="69"/>
-      <c r="AF22" s="67"/>
-      <c r="AG22" s="68"/>
-      <c r="AH22" s="68"/>
-      <c r="AI22" s="68"/>
-      <c r="AJ22" s="68"/>
-      <c r="AK22" s="68"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="70" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="73"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="72"/>
+      <c r="Y22" s="72"/>
+      <c r="Z22" s="73"/>
+      <c r="AA22" s="71"/>
+      <c r="AB22" s="72"/>
+      <c r="AC22" s="72"/>
+      <c r="AD22" s="56"/>
+      <c r="AE22" s="73"/>
+      <c r="AF22" s="71"/>
+      <c r="AG22" s="72"/>
+      <c r="AH22" s="72"/>
+      <c r="AI22" s="72"/>
+      <c r="AJ22" s="72"/>
+      <c r="AK22" s="72"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="65"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="52"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="69"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="68"/>
-      <c r="Q23" s="68"/>
-      <c r="R23" s="68"/>
-      <c r="S23" s="68"/>
-      <c r="T23" s="68"/>
-      <c r="U23" s="68"/>
-      <c r="V23" s="69"/>
-      <c r="W23" s="55"/>
-      <c r="X23" s="68"/>
-      <c r="Y23" s="68"/>
-      <c r="Z23" s="69"/>
-      <c r="AA23" s="67"/>
-      <c r="AB23" s="68"/>
-      <c r="AC23" s="68"/>
-      <c r="AD23" s="52"/>
-      <c r="AE23" s="69"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="68"/>
-      <c r="AH23" s="68"/>
-      <c r="AI23" s="68"/>
-      <c r="AJ23" s="68"/>
-      <c r="AK23" s="68"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="73"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="72"/>
+      <c r="V23" s="73"/>
+      <c r="W23" s="59"/>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="72"/>
+      <c r="Z23" s="73"/>
+      <c r="AA23" s="71"/>
+      <c r="AB23" s="72"/>
+      <c r="AC23" s="72"/>
+      <c r="AD23" s="56"/>
+      <c r="AE23" s="73"/>
+      <c r="AF23" s="71"/>
+      <c r="AG23" s="72"/>
+      <c r="AH23" s="72"/>
+      <c r="AI23" s="72"/>
+      <c r="AJ23" s="72"/>
+      <c r="AK23" s="72"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="65"/>
-      <c r="C24" s="66" t="s">
-        <v>145</v>
-      </c>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="67"/>
-      <c r="P24" s="68"/>
-      <c r="Q24" s="68"/>
-      <c r="R24" s="68"/>
-      <c r="S24" s="68"/>
-      <c r="T24" s="68"/>
-      <c r="U24" s="68"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="55"/>
-      <c r="X24" s="68"/>
-      <c r="Y24" s="68"/>
-      <c r="Z24" s="69"/>
-      <c r="AA24" s="67"/>
-      <c r="AB24" s="68"/>
-      <c r="AC24" s="68"/>
-      <c r="AD24" s="52"/>
-      <c r="AE24" s="69"/>
-      <c r="AF24" s="67"/>
-      <c r="AG24" s="68"/>
-      <c r="AH24" s="68"/>
-      <c r="AI24" s="68"/>
-      <c r="AJ24" s="68"/>
-      <c r="AK24" s="68"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="70" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="66"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="73"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="72"/>
+      <c r="V24" s="73"/>
+      <c r="W24" s="59"/>
+      <c r="X24" s="72"/>
+      <c r="Y24" s="72"/>
+      <c r="Z24" s="73"/>
+      <c r="AA24" s="71"/>
+      <c r="AB24" s="72"/>
+      <c r="AC24" s="72"/>
+      <c r="AD24" s="56"/>
+      <c r="AE24" s="73"/>
+      <c r="AF24" s="71"/>
+      <c r="AG24" s="72"/>
+      <c r="AH24" s="72"/>
+      <c r="AI24" s="72"/>
+      <c r="AJ24" s="72"/>
+      <c r="AK24" s="72"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="65"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="52"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="68"/>
-      <c r="R25" s="68"/>
-      <c r="S25" s="68"/>
-      <c r="T25" s="68"/>
-      <c r="U25" s="68"/>
-      <c r="V25" s="69"/>
-      <c r="W25" s="55"/>
-      <c r="X25" s="68"/>
-      <c r="Y25" s="68"/>
-      <c r="Z25" s="69"/>
-      <c r="AA25" s="67"/>
-      <c r="AB25" s="68"/>
-      <c r="AC25" s="68"/>
-      <c r="AD25" s="52"/>
-      <c r="AE25" s="69"/>
-      <c r="AF25" s="67"/>
-      <c r="AG25" s="68"/>
-      <c r="AH25" s="68"/>
-      <c r="AI25" s="68"/>
-      <c r="AJ25" s="68"/>
-      <c r="AK25" s="68"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="70"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="73"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="72"/>
+      <c r="U25" s="72"/>
+      <c r="V25" s="73"/>
+      <c r="W25" s="59"/>
+      <c r="X25" s="72"/>
+      <c r="Y25" s="72"/>
+      <c r="Z25" s="73"/>
+      <c r="AA25" s="71"/>
+      <c r="AB25" s="72"/>
+      <c r="AC25" s="72"/>
+      <c r="AD25" s="56"/>
+      <c r="AE25" s="73"/>
+      <c r="AF25" s="71"/>
+      <c r="AG25" s="72"/>
+      <c r="AH25" s="72"/>
+      <c r="AI25" s="72"/>
+      <c r="AJ25" s="72"/>
+      <c r="AK25" s="72"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>147</v>
-      </c>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="48"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="48"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="53"/>
-      <c r="W26" s="55"/>
-      <c r="X26" s="48"/>
-      <c r="Y26" s="48"/>
-      <c r="Z26" s="53"/>
-      <c r="AA26" s="54"/>
-      <c r="AB26" s="48"/>
-      <c r="AC26" s="48"/>
-      <c r="AD26" s="52"/>
-      <c r="AE26" s="53"/>
-      <c r="AF26" s="54"/>
-      <c r="AG26" s="48"/>
-      <c r="AH26" s="48"/>
-      <c r="AI26" s="48"/>
-      <c r="AJ26" s="48"/>
-      <c r="AK26" s="48"/>
+      <c r="B26" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="52"/>
+      <c r="Q26" s="52"/>
+      <c r="R26" s="52"/>
+      <c r="S26" s="52"/>
+      <c r="T26" s="52"/>
+      <c r="U26" s="52"/>
+      <c r="V26" s="57"/>
+      <c r="W26" s="59"/>
+      <c r="X26" s="52"/>
+      <c r="Y26" s="52"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="58"/>
+      <c r="AB26" s="52"/>
+      <c r="AC26" s="52"/>
+      <c r="AD26" s="56"/>
+      <c r="AE26" s="57"/>
+      <c r="AF26" s="58"/>
+      <c r="AG26" s="52"/>
+      <c r="AH26" s="52"/>
+      <c r="AI26" s="52"/>
+      <c r="AJ26" s="52"/>
+      <c r="AK26" s="52"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="46"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="48"/>
-      <c r="S27" s="48"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="53"/>
-      <c r="W27" s="55"/>
-      <c r="X27" s="48"/>
-      <c r="Y27" s="48"/>
-      <c r="Z27" s="53"/>
-      <c r="AA27" s="54"/>
-      <c r="AB27" s="48"/>
-      <c r="AC27" s="48"/>
-      <c r="AD27" s="52"/>
-      <c r="AE27" s="53"/>
-      <c r="AF27" s="54"/>
-      <c r="AG27" s="48"/>
-      <c r="AH27" s="48"/>
-      <c r="AI27" s="48"/>
-      <c r="AJ27" s="48"/>
-      <c r="AK27" s="48"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="52"/>
+      <c r="R27" s="52"/>
+      <c r="S27" s="52"/>
+      <c r="T27" s="52"/>
+      <c r="U27" s="52"/>
+      <c r="V27" s="57"/>
+      <c r="W27" s="59"/>
+      <c r="X27" s="52"/>
+      <c r="Y27" s="52"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="58"/>
+      <c r="AB27" s="52"/>
+      <c r="AC27" s="52"/>
+      <c r="AD27" s="56"/>
+      <c r="AE27" s="57"/>
+      <c r="AF27" s="58"/>
+      <c r="AG27" s="52"/>
+      <c r="AH27" s="52"/>
+      <c r="AI27" s="52"/>
+      <c r="AJ27" s="52"/>
+      <c r="AK27" s="52"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="46"/>
-      <c r="C28" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="52"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="54"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="48"/>
-      <c r="U28" s="48"/>
-      <c r="V28" s="53"/>
-      <c r="W28" s="55"/>
-      <c r="X28" s="48"/>
-      <c r="Y28" s="48"/>
-      <c r="Z28" s="53"/>
-      <c r="AA28" s="54"/>
-      <c r="AB28" s="48"/>
-      <c r="AC28" s="48"/>
-      <c r="AD28" s="52"/>
-      <c r="AE28" s="53"/>
-      <c r="AF28" s="54"/>
-      <c r="AG28" s="48"/>
-      <c r="AH28" s="48"/>
-      <c r="AI28" s="48"/>
-      <c r="AJ28" s="48"/>
-      <c r="AK28" s="48"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="52"/>
+      <c r="R28" s="52"/>
+      <c r="S28" s="52"/>
+      <c r="T28" s="52"/>
+      <c r="U28" s="52"/>
+      <c r="V28" s="57"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="52"/>
+      <c r="Y28" s="52"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="58"/>
+      <c r="AB28" s="52"/>
+      <c r="AC28" s="52"/>
+      <c r="AD28" s="56"/>
+      <c r="AE28" s="57"/>
+      <c r="AF28" s="58"/>
+      <c r="AG28" s="52"/>
+      <c r="AH28" s="52"/>
+      <c r="AI28" s="52"/>
+      <c r="AJ28" s="52"/>
+      <c r="AK28" s="52"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="46"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="59"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="48"/>
-      <c r="V29" s="53"/>
-      <c r="W29" s="55"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="53"/>
-      <c r="AA29" s="54"/>
-      <c r="AB29" s="48"/>
-      <c r="AC29" s="48"/>
-      <c r="AD29" s="52"/>
-      <c r="AE29" s="53"/>
-      <c r="AF29" s="54"/>
-      <c r="AG29" s="48"/>
-      <c r="AH29" s="48"/>
-      <c r="AI29" s="48"/>
-      <c r="AJ29" s="48"/>
-      <c r="AK29" s="48"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="52"/>
+      <c r="Q29" s="52"/>
+      <c r="R29" s="52"/>
+      <c r="S29" s="52"/>
+      <c r="T29" s="52"/>
+      <c r="U29" s="52"/>
+      <c r="V29" s="57"/>
+      <c r="W29" s="59"/>
+      <c r="X29" s="52"/>
+      <c r="Y29" s="52"/>
+      <c r="Z29" s="57"/>
+      <c r="AA29" s="58"/>
+      <c r="AB29" s="52"/>
+      <c r="AC29" s="52"/>
+      <c r="AD29" s="56"/>
+      <c r="AE29" s="57"/>
+      <c r="AF29" s="58"/>
+      <c r="AG29" s="52"/>
+      <c r="AH29" s="52"/>
+      <c r="AI29" s="52"/>
+      <c r="AJ29" s="52"/>
+      <c r="AK29" s="52"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="46"/>
-      <c r="C30" s="47" t="s">
-        <v>149</v>
-      </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="62"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="62"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="62"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="54"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="48"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="48"/>
-      <c r="V30" s="53"/>
-      <c r="W30" s="55"/>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="53"/>
-      <c r="AA30" s="54"/>
-      <c r="AB30" s="48"/>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="52"/>
-      <c r="AE30" s="53"/>
-      <c r="AF30" s="54"/>
-      <c r="AG30" s="48"/>
-      <c r="AH30" s="48"/>
-      <c r="AI30" s="48"/>
-      <c r="AJ30" s="48"/>
-      <c r="AK30" s="48"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="52"/>
+      <c r="R30" s="52"/>
+      <c r="S30" s="52"/>
+      <c r="T30" s="52"/>
+      <c r="U30" s="52"/>
+      <c r="V30" s="57"/>
+      <c r="W30" s="59"/>
+      <c r="X30" s="52"/>
+      <c r="Y30" s="52"/>
+      <c r="Z30" s="57"/>
+      <c r="AA30" s="58"/>
+      <c r="AB30" s="52"/>
+      <c r="AC30" s="52"/>
+      <c r="AD30" s="56"/>
+      <c r="AE30" s="57"/>
+      <c r="AF30" s="58"/>
+      <c r="AG30" s="52"/>
+      <c r="AH30" s="52"/>
+      <c r="AI30" s="52"/>
+      <c r="AJ30" s="52"/>
+      <c r="AK30" s="52"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="46"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="60"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="63"/>
-      <c r="K31" s="63"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="48"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="48"/>
-      <c r="U31" s="48"/>
-      <c r="V31" s="53"/>
-      <c r="W31" s="55"/>
-      <c r="X31" s="48"/>
-      <c r="Y31" s="48"/>
-      <c r="Z31" s="53"/>
-      <c r="AA31" s="54"/>
-      <c r="AB31" s="48"/>
-      <c r="AC31" s="48"/>
-      <c r="AD31" s="52"/>
-      <c r="AE31" s="53"/>
-      <c r="AF31" s="54"/>
-      <c r="AG31" s="48"/>
-      <c r="AH31" s="48"/>
-      <c r="AI31" s="48"/>
-      <c r="AJ31" s="48"/>
-      <c r="AK31" s="48"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="77"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="52"/>
+      <c r="Q31" s="52"/>
+      <c r="R31" s="52"/>
+      <c r="S31" s="52"/>
+      <c r="T31" s="52"/>
+      <c r="U31" s="52"/>
+      <c r="V31" s="57"/>
+      <c r="W31" s="59"/>
+      <c r="X31" s="52"/>
+      <c r="Y31" s="52"/>
+      <c r="Z31" s="57"/>
+      <c r="AA31" s="58"/>
+      <c r="AB31" s="52"/>
+      <c r="AC31" s="52"/>
+      <c r="AD31" s="56"/>
+      <c r="AE31" s="57"/>
+      <c r="AF31" s="58"/>
+      <c r="AG31" s="52"/>
+      <c r="AH31" s="52"/>
+      <c r="AI31" s="52"/>
+      <c r="AJ31" s="52"/>
+      <c r="AK31" s="52"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="46"/>
-      <c r="C32" s="47" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="54"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="62"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="48"/>
-      <c r="R32" s="48"/>
-      <c r="S32" s="48"/>
-      <c r="T32" s="48"/>
-      <c r="U32" s="48"/>
-      <c r="V32" s="53"/>
-      <c r="W32" s="55"/>
-      <c r="X32" s="48"/>
-      <c r="Y32" s="48"/>
-      <c r="Z32" s="53"/>
-      <c r="AA32" s="54"/>
-      <c r="AB32" s="48"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="52"/>
-      <c r="AE32" s="53"/>
-      <c r="AF32" s="54"/>
-      <c r="AG32" s="48"/>
-      <c r="AH32" s="48"/>
-      <c r="AI32" s="48"/>
-      <c r="AJ32" s="48"/>
-      <c r="AK32" s="48"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="66"/>
+      <c r="N32" s="54"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="52"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="52"/>
+      <c r="T32" s="52"/>
+      <c r="U32" s="52"/>
+      <c r="V32" s="57"/>
+      <c r="W32" s="59"/>
+      <c r="X32" s="52"/>
+      <c r="Y32" s="52"/>
+      <c r="Z32" s="57"/>
+      <c r="AA32" s="58"/>
+      <c r="AB32" s="52"/>
+      <c r="AC32" s="52"/>
+      <c r="AD32" s="56"/>
+      <c r="AE32" s="57"/>
+      <c r="AF32" s="58"/>
+      <c r="AG32" s="52"/>
+      <c r="AH32" s="52"/>
+      <c r="AI32" s="52"/>
+      <c r="AJ32" s="52"/>
+      <c r="AK32" s="52"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="46"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="54"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="52"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="59"/>
-      <c r="O33" s="54"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="48"/>
-      <c r="R33" s="48"/>
-      <c r="S33" s="48"/>
-      <c r="T33" s="48"/>
-      <c r="U33" s="48"/>
-      <c r="V33" s="53"/>
-      <c r="W33" s="55"/>
-      <c r="X33" s="48"/>
-      <c r="Y33" s="48"/>
-      <c r="Z33" s="53"/>
-      <c r="AA33" s="54"/>
-      <c r="AB33" s="48"/>
-      <c r="AC33" s="48"/>
-      <c r="AD33" s="52"/>
-      <c r="AE33" s="53"/>
-      <c r="AF33" s="54"/>
-      <c r="AG33" s="48"/>
-      <c r="AH33" s="48"/>
-      <c r="AI33" s="48"/>
-      <c r="AJ33" s="48"/>
-      <c r="AK33" s="48"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="63"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="52"/>
+      <c r="Q33" s="52"/>
+      <c r="R33" s="52"/>
+      <c r="S33" s="52"/>
+      <c r="T33" s="52"/>
+      <c r="U33" s="52"/>
+      <c r="V33" s="57"/>
+      <c r="W33" s="59"/>
+      <c r="X33" s="52"/>
+      <c r="Y33" s="52"/>
+      <c r="Z33" s="57"/>
+      <c r="AA33" s="58"/>
+      <c r="AB33" s="52"/>
+      <c r="AC33" s="52"/>
+      <c r="AD33" s="56"/>
+      <c r="AE33" s="57"/>
+      <c r="AF33" s="58"/>
+      <c r="AG33" s="52"/>
+      <c r="AH33" s="52"/>
+      <c r="AI33" s="52"/>
+      <c r="AJ33" s="52"/>
+      <c r="AK33" s="52"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="65" t="s">
-        <v>151</v>
-      </c>
-      <c r="C34" s="74" t="s">
-        <v>152</v>
-      </c>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="67"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="68"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="62"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="51"/>
-      <c r="P34" s="62"/>
-      <c r="Q34" s="62"/>
-      <c r="R34" s="62"/>
-      <c r="S34" s="68"/>
-      <c r="T34" s="68"/>
-      <c r="U34" s="68"/>
-      <c r="V34" s="69"/>
-      <c r="W34" s="55"/>
-      <c r="X34" s="68"/>
-      <c r="Y34" s="68"/>
-      <c r="Z34" s="69"/>
-      <c r="AA34" s="67"/>
-      <c r="AB34" s="68"/>
-      <c r="AC34" s="68"/>
-      <c r="AD34" s="52"/>
-      <c r="AE34" s="69"/>
-      <c r="AF34" s="67"/>
-      <c r="AG34" s="68"/>
-      <c r="AH34" s="68"/>
-      <c r="AI34" s="68"/>
-      <c r="AJ34" s="68"/>
-      <c r="AK34" s="68"/>
+      <c r="B34" s="69" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="78" t="s">
+        <v>155</v>
+      </c>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="66"/>
+      <c r="N34" s="54"/>
+      <c r="O34" s="55"/>
+      <c r="P34" s="66"/>
+      <c r="Q34" s="66"/>
+      <c r="R34" s="66"/>
+      <c r="S34" s="72"/>
+      <c r="T34" s="72"/>
+      <c r="U34" s="72"/>
+      <c r="V34" s="73"/>
+      <c r="W34" s="59"/>
+      <c r="X34" s="72"/>
+      <c r="Y34" s="72"/>
+      <c r="Z34" s="73"/>
+      <c r="AA34" s="71"/>
+      <c r="AB34" s="72"/>
+      <c r="AC34" s="72"/>
+      <c r="AD34" s="56"/>
+      <c r="AE34" s="73"/>
+      <c r="AF34" s="71"/>
+      <c r="AG34" s="72"/>
+      <c r="AH34" s="72"/>
+      <c r="AI34" s="72"/>
+      <c r="AJ34" s="72"/>
+      <c r="AK34" s="72"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="65"/>
-      <c r="C35" s="74"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="67"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="59"/>
-      <c r="O35" s="67"/>
-      <c r="P35" s="61"/>
-      <c r="Q35" s="68"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="76"/>
-      <c r="T35" s="57"/>
-      <c r="U35" s="68"/>
-      <c r="V35" s="69"/>
-      <c r="W35" s="55"/>
-      <c r="X35" s="68"/>
-      <c r="Y35" s="68"/>
-      <c r="Z35" s="69"/>
-      <c r="AA35" s="67"/>
-      <c r="AB35" s="68"/>
-      <c r="AC35" s="68"/>
-      <c r="AD35" s="52"/>
-      <c r="AE35" s="69"/>
-      <c r="AF35" s="67"/>
-      <c r="AG35" s="68"/>
-      <c r="AH35" s="68"/>
-      <c r="AI35" s="68"/>
-      <c r="AJ35" s="68"/>
-      <c r="AK35" s="68"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="72"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="72"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="80"/>
+      <c r="S35" s="80"/>
+      <c r="T35" s="61"/>
+      <c r="U35" s="72"/>
+      <c r="V35" s="73"/>
+      <c r="W35" s="59"/>
+      <c r="X35" s="72"/>
+      <c r="Y35" s="72"/>
+      <c r="Z35" s="73"/>
+      <c r="AA35" s="71"/>
+      <c r="AB35" s="72"/>
+      <c r="AC35" s="72"/>
+      <c r="AD35" s="56"/>
+      <c r="AE35" s="73"/>
+      <c r="AF35" s="71"/>
+      <c r="AG35" s="72"/>
+      <c r="AH35" s="72"/>
+      <c r="AI35" s="72"/>
+      <c r="AJ35" s="72"/>
+      <c r="AK35" s="72"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="65"/>
-      <c r="C36" s="74" t="s">
-        <v>153</v>
-      </c>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="68"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="62"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="62"/>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="68"/>
-      <c r="S36" s="68"/>
-      <c r="T36" s="68"/>
-      <c r="U36" s="68"/>
-      <c r="V36" s="69"/>
-      <c r="W36" s="55"/>
-      <c r="X36" s="68"/>
-      <c r="Y36" s="68"/>
-      <c r="Z36" s="69"/>
-      <c r="AA36" s="67"/>
-      <c r="AB36" s="68"/>
-      <c r="AC36" s="68"/>
-      <c r="AD36" s="52"/>
-      <c r="AE36" s="69"/>
-      <c r="AF36" s="67"/>
-      <c r="AG36" s="68"/>
-      <c r="AH36" s="68"/>
-      <c r="AI36" s="68"/>
-      <c r="AJ36" s="68"/>
-      <c r="AK36" s="68"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="78" t="s">
+        <v>156</v>
+      </c>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="72"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="66"/>
+      <c r="N36" s="54"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="66"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="72"/>
+      <c r="T36" s="72"/>
+      <c r="U36" s="72"/>
+      <c r="V36" s="73"/>
+      <c r="W36" s="59"/>
+      <c r="X36" s="72"/>
+      <c r="Y36" s="72"/>
+      <c r="Z36" s="73"/>
+      <c r="AA36" s="71"/>
+      <c r="AB36" s="72"/>
+      <c r="AC36" s="72"/>
+      <c r="AD36" s="56"/>
+      <c r="AE36" s="73"/>
+      <c r="AF36" s="71"/>
+      <c r="AG36" s="72"/>
+      <c r="AH36" s="72"/>
+      <c r="AI36" s="72"/>
+      <c r="AJ36" s="72"/>
+      <c r="AK36" s="72"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="65"/>
-      <c r="C37" s="74"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="75"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="67"/>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="68"/>
-      <c r="R37" s="76"/>
-      <c r="S37" s="76"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="68"/>
-      <c r="V37" s="69"/>
-      <c r="W37" s="55"/>
-      <c r="X37" s="68"/>
-      <c r="Y37" s="68"/>
-      <c r="Z37" s="69"/>
-      <c r="AA37" s="67"/>
-      <c r="AB37" s="68"/>
-      <c r="AC37" s="68"/>
-      <c r="AD37" s="52"/>
-      <c r="AE37" s="69"/>
-      <c r="AF37" s="67"/>
-      <c r="AG37" s="68"/>
-      <c r="AH37" s="68"/>
-      <c r="AI37" s="68"/>
-      <c r="AJ37" s="68"/>
-      <c r="AK37" s="68"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="78"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="72"/>
+      <c r="J37" s="72"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="73"/>
+      <c r="O37" s="71"/>
+      <c r="P37" s="65"/>
+      <c r="Q37" s="72"/>
+      <c r="R37" s="80"/>
+      <c r="S37" s="80"/>
+      <c r="T37" s="61"/>
+      <c r="U37" s="72"/>
+      <c r="V37" s="73"/>
+      <c r="W37" s="59"/>
+      <c r="X37" s="72"/>
+      <c r="Y37" s="72"/>
+      <c r="Z37" s="73"/>
+      <c r="AA37" s="71"/>
+      <c r="AB37" s="72"/>
+      <c r="AC37" s="72"/>
+      <c r="AD37" s="56"/>
+      <c r="AE37" s="73"/>
+      <c r="AF37" s="71"/>
+      <c r="AG37" s="72"/>
+      <c r="AH37" s="72"/>
+      <c r="AI37" s="72"/>
+      <c r="AJ37" s="72"/>
+      <c r="AK37" s="72"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="65"/>
-      <c r="C38" s="74" t="s">
-        <v>154</v>
-      </c>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="71"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="62"/>
-      <c r="Q38" s="62"/>
-      <c r="R38" s="62"/>
-      <c r="S38" s="62"/>
-      <c r="T38" s="62"/>
-      <c r="U38" s="62"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="55"/>
-      <c r="X38" s="62"/>
-      <c r="Y38" s="62"/>
-      <c r="Z38" s="69"/>
-      <c r="AA38" s="67"/>
-      <c r="AB38" s="68"/>
-      <c r="AC38" s="68"/>
-      <c r="AD38" s="52"/>
-      <c r="AE38" s="69"/>
-      <c r="AF38" s="67"/>
-      <c r="AG38" s="68"/>
-      <c r="AH38" s="68"/>
-      <c r="AI38" s="68"/>
-      <c r="AJ38" s="68"/>
-      <c r="AK38" s="68"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="73"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="72"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="73"/>
+      <c r="O38" s="55"/>
+      <c r="P38" s="66"/>
+      <c r="Q38" s="66"/>
+      <c r="R38" s="66"/>
+      <c r="S38" s="66"/>
+      <c r="T38" s="66"/>
+      <c r="U38" s="66"/>
+      <c r="V38" s="54"/>
+      <c r="W38" s="59"/>
+      <c r="X38" s="66"/>
+      <c r="Y38" s="66"/>
+      <c r="Z38" s="73"/>
+      <c r="AA38" s="71"/>
+      <c r="AB38" s="72"/>
+      <c r="AC38" s="72"/>
+      <c r="AD38" s="56"/>
+      <c r="AE38" s="73"/>
+      <c r="AF38" s="71"/>
+      <c r="AG38" s="72"/>
+      <c r="AH38" s="72"/>
+      <c r="AI38" s="72"/>
+      <c r="AJ38" s="72"/>
+      <c r="AK38" s="72"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="65"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="71"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="52"/>
-      <c r="M39" s="68"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="68"/>
-      <c r="Q39" s="68"/>
-      <c r="R39" s="75"/>
-      <c r="S39" s="75"/>
-      <c r="T39" s="68"/>
-      <c r="U39" s="68"/>
-      <c r="V39" s="69"/>
-      <c r="W39" s="55"/>
-      <c r="X39" s="68"/>
-      <c r="Y39" s="68"/>
-      <c r="Z39" s="69"/>
-      <c r="AA39" s="67"/>
-      <c r="AB39" s="68"/>
-      <c r="AC39" s="68"/>
-      <c r="AD39" s="52"/>
-      <c r="AE39" s="69"/>
-      <c r="AF39" s="67"/>
-      <c r="AG39" s="68"/>
-      <c r="AH39" s="68"/>
-      <c r="AI39" s="68"/>
-      <c r="AJ39" s="68"/>
-      <c r="AK39" s="68"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="72"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="72"/>
+      <c r="J39" s="72"/>
+      <c r="K39" s="72"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="72"/>
+      <c r="N39" s="73"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="79"/>
+      <c r="S39" s="79"/>
+      <c r="T39" s="72"/>
+      <c r="U39" s="72"/>
+      <c r="V39" s="73"/>
+      <c r="W39" s="59"/>
+      <c r="X39" s="72"/>
+      <c r="Y39" s="72"/>
+      <c r="Z39" s="73"/>
+      <c r="AA39" s="71"/>
+      <c r="AB39" s="72"/>
+      <c r="AC39" s="72"/>
+      <c r="AD39" s="56"/>
+      <c r="AE39" s="73"/>
+      <c r="AF39" s="71"/>
+      <c r="AG39" s="72"/>
+      <c r="AH39" s="72"/>
+      <c r="AI39" s="72"/>
+      <c r="AJ39" s="72"/>
+      <c r="AK39" s="72"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="65"/>
-      <c r="C40" s="74" t="s">
-        <v>155</v>
-      </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="69"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="68"/>
-      <c r="Q40" s="68"/>
-      <c r="R40" s="62"/>
-      <c r="S40" s="62"/>
-      <c r="T40" s="62"/>
-      <c r="U40" s="62"/>
-      <c r="V40" s="50"/>
-      <c r="W40" s="55"/>
-      <c r="X40" s="62"/>
-      <c r="Y40" s="62"/>
-      <c r="Z40" s="50"/>
-      <c r="AA40" s="51"/>
-      <c r="AB40" s="62"/>
-      <c r="AC40" s="62"/>
-      <c r="AD40" s="52"/>
-      <c r="AE40" s="69"/>
-      <c r="AF40" s="67"/>
-      <c r="AG40" s="68"/>
-      <c r="AH40" s="68"/>
-      <c r="AI40" s="68"/>
-      <c r="AJ40" s="68"/>
-      <c r="AK40" s="68"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="78" t="s">
+        <v>158</v>
+      </c>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="75"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="72"/>
+      <c r="J40" s="72"/>
+      <c r="K40" s="72"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="72"/>
+      <c r="N40" s="73"/>
+      <c r="O40" s="71"/>
+      <c r="P40" s="72"/>
+      <c r="Q40" s="72"/>
+      <c r="R40" s="66"/>
+      <c r="S40" s="66"/>
+      <c r="T40" s="66"/>
+      <c r="U40" s="66"/>
+      <c r="V40" s="54"/>
+      <c r="W40" s="59"/>
+      <c r="X40" s="66"/>
+      <c r="Y40" s="66"/>
+      <c r="Z40" s="54"/>
+      <c r="AA40" s="55"/>
+      <c r="AB40" s="66"/>
+      <c r="AC40" s="66"/>
+      <c r="AD40" s="56"/>
+      <c r="AE40" s="73"/>
+      <c r="AF40" s="71"/>
+      <c r="AG40" s="72"/>
+      <c r="AH40" s="72"/>
+      <c r="AI40" s="72"/>
+      <c r="AJ40" s="72"/>
+      <c r="AK40" s="72"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="65"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="52"/>
-      <c r="M41" s="68"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="68"/>
-      <c r="Q41" s="61"/>
-      <c r="R41" s="75"/>
-      <c r="S41" s="75"/>
-      <c r="T41" s="61"/>
-      <c r="U41" s="68"/>
-      <c r="V41" s="69"/>
-      <c r="W41" s="55"/>
-      <c r="X41" s="68"/>
-      <c r="Y41" s="68"/>
-      <c r="Z41" s="69"/>
-      <c r="AA41" s="67"/>
-      <c r="AB41" s="68"/>
-      <c r="AC41" s="68"/>
-      <c r="AD41" s="52"/>
-      <c r="AE41" s="69"/>
-      <c r="AF41" s="67"/>
-      <c r="AG41" s="68"/>
-      <c r="AH41" s="68"/>
-      <c r="AI41" s="68"/>
-      <c r="AJ41" s="68"/>
-      <c r="AK41" s="68"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="72"/>
+      <c r="K41" s="72"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="72"/>
+      <c r="N41" s="73"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="72"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="79"/>
+      <c r="S41" s="79"/>
+      <c r="T41" s="65"/>
+      <c r="U41" s="72"/>
+      <c r="V41" s="73"/>
+      <c r="W41" s="59"/>
+      <c r="X41" s="72"/>
+      <c r="Y41" s="72"/>
+      <c r="Z41" s="73"/>
+      <c r="AA41" s="71"/>
+      <c r="AB41" s="72"/>
+      <c r="AC41" s="72"/>
+      <c r="AD41" s="56"/>
+      <c r="AE41" s="73"/>
+      <c r="AF41" s="71"/>
+      <c r="AG41" s="72"/>
+      <c r="AH41" s="72"/>
+      <c r="AI41" s="72"/>
+      <c r="AJ41" s="72"/>
+      <c r="AK41" s="72"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="54"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
-      <c r="L42" s="52"/>
-      <c r="M42" s="48"/>
-      <c r="N42" s="53"/>
-      <c r="O42" s="54"/>
-      <c r="P42" s="62"/>
-      <c r="Q42" s="62"/>
-      <c r="R42" s="48"/>
-      <c r="S42" s="48"/>
-      <c r="T42" s="61"/>
-      <c r="U42" s="48"/>
-      <c r="V42" s="50"/>
-      <c r="W42" s="55"/>
-      <c r="X42" s="62"/>
-      <c r="Y42" s="62"/>
-      <c r="Z42" s="50"/>
-      <c r="AA42" s="51"/>
-      <c r="AB42" s="62"/>
-      <c r="AC42" s="62"/>
-      <c r="AD42" s="52"/>
-      <c r="AE42" s="53"/>
-      <c r="AF42" s="54"/>
-      <c r="AG42" s="48"/>
-      <c r="AH42" s="48"/>
-      <c r="AI42" s="48"/>
-      <c r="AJ42" s="48"/>
-      <c r="AK42" s="48"/>
+      <c r="C42" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="57"/>
+      <c r="O42" s="58"/>
+      <c r="P42" s="66"/>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="52"/>
+      <c r="T42" s="65"/>
+      <c r="U42" s="52"/>
+      <c r="V42" s="54"/>
+      <c r="W42" s="59"/>
+      <c r="X42" s="66"/>
+      <c r="Y42" s="66"/>
+      <c r="Z42" s="54"/>
+      <c r="AA42" s="55"/>
+      <c r="AB42" s="66"/>
+      <c r="AC42" s="66"/>
+      <c r="AD42" s="56"/>
+      <c r="AE42" s="57"/>
+      <c r="AF42" s="58"/>
+      <c r="AG42" s="52"/>
+      <c r="AH42" s="52"/>
+      <c r="AI42" s="52"/>
+      <c r="AJ42" s="52"/>
+      <c r="AK42" s="52"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="46"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="53"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
-      <c r="L43" s="52"/>
-      <c r="M43" s="48"/>
-      <c r="N43" s="53"/>
-      <c r="O43" s="54"/>
-      <c r="P43" s="48"/>
-      <c r="Q43" s="61"/>
-      <c r="R43" s="48"/>
-      <c r="S43" s="63"/>
-      <c r="T43" s="48"/>
-      <c r="U43" s="48"/>
-      <c r="V43" s="53"/>
-      <c r="W43" s="55"/>
-      <c r="X43" s="48"/>
-      <c r="Y43" s="48"/>
-      <c r="Z43" s="53"/>
-      <c r="AA43" s="54"/>
-      <c r="AB43" s="48"/>
-      <c r="AC43" s="48"/>
-      <c r="AD43" s="52"/>
-      <c r="AE43" s="53"/>
-      <c r="AF43" s="54"/>
-      <c r="AG43" s="48"/>
-      <c r="AH43" s="48"/>
-      <c r="AI43" s="48"/>
-      <c r="AJ43" s="48"/>
-      <c r="AK43" s="48"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
+      <c r="K43" s="52"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="52"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="58"/>
+      <c r="P43" s="52"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="67"/>
+      <c r="T43" s="52"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="57"/>
+      <c r="W43" s="59"/>
+      <c r="X43" s="52"/>
+      <c r="Y43" s="52"/>
+      <c r="Z43" s="57"/>
+      <c r="AA43" s="58"/>
+      <c r="AB43" s="52"/>
+      <c r="AC43" s="52"/>
+      <c r="AD43" s="56"/>
+      <c r="AE43" s="57"/>
+      <c r="AF43" s="58"/>
+      <c r="AG43" s="52"/>
+      <c r="AH43" s="52"/>
+      <c r="AI43" s="52"/>
+      <c r="AJ43" s="52"/>
+      <c r="AK43" s="52"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="46"/>
-      <c r="C44" s="77" t="s">
-        <v>157</v>
-      </c>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="56"/>
-      <c r="G44" s="53"/>
-      <c r="H44" s="54"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
-      <c r="L44" s="52"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="53"/>
-      <c r="O44" s="54"/>
-      <c r="P44" s="62"/>
-      <c r="Q44" s="62"/>
-      <c r="R44" s="48"/>
-      <c r="S44" s="48"/>
-      <c r="T44" s="48"/>
-      <c r="U44" s="48"/>
-      <c r="V44" s="53"/>
-      <c r="W44" s="55"/>
-      <c r="X44" s="62"/>
-      <c r="Y44" s="62"/>
-      <c r="Z44" s="53"/>
-      <c r="AA44" s="54"/>
-      <c r="AB44" s="48"/>
-      <c r="AC44" s="62"/>
-      <c r="AD44" s="52"/>
-      <c r="AE44" s="50"/>
-      <c r="AF44" s="51"/>
-      <c r="AG44" s="48"/>
-      <c r="AH44" s="48"/>
-      <c r="AI44" s="62"/>
-      <c r="AJ44" s="48"/>
-      <c r="AK44" s="48"/>
+      <c r="B44" s="50"/>
+      <c r="C44" s="81" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="57"/>
+      <c r="O44" s="58"/>
+      <c r="P44" s="66"/>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="52"/>
+      <c r="S44" s="52"/>
+      <c r="T44" s="52"/>
+      <c r="U44" s="52"/>
+      <c r="V44" s="57"/>
+      <c r="W44" s="59"/>
+      <c r="X44" s="66"/>
+      <c r="Y44" s="66"/>
+      <c r="Z44" s="57"/>
+      <c r="AA44" s="58"/>
+      <c r="AB44" s="52"/>
+      <c r="AC44" s="66"/>
+      <c r="AD44" s="56"/>
+      <c r="AE44" s="54"/>
+      <c r="AF44" s="55"/>
+      <c r="AG44" s="52"/>
+      <c r="AH44" s="52"/>
+      <c r="AI44" s="66"/>
+      <c r="AJ44" s="52"/>
+      <c r="AK44" s="52"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="46"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="56"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="54"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="48"/>
-      <c r="N45" s="53"/>
-      <c r="O45" s="54"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="48"/>
-      <c r="R45" s="48"/>
-      <c r="S45" s="48"/>
-      <c r="T45" s="48"/>
-      <c r="U45" s="48"/>
-      <c r="V45" s="53"/>
-      <c r="W45" s="55"/>
-      <c r="X45" s="48"/>
-      <c r="Y45" s="61"/>
-      <c r="Z45" s="78"/>
-      <c r="AA45" s="54"/>
-      <c r="AB45" s="48"/>
-      <c r="AC45" s="48"/>
-      <c r="AD45" s="52"/>
-      <c r="AE45" s="53"/>
-      <c r="AF45" s="54"/>
-      <c r="AG45" s="48"/>
-      <c r="AH45" s="48"/>
-      <c r="AI45" s="48"/>
-      <c r="AJ45" s="48"/>
-      <c r="AK45" s="48"/>
+      <c r="B45" s="50"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="58"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="58"/>
+      <c r="P45" s="52"/>
+      <c r="Q45" s="52"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="52"/>
+      <c r="T45" s="52"/>
+      <c r="U45" s="52"/>
+      <c r="V45" s="57"/>
+      <c r="W45" s="59"/>
+      <c r="X45" s="52"/>
+      <c r="Y45" s="65"/>
+      <c r="Z45" s="82"/>
+      <c r="AA45" s="58"/>
+      <c r="AB45" s="52"/>
+      <c r="AC45" s="52"/>
+      <c r="AD45" s="56"/>
+      <c r="AE45" s="57"/>
+      <c r="AF45" s="58"/>
+      <c r="AG45" s="52"/>
+      <c r="AH45" s="52"/>
+      <c r="AI45" s="52"/>
+      <c r="AJ45" s="52"/>
+      <c r="AK45" s="52"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="65" t="s">
-        <v>158</v>
-      </c>
-      <c r="C46" s="66" t="s">
+      <c r="B46" s="69" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="71"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="67"/>
-      <c r="I46" s="68"/>
-      <c r="J46" s="68"/>
-      <c r="K46" s="68"/>
-      <c r="L46" s="52"/>
-      <c r="M46" s="68"/>
-      <c r="N46" s="69"/>
-      <c r="O46" s="67"/>
-      <c r="P46" s="68"/>
-      <c r="Q46" s="68"/>
-      <c r="R46" s="68"/>
-      <c r="S46" s="68"/>
-      <c r="T46" s="68"/>
-      <c r="U46" s="68"/>
-      <c r="V46" s="69"/>
-      <c r="W46" s="55"/>
-      <c r="X46" s="68"/>
-      <c r="Y46" s="68"/>
-      <c r="Z46" s="69"/>
-      <c r="AA46" s="67"/>
-      <c r="AB46" s="68"/>
-      <c r="AC46" s="68"/>
-      <c r="AD46" s="52"/>
-      <c r="AE46" s="69"/>
-      <c r="AF46" s="67"/>
-      <c r="AG46" s="68"/>
-      <c r="AH46" s="68"/>
-      <c r="AI46" s="68"/>
-      <c r="AJ46" s="62"/>
-      <c r="AK46" s="68"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="75"/>
+      <c r="G46" s="73"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="72"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="72"/>
+      <c r="N46" s="73"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="72"/>
+      <c r="T46" s="72"/>
+      <c r="U46" s="72"/>
+      <c r="V46" s="73"/>
+      <c r="W46" s="59"/>
+      <c r="X46" s="72"/>
+      <c r="Y46" s="72"/>
+      <c r="Z46" s="73"/>
+      <c r="AA46" s="71"/>
+      <c r="AB46" s="72"/>
+      <c r="AC46" s="72"/>
+      <c r="AD46" s="56"/>
+      <c r="AE46" s="73"/>
+      <c r="AF46" s="71"/>
+      <c r="AG46" s="72"/>
+      <c r="AH46" s="72"/>
+      <c r="AI46" s="72"/>
+      <c r="AJ46" s="66"/>
+      <c r="AK46" s="72"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="65"/>
-      <c r="C47" s="66"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="71"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="68"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="68"/>
-      <c r="L47" s="52"/>
-      <c r="M47" s="68"/>
-      <c r="N47" s="69"/>
-      <c r="O47" s="67"/>
-      <c r="P47" s="68"/>
-      <c r="Q47" s="68"/>
-      <c r="R47" s="68"/>
-      <c r="S47" s="68"/>
-      <c r="T47" s="68"/>
-      <c r="U47" s="68"/>
-      <c r="V47" s="69"/>
-      <c r="W47" s="55"/>
-      <c r="X47" s="68"/>
-      <c r="Y47" s="68"/>
-      <c r="Z47" s="69"/>
-      <c r="AA47" s="67"/>
-      <c r="AB47" s="68"/>
-      <c r="AC47" s="68"/>
-      <c r="AD47" s="52"/>
-      <c r="AE47" s="69"/>
-      <c r="AF47" s="67"/>
-      <c r="AG47" s="68"/>
-      <c r="AH47" s="68"/>
-      <c r="AI47" s="68"/>
-      <c r="AJ47" s="68"/>
-      <c r="AK47" s="68"/>
-      <c r="AN47" s="79" t="s">
-        <v>159</v>
-      </c>
-      <c r="AO47" s="62"/>
+      <c r="B47" s="69"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="72"/>
+      <c r="E47" s="72"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="73"/>
+      <c r="H47" s="71"/>
+      <c r="I47" s="72"/>
+      <c r="J47" s="72"/>
+      <c r="K47" s="72"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="72"/>
+      <c r="N47" s="73"/>
+      <c r="O47" s="71"/>
+      <c r="P47" s="72"/>
+      <c r="Q47" s="72"/>
+      <c r="R47" s="72"/>
+      <c r="S47" s="72"/>
+      <c r="T47" s="72"/>
+      <c r="U47" s="72"/>
+      <c r="V47" s="73"/>
+      <c r="W47" s="59"/>
+      <c r="X47" s="72"/>
+      <c r="Y47" s="72"/>
+      <c r="Z47" s="73"/>
+      <c r="AA47" s="71"/>
+      <c r="AB47" s="72"/>
+      <c r="AC47" s="72"/>
+      <c r="AD47" s="56"/>
+      <c r="AE47" s="73"/>
+      <c r="AF47" s="71"/>
+      <c r="AG47" s="72"/>
+      <c r="AH47" s="72"/>
+      <c r="AI47" s="72"/>
+      <c r="AJ47" s="72"/>
+      <c r="AK47" s="72"/>
+      <c r="AN47" s="83" t="s">
+        <v>162</v>
+      </c>
+      <c r="AO47" s="66"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="65"/>
-      <c r="C48" s="66" t="s">
-        <v>160</v>
-      </c>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="71"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="67"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="68"/>
-      <c r="L48" s="52"/>
-      <c r="M48" s="68"/>
-      <c r="N48" s="69"/>
-      <c r="O48" s="67"/>
-      <c r="P48" s="68"/>
-      <c r="Q48" s="68"/>
-      <c r="R48" s="68"/>
-      <c r="S48" s="68"/>
-      <c r="T48" s="68"/>
-      <c r="U48" s="68"/>
-      <c r="V48" s="69"/>
-      <c r="W48" s="55"/>
-      <c r="X48" s="68"/>
-      <c r="Y48" s="68"/>
-      <c r="Z48" s="69"/>
-      <c r="AA48" s="67"/>
-      <c r="AB48" s="68"/>
-      <c r="AC48" s="68"/>
-      <c r="AD48" s="52"/>
-      <c r="AE48" s="69"/>
-      <c r="AF48" s="67"/>
-      <c r="AG48" s="68"/>
-      <c r="AH48" s="68"/>
-      <c r="AI48" s="68"/>
-      <c r="AJ48" s="68"/>
-      <c r="AK48" s="80"/>
-      <c r="AN48" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="AO48" s="61"/>
+      <c r="B48" s="69"/>
+      <c r="C48" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="D48" s="72"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="72"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="72"/>
+      <c r="N48" s="73"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="72"/>
+      <c r="T48" s="72"/>
+      <c r="U48" s="72"/>
+      <c r="V48" s="73"/>
+      <c r="W48" s="59"/>
+      <c r="X48" s="72"/>
+      <c r="Y48" s="72"/>
+      <c r="Z48" s="73"/>
+      <c r="AA48" s="71"/>
+      <c r="AB48" s="72"/>
+      <c r="AC48" s="72"/>
+      <c r="AD48" s="56"/>
+      <c r="AE48" s="73"/>
+      <c r="AF48" s="71"/>
+      <c r="AG48" s="72"/>
+      <c r="AH48" s="72"/>
+      <c r="AI48" s="72"/>
+      <c r="AJ48" s="72"/>
+      <c r="AK48" s="84"/>
+      <c r="AN48" s="83" t="s">
+        <v>164</v>
+      </c>
+      <c r="AO48" s="65"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="65"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="68"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="71"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="68"/>
-      <c r="K49" s="68"/>
-      <c r="L49" s="52"/>
-      <c r="M49" s="68"/>
-      <c r="N49" s="69"/>
-      <c r="O49" s="67"/>
-      <c r="P49" s="68"/>
-      <c r="Q49" s="68"/>
-      <c r="R49" s="68"/>
-      <c r="S49" s="68"/>
-      <c r="T49" s="68"/>
-      <c r="U49" s="68"/>
-      <c r="V49" s="69"/>
-      <c r="W49" s="55"/>
-      <c r="X49" s="68"/>
-      <c r="Y49" s="68"/>
-      <c r="Z49" s="69"/>
-      <c r="AA49" s="67"/>
-      <c r="AB49" s="68"/>
-      <c r="AC49" s="68"/>
-      <c r="AD49" s="52"/>
-      <c r="AE49" s="69"/>
-      <c r="AF49" s="67"/>
-      <c r="AG49" s="68"/>
-      <c r="AH49" s="68"/>
-      <c r="AI49" s="68"/>
-      <c r="AJ49" s="68"/>
-      <c r="AK49" s="68"/>
-      <c r="AN49" s="79" t="s">
-        <v>162</v>
-      </c>
-      <c r="AO49" s="57"/>
+      <c r="B49" s="69"/>
+      <c r="C49" s="70"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="75"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="72"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="72"/>
+      <c r="N49" s="73"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="72"/>
+      <c r="T49" s="72"/>
+      <c r="U49" s="72"/>
+      <c r="V49" s="73"/>
+      <c r="W49" s="59"/>
+      <c r="X49" s="72"/>
+      <c r="Y49" s="72"/>
+      <c r="Z49" s="73"/>
+      <c r="AA49" s="71"/>
+      <c r="AB49" s="72"/>
+      <c r="AC49" s="72"/>
+      <c r="AD49" s="56"/>
+      <c r="AE49" s="73"/>
+      <c r="AF49" s="71"/>
+      <c r="AG49" s="72"/>
+      <c r="AH49" s="72"/>
+      <c r="AI49" s="72"/>
+      <c r="AJ49" s="72"/>
+      <c r="AK49" s="72"/>
+      <c r="AN49" s="83" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO49" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -10982,801 +11027,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="81"/>
+      <c r="B1" s="85"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="82" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="83" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" s="84" t="s">
-        <v>163</v>
-      </c>
-      <c r="E2" s="85" t="s">
-        <v>164</v>
-      </c>
-      <c r="F2" s="86" t="s">
-        <v>165</v>
-      </c>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="86" t="s">
+      <c r="B2" s="86" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="88" t="s">
         <v>166</v>
       </c>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="86" t="s">
-        <v>101</v>
-      </c>
-      <c r="O2" s="86"/>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="86" t="s">
-        <v>102</v>
-      </c>
-      <c r="S2" s="87"/>
-      <c r="AD2" s="88"/>
+      <c r="E2" s="89" t="s">
+        <v>167</v>
+      </c>
+      <c r="F2" s="90" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="90" t="s">
+        <v>169</v>
+      </c>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="90" t="s">
+        <v>104</v>
+      </c>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="90" t="s">
+        <v>105</v>
+      </c>
+      <c r="S2" s="91"/>
+      <c r="AD2" s="92"/>
     </row>
     <row r="3">
-      <c r="B3" s="89"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="91" t="s">
-        <v>167</v>
-      </c>
-      <c r="E3" s="92">
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="95" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="96">
         <v>4</v>
       </c>
-      <c r="F3" s="93">
+      <c r="F3" s="97">
         <v>1</v>
       </c>
-      <c r="G3" s="94">
+      <c r="G3" s="98">
         <v>2</v>
       </c>
-      <c r="H3" s="94">
+      <c r="H3" s="98">
         <v>3</v>
       </c>
-      <c r="I3" s="92">
+      <c r="I3" s="96">
         <v>4</v>
       </c>
-      <c r="J3" s="93">
+      <c r="J3" s="97">
         <v>1</v>
       </c>
-      <c r="K3" s="94">
+      <c r="K3" s="98">
         <v>2</v>
       </c>
-      <c r="L3" s="94">
+      <c r="L3" s="98">
         <v>3</v>
       </c>
-      <c r="M3" s="92">
+      <c r="M3" s="96">
         <v>4</v>
       </c>
-      <c r="N3" s="93">
+      <c r="N3" s="97">
         <v>1</v>
       </c>
-      <c r="O3" s="94">
+      <c r="O3" s="98">
         <v>2</v>
       </c>
-      <c r="P3" s="94">
+      <c r="P3" s="98">
         <v>3</v>
       </c>
-      <c r="Q3" s="92">
+      <c r="Q3" s="96">
         <v>4</v>
       </c>
-      <c r="R3" s="93">
+      <c r="R3" s="97">
         <v>1</v>
       </c>
-      <c r="S3" s="95">
+      <c r="S3" s="99">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="96" t="s">
-        <v>169</v>
-      </c>
-      <c r="C4" s="83" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="97"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="101"/>
-      <c r="O4" s="100"/>
-      <c r="P4" s="100"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="101"/>
-      <c r="S4" s="102"/>
+      <c r="B4" s="100" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="87" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="101"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="105"/>
+      <c r="O4" s="104"/>
+      <c r="P4" s="104"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="105"/>
+      <c r="S4" s="106"/>
       <c r="U4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="96"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
-      <c r="M5" s="105"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="108"/>
-      <c r="P5" s="108"/>
-      <c r="Q5" s="105"/>
-      <c r="R5" s="109"/>
-      <c r="S5" s="110"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="109"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="112"/>
+      <c r="P5" s="112"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="114"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="96"/>
-      <c r="C6" s="111" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="112"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="114"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="116"/>
-      <c r="I6" s="113"/>
-      <c r="J6" s="117"/>
-      <c r="K6" s="116"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="113"/>
-      <c r="N6" s="117"/>
-      <c r="O6" s="116"/>
-      <c r="P6" s="116"/>
-      <c r="Q6" s="113"/>
-      <c r="R6" s="117"/>
-      <c r="S6" s="118"/>
-      <c r="U6" s="119" t="s">
-        <v>173</v>
-      </c>
-      <c r="V6" s="119"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="115" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="116"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="120"/>
+      <c r="L6" s="120"/>
+      <c r="M6" s="117"/>
+      <c r="N6" s="121"/>
+      <c r="O6" s="120"/>
+      <c r="P6" s="120"/>
+      <c r="Q6" s="117"/>
+      <c r="R6" s="121"/>
+      <c r="S6" s="122"/>
+      <c r="U6" s="123" t="s">
+        <v>176</v>
+      </c>
+      <c r="V6" s="123"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="96"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="109"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="109"/>
-      <c r="K7" s="108"/>
-      <c r="L7" s="108"/>
-      <c r="M7" s="105"/>
-      <c r="N7" s="109"/>
-      <c r="O7" s="108"/>
-      <c r="P7" s="108"/>
-      <c r="Q7" s="105"/>
-      <c r="R7" s="109"/>
-      <c r="S7" s="110"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="112"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="113"/>
+      <c r="O7" s="112"/>
+      <c r="P7" s="112"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="113"/>
+      <c r="S7" s="114"/>
       <c r="U7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="96"/>
-      <c r="C8" s="111" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="112"/>
-      <c r="E8" s="113"/>
-      <c r="F8" s="114"/>
-      <c r="G8" s="116"/>
-      <c r="H8" s="116"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="117"/>
-      <c r="K8" s="116"/>
-      <c r="L8" s="116"/>
-      <c r="M8" s="113"/>
-      <c r="N8" s="117"/>
-      <c r="O8" s="116"/>
-      <c r="P8" s="116"/>
-      <c r="Q8" s="113"/>
-      <c r="R8" s="117"/>
-      <c r="S8" s="118"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="115" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="116"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="120"/>
+      <c r="L8" s="120"/>
+      <c r="M8" s="117"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="120"/>
+      <c r="P8" s="120"/>
+      <c r="Q8" s="117"/>
+      <c r="R8" s="121"/>
+      <c r="S8" s="122"/>
       <c r="U8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="96"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="109"/>
-      <c r="G9" s="107"/>
-      <c r="H9" s="108"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="109"/>
-      <c r="K9" s="108"/>
-      <c r="L9" s="108"/>
-      <c r="M9" s="105"/>
-      <c r="N9" s="109"/>
-      <c r="O9" s="108"/>
-      <c r="P9" s="108"/>
-      <c r="Q9" s="105"/>
-      <c r="R9" s="109"/>
-      <c r="S9" s="110"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="109"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="109"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="112"/>
+      <c r="M9" s="109"/>
+      <c r="N9" s="113"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="112"/>
+      <c r="Q9" s="109"/>
+      <c r="R9" s="113"/>
+      <c r="S9" s="114"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="96"/>
-      <c r="C10" s="111" t="s">
-        <v>177</v>
-      </c>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113"/>
-      <c r="F10" s="117"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="113"/>
-      <c r="J10" s="117"/>
-      <c r="K10" s="116"/>
-      <c r="L10" s="116"/>
-      <c r="M10" s="113"/>
-      <c r="N10" s="117"/>
-      <c r="O10" s="116"/>
-      <c r="P10" s="116"/>
-      <c r="Q10" s="113"/>
-      <c r="R10" s="117"/>
-      <c r="S10" s="118"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="116"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="117"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="120"/>
+      <c r="L10" s="120"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="120"/>
+      <c r="P10" s="120"/>
+      <c r="Q10" s="117"/>
+      <c r="R10" s="121"/>
+      <c r="S10" s="122"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="120"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="124"/>
-      <c r="K11" s="126"/>
-      <c r="L11" s="126"/>
-      <c r="M11" s="123"/>
-      <c r="N11" s="124"/>
-      <c r="O11" s="126"/>
-      <c r="P11" s="126"/>
-      <c r="Q11" s="123"/>
-      <c r="R11" s="124"/>
-      <c r="S11" s="127"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="126"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="130"/>
+      <c r="P11" s="130"/>
+      <c r="Q11" s="127"/>
+      <c r="R11" s="128"/>
+      <c r="S11" s="131"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="82" t="s">
-        <v>178</v>
-      </c>
-      <c r="C12" s="83" t="s">
-        <v>179</v>
-      </c>
-      <c r="D12" s="97"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="128"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="100"/>
-      <c r="M12" s="98"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="100"/>
-      <c r="P12" s="100"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="101"/>
-      <c r="S12" s="102"/>
+      <c r="B12" s="86" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="87" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" s="101"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="102"/>
+      <c r="N12" s="105"/>
+      <c r="O12" s="104"/>
+      <c r="P12" s="104"/>
+      <c r="Q12" s="102"/>
+      <c r="R12" s="105"/>
+      <c r="S12" s="106"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="96"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="108"/>
-      <c r="H13" s="108"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="108"/>
-      <c r="L13" s="108"/>
-      <c r="M13" s="105"/>
-      <c r="N13" s="109"/>
-      <c r="O13" s="108"/>
-      <c r="P13" s="108"/>
-      <c r="Q13" s="105"/>
-      <c r="R13" s="109"/>
-      <c r="S13" s="110"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="109"/>
+      <c r="N13" s="113"/>
+      <c r="O13" s="112"/>
+      <c r="P13" s="112"/>
+      <c r="Q13" s="109"/>
+      <c r="R13" s="113"/>
+      <c r="S13" s="114"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="96"/>
-      <c r="C14" s="111" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" s="130"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="116"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="113"/>
-      <c r="J14" s="117"/>
-      <c r="K14" s="116"/>
-      <c r="L14" s="116"/>
-      <c r="M14" s="113"/>
-      <c r="N14" s="117"/>
-      <c r="O14" s="116"/>
-      <c r="P14" s="116"/>
-      <c r="Q14" s="113"/>
-      <c r="R14" s="117"/>
-      <c r="S14" s="118"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="115" t="s">
+        <v>183</v>
+      </c>
+      <c r="D14" s="134"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="120"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="120"/>
+      <c r="P14" s="120"/>
+      <c r="Q14" s="117"/>
+      <c r="R14" s="121"/>
+      <c r="S14" s="122"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="96"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="109"/>
-      <c r="G15" s="108"/>
-      <c r="H15" s="108"/>
-      <c r="I15" s="131"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="108"/>
-      <c r="L15" s="108"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="109"/>
-      <c r="O15" s="108"/>
-      <c r="P15" s="108"/>
-      <c r="Q15" s="105"/>
-      <c r="R15" s="109"/>
-      <c r="S15" s="110"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="107"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="109"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="109"/>
+      <c r="N15" s="113"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="109"/>
+      <c r="R15" s="113"/>
+      <c r="S15" s="114"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="96"/>
-      <c r="C16" s="111" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16" s="112"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="116"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="132"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="116"/>
-      <c r="L16" s="116"/>
-      <c r="M16" s="113"/>
-      <c r="N16" s="117"/>
-      <c r="O16" s="116"/>
-      <c r="P16" s="116"/>
-      <c r="Q16" s="113"/>
-      <c r="R16" s="117"/>
-      <c r="S16" s="118"/>
+      <c r="B16" s="100"/>
+      <c r="C16" s="115" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="116"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="117"/>
+      <c r="R16" s="121"/>
+      <c r="S16" s="122"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="120"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="123"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="126"/>
-      <c r="H17" s="126"/>
-      <c r="I17" s="123"/>
-      <c r="J17" s="133"/>
-      <c r="K17" s="125"/>
-      <c r="L17" s="126"/>
-      <c r="M17" s="123"/>
-      <c r="N17" s="124"/>
-      <c r="O17" s="126"/>
-      <c r="P17" s="126"/>
-      <c r="Q17" s="123"/>
-      <c r="R17" s="124"/>
-      <c r="S17" s="127"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="125"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="137"/>
+      <c r="K17" s="129"/>
+      <c r="L17" s="130"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="128"/>
+      <c r="O17" s="130"/>
+      <c r="P17" s="130"/>
+      <c r="Q17" s="127"/>
+      <c r="R17" s="128"/>
+      <c r="S17" s="131"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="84" t="s">
-        <v>182</v>
-      </c>
-      <c r="C18" s="83" t="s">
-        <v>183</v>
-      </c>
-      <c r="D18" s="97"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="100"/>
-      <c r="H18" s="100"/>
-      <c r="I18" s="129"/>
-      <c r="J18" s="101"/>
-      <c r="K18" s="100"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="98"/>
-      <c r="N18" s="101"/>
-      <c r="O18" s="100"/>
-      <c r="P18" s="100"/>
-      <c r="Q18" s="98"/>
-      <c r="R18" s="101"/>
-      <c r="S18" s="102"/>
+      <c r="B18" s="88" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="87" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18" s="101"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="102"/>
+      <c r="N18" s="105"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="104"/>
+      <c r="Q18" s="102"/>
+      <c r="R18" s="105"/>
+      <c r="S18" s="106"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="96"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="109"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="108"/>
-      <c r="I19" s="105"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="108"/>
-      <c r="L19" s="108"/>
-      <c r="M19" s="105"/>
-      <c r="N19" s="109"/>
-      <c r="O19" s="108"/>
-      <c r="P19" s="108"/>
-      <c r="Q19" s="105"/>
-      <c r="R19" s="109"/>
-      <c r="S19" s="110"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="109"/>
+      <c r="N19" s="113"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="109"/>
+      <c r="R19" s="113"/>
+      <c r="S19" s="114"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="96"/>
-      <c r="C20" s="111" t="s">
-        <v>184</v>
-      </c>
-      <c r="D20" s="112"/>
-      <c r="E20" s="113"/>
-      <c r="F20" s="117"/>
-      <c r="G20" s="116"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="132"/>
-      <c r="J20" s="114"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="113"/>
-      <c r="N20" s="117"/>
-      <c r="O20" s="116"/>
-      <c r="P20" s="116"/>
-      <c r="Q20" s="113"/>
-      <c r="R20" s="117"/>
-      <c r="S20" s="118"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="115" t="s">
+        <v>187</v>
+      </c>
+      <c r="D20" s="116"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="118"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="117"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="120"/>
+      <c r="P20" s="120"/>
+      <c r="Q20" s="117"/>
+      <c r="R20" s="121"/>
+      <c r="S20" s="122"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="96"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="108"/>
-      <c r="H21" s="108"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="108"/>
-      <c r="L21" s="108"/>
-      <c r="M21" s="105"/>
-      <c r="N21" s="134"/>
-      <c r="O21" s="108"/>
-      <c r="P21" s="108"/>
-      <c r="Q21" s="105"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="110"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="138"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="113"/>
+      <c r="S21" s="114"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="96"/>
-      <c r="C22" s="111" t="s">
-        <v>185</v>
-      </c>
-      <c r="D22" s="112"/>
-      <c r="E22" s="113"/>
-      <c r="F22" s="117"/>
-      <c r="G22" s="116"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="113"/>
-      <c r="J22" s="117"/>
-      <c r="K22" s="115"/>
-      <c r="L22" s="115"/>
-      <c r="M22" s="113"/>
-      <c r="N22" s="117"/>
-      <c r="O22" s="116"/>
-      <c r="P22" s="116"/>
-      <c r="Q22" s="113"/>
-      <c r="R22" s="117"/>
-      <c r="S22" s="118"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="115" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="116"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="120"/>
+      <c r="P22" s="120"/>
+      <c r="Q22" s="117"/>
+      <c r="R22" s="121"/>
+      <c r="S22" s="122"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="120"/>
-      <c r="C23" s="121"/>
-      <c r="D23" s="122"/>
-      <c r="E23" s="123"/>
-      <c r="F23" s="124"/>
-      <c r="G23" s="126"/>
-      <c r="H23" s="126"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="124"/>
-      <c r="K23" s="126"/>
-      <c r="L23" s="126"/>
-      <c r="M23" s="123"/>
-      <c r="N23" s="124"/>
-      <c r="O23" s="126"/>
-      <c r="P23" s="126"/>
-      <c r="Q23" s="123"/>
-      <c r="R23" s="124"/>
-      <c r="S23" s="127"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="130"/>
+      <c r="I23" s="127"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="130"/>
+      <c r="L23" s="130"/>
+      <c r="M23" s="127"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="130"/>
+      <c r="P23" s="130"/>
+      <c r="Q23" s="127"/>
+      <c r="R23" s="128"/>
+      <c r="S23" s="131"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="84" t="s">
-        <v>186</v>
-      </c>
-      <c r="C24" s="83" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" s="97"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="101"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="129"/>
-      <c r="N24" s="99"/>
-      <c r="O24" s="128"/>
-      <c r="P24" s="128"/>
-      <c r="Q24" s="98"/>
-      <c r="R24" s="101"/>
-      <c r="S24" s="102"/>
+      <c r="B24" s="88" t="s">
+        <v>189</v>
+      </c>
+      <c r="C24" s="87" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="101"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="133"/>
+      <c r="N24" s="103"/>
+      <c r="O24" s="132"/>
+      <c r="P24" s="132"/>
+      <c r="Q24" s="102"/>
+      <c r="R24" s="105"/>
+      <c r="S24" s="106"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="96"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="109"/>
-      <c r="G25" s="108"/>
-      <c r="H25" s="108"/>
-      <c r="I25" s="105"/>
-      <c r="J25" s="109"/>
-      <c r="K25" s="108"/>
-      <c r="L25" s="108"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="109"/>
-      <c r="O25" s="108"/>
-      <c r="P25" s="108"/>
-      <c r="Q25" s="105"/>
-      <c r="R25" s="109"/>
-      <c r="S25" s="110"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="113"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="109"/>
+      <c r="R25" s="113"/>
+      <c r="S25" s="114"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="96"/>
-      <c r="C26" s="111" t="s">
-        <v>188</v>
-      </c>
-      <c r="D26" s="112"/>
-      <c r="E26" s="113"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="116"/>
-      <c r="I26" s="113"/>
-      <c r="J26" s="117"/>
-      <c r="K26" s="116"/>
-      <c r="L26" s="116"/>
-      <c r="M26" s="113"/>
-      <c r="N26" s="117"/>
-      <c r="O26" s="115"/>
-      <c r="P26" s="115"/>
-      <c r="Q26" s="113"/>
-      <c r="R26" s="117"/>
-      <c r="S26" s="118"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="115" t="s">
+        <v>191</v>
+      </c>
+      <c r="D26" s="116"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="121"/>
+      <c r="K26" s="120"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="117"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="119"/>
+      <c r="P26" s="119"/>
+      <c r="Q26" s="117"/>
+      <c r="R26" s="121"/>
+      <c r="S26" s="122"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="96"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="109"/>
-      <c r="G27" s="108"/>
-      <c r="H27" s="108"/>
-      <c r="I27" s="105"/>
-      <c r="J27" s="109"/>
-      <c r="K27" s="108"/>
-      <c r="L27" s="108"/>
-      <c r="M27" s="105"/>
-      <c r="N27" s="109"/>
-      <c r="O27" s="108"/>
-      <c r="P27" s="108"/>
-      <c r="Q27" s="105"/>
-      <c r="R27" s="109"/>
-      <c r="S27" s="110"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="109"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="112"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="109"/>
+      <c r="N27" s="113"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="109"/>
+      <c r="R27" s="113"/>
+      <c r="S27" s="114"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="96"/>
-      <c r="C28" s="111" t="s">
-        <v>189</v>
-      </c>
-      <c r="D28" s="112"/>
-      <c r="E28" s="113"/>
-      <c r="F28" s="117"/>
-      <c r="G28" s="116"/>
-      <c r="H28" s="116"/>
-      <c r="I28" s="113"/>
-      <c r="J28" s="117"/>
-      <c r="K28" s="116"/>
-      <c r="L28" s="116"/>
-      <c r="M28" s="113"/>
-      <c r="N28" s="117"/>
-      <c r="O28" s="116"/>
-      <c r="P28" s="115"/>
-      <c r="Q28" s="132"/>
-      <c r="R28" s="117"/>
-      <c r="S28" s="118"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="115" t="s">
+        <v>192</v>
+      </c>
+      <c r="D28" s="116"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="121"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="117"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="120"/>
+      <c r="P28" s="119"/>
+      <c r="Q28" s="136"/>
+      <c r="R28" s="121"/>
+      <c r="S28" s="122"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="96"/>
-      <c r="C29" s="90"/>
-      <c r="D29" s="135"/>
-      <c r="E29" s="136"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="139"/>
-      <c r="I29" s="136"/>
-      <c r="J29" s="137"/>
-      <c r="K29" s="138"/>
-      <c r="L29" s="139"/>
-      <c r="M29" s="136"/>
-      <c r="N29" s="140"/>
-      <c r="O29" s="139"/>
-      <c r="P29" s="138"/>
-      <c r="Q29" s="136"/>
-      <c r="R29" s="137"/>
-      <c r="S29" s="141"/>
+      <c r="B29" s="100"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="143"/>
+      <c r="I29" s="140"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="142"/>
+      <c r="L29" s="143"/>
+      <c r="M29" s="140"/>
+      <c r="N29" s="144"/>
+      <c r="O29" s="143"/>
+      <c r="P29" s="142"/>
+      <c r="Q29" s="140"/>
+      <c r="R29" s="141"/>
+      <c r="S29" s="145"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="142" t="s">
+      <c r="B30" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="143" t="s">
-        <v>135</v>
-      </c>
-      <c r="D30" s="97"/>
-      <c r="E30" s="144"/>
-      <c r="F30" s="145"/>
-      <c r="G30" s="145"/>
-      <c r="H30" s="146"/>
-      <c r="I30" s="147"/>
-      <c r="J30" s="145"/>
-      <c r="K30" s="145"/>
-      <c r="L30" s="146"/>
-      <c r="M30" s="147"/>
-      <c r="N30" s="145"/>
-      <c r="O30" s="146"/>
-      <c r="P30" s="145"/>
-      <c r="Q30" s="147"/>
-      <c r="R30" s="145"/>
-      <c r="S30" s="148"/>
+      <c r="C30" s="147" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="101"/>
+      <c r="E30" s="148"/>
+      <c r="F30" s="149"/>
+      <c r="G30" s="149"/>
+      <c r="H30" s="150"/>
+      <c r="I30" s="151"/>
+      <c r="J30" s="149"/>
+      <c r="K30" s="149"/>
+      <c r="L30" s="150"/>
+      <c r="M30" s="151"/>
+      <c r="N30" s="149"/>
+      <c r="O30" s="150"/>
+      <c r="P30" s="149"/>
+      <c r="Q30" s="151"/>
+      <c r="R30" s="149"/>
+      <c r="S30" s="152"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="149"/>
-      <c r="C31" s="150"/>
-      <c r="D31" s="104"/>
-      <c r="E31" s="151"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="152"/>
-      <c r="H31" s="153"/>
-      <c r="I31" s="154"/>
-      <c r="J31" s="152"/>
-      <c r="K31" s="155"/>
-      <c r="L31" s="153"/>
-      <c r="M31" s="154"/>
-      <c r="N31" s="152"/>
-      <c r="O31" s="153"/>
-      <c r="P31" s="152"/>
-      <c r="Q31" s="154"/>
-      <c r="R31" s="152"/>
-      <c r="S31" s="110"/>
+      <c r="B31" s="153"/>
+      <c r="C31" s="154"/>
+      <c r="D31" s="108"/>
+      <c r="E31" s="155"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="156"/>
+      <c r="H31" s="157"/>
+      <c r="I31" s="158"/>
+      <c r="J31" s="156"/>
+      <c r="K31" s="159"/>
+      <c r="L31" s="157"/>
+      <c r="M31" s="158"/>
+      <c r="N31" s="156"/>
+      <c r="O31" s="157"/>
+      <c r="P31" s="156"/>
+      <c r="Q31" s="158"/>
+      <c r="R31" s="156"/>
+      <c r="S31" s="114"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="149"/>
-      <c r="C32" s="150" t="s">
+      <c r="B32" s="153"/>
+      <c r="C32" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="112"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="157"/>
-      <c r="G32" s="157"/>
-      <c r="H32" s="158"/>
-      <c r="I32" s="159"/>
-      <c r="J32" s="157"/>
-      <c r="K32" s="157"/>
-      <c r="L32" s="158"/>
-      <c r="M32" s="159"/>
-      <c r="N32" s="157"/>
-      <c r="O32" s="158"/>
-      <c r="P32" s="157"/>
-      <c r="Q32" s="159"/>
-      <c r="R32" s="157"/>
-      <c r="S32" s="160"/>
+      <c r="D32" s="116"/>
+      <c r="E32" s="160"/>
+      <c r="F32" s="161"/>
+      <c r="G32" s="161"/>
+      <c r="H32" s="162"/>
+      <c r="I32" s="163"/>
+      <c r="J32" s="161"/>
+      <c r="K32" s="161"/>
+      <c r="L32" s="162"/>
+      <c r="M32" s="163"/>
+      <c r="N32" s="161"/>
+      <c r="O32" s="162"/>
+      <c r="P32" s="161"/>
+      <c r="Q32" s="163"/>
+      <c r="R32" s="161"/>
+      <c r="S32" s="164"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="149"/>
-      <c r="C33" s="150"/>
-      <c r="D33" s="104"/>
-      <c r="E33" s="151"/>
-      <c r="F33" s="155"/>
-      <c r="G33" s="152"/>
-      <c r="H33" s="161"/>
-      <c r="I33" s="162"/>
-      <c r="J33" s="152"/>
-      <c r="K33" s="155"/>
-      <c r="L33" s="153"/>
-      <c r="M33" s="154"/>
-      <c r="N33" s="152"/>
-      <c r="O33" s="153"/>
-      <c r="P33" s="152"/>
-      <c r="Q33" s="154"/>
-      <c r="R33" s="152"/>
-      <c r="S33" s="110"/>
+      <c r="B33" s="153"/>
+      <c r="C33" s="154"/>
+      <c r="D33" s="108"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="159"/>
+      <c r="G33" s="156"/>
+      <c r="H33" s="165"/>
+      <c r="I33" s="166"/>
+      <c r="J33" s="156"/>
+      <c r="K33" s="159"/>
+      <c r="L33" s="157"/>
+      <c r="M33" s="158"/>
+      <c r="N33" s="156"/>
+      <c r="O33" s="157"/>
+      <c r="P33" s="156"/>
+      <c r="Q33" s="158"/>
+      <c r="R33" s="156"/>
+      <c r="S33" s="114"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="149"/>
-      <c r="C34" s="103" t="s">
-        <v>190</v>
-      </c>
-      <c r="D34" s="135"/>
-      <c r="E34" s="163"/>
-      <c r="F34" s="164"/>
-      <c r="G34" s="164"/>
-      <c r="H34" s="165"/>
-      <c r="I34" s="166"/>
-      <c r="J34" s="164"/>
-      <c r="K34" s="164"/>
-      <c r="L34" s="165"/>
-      <c r="M34" s="166"/>
-      <c r="N34" s="164"/>
-      <c r="O34" s="165"/>
-      <c r="P34" s="164"/>
-      <c r="Q34" s="166"/>
-      <c r="R34" s="164"/>
-      <c r="S34" s="167"/>
-      <c r="U34" s="168"/>
-      <c r="V34" s="169" t="s">
-        <v>191</v>
+      <c r="B34" s="153"/>
+      <c r="C34" s="107" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" s="139"/>
+      <c r="E34" s="167"/>
+      <c r="F34" s="168"/>
+      <c r="G34" s="168"/>
+      <c r="H34" s="169"/>
+      <c r="I34" s="170"/>
+      <c r="J34" s="168"/>
+      <c r="K34" s="168"/>
+      <c r="L34" s="169"/>
+      <c r="M34" s="170"/>
+      <c r="N34" s="168"/>
+      <c r="O34" s="169"/>
+      <c r="P34" s="168"/>
+      <c r="Q34" s="170"/>
+      <c r="R34" s="168"/>
+      <c r="S34" s="171"/>
+      <c r="U34" s="172"/>
+      <c r="V34" s="173" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="170"/>
-      <c r="C35" s="171"/>
-      <c r="D35" s="122"/>
-      <c r="E35" s="172"/>
-      <c r="F35" s="173"/>
-      <c r="G35" s="173"/>
-      <c r="H35" s="174"/>
-      <c r="I35" s="175"/>
-      <c r="J35" s="173"/>
-      <c r="K35" s="173"/>
-      <c r="L35" s="174"/>
-      <c r="M35" s="175"/>
-      <c r="N35" s="173"/>
-      <c r="O35" s="174"/>
-      <c r="P35" s="173"/>
-      <c r="Q35" s="175"/>
-      <c r="R35" s="173"/>
-      <c r="S35" s="127"/>
-      <c r="U35" s="176"/>
-      <c r="V35" s="177" t="s">
-        <v>192</v>
+      <c r="B35" s="174"/>
+      <c r="C35" s="175"/>
+      <c r="D35" s="126"/>
+      <c r="E35" s="176"/>
+      <c r="F35" s="177"/>
+      <c r="G35" s="177"/>
+      <c r="H35" s="178"/>
+      <c r="I35" s="179"/>
+      <c r="J35" s="177"/>
+      <c r="K35" s="177"/>
+      <c r="L35" s="178"/>
+      <c r="M35" s="179"/>
+      <c r="N35" s="177"/>
+      <c r="O35" s="178"/>
+      <c r="P35" s="177"/>
+      <c r="Q35" s="179"/>
+      <c r="R35" s="177"/>
+      <c r="S35" s="131"/>
+      <c r="U35" s="180"/>
+      <c r="V35" s="181" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/LHO - M5 - JournalPlanif.xlsx
+++ b/Documentation/LHO - M5 - JournalPlanif.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t>date</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;-- A jour avec la BDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation du processus de déploiement multiplateforme.</t>
   </si>
   <si>
     <t xml:space="preserve">Par jour</t>
@@ -1599,7 +1602,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="180">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1648,12 +1651,6 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1661,10 +1658,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4900,8 +4897,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E73">
-  <autoFilter ref="B2:E73"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E74">
+  <autoFilter ref="B2:E74"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5465,7 +5462,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.7595307917888561e-002</v>
+        <v>1.7492711370262388e-002</v>
       </c>
       <c r="J3" s="12" t="str">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -5498,7 +5495,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.7595307917888561e-002</v>
+        <v>1.7492711370262388e-002</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -5531,7 +5528,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>5.5718475073313775e-002</v>
+        <v>5.5393586005830893e-002</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -5564,7 +5561,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>9.9706744868035171e-002</v>
+        <v>9.9125364431486868e-002</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -5593,11 +5590,11 @@
       </c>
       <c r="H7" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.32551319648093835</v>
+        <v>0.32944606413994165</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -5605,7 +5602,7 @@
       </c>
       <c r="K7" s="13">
         <f/>
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="8" ht="28.5">
@@ -5630,7 +5627,7 @@
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.44379276637341147</v>
+        <v>0.44120505344995137</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -5663,7 +5660,7 @@
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>3.714565004887585e-002</v>
+        <v>3.69290573372206e-002</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -5696,7 +5693,7 @@
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.9325513196480934e-003</v>
+        <v>2.9154518950437313e-003</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -5719,7 +5716,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>170.50000000000003</v>
+        <v>171.50000000000003</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -6562,24 +6559,24 @@
       <c r="C71" s="21">
         <v>3.4722222222222224e-002</v>
       </c>
-      <c r="D71" s="22" t="s">
+      <c r="D71" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E71" s="23" t="s">
+      <c r="E71" s="8" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="24">
+      <c r="B72" s="22">
         <v>46177</v>
       </c>
-      <c r="C72" s="25">
+      <c r="C72" s="23">
         <v>0.125</v>
       </c>
-      <c r="D72" s="26" t="s">
+      <c r="D72" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E72" s="27" t="s">
+      <c r="E72" s="2" t="s">
         <v>96</v>
       </c>
     </row>
@@ -6590,10 +6587,10 @@
       <c r="C73" s="21">
         <v>0.125</v>
       </c>
-      <c r="D73" s="22" t="s">
+      <c r="D73" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E73" s="23" t="s">
+      <c r="E73" s="8" t="s">
         <v>97</v>
       </c>
       <c r="G73" t="s">
@@ -6601,10 +6598,18 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="5"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="8"/>
+      <c r="B74" s="5">
+        <v>46180</v>
+      </c>
+      <c r="C74" s="21">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="D74" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" s="25" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="75">
       <c r="B75" s="5"/>
@@ -6664,7 +6669,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{BCC6999D-ED5A-4D2A-8069-60D39E73A911}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{53EDA031-9E73-4259-AEA0-810F96CBD0A0}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6688,11 +6693,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -6706,47 +6711,47 @@
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28">
+      <c r="A3" s="26">
         <v>46042</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C3" s="29"/>
+      <c r="C3" s="27"/>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="30">
+        <v>105</v>
+      </c>
+      <c r="F3" s="28">
         <f t="shared" ref="F3:F8" si="0">SUMPRODUCT((MONTH($A$3:$A$152)=D3)*($A$3:$A$152&lt;&gt;"")*$B$3:$B$152)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="29">
         <f t="shared" ref="G3:G8" si="1">F3*24</f>
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28">
+      <c r="A4" s="26">
         <v>46043</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6755,22 +6760,22 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" s="30">
+        <v>106</v>
+      </c>
+      <c r="F4" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28">
+      <c r="A5" s="26">
         <v>46044</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6779,22 +6784,22 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F5" s="30">
+        <v>107</v>
+      </c>
+      <c r="F5" s="28">
         <f t="shared" si="0"/>
         <v>2.6805555555555558</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="29">
         <f t="shared" si="1"/>
         <v>64.333333333333343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28">
+      <c r="A6" s="26">
         <v>46045</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6803,22 +6808,22 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F6" s="30">
+        <v>108</v>
+      </c>
+      <c r="F6" s="28">
         <f t="shared" si="0"/>
         <v>1.2083333333333333</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="29">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28">
+      <c r="A7" s="26">
         <v>46046</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6827,22 +6832,22 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7" s="30">
+        <v>109</v>
+      </c>
+      <c r="F7" s="28">
         <f t="shared" si="0"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="29">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28">
+      <c r="A8" s="26">
         <v>46047</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6851,2071 +6856,2071 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="30">
+        <v>110</v>
+      </c>
+      <c r="F8" s="28">
         <f t="shared" si="0"/>
-        <v>0.2986111111111111</v>
-      </c>
-      <c r="G8" s="31">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="G8" s="29">
         <f t="shared" si="1"/>
-        <v>7.1666666666666661</v>
+        <v>8.1666666666666679</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28">
+      <c r="A9" s="26">
         <v>46048</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
-      <c r="G9" s="31">
+      <c r="G9" s="29">
         <f>SUM(G3:G8)</f>
-        <v>107.50000000000001</v>
+        <v>108.50000000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28">
+      <c r="A10" s="26">
         <v>46049</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="28">
+      <c r="A11" s="26">
         <v>46050</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="28">
+      <c r="A12" s="26">
         <v>46051</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="28">
+      <c r="A13" s="26">
         <v>46052</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="28">
+      <c r="A14" s="26">
         <v>46053</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="28">
+      <c r="A15" s="26">
         <v>46054</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="28">
+      <c r="A16" s="26">
         <v>46055</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="28">
+      <c r="A17" s="26">
         <v>46056</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="28">
+      <c r="A18" s="26">
         <v>46057</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="28">
+      <c r="A19" s="26">
         <v>46058</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="28">
+      <c r="A20" s="26">
         <v>46059</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="28">
+      <c r="A21" s="26">
         <v>46060</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="28">
+      <c r="A22" s="26">
         <v>46061</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="28">
+      <c r="A23" s="26">
         <v>46062</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="28">
+      <c r="A24" s="26">
         <v>46063</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="28">
+      <c r="A25" s="26">
         <v>46064</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
     </row>
     <row r="26">
-      <c r="A26" s="28">
+      <c r="A26" s="26">
         <v>46065</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C26"/>
-      <c r="F26" s="31"/>
+      <c r="F26" s="29"/>
     </row>
     <row r="27">
-      <c r="A27" s="28">
+      <c r="A27" s="26">
         <v>46066</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28">
+      <c r="A28" s="26">
         <v>46067</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28">
+      <c r="A29" s="26">
         <v>46068</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28">
+      <c r="A30" s="26">
         <v>46069</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="28">
+      <c r="A31" s="26">
         <v>46070</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="28">
+      <c r="A32" s="26">
         <v>46071</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="28">
+      <c r="A33" s="26">
         <v>46072</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="28">
+      <c r="A34" s="26">
         <v>46073</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="28">
+      <c r="A35" s="26">
         <v>46074</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="28">
+      <c r="A36" s="26">
         <v>46075</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="28">
+      <c r="A37" s="26">
         <v>46076</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C37" s="32">
+      <c r="C37" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28">
+      <c r="A38" s="26">
         <v>46077</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="28">
+      <c r="A39" s="26">
         <v>46078</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="28">
+      <c r="A40" s="26">
         <v>46079</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="28">
+      <c r="A41" s="26">
         <v>46080</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28">
+      <c r="A42" s="26">
         <v>46081</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28">
+      <c r="A43" s="26">
         <v>46082</v>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28">
+      <c r="A44" s="26">
         <v>46083</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28">
+      <c r="A45" s="26">
         <v>46084</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="28">
+      <c r="A46" s="26">
         <v>46085</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="28">
+      <c r="A47" s="26">
         <v>46086</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="28">
+      <c r="A48" s="26">
         <v>46087</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="28">
+      <c r="A49" s="26">
         <v>46088</v>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="28">
+      <c r="A50" s="26">
         <v>46089</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="28">
+      <c r="A51" s="26">
         <v>46090</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="28">
+      <c r="A52" s="26">
         <v>46091</v>
       </c>
-      <c r="B52" s="29">
+      <c r="B52" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="28">
+      <c r="A53" s="26">
         <v>46092</v>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="28">
+      <c r="A54" s="26">
         <v>46093</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="28">
+      <c r="A55" s="26">
         <v>46094</v>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C55" s="32">
+      <c r="C55" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="28">
+      <c r="A56" s="26">
         <v>46095</v>
       </c>
-      <c r="B56" s="29">
+      <c r="B56" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="28">
+      <c r="A57" s="26">
         <v>46096</v>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="28">
+      <c r="A58" s="26">
         <v>46097</v>
       </c>
-      <c r="B58" s="29">
+      <c r="B58" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C58" s="32">
+      <c r="C58" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="28">
+      <c r="A59" s="26">
         <v>46098</v>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="28">
+      <c r="A60" s="26">
         <v>46099</v>
       </c>
-      <c r="B60" s="29">
+      <c r="B60" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="28">
+      <c r="A61" s="26">
         <v>46100</v>
       </c>
-      <c r="B61" s="29">
+      <c r="B61" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="C61" s="32">
+      <c r="C61" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="28">
+      <c r="A62" s="26">
         <v>46101</v>
       </c>
-      <c r="B62" s="29">
+      <c r="B62" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="28">
+      <c r="A63" s="26">
         <v>46102</v>
       </c>
-      <c r="B63" s="29">
+      <c r="B63" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="28">
+      <c r="A64" s="26">
         <v>46103</v>
       </c>
-      <c r="B64" s="29">
+      <c r="B64" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C64" s="32">
+      <c r="C64" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="28">
+      <c r="A65" s="26">
         <v>46104</v>
       </c>
-      <c r="B65" s="29">
+      <c r="B65" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="28">
+      <c r="A66" s="26">
         <v>46105</v>
       </c>
-      <c r="B66" s="29">
+      <c r="B66" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="28">
+      <c r="A67" s="26">
         <v>46106</v>
       </c>
-      <c r="B67" s="29">
+      <c r="B67" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C67" s="32">
+      <c r="C67" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="28">
+      <c r="A68" s="26">
         <v>46107</v>
       </c>
-      <c r="B68" s="29">
+      <c r="B68" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="28">
+      <c r="A69" s="26">
         <v>46108</v>
       </c>
-      <c r="B69" s="29">
+      <c r="B69" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="28">
+      <c r="A70" s="26">
         <v>46109</v>
       </c>
-      <c r="B70" s="29">
+      <c r="B70" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C70" s="32">
+      <c r="C70" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="28">
+      <c r="A71" s="26">
         <v>46110</v>
       </c>
-      <c r="B71" s="29">
+      <c r="B71" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C71" s="32">
+      <c r="C71" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="28">
+      <c r="A72" s="26">
         <v>46111</v>
       </c>
-      <c r="B72" s="29">
+      <c r="B72" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="28">
+      <c r="A73" s="26">
         <v>46112</v>
       </c>
-      <c r="B73" s="29">
+      <c r="B73" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C73" s="32">
+      <c r="C73" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="28">
+      <c r="A74" s="26">
         <v>46113</v>
       </c>
-      <c r="B74" s="29">
+      <c r="B74" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C74" s="32">
+      <c r="C74" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="28">
+      <c r="A75" s="26">
         <v>46114</v>
       </c>
-      <c r="B75" s="29">
+      <c r="B75" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C75" s="32">
+      <c r="C75" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="28">
+      <c r="A76" s="26">
         <v>46115</v>
       </c>
-      <c r="B76" s="29">
+      <c r="B76" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C76" s="32">
+      <c r="C76" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="28">
+      <c r="A77" s="26">
         <v>46116</v>
       </c>
-      <c r="B77" s="29">
+      <c r="B77" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C77" s="32">
+      <c r="C77" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="28">
+      <c r="A78" s="26">
         <v>46117</v>
       </c>
-      <c r="B78" s="29">
+      <c r="B78" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C78" s="32">
+      <c r="C78" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="28">
+      <c r="A79" s="26">
         <v>46118</v>
       </c>
-      <c r="B79" s="29">
+      <c r="B79" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C79" s="32">
+      <c r="C79" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="28">
+      <c r="A80" s="26">
         <v>46119</v>
       </c>
-      <c r="B80" s="29">
+      <c r="B80" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C80" s="32">
+      <c r="C80" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="28">
+      <c r="A81" s="26">
         <v>46120</v>
       </c>
-      <c r="B81" s="29">
+      <c r="B81" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C81" s="32">
+      <c r="C81" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="28">
+      <c r="A82" s="26">
         <v>46121</v>
       </c>
-      <c r="B82" s="29">
+      <c r="B82" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C82" s="32">
+      <c r="C82" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="28">
+      <c r="A83" s="26">
         <v>46122</v>
       </c>
-      <c r="B83" s="29">
+      <c r="B83" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C83" s="32">
+      <c r="C83" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="28">
+      <c r="A84" s="26">
         <v>46123</v>
       </c>
-      <c r="B84" s="29">
+      <c r="B84" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C84" s="32">
+      <c r="C84" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="28">
+      <c r="A85" s="26">
         <v>46124</v>
       </c>
-      <c r="B85" s="29">
+      <c r="B85" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C85" s="32">
+      <c r="C85" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="28">
+      <c r="A86" s="26">
         <v>46125</v>
       </c>
-      <c r="B86" s="29">
+      <c r="B86" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C86" s="32">
+      <c r="C86" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="28">
+      <c r="A87" s="26">
         <v>46126</v>
       </c>
-      <c r="B87" s="29">
+      <c r="B87" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C87" s="32">
+      <c r="C87" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="28">
+      <c r="A88" s="26">
         <v>46127</v>
       </c>
-      <c r="B88" s="29">
+      <c r="B88" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C88" s="32">
+      <c r="C88" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="28">
+      <c r="A89" s="26">
         <v>46128</v>
       </c>
-      <c r="B89" s="29">
+      <c r="B89" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C89" s="32">
+      <c r="C89" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="28">
+      <c r="A90" s="26">
         <v>46129</v>
       </c>
-      <c r="B90" s="29">
+      <c r="B90" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C90" s="32">
+      <c r="C90" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="28">
+      <c r="A91" s="26">
         <v>46130</v>
       </c>
-      <c r="B91" s="29">
+      <c r="B91" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C91" s="32">
+      <c r="C91" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="28">
+      <c r="A92" s="26">
         <v>46131</v>
       </c>
-      <c r="B92" s="29">
+      <c r="B92" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C92" s="32">
+      <c r="C92" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="28">
+      <c r="A93" s="26">
         <v>46132</v>
       </c>
-      <c r="B93" s="29">
+      <c r="B93" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C93" s="32">
+      <c r="C93" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="28">
+      <c r="A94" s="26">
         <v>46133</v>
       </c>
-      <c r="B94" s="29">
+      <c r="B94" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C94" s="32">
+      <c r="C94" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="28">
+      <c r="A95" s="26">
         <v>46134</v>
       </c>
-      <c r="B95" s="29">
+      <c r="B95" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
-      <c r="C95" s="32">
+      <c r="C95" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="28">
+      <c r="A96" s="26">
         <v>46135</v>
       </c>
-      <c r="B96" s="29">
+      <c r="B96" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
-      <c r="C96" s="32">
+      <c r="C96" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="28">
+      <c r="A97" s="26">
         <v>46136</v>
       </c>
-      <c r="B97" s="29">
+      <c r="B97" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C97" s="32">
+      <c r="C97" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="28">
+      <c r="A98" s="26">
         <v>46137</v>
       </c>
-      <c r="B98" s="29">
+      <c r="B98" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C98" s="32">
+      <c r="C98" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="28">
+      <c r="A99" s="26">
         <v>46138</v>
       </c>
-      <c r="B99" s="29">
+      <c r="B99" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C99" s="32">
+      <c r="C99" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="28">
+      <c r="A100" s="26">
         <v>46139</v>
       </c>
-      <c r="B100" s="29">
+      <c r="B100" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C100" s="32">
+      <c r="C100" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="28">
+      <c r="A101" s="26">
         <v>46140</v>
       </c>
-      <c r="B101" s="29">
+      <c r="B101" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
-      <c r="C101" s="32">
+      <c r="C101" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="28">
+      <c r="A102" s="26">
         <v>46141</v>
       </c>
-      <c r="B102" s="29">
+      <c r="B102" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C102" s="32">
+      <c r="C102" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="28">
+      <c r="A103" s="26">
         <v>46142</v>
       </c>
-      <c r="B103" s="29">
+      <c r="B103" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C103" s="32">
+      <c r="C103" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="28">
+      <c r="A104" s="26">
         <v>46143</v>
       </c>
-      <c r="B104" s="29">
+      <c r="B104" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C104" s="32">
+      <c r="C104" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="28">
+      <c r="A105" s="26">
         <v>46144</v>
       </c>
-      <c r="B105" s="29">
+      <c r="B105" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C105" s="32">
+      <c r="C105" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="28">
+      <c r="A106" s="26">
         <v>46145</v>
       </c>
-      <c r="B106" s="29">
+      <c r="B106" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C106" s="32">
+      <c r="C106" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="28">
+      <c r="A107" s="26">
         <v>46146</v>
       </c>
-      <c r="B107" s="29">
+      <c r="B107" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C107" s="32">
+      <c r="C107" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="28">
+      <c r="A108" s="26">
         <v>46147</v>
       </c>
-      <c r="B108" s="29">
+      <c r="B108" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C108" s="32">
+      <c r="C108" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="28">
+      <c r="A109" s="26">
         <v>46148</v>
       </c>
-      <c r="B109" s="29">
+      <c r="B109" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C109" s="32">
+      <c r="C109" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="28">
+      <c r="A110" s="26">
         <v>46149</v>
       </c>
-      <c r="B110" s="29">
+      <c r="B110" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C110" s="32">
+      <c r="C110" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="28">
+      <c r="A111" s="26">
         <v>46150</v>
       </c>
-      <c r="B111" s="29">
+      <c r="B111" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C111" s="32">
+      <c r="C111" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="28">
+      <c r="A112" s="26">
         <v>46151</v>
       </c>
-      <c r="B112" s="29">
+      <c r="B112" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C112" s="32">
+      <c r="C112" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="28">
+      <c r="A113" s="26">
         <v>46152</v>
       </c>
-      <c r="B113" s="29">
+      <c r="B113" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C113" s="32">
+      <c r="C113" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="28">
+      <c r="A114" s="26">
         <v>46153</v>
       </c>
-      <c r="B114" s="29">
+      <c r="B114" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C114" s="32">
+      <c r="C114" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="28">
+      <c r="A115" s="26">
         <v>46154</v>
       </c>
-      <c r="B115" s="29">
+      <c r="B115" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C115" s="32">
+      <c r="C115" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="28">
+      <c r="A116" s="26">
         <v>46155</v>
       </c>
-      <c r="B116" s="29">
+      <c r="B116" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A116,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C116" s="32"/>
+      <c r="C116" s="30"/>
     </row>
     <row r="117">
-      <c r="A117" s="28">
+      <c r="A117" s="26">
         <v>46156</v>
       </c>
-      <c r="B117" s="29">
+      <c r="B117" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A117,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C117" s="32"/>
+      <c r="C117" s="30"/>
     </row>
     <row r="118">
-      <c r="A118" s="28">
+      <c r="A118" s="26">
         <v>46157</v>
       </c>
-      <c r="B118" s="29">
+      <c r="B118" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A118,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C118" s="32"/>
+      <c r="C118" s="30"/>
     </row>
     <row r="119">
-      <c r="A119" s="28">
+      <c r="A119" s="26">
         <v>46158</v>
       </c>
-      <c r="B119" s="29">
+      <c r="B119" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A119,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C119" s="32"/>
+      <c r="C119" s="30"/>
     </row>
     <row r="120">
-      <c r="A120" s="28">
+      <c r="A120" s="26">
         <v>46159</v>
       </c>
-      <c r="B120" s="29">
+      <c r="B120" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A120,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C120" s="32"/>
+      <c r="C120" s="30"/>
     </row>
     <row r="121">
-      <c r="A121" s="28">
+      <c r="A121" s="26">
         <v>46160</v>
       </c>
-      <c r="B121" s="29">
+      <c r="B121" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A121,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C121" s="32"/>
+      <c r="C121" s="30"/>
     </row>
     <row r="122">
-      <c r="A122" s="28">
+      <c r="A122" s="26">
         <v>46161</v>
       </c>
-      <c r="B122" s="29">
+      <c r="B122" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A122,Journal[Temps])</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="C122" s="32"/>
+      <c r="C122" s="30"/>
     </row>
     <row r="123">
-      <c r="A123" s="28">
+      <c r="A123" s="26">
         <v>46162</v>
       </c>
-      <c r="B123" s="29">
+      <c r="B123" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A123,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C123" s="32"/>
+      <c r="C123" s="30"/>
     </row>
     <row r="124">
-      <c r="A124" s="28">
+      <c r="A124" s="26">
         <v>46163</v>
       </c>
-      <c r="B124" s="29">
+      <c r="B124" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A124,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C124" s="32"/>
+      <c r="C124" s="30"/>
     </row>
     <row r="125">
-      <c r="A125" s="28">
+      <c r="A125" s="26">
         <v>46164</v>
       </c>
-      <c r="B125" s="29">
+      <c r="B125" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A125,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C125" s="32"/>
+      <c r="C125" s="30"/>
     </row>
     <row r="126">
-      <c r="A126" s="28">
+      <c r="A126" s="26">
         <v>46165</v>
       </c>
-      <c r="B126" s="29">
+      <c r="B126" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A126,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C126" s="32"/>
+      <c r="C126" s="30"/>
     </row>
     <row r="127">
-      <c r="A127" s="28">
+      <c r="A127" s="26">
         <v>46166</v>
       </c>
-      <c r="B127" s="29">
+      <c r="B127" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A127,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C127" s="32"/>
+      <c r="C127" s="30"/>
     </row>
     <row r="128">
-      <c r="A128" s="28">
+      <c r="A128" s="26">
         <v>46167</v>
       </c>
-      <c r="B128" s="29">
+      <c r="B128" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A128,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C128" s="32"/>
+      <c r="C128" s="30"/>
     </row>
     <row r="129">
-      <c r="A129" s="28">
+      <c r="A129" s="26">
         <v>46168</v>
       </c>
-      <c r="B129" s="29">
+      <c r="B129" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A129,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C129" s="32"/>
+      <c r="C129" s="30"/>
     </row>
     <row r="130">
-      <c r="A130" s="28">
+      <c r="A130" s="26">
         <v>46169</v>
       </c>
-      <c r="B130" s="29">
+      <c r="B130" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A130,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C130" s="32"/>
+      <c r="C130" s="30"/>
     </row>
     <row r="131">
-      <c r="A131" s="28">
+      <c r="A131" s="26">
         <v>46170</v>
       </c>
-      <c r="B131" s="29">
+      <c r="B131" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A131,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C131" s="32"/>
+      <c r="C131" s="30"/>
     </row>
     <row r="132">
-      <c r="A132" s="28">
+      <c r="A132" s="26">
         <v>46171</v>
       </c>
-      <c r="B132" s="29">
+      <c r="B132" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A132,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C132" s="32"/>
+      <c r="C132" s="30"/>
     </row>
     <row r="133">
-      <c r="A133" s="28">
+      <c r="A133" s="26">
         <v>46172</v>
       </c>
-      <c r="B133" s="29">
+      <c r="B133" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A133,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C133" s="32"/>
+      <c r="C133" s="30"/>
     </row>
     <row r="134">
-      <c r="A134" s="28">
+      <c r="A134" s="26">
         <v>46173</v>
       </c>
-      <c r="B134" s="29">
+      <c r="B134" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A134,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C134" s="32"/>
+      <c r="C134" s="30"/>
     </row>
     <row r="135">
-      <c r="A135" s="28">
+      <c r="A135" s="26">
         <v>46174</v>
       </c>
-      <c r="B135" s="29">
+      <c r="B135" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A135,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C135" s="32"/>
+      <c r="C135" s="30"/>
     </row>
     <row r="136">
-      <c r="A136" s="28">
+      <c r="A136" s="26">
         <v>46175</v>
       </c>
-      <c r="B136" s="29">
+      <c r="B136" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A136,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C136" s="32"/>
+      <c r="C136" s="30"/>
     </row>
     <row r="137">
-      <c r="A137" s="28">
+      <c r="A137" s="26">
         <v>46176</v>
       </c>
-      <c r="B137" s="29">
+      <c r="B137" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A137,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C137" s="32"/>
+      <c r="C137" s="30"/>
     </row>
     <row r="138">
-      <c r="A138" s="28">
+      <c r="A138" s="26">
         <v>46177</v>
       </c>
-      <c r="B138" s="29">
+      <c r="B138" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A138,Journal[Temps])</f>
         <v>0.2986111111111111</v>
       </c>
-      <c r="C138" s="32"/>
+      <c r="C138" s="30"/>
     </row>
     <row r="139">
-      <c r="A139" s="28">
+      <c r="A139" s="26">
         <v>46178</v>
       </c>
-      <c r="B139" s="29">
+      <c r="B139" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A139,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C139" s="32"/>
+      <c r="C139" s="30"/>
     </row>
     <row r="140">
-      <c r="A140" s="28">
+      <c r="A140" s="26">
         <v>46179</v>
       </c>
-      <c r="B140" s="29">
+      <c r="B140" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A140,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C140" s="32"/>
+      <c r="C140" s="30"/>
     </row>
     <row r="141">
-      <c r="A141" s="28">
+      <c r="A141" s="26">
         <v>46180</v>
       </c>
-      <c r="B141" s="29">
+      <c r="B141" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A141,Journal[Temps])</f>
-        <v>0</v>
-      </c>
-      <c r="C141" s="32"/>
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="C141" s="30"/>
     </row>
     <row r="142">
-      <c r="A142" s="28">
+      <c r="A142" s="26">
         <v>46181</v>
       </c>
-      <c r="B142" s="29">
+      <c r="B142" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A142,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C142" s="32"/>
+      <c r="C142" s="30"/>
     </row>
     <row r="143">
-      <c r="A143" s="28">
+      <c r="A143" s="26">
         <v>46182</v>
       </c>
-      <c r="B143" s="29">
+      <c r="B143" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A143,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C143" s="32"/>
+      <c r="C143" s="30"/>
     </row>
     <row r="144">
-      <c r="A144" s="28">
+      <c r="A144" s="26">
         <v>46183</v>
       </c>
-      <c r="B144" s="29">
+      <c r="B144" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A144,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C144" s="32"/>
+      <c r="C144" s="30"/>
     </row>
     <row r="145">
-      <c r="A145" s="28">
+      <c r="A145" s="26">
         <v>46184</v>
       </c>
-      <c r="B145" s="29">
+      <c r="B145" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A145,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C145" s="32"/>
+      <c r="C145" s="30"/>
     </row>
     <row r="146">
-      <c r="A146" s="28">
+      <c r="A146" s="26">
         <v>46185</v>
       </c>
-      <c r="B146" s="29">
+      <c r="B146" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A146,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C146" s="32"/>
+      <c r="C146" s="30"/>
     </row>
     <row r="147">
-      <c r="A147" s="28">
+      <c r="A147" s="26">
         <v>46186</v>
       </c>
-      <c r="B147" s="29">
+      <c r="B147" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A147,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C147" s="32"/>
+      <c r="C147" s="30"/>
     </row>
     <row r="148">
-      <c r="A148" s="28">
+      <c r="A148" s="26">
         <v>46187</v>
       </c>
-      <c r="B148" s="29">
+      <c r="B148" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A148,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C148" s="32"/>
+      <c r="C148" s="30"/>
     </row>
     <row r="149">
-      <c r="A149" s="28">
+      <c r="A149" s="26">
         <v>46188</v>
       </c>
-      <c r="B149" s="29">
+      <c r="B149" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A149,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C149" s="32"/>
+      <c r="C149" s="30"/>
     </row>
     <row r="150">
-      <c r="A150" s="28">
+      <c r="A150" s="26">
         <v>46189</v>
       </c>
-      <c r="B150" s="29">
+      <c r="B150" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A150,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C150" s="32"/>
+      <c r="C150" s="30"/>
     </row>
     <row r="151">
-      <c r="A151" s="28">
+      <c r="A151" s="26">
         <v>46190</v>
       </c>
-      <c r="B151" s="29">
+      <c r="B151" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A151,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C151" s="32"/>
+      <c r="C151" s="30"/>
     </row>
     <row r="152">
-      <c r="A152" s="28">
+      <c r="A152" s="26">
         <v>46191</v>
       </c>
-      <c r="B152" s="29">
+      <c r="B152" s="27">
         <f>SUMIF(Journal[date],SommeParJours!A152,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C152" s="32"/>
+      <c r="C152" s="30"/>
     </row>
     <row r="153">
-      <c r="A153" s="28"/>
-      <c r="B153" s="33"/>
-      <c r="C153" s="32"/>
+      <c r="A153" s="26"/>
+      <c r="B153" s="31"/>
+      <c r="C153" s="30"/>
     </row>
     <row r="154">
-      <c r="A154" s="28"/>
-      <c r="B154" s="33"/>
-      <c r="C154" s="32"/>
+      <c r="A154" s="26"/>
+      <c r="B154" s="31"/>
+      <c r="C154" s="30"/>
     </row>
     <row r="155">
-      <c r="A155" s="28"/>
-      <c r="B155" s="33"/>
-      <c r="C155" s="32"/>
+      <c r="A155" s="26"/>
+      <c r="B155" s="31"/>
+      <c r="C155" s="30"/>
     </row>
     <row r="156">
-      <c r="A156" s="28"/>
-      <c r="B156" s="33"/>
-      <c r="C156" s="32"/>
+      <c r="A156" s="26"/>
+      <c r="B156" s="31"/>
+      <c r="C156" s="30"/>
     </row>
     <row r="157">
-      <c r="A157" s="28"/>
-      <c r="B157" s="33"/>
-      <c r="C157" s="32"/>
+      <c r="A157" s="26"/>
+      <c r="B157" s="31"/>
+      <c r="C157" s="30"/>
     </row>
     <row r="158">
-      <c r="A158" s="28"/>
-      <c r="B158" s="33"/>
-      <c r="C158" s="32"/>
+      <c r="A158" s="26"/>
+      <c r="B158" s="31"/>
+      <c r="C158" s="30"/>
     </row>
     <row r="159">
-      <c r="A159" s="28"/>
-      <c r="B159" s="33"/>
-      <c r="C159" s="32"/>
+      <c r="A159" s="26"/>
+      <c r="B159" s="31"/>
+      <c r="C159" s="30"/>
     </row>
     <row r="160">
-      <c r="A160" s="28"/>
-      <c r="B160" s="33"/>
+      <c r="A160" s="26"/>
+      <c r="B160" s="31"/>
     </row>
     <row r="161">
-      <c r="A161" s="28"/>
-      <c r="B161" s="33"/>
+      <c r="A161" s="26"/>
+      <c r="B161" s="31"/>
     </row>
     <row r="162">
-      <c r="A162" s="28"/>
-      <c r="B162" s="33"/>
+      <c r="A162" s="26"/>
+      <c r="B162" s="31"/>
     </row>
     <row r="163">
-      <c r="A163" s="28"/>
-      <c r="B163" s="33"/>
+      <c r="A163" s="26"/>
+      <c r="B163" s="31"/>
     </row>
     <row r="164">
-      <c r="A164" s="28"/>
-      <c r="B164" s="33"/>
+      <c r="A164" s="26"/>
+      <c r="B164" s="31"/>
     </row>
     <row r="165">
-      <c r="A165" s="28"/>
-      <c r="B165" s="33"/>
+      <c r="A165" s="26"/>
+      <c r="B165" s="31"/>
     </row>
     <row r="166">
-      <c r="A166" s="28"/>
-      <c r="B166" s="33"/>
+      <c r="A166" s="26"/>
+      <c r="B166" s="31"/>
     </row>
     <row r="167">
-      <c r="A167" s="28"/>
-      <c r="B167" s="33"/>
+      <c r="A167" s="26"/>
+      <c r="B167" s="31"/>
     </row>
     <row r="168">
-      <c r="A168" s="28"/>
-      <c r="B168" s="33"/>
+      <c r="A168" s="26"/>
+      <c r="B168" s="31"/>
     </row>
     <row r="169">
-      <c r="A169" s="28"/>
-      <c r="B169" s="33"/>
+      <c r="A169" s="26"/>
+      <c r="B169" s="31"/>
     </row>
     <row r="170">
-      <c r="A170" s="28"/>
-      <c r="B170" s="33"/>
+      <c r="A170" s="26"/>
+      <c r="B170" s="31"/>
     </row>
     <row r="171">
-      <c r="A171" s="28"/>
-      <c r="B171" s="33"/>
+      <c r="A171" s="26"/>
+      <c r="B171" s="31"/>
     </row>
     <row r="172">
-      <c r="A172" s="28"/>
-      <c r="B172" s="33"/>
+      <c r="A172" s="26"/>
+      <c r="B172" s="31"/>
     </row>
     <row r="173">
-      <c r="A173" s="28"/>
-      <c r="B173" s="33"/>
+      <c r="A173" s="26"/>
+      <c r="B173" s="31"/>
     </row>
     <row r="174">
-      <c r="A174" s="28"/>
-      <c r="B174" s="33"/>
+      <c r="A174" s="26"/>
+      <c r="B174" s="31"/>
     </row>
     <row r="175">
-      <c r="A175" s="28"/>
-      <c r="B175" s="33"/>
+      <c r="A175" s="26"/>
+      <c r="B175" s="31"/>
     </row>
     <row r="176">
-      <c r="A176" s="28"/>
-      <c r="B176" s="33"/>
+      <c r="A176" s="26"/>
+      <c r="B176" s="31"/>
     </row>
     <row r="177">
-      <c r="A177" s="28"/>
-      <c r="B177" s="33"/>
+      <c r="A177" s="26"/>
+      <c r="B177" s="31"/>
     </row>
     <row r="178">
-      <c r="A178" s="28"/>
-      <c r="B178" s="33"/>
+      <c r="A178" s="26"/>
+      <c r="B178" s="31"/>
     </row>
     <row r="179">
-      <c r="A179" s="28"/>
-      <c r="B179" s="33"/>
+      <c r="A179" s="26"/>
+      <c r="B179" s="31"/>
     </row>
     <row r="180">
-      <c r="A180" s="28"/>
-      <c r="B180" s="33"/>
+      <c r="A180" s="26"/>
+      <c r="B180" s="31"/>
     </row>
     <row r="181">
-      <c r="A181" s="28"/>
-      <c r="B181" s="33"/>
+      <c r="A181" s="26"/>
+      <c r="B181" s="31"/>
     </row>
     <row r="182">
-      <c r="A182" s="28"/>
-      <c r="B182" s="33"/>
+      <c r="A182" s="26"/>
+      <c r="B182" s="31"/>
     </row>
     <row r="183">
-      <c r="A183" s="28"/>
-      <c r="B183" s="33"/>
+      <c r="A183" s="26"/>
+      <c r="B183" s="31"/>
     </row>
     <row r="184">
-      <c r="A184" s="28"/>
-      <c r="B184" s="33"/>
+      <c r="A184" s="26"/>
+      <c r="B184" s="31"/>
     </row>
     <row r="185">
-      <c r="A185" s="28"/>
-      <c r="B185" s="33"/>
+      <c r="A185" s="26"/>
+      <c r="B185" s="31"/>
     </row>
     <row r="186">
-      <c r="A186" s="28"/>
-      <c r="B186" s="33"/>
+      <c r="A186" s="26"/>
+      <c r="B186" s="31"/>
     </row>
     <row r="187">
-      <c r="A187" s="28"/>
-      <c r="B187" s="33"/>
+      <c r="A187" s="26"/>
+      <c r="B187" s="31"/>
     </row>
     <row r="188">
-      <c r="A188" s="33"/>
-      <c r="B188" s="33"/>
+      <c r="A188" s="31"/>
+      <c r="B188" s="31"/>
     </row>
     <row r="189">
-      <c r="A189" s="33"/>
-      <c r="B189" s="33"/>
+      <c r="A189" s="31"/>
+      <c r="B189" s="31"/>
     </row>
     <row r="190">
-      <c r="A190" s="33"/>
-      <c r="B190" s="33"/>
+      <c r="A190" s="31"/>
+      <c r="B190" s="31"/>
     </row>
     <row r="191">
-      <c r="A191" s="33"/>
-      <c r="B191" s="33"/>
+      <c r="A191" s="31"/>
+      <c r="B191" s="31"/>
     </row>
     <row r="192">
-      <c r="A192" s="33"/>
-      <c r="B192" s="33"/>
+      <c r="A192" s="31"/>
+      <c r="B192" s="31"/>
     </row>
     <row r="193">
-      <c r="A193" s="33"/>
-      <c r="B193" s="33"/>
+      <c r="A193" s="31"/>
+      <c r="B193" s="31"/>
     </row>
     <row r="194">
-      <c r="A194" s="33"/>
-      <c r="B194" s="33"/>
+      <c r="A194" s="31"/>
+      <c r="B194" s="31"/>
     </row>
     <row r="195">
-      <c r="A195" s="33"/>
-      <c r="B195" s="33"/>
+      <c r="A195" s="31"/>
+      <c r="B195" s="31"/>
     </row>
     <row r="196">
-      <c r="A196" s="33"/>
-      <c r="B196" s="33"/>
+      <c r="A196" s="31"/>
+      <c r="B196" s="31"/>
     </row>
     <row r="197">
-      <c r="A197" s="33"/>
-      <c r="B197" s="33"/>
+      <c r="A197" s="31"/>
+      <c r="B197" s="31"/>
     </row>
     <row r="198">
-      <c r="A198" s="33"/>
-      <c r="B198" s="33"/>
+      <c r="A198" s="31"/>
+      <c r="B198" s="31"/>
     </row>
     <row r="199">
-      <c r="A199" s="33"/>
-      <c r="B199" s="33"/>
+      <c r="A199" s="31"/>
+      <c r="B199" s="31"/>
     </row>
     <row r="200">
-      <c r="A200" s="33"/>
-      <c r="B200" s="33"/>
+      <c r="A200" s="31"/>
+      <c r="B200" s="31"/>
     </row>
     <row r="201">
-      <c r="A201" s="33"/>
-      <c r="B201" s="33"/>
+      <c r="A201" s="31"/>
+      <c r="B201" s="31"/>
     </row>
     <row r="202">
-      <c r="A202" s="33"/>
-      <c r="B202" s="33"/>
+      <c r="A202" s="31"/>
+      <c r="B202" s="31"/>
     </row>
     <row r="203">
-      <c r="A203" s="33"/>
-      <c r="B203" s="33"/>
+      <c r="A203" s="31"/>
+      <c r="B203" s="31"/>
     </row>
     <row r="204">
-      <c r="A204" s="33"/>
-      <c r="B204" s="33"/>
+      <c r="A204" s="31"/>
+      <c r="B204" s="31"/>
     </row>
     <row r="205">
-      <c r="A205" s="33"/>
-      <c r="B205" s="33"/>
+      <c r="A205" s="31"/>
+      <c r="B205" s="31"/>
     </row>
     <row r="206">
-      <c r="A206" s="33"/>
-      <c r="B206" s="33"/>
+      <c r="A206" s="31"/>
+      <c r="B206" s="31"/>
     </row>
     <row r="207">
-      <c r="A207" s="33"/>
-      <c r="B207" s="33"/>
+      <c r="A207" s="31"/>
+      <c r="B207" s="31"/>
     </row>
     <row r="208">
-      <c r="A208" s="33"/>
-      <c r="B208" s="33"/>
+      <c r="A208" s="31"/>
+      <c r="B208" s="31"/>
     </row>
     <row r="209">
-      <c r="A209" s="33"/>
-      <c r="B209" s="33"/>
+      <c r="A209" s="31"/>
+      <c r="B209" s="31"/>
     </row>
     <row r="210">
-      <c r="A210" s="33"/>
-      <c r="B210" s="33"/>
+      <c r="A210" s="31"/>
+      <c r="B210" s="31"/>
     </row>
     <row r="211">
-      <c r="A211" s="33"/>
-      <c r="B211" s="33"/>
+      <c r="A211" s="31"/>
+      <c r="B211" s="31"/>
     </row>
     <row r="212">
-      <c r="A212" s="33"/>
-      <c r="B212" s="33"/>
+      <c r="A212" s="31"/>
+      <c r="B212" s="31"/>
     </row>
     <row r="213">
-      <c r="A213" s="33"/>
-      <c r="B213" s="33"/>
+      <c r="A213" s="31"/>
+      <c r="B213" s="31"/>
     </row>
     <row r="214">
-      <c r="A214" s="33"/>
-      <c r="B214" s="33"/>
+      <c r="A214" s="31"/>
+      <c r="B214" s="31"/>
     </row>
     <row r="215">
-      <c r="A215" s="33"/>
-      <c r="B215" s="33"/>
+      <c r="A215" s="31"/>
+      <c r="B215" s="31"/>
     </row>
     <row r="216">
-      <c r="A216" s="33"/>
-      <c r="B216" s="33"/>
+      <c r="A216" s="31"/>
+      <c r="B216" s="31"/>
     </row>
     <row r="217">
-      <c r="A217" s="33"/>
-      <c r="B217" s="33"/>
+      <c r="A217" s="31"/>
+      <c r="B217" s="31"/>
     </row>
     <row r="218">
-      <c r="A218" s="33"/>
-      <c r="B218" s="33"/>
+      <c r="A218" s="31"/>
+      <c r="B218" s="31"/>
     </row>
     <row r="219">
-      <c r="A219" s="33"/>
-      <c r="B219" s="33"/>
+      <c r="A219" s="31"/>
+      <c r="B219" s="31"/>
     </row>
     <row r="220">
-      <c r="A220" s="33"/>
-      <c r="B220" s="33"/>
+      <c r="A220" s="31"/>
+      <c r="B220" s="31"/>
     </row>
     <row r="221">
-      <c r="A221" s="33"/>
-      <c r="B221" s="33"/>
+      <c r="A221" s="31"/>
+      <c r="B221" s="31"/>
     </row>
     <row r="222">
-      <c r="A222" s="33"/>
-      <c r="B222" s="33"/>
+      <c r="A222" s="31"/>
+      <c r="B222" s="31"/>
     </row>
     <row r="223">
-      <c r="A223" s="33"/>
-      <c r="B223" s="33"/>
+      <c r="A223" s="31"/>
+      <c r="B223" s="31"/>
     </row>
     <row r="224">
-      <c r="A224" s="33"/>
-      <c r="B224" s="33"/>
+      <c r="A224" s="31"/>
+      <c r="B224" s="31"/>
     </row>
     <row r="225">
-      <c r="A225" s="33"/>
-      <c r="B225" s="33"/>
+      <c r="A225" s="31"/>
+      <c r="B225" s="31"/>
     </row>
     <row r="226">
-      <c r="A226" s="33"/>
-      <c r="B226" s="33"/>
+      <c r="A226" s="31"/>
+      <c r="B226" s="31"/>
     </row>
     <row r="227">
-      <c r="A227" s="33"/>
-      <c r="B227" s="33"/>
+      <c r="A227" s="31"/>
+      <c r="B227" s="31"/>
     </row>
     <row r="228">
-      <c r="A228" s="33"/>
-      <c r="B228" s="33"/>
+      <c r="A228" s="31"/>
+      <c r="B228" s="31"/>
     </row>
     <row r="229">
-      <c r="A229" s="33"/>
-      <c r="B229" s="33"/>
+      <c r="A229" s="31"/>
+      <c r="B229" s="31"/>
     </row>
     <row r="230">
-      <c r="A230" s="33"/>
-      <c r="B230" s="33"/>
+      <c r="A230" s="31"/>
+      <c r="B230" s="31"/>
     </row>
     <row r="231">
-      <c r="A231" s="33"/>
-      <c r="B231" s="33"/>
+      <c r="A231" s="31"/>
+      <c r="B231" s="31"/>
     </row>
     <row r="232">
-      <c r="A232" s="33"/>
-      <c r="B232" s="33"/>
+      <c r="A232" s="31"/>
+      <c r="B232" s="31"/>
     </row>
     <row r="233">
-      <c r="A233" s="33"/>
-      <c r="B233" s="33"/>
+      <c r="A233" s="31"/>
+      <c r="B233" s="31"/>
     </row>
     <row r="234">
-      <c r="A234" s="33"/>
-      <c r="B234" s="33"/>
+      <c r="A234" s="31"/>
+      <c r="B234" s="31"/>
     </row>
     <row r="235">
-      <c r="A235" s="33"/>
-      <c r="B235" s="33"/>
+      <c r="A235" s="31"/>
+      <c r="B235" s="31"/>
     </row>
     <row r="236">
-      <c r="A236" s="33"/>
-      <c r="B236" s="33"/>
+      <c r="A236" s="31"/>
+      <c r="B236" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8937,2034 +8942,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="34" width="6"/>
+    <col customWidth="1" min="12" max="12" style="32" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="34" width="6"/>
+    <col customWidth="1" min="23" max="23" style="32" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="34" width="6"/>
+    <col customWidth="1" min="30" max="30" style="32" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="35" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1" s="37" t="s">
+    <row r="1" s="33" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="C1" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="39" t="s">
+      <c r="E1" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="I1" s="38" t="s">
+      <c r="H1" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="L1" s="42" t="s">
+      <c r="K1" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="M1" s="38" t="s">
+      <c r="L1" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="N1" s="40" t="s">
+      <c r="M1" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="N1" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="P1" s="38" t="s">
+      <c r="O1" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="P1" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="R1" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="S1" s="38" t="s">
+      <c r="Q1" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="R1" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="T1" s="38" t="s">
+      <c r="S1" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="U1" s="38" t="s">
+      <c r="T1" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="V1" s="40" t="s">
+      <c r="U1" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="W1" s="43" t="s">
+      <c r="V1" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="X1" s="38" t="s">
+      <c r="W1" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="Y1" s="38" t="s">
+      <c r="X1" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="Z1" s="40" t="s">
+      <c r="Y1" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="AA1" s="44" t="s">
+      <c r="Z1" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="AB1" s="45" t="s">
+      <c r="AA1" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="AC1" s="45" t="s">
+      <c r="AB1" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="AD1" s="42" t="s">
+      <c r="AC1" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="AE1" s="46" t="s">
+      <c r="AD1" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="AF1" s="47" t="s">
+      <c r="AE1" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="AG1" s="48" t="s">
+      <c r="AF1" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="AG1" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="AH1" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="AI1" s="48" t="s">
+      <c r="AH1" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="AJ1" s="48" t="s">
+      <c r="AI1" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="AK1" s="45" t="s">
+      <c r="AJ1" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="AL1" s="49"/>
-      <c r="AM1" s="49"/>
-      <c r="AN1" s="49"/>
-      <c r="AO1" s="49"/>
-      <c r="AP1" s="49"/>
-      <c r="AQ1" s="49"/>
-      <c r="AR1" s="49"/>
-      <c r="AS1" s="49"/>
-      <c r="AT1" s="49"/>
-      <c r="AU1" s="49"/>
+      <c r="AK1" s="43" t="s">
+        <v>137</v>
+      </c>
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="47"/>
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="47"/>
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="47"/>
+      <c r="AT1" s="47"/>
+      <c r="AU1" s="47"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
-      <c r="Z2" s="57"/>
-      <c r="AA2" s="58"/>
-      <c r="AB2" s="52"/>
-      <c r="AC2" s="52"/>
-      <c r="AD2" s="56"/>
-      <c r="AE2" s="57"/>
-      <c r="AF2" s="58"/>
-      <c r="AG2" s="52"/>
-      <c r="AH2" s="52"/>
-      <c r="AI2" s="52"/>
-      <c r="AJ2" s="52"/>
-      <c r="AK2" s="52"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="50"/>
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="50"/>
+      <c r="AK2" s="50"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="57"/>
-      <c r="W3" s="59"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
-      <c r="Z3" s="57"/>
-      <c r="AA3" s="58"/>
-      <c r="AB3" s="52"/>
-      <c r="AC3" s="52"/>
-      <c r="AD3" s="56"/>
-      <c r="AE3" s="57"/>
-      <c r="AF3" s="58"/>
-      <c r="AG3" s="52"/>
-      <c r="AH3" s="52"/>
-      <c r="AI3" s="52"/>
-      <c r="AJ3" s="52"/>
-      <c r="AK3" s="52"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="50"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="55"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="50"/>
+      <c r="Y3" s="50"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="50"/>
+      <c r="AC3" s="50"/>
+      <c r="AD3" s="54"/>
+      <c r="AE3" s="55"/>
+      <c r="AF3" s="56"/>
+      <c r="AG3" s="50"/>
+      <c r="AH3" s="50"/>
+      <c r="AI3" s="50"/>
+      <c r="AJ3" s="50"/>
+      <c r="AK3" s="50"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="50"/>
-      <c r="C4" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="57"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="57"/>
-      <c r="W4" s="59"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
-      <c r="Z4" s="57"/>
-      <c r="AA4" s="58"/>
-      <c r="AB4" s="52"/>
-      <c r="AC4" s="52"/>
-      <c r="AD4" s="56"/>
-      <c r="AE4" s="57"/>
-      <c r="AF4" s="58"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="52"/>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="52"/>
-      <c r="AK4" s="52"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="55"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="50"/>
+      <c r="Q4" s="50"/>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="50"/>
+      <c r="U4" s="50"/>
+      <c r="V4" s="55"/>
+      <c r="W4" s="57"/>
+      <c r="X4" s="50"/>
+      <c r="Y4" s="50"/>
+      <c r="Z4" s="55"/>
+      <c r="AA4" s="56"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="50"/>
+      <c r="AD4" s="54"/>
+      <c r="AE4" s="55"/>
+      <c r="AF4" s="56"/>
+      <c r="AG4" s="50"/>
+      <c r="AH4" s="50"/>
+      <c r="AI4" s="50"/>
+      <c r="AJ4" s="50"/>
+      <c r="AK4" s="50"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="50"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="56"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="52"/>
-      <c r="V5" s="57"/>
-      <c r="W5" s="59"/>
-      <c r="X5" s="52"/>
-      <c r="Y5" s="52"/>
-      <c r="Z5" s="57"/>
-      <c r="AA5" s="58"/>
-      <c r="AB5" s="52"/>
-      <c r="AC5" s="52"/>
-      <c r="AD5" s="56"/>
-      <c r="AE5" s="57"/>
-      <c r="AF5" s="58"/>
-      <c r="AG5" s="52"/>
-      <c r="AH5" s="52"/>
-      <c r="AI5" s="52"/>
-      <c r="AJ5" s="52"/>
-      <c r="AK5" s="52"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="60"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="50"/>
+      <c r="Q5" s="50"/>
+      <c r="R5" s="50"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="50"/>
+      <c r="U5" s="50"/>
+      <c r="V5" s="55"/>
+      <c r="W5" s="57"/>
+      <c r="X5" s="50"/>
+      <c r="Y5" s="50"/>
+      <c r="Z5" s="55"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="50"/>
+      <c r="AC5" s="50"/>
+      <c r="AD5" s="54"/>
+      <c r="AE5" s="55"/>
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="50"/>
+      <c r="AH5" s="50"/>
+      <c r="AI5" s="50"/>
+      <c r="AJ5" s="50"/>
+      <c r="AK5" s="50"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="50"/>
-      <c r="C6" s="51" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="56"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="52"/>
-      <c r="S6" s="52"/>
-      <c r="T6" s="52"/>
-      <c r="U6" s="52"/>
-      <c r="V6" s="57"/>
-      <c r="W6" s="59"/>
-      <c r="X6" s="52"/>
-      <c r="Y6" s="52"/>
-      <c r="Z6" s="57"/>
-      <c r="AA6" s="58"/>
-      <c r="AB6" s="52"/>
-      <c r="AC6" s="52"/>
-      <c r="AD6" s="56"/>
-      <c r="AE6" s="54"/>
-      <c r="AF6" s="55"/>
-      <c r="AG6" s="66"/>
-      <c r="AH6" s="66"/>
-      <c r="AI6" s="66"/>
-      <c r="AJ6" s="66"/>
-      <c r="AK6" s="66"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="50"/>
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
+      <c r="V6" s="55"/>
+      <c r="W6" s="57"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="50"/>
+      <c r="Z6" s="55"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="50"/>
+      <c r="AC6" s="50"/>
+      <c r="AD6" s="54"/>
+      <c r="AE6" s="52"/>
+      <c r="AF6" s="53"/>
+      <c r="AG6" s="64"/>
+      <c r="AH6" s="64"/>
+      <c r="AI6" s="64"/>
+      <c r="AJ6" s="64"/>
+      <c r="AK6" s="64"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="50"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="57"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="52"/>
-      <c r="U7" s="52"/>
-      <c r="V7" s="57"/>
-      <c r="W7" s="59"/>
-      <c r="X7" s="52"/>
-      <c r="Y7" s="52"/>
-      <c r="Z7" s="57"/>
-      <c r="AA7" s="58"/>
-      <c r="AB7" s="52"/>
-      <c r="AC7" s="52"/>
-      <c r="AD7" s="56"/>
-      <c r="AE7" s="57"/>
-      <c r="AF7" s="58"/>
-      <c r="AG7" s="52"/>
-      <c r="AH7" s="52"/>
-      <c r="AI7" s="52"/>
-      <c r="AJ7" s="52"/>
-      <c r="AK7" s="52"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="55"/>
+      <c r="W7" s="57"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="50"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="56"/>
+      <c r="AB7" s="50"/>
+      <c r="AC7" s="50"/>
+      <c r="AD7" s="54"/>
+      <c r="AE7" s="55"/>
+      <c r="AF7" s="56"/>
+      <c r="AG7" s="50"/>
+      <c r="AH7" s="50"/>
+      <c r="AI7" s="50"/>
+      <c r="AJ7" s="50"/>
+      <c r="AK7" s="50"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="50"/>
-      <c r="C8" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="66"/>
-      <c r="E8" s="66"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="66"/>
-      <c r="K8" s="66"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="66"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="66"/>
-      <c r="S8" s="66"/>
-      <c r="T8" s="66"/>
-      <c r="U8" s="66"/>
-      <c r="V8" s="54"/>
-      <c r="W8" s="59"/>
-      <c r="X8" s="66"/>
-      <c r="Y8" s="66"/>
-      <c r="Z8" s="54"/>
-      <c r="AA8" s="55"/>
-      <c r="AB8" s="66"/>
-      <c r="AC8" s="66"/>
-      <c r="AD8" s="56"/>
-      <c r="AE8" s="54"/>
-      <c r="AF8" s="55"/>
-      <c r="AG8" s="66"/>
-      <c r="AH8" s="66"/>
-      <c r="AI8" s="66"/>
-      <c r="AJ8" s="66"/>
-      <c r="AK8" s="66"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="64"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="52"/>
+      <c r="W8" s="57"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="52"/>
+      <c r="AA8" s="53"/>
+      <c r="AB8" s="64"/>
+      <c r="AC8" s="64"/>
+      <c r="AD8" s="54"/>
+      <c r="AE8" s="52"/>
+      <c r="AF8" s="53"/>
+      <c r="AG8" s="64"/>
+      <c r="AH8" s="64"/>
+      <c r="AI8" s="64"/>
+      <c r="AJ8" s="64"/>
+      <c r="AK8" s="64"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="50"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="65"/>
-      <c r="K9" s="52"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="65"/>
-      <c r="N9" s="57"/>
-      <c r="O9" s="64"/>
-      <c r="P9" s="52"/>
-      <c r="Q9" s="65"/>
-      <c r="R9" s="52"/>
-      <c r="S9" s="67"/>
-      <c r="T9" s="52"/>
-      <c r="U9" s="52"/>
-      <c r="V9" s="63"/>
-      <c r="W9" s="59"/>
-      <c r="X9" s="65"/>
-      <c r="Y9" s="52"/>
-      <c r="Z9" s="63"/>
-      <c r="AA9" s="64"/>
-      <c r="AB9" s="52"/>
-      <c r="AC9" s="52"/>
-      <c r="AD9" s="65"/>
-      <c r="AE9" s="57"/>
-      <c r="AF9" s="58"/>
-      <c r="AG9" s="52"/>
-      <c r="AH9" s="52"/>
-      <c r="AI9" s="52"/>
-      <c r="AJ9" s="52"/>
-      <c r="AK9" s="52"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="60"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="50"/>
+      <c r="L9" s="54"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="55"/>
+      <c r="O9" s="62"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="50"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="61"/>
+      <c r="W9" s="57"/>
+      <c r="X9" s="63"/>
+      <c r="Y9" s="50"/>
+      <c r="Z9" s="61"/>
+      <c r="AA9" s="62"/>
+      <c r="AB9" s="50"/>
+      <c r="AC9" s="50"/>
+      <c r="AD9" s="63"/>
+      <c r="AE9" s="55"/>
+      <c r="AF9" s="56"/>
+      <c r="AG9" s="50"/>
+      <c r="AH9" s="50"/>
+      <c r="AI9" s="50"/>
+      <c r="AJ9" s="50"/>
+      <c r="AK9" s="50"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="50"/>
-      <c r="C10" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="52"/>
-      <c r="N10" s="57"/>
-      <c r="O10" s="58"/>
-      <c r="P10" s="52"/>
-      <c r="Q10" s="52"/>
-      <c r="R10" s="52"/>
-      <c r="S10" s="52"/>
-      <c r="T10" s="52"/>
-      <c r="U10" s="52"/>
-      <c r="V10" s="54"/>
-      <c r="W10" s="59"/>
-      <c r="X10" s="66"/>
-      <c r="Y10" s="66"/>
-      <c r="Z10" s="54"/>
-      <c r="AA10" s="58"/>
-      <c r="AB10" s="52"/>
-      <c r="AC10" s="52"/>
-      <c r="AD10" s="56"/>
-      <c r="AE10" s="57"/>
-      <c r="AF10" s="58"/>
-      <c r="AG10" s="52"/>
-      <c r="AH10" s="52"/>
-      <c r="AI10" s="52"/>
-      <c r="AJ10" s="52"/>
-      <c r="AK10" s="52"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="50"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="50"/>
+      <c r="J10" s="50"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="50"/>
+      <c r="N10" s="55"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="50"/>
+      <c r="Q10" s="50"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="52"/>
+      <c r="W10" s="57"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="52"/>
+      <c r="AA10" s="56"/>
+      <c r="AB10" s="50"/>
+      <c r="AC10" s="50"/>
+      <c r="AD10" s="54"/>
+      <c r="AE10" s="55"/>
+      <c r="AF10" s="56"/>
+      <c r="AG10" s="50"/>
+      <c r="AH10" s="50"/>
+      <c r="AI10" s="50"/>
+      <c r="AJ10" s="50"/>
+      <c r="AK10" s="50"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="50"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="56"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="57"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="52"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="52"/>
-      <c r="S11" s="52"/>
-      <c r="T11" s="52"/>
-      <c r="U11" s="52"/>
-      <c r="V11" s="57"/>
-      <c r="W11" s="59"/>
-      <c r="X11" s="52"/>
-      <c r="Y11" s="52"/>
-      <c r="Z11" s="57"/>
-      <c r="AA11" s="58"/>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="68"/>
-      <c r="AE11" s="57"/>
-      <c r="AF11" s="58"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="52"/>
-      <c r="AI11" s="52"/>
-      <c r="AJ11" s="52"/>
-      <c r="AK11" s="52"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="50"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="55"/>
+      <c r="W11" s="57"/>
+      <c r="X11" s="50"/>
+      <c r="Y11" s="50"/>
+      <c r="Z11" s="55"/>
+      <c r="AA11" s="56"/>
+      <c r="AB11" s="50"/>
+      <c r="AC11" s="50"/>
+      <c r="AD11" s="66"/>
+      <c r="AE11" s="55"/>
+      <c r="AF11" s="56"/>
+      <c r="AG11" s="50"/>
+      <c r="AH11" s="50"/>
+      <c r="AI11" s="50"/>
+      <c r="AJ11" s="50"/>
+      <c r="AK11" s="50"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="50"/>
-      <c r="C12" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="57"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="52"/>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="52"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="52"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="57"/>
-      <c r="W12" s="59"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="52"/>
-      <c r="Z12" s="57"/>
-      <c r="AA12" s="58"/>
-      <c r="AB12" s="52"/>
-      <c r="AC12" s="52"/>
-      <c r="AD12" s="56"/>
-      <c r="AE12" s="57"/>
-      <c r="AF12" s="55"/>
-      <c r="AG12" s="66"/>
-      <c r="AH12" s="66"/>
-      <c r="AI12" s="66"/>
-      <c r="AJ12" s="66"/>
-      <c r="AK12" s="66"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="50"/>
+      <c r="K12" s="50"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="50"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="50"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="55"/>
+      <c r="W12" s="57"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="55"/>
+      <c r="AA12" s="56"/>
+      <c r="AB12" s="50"/>
+      <c r="AC12" s="50"/>
+      <c r="AD12" s="54"/>
+      <c r="AE12" s="55"/>
+      <c r="AF12" s="53"/>
+      <c r="AG12" s="64"/>
+      <c r="AH12" s="64"/>
+      <c r="AI12" s="64"/>
+      <c r="AJ12" s="64"/>
+      <c r="AK12" s="64"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="56"/>
-      <c r="M13" s="52"/>
-      <c r="N13" s="57"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="52"/>
-      <c r="Q13" s="52"/>
-      <c r="R13" s="52"/>
-      <c r="S13" s="52"/>
-      <c r="T13" s="52"/>
-      <c r="U13" s="52"/>
-      <c r="V13" s="57"/>
-      <c r="W13" s="59"/>
-      <c r="X13" s="52"/>
-      <c r="Y13" s="52"/>
-      <c r="Z13" s="57"/>
-      <c r="AA13" s="58"/>
-      <c r="AB13" s="52"/>
-      <c r="AC13" s="52"/>
-      <c r="AD13" s="56"/>
-      <c r="AE13" s="57"/>
-      <c r="AF13" s="58"/>
-      <c r="AG13" s="52"/>
-      <c r="AH13" s="52"/>
-      <c r="AI13" s="52"/>
-      <c r="AJ13" s="52"/>
-      <c r="AK13" s="52"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="54"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="50"/>
+      <c r="V13" s="55"/>
+      <c r="W13" s="57"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="55"/>
+      <c r="AA13" s="56"/>
+      <c r="AB13" s="50"/>
+      <c r="AC13" s="50"/>
+      <c r="AD13" s="54"/>
+      <c r="AE13" s="55"/>
+      <c r="AF13" s="56"/>
+      <c r="AG13" s="50"/>
+      <c r="AH13" s="50"/>
+      <c r="AI13" s="50"/>
+      <c r="AJ13" s="50"/>
+      <c r="AK13" s="50"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="69" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="70" t="s">
+      <c r="B14" s="67" t="s">
         <v>142</v>
       </c>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="54"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="56"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="72"/>
-      <c r="T14" s="72"/>
-      <c r="U14" s="72"/>
-      <c r="V14" s="73"/>
-      <c r="W14" s="59"/>
-      <c r="X14" s="72"/>
-      <c r="Y14" s="72"/>
-      <c r="Z14" s="73"/>
-      <c r="AA14" s="71"/>
-      <c r="AB14" s="72"/>
-      <c r="AC14" s="72"/>
-      <c r="AD14" s="56"/>
-      <c r="AE14" s="73"/>
-      <c r="AF14" s="71"/>
-      <c r="AG14" s="72"/>
-      <c r="AH14" s="72"/>
-      <c r="AI14" s="72"/>
-      <c r="AJ14" s="72"/>
-      <c r="AK14" s="72"/>
+      <c r="C14" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="70"/>
+      <c r="N14" s="71"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="70"/>
+      <c r="Q14" s="70"/>
+      <c r="R14" s="70"/>
+      <c r="S14" s="70"/>
+      <c r="T14" s="70"/>
+      <c r="U14" s="70"/>
+      <c r="V14" s="71"/>
+      <c r="W14" s="57"/>
+      <c r="X14" s="70"/>
+      <c r="Y14" s="70"/>
+      <c r="Z14" s="71"/>
+      <c r="AA14" s="69"/>
+      <c r="AB14" s="70"/>
+      <c r="AC14" s="70"/>
+      <c r="AD14" s="54"/>
+      <c r="AE14" s="71"/>
+      <c r="AF14" s="69"/>
+      <c r="AG14" s="70"/>
+      <c r="AH14" s="70"/>
+      <c r="AI14" s="70"/>
+      <c r="AJ14" s="70"/>
+      <c r="AK14" s="70"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="69"/>
-      <c r="C15" s="70"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="56"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="73"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="72"/>
-      <c r="R15" s="72"/>
-      <c r="S15" s="72"/>
-      <c r="T15" s="72"/>
-      <c r="U15" s="72"/>
-      <c r="V15" s="73"/>
-      <c r="W15" s="59"/>
-      <c r="X15" s="72"/>
-      <c r="Y15" s="72"/>
-      <c r="Z15" s="73"/>
-      <c r="AA15" s="71"/>
-      <c r="AB15" s="72"/>
-      <c r="AC15" s="72"/>
-      <c r="AD15" s="56"/>
-      <c r="AE15" s="73"/>
-      <c r="AF15" s="71"/>
-      <c r="AG15" s="72"/>
-      <c r="AH15" s="72"/>
-      <c r="AI15" s="72"/>
-      <c r="AJ15" s="72"/>
-      <c r="AK15" s="72"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="70"/>
+      <c r="Q15" s="70"/>
+      <c r="R15" s="70"/>
+      <c r="S15" s="70"/>
+      <c r="T15" s="70"/>
+      <c r="U15" s="70"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="57"/>
+      <c r="X15" s="70"/>
+      <c r="Y15" s="70"/>
+      <c r="Z15" s="71"/>
+      <c r="AA15" s="69"/>
+      <c r="AB15" s="70"/>
+      <c r="AC15" s="70"/>
+      <c r="AD15" s="54"/>
+      <c r="AE15" s="71"/>
+      <c r="AF15" s="69"/>
+      <c r="AG15" s="70"/>
+      <c r="AH15" s="70"/>
+      <c r="AI15" s="70"/>
+      <c r="AJ15" s="70"/>
+      <c r="AK15" s="70"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="69"/>
-      <c r="C16" s="70" t="s">
-        <v>143</v>
-      </c>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="73"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="73"/>
-      <c r="O16" s="71"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="72"/>
-      <c r="T16" s="72"/>
-      <c r="U16" s="72"/>
-      <c r="V16" s="73"/>
-      <c r="W16" s="59"/>
-      <c r="X16" s="72"/>
-      <c r="Y16" s="72"/>
-      <c r="Z16" s="73"/>
-      <c r="AA16" s="71"/>
-      <c r="AB16" s="72"/>
-      <c r="AC16" s="72"/>
-      <c r="AD16" s="56"/>
-      <c r="AE16" s="73"/>
-      <c r="AF16" s="71"/>
-      <c r="AG16" s="72"/>
-      <c r="AH16" s="72"/>
-      <c r="AI16" s="72"/>
-      <c r="AJ16" s="72"/>
-      <c r="AK16" s="72"/>
+      <c r="B16" s="67"/>
+      <c r="C16" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" s="64"/>
+      <c r="E16" s="64"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="70"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="69"/>
+      <c r="P16" s="70"/>
+      <c r="Q16" s="70"/>
+      <c r="R16" s="70"/>
+      <c r="S16" s="70"/>
+      <c r="T16" s="70"/>
+      <c r="U16" s="70"/>
+      <c r="V16" s="71"/>
+      <c r="W16" s="57"/>
+      <c r="X16" s="70"/>
+      <c r="Y16" s="70"/>
+      <c r="Z16" s="71"/>
+      <c r="AA16" s="69"/>
+      <c r="AB16" s="70"/>
+      <c r="AC16" s="70"/>
+      <c r="AD16" s="54"/>
+      <c r="AE16" s="71"/>
+      <c r="AF16" s="69"/>
+      <c r="AG16" s="70"/>
+      <c r="AH16" s="70"/>
+      <c r="AI16" s="70"/>
+      <c r="AJ16" s="70"/>
+      <c r="AK16" s="70"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="69"/>
-      <c r="C17" s="70"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="65"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="56"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="73"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="72"/>
-      <c r="U17" s="72"/>
-      <c r="V17" s="73"/>
-      <c r="W17" s="59"/>
-      <c r="X17" s="72"/>
-      <c r="Y17" s="72"/>
-      <c r="Z17" s="73"/>
-      <c r="AA17" s="71"/>
-      <c r="AB17" s="72"/>
-      <c r="AC17" s="72"/>
-      <c r="AD17" s="56"/>
-      <c r="AE17" s="73"/>
-      <c r="AF17" s="71"/>
-      <c r="AG17" s="72"/>
-      <c r="AH17" s="72"/>
-      <c r="AI17" s="72"/>
-      <c r="AJ17" s="72"/>
-      <c r="AK17" s="72"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="68"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="54"/>
+      <c r="M17" s="70"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="70"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="70"/>
+      <c r="S17" s="70"/>
+      <c r="T17" s="70"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="71"/>
+      <c r="W17" s="57"/>
+      <c r="X17" s="70"/>
+      <c r="Y17" s="70"/>
+      <c r="Z17" s="71"/>
+      <c r="AA17" s="69"/>
+      <c r="AB17" s="70"/>
+      <c r="AC17" s="70"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="71"/>
+      <c r="AF17" s="69"/>
+      <c r="AG17" s="70"/>
+      <c r="AH17" s="70"/>
+      <c r="AI17" s="70"/>
+      <c r="AJ17" s="70"/>
+      <c r="AK17" s="70"/>
       <c r="AN17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="69"/>
-      <c r="C18" s="70" t="s">
-        <v>145</v>
-      </c>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="56"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="73"/>
-      <c r="O18" s="71"/>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="72"/>
-      <c r="U18" s="72"/>
-      <c r="V18" s="73"/>
-      <c r="W18" s="59"/>
-      <c r="X18" s="72"/>
-      <c r="Y18" s="72"/>
-      <c r="Z18" s="73"/>
-      <c r="AA18" s="71"/>
-      <c r="AB18" s="72"/>
-      <c r="AC18" s="72"/>
-      <c r="AD18" s="56"/>
-      <c r="AE18" s="73"/>
-      <c r="AF18" s="71"/>
-      <c r="AG18" s="72"/>
-      <c r="AH18" s="72"/>
-      <c r="AI18" s="72"/>
-      <c r="AJ18" s="72"/>
-      <c r="AK18" s="72"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="68" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="70"/>
+      <c r="N18" s="71"/>
+      <c r="O18" s="69"/>
+      <c r="P18" s="70"/>
+      <c r="Q18" s="70"/>
+      <c r="R18" s="70"/>
+      <c r="S18" s="70"/>
+      <c r="T18" s="70"/>
+      <c r="U18" s="70"/>
+      <c r="V18" s="71"/>
+      <c r="W18" s="57"/>
+      <c r="X18" s="70"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="71"/>
+      <c r="AA18" s="69"/>
+      <c r="AB18" s="70"/>
+      <c r="AC18" s="70"/>
+      <c r="AD18" s="54"/>
+      <c r="AE18" s="71"/>
+      <c r="AF18" s="69"/>
+      <c r="AG18" s="70"/>
+      <c r="AH18" s="70"/>
+      <c r="AI18" s="70"/>
+      <c r="AJ18" s="70"/>
+      <c r="AK18" s="70"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="69"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="56"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="73"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="72"/>
-      <c r="U19" s="72"/>
-      <c r="V19" s="73"/>
-      <c r="W19" s="59"/>
-      <c r="X19" s="72"/>
-      <c r="Y19" s="72"/>
-      <c r="Z19" s="73"/>
-      <c r="AA19" s="71"/>
-      <c r="AB19" s="72"/>
-      <c r="AC19" s="72"/>
-      <c r="AD19" s="56"/>
-      <c r="AE19" s="73"/>
-      <c r="AF19" s="71"/>
-      <c r="AG19" s="72"/>
-      <c r="AH19" s="72"/>
-      <c r="AI19" s="72"/>
-      <c r="AJ19" s="72"/>
-      <c r="AK19" s="72"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="70"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="69"/>
+      <c r="P19" s="70"/>
+      <c r="Q19" s="70"/>
+      <c r="R19" s="70"/>
+      <c r="S19" s="70"/>
+      <c r="T19" s="70"/>
+      <c r="U19" s="70"/>
+      <c r="V19" s="71"/>
+      <c r="W19" s="57"/>
+      <c r="X19" s="70"/>
+      <c r="Y19" s="70"/>
+      <c r="Z19" s="71"/>
+      <c r="AA19" s="69"/>
+      <c r="AB19" s="70"/>
+      <c r="AC19" s="70"/>
+      <c r="AD19" s="54"/>
+      <c r="AE19" s="71"/>
+      <c r="AF19" s="69"/>
+      <c r="AG19" s="70"/>
+      <c r="AH19" s="70"/>
+      <c r="AI19" s="70"/>
+      <c r="AJ19" s="70"/>
+      <c r="AK19" s="70"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="69"/>
-      <c r="C20" s="70" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="55"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="56"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="73"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="72"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="72"/>
-      <c r="T20" s="72"/>
-      <c r="U20" s="72"/>
-      <c r="V20" s="73"/>
-      <c r="W20" s="59"/>
-      <c r="X20" s="72"/>
-      <c r="Y20" s="72"/>
-      <c r="Z20" s="73"/>
-      <c r="AA20" s="71"/>
-      <c r="AB20" s="72"/>
-      <c r="AC20" s="72"/>
-      <c r="AD20" s="56"/>
-      <c r="AE20" s="73"/>
-      <c r="AF20" s="71"/>
-      <c r="AG20" s="72"/>
-      <c r="AH20" s="72"/>
-      <c r="AI20" s="72"/>
-      <c r="AJ20" s="72"/>
-      <c r="AK20" s="72"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="70"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="71"/>
+      <c r="O20" s="69"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="70"/>
+      <c r="T20" s="70"/>
+      <c r="U20" s="70"/>
+      <c r="V20" s="71"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="70"/>
+      <c r="Y20" s="70"/>
+      <c r="Z20" s="71"/>
+      <c r="AA20" s="69"/>
+      <c r="AB20" s="70"/>
+      <c r="AC20" s="70"/>
+      <c r="AD20" s="54"/>
+      <c r="AE20" s="71"/>
+      <c r="AF20" s="69"/>
+      <c r="AG20" s="70"/>
+      <c r="AH20" s="70"/>
+      <c r="AI20" s="70"/>
+      <c r="AJ20" s="70"/>
+      <c r="AK20" s="70"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="69"/>
-      <c r="C21" s="70"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="72"/>
-      <c r="K21" s="72"/>
-      <c r="L21" s="56"/>
-      <c r="M21" s="72"/>
-      <c r="N21" s="73"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="72"/>
-      <c r="T21" s="72"/>
-      <c r="U21" s="72"/>
-      <c r="V21" s="73"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="72"/>
-      <c r="Y21" s="72"/>
-      <c r="Z21" s="73"/>
-      <c r="AA21" s="71"/>
-      <c r="AB21" s="72"/>
-      <c r="AC21" s="72"/>
-      <c r="AD21" s="56"/>
-      <c r="AE21" s="73"/>
-      <c r="AF21" s="71"/>
-      <c r="AG21" s="72"/>
-      <c r="AH21" s="72"/>
-      <c r="AI21" s="72"/>
-      <c r="AJ21" s="72"/>
-      <c r="AK21" s="72"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="54"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="69"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="70"/>
+      <c r="R21" s="70"/>
+      <c r="S21" s="70"/>
+      <c r="T21" s="70"/>
+      <c r="U21" s="70"/>
+      <c r="V21" s="71"/>
+      <c r="W21" s="57"/>
+      <c r="X21" s="70"/>
+      <c r="Y21" s="70"/>
+      <c r="Z21" s="71"/>
+      <c r="AA21" s="69"/>
+      <c r="AB21" s="70"/>
+      <c r="AC21" s="70"/>
+      <c r="AD21" s="54"/>
+      <c r="AE21" s="71"/>
+      <c r="AF21" s="69"/>
+      <c r="AG21" s="70"/>
+      <c r="AH21" s="70"/>
+      <c r="AI21" s="70"/>
+      <c r="AJ21" s="70"/>
+      <c r="AK21" s="70"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="69"/>
-      <c r="C22" s="70" t="s">
-        <v>147</v>
-      </c>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="56"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="73"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="72"/>
-      <c r="T22" s="72"/>
-      <c r="U22" s="72"/>
-      <c r="V22" s="73"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="72"/>
-      <c r="Y22" s="72"/>
-      <c r="Z22" s="73"/>
-      <c r="AA22" s="71"/>
-      <c r="AB22" s="72"/>
-      <c r="AC22" s="72"/>
-      <c r="AD22" s="56"/>
-      <c r="AE22" s="73"/>
-      <c r="AF22" s="71"/>
-      <c r="AG22" s="72"/>
-      <c r="AH22" s="72"/>
-      <c r="AI22" s="72"/>
-      <c r="AJ22" s="72"/>
-      <c r="AK22" s="72"/>
+      <c r="B22" s="67"/>
+      <c r="C22" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="71"/>
+      <c r="O22" s="69"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="70"/>
+      <c r="R22" s="70"/>
+      <c r="S22" s="70"/>
+      <c r="T22" s="70"/>
+      <c r="U22" s="70"/>
+      <c r="V22" s="71"/>
+      <c r="W22" s="57"/>
+      <c r="X22" s="70"/>
+      <c r="Y22" s="70"/>
+      <c r="Z22" s="71"/>
+      <c r="AA22" s="69"/>
+      <c r="AB22" s="70"/>
+      <c r="AC22" s="70"/>
+      <c r="AD22" s="54"/>
+      <c r="AE22" s="71"/>
+      <c r="AF22" s="69"/>
+      <c r="AG22" s="70"/>
+      <c r="AH22" s="70"/>
+      <c r="AI22" s="70"/>
+      <c r="AJ22" s="70"/>
+      <c r="AK22" s="70"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="69"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="72"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="56"/>
-      <c r="M23" s="72"/>
-      <c r="N23" s="73"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="72"/>
-      <c r="Q23" s="72"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="72"/>
-      <c r="T23" s="72"/>
-      <c r="U23" s="72"/>
-      <c r="V23" s="73"/>
-      <c r="W23" s="59"/>
-      <c r="X23" s="72"/>
-      <c r="Y23" s="72"/>
-      <c r="Z23" s="73"/>
-      <c r="AA23" s="71"/>
-      <c r="AB23" s="72"/>
-      <c r="AC23" s="72"/>
-      <c r="AD23" s="56"/>
-      <c r="AE23" s="73"/>
-      <c r="AF23" s="71"/>
-      <c r="AG23" s="72"/>
-      <c r="AH23" s="72"/>
-      <c r="AI23" s="72"/>
-      <c r="AJ23" s="72"/>
-      <c r="AK23" s="72"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="69"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
+      <c r="R23" s="70"/>
+      <c r="S23" s="70"/>
+      <c r="T23" s="70"/>
+      <c r="U23" s="70"/>
+      <c r="V23" s="71"/>
+      <c r="W23" s="57"/>
+      <c r="X23" s="70"/>
+      <c r="Y23" s="70"/>
+      <c r="Z23" s="71"/>
+      <c r="AA23" s="69"/>
+      <c r="AB23" s="70"/>
+      <c r="AC23" s="70"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="71"/>
+      <c r="AF23" s="69"/>
+      <c r="AG23" s="70"/>
+      <c r="AH23" s="70"/>
+      <c r="AI23" s="70"/>
+      <c r="AJ23" s="70"/>
+      <c r="AK23" s="70"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="69"/>
-      <c r="C24" s="70" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="56"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="73"/>
-      <c r="O24" s="71"/>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="72"/>
-      <c r="T24" s="72"/>
-      <c r="U24" s="72"/>
-      <c r="V24" s="73"/>
-      <c r="W24" s="59"/>
-      <c r="X24" s="72"/>
-      <c r="Y24" s="72"/>
-      <c r="Z24" s="73"/>
-      <c r="AA24" s="71"/>
-      <c r="AB24" s="72"/>
-      <c r="AC24" s="72"/>
-      <c r="AD24" s="56"/>
-      <c r="AE24" s="73"/>
-      <c r="AF24" s="71"/>
-      <c r="AG24" s="72"/>
-      <c r="AH24" s="72"/>
-      <c r="AI24" s="72"/>
-      <c r="AJ24" s="72"/>
-      <c r="AK24" s="72"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="68" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="71"/>
+      <c r="O24" s="69"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="70"/>
+      <c r="R24" s="70"/>
+      <c r="S24" s="70"/>
+      <c r="T24" s="70"/>
+      <c r="U24" s="70"/>
+      <c r="V24" s="71"/>
+      <c r="W24" s="57"/>
+      <c r="X24" s="70"/>
+      <c r="Y24" s="70"/>
+      <c r="Z24" s="71"/>
+      <c r="AA24" s="69"/>
+      <c r="AB24" s="70"/>
+      <c r="AC24" s="70"/>
+      <c r="AD24" s="54"/>
+      <c r="AE24" s="71"/>
+      <c r="AF24" s="69"/>
+      <c r="AG24" s="70"/>
+      <c r="AH24" s="70"/>
+      <c r="AI24" s="70"/>
+      <c r="AJ24" s="70"/>
+      <c r="AK24" s="70"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="69"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="56"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="73"/>
-      <c r="O25" s="71"/>
-      <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="72"/>
-      <c r="T25" s="72"/>
-      <c r="U25" s="72"/>
-      <c r="V25" s="73"/>
-      <c r="W25" s="59"/>
-      <c r="X25" s="72"/>
-      <c r="Y25" s="72"/>
-      <c r="Z25" s="73"/>
-      <c r="AA25" s="71"/>
-      <c r="AB25" s="72"/>
-      <c r="AC25" s="72"/>
-      <c r="AD25" s="56"/>
-      <c r="AE25" s="73"/>
-      <c r="AF25" s="71"/>
-      <c r="AG25" s="72"/>
-      <c r="AH25" s="72"/>
-      <c r="AI25" s="72"/>
-      <c r="AJ25" s="72"/>
-      <c r="AK25" s="72"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="54"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="69"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="70"/>
+      <c r="R25" s="70"/>
+      <c r="S25" s="70"/>
+      <c r="T25" s="70"/>
+      <c r="U25" s="70"/>
+      <c r="V25" s="71"/>
+      <c r="W25" s="57"/>
+      <c r="X25" s="70"/>
+      <c r="Y25" s="70"/>
+      <c r="Z25" s="71"/>
+      <c r="AA25" s="69"/>
+      <c r="AB25" s="70"/>
+      <c r="AC25" s="70"/>
+      <c r="AD25" s="54"/>
+      <c r="AE25" s="71"/>
+      <c r="AF25" s="69"/>
+      <c r="AG25" s="70"/>
+      <c r="AH25" s="70"/>
+      <c r="AI25" s="70"/>
+      <c r="AJ25" s="70"/>
+      <c r="AK25" s="70"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="50" t="s">
-        <v>149</v>
-      </c>
-      <c r="C26" s="51" t="s">
+      <c r="B26" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="55"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="56"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="58"/>
-      <c r="P26" s="52"/>
-      <c r="Q26" s="52"/>
-      <c r="R26" s="52"/>
-      <c r="S26" s="52"/>
-      <c r="T26" s="52"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="57"/>
-      <c r="W26" s="59"/>
-      <c r="X26" s="52"/>
-      <c r="Y26" s="52"/>
-      <c r="Z26" s="57"/>
-      <c r="AA26" s="58"/>
-      <c r="AB26" s="52"/>
-      <c r="AC26" s="52"/>
-      <c r="AD26" s="56"/>
-      <c r="AE26" s="57"/>
-      <c r="AF26" s="58"/>
-      <c r="AG26" s="52"/>
-      <c r="AH26" s="52"/>
-      <c r="AI26" s="52"/>
-      <c r="AJ26" s="52"/>
-      <c r="AK26" s="52"/>
+      <c r="C26" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="55"/>
+      <c r="W26" s="57"/>
+      <c r="X26" s="50"/>
+      <c r="Y26" s="50"/>
+      <c r="Z26" s="55"/>
+      <c r="AA26" s="56"/>
+      <c r="AB26" s="50"/>
+      <c r="AC26" s="50"/>
+      <c r="AD26" s="54"/>
+      <c r="AE26" s="55"/>
+      <c r="AF26" s="56"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="50"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="58"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="52"/>
-      <c r="R27" s="52"/>
-      <c r="S27" s="52"/>
-      <c r="T27" s="52"/>
-      <c r="U27" s="52"/>
-      <c r="V27" s="57"/>
-      <c r="W27" s="59"/>
-      <c r="X27" s="52"/>
-      <c r="Y27" s="52"/>
-      <c r="Z27" s="57"/>
-      <c r="AA27" s="58"/>
-      <c r="AB27" s="52"/>
-      <c r="AC27" s="52"/>
-      <c r="AD27" s="56"/>
-      <c r="AE27" s="57"/>
-      <c r="AF27" s="58"/>
-      <c r="AG27" s="52"/>
-      <c r="AH27" s="52"/>
-      <c r="AI27" s="52"/>
-      <c r="AJ27" s="52"/>
-      <c r="AK27" s="52"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="50"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="55"/>
+      <c r="W27" s="57"/>
+      <c r="X27" s="50"/>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="55"/>
+      <c r="AA27" s="56"/>
+      <c r="AB27" s="50"/>
+      <c r="AC27" s="50"/>
+      <c r="AD27" s="54"/>
+      <c r="AE27" s="55"/>
+      <c r="AF27" s="56"/>
+      <c r="AG27" s="50"/>
+      <c r="AH27" s="50"/>
+      <c r="AI27" s="50"/>
+      <c r="AJ27" s="50"/>
+      <c r="AK27" s="50"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="50"/>
-      <c r="C28" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="56"/>
-      <c r="M28" s="52"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="58"/>
-      <c r="P28" s="52"/>
-      <c r="Q28" s="52"/>
-      <c r="R28" s="52"/>
-      <c r="S28" s="52"/>
-      <c r="T28" s="52"/>
-      <c r="U28" s="52"/>
-      <c r="V28" s="57"/>
-      <c r="W28" s="59"/>
-      <c r="X28" s="52"/>
-      <c r="Y28" s="52"/>
-      <c r="Z28" s="57"/>
-      <c r="AA28" s="58"/>
-      <c r="AB28" s="52"/>
-      <c r="AC28" s="52"/>
-      <c r="AD28" s="56"/>
-      <c r="AE28" s="57"/>
-      <c r="AF28" s="58"/>
-      <c r="AG28" s="52"/>
-      <c r="AH28" s="52"/>
-      <c r="AI28" s="52"/>
-      <c r="AJ28" s="52"/>
-      <c r="AK28" s="52"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="64"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="64"/>
+      <c r="L28" s="54"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="56"/>
+      <c r="P28" s="50"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="50"/>
+      <c r="V28" s="55"/>
+      <c r="W28" s="57"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="55"/>
+      <c r="AA28" s="56"/>
+      <c r="AB28" s="50"/>
+      <c r="AC28" s="50"/>
+      <c r="AD28" s="54"/>
+      <c r="AE28" s="55"/>
+      <c r="AF28" s="56"/>
+      <c r="AG28" s="50"/>
+      <c r="AH28" s="50"/>
+      <c r="AI28" s="50"/>
+      <c r="AJ28" s="50"/>
+      <c r="AK28" s="50"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="50"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="63"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="67"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="56"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="52"/>
-      <c r="Q29" s="52"/>
-      <c r="R29" s="52"/>
-      <c r="S29" s="52"/>
-      <c r="T29" s="52"/>
-      <c r="U29" s="52"/>
-      <c r="V29" s="57"/>
-      <c r="W29" s="59"/>
-      <c r="X29" s="52"/>
-      <c r="Y29" s="52"/>
-      <c r="Z29" s="57"/>
-      <c r="AA29" s="58"/>
-      <c r="AB29" s="52"/>
-      <c r="AC29" s="52"/>
-      <c r="AD29" s="56"/>
-      <c r="AE29" s="57"/>
-      <c r="AF29" s="58"/>
-      <c r="AG29" s="52"/>
-      <c r="AH29" s="52"/>
-      <c r="AI29" s="52"/>
-      <c r="AJ29" s="52"/>
-      <c r="AK29" s="52"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="50"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="50"/>
+      <c r="V29" s="55"/>
+      <c r="W29" s="57"/>
+      <c r="X29" s="50"/>
+      <c r="Y29" s="50"/>
+      <c r="Z29" s="55"/>
+      <c r="AA29" s="56"/>
+      <c r="AB29" s="50"/>
+      <c r="AC29" s="50"/>
+      <c r="AD29" s="54"/>
+      <c r="AE29" s="55"/>
+      <c r="AF29" s="56"/>
+      <c r="AG29" s="50"/>
+      <c r="AH29" s="50"/>
+      <c r="AI29" s="50"/>
+      <c r="AJ29" s="50"/>
+      <c r="AK29" s="50"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="50"/>
-      <c r="C30" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="66"/>
-      <c r="N30" s="57"/>
-      <c r="O30" s="58"/>
-      <c r="P30" s="52"/>
-      <c r="Q30" s="52"/>
-      <c r="R30" s="52"/>
-      <c r="S30" s="52"/>
-      <c r="T30" s="52"/>
-      <c r="U30" s="52"/>
-      <c r="V30" s="57"/>
-      <c r="W30" s="59"/>
-      <c r="X30" s="52"/>
-      <c r="Y30" s="52"/>
-      <c r="Z30" s="57"/>
-      <c r="AA30" s="58"/>
-      <c r="AB30" s="52"/>
-      <c r="AC30" s="52"/>
-      <c r="AD30" s="56"/>
-      <c r="AE30" s="57"/>
-      <c r="AF30" s="58"/>
-      <c r="AG30" s="52"/>
-      <c r="AH30" s="52"/>
-      <c r="AI30" s="52"/>
-      <c r="AJ30" s="52"/>
-      <c r="AK30" s="52"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50"/>
+      <c r="S30" s="50"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="50"/>
+      <c r="V30" s="55"/>
+      <c r="W30" s="57"/>
+      <c r="X30" s="50"/>
+      <c r="Y30" s="50"/>
+      <c r="Z30" s="55"/>
+      <c r="AA30" s="56"/>
+      <c r="AB30" s="50"/>
+      <c r="AC30" s="50"/>
+      <c r="AD30" s="54"/>
+      <c r="AE30" s="55"/>
+      <c r="AF30" s="56"/>
+      <c r="AG30" s="50"/>
+      <c r="AH30" s="50"/>
+      <c r="AI30" s="50"/>
+      <c r="AJ30" s="50"/>
+      <c r="AK30" s="50"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="50"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="77"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="52"/>
-      <c r="Q31" s="52"/>
-      <c r="R31" s="52"/>
-      <c r="S31" s="52"/>
-      <c r="T31" s="52"/>
-      <c r="U31" s="52"/>
-      <c r="V31" s="57"/>
-      <c r="W31" s="59"/>
-      <c r="X31" s="52"/>
-      <c r="Y31" s="52"/>
-      <c r="Z31" s="57"/>
-      <c r="AA31" s="58"/>
-      <c r="AB31" s="52"/>
-      <c r="AC31" s="52"/>
-      <c r="AD31" s="56"/>
-      <c r="AE31" s="57"/>
-      <c r="AF31" s="58"/>
-      <c r="AG31" s="52"/>
-      <c r="AH31" s="52"/>
-      <c r="AI31" s="52"/>
-      <c r="AJ31" s="52"/>
-      <c r="AK31" s="52"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="65"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="75"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="61"/>
+      <c r="O31" s="56"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="50"/>
+      <c r="V31" s="55"/>
+      <c r="W31" s="57"/>
+      <c r="X31" s="50"/>
+      <c r="Y31" s="50"/>
+      <c r="Z31" s="55"/>
+      <c r="AA31" s="56"/>
+      <c r="AB31" s="50"/>
+      <c r="AC31" s="50"/>
+      <c r="AD31" s="54"/>
+      <c r="AE31" s="55"/>
+      <c r="AF31" s="56"/>
+      <c r="AG31" s="50"/>
+      <c r="AH31" s="50"/>
+      <c r="AI31" s="50"/>
+      <c r="AJ31" s="50"/>
+      <c r="AK31" s="50"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="50"/>
-      <c r="C32" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="66"/>
-      <c r="N32" s="54"/>
-      <c r="O32" s="58"/>
-      <c r="P32" s="52"/>
-      <c r="Q32" s="52"/>
-      <c r="R32" s="52"/>
-      <c r="S32" s="52"/>
-      <c r="T32" s="52"/>
-      <c r="U32" s="52"/>
-      <c r="V32" s="57"/>
-      <c r="W32" s="59"/>
-      <c r="X32" s="52"/>
-      <c r="Y32" s="52"/>
-      <c r="Z32" s="57"/>
-      <c r="AA32" s="58"/>
-      <c r="AB32" s="52"/>
-      <c r="AC32" s="52"/>
-      <c r="AD32" s="56"/>
-      <c r="AE32" s="57"/>
-      <c r="AF32" s="58"/>
-      <c r="AG32" s="52"/>
-      <c r="AH32" s="52"/>
-      <c r="AI32" s="52"/>
-      <c r="AJ32" s="52"/>
-      <c r="AK32" s="52"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="64"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="50"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="50"/>
+      <c r="S32" s="50"/>
+      <c r="T32" s="50"/>
+      <c r="U32" s="50"/>
+      <c r="V32" s="55"/>
+      <c r="W32" s="57"/>
+      <c r="X32" s="50"/>
+      <c r="Y32" s="50"/>
+      <c r="Z32" s="55"/>
+      <c r="AA32" s="56"/>
+      <c r="AB32" s="50"/>
+      <c r="AC32" s="50"/>
+      <c r="AD32" s="54"/>
+      <c r="AE32" s="55"/>
+      <c r="AF32" s="56"/>
+      <c r="AG32" s="50"/>
+      <c r="AH32" s="50"/>
+      <c r="AI32" s="50"/>
+      <c r="AJ32" s="50"/>
+      <c r="AK32" s="50"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="50"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
-      <c r="L33" s="56"/>
-      <c r="M33" s="52"/>
-      <c r="N33" s="63"/>
-      <c r="O33" s="58"/>
-      <c r="P33" s="52"/>
-      <c r="Q33" s="52"/>
-      <c r="R33" s="52"/>
-      <c r="S33" s="52"/>
-      <c r="T33" s="52"/>
-      <c r="U33" s="52"/>
-      <c r="V33" s="57"/>
-      <c r="W33" s="59"/>
-      <c r="X33" s="52"/>
-      <c r="Y33" s="52"/>
-      <c r="Z33" s="57"/>
-      <c r="AA33" s="58"/>
-      <c r="AB33" s="52"/>
-      <c r="AC33" s="52"/>
-      <c r="AD33" s="56"/>
-      <c r="AE33" s="57"/>
-      <c r="AF33" s="58"/>
-      <c r="AG33" s="52"/>
-      <c r="AH33" s="52"/>
-      <c r="AI33" s="52"/>
-      <c r="AJ33" s="52"/>
-      <c r="AK33" s="52"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="54"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="61"/>
+      <c r="O33" s="56"/>
+      <c r="P33" s="50"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50"/>
+      <c r="S33" s="50"/>
+      <c r="T33" s="50"/>
+      <c r="U33" s="50"/>
+      <c r="V33" s="55"/>
+      <c r="W33" s="57"/>
+      <c r="X33" s="50"/>
+      <c r="Y33" s="50"/>
+      <c r="Z33" s="55"/>
+      <c r="AA33" s="56"/>
+      <c r="AB33" s="50"/>
+      <c r="AC33" s="50"/>
+      <c r="AD33" s="54"/>
+      <c r="AE33" s="55"/>
+      <c r="AF33" s="56"/>
+      <c r="AG33" s="50"/>
+      <c r="AH33" s="50"/>
+      <c r="AI33" s="50"/>
+      <c r="AJ33" s="50"/>
+      <c r="AK33" s="50"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="69" t="s">
-        <v>154</v>
-      </c>
-      <c r="C34" s="78" t="s">
+      <c r="B34" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="73"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="72"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="56"/>
-      <c r="M34" s="66"/>
-      <c r="N34" s="54"/>
-      <c r="O34" s="55"/>
-      <c r="P34" s="66"/>
-      <c r="Q34" s="66"/>
-      <c r="R34" s="66"/>
-      <c r="S34" s="72"/>
-      <c r="T34" s="72"/>
-      <c r="U34" s="72"/>
-      <c r="V34" s="73"/>
-      <c r="W34" s="59"/>
-      <c r="X34" s="72"/>
-      <c r="Y34" s="72"/>
-      <c r="Z34" s="73"/>
-      <c r="AA34" s="71"/>
-      <c r="AB34" s="72"/>
-      <c r="AC34" s="72"/>
-      <c r="AD34" s="56"/>
-      <c r="AE34" s="73"/>
-      <c r="AF34" s="71"/>
-      <c r="AG34" s="72"/>
-      <c r="AH34" s="72"/>
-      <c r="AI34" s="72"/>
-      <c r="AJ34" s="72"/>
-      <c r="AK34" s="72"/>
+      <c r="C34" s="76" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="70"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="70"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="64"/>
+      <c r="N34" s="52"/>
+      <c r="O34" s="53"/>
+      <c r="P34" s="64"/>
+      <c r="Q34" s="64"/>
+      <c r="R34" s="64"/>
+      <c r="S34" s="70"/>
+      <c r="T34" s="70"/>
+      <c r="U34" s="70"/>
+      <c r="V34" s="71"/>
+      <c r="W34" s="57"/>
+      <c r="X34" s="70"/>
+      <c r="Y34" s="70"/>
+      <c r="Z34" s="71"/>
+      <c r="AA34" s="69"/>
+      <c r="AB34" s="70"/>
+      <c r="AC34" s="70"/>
+      <c r="AD34" s="54"/>
+      <c r="AE34" s="71"/>
+      <c r="AF34" s="69"/>
+      <c r="AG34" s="70"/>
+      <c r="AH34" s="70"/>
+      <c r="AI34" s="70"/>
+      <c r="AJ34" s="70"/>
+      <c r="AK34" s="70"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="69"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72"/>
-      <c r="K35" s="79"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="72"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="71"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="72"/>
-      <c r="R35" s="80"/>
-      <c r="S35" s="80"/>
-      <c r="T35" s="61"/>
-      <c r="U35" s="72"/>
-      <c r="V35" s="73"/>
-      <c r="W35" s="59"/>
-      <c r="X35" s="72"/>
-      <c r="Y35" s="72"/>
-      <c r="Z35" s="73"/>
-      <c r="AA35" s="71"/>
-      <c r="AB35" s="72"/>
-      <c r="AC35" s="72"/>
-      <c r="AD35" s="56"/>
-      <c r="AE35" s="73"/>
-      <c r="AF35" s="71"/>
-      <c r="AG35" s="72"/>
-      <c r="AH35" s="72"/>
-      <c r="AI35" s="72"/>
-      <c r="AJ35" s="72"/>
-      <c r="AK35" s="72"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="70"/>
+      <c r="N35" s="61"/>
+      <c r="O35" s="69"/>
+      <c r="P35" s="63"/>
+      <c r="Q35" s="70"/>
+      <c r="R35" s="78"/>
+      <c r="S35" s="78"/>
+      <c r="T35" s="59"/>
+      <c r="U35" s="70"/>
+      <c r="V35" s="71"/>
+      <c r="W35" s="57"/>
+      <c r="X35" s="70"/>
+      <c r="Y35" s="70"/>
+      <c r="Z35" s="71"/>
+      <c r="AA35" s="69"/>
+      <c r="AB35" s="70"/>
+      <c r="AC35" s="70"/>
+      <c r="AD35" s="54"/>
+      <c r="AE35" s="71"/>
+      <c r="AF35" s="69"/>
+      <c r="AG35" s="70"/>
+      <c r="AH35" s="70"/>
+      <c r="AI35" s="70"/>
+      <c r="AJ35" s="70"/>
+      <c r="AK35" s="70"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="69"/>
-      <c r="C36" s="78" t="s">
-        <v>156</v>
-      </c>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="73"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="72"/>
-      <c r="J36" s="72"/>
-      <c r="K36" s="72"/>
-      <c r="L36" s="56"/>
-      <c r="M36" s="66"/>
-      <c r="N36" s="54"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="66"/>
-      <c r="Q36" s="72"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="72"/>
-      <c r="T36" s="72"/>
-      <c r="U36" s="72"/>
-      <c r="V36" s="73"/>
-      <c r="W36" s="59"/>
-      <c r="X36" s="72"/>
-      <c r="Y36" s="72"/>
-      <c r="Z36" s="73"/>
-      <c r="AA36" s="71"/>
-      <c r="AB36" s="72"/>
-      <c r="AC36" s="72"/>
-      <c r="AD36" s="56"/>
-      <c r="AE36" s="73"/>
-      <c r="AF36" s="71"/>
-      <c r="AG36" s="72"/>
-      <c r="AH36" s="72"/>
-      <c r="AI36" s="72"/>
-      <c r="AJ36" s="72"/>
-      <c r="AK36" s="72"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="76" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="70"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="64"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="53"/>
+      <c r="P36" s="64"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="70"/>
+      <c r="S36" s="70"/>
+      <c r="T36" s="70"/>
+      <c r="U36" s="70"/>
+      <c r="V36" s="71"/>
+      <c r="W36" s="57"/>
+      <c r="X36" s="70"/>
+      <c r="Y36" s="70"/>
+      <c r="Z36" s="71"/>
+      <c r="AA36" s="69"/>
+      <c r="AB36" s="70"/>
+      <c r="AC36" s="70"/>
+      <c r="AD36" s="54"/>
+      <c r="AE36" s="71"/>
+      <c r="AF36" s="69"/>
+      <c r="AG36" s="70"/>
+      <c r="AH36" s="70"/>
+      <c r="AI36" s="70"/>
+      <c r="AJ36" s="70"/>
+      <c r="AK36" s="70"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="69"/>
-      <c r="C37" s="78"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="73"/>
-      <c r="H37" s="71"/>
-      <c r="I37" s="72"/>
-      <c r="J37" s="72"/>
-      <c r="K37" s="79"/>
-      <c r="L37" s="56"/>
-      <c r="M37" s="72"/>
-      <c r="N37" s="73"/>
-      <c r="O37" s="71"/>
-      <c r="P37" s="65"/>
-      <c r="Q37" s="72"/>
-      <c r="R37" s="80"/>
-      <c r="S37" s="80"/>
-      <c r="T37" s="61"/>
-      <c r="U37" s="72"/>
-      <c r="V37" s="73"/>
-      <c r="W37" s="59"/>
-      <c r="X37" s="72"/>
-      <c r="Y37" s="72"/>
-      <c r="Z37" s="73"/>
-      <c r="AA37" s="71"/>
-      <c r="AB37" s="72"/>
-      <c r="AC37" s="72"/>
-      <c r="AD37" s="56"/>
-      <c r="AE37" s="73"/>
-      <c r="AF37" s="71"/>
-      <c r="AG37" s="72"/>
-      <c r="AH37" s="72"/>
-      <c r="AI37" s="72"/>
-      <c r="AJ37" s="72"/>
-      <c r="AK37" s="72"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="77"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="70"/>
+      <c r="N37" s="71"/>
+      <c r="O37" s="69"/>
+      <c r="P37" s="63"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="78"/>
+      <c r="S37" s="78"/>
+      <c r="T37" s="59"/>
+      <c r="U37" s="70"/>
+      <c r="V37" s="71"/>
+      <c r="W37" s="57"/>
+      <c r="X37" s="70"/>
+      <c r="Y37" s="70"/>
+      <c r="Z37" s="71"/>
+      <c r="AA37" s="69"/>
+      <c r="AB37" s="70"/>
+      <c r="AC37" s="70"/>
+      <c r="AD37" s="54"/>
+      <c r="AE37" s="71"/>
+      <c r="AF37" s="69"/>
+      <c r="AG37" s="70"/>
+      <c r="AH37" s="70"/>
+      <c r="AI37" s="70"/>
+      <c r="AJ37" s="70"/>
+      <c r="AK37" s="70"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="69"/>
-      <c r="C38" s="78" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="72"/>
-      <c r="E38" s="72"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="73"/>
-      <c r="H38" s="71"/>
-      <c r="I38" s="72"/>
-      <c r="J38" s="72"/>
-      <c r="K38" s="72"/>
-      <c r="L38" s="56"/>
-      <c r="M38" s="72"/>
-      <c r="N38" s="73"/>
-      <c r="O38" s="55"/>
-      <c r="P38" s="66"/>
-      <c r="Q38" s="66"/>
-      <c r="R38" s="66"/>
-      <c r="S38" s="66"/>
-      <c r="T38" s="66"/>
-      <c r="U38" s="66"/>
-      <c r="V38" s="54"/>
-      <c r="W38" s="59"/>
-      <c r="X38" s="66"/>
-      <c r="Y38" s="66"/>
-      <c r="Z38" s="73"/>
-      <c r="AA38" s="71"/>
-      <c r="AB38" s="72"/>
-      <c r="AC38" s="72"/>
-      <c r="AD38" s="56"/>
-      <c r="AE38" s="73"/>
-      <c r="AF38" s="71"/>
-      <c r="AG38" s="72"/>
-      <c r="AH38" s="72"/>
-      <c r="AI38" s="72"/>
-      <c r="AJ38" s="72"/>
-      <c r="AK38" s="72"/>
+      <c r="B38" s="67"/>
+      <c r="C38" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="53"/>
+      <c r="P38" s="64"/>
+      <c r="Q38" s="64"/>
+      <c r="R38" s="64"/>
+      <c r="S38" s="64"/>
+      <c r="T38" s="64"/>
+      <c r="U38" s="64"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="57"/>
+      <c r="X38" s="64"/>
+      <c r="Y38" s="64"/>
+      <c r="Z38" s="71"/>
+      <c r="AA38" s="69"/>
+      <c r="AB38" s="70"/>
+      <c r="AC38" s="70"/>
+      <c r="AD38" s="54"/>
+      <c r="AE38" s="71"/>
+      <c r="AF38" s="69"/>
+      <c r="AG38" s="70"/>
+      <c r="AH38" s="70"/>
+      <c r="AI38" s="70"/>
+      <c r="AJ38" s="70"/>
+      <c r="AK38" s="70"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="69"/>
-      <c r="C39" s="78"/>
-      <c r="D39" s="72"/>
-      <c r="E39" s="72"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="72"/>
-      <c r="J39" s="72"/>
-      <c r="K39" s="72"/>
-      <c r="L39" s="56"/>
-      <c r="M39" s="72"/>
-      <c r="N39" s="73"/>
-      <c r="O39" s="71"/>
-      <c r="P39" s="72"/>
-      <c r="Q39" s="72"/>
-      <c r="R39" s="79"/>
-      <c r="S39" s="79"/>
-      <c r="T39" s="72"/>
-      <c r="U39" s="72"/>
-      <c r="V39" s="73"/>
-      <c r="W39" s="59"/>
-      <c r="X39" s="72"/>
-      <c r="Y39" s="72"/>
-      <c r="Z39" s="73"/>
-      <c r="AA39" s="71"/>
-      <c r="AB39" s="72"/>
-      <c r="AC39" s="72"/>
-      <c r="AD39" s="56"/>
-      <c r="AE39" s="73"/>
-      <c r="AF39" s="71"/>
-      <c r="AG39" s="72"/>
-      <c r="AH39" s="72"/>
-      <c r="AI39" s="72"/>
-      <c r="AJ39" s="72"/>
-      <c r="AK39" s="72"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="54"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="69"/>
+      <c r="P39" s="70"/>
+      <c r="Q39" s="70"/>
+      <c r="R39" s="77"/>
+      <c r="S39" s="77"/>
+      <c r="T39" s="70"/>
+      <c r="U39" s="70"/>
+      <c r="V39" s="71"/>
+      <c r="W39" s="57"/>
+      <c r="X39" s="70"/>
+      <c r="Y39" s="70"/>
+      <c r="Z39" s="71"/>
+      <c r="AA39" s="69"/>
+      <c r="AB39" s="70"/>
+      <c r="AC39" s="70"/>
+      <c r="AD39" s="54"/>
+      <c r="AE39" s="71"/>
+      <c r="AF39" s="69"/>
+      <c r="AG39" s="70"/>
+      <c r="AH39" s="70"/>
+      <c r="AI39" s="70"/>
+      <c r="AJ39" s="70"/>
+      <c r="AK39" s="70"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="69"/>
-      <c r="C40" s="78" t="s">
-        <v>158</v>
-      </c>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="75"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="72"/>
-      <c r="L40" s="56"/>
-      <c r="M40" s="72"/>
-      <c r="N40" s="73"/>
-      <c r="O40" s="71"/>
-      <c r="P40" s="72"/>
-      <c r="Q40" s="72"/>
-      <c r="R40" s="66"/>
-      <c r="S40" s="66"/>
-      <c r="T40" s="66"/>
-      <c r="U40" s="66"/>
-      <c r="V40" s="54"/>
-      <c r="W40" s="59"/>
-      <c r="X40" s="66"/>
-      <c r="Y40" s="66"/>
-      <c r="Z40" s="54"/>
-      <c r="AA40" s="55"/>
-      <c r="AB40" s="66"/>
-      <c r="AC40" s="66"/>
-      <c r="AD40" s="56"/>
-      <c r="AE40" s="73"/>
-      <c r="AF40" s="71"/>
-      <c r="AG40" s="72"/>
-      <c r="AH40" s="72"/>
-      <c r="AI40" s="72"/>
-      <c r="AJ40" s="72"/>
-      <c r="AK40" s="72"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="54"/>
+      <c r="M40" s="70"/>
+      <c r="N40" s="71"/>
+      <c r="O40" s="69"/>
+      <c r="P40" s="70"/>
+      <c r="Q40" s="70"/>
+      <c r="R40" s="64"/>
+      <c r="S40" s="64"/>
+      <c r="T40" s="64"/>
+      <c r="U40" s="64"/>
+      <c r="V40" s="52"/>
+      <c r="W40" s="57"/>
+      <c r="X40" s="64"/>
+      <c r="Y40" s="64"/>
+      <c r="Z40" s="52"/>
+      <c r="AA40" s="53"/>
+      <c r="AB40" s="64"/>
+      <c r="AC40" s="64"/>
+      <c r="AD40" s="54"/>
+      <c r="AE40" s="71"/>
+      <c r="AF40" s="69"/>
+      <c r="AG40" s="70"/>
+      <c r="AH40" s="70"/>
+      <c r="AI40" s="70"/>
+      <c r="AJ40" s="70"/>
+      <c r="AK40" s="70"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="69"/>
-      <c r="C41" s="78"/>
-      <c r="D41" s="72"/>
-      <c r="E41" s="72"/>
-      <c r="F41" s="75"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="72"/>
-      <c r="J41" s="72"/>
-      <c r="K41" s="72"/>
-      <c r="L41" s="56"/>
-      <c r="M41" s="72"/>
-      <c r="N41" s="73"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="72"/>
-      <c r="Q41" s="65"/>
-      <c r="R41" s="79"/>
-      <c r="S41" s="79"/>
-      <c r="T41" s="65"/>
-      <c r="U41" s="72"/>
-      <c r="V41" s="73"/>
-      <c r="W41" s="59"/>
-      <c r="X41" s="72"/>
-      <c r="Y41" s="72"/>
-      <c r="Z41" s="73"/>
-      <c r="AA41" s="71"/>
-      <c r="AB41" s="72"/>
-      <c r="AC41" s="72"/>
-      <c r="AD41" s="56"/>
-      <c r="AE41" s="73"/>
-      <c r="AF41" s="71"/>
-      <c r="AG41" s="72"/>
-      <c r="AH41" s="72"/>
-      <c r="AI41" s="72"/>
-      <c r="AJ41" s="72"/>
-      <c r="AK41" s="72"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="54"/>
+      <c r="M41" s="70"/>
+      <c r="N41" s="71"/>
+      <c r="O41" s="69"/>
+      <c r="P41" s="70"/>
+      <c r="Q41" s="63"/>
+      <c r="R41" s="77"/>
+      <c r="S41" s="77"/>
+      <c r="T41" s="63"/>
+      <c r="U41" s="70"/>
+      <c r="V41" s="71"/>
+      <c r="W41" s="57"/>
+      <c r="X41" s="70"/>
+      <c r="Y41" s="70"/>
+      <c r="Z41" s="71"/>
+      <c r="AA41" s="69"/>
+      <c r="AB41" s="70"/>
+      <c r="AC41" s="70"/>
+      <c r="AD41" s="54"/>
+      <c r="AE41" s="71"/>
+      <c r="AF41" s="69"/>
+      <c r="AG41" s="70"/>
+      <c r="AH41" s="70"/>
+      <c r="AI41" s="70"/>
+      <c r="AJ41" s="70"/>
+      <c r="AK41" s="70"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="50" t="s">
+      <c r="B42" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="81" t="s">
-        <v>159</v>
-      </c>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="56"/>
-      <c r="M42" s="52"/>
-      <c r="N42" s="57"/>
-      <c r="O42" s="58"/>
-      <c r="P42" s="66"/>
-      <c r="Q42" s="66"/>
-      <c r="R42" s="52"/>
-      <c r="S42" s="52"/>
-      <c r="T42" s="65"/>
-      <c r="U42" s="52"/>
-      <c r="V42" s="54"/>
-      <c r="W42" s="59"/>
-      <c r="X42" s="66"/>
-      <c r="Y42" s="66"/>
-      <c r="Z42" s="54"/>
-      <c r="AA42" s="55"/>
-      <c r="AB42" s="66"/>
-      <c r="AC42" s="66"/>
-      <c r="AD42" s="56"/>
-      <c r="AE42" s="57"/>
-      <c r="AF42" s="58"/>
-      <c r="AG42" s="52"/>
-      <c r="AH42" s="52"/>
-      <c r="AI42" s="52"/>
-      <c r="AJ42" s="52"/>
-      <c r="AK42" s="52"/>
+      <c r="C42" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="50"/>
+      <c r="J42" s="50"/>
+      <c r="K42" s="50"/>
+      <c r="L42" s="54"/>
+      <c r="M42" s="50"/>
+      <c r="N42" s="55"/>
+      <c r="O42" s="56"/>
+      <c r="P42" s="64"/>
+      <c r="Q42" s="64"/>
+      <c r="R42" s="50"/>
+      <c r="S42" s="50"/>
+      <c r="T42" s="63"/>
+      <c r="U42" s="50"/>
+      <c r="V42" s="52"/>
+      <c r="W42" s="57"/>
+      <c r="X42" s="64"/>
+      <c r="Y42" s="64"/>
+      <c r="Z42" s="52"/>
+      <c r="AA42" s="53"/>
+      <c r="AB42" s="64"/>
+      <c r="AC42" s="64"/>
+      <c r="AD42" s="54"/>
+      <c r="AE42" s="55"/>
+      <c r="AF42" s="56"/>
+      <c r="AG42" s="50"/>
+      <c r="AH42" s="50"/>
+      <c r="AI42" s="50"/>
+      <c r="AJ42" s="50"/>
+      <c r="AK42" s="50"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="50"/>
-      <c r="C43" s="81"/>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="60"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="52"/>
-      <c r="K43" s="52"/>
-      <c r="L43" s="56"/>
-      <c r="M43" s="52"/>
-      <c r="N43" s="57"/>
-      <c r="O43" s="58"/>
-      <c r="P43" s="52"/>
-      <c r="Q43" s="65"/>
-      <c r="R43" s="52"/>
-      <c r="S43" s="67"/>
-      <c r="T43" s="52"/>
-      <c r="U43" s="52"/>
-      <c r="V43" s="57"/>
-      <c r="W43" s="59"/>
-      <c r="X43" s="52"/>
-      <c r="Y43" s="52"/>
-      <c r="Z43" s="57"/>
-      <c r="AA43" s="58"/>
-      <c r="AB43" s="52"/>
-      <c r="AC43" s="52"/>
-      <c r="AD43" s="56"/>
-      <c r="AE43" s="57"/>
-      <c r="AF43" s="58"/>
-      <c r="AG43" s="52"/>
-      <c r="AH43" s="52"/>
-      <c r="AI43" s="52"/>
-      <c r="AJ43" s="52"/>
-      <c r="AK43" s="52"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="79"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="50"/>
+      <c r="L43" s="54"/>
+      <c r="M43" s="50"/>
+      <c r="N43" s="55"/>
+      <c r="O43" s="56"/>
+      <c r="P43" s="50"/>
+      <c r="Q43" s="63"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="65"/>
+      <c r="T43" s="50"/>
+      <c r="U43" s="50"/>
+      <c r="V43" s="55"/>
+      <c r="W43" s="57"/>
+      <c r="X43" s="50"/>
+      <c r="Y43" s="50"/>
+      <c r="Z43" s="55"/>
+      <c r="AA43" s="56"/>
+      <c r="AB43" s="50"/>
+      <c r="AC43" s="50"/>
+      <c r="AD43" s="54"/>
+      <c r="AE43" s="55"/>
+      <c r="AF43" s="56"/>
+      <c r="AG43" s="50"/>
+      <c r="AH43" s="50"/>
+      <c r="AI43" s="50"/>
+      <c r="AJ43" s="50"/>
+      <c r="AK43" s="50"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="50"/>
-      <c r="C44" s="81" t="s">
-        <v>160</v>
-      </c>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="60"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="56"/>
-      <c r="M44" s="52"/>
-      <c r="N44" s="57"/>
-      <c r="O44" s="58"/>
-      <c r="P44" s="66"/>
-      <c r="Q44" s="66"/>
-      <c r="R44" s="52"/>
-      <c r="S44" s="52"/>
-      <c r="T44" s="52"/>
-      <c r="U44" s="52"/>
-      <c r="V44" s="57"/>
-      <c r="W44" s="59"/>
-      <c r="X44" s="66"/>
-      <c r="Y44" s="66"/>
-      <c r="Z44" s="57"/>
-      <c r="AA44" s="58"/>
-      <c r="AB44" s="52"/>
-      <c r="AC44" s="66"/>
-      <c r="AD44" s="56"/>
-      <c r="AE44" s="54"/>
-      <c r="AF44" s="55"/>
-      <c r="AG44" s="52"/>
-      <c r="AH44" s="52"/>
-      <c r="AI44" s="66"/>
-      <c r="AJ44" s="52"/>
-      <c r="AK44" s="52"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
+      <c r="L44" s="54"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="55"/>
+      <c r="O44" s="56"/>
+      <c r="P44" s="64"/>
+      <c r="Q44" s="64"/>
+      <c r="R44" s="50"/>
+      <c r="S44" s="50"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="55"/>
+      <c r="W44" s="57"/>
+      <c r="X44" s="64"/>
+      <c r="Y44" s="64"/>
+      <c r="Z44" s="55"/>
+      <c r="AA44" s="56"/>
+      <c r="AB44" s="50"/>
+      <c r="AC44" s="64"/>
+      <c r="AD44" s="54"/>
+      <c r="AE44" s="52"/>
+      <c r="AF44" s="53"/>
+      <c r="AG44" s="50"/>
+      <c r="AH44" s="50"/>
+      <c r="AI44" s="64"/>
+      <c r="AJ44" s="50"/>
+      <c r="AK44" s="50"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="50"/>
-      <c r="C45" s="81"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="60"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="52"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="56"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="57"/>
-      <c r="O45" s="58"/>
-      <c r="P45" s="52"/>
-      <c r="Q45" s="52"/>
-      <c r="R45" s="52"/>
-      <c r="S45" s="52"/>
-      <c r="T45" s="52"/>
-      <c r="U45" s="52"/>
-      <c r="V45" s="57"/>
-      <c r="W45" s="59"/>
-      <c r="X45" s="52"/>
-      <c r="Y45" s="65"/>
-      <c r="Z45" s="82"/>
-      <c r="AA45" s="58"/>
-      <c r="AB45" s="52"/>
-      <c r="AC45" s="52"/>
-      <c r="AD45" s="56"/>
-      <c r="AE45" s="57"/>
-      <c r="AF45" s="58"/>
-      <c r="AG45" s="52"/>
-      <c r="AH45" s="52"/>
-      <c r="AI45" s="52"/>
-      <c r="AJ45" s="52"/>
-      <c r="AK45" s="52"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="79"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="50"/>
+      <c r="J45" s="50"/>
+      <c r="K45" s="50"/>
+      <c r="L45" s="54"/>
+      <c r="M45" s="50"/>
+      <c r="N45" s="55"/>
+      <c r="O45" s="56"/>
+      <c r="P45" s="50"/>
+      <c r="Q45" s="50"/>
+      <c r="R45" s="50"/>
+      <c r="S45" s="50"/>
+      <c r="T45" s="50"/>
+      <c r="U45" s="50"/>
+      <c r="V45" s="55"/>
+      <c r="W45" s="57"/>
+      <c r="X45" s="50"/>
+      <c r="Y45" s="63"/>
+      <c r="Z45" s="80"/>
+      <c r="AA45" s="56"/>
+      <c r="AB45" s="50"/>
+      <c r="AC45" s="50"/>
+      <c r="AD45" s="54"/>
+      <c r="AE45" s="55"/>
+      <c r="AF45" s="56"/>
+      <c r="AG45" s="50"/>
+      <c r="AH45" s="50"/>
+      <c r="AI45" s="50"/>
+      <c r="AJ45" s="50"/>
+      <c r="AK45" s="50"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="69" t="s">
-        <v>161</v>
-      </c>
-      <c r="C46" s="70" t="s">
+      <c r="B46" s="67" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="72"/>
-      <c r="E46" s="72"/>
-      <c r="F46" s="75"/>
-      <c r="G46" s="73"/>
-      <c r="H46" s="71"/>
-      <c r="I46" s="72"/>
-      <c r="J46" s="72"/>
-      <c r="K46" s="72"/>
-      <c r="L46" s="56"/>
-      <c r="M46" s="72"/>
-      <c r="N46" s="73"/>
-      <c r="O46" s="71"/>
-      <c r="P46" s="72"/>
-      <c r="Q46" s="72"/>
-      <c r="R46" s="72"/>
-      <c r="S46" s="72"/>
-      <c r="T46" s="72"/>
-      <c r="U46" s="72"/>
-      <c r="V46" s="73"/>
-      <c r="W46" s="59"/>
-      <c r="X46" s="72"/>
-      <c r="Y46" s="72"/>
-      <c r="Z46" s="73"/>
-      <c r="AA46" s="71"/>
-      <c r="AB46" s="72"/>
-      <c r="AC46" s="72"/>
-      <c r="AD46" s="56"/>
-      <c r="AE46" s="73"/>
-      <c r="AF46" s="71"/>
-      <c r="AG46" s="72"/>
-      <c r="AH46" s="72"/>
-      <c r="AI46" s="72"/>
-      <c r="AJ46" s="66"/>
-      <c r="AK46" s="72"/>
+      <c r="D46" s="70"/>
+      <c r="E46" s="70"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="70"/>
+      <c r="J46" s="70"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="54"/>
+      <c r="M46" s="70"/>
+      <c r="N46" s="71"/>
+      <c r="O46" s="69"/>
+      <c r="P46" s="70"/>
+      <c r="Q46" s="70"/>
+      <c r="R46" s="70"/>
+      <c r="S46" s="70"/>
+      <c r="T46" s="70"/>
+      <c r="U46" s="70"/>
+      <c r="V46" s="71"/>
+      <c r="W46" s="57"/>
+      <c r="X46" s="70"/>
+      <c r="Y46" s="70"/>
+      <c r="Z46" s="71"/>
+      <c r="AA46" s="69"/>
+      <c r="AB46" s="70"/>
+      <c r="AC46" s="70"/>
+      <c r="AD46" s="54"/>
+      <c r="AE46" s="71"/>
+      <c r="AF46" s="69"/>
+      <c r="AG46" s="70"/>
+      <c r="AH46" s="70"/>
+      <c r="AI46" s="70"/>
+      <c r="AJ46" s="64"/>
+      <c r="AK46" s="70"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="69"/>
-      <c r="C47" s="70"/>
-      <c r="D47" s="72"/>
-      <c r="E47" s="72"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="73"/>
-      <c r="H47" s="71"/>
-      <c r="I47" s="72"/>
-      <c r="J47" s="72"/>
-      <c r="K47" s="72"/>
-      <c r="L47" s="56"/>
-      <c r="M47" s="72"/>
-      <c r="N47" s="73"/>
-      <c r="O47" s="71"/>
-      <c r="P47" s="72"/>
-      <c r="Q47" s="72"/>
-      <c r="R47" s="72"/>
-      <c r="S47" s="72"/>
-      <c r="T47" s="72"/>
-      <c r="U47" s="72"/>
-      <c r="V47" s="73"/>
-      <c r="W47" s="59"/>
-      <c r="X47" s="72"/>
-      <c r="Y47" s="72"/>
-      <c r="Z47" s="73"/>
-      <c r="AA47" s="71"/>
-      <c r="AB47" s="72"/>
-      <c r="AC47" s="72"/>
-      <c r="AD47" s="56"/>
-      <c r="AE47" s="73"/>
-      <c r="AF47" s="71"/>
-      <c r="AG47" s="72"/>
-      <c r="AH47" s="72"/>
-      <c r="AI47" s="72"/>
-      <c r="AJ47" s="72"/>
-      <c r="AK47" s="72"/>
-      <c r="AN47" s="83" t="s">
-        <v>162</v>
-      </c>
-      <c r="AO47" s="66"/>
+      <c r="B47" s="67"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="70"/>
+      <c r="E47" s="70"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="71"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="70"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="54"/>
+      <c r="M47" s="70"/>
+      <c r="N47" s="71"/>
+      <c r="O47" s="69"/>
+      <c r="P47" s="70"/>
+      <c r="Q47" s="70"/>
+      <c r="R47" s="70"/>
+      <c r="S47" s="70"/>
+      <c r="T47" s="70"/>
+      <c r="U47" s="70"/>
+      <c r="V47" s="71"/>
+      <c r="W47" s="57"/>
+      <c r="X47" s="70"/>
+      <c r="Y47" s="70"/>
+      <c r="Z47" s="71"/>
+      <c r="AA47" s="69"/>
+      <c r="AB47" s="70"/>
+      <c r="AC47" s="70"/>
+      <c r="AD47" s="54"/>
+      <c r="AE47" s="71"/>
+      <c r="AF47" s="69"/>
+      <c r="AG47" s="70"/>
+      <c r="AH47" s="70"/>
+      <c r="AI47" s="70"/>
+      <c r="AJ47" s="70"/>
+      <c r="AK47" s="70"/>
+      <c r="AN47" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="AO47" s="64"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="69"/>
-      <c r="C48" s="70" t="s">
-        <v>163</v>
-      </c>
-      <c r="D48" s="72"/>
-      <c r="E48" s="72"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="71"/>
-      <c r="I48" s="72"/>
-      <c r="J48" s="72"/>
-      <c r="K48" s="72"/>
-      <c r="L48" s="56"/>
-      <c r="M48" s="72"/>
-      <c r="N48" s="73"/>
-      <c r="O48" s="71"/>
-      <c r="P48" s="72"/>
-      <c r="Q48" s="72"/>
-      <c r="R48" s="72"/>
-      <c r="S48" s="72"/>
-      <c r="T48" s="72"/>
-      <c r="U48" s="72"/>
-      <c r="V48" s="73"/>
-      <c r="W48" s="59"/>
-      <c r="X48" s="72"/>
-      <c r="Y48" s="72"/>
-      <c r="Z48" s="73"/>
-      <c r="AA48" s="71"/>
-      <c r="AB48" s="72"/>
-      <c r="AC48" s="72"/>
-      <c r="AD48" s="56"/>
-      <c r="AE48" s="73"/>
-      <c r="AF48" s="71"/>
-      <c r="AG48" s="72"/>
-      <c r="AH48" s="72"/>
-      <c r="AI48" s="72"/>
-      <c r="AJ48" s="72"/>
-      <c r="AK48" s="84"/>
-      <c r="AN48" s="83" t="s">
+      <c r="B48" s="67"/>
+      <c r="C48" s="68" t="s">
         <v>164</v>
       </c>
-      <c r="AO48" s="65"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="71"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="70"/>
+      <c r="K48" s="70"/>
+      <c r="L48" s="54"/>
+      <c r="M48" s="70"/>
+      <c r="N48" s="71"/>
+      <c r="O48" s="69"/>
+      <c r="P48" s="70"/>
+      <c r="Q48" s="70"/>
+      <c r="R48" s="70"/>
+      <c r="S48" s="70"/>
+      <c r="T48" s="70"/>
+      <c r="U48" s="70"/>
+      <c r="V48" s="71"/>
+      <c r="W48" s="57"/>
+      <c r="X48" s="70"/>
+      <c r="Y48" s="70"/>
+      <c r="Z48" s="71"/>
+      <c r="AA48" s="69"/>
+      <c r="AB48" s="70"/>
+      <c r="AC48" s="70"/>
+      <c r="AD48" s="54"/>
+      <c r="AE48" s="71"/>
+      <c r="AF48" s="69"/>
+      <c r="AG48" s="70"/>
+      <c r="AH48" s="70"/>
+      <c r="AI48" s="70"/>
+      <c r="AJ48" s="70"/>
+      <c r="AK48" s="82"/>
+      <c r="AN48" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO48" s="63"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="69"/>
-      <c r="C49" s="70"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="72"/>
-      <c r="F49" s="75"/>
-      <c r="G49" s="73"/>
-      <c r="H49" s="71"/>
-      <c r="I49" s="72"/>
-      <c r="J49" s="72"/>
-      <c r="K49" s="72"/>
-      <c r="L49" s="56"/>
-      <c r="M49" s="72"/>
-      <c r="N49" s="73"/>
-      <c r="O49" s="71"/>
-      <c r="P49" s="72"/>
-      <c r="Q49" s="72"/>
-      <c r="R49" s="72"/>
-      <c r="S49" s="72"/>
-      <c r="T49" s="72"/>
-      <c r="U49" s="72"/>
-      <c r="V49" s="73"/>
-      <c r="W49" s="59"/>
-      <c r="X49" s="72"/>
-      <c r="Y49" s="72"/>
-      <c r="Z49" s="73"/>
-      <c r="AA49" s="71"/>
-      <c r="AB49" s="72"/>
-      <c r="AC49" s="72"/>
-      <c r="AD49" s="56"/>
-      <c r="AE49" s="73"/>
-      <c r="AF49" s="71"/>
-      <c r="AG49" s="72"/>
-      <c r="AH49" s="72"/>
-      <c r="AI49" s="72"/>
-      <c r="AJ49" s="72"/>
-      <c r="AK49" s="72"/>
-      <c r="AN49" s="83" t="s">
-        <v>165</v>
-      </c>
-      <c r="AO49" s="61"/>
+      <c r="B49" s="67"/>
+      <c r="C49" s="68"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="70"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="71"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="70"/>
+      <c r="J49" s="70"/>
+      <c r="K49" s="70"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="70"/>
+      <c r="N49" s="71"/>
+      <c r="O49" s="69"/>
+      <c r="P49" s="70"/>
+      <c r="Q49" s="70"/>
+      <c r="R49" s="70"/>
+      <c r="S49" s="70"/>
+      <c r="T49" s="70"/>
+      <c r="U49" s="70"/>
+      <c r="V49" s="71"/>
+      <c r="W49" s="57"/>
+      <c r="X49" s="70"/>
+      <c r="Y49" s="70"/>
+      <c r="Z49" s="71"/>
+      <c r="AA49" s="69"/>
+      <c r="AB49" s="70"/>
+      <c r="AC49" s="70"/>
+      <c r="AD49" s="54"/>
+      <c r="AE49" s="71"/>
+      <c r="AF49" s="69"/>
+      <c r="AG49" s="70"/>
+      <c r="AH49" s="70"/>
+      <c r="AI49" s="70"/>
+      <c r="AJ49" s="70"/>
+      <c r="AK49" s="70"/>
+      <c r="AN49" s="81" t="s">
+        <v>166</v>
+      </c>
+      <c r="AO49" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -11027,801 +11032,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="85"/>
+      <c r="B1" s="83"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="86" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="87" t="s">
+      <c r="B2" s="84" t="s">
         <v>111</v>
       </c>
-      <c r="D2" s="88" t="s">
-        <v>166</v>
-      </c>
-      <c r="E2" s="89" t="s">
+      <c r="C2" s="85" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="F2" s="90" t="s">
+      <c r="E2" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="90" t="s">
+      <c r="F2" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="90" t="s">
-        <v>104</v>
-      </c>
-      <c r="O2" s="90"/>
-      <c r="P2" s="90"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="90" t="s">
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="87"/>
+      <c r="J2" s="88" t="s">
+        <v>170</v>
+      </c>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="S2" s="91"/>
-      <c r="AD2" s="92"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="87"/>
+      <c r="R2" s="88" t="s">
+        <v>106</v>
+      </c>
+      <c r="S2" s="89"/>
+      <c r="AD2" s="90"/>
     </row>
     <row r="3">
-      <c r="B3" s="93"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="95" t="s">
-        <v>170</v>
-      </c>
-      <c r="E3" s="96">
+      <c r="B3" s="91"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="93" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" s="94">
         <v>4</v>
       </c>
-      <c r="F3" s="97">
+      <c r="F3" s="95">
         <v>1</v>
       </c>
-      <c r="G3" s="98">
+      <c r="G3" s="96">
         <v>2</v>
       </c>
-      <c r="H3" s="98">
+      <c r="H3" s="96">
         <v>3</v>
       </c>
-      <c r="I3" s="96">
+      <c r="I3" s="94">
         <v>4</v>
       </c>
-      <c r="J3" s="97">
+      <c r="J3" s="95">
         <v>1</v>
       </c>
-      <c r="K3" s="98">
+      <c r="K3" s="96">
         <v>2</v>
       </c>
-      <c r="L3" s="98">
+      <c r="L3" s="96">
         <v>3</v>
       </c>
-      <c r="M3" s="96">
+      <c r="M3" s="94">
         <v>4</v>
       </c>
-      <c r="N3" s="97">
+      <c r="N3" s="95">
         <v>1</v>
       </c>
-      <c r="O3" s="98">
+      <c r="O3" s="96">
         <v>2</v>
       </c>
-      <c r="P3" s="98">
+      <c r="P3" s="96">
         <v>3</v>
       </c>
-      <c r="Q3" s="96">
+      <c r="Q3" s="94">
         <v>4</v>
       </c>
-      <c r="R3" s="97">
+      <c r="R3" s="95">
         <v>1</v>
       </c>
-      <c r="S3" s="99">
+      <c r="S3" s="97">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="100" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="87" t="s">
+      <c r="B4" s="98" t="s">
         <v>173</v>
       </c>
-      <c r="D4" s="101"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="105"/>
-      <c r="O4" s="104"/>
-      <c r="P4" s="104"/>
-      <c r="Q4" s="102"/>
-      <c r="R4" s="105"/>
-      <c r="S4" s="106"/>
+      <c r="C4" s="85" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="99"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="100"/>
+      <c r="R4" s="103"/>
+      <c r="S4" s="104"/>
       <c r="U4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="100"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="109"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="112"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="112"/>
-      <c r="M5" s="109"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="112"/>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="109"/>
-      <c r="R5" s="113"/>
-      <c r="S5" s="114"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="110"/>
+      <c r="L5" s="110"/>
+      <c r="M5" s="107"/>
+      <c r="N5" s="111"/>
+      <c r="O5" s="110"/>
+      <c r="P5" s="110"/>
+      <c r="Q5" s="107"/>
+      <c r="R5" s="111"/>
+      <c r="S5" s="112"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="100"/>
-      <c r="C6" s="115" t="s">
-        <v>175</v>
-      </c>
-      <c r="D6" s="116"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="121"/>
-      <c r="K6" s="120"/>
-      <c r="L6" s="120"/>
-      <c r="M6" s="117"/>
-      <c r="N6" s="121"/>
-      <c r="O6" s="120"/>
-      <c r="P6" s="120"/>
-      <c r="Q6" s="117"/>
-      <c r="R6" s="121"/>
-      <c r="S6" s="122"/>
-      <c r="U6" s="123" t="s">
+      <c r="B6" s="98"/>
+      <c r="C6" s="113" t="s">
         <v>176</v>
       </c>
-      <c r="V6" s="123"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="119"/>
+      <c r="K6" s="118"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="115"/>
+      <c r="N6" s="119"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="119"/>
+      <c r="S6" s="120"/>
+      <c r="U6" s="121" t="s">
+        <v>177</v>
+      </c>
+      <c r="V6" s="121"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="100"/>
-      <c r="C7" s="107"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="113"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="113"/>
-      <c r="K7" s="112"/>
-      <c r="L7" s="112"/>
-      <c r="M7" s="109"/>
-      <c r="N7" s="113"/>
-      <c r="O7" s="112"/>
-      <c r="P7" s="112"/>
-      <c r="Q7" s="109"/>
-      <c r="R7" s="113"/>
-      <c r="S7" s="114"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="111"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="111"/>
+      <c r="S7" s="112"/>
       <c r="U7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="100"/>
-      <c r="C8" s="115" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="116"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="117"/>
-      <c r="J8" s="121"/>
-      <c r="K8" s="120"/>
-      <c r="L8" s="120"/>
-      <c r="M8" s="117"/>
-      <c r="N8" s="121"/>
-      <c r="O8" s="120"/>
-      <c r="P8" s="120"/>
-      <c r="Q8" s="117"/>
-      <c r="R8" s="121"/>
-      <c r="S8" s="122"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="113" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="114"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="115"/>
+      <c r="J8" s="119"/>
+      <c r="K8" s="118"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="115"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="118"/>
+      <c r="P8" s="118"/>
+      <c r="Q8" s="115"/>
+      <c r="R8" s="119"/>
+      <c r="S8" s="120"/>
       <c r="U8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="100"/>
-      <c r="C9" s="107"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="109"/>
-      <c r="F9" s="113"/>
-      <c r="G9" s="111"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="109"/>
-      <c r="J9" s="113"/>
-      <c r="K9" s="112"/>
-      <c r="L9" s="112"/>
-      <c r="M9" s="109"/>
-      <c r="N9" s="113"/>
-      <c r="O9" s="112"/>
-      <c r="P9" s="112"/>
-      <c r="Q9" s="109"/>
-      <c r="R9" s="113"/>
-      <c r="S9" s="114"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="109"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="110"/>
+      <c r="L9" s="110"/>
+      <c r="M9" s="107"/>
+      <c r="N9" s="111"/>
+      <c r="O9" s="110"/>
+      <c r="P9" s="110"/>
+      <c r="Q9" s="107"/>
+      <c r="R9" s="111"/>
+      <c r="S9" s="112"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="100"/>
-      <c r="C10" s="115" t="s">
-        <v>180</v>
-      </c>
-      <c r="D10" s="116"/>
-      <c r="E10" s="117"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="119"/>
-      <c r="H10" s="119"/>
-      <c r="I10" s="117"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="120"/>
-      <c r="L10" s="120"/>
-      <c r="M10" s="117"/>
-      <c r="N10" s="121"/>
-      <c r="O10" s="120"/>
-      <c r="P10" s="120"/>
-      <c r="Q10" s="117"/>
-      <c r="R10" s="121"/>
-      <c r="S10" s="122"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="113" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" s="114"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="118"/>
+      <c r="L10" s="118"/>
+      <c r="M10" s="115"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="118"/>
+      <c r="P10" s="118"/>
+      <c r="Q10" s="115"/>
+      <c r="R10" s="119"/>
+      <c r="S10" s="120"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="124"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="126"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="128"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="127"/>
-      <c r="N11" s="128"/>
-      <c r="O11" s="130"/>
-      <c r="P11" s="130"/>
-      <c r="Q11" s="127"/>
-      <c r="R11" s="128"/>
-      <c r="S11" s="131"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="126"/>
+      <c r="K11" s="128"/>
+      <c r="L11" s="128"/>
+      <c r="M11" s="125"/>
+      <c r="N11" s="126"/>
+      <c r="O11" s="128"/>
+      <c r="P11" s="128"/>
+      <c r="Q11" s="125"/>
+      <c r="R11" s="126"/>
+      <c r="S11" s="129"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="86" t="s">
-        <v>181</v>
-      </c>
-      <c r="C12" s="87" t="s">
+      <c r="B12" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="D12" s="101"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="105"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="132"/>
-      <c r="I12" s="133"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="104"/>
-      <c r="M12" s="102"/>
-      <c r="N12" s="105"/>
-      <c r="O12" s="104"/>
-      <c r="P12" s="104"/>
-      <c r="Q12" s="102"/>
-      <c r="R12" s="105"/>
-      <c r="S12" s="106"/>
+      <c r="C12" s="85" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="99"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="102"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="100"/>
+      <c r="N12" s="103"/>
+      <c r="O12" s="102"/>
+      <c r="P12" s="102"/>
+      <c r="Q12" s="100"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="104"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="100"/>
-      <c r="C13" s="107"/>
-      <c r="D13" s="108"/>
-      <c r="E13" s="109"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="112"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="112"/>
-      <c r="L13" s="112"/>
-      <c r="M13" s="109"/>
-      <c r="N13" s="113"/>
-      <c r="O13" s="112"/>
-      <c r="P13" s="112"/>
-      <c r="Q13" s="109"/>
-      <c r="R13" s="113"/>
-      <c r="S13" s="114"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="107"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="110"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="108"/>
+      <c r="K13" s="110"/>
+      <c r="L13" s="110"/>
+      <c r="M13" s="107"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="110"/>
+      <c r="P13" s="110"/>
+      <c r="Q13" s="107"/>
+      <c r="R13" s="111"/>
+      <c r="S13" s="112"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="100"/>
-      <c r="C14" s="115" t="s">
-        <v>183</v>
-      </c>
-      <c r="D14" s="134"/>
-      <c r="E14" s="117"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="121"/>
-      <c r="K14" s="120"/>
-      <c r="L14" s="120"/>
-      <c r="M14" s="117"/>
-      <c r="N14" s="121"/>
-      <c r="O14" s="120"/>
-      <c r="P14" s="120"/>
-      <c r="Q14" s="117"/>
-      <c r="R14" s="121"/>
-      <c r="S14" s="122"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="113" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="132"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="118"/>
+      <c r="L14" s="118"/>
+      <c r="M14" s="115"/>
+      <c r="N14" s="119"/>
+      <c r="O14" s="118"/>
+      <c r="P14" s="118"/>
+      <c r="Q14" s="115"/>
+      <c r="R14" s="119"/>
+      <c r="S14" s="120"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="100"/>
-      <c r="C15" s="107"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="113"/>
-      <c r="G15" s="112"/>
-      <c r="H15" s="112"/>
-      <c r="I15" s="135"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="112"/>
-      <c r="L15" s="112"/>
-      <c r="M15" s="109"/>
-      <c r="N15" s="113"/>
-      <c r="O15" s="112"/>
-      <c r="P15" s="112"/>
-      <c r="Q15" s="109"/>
-      <c r="R15" s="113"/>
-      <c r="S15" s="114"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="106"/>
+      <c r="E15" s="107"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="108"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="110"/>
+      <c r="M15" s="107"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="110"/>
+      <c r="P15" s="110"/>
+      <c r="Q15" s="107"/>
+      <c r="R15" s="111"/>
+      <c r="S15" s="112"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="100"/>
-      <c r="C16" s="115" t="s">
-        <v>184</v>
-      </c>
-      <c r="D16" s="116"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="121"/>
-      <c r="G16" s="120"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="136"/>
-      <c r="J16" s="121"/>
-      <c r="K16" s="120"/>
-      <c r="L16" s="120"/>
-      <c r="M16" s="117"/>
-      <c r="N16" s="121"/>
-      <c r="O16" s="120"/>
-      <c r="P16" s="120"/>
-      <c r="Q16" s="117"/>
-      <c r="R16" s="121"/>
-      <c r="S16" s="122"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="113" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="114"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="117"/>
+      <c r="I16" s="134"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118"/>
+      <c r="M16" s="115"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="118"/>
+      <c r="P16" s="118"/>
+      <c r="Q16" s="115"/>
+      <c r="R16" s="119"/>
+      <c r="S16" s="120"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="124"/>
-      <c r="C17" s="125"/>
-      <c r="D17" s="126"/>
-      <c r="E17" s="127"/>
-      <c r="F17" s="128"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="137"/>
-      <c r="K17" s="129"/>
-      <c r="L17" s="130"/>
-      <c r="M17" s="127"/>
-      <c r="N17" s="128"/>
-      <c r="O17" s="130"/>
-      <c r="P17" s="130"/>
-      <c r="Q17" s="127"/>
-      <c r="R17" s="128"/>
-      <c r="S17" s="131"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="123"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="125"/>
+      <c r="F17" s="126"/>
+      <c r="G17" s="128"/>
+      <c r="H17" s="128"/>
+      <c r="I17" s="125"/>
+      <c r="J17" s="135"/>
+      <c r="K17" s="127"/>
+      <c r="L17" s="128"/>
+      <c r="M17" s="125"/>
+      <c r="N17" s="126"/>
+      <c r="O17" s="128"/>
+      <c r="P17" s="128"/>
+      <c r="Q17" s="125"/>
+      <c r="R17" s="126"/>
+      <c r="S17" s="129"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="88" t="s">
-        <v>185</v>
-      </c>
-      <c r="C18" s="87" t="s">
+      <c r="B18" s="86" t="s">
         <v>186</v>
       </c>
-      <c r="D18" s="101"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="105"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="133"/>
-      <c r="J18" s="105"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="102"/>
-      <c r="N18" s="105"/>
-      <c r="O18" s="104"/>
-      <c r="P18" s="104"/>
-      <c r="Q18" s="102"/>
-      <c r="R18" s="105"/>
-      <c r="S18" s="106"/>
+      <c r="C18" s="85" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" s="99"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="102"/>
+      <c r="I18" s="131"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="102"/>
+      <c r="L18" s="102"/>
+      <c r="M18" s="100"/>
+      <c r="N18" s="103"/>
+      <c r="O18" s="102"/>
+      <c r="P18" s="102"/>
+      <c r="Q18" s="100"/>
+      <c r="R18" s="103"/>
+      <c r="S18" s="104"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="100"/>
-      <c r="C19" s="107"/>
-      <c r="D19" s="108"/>
-      <c r="E19" s="109"/>
-      <c r="F19" s="113"/>
-      <c r="G19" s="111"/>
-      <c r="H19" s="112"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="109"/>
-      <c r="N19" s="113"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="109"/>
-      <c r="R19" s="113"/>
-      <c r="S19" s="114"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="106"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="111"/>
+      <c r="G19" s="109"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="107"/>
+      <c r="J19" s="111"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110"/>
+      <c r="M19" s="107"/>
+      <c r="N19" s="111"/>
+      <c r="O19" s="110"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="107"/>
+      <c r="R19" s="111"/>
+      <c r="S19" s="112"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="100"/>
-      <c r="C20" s="115" t="s">
-        <v>187</v>
-      </c>
-      <c r="D20" s="116"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="121"/>
-      <c r="G20" s="120"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="136"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="119"/>
-      <c r="L20" s="119"/>
-      <c r="M20" s="117"/>
-      <c r="N20" s="121"/>
-      <c r="O20" s="120"/>
-      <c r="P20" s="120"/>
-      <c r="Q20" s="117"/>
-      <c r="R20" s="121"/>
-      <c r="S20" s="122"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="113" t="s">
+        <v>188</v>
+      </c>
+      <c r="D20" s="114"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="134"/>
+      <c r="J20" s="116"/>
+      <c r="K20" s="117"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="115"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="118"/>
+      <c r="P20" s="118"/>
+      <c r="Q20" s="115"/>
+      <c r="R20" s="119"/>
+      <c r="S20" s="120"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="100"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="108"/>
-      <c r="E21" s="109"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="112"/>
-      <c r="H21" s="112"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="112"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="138"/>
-      <c r="O21" s="112"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="113"/>
-      <c r="S21" s="114"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="106"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="111"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="111"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="110"/>
+      <c r="M21" s="107"/>
+      <c r="N21" s="136"/>
+      <c r="O21" s="110"/>
+      <c r="P21" s="110"/>
+      <c r="Q21" s="107"/>
+      <c r="R21" s="111"/>
+      <c r="S21" s="112"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="100"/>
-      <c r="C22" s="115" t="s">
-        <v>188</v>
-      </c>
-      <c r="D22" s="116"/>
-      <c r="E22" s="117"/>
-      <c r="F22" s="121"/>
-      <c r="G22" s="120"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="121"/>
-      <c r="K22" s="119"/>
-      <c r="L22" s="119"/>
-      <c r="M22" s="117"/>
-      <c r="N22" s="121"/>
-      <c r="O22" s="120"/>
-      <c r="P22" s="120"/>
-      <c r="Q22" s="117"/>
-      <c r="R22" s="121"/>
-      <c r="S22" s="122"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="113" t="s">
+        <v>189</v>
+      </c>
+      <c r="D22" s="114"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="118"/>
+      <c r="H22" s="118"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="117"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="115"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="118"/>
+      <c r="P22" s="118"/>
+      <c r="Q22" s="115"/>
+      <c r="R22" s="119"/>
+      <c r="S22" s="120"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="124"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="126"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="130"/>
-      <c r="H23" s="130"/>
-      <c r="I23" s="127"/>
-      <c r="J23" s="128"/>
-      <c r="K23" s="130"/>
-      <c r="L23" s="130"/>
-      <c r="M23" s="127"/>
-      <c r="N23" s="128"/>
-      <c r="O23" s="130"/>
-      <c r="P23" s="130"/>
-      <c r="Q23" s="127"/>
-      <c r="R23" s="128"/>
-      <c r="S23" s="131"/>
+      <c r="B23" s="122"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="126"/>
+      <c r="K23" s="128"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="125"/>
+      <c r="N23" s="126"/>
+      <c r="O23" s="128"/>
+      <c r="P23" s="128"/>
+      <c r="Q23" s="125"/>
+      <c r="R23" s="126"/>
+      <c r="S23" s="129"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="88" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="87" t="s">
+      <c r="B24" s="86" t="s">
         <v>190</v>
       </c>
-      <c r="D24" s="101"/>
-      <c r="E24" s="102"/>
-      <c r="F24" s="105"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="102"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="104"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="133"/>
-      <c r="N24" s="103"/>
-      <c r="O24" s="132"/>
-      <c r="P24" s="132"/>
-      <c r="Q24" s="102"/>
-      <c r="R24" s="105"/>
-      <c r="S24" s="106"/>
+      <c r="C24" s="85" t="s">
+        <v>191</v>
+      </c>
+      <c r="D24" s="99"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="102"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="103"/>
+      <c r="K24" s="102"/>
+      <c r="L24" s="102"/>
+      <c r="M24" s="131"/>
+      <c r="N24" s="101"/>
+      <c r="O24" s="130"/>
+      <c r="P24" s="130"/>
+      <c r="Q24" s="100"/>
+      <c r="R24" s="103"/>
+      <c r="S24" s="104"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="100"/>
-      <c r="C25" s="107"/>
-      <c r="D25" s="108"/>
-      <c r="E25" s="109"/>
-      <c r="F25" s="113"/>
-      <c r="G25" s="112"/>
-      <c r="H25" s="112"/>
-      <c r="I25" s="109"/>
-      <c r="J25" s="113"/>
-      <c r="K25" s="112"/>
-      <c r="L25" s="112"/>
-      <c r="M25" s="109"/>
-      <c r="N25" s="113"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="112"/>
-      <c r="Q25" s="109"/>
-      <c r="R25" s="113"/>
-      <c r="S25" s="114"/>
+      <c r="B25" s="98"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="106"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="110"/>
+      <c r="L25" s="110"/>
+      <c r="M25" s="107"/>
+      <c r="N25" s="111"/>
+      <c r="O25" s="110"/>
+      <c r="P25" s="110"/>
+      <c r="Q25" s="107"/>
+      <c r="R25" s="111"/>
+      <c r="S25" s="112"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="100"/>
-      <c r="C26" s="115" t="s">
-        <v>191</v>
-      </c>
-      <c r="D26" s="116"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="121"/>
-      <c r="G26" s="120"/>
-      <c r="H26" s="120"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="121"/>
-      <c r="K26" s="120"/>
-      <c r="L26" s="120"/>
-      <c r="M26" s="117"/>
-      <c r="N26" s="121"/>
-      <c r="O26" s="119"/>
-      <c r="P26" s="119"/>
-      <c r="Q26" s="117"/>
-      <c r="R26" s="121"/>
-      <c r="S26" s="122"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="113" t="s">
+        <v>192</v>
+      </c>
+      <c r="D26" s="114"/>
+      <c r="E26" s="115"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="118"/>
+      <c r="H26" s="118"/>
+      <c r="I26" s="115"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="118"/>
+      <c r="L26" s="118"/>
+      <c r="M26" s="115"/>
+      <c r="N26" s="119"/>
+      <c r="O26" s="117"/>
+      <c r="P26" s="117"/>
+      <c r="Q26" s="115"/>
+      <c r="R26" s="119"/>
+      <c r="S26" s="120"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="100"/>
-      <c r="C27" s="107"/>
-      <c r="D27" s="108"/>
-      <c r="E27" s="109"/>
-      <c r="F27" s="113"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="109"/>
-      <c r="J27" s="113"/>
-      <c r="K27" s="112"/>
-      <c r="L27" s="112"/>
-      <c r="M27" s="109"/>
-      <c r="N27" s="113"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="112"/>
-      <c r="Q27" s="109"/>
-      <c r="R27" s="113"/>
-      <c r="S27" s="114"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="106"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="107"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="110"/>
+      <c r="L27" s="110"/>
+      <c r="M27" s="107"/>
+      <c r="N27" s="111"/>
+      <c r="O27" s="110"/>
+      <c r="P27" s="110"/>
+      <c r="Q27" s="107"/>
+      <c r="R27" s="111"/>
+      <c r="S27" s="112"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="100"/>
-      <c r="C28" s="115" t="s">
-        <v>192</v>
-      </c>
-      <c r="D28" s="116"/>
-      <c r="E28" s="117"/>
-      <c r="F28" s="121"/>
-      <c r="G28" s="120"/>
-      <c r="H28" s="120"/>
-      <c r="I28" s="117"/>
-      <c r="J28" s="121"/>
-      <c r="K28" s="120"/>
-      <c r="L28" s="120"/>
-      <c r="M28" s="117"/>
-      <c r="N28" s="121"/>
-      <c r="O28" s="120"/>
-      <c r="P28" s="119"/>
-      <c r="Q28" s="136"/>
-      <c r="R28" s="121"/>
-      <c r="S28" s="122"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="113" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="114"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="118"/>
+      <c r="H28" s="118"/>
+      <c r="I28" s="115"/>
+      <c r="J28" s="119"/>
+      <c r="K28" s="118"/>
+      <c r="L28" s="118"/>
+      <c r="M28" s="115"/>
+      <c r="N28" s="119"/>
+      <c r="O28" s="118"/>
+      <c r="P28" s="117"/>
+      <c r="Q28" s="134"/>
+      <c r="R28" s="119"/>
+      <c r="S28" s="120"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="100"/>
-      <c r="C29" s="94"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="141"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="143"/>
-      <c r="I29" s="140"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="142"/>
-      <c r="L29" s="143"/>
-      <c r="M29" s="140"/>
-      <c r="N29" s="144"/>
-      <c r="O29" s="143"/>
-      <c r="P29" s="142"/>
-      <c r="Q29" s="140"/>
-      <c r="R29" s="141"/>
-      <c r="S29" s="145"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="92"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="140"/>
+      <c r="H29" s="141"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="139"/>
+      <c r="K29" s="140"/>
+      <c r="L29" s="141"/>
+      <c r="M29" s="138"/>
+      <c r="N29" s="142"/>
+      <c r="O29" s="141"/>
+      <c r="P29" s="140"/>
+      <c r="Q29" s="138"/>
+      <c r="R29" s="139"/>
+      <c r="S29" s="143"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="146" t="s">
+      <c r="B30" s="144" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="147" t="s">
-        <v>138</v>
-      </c>
-      <c r="D30" s="101"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="149"/>
-      <c r="G30" s="149"/>
-      <c r="H30" s="150"/>
-      <c r="I30" s="151"/>
-      <c r="J30" s="149"/>
-      <c r="K30" s="149"/>
-      <c r="L30" s="150"/>
-      <c r="M30" s="151"/>
-      <c r="N30" s="149"/>
-      <c r="O30" s="150"/>
-      <c r="P30" s="149"/>
-      <c r="Q30" s="151"/>
-      <c r="R30" s="149"/>
-      <c r="S30" s="152"/>
+      <c r="C30" s="145" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" s="99"/>
+      <c r="E30" s="146"/>
+      <c r="F30" s="147"/>
+      <c r="G30" s="147"/>
+      <c r="H30" s="148"/>
+      <c r="I30" s="149"/>
+      <c r="J30" s="147"/>
+      <c r="K30" s="147"/>
+      <c r="L30" s="148"/>
+      <c r="M30" s="149"/>
+      <c r="N30" s="147"/>
+      <c r="O30" s="148"/>
+      <c r="P30" s="147"/>
+      <c r="Q30" s="149"/>
+      <c r="R30" s="147"/>
+      <c r="S30" s="150"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="153"/>
-      <c r="C31" s="154"/>
-      <c r="D31" s="108"/>
-      <c r="E31" s="155"/>
-      <c r="F31" s="156"/>
-      <c r="G31" s="156"/>
-      <c r="H31" s="157"/>
-      <c r="I31" s="158"/>
-      <c r="J31" s="156"/>
-      <c r="K31" s="159"/>
-      <c r="L31" s="157"/>
-      <c r="M31" s="158"/>
-      <c r="N31" s="156"/>
-      <c r="O31" s="157"/>
-      <c r="P31" s="156"/>
-      <c r="Q31" s="158"/>
-      <c r="R31" s="156"/>
-      <c r="S31" s="114"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="152"/>
+      <c r="D31" s="106"/>
+      <c r="E31" s="153"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="155"/>
+      <c r="I31" s="156"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="157"/>
+      <c r="L31" s="155"/>
+      <c r="M31" s="156"/>
+      <c r="N31" s="154"/>
+      <c r="O31" s="155"/>
+      <c r="P31" s="154"/>
+      <c r="Q31" s="156"/>
+      <c r="R31" s="154"/>
+      <c r="S31" s="112"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="153"/>
-      <c r="C32" s="154" t="s">
+      <c r="B32" s="151"/>
+      <c r="C32" s="152" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="116"/>
-      <c r="E32" s="160"/>
-      <c r="F32" s="161"/>
-      <c r="G32" s="161"/>
-      <c r="H32" s="162"/>
-      <c r="I32" s="163"/>
-      <c r="J32" s="161"/>
-      <c r="K32" s="161"/>
-      <c r="L32" s="162"/>
-      <c r="M32" s="163"/>
-      <c r="N32" s="161"/>
-      <c r="O32" s="162"/>
-      <c r="P32" s="161"/>
-      <c r="Q32" s="163"/>
-      <c r="R32" s="161"/>
-      <c r="S32" s="164"/>
+      <c r="D32" s="114"/>
+      <c r="E32" s="158"/>
+      <c r="F32" s="159"/>
+      <c r="G32" s="159"/>
+      <c r="H32" s="160"/>
+      <c r="I32" s="161"/>
+      <c r="J32" s="159"/>
+      <c r="K32" s="159"/>
+      <c r="L32" s="160"/>
+      <c r="M32" s="161"/>
+      <c r="N32" s="159"/>
+      <c r="O32" s="160"/>
+      <c r="P32" s="159"/>
+      <c r="Q32" s="161"/>
+      <c r="R32" s="159"/>
+      <c r="S32" s="162"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="153"/>
-      <c r="C33" s="154"/>
-      <c r="D33" s="108"/>
-      <c r="E33" s="155"/>
-      <c r="F33" s="159"/>
-      <c r="G33" s="156"/>
-      <c r="H33" s="165"/>
-      <c r="I33" s="166"/>
-      <c r="J33" s="156"/>
-      <c r="K33" s="159"/>
-      <c r="L33" s="157"/>
-      <c r="M33" s="158"/>
-      <c r="N33" s="156"/>
-      <c r="O33" s="157"/>
-      <c r="P33" s="156"/>
-      <c r="Q33" s="158"/>
-      <c r="R33" s="156"/>
-      <c r="S33" s="114"/>
+      <c r="B33" s="151"/>
+      <c r="C33" s="152"/>
+      <c r="D33" s="106"/>
+      <c r="E33" s="153"/>
+      <c r="F33" s="157"/>
+      <c r="G33" s="154"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="157"/>
+      <c r="L33" s="155"/>
+      <c r="M33" s="156"/>
+      <c r="N33" s="154"/>
+      <c r="O33" s="155"/>
+      <c r="P33" s="154"/>
+      <c r="Q33" s="156"/>
+      <c r="R33" s="154"/>
+      <c r="S33" s="112"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="153"/>
-      <c r="C34" s="107" t="s">
-        <v>193</v>
-      </c>
-      <c r="D34" s="139"/>
-      <c r="E34" s="167"/>
-      <c r="F34" s="168"/>
-      <c r="G34" s="168"/>
-      <c r="H34" s="169"/>
-      <c r="I34" s="170"/>
-      <c r="J34" s="168"/>
-      <c r="K34" s="168"/>
-      <c r="L34" s="169"/>
-      <c r="M34" s="170"/>
-      <c r="N34" s="168"/>
-      <c r="O34" s="169"/>
-      <c r="P34" s="168"/>
-      <c r="Q34" s="170"/>
-      <c r="R34" s="168"/>
-      <c r="S34" s="171"/>
-      <c r="U34" s="172"/>
-      <c r="V34" s="173" t="s">
+      <c r="B34" s="151"/>
+      <c r="C34" s="105" t="s">
         <v>194</v>
       </c>
+      <c r="D34" s="137"/>
+      <c r="E34" s="165"/>
+      <c r="F34" s="166"/>
+      <c r="G34" s="166"/>
+      <c r="H34" s="167"/>
+      <c r="I34" s="168"/>
+      <c r="J34" s="166"/>
+      <c r="K34" s="166"/>
+      <c r="L34" s="167"/>
+      <c r="M34" s="168"/>
+      <c r="N34" s="166"/>
+      <c r="O34" s="167"/>
+      <c r="P34" s="166"/>
+      <c r="Q34" s="168"/>
+      <c r="R34" s="166"/>
+      <c r="S34" s="169"/>
+      <c r="U34" s="170"/>
+      <c r="V34" s="171" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="174"/>
-      <c r="C35" s="175"/>
-      <c r="D35" s="126"/>
-      <c r="E35" s="176"/>
-      <c r="F35" s="177"/>
-      <c r="G35" s="177"/>
-      <c r="H35" s="178"/>
-      <c r="I35" s="179"/>
-      <c r="J35" s="177"/>
-      <c r="K35" s="177"/>
-      <c r="L35" s="178"/>
-      <c r="M35" s="179"/>
-      <c r="N35" s="177"/>
-      <c r="O35" s="178"/>
-      <c r="P35" s="177"/>
-      <c r="Q35" s="179"/>
-      <c r="R35" s="177"/>
-      <c r="S35" s="131"/>
-      <c r="U35" s="180"/>
-      <c r="V35" s="181" t="s">
-        <v>195</v>
+      <c r="B35" s="172"/>
+      <c r="C35" s="173"/>
+      <c r="D35" s="124"/>
+      <c r="E35" s="174"/>
+      <c r="F35" s="175"/>
+      <c r="G35" s="175"/>
+      <c r="H35" s="176"/>
+      <c r="I35" s="177"/>
+      <c r="J35" s="175"/>
+      <c r="K35" s="175"/>
+      <c r="L35" s="176"/>
+      <c r="M35" s="177"/>
+      <c r="N35" s="175"/>
+      <c r="O35" s="176"/>
+      <c r="P35" s="175"/>
+      <c r="Q35" s="177"/>
+      <c r="R35" s="175"/>
+      <c r="S35" s="129"/>
+      <c r="U35" s="178"/>
+      <c r="V35" s="179" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/LHO - M5 - JournalPlanif.xlsx
+++ b/Documentation/LHO - M5 - JournalPlanif.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t>date</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t xml:space="preserve">Documentation du processus de déploiement multiplateforme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création des différents test pour l'application. pas encore testé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relecture et correction de la documentation</t>
   </si>
   <si>
     <t xml:space="preserve">Par jour</t>
@@ -1602,7 +1608,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="181">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1656,6 +1662,9 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4897,8 +4906,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E74">
-  <autoFilter ref="B2:E74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E76">
+  <autoFilter ref="B2:E76"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5462,7 +5471,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.7492711370262388e-002</v>
+        <v>1.714285714285714e-002</v>
       </c>
       <c r="J3" s="12" t="str">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -5495,7 +5504,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.7492711370262388e-002</v>
+        <v>1.714285714285714e-002</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -5528,7 +5537,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>5.5393586005830893e-002</v>
+        <v>5.4285714285714277e-002</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -5561,7 +5570,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>9.9125364431486868e-002</v>
+        <v>9.7142857142857128e-002</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -5590,11 +5599,11 @@
       </c>
       <c r="H7" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>56.5</v>
+        <v>57</v>
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.32944606413994165</v>
+        <v>0.32571428571428568</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -5602,7 +5611,7 @@
       </c>
       <c r="K7" s="13">
         <f/>
-        <v>56.5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" ht="28.5">
@@ -5627,7 +5636,7 @@
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.44120505344995137</v>
+        <v>0.43238095238095231</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -5656,11 +5665,11 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>6.3333333333333339</v>
+        <v>9.3333333333333339</v>
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>3.69290573372206e-002</v>
+        <v>5.333333333333333e-002</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -5668,7 +5677,7 @@
       </c>
       <c r="K9" s="14">
         <f/>
-        <v>6.3333333333333339</v>
+        <v>9.3333333333333339</v>
       </c>
     </row>
     <row r="10">
@@ -5693,7 +5702,7 @@
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.9154518950437313e-003</v>
+        <v>2.8571428571428567e-003</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -5716,7 +5725,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>171.50000000000003</v>
+        <v>175.00000000000003</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -6604,24 +6613,40 @@
       <c r="C74" s="21">
         <v>4.1666666666666664e-002</v>
       </c>
-      <c r="D74" s="24" t="s">
+      <c r="D74" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E74" s="25" t="s">
+      <c r="E74" s="8" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="5"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="8"/>
+      <c r="B75" s="5">
+        <v>46181</v>
+      </c>
+      <c r="C75" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="76">
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="8"/>
+      <c r="B76" s="24">
+        <v>46181</v>
+      </c>
+      <c r="C76" s="21">
+        <v>2.0833333333333332e-002</v>
+      </c>
+      <c r="D76" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="26" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="77">
       <c r="B77" s="7"/>
@@ -6669,7 +6694,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{53EDA031-9E73-4259-AEA0-810F96CBD0A0}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{9D101B69-AAA9-4629-B9B2-C1792FD1C30C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6693,11 +6718,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -6711,47 +6736,47 @@
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26">
+      <c r="A3" s="27">
         <v>46042</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C3" s="27"/>
+      <c r="C3" s="28"/>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F3" s="28">
+        <v>107</v>
+      </c>
+      <c r="F3" s="29">
         <f t="shared" ref="F3:F8" si="0">SUMPRODUCT((MONTH($A$3:$A$152)=D3)*($A$3:$A$152&lt;&gt;"")*$B$3:$B$152)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="29">
+      <c r="G3" s="30">
         <f t="shared" ref="G3:G8" si="1">F3*24</f>
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26">
+      <c r="A4" s="27">
         <v>46043</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6760,22 +6785,22 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="28">
+        <v>108</v>
+      </c>
+      <c r="F4" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26">
+      <c r="A5" s="27">
         <v>46044</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6784,22 +6809,22 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="28">
+        <v>109</v>
+      </c>
+      <c r="F5" s="29">
         <f t="shared" si="0"/>
         <v>2.6805555555555558</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="30">
         <f t="shared" si="1"/>
         <v>64.333333333333343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26">
+      <c r="A6" s="27">
         <v>46045</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6808,22 +6833,22 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F6" s="28">
+        <v>110</v>
+      </c>
+      <c r="F6" s="29">
         <f t="shared" si="0"/>
         <v>1.2083333333333333</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="30">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26">
+      <c r="A7" s="27">
         <v>46046</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6832,22 +6857,22 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
-      </c>
-      <c r="F7" s="28">
+        <v>111</v>
+      </c>
+      <c r="F7" s="29">
         <f t="shared" si="0"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26">
+      <c r="A8" s="27">
         <v>46047</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6856,2071 +6881,2071 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
-      </c>
-      <c r="F8" s="28">
+        <v>112</v>
+      </c>
+      <c r="F8" s="29">
         <f t="shared" si="0"/>
-        <v>0.34027777777777779</v>
-      </c>
-      <c r="G8" s="29">
+        <v>0.48611111111111116</v>
+      </c>
+      <c r="G8" s="30">
         <f t="shared" si="1"/>
-        <v>8.1666666666666679</v>
+        <v>11.666666666666668</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26">
+      <c r="A9" s="27">
         <v>46048</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <f>SUM(G3:G8)</f>
-        <v>108.50000000000001</v>
+        <v>112.00000000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26">
+      <c r="A10" s="27">
         <v>46049</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="26">
+      <c r="A11" s="27">
         <v>46050</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="26">
+      <c r="A12" s="27">
         <v>46051</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="26">
+      <c r="A13" s="27">
         <v>46052</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="26">
+      <c r="A14" s="27">
         <v>46053</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="26">
+      <c r="A15" s="27">
         <v>46054</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="26">
+      <c r="A16" s="27">
         <v>46055</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="26">
+      <c r="A17" s="27">
         <v>46056</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="26">
+      <c r="A18" s="27">
         <v>46057</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="26">
+      <c r="A19" s="27">
         <v>46058</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="26">
+      <c r="A20" s="27">
         <v>46059</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="26">
+      <c r="A21" s="27">
         <v>46060</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="26">
+      <c r="A22" s="27">
         <v>46061</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="26">
+      <c r="A23" s="27">
         <v>46062</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="26">
+      <c r="A24" s="27">
         <v>46063</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="26">
+      <c r="A25" s="27">
         <v>46064</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
     </row>
     <row r="26">
-      <c r="A26" s="26">
+      <c r="A26" s="27">
         <v>46065</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C26"/>
-      <c r="F26" s="29"/>
+      <c r="F26" s="30"/>
     </row>
     <row r="27">
-      <c r="A27" s="26">
+      <c r="A27" s="27">
         <v>46066</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26">
+      <c r="A28" s="27">
         <v>46067</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26">
+      <c r="A29" s="27">
         <v>46068</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26">
+      <c r="A30" s="27">
         <v>46069</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26">
+      <c r="A31" s="27">
         <v>46070</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26">
+      <c r="A32" s="27">
         <v>46071</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26">
+      <c r="A33" s="27">
         <v>46072</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26">
+      <c r="A34" s="27">
         <v>46073</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26">
+      <c r="A35" s="27">
         <v>46074</v>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26">
+      <c r="A36" s="27">
         <v>46075</v>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26">
+      <c r="A37" s="27">
         <v>46076</v>
       </c>
-      <c r="B37" s="27">
+      <c r="B37" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26">
+      <c r="A38" s="27">
         <v>46077</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="26">
+      <c r="A39" s="27">
         <v>46078</v>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26">
+      <c r="A40" s="27">
         <v>46079</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26">
+      <c r="A41" s="27">
         <v>46080</v>
       </c>
-      <c r="B41" s="27">
+      <c r="B41" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="26">
+      <c r="A42" s="27">
         <v>46081</v>
       </c>
-      <c r="B42" s="27">
+      <c r="B42" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="26">
+      <c r="A43" s="27">
         <v>46082</v>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="26">
+      <c r="A44" s="27">
         <v>46083</v>
       </c>
-      <c r="B44" s="27">
+      <c r="B44" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="26">
+      <c r="A45" s="27">
         <v>46084</v>
       </c>
-      <c r="B45" s="27">
+      <c r="B45" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C45" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="26">
+      <c r="A46" s="27">
         <v>46085</v>
       </c>
-      <c r="B46" s="27">
+      <c r="B46" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C46" s="30">
+      <c r="C46" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="26">
+      <c r="A47" s="27">
         <v>46086</v>
       </c>
-      <c r="B47" s="27">
+      <c r="B47" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C47" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="26">
+      <c r="A48" s="27">
         <v>46087</v>
       </c>
-      <c r="B48" s="27">
+      <c r="B48" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="26">
+      <c r="A49" s="27">
         <v>46088</v>
       </c>
-      <c r="B49" s="27">
+      <c r="B49" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
-      <c r="C49" s="30">
+      <c r="C49" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26">
+      <c r="A50" s="27">
         <v>46089</v>
       </c>
-      <c r="B50" s="27">
+      <c r="B50" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C50" s="30">
+      <c r="C50" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="26">
+      <c r="A51" s="27">
         <v>46090</v>
       </c>
-      <c r="B51" s="27">
+      <c r="B51" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C51" s="30">
+      <c r="C51" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26">
+      <c r="A52" s="27">
         <v>46091</v>
       </c>
-      <c r="B52" s="27">
+      <c r="B52" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C52" s="30">
+      <c r="C52" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="26">
+      <c r="A53" s="27">
         <v>46092</v>
       </c>
-      <c r="B53" s="27">
+      <c r="B53" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C53" s="30">
+      <c r="C53" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="26">
+      <c r="A54" s="27">
         <v>46093</v>
       </c>
-      <c r="B54" s="27">
+      <c r="B54" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C54" s="30">
+      <c r="C54" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="26">
+      <c r="A55" s="27">
         <v>46094</v>
       </c>
-      <c r="B55" s="27">
+      <c r="B55" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C55" s="30">
+      <c r="C55" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="26">
+      <c r="A56" s="27">
         <v>46095</v>
       </c>
-      <c r="B56" s="27">
+      <c r="B56" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
-      <c r="C56" s="30">
+      <c r="C56" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="26">
+      <c r="A57" s="27">
         <v>46096</v>
       </c>
-      <c r="B57" s="27">
+      <c r="B57" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C57" s="30">
+      <c r="C57" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="26">
+      <c r="A58" s="27">
         <v>46097</v>
       </c>
-      <c r="B58" s="27">
+      <c r="B58" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C58" s="30">
+      <c r="C58" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="26">
+      <c r="A59" s="27">
         <v>46098</v>
       </c>
-      <c r="B59" s="27">
+      <c r="B59" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C59" s="30">
+      <c r="C59" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="26">
+      <c r="A60" s="27">
         <v>46099</v>
       </c>
-      <c r="B60" s="27">
+      <c r="B60" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C60" s="30">
+      <c r="C60" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="26">
+      <c r="A61" s="27">
         <v>46100</v>
       </c>
-      <c r="B61" s="27">
+      <c r="B61" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="C61" s="30">
+      <c r="C61" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="26">
+      <c r="A62" s="27">
         <v>46101</v>
       </c>
-      <c r="B62" s="27">
+      <c r="B62" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C62" s="30">
+      <c r="C62" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="26">
+      <c r="A63" s="27">
         <v>46102</v>
       </c>
-      <c r="B63" s="27">
+      <c r="B63" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C63" s="30">
+      <c r="C63" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="26">
+      <c r="A64" s="27">
         <v>46103</v>
       </c>
-      <c r="B64" s="27">
+      <c r="B64" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C64" s="30">
+      <c r="C64" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="26">
+      <c r="A65" s="27">
         <v>46104</v>
       </c>
-      <c r="B65" s="27">
+      <c r="B65" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
       </c>
-      <c r="C65" s="30">
+      <c r="C65" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="26">
+      <c r="A66" s="27">
         <v>46105</v>
       </c>
-      <c r="B66" s="27">
+      <c r="B66" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C66" s="30">
+      <c r="C66" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="26">
+      <c r="A67" s="27">
         <v>46106</v>
       </c>
-      <c r="B67" s="27">
+      <c r="B67" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C67" s="30">
+      <c r="C67" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="26">
+      <c r="A68" s="27">
         <v>46107</v>
       </c>
-      <c r="B68" s="27">
+      <c r="B68" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C68" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="26">
+      <c r="A69" s="27">
         <v>46108</v>
       </c>
-      <c r="B69" s="27">
+      <c r="B69" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C69" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="26">
+      <c r="A70" s="27">
         <v>46109</v>
       </c>
-      <c r="B70" s="27">
+      <c r="B70" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C70" s="30">
+      <c r="C70" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="26">
+      <c r="A71" s="27">
         <v>46110</v>
       </c>
-      <c r="B71" s="27">
+      <c r="B71" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C71" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="26">
+      <c r="A72" s="27">
         <v>46111</v>
       </c>
-      <c r="B72" s="27">
+      <c r="B72" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C72" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="26">
+      <c r="A73" s="27">
         <v>46112</v>
       </c>
-      <c r="B73" s="27">
+      <c r="B73" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C73" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="26">
+      <c r="A74" s="27">
         <v>46113</v>
       </c>
-      <c r="B74" s="27">
+      <c r="B74" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C74" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="26">
+      <c r="A75" s="27">
         <v>46114</v>
       </c>
-      <c r="B75" s="27">
+      <c r="B75" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C75" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="26">
+      <c r="A76" s="27">
         <v>46115</v>
       </c>
-      <c r="B76" s="27">
+      <c r="B76" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C76" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="26">
+      <c r="A77" s="27">
         <v>46116</v>
       </c>
-      <c r="B77" s="27">
+      <c r="B77" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C77" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="26">
+      <c r="A78" s="27">
         <v>46117</v>
       </c>
-      <c r="B78" s="27">
+      <c r="B78" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C78" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="26">
+      <c r="A79" s="27">
         <v>46118</v>
       </c>
-      <c r="B79" s="27">
+      <c r="B79" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C79" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="26">
+      <c r="A80" s="27">
         <v>46119</v>
       </c>
-      <c r="B80" s="27">
+      <c r="B80" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C80" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="26">
+      <c r="A81" s="27">
         <v>46120</v>
       </c>
-      <c r="B81" s="27">
+      <c r="B81" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C81" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="26">
+      <c r="A82" s="27">
         <v>46121</v>
       </c>
-      <c r="B82" s="27">
+      <c r="B82" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C82" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="26">
+      <c r="A83" s="27">
         <v>46122</v>
       </c>
-      <c r="B83" s="27">
+      <c r="B83" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C83" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="26">
+      <c r="A84" s="27">
         <v>46123</v>
       </c>
-      <c r="B84" s="27">
+      <c r="B84" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C84" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="26">
+      <c r="A85" s="27">
         <v>46124</v>
       </c>
-      <c r="B85" s="27">
+      <c r="B85" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C85" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="26">
+      <c r="A86" s="27">
         <v>46125</v>
       </c>
-      <c r="B86" s="27">
+      <c r="B86" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C86" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="26">
+      <c r="A87" s="27">
         <v>46126</v>
       </c>
-      <c r="B87" s="27">
+      <c r="B87" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C87" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="26">
+      <c r="A88" s="27">
         <v>46127</v>
       </c>
-      <c r="B88" s="27">
+      <c r="B88" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C88" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="26">
+      <c r="A89" s="27">
         <v>46128</v>
       </c>
-      <c r="B89" s="27">
+      <c r="B89" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C89" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="26">
+      <c r="A90" s="27">
         <v>46129</v>
       </c>
-      <c r="B90" s="27">
+      <c r="B90" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C90" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="26">
+      <c r="A91" s="27">
         <v>46130</v>
       </c>
-      <c r="B91" s="27">
+      <c r="B91" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C91" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="26">
+      <c r="A92" s="27">
         <v>46131</v>
       </c>
-      <c r="B92" s="27">
+      <c r="B92" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C92" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="26">
+      <c r="A93" s="27">
         <v>46132</v>
       </c>
-      <c r="B93" s="27">
+      <c r="B93" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C93" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="26">
+      <c r="A94" s="27">
         <v>46133</v>
       </c>
-      <c r="B94" s="27">
+      <c r="B94" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C94" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="26">
+      <c r="A95" s="27">
         <v>46134</v>
       </c>
-      <c r="B95" s="27">
+      <c r="B95" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C95" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="26">
+      <c r="A96" s="27">
         <v>46135</v>
       </c>
-      <c r="B96" s="27">
+      <c r="B96" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C96" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="26">
+      <c r="A97" s="27">
         <v>46136</v>
       </c>
-      <c r="B97" s="27">
+      <c r="B97" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C97" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="26">
+      <c r="A98" s="27">
         <v>46137</v>
       </c>
-      <c r="B98" s="27">
+      <c r="B98" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C98" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="26">
+      <c r="A99" s="27">
         <v>46138</v>
       </c>
-      <c r="B99" s="27">
+      <c r="B99" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C99" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="26">
+      <c r="A100" s="27">
         <v>46139</v>
       </c>
-      <c r="B100" s="27">
+      <c r="B100" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C100" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="26">
+      <c r="A101" s="27">
         <v>46140</v>
       </c>
-      <c r="B101" s="27">
+      <c r="B101" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C101" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="26">
+      <c r="A102" s="27">
         <v>46141</v>
       </c>
-      <c r="B102" s="27">
+      <c r="B102" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C102" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="26">
+      <c r="A103" s="27">
         <v>46142</v>
       </c>
-      <c r="B103" s="27">
+      <c r="B103" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C103" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="26">
+      <c r="A104" s="27">
         <v>46143</v>
       </c>
-      <c r="B104" s="27">
+      <c r="B104" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C104" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="26">
+      <c r="A105" s="27">
         <v>46144</v>
       </c>
-      <c r="B105" s="27">
+      <c r="B105" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C105" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="26">
+      <c r="A106" s="27">
         <v>46145</v>
       </c>
-      <c r="B106" s="27">
+      <c r="B106" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C106" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="26">
+      <c r="A107" s="27">
         <v>46146</v>
       </c>
-      <c r="B107" s="27">
+      <c r="B107" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C107" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="26">
+      <c r="A108" s="27">
         <v>46147</v>
       </c>
-      <c r="B108" s="27">
+      <c r="B108" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C108" s="30">
+      <c r="C108" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="26">
+      <c r="A109" s="27">
         <v>46148</v>
       </c>
-      <c r="B109" s="27">
+      <c r="B109" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C109" s="30">
+      <c r="C109" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="26">
+      <c r="A110" s="27">
         <v>46149</v>
       </c>
-      <c r="B110" s="27">
+      <c r="B110" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C110" s="30">
+      <c r="C110" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="26">
+      <c r="A111" s="27">
         <v>46150</v>
       </c>
-      <c r="B111" s="27">
+      <c r="B111" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C111" s="30">
+      <c r="C111" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="26">
+      <c r="A112" s="27">
         <v>46151</v>
       </c>
-      <c r="B112" s="27">
+      <c r="B112" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C112" s="30">
+      <c r="C112" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="26">
+      <c r="A113" s="27">
         <v>46152</v>
       </c>
-      <c r="B113" s="27">
+      <c r="B113" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C113" s="30">
+      <c r="C113" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="26">
+      <c r="A114" s="27">
         <v>46153</v>
       </c>
-      <c r="B114" s="27">
+      <c r="B114" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C114" s="30">
+      <c r="C114" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="26">
+      <c r="A115" s="27">
         <v>46154</v>
       </c>
-      <c r="B115" s="27">
+      <c r="B115" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C115" s="30">
+      <c r="C115" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="26">
+      <c r="A116" s="27">
         <v>46155</v>
       </c>
-      <c r="B116" s="27">
+      <c r="B116" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A116,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C116" s="30"/>
+      <c r="C116" s="31"/>
     </row>
     <row r="117">
-      <c r="A117" s="26">
+      <c r="A117" s="27">
         <v>46156</v>
       </c>
-      <c r="B117" s="27">
+      <c r="B117" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A117,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C117" s="30"/>
+      <c r="C117" s="31"/>
     </row>
     <row r="118">
-      <c r="A118" s="26">
+      <c r="A118" s="27">
         <v>46157</v>
       </c>
-      <c r="B118" s="27">
+      <c r="B118" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A118,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C118" s="30"/>
+      <c r="C118" s="31"/>
     </row>
     <row r="119">
-      <c r="A119" s="26">
+      <c r="A119" s="27">
         <v>46158</v>
       </c>
-      <c r="B119" s="27">
+      <c r="B119" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A119,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C119" s="30"/>
+      <c r="C119" s="31"/>
     </row>
     <row r="120">
-      <c r="A120" s="26">
+      <c r="A120" s="27">
         <v>46159</v>
       </c>
-      <c r="B120" s="27">
+      <c r="B120" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A120,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C120" s="30"/>
+      <c r="C120" s="31"/>
     </row>
     <row r="121">
-      <c r="A121" s="26">
+      <c r="A121" s="27">
         <v>46160</v>
       </c>
-      <c r="B121" s="27">
+      <c r="B121" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A121,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C121" s="30"/>
+      <c r="C121" s="31"/>
     </row>
     <row r="122">
-      <c r="A122" s="26">
+      <c r="A122" s="27">
         <v>46161</v>
       </c>
-      <c r="B122" s="27">
+      <c r="B122" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A122,Journal[Temps])</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="C122" s="30"/>
+      <c r="C122" s="31"/>
     </row>
     <row r="123">
-      <c r="A123" s="26">
+      <c r="A123" s="27">
         <v>46162</v>
       </c>
-      <c r="B123" s="27">
+      <c r="B123" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A123,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C123" s="30"/>
+      <c r="C123" s="31"/>
     </row>
     <row r="124">
-      <c r="A124" s="26">
+      <c r="A124" s="27">
         <v>46163</v>
       </c>
-      <c r="B124" s="27">
+      <c r="B124" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A124,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C124" s="30"/>
+      <c r="C124" s="31"/>
     </row>
     <row r="125">
-      <c r="A125" s="26">
+      <c r="A125" s="27">
         <v>46164</v>
       </c>
-      <c r="B125" s="27">
+      <c r="B125" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A125,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C125" s="30"/>
+      <c r="C125" s="31"/>
     </row>
     <row r="126">
-      <c r="A126" s="26">
+      <c r="A126" s="27">
         <v>46165</v>
       </c>
-      <c r="B126" s="27">
+      <c r="B126" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A126,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C126" s="30"/>
+      <c r="C126" s="31"/>
     </row>
     <row r="127">
-      <c r="A127" s="26">
+      <c r="A127" s="27">
         <v>46166</v>
       </c>
-      <c r="B127" s="27">
+      <c r="B127" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A127,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C127" s="30"/>
+      <c r="C127" s="31"/>
     </row>
     <row r="128">
-      <c r="A128" s="26">
+      <c r="A128" s="27">
         <v>46167</v>
       </c>
-      <c r="B128" s="27">
+      <c r="B128" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A128,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C128" s="30"/>
+      <c r="C128" s="31"/>
     </row>
     <row r="129">
-      <c r="A129" s="26">
+      <c r="A129" s="27">
         <v>46168</v>
       </c>
-      <c r="B129" s="27">
+      <c r="B129" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A129,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C129" s="30"/>
+      <c r="C129" s="31"/>
     </row>
     <row r="130">
-      <c r="A130" s="26">
+      <c r="A130" s="27">
         <v>46169</v>
       </c>
-      <c r="B130" s="27">
+      <c r="B130" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A130,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C130" s="30"/>
+      <c r="C130" s="31"/>
     </row>
     <row r="131">
-      <c r="A131" s="26">
+      <c r="A131" s="27">
         <v>46170</v>
       </c>
-      <c r="B131" s="27">
+      <c r="B131" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A131,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C131" s="30"/>
+      <c r="C131" s="31"/>
     </row>
     <row r="132">
-      <c r="A132" s="26">
+      <c r="A132" s="27">
         <v>46171</v>
       </c>
-      <c r="B132" s="27">
+      <c r="B132" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A132,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C132" s="30"/>
+      <c r="C132" s="31"/>
     </row>
     <row r="133">
-      <c r="A133" s="26">
+      <c r="A133" s="27">
         <v>46172</v>
       </c>
-      <c r="B133" s="27">
+      <c r="B133" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A133,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C133" s="30"/>
+      <c r="C133" s="31"/>
     </row>
     <row r="134">
-      <c r="A134" s="26">
+      <c r="A134" s="27">
         <v>46173</v>
       </c>
-      <c r="B134" s="27">
+      <c r="B134" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A134,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C134" s="30"/>
+      <c r="C134" s="31"/>
     </row>
     <row r="135">
-      <c r="A135" s="26">
+      <c r="A135" s="27">
         <v>46174</v>
       </c>
-      <c r="B135" s="27">
+      <c r="B135" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A135,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C135" s="30"/>
+      <c r="C135" s="31"/>
     </row>
     <row r="136">
-      <c r="A136" s="26">
+      <c r="A136" s="27">
         <v>46175</v>
       </c>
-      <c r="B136" s="27">
+      <c r="B136" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A136,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C136" s="30"/>
+      <c r="C136" s="31"/>
     </row>
     <row r="137">
-      <c r="A137" s="26">
+      <c r="A137" s="27">
         <v>46176</v>
       </c>
-      <c r="B137" s="27">
+      <c r="B137" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A137,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C137" s="30"/>
+      <c r="C137" s="31"/>
     </row>
     <row r="138">
-      <c r="A138" s="26">
+      <c r="A138" s="27">
         <v>46177</v>
       </c>
-      <c r="B138" s="27">
+      <c r="B138" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A138,Journal[Temps])</f>
         <v>0.2986111111111111</v>
       </c>
-      <c r="C138" s="30"/>
+      <c r="C138" s="31"/>
     </row>
     <row r="139">
-      <c r="A139" s="26">
+      <c r="A139" s="27">
         <v>46178</v>
       </c>
-      <c r="B139" s="27">
+      <c r="B139" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A139,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C139" s="30"/>
+      <c r="C139" s="31"/>
     </row>
     <row r="140">
-      <c r="A140" s="26">
+      <c r="A140" s="27">
         <v>46179</v>
       </c>
-      <c r="B140" s="27">
+      <c r="B140" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A140,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C140" s="30"/>
+      <c r="C140" s="31"/>
     </row>
     <row r="141">
-      <c r="A141" s="26">
+      <c r="A141" s="27">
         <v>46180</v>
       </c>
-      <c r="B141" s="27">
+      <c r="B141" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A141,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
-      <c r="C141" s="30"/>
+      <c r="C141" s="31"/>
     </row>
     <row r="142">
-      <c r="A142" s="26">
+      <c r="A142" s="27">
         <v>46181</v>
       </c>
-      <c r="B142" s="27">
+      <c r="B142" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A142,Journal[Temps])</f>
-        <v>0</v>
-      </c>
-      <c r="C142" s="30"/>
+        <v>0.14583333333333334</v>
+      </c>
+      <c r="C142" s="31"/>
     </row>
     <row r="143">
-      <c r="A143" s="26">
+      <c r="A143" s="27">
         <v>46182</v>
       </c>
-      <c r="B143" s="27">
+      <c r="B143" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A143,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C143" s="30"/>
+      <c r="C143" s="31"/>
     </row>
     <row r="144">
-      <c r="A144" s="26">
+      <c r="A144" s="27">
         <v>46183</v>
       </c>
-      <c r="B144" s="27">
+      <c r="B144" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A144,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C144" s="30"/>
+      <c r="C144" s="31"/>
     </row>
     <row r="145">
-      <c r="A145" s="26">
+      <c r="A145" s="27">
         <v>46184</v>
       </c>
-      <c r="B145" s="27">
+      <c r="B145" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A145,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C145" s="30"/>
+      <c r="C145" s="31"/>
     </row>
     <row r="146">
-      <c r="A146" s="26">
+      <c r="A146" s="27">
         <v>46185</v>
       </c>
-      <c r="B146" s="27">
+      <c r="B146" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A146,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C146" s="30"/>
+      <c r="C146" s="31"/>
     </row>
     <row r="147">
-      <c r="A147" s="26">
+      <c r="A147" s="27">
         <v>46186</v>
       </c>
-      <c r="B147" s="27">
+      <c r="B147" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A147,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C147" s="30"/>
+      <c r="C147" s="31"/>
     </row>
     <row r="148">
-      <c r="A148" s="26">
+      <c r="A148" s="27">
         <v>46187</v>
       </c>
-      <c r="B148" s="27">
+      <c r="B148" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A148,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C148" s="30"/>
+      <c r="C148" s="31"/>
     </row>
     <row r="149">
-      <c r="A149" s="26">
+      <c r="A149" s="27">
         <v>46188</v>
       </c>
-      <c r="B149" s="27">
+      <c r="B149" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A149,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C149" s="30"/>
+      <c r="C149" s="31"/>
     </row>
     <row r="150">
-      <c r="A150" s="26">
+      <c r="A150" s="27">
         <v>46189</v>
       </c>
-      <c r="B150" s="27">
+      <c r="B150" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A150,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C150" s="30"/>
+      <c r="C150" s="31"/>
     </row>
     <row r="151">
-      <c r="A151" s="26">
+      <c r="A151" s="27">
         <v>46190</v>
       </c>
-      <c r="B151" s="27">
+      <c r="B151" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A151,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C151" s="30"/>
+      <c r="C151" s="31"/>
     </row>
     <row r="152">
-      <c r="A152" s="26">
+      <c r="A152" s="27">
         <v>46191</v>
       </c>
-      <c r="B152" s="27">
+      <c r="B152" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A152,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C152" s="30"/>
+      <c r="C152" s="31"/>
     </row>
     <row r="153">
-      <c r="A153" s="26"/>
-      <c r="B153" s="31"/>
-      <c r="C153" s="30"/>
+      <c r="A153" s="27"/>
+      <c r="B153" s="32"/>
+      <c r="C153" s="31"/>
     </row>
     <row r="154">
-      <c r="A154" s="26"/>
-      <c r="B154" s="31"/>
-      <c r="C154" s="30"/>
+      <c r="A154" s="27"/>
+      <c r="B154" s="32"/>
+      <c r="C154" s="31"/>
     </row>
     <row r="155">
-      <c r="A155" s="26"/>
-      <c r="B155" s="31"/>
-      <c r="C155" s="30"/>
+      <c r="A155" s="27"/>
+      <c r="B155" s="32"/>
+      <c r="C155" s="31"/>
     </row>
     <row r="156">
-      <c r="A156" s="26"/>
-      <c r="B156" s="31"/>
-      <c r="C156" s="30"/>
+      <c r="A156" s="27"/>
+      <c r="B156" s="32"/>
+      <c r="C156" s="31"/>
     </row>
     <row r="157">
-      <c r="A157" s="26"/>
-      <c r="B157" s="31"/>
-      <c r="C157" s="30"/>
+      <c r="A157" s="27"/>
+      <c r="B157" s="32"/>
+      <c r="C157" s="31"/>
     </row>
     <row r="158">
-      <c r="A158" s="26"/>
-      <c r="B158" s="31"/>
-      <c r="C158" s="30"/>
+      <c r="A158" s="27"/>
+      <c r="B158" s="32"/>
+      <c r="C158" s="31"/>
     </row>
     <row r="159">
-      <c r="A159" s="26"/>
-      <c r="B159" s="31"/>
-      <c r="C159" s="30"/>
+      <c r="A159" s="27"/>
+      <c r="B159" s="32"/>
+      <c r="C159" s="31"/>
     </row>
     <row r="160">
-      <c r="A160" s="26"/>
-      <c r="B160" s="31"/>
+      <c r="A160" s="27"/>
+      <c r="B160" s="32"/>
     </row>
     <row r="161">
-      <c r="A161" s="26"/>
-      <c r="B161" s="31"/>
+      <c r="A161" s="27"/>
+      <c r="B161" s="32"/>
     </row>
     <row r="162">
-      <c r="A162" s="26"/>
-      <c r="B162" s="31"/>
+      <c r="A162" s="27"/>
+      <c r="B162" s="32"/>
     </row>
     <row r="163">
-      <c r="A163" s="26"/>
-      <c r="B163" s="31"/>
+      <c r="A163" s="27"/>
+      <c r="B163" s="32"/>
     </row>
     <row r="164">
-      <c r="A164" s="26"/>
-      <c r="B164" s="31"/>
+      <c r="A164" s="27"/>
+      <c r="B164" s="32"/>
     </row>
     <row r="165">
-      <c r="A165" s="26"/>
-      <c r="B165" s="31"/>
+      <c r="A165" s="27"/>
+      <c r="B165" s="32"/>
     </row>
     <row r="166">
-      <c r="A166" s="26"/>
-      <c r="B166" s="31"/>
+      <c r="A166" s="27"/>
+      <c r="B166" s="32"/>
     </row>
     <row r="167">
-      <c r="A167" s="26"/>
-      <c r="B167" s="31"/>
+      <c r="A167" s="27"/>
+      <c r="B167" s="32"/>
     </row>
     <row r="168">
-      <c r="A168" s="26"/>
-      <c r="B168" s="31"/>
+      <c r="A168" s="27"/>
+      <c r="B168" s="32"/>
     </row>
     <row r="169">
-      <c r="A169" s="26"/>
-      <c r="B169" s="31"/>
+      <c r="A169" s="27"/>
+      <c r="B169" s="32"/>
     </row>
     <row r="170">
-      <c r="A170" s="26"/>
-      <c r="B170" s="31"/>
+      <c r="A170" s="27"/>
+      <c r="B170" s="32"/>
     </row>
     <row r="171">
-      <c r="A171" s="26"/>
-      <c r="B171" s="31"/>
+      <c r="A171" s="27"/>
+      <c r="B171" s="32"/>
     </row>
     <row r="172">
-      <c r="A172" s="26"/>
-      <c r="B172" s="31"/>
+      <c r="A172" s="27"/>
+      <c r="B172" s="32"/>
     </row>
     <row r="173">
-      <c r="A173" s="26"/>
-      <c r="B173" s="31"/>
+      <c r="A173" s="27"/>
+      <c r="B173" s="32"/>
     </row>
     <row r="174">
-      <c r="A174" s="26"/>
-      <c r="B174" s="31"/>
+      <c r="A174" s="27"/>
+      <c r="B174" s="32"/>
     </row>
     <row r="175">
-      <c r="A175" s="26"/>
-      <c r="B175" s="31"/>
+      <c r="A175" s="27"/>
+      <c r="B175" s="32"/>
     </row>
     <row r="176">
-      <c r="A176" s="26"/>
-      <c r="B176" s="31"/>
+      <c r="A176" s="27"/>
+      <c r="B176" s="32"/>
     </row>
     <row r="177">
-      <c r="A177" s="26"/>
-      <c r="B177" s="31"/>
+      <c r="A177" s="27"/>
+      <c r="B177" s="32"/>
     </row>
     <row r="178">
-      <c r="A178" s="26"/>
-      <c r="B178" s="31"/>
+      <c r="A178" s="27"/>
+      <c r="B178" s="32"/>
     </row>
     <row r="179">
-      <c r="A179" s="26"/>
-      <c r="B179" s="31"/>
+      <c r="A179" s="27"/>
+      <c r="B179" s="32"/>
     </row>
     <row r="180">
-      <c r="A180" s="26"/>
-      <c r="B180" s="31"/>
+      <c r="A180" s="27"/>
+      <c r="B180" s="32"/>
     </row>
     <row r="181">
-      <c r="A181" s="26"/>
-      <c r="B181" s="31"/>
+      <c r="A181" s="27"/>
+      <c r="B181" s="32"/>
     </row>
     <row r="182">
-      <c r="A182" s="26"/>
-      <c r="B182" s="31"/>
+      <c r="A182" s="27"/>
+      <c r="B182" s="32"/>
     </row>
     <row r="183">
-      <c r="A183" s="26"/>
-      <c r="B183" s="31"/>
+      <c r="A183" s="27"/>
+      <c r="B183" s="32"/>
     </row>
     <row r="184">
-      <c r="A184" s="26"/>
-      <c r="B184" s="31"/>
+      <c r="A184" s="27"/>
+      <c r="B184" s="32"/>
     </row>
     <row r="185">
-      <c r="A185" s="26"/>
-      <c r="B185" s="31"/>
+      <c r="A185" s="27"/>
+      <c r="B185" s="32"/>
     </row>
     <row r="186">
-      <c r="A186" s="26"/>
-      <c r="B186" s="31"/>
+      <c r="A186" s="27"/>
+      <c r="B186" s="32"/>
     </row>
     <row r="187">
-      <c r="A187" s="26"/>
-      <c r="B187" s="31"/>
+      <c r="A187" s="27"/>
+      <c r="B187" s="32"/>
     </row>
     <row r="188">
-      <c r="A188" s="31"/>
-      <c r="B188" s="31"/>
+      <c r="A188" s="32"/>
+      <c r="B188" s="32"/>
     </row>
     <row r="189">
-      <c r="A189" s="31"/>
-      <c r="B189" s="31"/>
+      <c r="A189" s="32"/>
+      <c r="B189" s="32"/>
     </row>
     <row r="190">
-      <c r="A190" s="31"/>
-      <c r="B190" s="31"/>
+      <c r="A190" s="32"/>
+      <c r="B190" s="32"/>
     </row>
     <row r="191">
-      <c r="A191" s="31"/>
-      <c r="B191" s="31"/>
+      <c r="A191" s="32"/>
+      <c r="B191" s="32"/>
     </row>
     <row r="192">
-      <c r="A192" s="31"/>
-      <c r="B192" s="31"/>
+      <c r="A192" s="32"/>
+      <c r="B192" s="32"/>
     </row>
     <row r="193">
-      <c r="A193" s="31"/>
-      <c r="B193" s="31"/>
+      <c r="A193" s="32"/>
+      <c r="B193" s="32"/>
     </row>
     <row r="194">
-      <c r="A194" s="31"/>
-      <c r="B194" s="31"/>
+      <c r="A194" s="32"/>
+      <c r="B194" s="32"/>
     </row>
     <row r="195">
-      <c r="A195" s="31"/>
-      <c r="B195" s="31"/>
+      <c r="A195" s="32"/>
+      <c r="B195" s="32"/>
     </row>
     <row r="196">
-      <c r="A196" s="31"/>
-      <c r="B196" s="31"/>
+      <c r="A196" s="32"/>
+      <c r="B196" s="32"/>
     </row>
     <row r="197">
-      <c r="A197" s="31"/>
-      <c r="B197" s="31"/>
+      <c r="A197" s="32"/>
+      <c r="B197" s="32"/>
     </row>
     <row r="198">
-      <c r="A198" s="31"/>
-      <c r="B198" s="31"/>
+      <c r="A198" s="32"/>
+      <c r="B198" s="32"/>
     </row>
     <row r="199">
-      <c r="A199" s="31"/>
-      <c r="B199" s="31"/>
+      <c r="A199" s="32"/>
+      <c r="B199" s="32"/>
     </row>
     <row r="200">
-      <c r="A200" s="31"/>
-      <c r="B200" s="31"/>
+      <c r="A200" s="32"/>
+      <c r="B200" s="32"/>
     </row>
     <row r="201">
-      <c r="A201" s="31"/>
-      <c r="B201" s="31"/>
+      <c r="A201" s="32"/>
+      <c r="B201" s="32"/>
     </row>
     <row r="202">
-      <c r="A202" s="31"/>
-      <c r="B202" s="31"/>
+      <c r="A202" s="32"/>
+      <c r="B202" s="32"/>
     </row>
     <row r="203">
-      <c r="A203" s="31"/>
-      <c r="B203" s="31"/>
+      <c r="A203" s="32"/>
+      <c r="B203" s="32"/>
     </row>
     <row r="204">
-      <c r="A204" s="31"/>
-      <c r="B204" s="31"/>
+      <c r="A204" s="32"/>
+      <c r="B204" s="32"/>
     </row>
     <row r="205">
-      <c r="A205" s="31"/>
-      <c r="B205" s="31"/>
+      <c r="A205" s="32"/>
+      <c r="B205" s="32"/>
     </row>
     <row r="206">
-      <c r="A206" s="31"/>
-      <c r="B206" s="31"/>
+      <c r="A206" s="32"/>
+      <c r="B206" s="32"/>
     </row>
     <row r="207">
-      <c r="A207" s="31"/>
-      <c r="B207" s="31"/>
+      <c r="A207" s="32"/>
+      <c r="B207" s="32"/>
     </row>
     <row r="208">
-      <c r="A208" s="31"/>
-      <c r="B208" s="31"/>
+      <c r="A208" s="32"/>
+      <c r="B208" s="32"/>
     </row>
     <row r="209">
-      <c r="A209" s="31"/>
-      <c r="B209" s="31"/>
+      <c r="A209" s="32"/>
+      <c r="B209" s="32"/>
     </row>
     <row r="210">
-      <c r="A210" s="31"/>
-      <c r="B210" s="31"/>
+      <c r="A210" s="32"/>
+      <c r="B210" s="32"/>
     </row>
     <row r="211">
-      <c r="A211" s="31"/>
-      <c r="B211" s="31"/>
+      <c r="A211" s="32"/>
+      <c r="B211" s="32"/>
     </row>
     <row r="212">
-      <c r="A212" s="31"/>
-      <c r="B212" s="31"/>
+      <c r="A212" s="32"/>
+      <c r="B212" s="32"/>
     </row>
     <row r="213">
-      <c r="A213" s="31"/>
-      <c r="B213" s="31"/>
+      <c r="A213" s="32"/>
+      <c r="B213" s="32"/>
     </row>
     <row r="214">
-      <c r="A214" s="31"/>
-      <c r="B214" s="31"/>
+      <c r="A214" s="32"/>
+      <c r="B214" s="32"/>
     </row>
     <row r="215">
-      <c r="A215" s="31"/>
-      <c r="B215" s="31"/>
+      <c r="A215" s="32"/>
+      <c r="B215" s="32"/>
     </row>
     <row r="216">
-      <c r="A216" s="31"/>
-      <c r="B216" s="31"/>
+      <c r="A216" s="32"/>
+      <c r="B216" s="32"/>
     </row>
     <row r="217">
-      <c r="A217" s="31"/>
-      <c r="B217" s="31"/>
+      <c r="A217" s="32"/>
+      <c r="B217" s="32"/>
     </row>
     <row r="218">
-      <c r="A218" s="31"/>
-      <c r="B218" s="31"/>
+      <c r="A218" s="32"/>
+      <c r="B218" s="32"/>
     </row>
     <row r="219">
-      <c r="A219" s="31"/>
-      <c r="B219" s="31"/>
+      <c r="A219" s="32"/>
+      <c r="B219" s="32"/>
     </row>
     <row r="220">
-      <c r="A220" s="31"/>
-      <c r="B220" s="31"/>
+      <c r="A220" s="32"/>
+      <c r="B220" s="32"/>
     </row>
     <row r="221">
-      <c r="A221" s="31"/>
-      <c r="B221" s="31"/>
+      <c r="A221" s="32"/>
+      <c r="B221" s="32"/>
     </row>
     <row r="222">
-      <c r="A222" s="31"/>
-      <c r="B222" s="31"/>
+      <c r="A222" s="32"/>
+      <c r="B222" s="32"/>
     </row>
     <row r="223">
-      <c r="A223" s="31"/>
-      <c r="B223" s="31"/>
+      <c r="A223" s="32"/>
+      <c r="B223" s="32"/>
     </row>
     <row r="224">
-      <c r="A224" s="31"/>
-      <c r="B224" s="31"/>
+      <c r="A224" s="32"/>
+      <c r="B224" s="32"/>
     </row>
     <row r="225">
-      <c r="A225" s="31"/>
-      <c r="B225" s="31"/>
+      <c r="A225" s="32"/>
+      <c r="B225" s="32"/>
     </row>
     <row r="226">
-      <c r="A226" s="31"/>
-      <c r="B226" s="31"/>
+      <c r="A226" s="32"/>
+      <c r="B226" s="32"/>
     </row>
     <row r="227">
-      <c r="A227" s="31"/>
-      <c r="B227" s="31"/>
+      <c r="A227" s="32"/>
+      <c r="B227" s="32"/>
     </row>
     <row r="228">
-      <c r="A228" s="31"/>
-      <c r="B228" s="31"/>
+      <c r="A228" s="32"/>
+      <c r="B228" s="32"/>
     </row>
     <row r="229">
-      <c r="A229" s="31"/>
-      <c r="B229" s="31"/>
+      <c r="A229" s="32"/>
+      <c r="B229" s="32"/>
     </row>
     <row r="230">
-      <c r="A230" s="31"/>
-      <c r="B230" s="31"/>
+      <c r="A230" s="32"/>
+      <c r="B230" s="32"/>
     </row>
     <row r="231">
-      <c r="A231" s="31"/>
-      <c r="B231" s="31"/>
+      <c r="A231" s="32"/>
+      <c r="B231" s="32"/>
     </row>
     <row r="232">
-      <c r="A232" s="31"/>
-      <c r="B232" s="31"/>
+      <c r="A232" s="32"/>
+      <c r="B232" s="32"/>
     </row>
     <row r="233">
-      <c r="A233" s="31"/>
-      <c r="B233" s="31"/>
+      <c r="A233" s="32"/>
+      <c r="B233" s="32"/>
     </row>
     <row r="234">
-      <c r="A234" s="31"/>
-      <c r="B234" s="31"/>
+      <c r="A234" s="32"/>
+      <c r="B234" s="32"/>
     </row>
     <row r="235">
-      <c r="A235" s="31"/>
-      <c r="B235" s="31"/>
+      <c r="A235" s="32"/>
+      <c r="B235" s="32"/>
     </row>
     <row r="236">
-      <c r="A236" s="31"/>
-      <c r="B236" s="31"/>
+      <c r="A236" s="32"/>
+      <c r="B236" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8942,2034 +8967,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="32" width="6"/>
+    <col customWidth="1" min="12" max="12" style="33" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="32" width="6"/>
+    <col customWidth="1" min="23" max="23" style="33" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="32" width="6"/>
+    <col customWidth="1" min="30" max="30" style="33" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="33" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D1" s="36" t="s">
+    <row r="1" s="34" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="F1" s="37" t="s">
+      <c r="E1" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="G1" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="39" t="s">
-        <v>114</v>
-      </c>
-      <c r="I1" s="36" t="s">
+      <c r="H1" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="L1" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="M1" s="36" t="s">
+      <c r="K1" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="L1" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="M1" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="N1" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="P1" s="36" t="s">
+      <c r="O1" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="P1" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="R1" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="S1" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="T1" s="36" t="s">
+      <c r="Q1" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="R1" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="U1" s="36" t="s">
+      <c r="S1" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="V1" s="38" t="s">
+      <c r="T1" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="W1" s="41" t="s">
+      <c r="U1" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="X1" s="36" t="s">
+      <c r="V1" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="Y1" s="36" t="s">
+      <c r="W1" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="Z1" s="38" t="s">
+      <c r="X1" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="AA1" s="42" t="s">
+      <c r="Y1" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="AB1" s="43" t="s">
+      <c r="Z1" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="AC1" s="43" t="s">
+      <c r="AA1" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="AD1" s="40" t="s">
+      <c r="AB1" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="AE1" s="44" t="s">
+      <c r="AC1" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="AF1" s="45" t="s">
+      <c r="AD1" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="AG1" s="46" t="s">
+      <c r="AE1" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="AF1" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG1" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="AH1" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="AI1" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="AJ1" s="46" t="s">
+      <c r="AH1" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="AK1" s="43" t="s">
+      <c r="AI1" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="AL1" s="47"/>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="47"/>
-      <c r="AO1" s="47"/>
-      <c r="AP1" s="47"/>
-      <c r="AQ1" s="47"/>
-      <c r="AR1" s="47"/>
-      <c r="AS1" s="47"/>
-      <c r="AT1" s="47"/>
-      <c r="AU1" s="47"/>
+      <c r="AJ1" s="47" t="s">
+        <v>138</v>
+      </c>
+      <c r="AK1" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="AL1" s="48"/>
+      <c r="AM1" s="48"/>
+      <c r="AN1" s="48"/>
+      <c r="AO1" s="48"/>
+      <c r="AP1" s="48"/>
+      <c r="AQ1" s="48"/>
+      <c r="AR1" s="48"/>
+      <c r="AS1" s="48"/>
+      <c r="AT1" s="48"/>
+      <c r="AU1" s="48"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
-      <c r="V2" s="55"/>
-      <c r="W2" s="57"/>
-      <c r="X2" s="50"/>
-      <c r="Y2" s="50"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="56"/>
-      <c r="AB2" s="50"/>
-      <c r="AC2" s="50"/>
-      <c r="AD2" s="54"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="56"/>
-      <c r="AG2" s="50"/>
-      <c r="AH2" s="50"/>
-      <c r="AI2" s="50"/>
-      <c r="AJ2" s="50"/>
-      <c r="AK2" s="50"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="58"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="57"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="56"/>
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="48"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="55"/>
-      <c r="W3" s="57"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="55"/>
-      <c r="AA3" s="56"/>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="50"/>
-      <c r="AD3" s="54"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="56"/>
-      <c r="AG3" s="50"/>
-      <c r="AH3" s="50"/>
-      <c r="AI3" s="50"/>
-      <c r="AJ3" s="50"/>
-      <c r="AK3" s="50"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="58"/>
+      <c r="X3" s="51"/>
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="51"/>
+      <c r="AC3" s="51"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="56"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="51"/>
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="51"/>
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="51"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="48"/>
-      <c r="C4" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="57"/>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="55"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="50"/>
-      <c r="AC4" s="50"/>
-      <c r="AD4" s="54"/>
-      <c r="AE4" s="55"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="50"/>
-      <c r="AH4" s="50"/>
-      <c r="AI4" s="50"/>
-      <c r="AJ4" s="50"/>
-      <c r="AK4" s="50"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="56"/>
+      <c r="W4" s="58"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="57"/>
+      <c r="AB4" s="51"/>
+      <c r="AC4" s="51"/>
+      <c r="AD4" s="55"/>
+      <c r="AE4" s="56"/>
+      <c r="AF4" s="57"/>
+      <c r="AG4" s="51"/>
+      <c r="AH4" s="51"/>
+      <c r="AI4" s="51"/>
+      <c r="AJ4" s="51"/>
+      <c r="AK4" s="51"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="48"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="61"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="57"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="50"/>
-      <c r="Z5" s="55"/>
-      <c r="AA5" s="56"/>
-      <c r="AB5" s="50"/>
-      <c r="AC5" s="50"/>
-      <c r="AD5" s="54"/>
-      <c r="AE5" s="55"/>
-      <c r="AF5" s="56"/>
-      <c r="AG5" s="50"/>
-      <c r="AH5" s="50"/>
-      <c r="AI5" s="50"/>
-      <c r="AJ5" s="50"/>
-      <c r="AK5" s="50"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="51"/>
+      <c r="R5" s="51"/>
+      <c r="S5" s="51"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="51"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="58"/>
+      <c r="X5" s="51"/>
+      <c r="Y5" s="51"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="57"/>
+      <c r="AB5" s="51"/>
+      <c r="AC5" s="51"/>
+      <c r="AD5" s="55"/>
+      <c r="AE5" s="56"/>
+      <c r="AF5" s="57"/>
+      <c r="AG5" s="51"/>
+      <c r="AH5" s="51"/>
+      <c r="AI5" s="51"/>
+      <c r="AJ5" s="51"/>
+      <c r="AK5" s="51"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="48"/>
-      <c r="C6" s="49" t="s">
+      <c r="B6" s="49"/>
+      <c r="C6" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="57"/>
-      <c r="X6" s="50"/>
-      <c r="Y6" s="50"/>
-      <c r="Z6" s="55"/>
-      <c r="AA6" s="56"/>
-      <c r="AB6" s="50"/>
-      <c r="AC6" s="50"/>
-      <c r="AD6" s="54"/>
-      <c r="AE6" s="52"/>
-      <c r="AF6" s="53"/>
-      <c r="AG6" s="64"/>
-      <c r="AH6" s="64"/>
-      <c r="AI6" s="64"/>
-      <c r="AJ6" s="64"/>
-      <c r="AK6" s="64"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="51"/>
+      <c r="U6" s="51"/>
+      <c r="V6" s="56"/>
+      <c r="W6" s="58"/>
+      <c r="X6" s="51"/>
+      <c r="Y6" s="51"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="51"/>
+      <c r="AC6" s="51"/>
+      <c r="AD6" s="55"/>
+      <c r="AE6" s="53"/>
+      <c r="AF6" s="54"/>
+      <c r="AG6" s="65"/>
+      <c r="AH6" s="65"/>
+      <c r="AI6" s="65"/>
+      <c r="AJ6" s="65"/>
+      <c r="AK6" s="65"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="48"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="50"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="54"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="63"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="50"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="57"/>
-      <c r="X7" s="50"/>
-      <c r="Y7" s="50"/>
-      <c r="Z7" s="55"/>
-      <c r="AA7" s="56"/>
-      <c r="AB7" s="50"/>
-      <c r="AC7" s="50"/>
-      <c r="AD7" s="54"/>
-      <c r="AE7" s="55"/>
-      <c r="AF7" s="56"/>
-      <c r="AG7" s="50"/>
-      <c r="AH7" s="50"/>
-      <c r="AI7" s="50"/>
-      <c r="AJ7" s="50"/>
-      <c r="AK7" s="50"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="51"/>
+      <c r="T7" s="51"/>
+      <c r="U7" s="51"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="58"/>
+      <c r="X7" s="51"/>
+      <c r="Y7" s="51"/>
+      <c r="Z7" s="56"/>
+      <c r="AA7" s="57"/>
+      <c r="AB7" s="51"/>
+      <c r="AC7" s="51"/>
+      <c r="AD7" s="55"/>
+      <c r="AE7" s="56"/>
+      <c r="AF7" s="57"/>
+      <c r="AG7" s="51"/>
+      <c r="AH7" s="51"/>
+      <c r="AI7" s="51"/>
+      <c r="AJ7" s="51"/>
+      <c r="AK7" s="51"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="48"/>
-      <c r="C8" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="52"/>
-      <c r="O8" s="53"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
-      <c r="R8" s="64"/>
-      <c r="S8" s="64"/>
-      <c r="T8" s="64"/>
-      <c r="U8" s="64"/>
-      <c r="V8" s="52"/>
-      <c r="W8" s="57"/>
-      <c r="X8" s="64"/>
-      <c r="Y8" s="64"/>
-      <c r="Z8" s="52"/>
-      <c r="AA8" s="53"/>
-      <c r="AB8" s="64"/>
-      <c r="AC8" s="64"/>
-      <c r="AD8" s="54"/>
-      <c r="AE8" s="52"/>
-      <c r="AF8" s="53"/>
-      <c r="AG8" s="64"/>
-      <c r="AH8" s="64"/>
-      <c r="AI8" s="64"/>
-      <c r="AJ8" s="64"/>
-      <c r="AK8" s="64"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="53"/>
+      <c r="W8" s="58"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="53"/>
+      <c r="AA8" s="54"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="55"/>
+      <c r="AE8" s="53"/>
+      <c r="AF8" s="54"/>
+      <c r="AG8" s="65"/>
+      <c r="AH8" s="65"/>
+      <c r="AI8" s="65"/>
+      <c r="AJ8" s="65"/>
+      <c r="AK8" s="65"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="48"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="54"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="55"/>
-      <c r="O9" s="62"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="65"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="50"/>
-      <c r="V9" s="61"/>
-      <c r="W9" s="57"/>
-      <c r="X9" s="63"/>
-      <c r="Y9" s="50"/>
-      <c r="Z9" s="61"/>
-      <c r="AA9" s="62"/>
-      <c r="AB9" s="50"/>
-      <c r="AC9" s="50"/>
-      <c r="AD9" s="63"/>
-      <c r="AE9" s="55"/>
-      <c r="AF9" s="56"/>
-      <c r="AG9" s="50"/>
-      <c r="AH9" s="50"/>
-      <c r="AI9" s="50"/>
-      <c r="AJ9" s="50"/>
-      <c r="AK9" s="50"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="63"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="64"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="51"/>
+      <c r="U9" s="51"/>
+      <c r="V9" s="62"/>
+      <c r="W9" s="58"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="51"/>
+      <c r="Z9" s="62"/>
+      <c r="AA9" s="63"/>
+      <c r="AB9" s="51"/>
+      <c r="AC9" s="51"/>
+      <c r="AD9" s="64"/>
+      <c r="AE9" s="56"/>
+      <c r="AF9" s="57"/>
+      <c r="AG9" s="51"/>
+      <c r="AH9" s="51"/>
+      <c r="AI9" s="51"/>
+      <c r="AJ9" s="51"/>
+      <c r="AK9" s="51"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="48"/>
-      <c r="C10" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
-      <c r="U10" s="50"/>
-      <c r="V10" s="52"/>
-      <c r="W10" s="57"/>
-      <c r="X10" s="64"/>
-      <c r="Y10" s="64"/>
-      <c r="Z10" s="52"/>
-      <c r="AA10" s="56"/>
-      <c r="AB10" s="50"/>
-      <c r="AC10" s="50"/>
-      <c r="AD10" s="54"/>
-      <c r="AE10" s="55"/>
-      <c r="AF10" s="56"/>
-      <c r="AG10" s="50"/>
-      <c r="AH10" s="50"/>
-      <c r="AI10" s="50"/>
-      <c r="AJ10" s="50"/>
-      <c r="AK10" s="50"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="51"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="51"/>
+      <c r="U10" s="51"/>
+      <c r="V10" s="53"/>
+      <c r="W10" s="58"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="65"/>
+      <c r="Z10" s="53"/>
+      <c r="AA10" s="57"/>
+      <c r="AB10" s="51"/>
+      <c r="AC10" s="51"/>
+      <c r="AD10" s="55"/>
+      <c r="AE10" s="56"/>
+      <c r="AF10" s="57"/>
+      <c r="AG10" s="51"/>
+      <c r="AH10" s="51"/>
+      <c r="AI10" s="51"/>
+      <c r="AJ10" s="51"/>
+      <c r="AK10" s="51"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="48"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="55"/>
-      <c r="O11" s="56"/>
-      <c r="P11" s="50"/>
-      <c r="Q11" s="50"/>
-      <c r="R11" s="50"/>
-      <c r="S11" s="50"/>
-      <c r="T11" s="50"/>
-      <c r="U11" s="50"/>
-      <c r="V11" s="55"/>
-      <c r="W11" s="57"/>
-      <c r="X11" s="50"/>
-      <c r="Y11" s="50"/>
-      <c r="Z11" s="55"/>
-      <c r="AA11" s="56"/>
-      <c r="AB11" s="50"/>
-      <c r="AC11" s="50"/>
-      <c r="AD11" s="66"/>
-      <c r="AE11" s="55"/>
-      <c r="AF11" s="56"/>
-      <c r="AG11" s="50"/>
-      <c r="AH11" s="50"/>
-      <c r="AI11" s="50"/>
-      <c r="AJ11" s="50"/>
-      <c r="AK11" s="50"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="57"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="51"/>
+      <c r="U11" s="51"/>
+      <c r="V11" s="56"/>
+      <c r="W11" s="58"/>
+      <c r="X11" s="51"/>
+      <c r="Y11" s="51"/>
+      <c r="Z11" s="56"/>
+      <c r="AA11" s="57"/>
+      <c r="AB11" s="51"/>
+      <c r="AC11" s="51"/>
+      <c r="AD11" s="67"/>
+      <c r="AE11" s="56"/>
+      <c r="AF11" s="57"/>
+      <c r="AG11" s="51"/>
+      <c r="AH11" s="51"/>
+      <c r="AI11" s="51"/>
+      <c r="AJ11" s="51"/>
+      <c r="AK11" s="51"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="48"/>
-      <c r="C12" s="49" t="s">
-        <v>141</v>
-      </c>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="50"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="56"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="55"/>
-      <c r="W12" s="57"/>
-      <c r="X12" s="50"/>
-      <c r="Y12" s="50"/>
-      <c r="Z12" s="55"/>
-      <c r="AA12" s="56"/>
-      <c r="AB12" s="50"/>
-      <c r="AC12" s="50"/>
-      <c r="AD12" s="54"/>
-      <c r="AE12" s="55"/>
-      <c r="AF12" s="53"/>
-      <c r="AG12" s="64"/>
-      <c r="AH12" s="64"/>
-      <c r="AI12" s="64"/>
-      <c r="AJ12" s="64"/>
-      <c r="AK12" s="64"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="57"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="51"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="51"/>
+      <c r="U12" s="51"/>
+      <c r="V12" s="56"/>
+      <c r="W12" s="58"/>
+      <c r="X12" s="51"/>
+      <c r="Y12" s="51"/>
+      <c r="Z12" s="56"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="51"/>
+      <c r="AC12" s="51"/>
+      <c r="AD12" s="55"/>
+      <c r="AE12" s="56"/>
+      <c r="AF12" s="54"/>
+      <c r="AG12" s="65"/>
+      <c r="AH12" s="65"/>
+      <c r="AI12" s="65"/>
+      <c r="AJ12" s="65"/>
+      <c r="AK12" s="65"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="48"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="50"/>
-      <c r="K13" s="50"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="56"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="50"/>
-      <c r="V13" s="55"/>
-      <c r="W13" s="57"/>
-      <c r="X13" s="50"/>
-      <c r="Y13" s="50"/>
-      <c r="Z13" s="55"/>
-      <c r="AA13" s="56"/>
-      <c r="AB13" s="50"/>
-      <c r="AC13" s="50"/>
-      <c r="AD13" s="54"/>
-      <c r="AE13" s="55"/>
-      <c r="AF13" s="56"/>
-      <c r="AG13" s="50"/>
-      <c r="AH13" s="50"/>
-      <c r="AI13" s="50"/>
-      <c r="AJ13" s="50"/>
-      <c r="AK13" s="50"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="51"/>
+      <c r="S13" s="51"/>
+      <c r="T13" s="51"/>
+      <c r="U13" s="51"/>
+      <c r="V13" s="56"/>
+      <c r="W13" s="58"/>
+      <c r="X13" s="51"/>
+      <c r="Y13" s="51"/>
+      <c r="Z13" s="56"/>
+      <c r="AA13" s="57"/>
+      <c r="AB13" s="51"/>
+      <c r="AC13" s="51"/>
+      <c r="AD13" s="55"/>
+      <c r="AE13" s="56"/>
+      <c r="AF13" s="57"/>
+      <c r="AG13" s="51"/>
+      <c r="AH13" s="51"/>
+      <c r="AI13" s="51"/>
+      <c r="AJ13" s="51"/>
+      <c r="AK13" s="51"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="67" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="70"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="70"/>
-      <c r="N14" s="71"/>
-      <c r="O14" s="69"/>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="70"/>
-      <c r="R14" s="70"/>
-      <c r="S14" s="70"/>
-      <c r="T14" s="70"/>
-      <c r="U14" s="70"/>
-      <c r="V14" s="71"/>
-      <c r="W14" s="57"/>
-      <c r="X14" s="70"/>
-      <c r="Y14" s="70"/>
-      <c r="Z14" s="71"/>
-      <c r="AA14" s="69"/>
-      <c r="AB14" s="70"/>
-      <c r="AC14" s="70"/>
-      <c r="AD14" s="54"/>
-      <c r="AE14" s="71"/>
-      <c r="AF14" s="69"/>
-      <c r="AG14" s="70"/>
-      <c r="AH14" s="70"/>
-      <c r="AI14" s="70"/>
-      <c r="AJ14" s="70"/>
-      <c r="AK14" s="70"/>
+      <c r="B14" s="68" t="s">
+        <v>144</v>
+      </c>
+      <c r="C14" s="69" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="71"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="71"/>
+      <c r="S14" s="71"/>
+      <c r="T14" s="71"/>
+      <c r="U14" s="71"/>
+      <c r="V14" s="72"/>
+      <c r="W14" s="58"/>
+      <c r="X14" s="71"/>
+      <c r="Y14" s="71"/>
+      <c r="Z14" s="72"/>
+      <c r="AA14" s="70"/>
+      <c r="AB14" s="71"/>
+      <c r="AC14" s="71"/>
+      <c r="AD14" s="55"/>
+      <c r="AE14" s="72"/>
+      <c r="AF14" s="70"/>
+      <c r="AG14" s="71"/>
+      <c r="AH14" s="71"/>
+      <c r="AI14" s="71"/>
+      <c r="AJ14" s="71"/>
+      <c r="AK14" s="71"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="67"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="70"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="70"/>
-      <c r="J15" s="70"/>
-      <c r="K15" s="70"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="70"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="70"/>
-      <c r="Q15" s="70"/>
-      <c r="R15" s="70"/>
-      <c r="S15" s="70"/>
-      <c r="T15" s="70"/>
-      <c r="U15" s="70"/>
-      <c r="V15" s="71"/>
-      <c r="W15" s="57"/>
-      <c r="X15" s="70"/>
-      <c r="Y15" s="70"/>
-      <c r="Z15" s="71"/>
-      <c r="AA15" s="69"/>
-      <c r="AB15" s="70"/>
-      <c r="AC15" s="70"/>
-      <c r="AD15" s="54"/>
-      <c r="AE15" s="71"/>
-      <c r="AF15" s="69"/>
-      <c r="AG15" s="70"/>
-      <c r="AH15" s="70"/>
-      <c r="AI15" s="70"/>
-      <c r="AJ15" s="70"/>
-      <c r="AK15" s="70"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
+      <c r="V15" s="72"/>
+      <c r="W15" s="58"/>
+      <c r="X15" s="71"/>
+      <c r="Y15" s="71"/>
+      <c r="Z15" s="72"/>
+      <c r="AA15" s="70"/>
+      <c r="AB15" s="71"/>
+      <c r="AC15" s="71"/>
+      <c r="AD15" s="55"/>
+      <c r="AE15" s="72"/>
+      <c r="AF15" s="70"/>
+      <c r="AG15" s="71"/>
+      <c r="AH15" s="71"/>
+      <c r="AI15" s="71"/>
+      <c r="AJ15" s="71"/>
+      <c r="AK15" s="71"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="67"/>
-      <c r="C16" s="68" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="70"/>
-      <c r="J16" s="70"/>
-      <c r="K16" s="70"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="70"/>
-      <c r="N16" s="71"/>
-      <c r="O16" s="69"/>
-      <c r="P16" s="70"/>
-      <c r="Q16" s="70"/>
-      <c r="R16" s="70"/>
-      <c r="S16" s="70"/>
-      <c r="T16" s="70"/>
-      <c r="U16" s="70"/>
-      <c r="V16" s="71"/>
-      <c r="W16" s="57"/>
-      <c r="X16" s="70"/>
-      <c r="Y16" s="70"/>
-      <c r="Z16" s="71"/>
-      <c r="AA16" s="69"/>
-      <c r="AB16" s="70"/>
-      <c r="AC16" s="70"/>
-      <c r="AD16" s="54"/>
-      <c r="AE16" s="71"/>
-      <c r="AF16" s="69"/>
-      <c r="AG16" s="70"/>
-      <c r="AH16" s="70"/>
-      <c r="AI16" s="70"/>
-      <c r="AJ16" s="70"/>
-      <c r="AK16" s="70"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="69" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="71"/>
+      <c r="S16" s="71"/>
+      <c r="T16" s="71"/>
+      <c r="U16" s="71"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="58"/>
+      <c r="X16" s="71"/>
+      <c r="Y16" s="71"/>
+      <c r="Z16" s="72"/>
+      <c r="AA16" s="70"/>
+      <c r="AB16" s="71"/>
+      <c r="AC16" s="71"/>
+      <c r="AD16" s="55"/>
+      <c r="AE16" s="72"/>
+      <c r="AF16" s="70"/>
+      <c r="AG16" s="71"/>
+      <c r="AH16" s="71"/>
+      <c r="AI16" s="71"/>
+      <c r="AJ16" s="71"/>
+      <c r="AK16" s="71"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="67"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="63"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="70"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="69"/>
-      <c r="P17" s="70"/>
-      <c r="Q17" s="70"/>
-      <c r="R17" s="70"/>
-      <c r="S17" s="70"/>
-      <c r="T17" s="70"/>
-      <c r="U17" s="70"/>
-      <c r="V17" s="71"/>
-      <c r="W17" s="57"/>
-      <c r="X17" s="70"/>
-      <c r="Y17" s="70"/>
-      <c r="Z17" s="71"/>
-      <c r="AA17" s="69"/>
-      <c r="AB17" s="70"/>
-      <c r="AC17" s="70"/>
-      <c r="AD17" s="54"/>
-      <c r="AE17" s="71"/>
-      <c r="AF17" s="69"/>
-      <c r="AG17" s="70"/>
-      <c r="AH17" s="70"/>
-      <c r="AI17" s="70"/>
-      <c r="AJ17" s="70"/>
-      <c r="AK17" s="70"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="71"/>
+      <c r="U17" s="71"/>
+      <c r="V17" s="72"/>
+      <c r="W17" s="58"/>
+      <c r="X17" s="71"/>
+      <c r="Y17" s="71"/>
+      <c r="Z17" s="72"/>
+      <c r="AA17" s="70"/>
+      <c r="AB17" s="71"/>
+      <c r="AC17" s="71"/>
+      <c r="AD17" s="55"/>
+      <c r="AE17" s="72"/>
+      <c r="AF17" s="70"/>
+      <c r="AG17" s="71"/>
+      <c r="AH17" s="71"/>
+      <c r="AI17" s="71"/>
+      <c r="AJ17" s="71"/>
+      <c r="AK17" s="71"/>
       <c r="AN17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="67"/>
-      <c r="C18" s="68" t="s">
-        <v>146</v>
-      </c>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="70"/>
-      <c r="J18" s="70"/>
-      <c r="K18" s="70"/>
-      <c r="L18" s="54"/>
-      <c r="M18" s="70"/>
-      <c r="N18" s="71"/>
-      <c r="O18" s="69"/>
-      <c r="P18" s="70"/>
-      <c r="Q18" s="70"/>
-      <c r="R18" s="70"/>
-      <c r="S18" s="70"/>
-      <c r="T18" s="70"/>
-      <c r="U18" s="70"/>
-      <c r="V18" s="71"/>
-      <c r="W18" s="57"/>
-      <c r="X18" s="70"/>
-      <c r="Y18" s="70"/>
-      <c r="Z18" s="71"/>
-      <c r="AA18" s="69"/>
-      <c r="AB18" s="70"/>
-      <c r="AC18" s="70"/>
-      <c r="AD18" s="54"/>
-      <c r="AE18" s="71"/>
-      <c r="AF18" s="69"/>
-      <c r="AG18" s="70"/>
-      <c r="AH18" s="70"/>
-      <c r="AI18" s="70"/>
-      <c r="AJ18" s="70"/>
-      <c r="AK18" s="70"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="69" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="71"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="71"/>
+      <c r="S18" s="71"/>
+      <c r="T18" s="71"/>
+      <c r="U18" s="71"/>
+      <c r="V18" s="72"/>
+      <c r="W18" s="58"/>
+      <c r="X18" s="71"/>
+      <c r="Y18" s="71"/>
+      <c r="Z18" s="72"/>
+      <c r="AA18" s="70"/>
+      <c r="AB18" s="71"/>
+      <c r="AC18" s="71"/>
+      <c r="AD18" s="55"/>
+      <c r="AE18" s="72"/>
+      <c r="AF18" s="70"/>
+      <c r="AG18" s="71"/>
+      <c r="AH18" s="71"/>
+      <c r="AI18" s="71"/>
+      <c r="AJ18" s="71"/>
+      <c r="AK18" s="71"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="67"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="70"/>
-      <c r="J19" s="70"/>
-      <c r="K19" s="70"/>
-      <c r="L19" s="54"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="69"/>
-      <c r="P19" s="70"/>
-      <c r="Q19" s="70"/>
-      <c r="R19" s="70"/>
-      <c r="S19" s="70"/>
-      <c r="T19" s="70"/>
-      <c r="U19" s="70"/>
-      <c r="V19" s="71"/>
-      <c r="W19" s="57"/>
-      <c r="X19" s="70"/>
-      <c r="Y19" s="70"/>
-      <c r="Z19" s="71"/>
-      <c r="AA19" s="69"/>
-      <c r="AB19" s="70"/>
-      <c r="AC19" s="70"/>
-      <c r="AD19" s="54"/>
-      <c r="AE19" s="71"/>
-      <c r="AF19" s="69"/>
-      <c r="AG19" s="70"/>
-      <c r="AH19" s="70"/>
-      <c r="AI19" s="70"/>
-      <c r="AJ19" s="70"/>
-      <c r="AK19" s="70"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="72"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
+      <c r="U19" s="71"/>
+      <c r="V19" s="72"/>
+      <c r="W19" s="58"/>
+      <c r="X19" s="71"/>
+      <c r="Y19" s="71"/>
+      <c r="Z19" s="72"/>
+      <c r="AA19" s="70"/>
+      <c r="AB19" s="71"/>
+      <c r="AC19" s="71"/>
+      <c r="AD19" s="55"/>
+      <c r="AE19" s="72"/>
+      <c r="AF19" s="70"/>
+      <c r="AG19" s="71"/>
+      <c r="AH19" s="71"/>
+      <c r="AI19" s="71"/>
+      <c r="AJ19" s="71"/>
+      <c r="AK19" s="71"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="67"/>
-      <c r="C20" s="68" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="70"/>
-      <c r="L20" s="54"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="71"/>
-      <c r="O20" s="69"/>
-      <c r="P20" s="70"/>
-      <c r="Q20" s="70"/>
-      <c r="R20" s="70"/>
-      <c r="S20" s="70"/>
-      <c r="T20" s="70"/>
-      <c r="U20" s="70"/>
-      <c r="V20" s="71"/>
-      <c r="W20" s="57"/>
-      <c r="X20" s="70"/>
-      <c r="Y20" s="70"/>
-      <c r="Z20" s="71"/>
-      <c r="AA20" s="69"/>
-      <c r="AB20" s="70"/>
-      <c r="AC20" s="70"/>
-      <c r="AD20" s="54"/>
-      <c r="AE20" s="71"/>
-      <c r="AF20" s="69"/>
-      <c r="AG20" s="70"/>
-      <c r="AH20" s="70"/>
-      <c r="AI20" s="70"/>
-      <c r="AJ20" s="70"/>
-      <c r="AK20" s="70"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="69" t="s">
+        <v>149</v>
+      </c>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="72"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="71"/>
+      <c r="S20" s="71"/>
+      <c r="T20" s="71"/>
+      <c r="U20" s="71"/>
+      <c r="V20" s="72"/>
+      <c r="W20" s="58"/>
+      <c r="X20" s="71"/>
+      <c r="Y20" s="71"/>
+      <c r="Z20" s="72"/>
+      <c r="AA20" s="70"/>
+      <c r="AB20" s="71"/>
+      <c r="AC20" s="71"/>
+      <c r="AD20" s="55"/>
+      <c r="AE20" s="72"/>
+      <c r="AF20" s="70"/>
+      <c r="AG20" s="71"/>
+      <c r="AH20" s="71"/>
+      <c r="AI20" s="71"/>
+      <c r="AJ20" s="71"/>
+      <c r="AK20" s="71"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="67"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="63"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="70"/>
-      <c r="L21" s="54"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="69"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="70"/>
-      <c r="R21" s="70"/>
-      <c r="S21" s="70"/>
-      <c r="T21" s="70"/>
-      <c r="U21" s="70"/>
-      <c r="V21" s="71"/>
-      <c r="W21" s="57"/>
-      <c r="X21" s="70"/>
-      <c r="Y21" s="70"/>
-      <c r="Z21" s="71"/>
-      <c r="AA21" s="69"/>
-      <c r="AB21" s="70"/>
-      <c r="AC21" s="70"/>
-      <c r="AD21" s="54"/>
-      <c r="AE21" s="71"/>
-      <c r="AF21" s="69"/>
-      <c r="AG21" s="70"/>
-      <c r="AH21" s="70"/>
-      <c r="AI21" s="70"/>
-      <c r="AJ21" s="70"/>
-      <c r="AK21" s="70"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="71"/>
+      <c r="T21" s="71"/>
+      <c r="U21" s="71"/>
+      <c r="V21" s="72"/>
+      <c r="W21" s="58"/>
+      <c r="X21" s="71"/>
+      <c r="Y21" s="71"/>
+      <c r="Z21" s="72"/>
+      <c r="AA21" s="70"/>
+      <c r="AB21" s="71"/>
+      <c r="AC21" s="71"/>
+      <c r="AD21" s="55"/>
+      <c r="AE21" s="72"/>
+      <c r="AF21" s="70"/>
+      <c r="AG21" s="71"/>
+      <c r="AH21" s="71"/>
+      <c r="AI21" s="71"/>
+      <c r="AJ21" s="71"/>
+      <c r="AK21" s="71"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="67"/>
-      <c r="C22" s="68" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="70"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="69"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="70"/>
-      <c r="R22" s="70"/>
-      <c r="S22" s="70"/>
-      <c r="T22" s="70"/>
-      <c r="U22" s="70"/>
-      <c r="V22" s="71"/>
-      <c r="W22" s="57"/>
-      <c r="X22" s="70"/>
-      <c r="Y22" s="70"/>
-      <c r="Z22" s="71"/>
-      <c r="AA22" s="69"/>
-      <c r="AB22" s="70"/>
-      <c r="AC22" s="70"/>
-      <c r="AD22" s="54"/>
-      <c r="AE22" s="71"/>
-      <c r="AF22" s="69"/>
-      <c r="AG22" s="70"/>
-      <c r="AH22" s="70"/>
-      <c r="AI22" s="70"/>
-      <c r="AJ22" s="70"/>
-      <c r="AK22" s="70"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="71"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="71"/>
+      <c r="S22" s="71"/>
+      <c r="T22" s="71"/>
+      <c r="U22" s="71"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="58"/>
+      <c r="X22" s="71"/>
+      <c r="Y22" s="71"/>
+      <c r="Z22" s="72"/>
+      <c r="AA22" s="70"/>
+      <c r="AB22" s="71"/>
+      <c r="AC22" s="71"/>
+      <c r="AD22" s="55"/>
+      <c r="AE22" s="72"/>
+      <c r="AF22" s="70"/>
+      <c r="AG22" s="71"/>
+      <c r="AH22" s="71"/>
+      <c r="AI22" s="71"/>
+      <c r="AJ22" s="71"/>
+      <c r="AK22" s="71"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="67"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="70"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="70"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="69"/>
-      <c r="P23" s="70"/>
-      <c r="Q23" s="70"/>
-      <c r="R23" s="70"/>
-      <c r="S23" s="70"/>
-      <c r="T23" s="70"/>
-      <c r="U23" s="70"/>
-      <c r="V23" s="71"/>
-      <c r="W23" s="57"/>
-      <c r="X23" s="70"/>
-      <c r="Y23" s="70"/>
-      <c r="Z23" s="71"/>
-      <c r="AA23" s="69"/>
-      <c r="AB23" s="70"/>
-      <c r="AC23" s="70"/>
-      <c r="AD23" s="54"/>
-      <c r="AE23" s="71"/>
-      <c r="AF23" s="69"/>
-      <c r="AG23" s="70"/>
-      <c r="AH23" s="70"/>
-      <c r="AI23" s="70"/>
-      <c r="AJ23" s="70"/>
-      <c r="AK23" s="70"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="71"/>
+      <c r="T23" s="71"/>
+      <c r="U23" s="71"/>
+      <c r="V23" s="72"/>
+      <c r="W23" s="58"/>
+      <c r="X23" s="71"/>
+      <c r="Y23" s="71"/>
+      <c r="Z23" s="72"/>
+      <c r="AA23" s="70"/>
+      <c r="AB23" s="71"/>
+      <c r="AC23" s="71"/>
+      <c r="AD23" s="55"/>
+      <c r="AE23" s="72"/>
+      <c r="AF23" s="70"/>
+      <c r="AG23" s="71"/>
+      <c r="AH23" s="71"/>
+      <c r="AI23" s="71"/>
+      <c r="AJ23" s="71"/>
+      <c r="AK23" s="71"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="67"/>
-      <c r="C24" s="68" t="s">
-        <v>149</v>
-      </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="70"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="71"/>
-      <c r="O24" s="69"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="70"/>
-      <c r="R24" s="70"/>
-      <c r="S24" s="70"/>
-      <c r="T24" s="70"/>
-      <c r="U24" s="70"/>
-      <c r="V24" s="71"/>
-      <c r="W24" s="57"/>
-      <c r="X24" s="70"/>
-      <c r="Y24" s="70"/>
-      <c r="Z24" s="71"/>
-      <c r="AA24" s="69"/>
-      <c r="AB24" s="70"/>
-      <c r="AC24" s="70"/>
-      <c r="AD24" s="54"/>
-      <c r="AE24" s="71"/>
-      <c r="AF24" s="69"/>
-      <c r="AG24" s="70"/>
-      <c r="AH24" s="70"/>
-      <c r="AI24" s="70"/>
-      <c r="AJ24" s="70"/>
-      <c r="AK24" s="70"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="69" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="71"/>
+      <c r="S24" s="71"/>
+      <c r="T24" s="71"/>
+      <c r="U24" s="71"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="58"/>
+      <c r="X24" s="71"/>
+      <c r="Y24" s="71"/>
+      <c r="Z24" s="72"/>
+      <c r="AA24" s="70"/>
+      <c r="AB24" s="71"/>
+      <c r="AC24" s="71"/>
+      <c r="AD24" s="55"/>
+      <c r="AE24" s="72"/>
+      <c r="AF24" s="70"/>
+      <c r="AG24" s="71"/>
+      <c r="AH24" s="71"/>
+      <c r="AI24" s="71"/>
+      <c r="AJ24" s="71"/>
+      <c r="AK24" s="71"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="67"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="54"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="71"/>
-      <c r="O25" s="69"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
-      <c r="S25" s="70"/>
-      <c r="T25" s="70"/>
-      <c r="U25" s="70"/>
-      <c r="V25" s="71"/>
-      <c r="W25" s="57"/>
-      <c r="X25" s="70"/>
-      <c r="Y25" s="70"/>
-      <c r="Z25" s="71"/>
-      <c r="AA25" s="69"/>
-      <c r="AB25" s="70"/>
-      <c r="AC25" s="70"/>
-      <c r="AD25" s="54"/>
-      <c r="AE25" s="71"/>
-      <c r="AF25" s="69"/>
-      <c r="AG25" s="70"/>
-      <c r="AH25" s="70"/>
-      <c r="AI25" s="70"/>
-      <c r="AJ25" s="70"/>
-      <c r="AK25" s="70"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="71"/>
+      <c r="T25" s="71"/>
+      <c r="U25" s="71"/>
+      <c r="V25" s="72"/>
+      <c r="W25" s="58"/>
+      <c r="X25" s="71"/>
+      <c r="Y25" s="71"/>
+      <c r="Z25" s="72"/>
+      <c r="AA25" s="70"/>
+      <c r="AB25" s="71"/>
+      <c r="AC25" s="71"/>
+      <c r="AD25" s="55"/>
+      <c r="AE25" s="72"/>
+      <c r="AF25" s="70"/>
+      <c r="AG25" s="71"/>
+      <c r="AH25" s="71"/>
+      <c r="AI25" s="71"/>
+      <c r="AJ25" s="71"/>
+      <c r="AK25" s="71"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="48" t="s">
-        <v>150</v>
-      </c>
-      <c r="C26" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="55"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="64"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
-      <c r="L26" s="54"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="56"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="55"/>
-      <c r="W26" s="57"/>
-      <c r="X26" s="50"/>
-      <c r="Y26" s="50"/>
-      <c r="Z26" s="55"/>
-      <c r="AA26" s="56"/>
-      <c r="AB26" s="50"/>
-      <c r="AC26" s="50"/>
-      <c r="AD26" s="54"/>
-      <c r="AE26" s="55"/>
-      <c r="AF26" s="56"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
+      <c r="B26" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="51"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="51"/>
+      <c r="R26" s="51"/>
+      <c r="S26" s="51"/>
+      <c r="T26" s="51"/>
+      <c r="U26" s="51"/>
+      <c r="V26" s="56"/>
+      <c r="W26" s="58"/>
+      <c r="X26" s="51"/>
+      <c r="Y26" s="51"/>
+      <c r="Z26" s="56"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="51"/>
+      <c r="AC26" s="51"/>
+      <c r="AD26" s="55"/>
+      <c r="AE26" s="56"/>
+      <c r="AF26" s="57"/>
+      <c r="AG26" s="51"/>
+      <c r="AH26" s="51"/>
+      <c r="AI26" s="51"/>
+      <c r="AJ26" s="51"/>
+      <c r="AK26" s="51"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="48"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="55"/>
-      <c r="W27" s="57"/>
-      <c r="X27" s="50"/>
-      <c r="Y27" s="50"/>
-      <c r="Z27" s="55"/>
-      <c r="AA27" s="56"/>
-      <c r="AB27" s="50"/>
-      <c r="AC27" s="50"/>
-      <c r="AD27" s="54"/>
-      <c r="AE27" s="55"/>
-      <c r="AF27" s="56"/>
-      <c r="AG27" s="50"/>
-      <c r="AH27" s="50"/>
-      <c r="AI27" s="50"/>
-      <c r="AJ27" s="50"/>
-      <c r="AK27" s="50"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="57"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="51"/>
+      <c r="R27" s="51"/>
+      <c r="S27" s="51"/>
+      <c r="T27" s="51"/>
+      <c r="U27" s="51"/>
+      <c r="V27" s="56"/>
+      <c r="W27" s="58"/>
+      <c r="X27" s="51"/>
+      <c r="Y27" s="51"/>
+      <c r="Z27" s="56"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="51"/>
+      <c r="AC27" s="51"/>
+      <c r="AD27" s="55"/>
+      <c r="AE27" s="56"/>
+      <c r="AF27" s="57"/>
+      <c r="AG27" s="51"/>
+      <c r="AH27" s="51"/>
+      <c r="AI27" s="51"/>
+      <c r="AJ27" s="51"/>
+      <c r="AK27" s="51"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="48"/>
-      <c r="C28" s="49" t="s">
-        <v>152</v>
-      </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="53"/>
-      <c r="I28" s="64"/>
-      <c r="J28" s="64"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="54"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="56"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="50"/>
-      <c r="V28" s="55"/>
-      <c r="W28" s="57"/>
-      <c r="X28" s="50"/>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="55"/>
-      <c r="AA28" s="56"/>
-      <c r="AB28" s="50"/>
-      <c r="AC28" s="50"/>
-      <c r="AD28" s="54"/>
-      <c r="AE28" s="55"/>
-      <c r="AF28" s="56"/>
-      <c r="AG28" s="50"/>
-      <c r="AH28" s="50"/>
-      <c r="AI28" s="50"/>
-      <c r="AJ28" s="50"/>
-      <c r="AK28" s="50"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="51"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="57"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="51"/>
+      <c r="R28" s="51"/>
+      <c r="S28" s="51"/>
+      <c r="T28" s="51"/>
+      <c r="U28" s="51"/>
+      <c r="V28" s="56"/>
+      <c r="W28" s="58"/>
+      <c r="X28" s="51"/>
+      <c r="Y28" s="51"/>
+      <c r="Z28" s="56"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="51"/>
+      <c r="AC28" s="51"/>
+      <c r="AD28" s="55"/>
+      <c r="AE28" s="56"/>
+      <c r="AF28" s="57"/>
+      <c r="AG28" s="51"/>
+      <c r="AH28" s="51"/>
+      <c r="AI28" s="51"/>
+      <c r="AJ28" s="51"/>
+      <c r="AK28" s="51"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="48"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="56"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="50"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="50"/>
-      <c r="V29" s="55"/>
-      <c r="W29" s="57"/>
-      <c r="X29" s="50"/>
-      <c r="Y29" s="50"/>
-      <c r="Z29" s="55"/>
-      <c r="AA29" s="56"/>
-      <c r="AB29" s="50"/>
-      <c r="AC29" s="50"/>
-      <c r="AD29" s="54"/>
-      <c r="AE29" s="55"/>
-      <c r="AF29" s="56"/>
-      <c r="AG29" s="50"/>
-      <c r="AH29" s="50"/>
-      <c r="AI29" s="50"/>
-      <c r="AJ29" s="50"/>
-      <c r="AK29" s="50"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="51"/>
+      <c r="R29" s="51"/>
+      <c r="S29" s="51"/>
+      <c r="T29" s="51"/>
+      <c r="U29" s="51"/>
+      <c r="V29" s="56"/>
+      <c r="W29" s="58"/>
+      <c r="X29" s="51"/>
+      <c r="Y29" s="51"/>
+      <c r="Z29" s="56"/>
+      <c r="AA29" s="57"/>
+      <c r="AB29" s="51"/>
+      <c r="AC29" s="51"/>
+      <c r="AD29" s="55"/>
+      <c r="AE29" s="56"/>
+      <c r="AF29" s="57"/>
+      <c r="AG29" s="51"/>
+      <c r="AH29" s="51"/>
+      <c r="AI29" s="51"/>
+      <c r="AJ29" s="51"/>
+      <c r="AK29" s="51"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="48"/>
-      <c r="C30" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="54"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="56"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="50"/>
-      <c r="V30" s="55"/>
-      <c r="W30" s="57"/>
-      <c r="X30" s="50"/>
-      <c r="Y30" s="50"/>
-      <c r="Z30" s="55"/>
-      <c r="AA30" s="56"/>
-      <c r="AB30" s="50"/>
-      <c r="AC30" s="50"/>
-      <c r="AD30" s="54"/>
-      <c r="AE30" s="55"/>
-      <c r="AF30" s="56"/>
-      <c r="AG30" s="50"/>
-      <c r="AH30" s="50"/>
-      <c r="AI30" s="50"/>
-      <c r="AJ30" s="50"/>
-      <c r="AK30" s="50"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="51"/>
+      <c r="R30" s="51"/>
+      <c r="S30" s="51"/>
+      <c r="T30" s="51"/>
+      <c r="U30" s="51"/>
+      <c r="V30" s="56"/>
+      <c r="W30" s="58"/>
+      <c r="X30" s="51"/>
+      <c r="Y30" s="51"/>
+      <c r="Z30" s="56"/>
+      <c r="AA30" s="57"/>
+      <c r="AB30" s="51"/>
+      <c r="AC30" s="51"/>
+      <c r="AD30" s="55"/>
+      <c r="AE30" s="56"/>
+      <c r="AF30" s="57"/>
+      <c r="AG30" s="51"/>
+      <c r="AH30" s="51"/>
+      <c r="AI30" s="51"/>
+      <c r="AJ30" s="51"/>
+      <c r="AK30" s="51"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="48"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="75"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="61"/>
-      <c r="O31" s="56"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="50"/>
-      <c r="V31" s="55"/>
-      <c r="W31" s="57"/>
-      <c r="X31" s="50"/>
-      <c r="Y31" s="50"/>
-      <c r="Z31" s="55"/>
-      <c r="AA31" s="56"/>
-      <c r="AB31" s="50"/>
-      <c r="AC31" s="50"/>
-      <c r="AD31" s="54"/>
-      <c r="AE31" s="55"/>
-      <c r="AF31" s="56"/>
-      <c r="AG31" s="50"/>
-      <c r="AH31" s="50"/>
-      <c r="AI31" s="50"/>
-      <c r="AJ31" s="50"/>
-      <c r="AK31" s="50"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="76"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="57"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="51"/>
+      <c r="R31" s="51"/>
+      <c r="S31" s="51"/>
+      <c r="T31" s="51"/>
+      <c r="U31" s="51"/>
+      <c r="V31" s="56"/>
+      <c r="W31" s="58"/>
+      <c r="X31" s="51"/>
+      <c r="Y31" s="51"/>
+      <c r="Z31" s="56"/>
+      <c r="AA31" s="57"/>
+      <c r="AB31" s="51"/>
+      <c r="AC31" s="51"/>
+      <c r="AD31" s="55"/>
+      <c r="AE31" s="56"/>
+      <c r="AF31" s="57"/>
+      <c r="AG31" s="51"/>
+      <c r="AH31" s="51"/>
+      <c r="AI31" s="51"/>
+      <c r="AJ31" s="51"/>
+      <c r="AK31" s="51"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="48"/>
-      <c r="C32" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="55"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="54"/>
-      <c r="M32" s="64"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="56"/>
-      <c r="P32" s="50"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50"/>
-      <c r="S32" s="50"/>
-      <c r="T32" s="50"/>
-      <c r="U32" s="50"/>
-      <c r="V32" s="55"/>
-      <c r="W32" s="57"/>
-      <c r="X32" s="50"/>
-      <c r="Y32" s="50"/>
-      <c r="Z32" s="55"/>
-      <c r="AA32" s="56"/>
-      <c r="AB32" s="50"/>
-      <c r="AC32" s="50"/>
-      <c r="AD32" s="54"/>
-      <c r="AE32" s="55"/>
-      <c r="AF32" s="56"/>
-      <c r="AG32" s="50"/>
-      <c r="AH32" s="50"/>
-      <c r="AI32" s="50"/>
-      <c r="AJ32" s="50"/>
-      <c r="AK32" s="50"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
+      <c r="K32" s="51"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="57"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="51"/>
+      <c r="R32" s="51"/>
+      <c r="S32" s="51"/>
+      <c r="T32" s="51"/>
+      <c r="U32" s="51"/>
+      <c r="V32" s="56"/>
+      <c r="W32" s="58"/>
+      <c r="X32" s="51"/>
+      <c r="Y32" s="51"/>
+      <c r="Z32" s="56"/>
+      <c r="AA32" s="57"/>
+      <c r="AB32" s="51"/>
+      <c r="AC32" s="51"/>
+      <c r="AD32" s="55"/>
+      <c r="AE32" s="56"/>
+      <c r="AF32" s="57"/>
+      <c r="AG32" s="51"/>
+      <c r="AH32" s="51"/>
+      <c r="AI32" s="51"/>
+      <c r="AJ32" s="51"/>
+      <c r="AK32" s="51"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="48"/>
-      <c r="C33" s="49"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="55"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
-      <c r="L33" s="54"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="61"/>
-      <c r="O33" s="56"/>
-      <c r="P33" s="50"/>
-      <c r="Q33" s="50"/>
-      <c r="R33" s="50"/>
-      <c r="S33" s="50"/>
-      <c r="T33" s="50"/>
-      <c r="U33" s="50"/>
-      <c r="V33" s="55"/>
-      <c r="W33" s="57"/>
-      <c r="X33" s="50"/>
-      <c r="Y33" s="50"/>
-      <c r="Z33" s="55"/>
-      <c r="AA33" s="56"/>
-      <c r="AB33" s="50"/>
-      <c r="AC33" s="50"/>
-      <c r="AD33" s="54"/>
-      <c r="AE33" s="55"/>
-      <c r="AF33" s="56"/>
-      <c r="AG33" s="50"/>
-      <c r="AH33" s="50"/>
-      <c r="AI33" s="50"/>
-      <c r="AJ33" s="50"/>
-      <c r="AK33" s="50"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="51"/>
+      <c r="N33" s="62"/>
+      <c r="O33" s="57"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="51"/>
+      <c r="R33" s="51"/>
+      <c r="S33" s="51"/>
+      <c r="T33" s="51"/>
+      <c r="U33" s="51"/>
+      <c r="V33" s="56"/>
+      <c r="W33" s="58"/>
+      <c r="X33" s="51"/>
+      <c r="Y33" s="51"/>
+      <c r="Z33" s="56"/>
+      <c r="AA33" s="57"/>
+      <c r="AB33" s="51"/>
+      <c r="AC33" s="51"/>
+      <c r="AD33" s="55"/>
+      <c r="AE33" s="56"/>
+      <c r="AF33" s="57"/>
+      <c r="AG33" s="51"/>
+      <c r="AH33" s="51"/>
+      <c r="AI33" s="51"/>
+      <c r="AJ33" s="51"/>
+      <c r="AK33" s="51"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="67" t="s">
-        <v>155</v>
-      </c>
-      <c r="C34" s="76" t="s">
-        <v>156</v>
-      </c>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="70"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="54"/>
-      <c r="M34" s="64"/>
-      <c r="N34" s="52"/>
-      <c r="O34" s="53"/>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="64"/>
-      <c r="R34" s="64"/>
-      <c r="S34" s="70"/>
-      <c r="T34" s="70"/>
-      <c r="U34" s="70"/>
-      <c r="V34" s="71"/>
-      <c r="W34" s="57"/>
-      <c r="X34" s="70"/>
-      <c r="Y34" s="70"/>
-      <c r="Z34" s="71"/>
-      <c r="AA34" s="69"/>
-      <c r="AB34" s="70"/>
-      <c r="AC34" s="70"/>
-      <c r="AD34" s="54"/>
-      <c r="AE34" s="71"/>
-      <c r="AF34" s="69"/>
-      <c r="AG34" s="70"/>
-      <c r="AH34" s="70"/>
-      <c r="AI34" s="70"/>
-      <c r="AJ34" s="70"/>
-      <c r="AK34" s="70"/>
+      <c r="B34" s="68" t="s">
+        <v>157</v>
+      </c>
+      <c r="C34" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="71"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="54"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="65"/>
+      <c r="R34" s="65"/>
+      <c r="S34" s="71"/>
+      <c r="T34" s="71"/>
+      <c r="U34" s="71"/>
+      <c r="V34" s="72"/>
+      <c r="W34" s="58"/>
+      <c r="X34" s="71"/>
+      <c r="Y34" s="71"/>
+      <c r="Z34" s="72"/>
+      <c r="AA34" s="70"/>
+      <c r="AB34" s="71"/>
+      <c r="AC34" s="71"/>
+      <c r="AD34" s="55"/>
+      <c r="AE34" s="72"/>
+      <c r="AF34" s="70"/>
+      <c r="AG34" s="71"/>
+      <c r="AH34" s="71"/>
+      <c r="AI34" s="71"/>
+      <c r="AJ34" s="71"/>
+      <c r="AK34" s="71"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="67"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="70"/>
-      <c r="K35" s="77"/>
-      <c r="L35" s="54"/>
-      <c r="M35" s="70"/>
-      <c r="N35" s="61"/>
-      <c r="O35" s="69"/>
-      <c r="P35" s="63"/>
-      <c r="Q35" s="70"/>
-      <c r="R35" s="78"/>
-      <c r="S35" s="78"/>
-      <c r="T35" s="59"/>
-      <c r="U35" s="70"/>
-      <c r="V35" s="71"/>
-      <c r="W35" s="57"/>
-      <c r="X35" s="70"/>
-      <c r="Y35" s="70"/>
-      <c r="Z35" s="71"/>
-      <c r="AA35" s="69"/>
-      <c r="AB35" s="70"/>
-      <c r="AC35" s="70"/>
-      <c r="AD35" s="54"/>
-      <c r="AE35" s="71"/>
-      <c r="AF35" s="69"/>
-      <c r="AG35" s="70"/>
-      <c r="AH35" s="70"/>
-      <c r="AI35" s="70"/>
-      <c r="AJ35" s="70"/>
-      <c r="AK35" s="70"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="78"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="71"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="64"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="79"/>
+      <c r="S35" s="79"/>
+      <c r="T35" s="60"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="72"/>
+      <c r="W35" s="58"/>
+      <c r="X35" s="71"/>
+      <c r="Y35" s="71"/>
+      <c r="Z35" s="72"/>
+      <c r="AA35" s="70"/>
+      <c r="AB35" s="71"/>
+      <c r="AC35" s="71"/>
+      <c r="AD35" s="55"/>
+      <c r="AE35" s="72"/>
+      <c r="AF35" s="70"/>
+      <c r="AG35" s="71"/>
+      <c r="AH35" s="71"/>
+      <c r="AI35" s="71"/>
+      <c r="AJ35" s="71"/>
+      <c r="AK35" s="71"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="67"/>
-      <c r="C36" s="76" t="s">
-        <v>157</v>
-      </c>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="73"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="70"/>
-      <c r="K36" s="70"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="64"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="53"/>
-      <c r="P36" s="64"/>
-      <c r="Q36" s="70"/>
-      <c r="R36" s="70"/>
-      <c r="S36" s="70"/>
-      <c r="T36" s="70"/>
-      <c r="U36" s="70"/>
-      <c r="V36" s="71"/>
-      <c r="W36" s="57"/>
-      <c r="X36" s="70"/>
-      <c r="Y36" s="70"/>
-      <c r="Z36" s="71"/>
-      <c r="AA36" s="69"/>
-      <c r="AB36" s="70"/>
-      <c r="AC36" s="70"/>
-      <c r="AD36" s="54"/>
-      <c r="AE36" s="71"/>
-      <c r="AF36" s="69"/>
-      <c r="AG36" s="70"/>
-      <c r="AH36" s="70"/>
-      <c r="AI36" s="70"/>
-      <c r="AJ36" s="70"/>
-      <c r="AK36" s="70"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="72"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="54"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="71"/>
+      <c r="S36" s="71"/>
+      <c r="T36" s="71"/>
+      <c r="U36" s="71"/>
+      <c r="V36" s="72"/>
+      <c r="W36" s="58"/>
+      <c r="X36" s="71"/>
+      <c r="Y36" s="71"/>
+      <c r="Z36" s="72"/>
+      <c r="AA36" s="70"/>
+      <c r="AB36" s="71"/>
+      <c r="AC36" s="71"/>
+      <c r="AD36" s="55"/>
+      <c r="AE36" s="72"/>
+      <c r="AF36" s="70"/>
+      <c r="AG36" s="71"/>
+      <c r="AH36" s="71"/>
+      <c r="AI36" s="71"/>
+      <c r="AJ36" s="71"/>
+      <c r="AK36" s="71"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="67"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="73"/>
-      <c r="G37" s="71"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="70"/>
-      <c r="K37" s="77"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="70"/>
-      <c r="N37" s="71"/>
-      <c r="O37" s="69"/>
-      <c r="P37" s="63"/>
-      <c r="Q37" s="70"/>
-      <c r="R37" s="78"/>
-      <c r="S37" s="78"/>
-      <c r="T37" s="59"/>
-      <c r="U37" s="70"/>
-      <c r="V37" s="71"/>
-      <c r="W37" s="57"/>
-      <c r="X37" s="70"/>
-      <c r="Y37" s="70"/>
-      <c r="Z37" s="71"/>
-      <c r="AA37" s="69"/>
-      <c r="AB37" s="70"/>
-      <c r="AC37" s="70"/>
-      <c r="AD37" s="54"/>
-      <c r="AE37" s="71"/>
-      <c r="AF37" s="69"/>
-      <c r="AG37" s="70"/>
-      <c r="AH37" s="70"/>
-      <c r="AI37" s="70"/>
-      <c r="AJ37" s="70"/>
-      <c r="AK37" s="70"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="72"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="78"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="72"/>
+      <c r="O37" s="70"/>
+      <c r="P37" s="64"/>
+      <c r="Q37" s="71"/>
+      <c r="R37" s="79"/>
+      <c r="S37" s="79"/>
+      <c r="T37" s="60"/>
+      <c r="U37" s="71"/>
+      <c r="V37" s="72"/>
+      <c r="W37" s="58"/>
+      <c r="X37" s="71"/>
+      <c r="Y37" s="71"/>
+      <c r="Z37" s="72"/>
+      <c r="AA37" s="70"/>
+      <c r="AB37" s="71"/>
+      <c r="AC37" s="71"/>
+      <c r="AD37" s="55"/>
+      <c r="AE37" s="72"/>
+      <c r="AF37" s="70"/>
+      <c r="AG37" s="71"/>
+      <c r="AH37" s="71"/>
+      <c r="AI37" s="71"/>
+      <c r="AJ37" s="71"/>
+      <c r="AK37" s="71"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="67"/>
-      <c r="C38" s="76" t="s">
-        <v>158</v>
-      </c>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="73"/>
-      <c r="G38" s="71"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="54"/>
-      <c r="M38" s="70"/>
-      <c r="N38" s="71"/>
-      <c r="O38" s="53"/>
-      <c r="P38" s="64"/>
-      <c r="Q38" s="64"/>
-      <c r="R38" s="64"/>
-      <c r="S38" s="64"/>
-      <c r="T38" s="64"/>
-      <c r="U38" s="64"/>
-      <c r="V38" s="52"/>
-      <c r="W38" s="57"/>
-      <c r="X38" s="64"/>
-      <c r="Y38" s="64"/>
-      <c r="Z38" s="71"/>
-      <c r="AA38" s="69"/>
-      <c r="AB38" s="70"/>
-      <c r="AC38" s="70"/>
-      <c r="AD38" s="54"/>
-      <c r="AE38" s="71"/>
-      <c r="AF38" s="69"/>
-      <c r="AG38" s="70"/>
-      <c r="AH38" s="70"/>
-      <c r="AI38" s="70"/>
-      <c r="AJ38" s="70"/>
-      <c r="AK38" s="70"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="77" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="72"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="71"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="54"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="65"/>
+      <c r="T38" s="65"/>
+      <c r="U38" s="65"/>
+      <c r="V38" s="53"/>
+      <c r="W38" s="58"/>
+      <c r="X38" s="65"/>
+      <c r="Y38" s="65"/>
+      <c r="Z38" s="72"/>
+      <c r="AA38" s="70"/>
+      <c r="AB38" s="71"/>
+      <c r="AC38" s="71"/>
+      <c r="AD38" s="55"/>
+      <c r="AE38" s="72"/>
+      <c r="AF38" s="70"/>
+      <c r="AG38" s="71"/>
+      <c r="AH38" s="71"/>
+      <c r="AI38" s="71"/>
+      <c r="AJ38" s="71"/>
+      <c r="AK38" s="71"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="67"/>
-      <c r="C39" s="76"/>
-      <c r="D39" s="70"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="70"/>
-      <c r="K39" s="70"/>
-      <c r="L39" s="54"/>
-      <c r="M39" s="70"/>
-      <c r="N39" s="71"/>
-      <c r="O39" s="69"/>
-      <c r="P39" s="70"/>
-      <c r="Q39" s="70"/>
-      <c r="R39" s="77"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="70"/>
-      <c r="U39" s="70"/>
-      <c r="V39" s="71"/>
-      <c r="W39" s="57"/>
-      <c r="X39" s="70"/>
-      <c r="Y39" s="70"/>
-      <c r="Z39" s="71"/>
-      <c r="AA39" s="69"/>
-      <c r="AB39" s="70"/>
-      <c r="AC39" s="70"/>
-      <c r="AD39" s="54"/>
-      <c r="AE39" s="71"/>
-      <c r="AF39" s="69"/>
-      <c r="AG39" s="70"/>
-      <c r="AH39" s="70"/>
-      <c r="AI39" s="70"/>
-      <c r="AJ39" s="70"/>
-      <c r="AK39" s="70"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="74"/>
+      <c r="G39" s="72"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="72"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="78"/>
+      <c r="S39" s="78"/>
+      <c r="T39" s="71"/>
+      <c r="U39" s="71"/>
+      <c r="V39" s="72"/>
+      <c r="W39" s="58"/>
+      <c r="X39" s="71"/>
+      <c r="Y39" s="71"/>
+      <c r="Z39" s="72"/>
+      <c r="AA39" s="70"/>
+      <c r="AB39" s="71"/>
+      <c r="AC39" s="71"/>
+      <c r="AD39" s="55"/>
+      <c r="AE39" s="72"/>
+      <c r="AF39" s="70"/>
+      <c r="AG39" s="71"/>
+      <c r="AH39" s="71"/>
+      <c r="AI39" s="71"/>
+      <c r="AJ39" s="71"/>
+      <c r="AK39" s="71"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="67"/>
-      <c r="C40" s="76" t="s">
-        <v>159</v>
-      </c>
-      <c r="D40" s="70"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="73"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="69"/>
-      <c r="I40" s="70"/>
-      <c r="J40" s="70"/>
-      <c r="K40" s="70"/>
-      <c r="L40" s="54"/>
-      <c r="M40" s="70"/>
-      <c r="N40" s="71"/>
-      <c r="O40" s="69"/>
-      <c r="P40" s="70"/>
-      <c r="Q40" s="70"/>
-      <c r="R40" s="64"/>
-      <c r="S40" s="64"/>
-      <c r="T40" s="64"/>
-      <c r="U40" s="64"/>
-      <c r="V40" s="52"/>
-      <c r="W40" s="57"/>
-      <c r="X40" s="64"/>
-      <c r="Y40" s="64"/>
-      <c r="Z40" s="52"/>
-      <c r="AA40" s="53"/>
-      <c r="AB40" s="64"/>
-      <c r="AC40" s="64"/>
-      <c r="AD40" s="54"/>
-      <c r="AE40" s="71"/>
-      <c r="AF40" s="69"/>
-      <c r="AG40" s="70"/>
-      <c r="AH40" s="70"/>
-      <c r="AI40" s="70"/>
-      <c r="AJ40" s="70"/>
-      <c r="AK40" s="70"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="77" t="s">
+        <v>161</v>
+      </c>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="74"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="71"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="70"/>
+      <c r="P40" s="71"/>
+      <c r="Q40" s="71"/>
+      <c r="R40" s="65"/>
+      <c r="S40" s="65"/>
+      <c r="T40" s="65"/>
+      <c r="U40" s="65"/>
+      <c r="V40" s="53"/>
+      <c r="W40" s="58"/>
+      <c r="X40" s="65"/>
+      <c r="Y40" s="65"/>
+      <c r="Z40" s="53"/>
+      <c r="AA40" s="54"/>
+      <c r="AB40" s="65"/>
+      <c r="AC40" s="65"/>
+      <c r="AD40" s="55"/>
+      <c r="AE40" s="72"/>
+      <c r="AF40" s="70"/>
+      <c r="AG40" s="71"/>
+      <c r="AH40" s="71"/>
+      <c r="AI40" s="71"/>
+      <c r="AJ40" s="71"/>
+      <c r="AK40" s="71"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="67"/>
-      <c r="C41" s="76"/>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="70"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="70"/>
-      <c r="N41" s="71"/>
-      <c r="O41" s="69"/>
-      <c r="P41" s="70"/>
-      <c r="Q41" s="63"/>
-      <c r="R41" s="77"/>
-      <c r="S41" s="77"/>
-      <c r="T41" s="63"/>
-      <c r="U41" s="70"/>
-      <c r="V41" s="71"/>
-      <c r="W41" s="57"/>
-      <c r="X41" s="70"/>
-      <c r="Y41" s="70"/>
-      <c r="Z41" s="71"/>
-      <c r="AA41" s="69"/>
-      <c r="AB41" s="70"/>
-      <c r="AC41" s="70"/>
-      <c r="AD41" s="54"/>
-      <c r="AE41" s="71"/>
-      <c r="AF41" s="69"/>
-      <c r="AG41" s="70"/>
-      <c r="AH41" s="70"/>
-      <c r="AI41" s="70"/>
-      <c r="AJ41" s="70"/>
-      <c r="AK41" s="70"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="74"/>
+      <c r="G41" s="72"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="71"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="71"/>
+      <c r="N41" s="72"/>
+      <c r="O41" s="70"/>
+      <c r="P41" s="71"/>
+      <c r="Q41" s="64"/>
+      <c r="R41" s="78"/>
+      <c r="S41" s="78"/>
+      <c r="T41" s="64"/>
+      <c r="U41" s="71"/>
+      <c r="V41" s="72"/>
+      <c r="W41" s="58"/>
+      <c r="X41" s="71"/>
+      <c r="Y41" s="71"/>
+      <c r="Z41" s="72"/>
+      <c r="AA41" s="70"/>
+      <c r="AB41" s="71"/>
+      <c r="AC41" s="71"/>
+      <c r="AD41" s="55"/>
+      <c r="AE41" s="72"/>
+      <c r="AF41" s="70"/>
+      <c r="AG41" s="71"/>
+      <c r="AH41" s="71"/>
+      <c r="AI41" s="71"/>
+      <c r="AJ41" s="71"/>
+      <c r="AK41" s="71"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="48" t="s">
+      <c r="B42" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="79" t="s">
-        <v>160</v>
-      </c>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="55"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="50"/>
-      <c r="J42" s="50"/>
-      <c r="K42" s="50"/>
-      <c r="L42" s="54"/>
-      <c r="M42" s="50"/>
-      <c r="N42" s="55"/>
-      <c r="O42" s="56"/>
-      <c r="P42" s="64"/>
-      <c r="Q42" s="64"/>
-      <c r="R42" s="50"/>
-      <c r="S42" s="50"/>
-      <c r="T42" s="63"/>
-      <c r="U42" s="50"/>
-      <c r="V42" s="52"/>
-      <c r="W42" s="57"/>
-      <c r="X42" s="64"/>
-      <c r="Y42" s="64"/>
-      <c r="Z42" s="52"/>
-      <c r="AA42" s="53"/>
-      <c r="AB42" s="64"/>
-      <c r="AC42" s="64"/>
-      <c r="AD42" s="54"/>
-      <c r="AE42" s="55"/>
-      <c r="AF42" s="56"/>
-      <c r="AG42" s="50"/>
-      <c r="AH42" s="50"/>
-      <c r="AI42" s="50"/>
-      <c r="AJ42" s="50"/>
-      <c r="AK42" s="50"/>
+      <c r="C42" s="80" t="s">
+        <v>162</v>
+      </c>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="51"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="51"/>
+      <c r="N42" s="56"/>
+      <c r="O42" s="57"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="51"/>
+      <c r="S42" s="51"/>
+      <c r="T42" s="64"/>
+      <c r="U42" s="51"/>
+      <c r="V42" s="53"/>
+      <c r="W42" s="58"/>
+      <c r="X42" s="65"/>
+      <c r="Y42" s="65"/>
+      <c r="Z42" s="53"/>
+      <c r="AA42" s="54"/>
+      <c r="AB42" s="65"/>
+      <c r="AC42" s="65"/>
+      <c r="AD42" s="55"/>
+      <c r="AE42" s="56"/>
+      <c r="AF42" s="57"/>
+      <c r="AG42" s="51"/>
+      <c r="AH42" s="51"/>
+      <c r="AI42" s="51"/>
+      <c r="AJ42" s="51"/>
+      <c r="AK42" s="51"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="48"/>
-      <c r="C43" s="79"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="54"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="55"/>
-      <c r="O43" s="56"/>
-      <c r="P43" s="50"/>
-      <c r="Q43" s="63"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="65"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="50"/>
-      <c r="V43" s="55"/>
-      <c r="W43" s="57"/>
-      <c r="X43" s="50"/>
-      <c r="Y43" s="50"/>
-      <c r="Z43" s="55"/>
-      <c r="AA43" s="56"/>
-      <c r="AB43" s="50"/>
-      <c r="AC43" s="50"/>
-      <c r="AD43" s="54"/>
-      <c r="AE43" s="55"/>
-      <c r="AF43" s="56"/>
-      <c r="AG43" s="50"/>
-      <c r="AH43" s="50"/>
-      <c r="AI43" s="50"/>
-      <c r="AJ43" s="50"/>
-      <c r="AK43" s="50"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="80"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="51"/>
+      <c r="K43" s="51"/>
+      <c r="L43" s="55"/>
+      <c r="M43" s="51"/>
+      <c r="N43" s="56"/>
+      <c r="O43" s="57"/>
+      <c r="P43" s="51"/>
+      <c r="Q43" s="64"/>
+      <c r="R43" s="51"/>
+      <c r="S43" s="66"/>
+      <c r="T43" s="51"/>
+      <c r="U43" s="51"/>
+      <c r="V43" s="56"/>
+      <c r="W43" s="58"/>
+      <c r="X43" s="51"/>
+      <c r="Y43" s="51"/>
+      <c r="Z43" s="56"/>
+      <c r="AA43" s="57"/>
+      <c r="AB43" s="51"/>
+      <c r="AC43" s="51"/>
+      <c r="AD43" s="55"/>
+      <c r="AE43" s="56"/>
+      <c r="AF43" s="57"/>
+      <c r="AG43" s="51"/>
+      <c r="AH43" s="51"/>
+      <c r="AI43" s="51"/>
+      <c r="AJ43" s="51"/>
+      <c r="AK43" s="51"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="48"/>
-      <c r="C44" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="55"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="54"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="55"/>
-      <c r="O44" s="56"/>
-      <c r="P44" s="64"/>
-      <c r="Q44" s="64"/>
-      <c r="R44" s="50"/>
-      <c r="S44" s="50"/>
-      <c r="T44" s="50"/>
-      <c r="U44" s="50"/>
-      <c r="V44" s="55"/>
-      <c r="W44" s="57"/>
-      <c r="X44" s="64"/>
-      <c r="Y44" s="64"/>
-      <c r="Z44" s="55"/>
-      <c r="AA44" s="56"/>
-      <c r="AB44" s="50"/>
-      <c r="AC44" s="64"/>
-      <c r="AD44" s="54"/>
-      <c r="AE44" s="52"/>
-      <c r="AF44" s="53"/>
-      <c r="AG44" s="50"/>
-      <c r="AH44" s="50"/>
-      <c r="AI44" s="64"/>
-      <c r="AJ44" s="50"/>
-      <c r="AK44" s="50"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="80" t="s">
+        <v>163</v>
+      </c>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="51"/>
+      <c r="K44" s="51"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="51"/>
+      <c r="N44" s="56"/>
+      <c r="O44" s="57"/>
+      <c r="P44" s="65"/>
+      <c r="Q44" s="65"/>
+      <c r="R44" s="51"/>
+      <c r="S44" s="51"/>
+      <c r="T44" s="51"/>
+      <c r="U44" s="51"/>
+      <c r="V44" s="56"/>
+      <c r="W44" s="58"/>
+      <c r="X44" s="65"/>
+      <c r="Y44" s="65"/>
+      <c r="Z44" s="56"/>
+      <c r="AA44" s="57"/>
+      <c r="AB44" s="51"/>
+      <c r="AC44" s="65"/>
+      <c r="AD44" s="55"/>
+      <c r="AE44" s="53"/>
+      <c r="AF44" s="54"/>
+      <c r="AG44" s="51"/>
+      <c r="AH44" s="51"/>
+      <c r="AI44" s="65"/>
+      <c r="AJ44" s="51"/>
+      <c r="AK44" s="51"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="48"/>
-      <c r="C45" s="79"/>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="50"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="54"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="55"/>
-      <c r="O45" s="56"/>
-      <c r="P45" s="50"/>
-      <c r="Q45" s="50"/>
-      <c r="R45" s="50"/>
-      <c r="S45" s="50"/>
-      <c r="T45" s="50"/>
-      <c r="U45" s="50"/>
-      <c r="V45" s="55"/>
-      <c r="W45" s="57"/>
-      <c r="X45" s="50"/>
-      <c r="Y45" s="63"/>
-      <c r="Z45" s="80"/>
-      <c r="AA45" s="56"/>
-      <c r="AB45" s="50"/>
-      <c r="AC45" s="50"/>
-      <c r="AD45" s="54"/>
-      <c r="AE45" s="55"/>
-      <c r="AF45" s="56"/>
-      <c r="AG45" s="50"/>
-      <c r="AH45" s="50"/>
-      <c r="AI45" s="50"/>
-      <c r="AJ45" s="50"/>
-      <c r="AK45" s="50"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="80"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="51"/>
+      <c r="K45" s="51"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="51"/>
+      <c r="N45" s="56"/>
+      <c r="O45" s="57"/>
+      <c r="P45" s="51"/>
+      <c r="Q45" s="51"/>
+      <c r="R45" s="51"/>
+      <c r="S45" s="51"/>
+      <c r="T45" s="51"/>
+      <c r="U45" s="51"/>
+      <c r="V45" s="56"/>
+      <c r="W45" s="58"/>
+      <c r="X45" s="51"/>
+      <c r="Y45" s="64"/>
+      <c r="Z45" s="81"/>
+      <c r="AA45" s="57"/>
+      <c r="AB45" s="51"/>
+      <c r="AC45" s="51"/>
+      <c r="AD45" s="55"/>
+      <c r="AE45" s="56"/>
+      <c r="AF45" s="57"/>
+      <c r="AG45" s="51"/>
+      <c r="AH45" s="51"/>
+      <c r="AI45" s="51"/>
+      <c r="AJ45" s="51"/>
+      <c r="AK45" s="51"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="67" t="s">
-        <v>162</v>
-      </c>
-      <c r="C46" s="68" t="s">
+      <c r="B46" s="68" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="70"/>
-      <c r="E46" s="70"/>
-      <c r="F46" s="73"/>
-      <c r="G46" s="71"/>
-      <c r="H46" s="69"/>
-      <c r="I46" s="70"/>
-      <c r="J46" s="70"/>
-      <c r="K46" s="70"/>
-      <c r="L46" s="54"/>
-      <c r="M46" s="70"/>
-      <c r="N46" s="71"/>
-      <c r="O46" s="69"/>
-      <c r="P46" s="70"/>
-      <c r="Q46" s="70"/>
-      <c r="R46" s="70"/>
-      <c r="S46" s="70"/>
-      <c r="T46" s="70"/>
-      <c r="U46" s="70"/>
-      <c r="V46" s="71"/>
-      <c r="W46" s="57"/>
-      <c r="X46" s="70"/>
-      <c r="Y46" s="70"/>
-      <c r="Z46" s="71"/>
-      <c r="AA46" s="69"/>
-      <c r="AB46" s="70"/>
-      <c r="AC46" s="70"/>
-      <c r="AD46" s="54"/>
-      <c r="AE46" s="71"/>
-      <c r="AF46" s="69"/>
-      <c r="AG46" s="70"/>
-      <c r="AH46" s="70"/>
-      <c r="AI46" s="70"/>
-      <c r="AJ46" s="64"/>
-      <c r="AK46" s="70"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="72"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="71"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="71"/>
+      <c r="N46" s="72"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="71"/>
+      <c r="S46" s="71"/>
+      <c r="T46" s="71"/>
+      <c r="U46" s="71"/>
+      <c r="V46" s="72"/>
+      <c r="W46" s="58"/>
+      <c r="X46" s="71"/>
+      <c r="Y46" s="71"/>
+      <c r="Z46" s="72"/>
+      <c r="AA46" s="70"/>
+      <c r="AB46" s="71"/>
+      <c r="AC46" s="71"/>
+      <c r="AD46" s="55"/>
+      <c r="AE46" s="72"/>
+      <c r="AF46" s="70"/>
+      <c r="AG46" s="71"/>
+      <c r="AH46" s="71"/>
+      <c r="AI46" s="71"/>
+      <c r="AJ46" s="65"/>
+      <c r="AK46" s="71"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="67"/>
-      <c r="C47" s="68"/>
-      <c r="D47" s="70"/>
-      <c r="E47" s="70"/>
-      <c r="F47" s="73"/>
-      <c r="G47" s="71"/>
-      <c r="H47" s="69"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="70"/>
-      <c r="K47" s="70"/>
-      <c r="L47" s="54"/>
-      <c r="M47" s="70"/>
-      <c r="N47" s="71"/>
-      <c r="O47" s="69"/>
-      <c r="P47" s="70"/>
-      <c r="Q47" s="70"/>
-      <c r="R47" s="70"/>
-      <c r="S47" s="70"/>
-      <c r="T47" s="70"/>
-      <c r="U47" s="70"/>
-      <c r="V47" s="71"/>
-      <c r="W47" s="57"/>
-      <c r="X47" s="70"/>
-      <c r="Y47" s="70"/>
-      <c r="Z47" s="71"/>
-      <c r="AA47" s="69"/>
-      <c r="AB47" s="70"/>
-      <c r="AC47" s="70"/>
-      <c r="AD47" s="54"/>
-      <c r="AE47" s="71"/>
-      <c r="AF47" s="69"/>
-      <c r="AG47" s="70"/>
-      <c r="AH47" s="70"/>
-      <c r="AI47" s="70"/>
-      <c r="AJ47" s="70"/>
-      <c r="AK47" s="70"/>
-      <c r="AN47" s="81" t="s">
-        <v>163</v>
-      </c>
-      <c r="AO47" s="64"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="71"/>
+      <c r="E47" s="71"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="72"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="71"/>
+      <c r="J47" s="71"/>
+      <c r="K47" s="71"/>
+      <c r="L47" s="55"/>
+      <c r="M47" s="71"/>
+      <c r="N47" s="72"/>
+      <c r="O47" s="70"/>
+      <c r="P47" s="71"/>
+      <c r="Q47" s="71"/>
+      <c r="R47" s="71"/>
+      <c r="S47" s="71"/>
+      <c r="T47" s="71"/>
+      <c r="U47" s="71"/>
+      <c r="V47" s="72"/>
+      <c r="W47" s="58"/>
+      <c r="X47" s="71"/>
+      <c r="Y47" s="71"/>
+      <c r="Z47" s="72"/>
+      <c r="AA47" s="70"/>
+      <c r="AB47" s="71"/>
+      <c r="AC47" s="71"/>
+      <c r="AD47" s="55"/>
+      <c r="AE47" s="72"/>
+      <c r="AF47" s="70"/>
+      <c r="AG47" s="71"/>
+      <c r="AH47" s="71"/>
+      <c r="AI47" s="71"/>
+      <c r="AJ47" s="71"/>
+      <c r="AK47" s="71"/>
+      <c r="AN47" s="82" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO47" s="65"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="67"/>
-      <c r="C48" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="71"/>
-      <c r="H48" s="69"/>
-      <c r="I48" s="70"/>
-      <c r="J48" s="70"/>
-      <c r="K48" s="70"/>
-      <c r="L48" s="54"/>
-      <c r="M48" s="70"/>
-      <c r="N48" s="71"/>
-      <c r="O48" s="69"/>
-      <c r="P48" s="70"/>
-      <c r="Q48" s="70"/>
-      <c r="R48" s="70"/>
-      <c r="S48" s="70"/>
-      <c r="T48" s="70"/>
-      <c r="U48" s="70"/>
-      <c r="V48" s="71"/>
-      <c r="W48" s="57"/>
-      <c r="X48" s="70"/>
-      <c r="Y48" s="70"/>
-      <c r="Z48" s="71"/>
-      <c r="AA48" s="69"/>
-      <c r="AB48" s="70"/>
-      <c r="AC48" s="70"/>
-      <c r="AD48" s="54"/>
-      <c r="AE48" s="71"/>
-      <c r="AF48" s="69"/>
-      <c r="AG48" s="70"/>
-      <c r="AH48" s="70"/>
-      <c r="AI48" s="70"/>
-      <c r="AJ48" s="70"/>
-      <c r="AK48" s="82"/>
-      <c r="AN48" s="81" t="s">
-        <v>165</v>
-      </c>
-      <c r="AO48" s="63"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="69" t="s">
+        <v>166</v>
+      </c>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="72"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="71"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="71"/>
+      <c r="N48" s="72"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="71"/>
+      <c r="S48" s="71"/>
+      <c r="T48" s="71"/>
+      <c r="U48" s="71"/>
+      <c r="V48" s="72"/>
+      <c r="W48" s="58"/>
+      <c r="X48" s="71"/>
+      <c r="Y48" s="71"/>
+      <c r="Z48" s="72"/>
+      <c r="AA48" s="70"/>
+      <c r="AB48" s="71"/>
+      <c r="AC48" s="71"/>
+      <c r="AD48" s="55"/>
+      <c r="AE48" s="72"/>
+      <c r="AF48" s="70"/>
+      <c r="AG48" s="71"/>
+      <c r="AH48" s="71"/>
+      <c r="AI48" s="71"/>
+      <c r="AJ48" s="71"/>
+      <c r="AK48" s="83"/>
+      <c r="AN48" s="82" t="s">
+        <v>167</v>
+      </c>
+      <c r="AO48" s="64"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="67"/>
-      <c r="C49" s="68"/>
-      <c r="D49" s="70"/>
-      <c r="E49" s="70"/>
-      <c r="F49" s="73"/>
-      <c r="G49" s="71"/>
-      <c r="H49" s="69"/>
-      <c r="I49" s="70"/>
-      <c r="J49" s="70"/>
-      <c r="K49" s="70"/>
-      <c r="L49" s="54"/>
-      <c r="M49" s="70"/>
-      <c r="N49" s="71"/>
-      <c r="O49" s="69"/>
-      <c r="P49" s="70"/>
-      <c r="Q49" s="70"/>
-      <c r="R49" s="70"/>
-      <c r="S49" s="70"/>
-      <c r="T49" s="70"/>
-      <c r="U49" s="70"/>
-      <c r="V49" s="71"/>
-      <c r="W49" s="57"/>
-      <c r="X49" s="70"/>
-      <c r="Y49" s="70"/>
-      <c r="Z49" s="71"/>
-      <c r="AA49" s="69"/>
-      <c r="AB49" s="70"/>
-      <c r="AC49" s="70"/>
-      <c r="AD49" s="54"/>
-      <c r="AE49" s="71"/>
-      <c r="AF49" s="69"/>
-      <c r="AG49" s="70"/>
-      <c r="AH49" s="70"/>
-      <c r="AI49" s="70"/>
-      <c r="AJ49" s="70"/>
-      <c r="AK49" s="70"/>
-      <c r="AN49" s="81" t="s">
-        <v>166</v>
-      </c>
-      <c r="AO49" s="59"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="69"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="72"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="71"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="71"/>
+      <c r="N49" s="72"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="71"/>
+      <c r="S49" s="71"/>
+      <c r="T49" s="71"/>
+      <c r="U49" s="71"/>
+      <c r="V49" s="72"/>
+      <c r="W49" s="58"/>
+      <c r="X49" s="71"/>
+      <c r="Y49" s="71"/>
+      <c r="Z49" s="72"/>
+      <c r="AA49" s="70"/>
+      <c r="AB49" s="71"/>
+      <c r="AC49" s="71"/>
+      <c r="AD49" s="55"/>
+      <c r="AE49" s="72"/>
+      <c r="AF49" s="70"/>
+      <c r="AG49" s="71"/>
+      <c r="AH49" s="71"/>
+      <c r="AI49" s="71"/>
+      <c r="AJ49" s="71"/>
+      <c r="AK49" s="71"/>
+      <c r="AN49" s="82" t="s">
+        <v>168</v>
+      </c>
+      <c r="AO49" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -11032,801 +11057,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="83"/>
+      <c r="B1" s="84"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="84" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" s="86" t="s">
-        <v>167</v>
-      </c>
-      <c r="E2" s="87" t="s">
-        <v>168</v>
-      </c>
-      <c r="F2" s="88" t="s">
+      <c r="B2" s="85" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="87" t="s">
         <v>169</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="88"/>
-      <c r="I2" s="87"/>
-      <c r="J2" s="88" t="s">
+      <c r="E2" s="88" t="s">
         <v>170</v>
       </c>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="88" t="s">
-        <v>105</v>
-      </c>
-      <c r="O2" s="88"/>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="87"/>
-      <c r="R2" s="88" t="s">
-        <v>106</v>
-      </c>
-      <c r="S2" s="89"/>
-      <c r="AD2" s="90"/>
+      <c r="F2" s="89" t="s">
+        <v>171</v>
+      </c>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="89" t="s">
+        <v>172</v>
+      </c>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="89" t="s">
+        <v>107</v>
+      </c>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="89" t="s">
+        <v>108</v>
+      </c>
+      <c r="S2" s="90"/>
+      <c r="AD2" s="91"/>
     </row>
     <row r="3">
-      <c r="B3" s="91"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="93" t="s">
-        <v>171</v>
-      </c>
-      <c r="E3" s="94">
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="94" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="95">
         <v>4</v>
       </c>
-      <c r="F3" s="95">
+      <c r="F3" s="96">
         <v>1</v>
       </c>
-      <c r="G3" s="96">
+      <c r="G3" s="97">
         <v>2</v>
       </c>
-      <c r="H3" s="96">
+      <c r="H3" s="97">
         <v>3</v>
       </c>
-      <c r="I3" s="94">
+      <c r="I3" s="95">
         <v>4</v>
       </c>
-      <c r="J3" s="95">
+      <c r="J3" s="96">
         <v>1</v>
       </c>
-      <c r="K3" s="96">
+      <c r="K3" s="97">
         <v>2</v>
       </c>
-      <c r="L3" s="96">
+      <c r="L3" s="97">
         <v>3</v>
       </c>
-      <c r="M3" s="94">
+      <c r="M3" s="95">
         <v>4</v>
       </c>
-      <c r="N3" s="95">
+      <c r="N3" s="96">
         <v>1</v>
       </c>
-      <c r="O3" s="96">
+      <c r="O3" s="97">
         <v>2</v>
       </c>
-      <c r="P3" s="96">
+      <c r="P3" s="97">
         <v>3</v>
       </c>
-      <c r="Q3" s="94">
+      <c r="Q3" s="95">
         <v>4</v>
       </c>
-      <c r="R3" s="95">
+      <c r="R3" s="96">
         <v>1</v>
       </c>
-      <c r="S3" s="97">
+      <c r="S3" s="98">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="98" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="85" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="100"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="102"/>
-      <c r="P4" s="102"/>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="103"/>
-      <c r="S4" s="104"/>
+      <c r="B4" s="99" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="86" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="100"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="104"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="104"/>
+      <c r="S4" s="105"/>
       <c r="U4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="98"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="107"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="110"/>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="107"/>
-      <c r="R5" s="111"/>
-      <c r="S5" s="112"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="111"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="112"/>
+      <c r="O5" s="111"/>
+      <c r="P5" s="111"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="112"/>
+      <c r="S5" s="113"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="98"/>
-      <c r="C6" s="113" t="s">
-        <v>176</v>
-      </c>
-      <c r="D6" s="114"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="118"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="119"/>
-      <c r="K6" s="118"/>
-      <c r="L6" s="118"/>
-      <c r="M6" s="115"/>
-      <c r="N6" s="119"/>
-      <c r="O6" s="118"/>
-      <c r="P6" s="118"/>
-      <c r="Q6" s="115"/>
-      <c r="R6" s="119"/>
-      <c r="S6" s="120"/>
-      <c r="U6" s="121" t="s">
-        <v>177</v>
-      </c>
-      <c r="V6" s="121"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="114" t="s">
+        <v>178</v>
+      </c>
+      <c r="D6" s="115"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="118"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="120"/>
+      <c r="K6" s="119"/>
+      <c r="L6" s="119"/>
+      <c r="M6" s="116"/>
+      <c r="N6" s="120"/>
+      <c r="O6" s="119"/>
+      <c r="P6" s="119"/>
+      <c r="Q6" s="116"/>
+      <c r="R6" s="120"/>
+      <c r="S6" s="121"/>
+      <c r="U6" s="122" t="s">
+        <v>179</v>
+      </c>
+      <c r="V6" s="122"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="98"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="111"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="111"/>
-      <c r="O7" s="110"/>
-      <c r="P7" s="110"/>
-      <c r="Q7" s="107"/>
-      <c r="R7" s="111"/>
-      <c r="S7" s="112"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="112"/>
+      <c r="O7" s="111"/>
+      <c r="P7" s="111"/>
+      <c r="Q7" s="108"/>
+      <c r="R7" s="112"/>
+      <c r="S7" s="113"/>
       <c r="U7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="98"/>
-      <c r="C8" s="113" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="114"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="116"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118"/>
-      <c r="I8" s="115"/>
-      <c r="J8" s="119"/>
-      <c r="K8" s="118"/>
-      <c r="L8" s="118"/>
-      <c r="M8" s="115"/>
-      <c r="N8" s="119"/>
-      <c r="O8" s="118"/>
-      <c r="P8" s="118"/>
-      <c r="Q8" s="115"/>
-      <c r="R8" s="119"/>
-      <c r="S8" s="120"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="114" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="115"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="120"/>
+      <c r="K8" s="119"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="116"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="119"/>
+      <c r="P8" s="119"/>
+      <c r="Q8" s="116"/>
+      <c r="R8" s="120"/>
+      <c r="S8" s="121"/>
       <c r="U8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="98"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="111"/>
-      <c r="G9" s="109"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="107"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110"/>
-      <c r="M9" s="107"/>
-      <c r="N9" s="111"/>
-      <c r="O9" s="110"/>
-      <c r="P9" s="110"/>
-      <c r="Q9" s="107"/>
-      <c r="R9" s="111"/>
-      <c r="S9" s="112"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="112"/>
+      <c r="O9" s="111"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="108"/>
+      <c r="R9" s="112"/>
+      <c r="S9" s="113"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="98"/>
-      <c r="C10" s="113" t="s">
-        <v>181</v>
-      </c>
-      <c r="D10" s="114"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="117"/>
-      <c r="H10" s="117"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="118"/>
-      <c r="L10" s="118"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="119"/>
-      <c r="O10" s="118"/>
-      <c r="P10" s="118"/>
-      <c r="Q10" s="115"/>
-      <c r="R10" s="119"/>
-      <c r="S10" s="120"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="114" t="s">
+        <v>183</v>
+      </c>
+      <c r="D10" s="115"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="120"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="116"/>
+      <c r="N10" s="120"/>
+      <c r="O10" s="119"/>
+      <c r="P10" s="119"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="120"/>
+      <c r="S10" s="121"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="122"/>
-      <c r="C11" s="123"/>
-      <c r="D11" s="124"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="126"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="126"/>
-      <c r="K11" s="128"/>
-      <c r="L11" s="128"/>
-      <c r="M11" s="125"/>
-      <c r="N11" s="126"/>
-      <c r="O11" s="128"/>
-      <c r="P11" s="128"/>
-      <c r="Q11" s="125"/>
-      <c r="R11" s="126"/>
-      <c r="S11" s="129"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="126"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="129"/>
+      <c r="P11" s="129"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="127"/>
+      <c r="S11" s="130"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="84" t="s">
-        <v>182</v>
-      </c>
-      <c r="C12" s="85" t="s">
-        <v>183</v>
-      </c>
-      <c r="D12" s="99"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="100"/>
-      <c r="N12" s="103"/>
-      <c r="O12" s="102"/>
-      <c r="P12" s="102"/>
-      <c r="Q12" s="100"/>
-      <c r="R12" s="103"/>
-      <c r="S12" s="104"/>
+      <c r="B12" s="85" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="100"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="104"/>
+      <c r="O12" s="103"/>
+      <c r="P12" s="103"/>
+      <c r="Q12" s="101"/>
+      <c r="R12" s="104"/>
+      <c r="S12" s="105"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="98"/>
-      <c r="C13" s="105"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="107"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="110"/>
-      <c r="L13" s="110"/>
-      <c r="M13" s="107"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="110"/>
-      <c r="P13" s="110"/>
-      <c r="Q13" s="107"/>
-      <c r="R13" s="111"/>
-      <c r="S13" s="112"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="109"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="108"/>
+      <c r="N13" s="112"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="108"/>
+      <c r="R13" s="112"/>
+      <c r="S13" s="113"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="98"/>
-      <c r="C14" s="113" t="s">
-        <v>184</v>
-      </c>
-      <c r="D14" s="132"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="119"/>
-      <c r="K14" s="118"/>
-      <c r="L14" s="118"/>
-      <c r="M14" s="115"/>
-      <c r="N14" s="119"/>
-      <c r="O14" s="118"/>
-      <c r="P14" s="118"/>
-      <c r="Q14" s="115"/>
-      <c r="R14" s="119"/>
-      <c r="S14" s="120"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="114" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="133"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="120"/>
+      <c r="K14" s="119"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="116"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="119"/>
+      <c r="P14" s="119"/>
+      <c r="Q14" s="116"/>
+      <c r="R14" s="120"/>
+      <c r="S14" s="121"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="98"/>
-      <c r="C15" s="105"/>
-      <c r="D15" s="106"/>
-      <c r="E15" s="107"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="107"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="110"/>
-      <c r="P15" s="110"/>
-      <c r="Q15" s="107"/>
-      <c r="R15" s="111"/>
-      <c r="S15" s="112"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="109"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="108"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="108"/>
+      <c r="R15" s="112"/>
+      <c r="S15" s="113"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="98"/>
-      <c r="C16" s="113" t="s">
-        <v>185</v>
-      </c>
-      <c r="D16" s="114"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="134"/>
-      <c r="J16" s="119"/>
-      <c r="K16" s="118"/>
-      <c r="L16" s="118"/>
-      <c r="M16" s="115"/>
-      <c r="N16" s="119"/>
-      <c r="O16" s="118"/>
-      <c r="P16" s="118"/>
-      <c r="Q16" s="115"/>
-      <c r="R16" s="119"/>
-      <c r="S16" s="120"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="114" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="115"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="116"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="119"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="116"/>
+      <c r="R16" s="120"/>
+      <c r="S16" s="121"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="122"/>
-      <c r="C17" s="123"/>
-      <c r="D17" s="124"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="126"/>
-      <c r="G17" s="128"/>
-      <c r="H17" s="128"/>
-      <c r="I17" s="125"/>
-      <c r="J17" s="135"/>
-      <c r="K17" s="127"/>
-      <c r="L17" s="128"/>
-      <c r="M17" s="125"/>
-      <c r="N17" s="126"/>
-      <c r="O17" s="128"/>
-      <c r="P17" s="128"/>
-      <c r="Q17" s="125"/>
-      <c r="R17" s="126"/>
-      <c r="S17" s="129"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="127"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="129"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="127"/>
+      <c r="O17" s="129"/>
+      <c r="P17" s="129"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="127"/>
+      <c r="S17" s="130"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="86" t="s">
-        <v>186</v>
-      </c>
-      <c r="C18" s="85" t="s">
-        <v>187</v>
-      </c>
-      <c r="D18" s="99"/>
-      <c r="E18" s="100"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="102"/>
-      <c r="I18" s="131"/>
-      <c r="J18" s="103"/>
-      <c r="K18" s="102"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="100"/>
-      <c r="N18" s="103"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="102"/>
-      <c r="Q18" s="100"/>
-      <c r="R18" s="103"/>
-      <c r="S18" s="104"/>
+      <c r="B18" s="87" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="100"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="101"/>
+      <c r="N18" s="104"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="101"/>
+      <c r="R18" s="104"/>
+      <c r="S18" s="105"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="98"/>
-      <c r="C19" s="105"/>
-      <c r="D19" s="106"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="111"/>
-      <c r="G19" s="109"/>
-      <c r="H19" s="110"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="111"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="107"/>
-      <c r="N19" s="111"/>
-      <c r="O19" s="110"/>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="107"/>
-      <c r="R19" s="111"/>
-      <c r="S19" s="112"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="108"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="111"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="108"/>
+      <c r="R19" s="112"/>
+      <c r="S19" s="113"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="98"/>
-      <c r="C20" s="113" t="s">
-        <v>188</v>
-      </c>
-      <c r="D20" s="114"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="134"/>
-      <c r="J20" s="116"/>
-      <c r="K20" s="117"/>
-      <c r="L20" s="117"/>
-      <c r="M20" s="115"/>
-      <c r="N20" s="119"/>
-      <c r="O20" s="118"/>
-      <c r="P20" s="118"/>
-      <c r="Q20" s="115"/>
-      <c r="R20" s="119"/>
-      <c r="S20" s="120"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="114" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20" s="115"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="118"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="116"/>
+      <c r="N20" s="120"/>
+      <c r="O20" s="119"/>
+      <c r="P20" s="119"/>
+      <c r="Q20" s="116"/>
+      <c r="R20" s="120"/>
+      <c r="S20" s="121"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="98"/>
-      <c r="C21" s="105"/>
-      <c r="D21" s="106"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="111"/>
-      <c r="G21" s="110"/>
-      <c r="H21" s="110"/>
-      <c r="I21" s="107"/>
-      <c r="J21" s="111"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="107"/>
-      <c r="N21" s="136"/>
-      <c r="O21" s="110"/>
-      <c r="P21" s="110"/>
-      <c r="Q21" s="107"/>
-      <c r="R21" s="111"/>
-      <c r="S21" s="112"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="108"/>
+      <c r="N21" s="137"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="108"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="113"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="98"/>
-      <c r="C22" s="113" t="s">
-        <v>189</v>
-      </c>
-      <c r="D22" s="114"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="119"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="115"/>
-      <c r="N22" s="119"/>
-      <c r="O22" s="118"/>
-      <c r="P22" s="118"/>
-      <c r="Q22" s="115"/>
-      <c r="R22" s="119"/>
-      <c r="S22" s="120"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="114" t="s">
+        <v>191</v>
+      </c>
+      <c r="D22" s="115"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="116"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="116"/>
+      <c r="N22" s="120"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="119"/>
+      <c r="Q22" s="116"/>
+      <c r="R22" s="120"/>
+      <c r="S22" s="121"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="122"/>
-      <c r="C23" s="123"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="128"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="126"/>
-      <c r="K23" s="128"/>
-      <c r="L23" s="128"/>
-      <c r="M23" s="125"/>
-      <c r="N23" s="126"/>
-      <c r="O23" s="128"/>
-      <c r="P23" s="128"/>
-      <c r="Q23" s="125"/>
-      <c r="R23" s="126"/>
-      <c r="S23" s="129"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="127"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="129"/>
+      <c r="M23" s="126"/>
+      <c r="N23" s="127"/>
+      <c r="O23" s="129"/>
+      <c r="P23" s="129"/>
+      <c r="Q23" s="126"/>
+      <c r="R23" s="127"/>
+      <c r="S23" s="130"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="86" t="s">
-        <v>190</v>
-      </c>
-      <c r="C24" s="85" t="s">
-        <v>191</v>
-      </c>
-      <c r="D24" s="99"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="102"/>
-      <c r="H24" s="102"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="103"/>
-      <c r="K24" s="102"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="131"/>
-      <c r="N24" s="101"/>
-      <c r="O24" s="130"/>
-      <c r="P24" s="130"/>
-      <c r="Q24" s="100"/>
-      <c r="R24" s="103"/>
-      <c r="S24" s="104"/>
+      <c r="B24" s="87" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="86" t="s">
+        <v>193</v>
+      </c>
+      <c r="D24" s="100"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="103"/>
+      <c r="L24" s="103"/>
+      <c r="M24" s="132"/>
+      <c r="N24" s="102"/>
+      <c r="O24" s="131"/>
+      <c r="P24" s="131"/>
+      <c r="Q24" s="101"/>
+      <c r="R24" s="104"/>
+      <c r="S24" s="105"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="98"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="106"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="107"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="110"/>
-      <c r="L25" s="110"/>
-      <c r="M25" s="107"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="110"/>
-      <c r="P25" s="110"/>
-      <c r="Q25" s="107"/>
-      <c r="R25" s="111"/>
-      <c r="S25" s="112"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="108"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="108"/>
+      <c r="R25" s="112"/>
+      <c r="S25" s="113"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="98"/>
-      <c r="C26" s="113" t="s">
-        <v>192</v>
-      </c>
-      <c r="D26" s="114"/>
-      <c r="E26" s="115"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="118"/>
-      <c r="I26" s="115"/>
-      <c r="J26" s="119"/>
-      <c r="K26" s="118"/>
-      <c r="L26" s="118"/>
-      <c r="M26" s="115"/>
-      <c r="N26" s="119"/>
-      <c r="O26" s="117"/>
-      <c r="P26" s="117"/>
-      <c r="Q26" s="115"/>
-      <c r="R26" s="119"/>
-      <c r="S26" s="120"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="114" t="s">
+        <v>194</v>
+      </c>
+      <c r="D26" s="115"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="116"/>
+      <c r="N26" s="120"/>
+      <c r="O26" s="118"/>
+      <c r="P26" s="118"/>
+      <c r="Q26" s="116"/>
+      <c r="R26" s="120"/>
+      <c r="S26" s="121"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="98"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="106"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="107"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="110"/>
-      <c r="L27" s="110"/>
-      <c r="M27" s="107"/>
-      <c r="N27" s="111"/>
-      <c r="O27" s="110"/>
-      <c r="P27" s="110"/>
-      <c r="Q27" s="107"/>
-      <c r="R27" s="111"/>
-      <c r="S27" s="112"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="112"/>
+      <c r="K27" s="111"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="108"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="111"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="108"/>
+      <c r="R27" s="112"/>
+      <c r="S27" s="113"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="98"/>
-      <c r="C28" s="113" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="114"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="119"/>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="115"/>
-      <c r="N28" s="119"/>
-      <c r="O28" s="118"/>
-      <c r="P28" s="117"/>
-      <c r="Q28" s="134"/>
-      <c r="R28" s="119"/>
-      <c r="S28" s="120"/>
+      <c r="B28" s="99"/>
+      <c r="C28" s="114" t="s">
+        <v>195</v>
+      </c>
+      <c r="D28" s="115"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="116"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="116"/>
+      <c r="N28" s="120"/>
+      <c r="O28" s="119"/>
+      <c r="P28" s="118"/>
+      <c r="Q28" s="135"/>
+      <c r="R28" s="120"/>
+      <c r="S28" s="121"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="98"/>
-      <c r="C29" s="92"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="140"/>
-      <c r="H29" s="141"/>
-      <c r="I29" s="138"/>
-      <c r="J29" s="139"/>
-      <c r="K29" s="140"/>
-      <c r="L29" s="141"/>
-      <c r="M29" s="138"/>
-      <c r="N29" s="142"/>
-      <c r="O29" s="141"/>
-      <c r="P29" s="140"/>
-      <c r="Q29" s="138"/>
-      <c r="R29" s="139"/>
-      <c r="S29" s="143"/>
+      <c r="B29" s="99"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="142"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="140"/>
+      <c r="K29" s="141"/>
+      <c r="L29" s="142"/>
+      <c r="M29" s="139"/>
+      <c r="N29" s="143"/>
+      <c r="O29" s="142"/>
+      <c r="P29" s="141"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="140"/>
+      <c r="S29" s="144"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="144" t="s">
+      <c r="B30" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="145" t="s">
-        <v>139</v>
-      </c>
-      <c r="D30" s="99"/>
-      <c r="E30" s="146"/>
-      <c r="F30" s="147"/>
-      <c r="G30" s="147"/>
-      <c r="H30" s="148"/>
-      <c r="I30" s="149"/>
-      <c r="J30" s="147"/>
-      <c r="K30" s="147"/>
-      <c r="L30" s="148"/>
-      <c r="M30" s="149"/>
-      <c r="N30" s="147"/>
-      <c r="O30" s="148"/>
-      <c r="P30" s="147"/>
-      <c r="Q30" s="149"/>
-      <c r="R30" s="147"/>
-      <c r="S30" s="150"/>
+      <c r="C30" s="146" t="s">
+        <v>141</v>
+      </c>
+      <c r="D30" s="100"/>
+      <c r="E30" s="147"/>
+      <c r="F30" s="148"/>
+      <c r="G30" s="148"/>
+      <c r="H30" s="149"/>
+      <c r="I30" s="150"/>
+      <c r="J30" s="148"/>
+      <c r="K30" s="148"/>
+      <c r="L30" s="149"/>
+      <c r="M30" s="150"/>
+      <c r="N30" s="148"/>
+      <c r="O30" s="149"/>
+      <c r="P30" s="148"/>
+      <c r="Q30" s="150"/>
+      <c r="R30" s="148"/>
+      <c r="S30" s="151"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="151"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="106"/>
-      <c r="E31" s="153"/>
-      <c r="F31" s="154"/>
-      <c r="G31" s="154"/>
-      <c r="H31" s="155"/>
-      <c r="I31" s="156"/>
-      <c r="J31" s="154"/>
-      <c r="K31" s="157"/>
-      <c r="L31" s="155"/>
-      <c r="M31" s="156"/>
-      <c r="N31" s="154"/>
-      <c r="O31" s="155"/>
-      <c r="P31" s="154"/>
-      <c r="Q31" s="156"/>
-      <c r="R31" s="154"/>
-      <c r="S31" s="112"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="107"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="155"/>
+      <c r="G31" s="155"/>
+      <c r="H31" s="156"/>
+      <c r="I31" s="157"/>
+      <c r="J31" s="155"/>
+      <c r="K31" s="158"/>
+      <c r="L31" s="156"/>
+      <c r="M31" s="157"/>
+      <c r="N31" s="155"/>
+      <c r="O31" s="156"/>
+      <c r="P31" s="155"/>
+      <c r="Q31" s="157"/>
+      <c r="R31" s="155"/>
+      <c r="S31" s="113"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="151"/>
-      <c r="C32" s="152" t="s">
+      <c r="B32" s="152"/>
+      <c r="C32" s="153" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="114"/>
-      <c r="E32" s="158"/>
-      <c r="F32" s="159"/>
-      <c r="G32" s="159"/>
-      <c r="H32" s="160"/>
-      <c r="I32" s="161"/>
-      <c r="J32" s="159"/>
-      <c r="K32" s="159"/>
-      <c r="L32" s="160"/>
-      <c r="M32" s="161"/>
-      <c r="N32" s="159"/>
-      <c r="O32" s="160"/>
-      <c r="P32" s="159"/>
-      <c r="Q32" s="161"/>
-      <c r="R32" s="159"/>
-      <c r="S32" s="162"/>
+      <c r="D32" s="115"/>
+      <c r="E32" s="159"/>
+      <c r="F32" s="160"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="161"/>
+      <c r="I32" s="162"/>
+      <c r="J32" s="160"/>
+      <c r="K32" s="160"/>
+      <c r="L32" s="161"/>
+      <c r="M32" s="162"/>
+      <c r="N32" s="160"/>
+      <c r="O32" s="161"/>
+      <c r="P32" s="160"/>
+      <c r="Q32" s="162"/>
+      <c r="R32" s="160"/>
+      <c r="S32" s="163"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="151"/>
-      <c r="C33" s="152"/>
-      <c r="D33" s="106"/>
-      <c r="E33" s="153"/>
-      <c r="F33" s="157"/>
-      <c r="G33" s="154"/>
-      <c r="H33" s="163"/>
-      <c r="I33" s="164"/>
-      <c r="J33" s="154"/>
-      <c r="K33" s="157"/>
-      <c r="L33" s="155"/>
-      <c r="M33" s="156"/>
-      <c r="N33" s="154"/>
-      <c r="O33" s="155"/>
-      <c r="P33" s="154"/>
-      <c r="Q33" s="156"/>
-      <c r="R33" s="154"/>
-      <c r="S33" s="112"/>
+      <c r="B33" s="152"/>
+      <c r="C33" s="153"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="158"/>
+      <c r="G33" s="155"/>
+      <c r="H33" s="164"/>
+      <c r="I33" s="165"/>
+      <c r="J33" s="155"/>
+      <c r="K33" s="158"/>
+      <c r="L33" s="156"/>
+      <c r="M33" s="157"/>
+      <c r="N33" s="155"/>
+      <c r="O33" s="156"/>
+      <c r="P33" s="155"/>
+      <c r="Q33" s="157"/>
+      <c r="R33" s="155"/>
+      <c r="S33" s="113"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="151"/>
-      <c r="C34" s="105" t="s">
-        <v>194</v>
-      </c>
-      <c r="D34" s="137"/>
-      <c r="E34" s="165"/>
-      <c r="F34" s="166"/>
-      <c r="G34" s="166"/>
-      <c r="H34" s="167"/>
-      <c r="I34" s="168"/>
-      <c r="J34" s="166"/>
-      <c r="K34" s="166"/>
-      <c r="L34" s="167"/>
-      <c r="M34" s="168"/>
-      <c r="N34" s="166"/>
-      <c r="O34" s="167"/>
-      <c r="P34" s="166"/>
-      <c r="Q34" s="168"/>
-      <c r="R34" s="166"/>
-      <c r="S34" s="169"/>
-      <c r="U34" s="170"/>
-      <c r="V34" s="171" t="s">
-        <v>195</v>
+      <c r="B34" s="152"/>
+      <c r="C34" s="106" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" s="138"/>
+      <c r="E34" s="166"/>
+      <c r="F34" s="167"/>
+      <c r="G34" s="167"/>
+      <c r="H34" s="168"/>
+      <c r="I34" s="169"/>
+      <c r="J34" s="167"/>
+      <c r="K34" s="167"/>
+      <c r="L34" s="168"/>
+      <c r="M34" s="169"/>
+      <c r="N34" s="167"/>
+      <c r="O34" s="168"/>
+      <c r="P34" s="167"/>
+      <c r="Q34" s="169"/>
+      <c r="R34" s="167"/>
+      <c r="S34" s="170"/>
+      <c r="U34" s="171"/>
+      <c r="V34" s="172" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="172"/>
-      <c r="C35" s="173"/>
-      <c r="D35" s="124"/>
-      <c r="E35" s="174"/>
-      <c r="F35" s="175"/>
-      <c r="G35" s="175"/>
-      <c r="H35" s="176"/>
-      <c r="I35" s="177"/>
-      <c r="J35" s="175"/>
-      <c r="K35" s="175"/>
-      <c r="L35" s="176"/>
-      <c r="M35" s="177"/>
-      <c r="N35" s="175"/>
-      <c r="O35" s="176"/>
-      <c r="P35" s="175"/>
-      <c r="Q35" s="177"/>
-      <c r="R35" s="175"/>
-      <c r="S35" s="129"/>
-      <c r="U35" s="178"/>
-      <c r="V35" s="179" t="s">
-        <v>196</v>
+      <c r="B35" s="173"/>
+      <c r="C35" s="174"/>
+      <c r="D35" s="125"/>
+      <c r="E35" s="175"/>
+      <c r="F35" s="176"/>
+      <c r="G35" s="176"/>
+      <c r="H35" s="177"/>
+      <c r="I35" s="178"/>
+      <c r="J35" s="176"/>
+      <c r="K35" s="176"/>
+      <c r="L35" s="177"/>
+      <c r="M35" s="178"/>
+      <c r="N35" s="176"/>
+      <c r="O35" s="177"/>
+      <c r="P35" s="176"/>
+      <c r="Q35" s="178"/>
+      <c r="R35" s="176"/>
+      <c r="S35" s="130"/>
+      <c r="U35" s="179"/>
+      <c r="V35" s="180" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/LHO - M5 - JournalPlanif.xlsx
+++ b/Documentation/LHO - M5 - JournalPlanif.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>date</t>
   </si>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">Correction d'affichage des document dans le menu notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Test de fonctionnement global de l'application</t>
+    <t xml:space="preserve">Création des test de fonctionnement global de l'application</t>
   </si>
   <si>
     <t xml:space="preserve">Déploiement de la première version sur Windows, Linux et MacOS. Avec Installateur universel pour windows Inno Setup.</t>
@@ -339,6 +339,12 @@
   </si>
   <si>
     <t xml:space="preserve">Relecture et correction de la documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test complet de l'application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation des résultats des tests</t>
   </si>
   <si>
     <t xml:space="preserve">Par jour</t>
@@ -1608,7 +1614,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="183">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1662,6 +1668,12 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4906,8 +4918,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E76">
-  <autoFilter ref="B2:E76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E78">
+  <autoFilter ref="B2:E78"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5471,7 +5483,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.714285714285714e-002</v>
+        <v>0.016925246826516218</v>
       </c>
       <c r="J3" s="12" t="str">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -5487,7 +5499,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
@@ -5504,7 +5516,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.714285714285714e-002</v>
+        <v>0.016925246826516218</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -5537,7 +5549,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>5.4285714285714277e-002</v>
+        <v>0.05359661495063469</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -5553,7 +5565,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
@@ -5570,7 +5582,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>9.7142857142857128e-002</v>
+        <v>0.095909732016925237</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -5586,7 +5598,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>8</v>
@@ -5599,11 +5611,11 @@
       </c>
       <c r="H7" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>57</v>
+        <v>60.25</v>
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.32571428571428568</v>
+        <v>0.33991537376586739</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -5611,7 +5623,7 @@
       </c>
       <c r="K7" s="13">
         <f/>
-        <v>57</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="8" ht="28.5">
@@ -5636,7 +5648,7 @@
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.43238095238095231</v>
+        <v>0.4268923366243535</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -5665,11 +5677,11 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>9.3333333333333339</v>
+        <v>8.3333333333333321</v>
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>5.333333333333333e-002</v>
+        <v>0.047014574518100594</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -5677,7 +5689,7 @@
       </c>
       <c r="K9" s="14">
         <f/>
-        <v>9.3333333333333339</v>
+        <v>8.3333333333333321</v>
       </c>
     </row>
     <row r="10">
@@ -5685,7 +5697,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>12</v>
@@ -5702,7 +5714,7 @@
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.8571428571428567e-003</v>
+        <v>0.0028208744710860362</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -5712,7 +5724,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>12</v>
@@ -5725,7 +5737,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>175.00000000000003</v>
+        <v>177.25000000000003</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -5735,7 +5747,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>10</v>
@@ -5750,7 +5762,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>12</v>
@@ -5765,7 +5777,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>12</v>
@@ -5821,7 +5833,7 @@
         <v>35</v>
       </c>
       <c r="C18" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>10</v>
@@ -5835,7 +5847,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>12</v>
@@ -5849,7 +5861,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>19</v>
@@ -5863,7 +5875,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>15</v>
@@ -5891,7 +5903,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>15</v>
@@ -5905,7 +5917,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="6">
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>15</v>
@@ -5947,7 +5959,7 @@
         <v>49</v>
       </c>
       <c r="C27" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>12</v>
@@ -5961,7 +5973,7 @@
         <v>52</v>
       </c>
       <c r="C28" s="6">
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>15</v>
@@ -6003,7 +6015,7 @@
         <v>46087</v>
       </c>
       <c r="C31" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>21</v>
@@ -6031,7 +6043,7 @@
         <v>46091</v>
       </c>
       <c r="C33" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>12</v>
@@ -6059,7 +6071,7 @@
         <v>46091</v>
       </c>
       <c r="C35" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>19</v>
@@ -6087,7 +6099,7 @@
         <v>46093</v>
       </c>
       <c r="C37" s="6">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>19</v>
@@ -6115,7 +6127,7 @@
         <v>46087</v>
       </c>
       <c r="C39" s="6">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>21</v>
@@ -6202,7 +6214,7 @@
         <v>46100</v>
       </c>
       <c r="C45" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>8</v>
@@ -6216,7 +6228,7 @@
         <v>46100</v>
       </c>
       <c r="C46" s="6">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>19</v>
@@ -6244,7 +6256,7 @@
         <v>46102</v>
       </c>
       <c r="C48" s="21">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>8</v>
@@ -6300,7 +6312,7 @@
         <v>46104</v>
       </c>
       <c r="C52" s="21">
-        <v>1.3888888888888888e-002</v>
+        <v>0.013888888888888888</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>21</v>
@@ -6328,7 +6340,7 @@
         <v>46118</v>
       </c>
       <c r="C54" s="21">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>19</v>
@@ -6342,7 +6354,7 @@
         <v>46119</v>
       </c>
       <c r="C55" s="21">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>8</v>
@@ -6356,7 +6368,7 @@
         <v>46119</v>
       </c>
       <c r="C56" s="21">
-        <v>6.25e-002</v>
+        <v>0.0625</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>19</v>
@@ -6398,7 +6410,7 @@
         <v>46134</v>
       </c>
       <c r="C59" s="21">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>12</v>
@@ -6412,7 +6424,7 @@
         <v>46134</v>
       </c>
       <c r="C60" s="21">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>19</v>
@@ -6426,7 +6438,7 @@
         <v>46135</v>
       </c>
       <c r="C61" s="21">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>19</v>
@@ -6468,7 +6480,7 @@
         <v>46140</v>
       </c>
       <c r="C64" s="21">
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>21</v>
@@ -6524,7 +6536,7 @@
         <v>46161</v>
       </c>
       <c r="C68" s="21">
-        <v>2.0833333333333332e-002</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>24</v>
@@ -6552,7 +6564,7 @@
         <v>46177</v>
       </c>
       <c r="C70" s="21">
-        <v>1.3888888888888888e-002</v>
+        <v>0.013888888888888888</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>19</v>
@@ -6566,7 +6578,7 @@
         <v>46177</v>
       </c>
       <c r="C71" s="21">
-        <v>3.4722222222222224e-002</v>
+        <v>0.034722222222222224</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>19</v>
@@ -6582,10 +6594,10 @@
       <c r="C72" s="23">
         <v>0.125</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72" s="2" t="s">
+      <c r="D72" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" s="25" t="s">
         <v>96</v>
       </c>
     </row>
@@ -6611,7 +6623,7 @@
         <v>46180</v>
       </c>
       <c r="C74" s="21">
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>12</v>
@@ -6635,30 +6647,46 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="24">
+      <c r="B76" s="26">
         <v>46181</v>
       </c>
       <c r="C76" s="21">
-        <v>2.0833333333333332e-002</v>
-      </c>
-      <c r="D76" s="25" t="s">
+        <v>0.020833333333333332</v>
+      </c>
+      <c r="D76" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E76" s="26" t="s">
+      <c r="E76" s="8" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="7"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="8"/>
+      <c r="B77" s="26">
+        <v>46182</v>
+      </c>
+      <c r="C77" s="21">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="D77" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E77" s="28" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="78">
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="8"/>
+      <c r="B78" s="26">
+        <v>46182</v>
+      </c>
+      <c r="C78" s="21">
+        <v>0.010416666666666666</v>
+      </c>
+      <c r="D78" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" s="28" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="7"/>
@@ -6694,7 +6722,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{9D101B69-AAA9-4629-B9B2-C1792FD1C30C}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00CF000C-009D-400F-A118-00DF00C800FB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6718,11 +6746,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -6736,47 +6764,47 @@
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27">
+      <c r="A3" s="29">
         <v>46042</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C3" s="28"/>
+      <c r="C3" s="30"/>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F3" s="29">
+        <v>109</v>
+      </c>
+      <c r="F3" s="31">
         <f t="shared" ref="F3:F8" si="0">SUMPRODUCT((MONTH($A$3:$A$152)=D3)*($A$3:$A$152&lt;&gt;"")*$B$3:$B$152)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="30">
+      <c r="G3" s="32">
         <f t="shared" ref="G3:G8" si="1">F3*24</f>
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27">
+      <c r="A4" s="29">
         <v>46043</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6785,22 +6813,22 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" s="29">
+        <v>110</v>
+      </c>
+      <c r="F4" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27">
+      <c r="A5" s="29">
         <v>46044</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6809,22 +6837,22 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="29">
+        <v>111</v>
+      </c>
+      <c r="F5" s="31">
         <f t="shared" si="0"/>
         <v>2.6805555555555558</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="32">
         <f t="shared" si="1"/>
         <v>64.333333333333343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27">
+      <c r="A6" s="29">
         <v>46045</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6833,22 +6861,22 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="29">
+        <v>112</v>
+      </c>
+      <c r="F6" s="31">
         <f t="shared" si="0"/>
         <v>1.2083333333333333</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="32">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27">
+      <c r="A7" s="29">
         <v>46046</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6857,22 +6885,22 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
-      </c>
-      <c r="F7" s="29">
+        <v>113</v>
+      </c>
+      <c r="F7" s="31">
         <f t="shared" si="0"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="32">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27">
+      <c r="A8" s="29">
         <v>46047</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6881,2071 +6909,2071 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F8" s="29">
+        <v>114</v>
+      </c>
+      <c r="F8" s="31">
         <f t="shared" si="0"/>
-        <v>0.48611111111111116</v>
-      </c>
-      <c r="G8" s="30">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="G8" s="32">
         <f t="shared" si="1"/>
-        <v>11.666666666666668</v>
+        <v>13.916666666666668</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27">
+      <c r="A9" s="29">
         <v>46048</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
-      <c r="G9" s="30">
+      <c r="G9" s="32">
         <f>SUM(G3:G8)</f>
-        <v>112.00000000000001</v>
+        <v>114.25000000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27">
+      <c r="A10" s="29">
         <v>46049</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="27">
+      <c r="A11" s="29">
         <v>46050</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="27">
+      <c r="A12" s="29">
         <v>46051</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="27">
+      <c r="A13" s="29">
         <v>46052</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="27">
+      <c r="A14" s="29">
         <v>46053</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="27">
+      <c r="A15" s="29">
         <v>46054</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="27">
+      <c r="A16" s="29">
         <v>46055</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="27">
+      <c r="A17" s="29">
         <v>46056</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="27">
+      <c r="A18" s="29">
         <v>46057</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="27">
+      <c r="A19" s="29">
         <v>46058</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="27">
+      <c r="A20" s="29">
         <v>46059</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="27">
+      <c r="A21" s="29">
         <v>46060</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="27">
+      <c r="A22" s="29">
         <v>46061</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="27">
+      <c r="A23" s="29">
         <v>46062</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="27">
+      <c r="A24" s="29">
         <v>46063</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="27">
+      <c r="A25" s="29">
         <v>46064</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
     </row>
     <row r="26">
-      <c r="A26" s="27">
+      <c r="A26" s="29">
         <v>46065</v>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C26"/>
-      <c r="F26" s="30"/>
+      <c r="F26" s="32"/>
     </row>
     <row r="27">
-      <c r="A27" s="27">
+      <c r="A27" s="29">
         <v>46066</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27">
+      <c r="A28" s="29">
         <v>46067</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27">
+      <c r="A29" s="29">
         <v>46068</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27">
+      <c r="A30" s="29">
         <v>46069</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27">
+      <c r="A31" s="29">
         <v>46070</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27">
+      <c r="A32" s="29">
         <v>46071</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27">
+      <c r="A33" s="29">
         <v>46072</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27">
+      <c r="A34" s="29">
         <v>46073</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27">
+      <c r="A35" s="29">
         <v>46074</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27">
+      <c r="A36" s="29">
         <v>46075</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27">
+      <c r="A37" s="29">
         <v>46076</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27">
+      <c r="A38" s="29">
         <v>46077</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="27">
+      <c r="A39" s="29">
         <v>46078</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="27">
+      <c r="A40" s="29">
         <v>46079</v>
       </c>
-      <c r="B40" s="28">
+      <c r="B40" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="27">
+      <c r="A41" s="29">
         <v>46080</v>
       </c>
-      <c r="B41" s="28">
+      <c r="B41" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="27">
+      <c r="A42" s="29">
         <v>46081</v>
       </c>
-      <c r="B42" s="28">
+      <c r="B42" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="27">
+      <c r="A43" s="29">
         <v>46082</v>
       </c>
-      <c r="B43" s="28">
+      <c r="B43" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="27">
+      <c r="A44" s="29">
         <v>46083</v>
       </c>
-      <c r="B44" s="28">
+      <c r="B44" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="27">
+      <c r="A45" s="29">
         <v>46084</v>
       </c>
-      <c r="B45" s="28">
+      <c r="B45" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="27">
+      <c r="A46" s="29">
         <v>46085</v>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="27">
+      <c r="A47" s="29">
         <v>46086</v>
       </c>
-      <c r="B47" s="28">
+      <c r="B47" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="27">
+      <c r="A48" s="29">
         <v>46087</v>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="27">
+      <c r="A49" s="29">
         <v>46088</v>
       </c>
-      <c r="B49" s="28">
+      <c r="B49" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="27">
+      <c r="A50" s="29">
         <v>46089</v>
       </c>
-      <c r="B50" s="28">
+      <c r="B50" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="27">
+      <c r="A51" s="29">
         <v>46090</v>
       </c>
-      <c r="B51" s="28">
+      <c r="B51" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="27">
+      <c r="A52" s="29">
         <v>46091</v>
       </c>
-      <c r="B52" s="28">
+      <c r="B52" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="27">
+      <c r="A53" s="29">
         <v>46092</v>
       </c>
-      <c r="B53" s="28">
+      <c r="B53" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="27">
+      <c r="A54" s="29">
         <v>46093</v>
       </c>
-      <c r="B54" s="28">
+      <c r="B54" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
-      </c>
-      <c r="C54" s="31">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="C54" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="27">
+      <c r="A55" s="29">
         <v>46094</v>
       </c>
-      <c r="B55" s="28">
+      <c r="B55" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="27">
+      <c r="A56" s="29">
         <v>46095</v>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="27">
+      <c r="A57" s="29">
         <v>46096</v>
       </c>
-      <c r="B57" s="28">
+      <c r="B57" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="27">
+      <c r="A58" s="29">
         <v>46097</v>
       </c>
-      <c r="B58" s="28">
+      <c r="B58" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="27">
+      <c r="A59" s="29">
         <v>46098</v>
       </c>
-      <c r="B59" s="28">
+      <c r="B59" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="27">
+      <c r="A60" s="29">
         <v>46099</v>
       </c>
-      <c r="B60" s="28">
+      <c r="B60" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="27">
+      <c r="A61" s="29">
         <v>46100</v>
       </c>
-      <c r="B61" s="28">
+      <c r="B61" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="27">
+      <c r="A62" s="29">
         <v>46101</v>
       </c>
-      <c r="B62" s="28">
+      <c r="B62" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="27">
+      <c r="A63" s="29">
         <v>46102</v>
       </c>
-      <c r="B63" s="28">
+      <c r="B63" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="27">
+      <c r="A64" s="29">
         <v>46103</v>
       </c>
-      <c r="B64" s="28">
+      <c r="B64" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C64" s="31">
+      <c r="C64" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="27">
+      <c r="A65" s="29">
         <v>46104</v>
       </c>
-      <c r="B65" s="28">
+      <c r="B65" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
-        <v>1.3888888888888888e-002</v>
-      </c>
-      <c r="C65" s="31">
+        <v>0.013888888888888888</v>
+      </c>
+      <c r="C65" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
-        <v>1.3888888888888888e-002</v>
+        <v>0.013888888888888888</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="27">
+      <c r="A66" s="29">
         <v>46105</v>
       </c>
-      <c r="B66" s="28">
+      <c r="B66" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="27">
+      <c r="A67" s="29">
         <v>46106</v>
       </c>
-      <c r="B67" s="28">
+      <c r="B67" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C67" s="31">
+      <c r="C67" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="27">
+      <c r="A68" s="29">
         <v>46107</v>
       </c>
-      <c r="B68" s="28">
+      <c r="B68" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="27">
+      <c r="A69" s="29">
         <v>46108</v>
       </c>
-      <c r="B69" s="28">
+      <c r="B69" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="27">
+      <c r="A70" s="29">
         <v>46109</v>
       </c>
-      <c r="B70" s="28">
+      <c r="B70" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C70" s="31">
+      <c r="C70" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="27">
+      <c r="A71" s="29">
         <v>46110</v>
       </c>
-      <c r="B71" s="28">
+      <c r="B71" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="27">
+      <c r="A72" s="29">
         <v>46111</v>
       </c>
-      <c r="B72" s="28">
+      <c r="B72" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="27">
+      <c r="A73" s="29">
         <v>46112</v>
       </c>
-      <c r="B73" s="28">
+      <c r="B73" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C73" s="31">
+      <c r="C73" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="27">
+      <c r="A74" s="29">
         <v>46113</v>
       </c>
-      <c r="B74" s="28">
+      <c r="B74" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C74" s="31">
+      <c r="C74" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="27">
+      <c r="A75" s="29">
         <v>46114</v>
       </c>
-      <c r="B75" s="28">
+      <c r="B75" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C75" s="31">
+      <c r="C75" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="27">
+      <c r="A76" s="29">
         <v>46115</v>
       </c>
-      <c r="B76" s="28">
+      <c r="B76" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C76" s="31">
+      <c r="C76" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="27">
+      <c r="A77" s="29">
         <v>46116</v>
       </c>
-      <c r="B77" s="28">
+      <c r="B77" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C77" s="31">
+      <c r="C77" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="27">
+      <c r="A78" s="29">
         <v>46117</v>
       </c>
-      <c r="B78" s="28">
+      <c r="B78" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C78" s="31">
+      <c r="C78" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="27">
+      <c r="A79" s="29">
         <v>46118</v>
       </c>
-      <c r="B79" s="28">
+      <c r="B79" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
-      </c>
-      <c r="C79" s="31">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="C79" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="27">
+      <c r="A80" s="29">
         <v>46119</v>
       </c>
-      <c r="B80" s="28">
+      <c r="B80" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
-      </c>
-      <c r="C80" s="31">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="C80" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
-        <v>8.3333333333333329e-002</v>
+        <v>0.083333333333333329</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="27">
+      <c r="A81" s="29">
         <v>46120</v>
       </c>
-      <c r="B81" s="28">
+      <c r="B81" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C81" s="31">
+      <c r="C81" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="27">
+      <c r="A82" s="29">
         <v>46121</v>
       </c>
-      <c r="B82" s="28">
+      <c r="B82" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C82" s="31">
+      <c r="C82" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="27">
+      <c r="A83" s="29">
         <v>46122</v>
       </c>
-      <c r="B83" s="28">
+      <c r="B83" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C83" s="31">
+      <c r="C83" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="27">
+      <c r="A84" s="29">
         <v>46123</v>
       </c>
-      <c r="B84" s="28">
+      <c r="B84" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C84" s="31">
+      <c r="C84" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="27">
+      <c r="A85" s="29">
         <v>46124</v>
       </c>
-      <c r="B85" s="28">
+      <c r="B85" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C85" s="31">
+      <c r="C85" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="27">
+      <c r="A86" s="29">
         <v>46125</v>
       </c>
-      <c r="B86" s="28">
+      <c r="B86" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C86" s="31">
+      <c r="C86" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="27">
+      <c r="A87" s="29">
         <v>46126</v>
       </c>
-      <c r="B87" s="28">
+      <c r="B87" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C87" s="31">
+      <c r="C87" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="27">
+      <c r="A88" s="29">
         <v>46127</v>
       </c>
-      <c r="B88" s="28">
+      <c r="B88" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C88" s="31">
+      <c r="C88" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="27">
+      <c r="A89" s="29">
         <v>46128</v>
       </c>
-      <c r="B89" s="28">
+      <c r="B89" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C89" s="31">
+      <c r="C89" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="27">
+      <c r="A90" s="29">
         <v>46129</v>
       </c>
-      <c r="B90" s="28">
+      <c r="B90" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C90" s="31">
+      <c r="C90" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="27">
+      <c r="A91" s="29">
         <v>46130</v>
       </c>
-      <c r="B91" s="28">
+      <c r="B91" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C91" s="31">
+      <c r="C91" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="27">
+      <c r="A92" s="29">
         <v>46131</v>
       </c>
-      <c r="B92" s="28">
+      <c r="B92" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C92" s="31">
+      <c r="C92" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="27">
+      <c r="A93" s="29">
         <v>46132</v>
       </c>
-      <c r="B93" s="28">
+      <c r="B93" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C93" s="31">
+      <c r="C93" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="27">
+      <c r="A94" s="29">
         <v>46133</v>
       </c>
-      <c r="B94" s="28">
+      <c r="B94" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C94" s="31">
+      <c r="C94" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="27">
+      <c r="A95" s="29">
         <v>46134</v>
       </c>
-      <c r="B95" s="28">
+      <c r="B95" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
-      <c r="C95" s="31">
+      <c r="C95" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="27">
+      <c r="A96" s="29">
         <v>46135</v>
       </c>
-      <c r="B96" s="28">
+      <c r="B96" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
-        <v>4.1666666666666664e-002</v>
-      </c>
-      <c r="C96" s="31">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="C96" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
-        <v>4.1666666666666664e-002</v>
+        <v>0.041666666666666664</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="27">
+      <c r="A97" s="29">
         <v>46136</v>
       </c>
-      <c r="B97" s="28">
+      <c r="B97" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C97" s="31">
+      <c r="C97" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="27">
+      <c r="A98" s="29">
         <v>46137</v>
       </c>
-      <c r="B98" s="28">
+      <c r="B98" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C98" s="31">
+      <c r="C98" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="27">
+      <c r="A99" s="29">
         <v>46138</v>
       </c>
-      <c r="B99" s="28">
+      <c r="B99" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C99" s="31">
+      <c r="C99" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="27">
+      <c r="A100" s="29">
         <v>46139</v>
       </c>
-      <c r="B100" s="28">
+      <c r="B100" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C100" s="31">
+      <c r="C100" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="27">
+      <c r="A101" s="29">
         <v>46140</v>
       </c>
-      <c r="B101" s="28">
+      <c r="B101" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
-      <c r="C101" s="31">
+      <c r="C101" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="27">
+      <c r="A102" s="29">
         <v>46141</v>
       </c>
-      <c r="B102" s="28">
+      <c r="B102" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C102" s="31">
+      <c r="C102" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="27">
+      <c r="A103" s="29">
         <v>46142</v>
       </c>
-      <c r="B103" s="28">
+      <c r="B103" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C103" s="31">
+      <c r="C103" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="27">
+      <c r="A104" s="29">
         <v>46143</v>
       </c>
-      <c r="B104" s="28">
+      <c r="B104" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C104" s="31">
+      <c r="C104" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="27">
+      <c r="A105" s="29">
         <v>46144</v>
       </c>
-      <c r="B105" s="28">
+      <c r="B105" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C105" s="31">
+      <c r="C105" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="27">
+      <c r="A106" s="29">
         <v>46145</v>
       </c>
-      <c r="B106" s="28">
+      <c r="B106" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C106" s="31">
+      <c r="C106" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="27">
+      <c r="A107" s="29">
         <v>46146</v>
       </c>
-      <c r="B107" s="28">
+      <c r="B107" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C107" s="31">
+      <c r="C107" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="27">
+      <c r="A108" s="29">
         <v>46147</v>
       </c>
-      <c r="B108" s="28">
+      <c r="B108" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C108" s="31">
+      <c r="C108" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="27">
+      <c r="A109" s="29">
         <v>46148</v>
       </c>
-      <c r="B109" s="28">
+      <c r="B109" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C109" s="31">
+      <c r="C109" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="27">
+      <c r="A110" s="29">
         <v>46149</v>
       </c>
-      <c r="B110" s="28">
+      <c r="B110" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C110" s="31">
+      <c r="C110" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="27">
+      <c r="A111" s="29">
         <v>46150</v>
       </c>
-      <c r="B111" s="28">
+      <c r="B111" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C111" s="31">
+      <c r="C111" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="27">
+      <c r="A112" s="29">
         <v>46151</v>
       </c>
-      <c r="B112" s="28">
+      <c r="B112" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C112" s="31">
+      <c r="C112" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="27">
+      <c r="A113" s="29">
         <v>46152</v>
       </c>
-      <c r="B113" s="28">
+      <c r="B113" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C113" s="31">
+      <c r="C113" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="27">
+      <c r="A114" s="29">
         <v>46153</v>
       </c>
-      <c r="B114" s="28">
+      <c r="B114" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C114" s="31">
+      <c r="C114" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="27">
+      <c r="A115" s="29">
         <v>46154</v>
       </c>
-      <c r="B115" s="28">
+      <c r="B115" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C115" s="31">
+      <c r="C115" s="33">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="27">
+      <c r="A116" s="29">
         <v>46155</v>
       </c>
-      <c r="B116" s="28">
+      <c r="B116" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A116,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C116" s="31"/>
+      <c r="C116" s="33"/>
     </row>
     <row r="117">
-      <c r="A117" s="27">
+      <c r="A117" s="29">
         <v>46156</v>
       </c>
-      <c r="B117" s="28">
+      <c r="B117" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A117,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C117" s="31"/>
+      <c r="C117" s="33"/>
     </row>
     <row r="118">
-      <c r="A118" s="27">
+      <c r="A118" s="29">
         <v>46157</v>
       </c>
-      <c r="B118" s="28">
+      <c r="B118" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A118,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C118" s="31"/>
+      <c r="C118" s="33"/>
     </row>
     <row r="119">
-      <c r="A119" s="27">
+      <c r="A119" s="29">
         <v>46158</v>
       </c>
-      <c r="B119" s="28">
+      <c r="B119" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A119,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C119" s="31"/>
+      <c r="C119" s="33"/>
     </row>
     <row r="120">
-      <c r="A120" s="27">
+      <c r="A120" s="29">
         <v>46159</v>
       </c>
-      <c r="B120" s="28">
+      <c r="B120" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A120,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C120" s="31"/>
+      <c r="C120" s="33"/>
     </row>
     <row r="121">
-      <c r="A121" s="27">
+      <c r="A121" s="29">
         <v>46160</v>
       </c>
-      <c r="B121" s="28">
+      <c r="B121" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A121,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C121" s="31"/>
+      <c r="C121" s="33"/>
     </row>
     <row r="122">
-      <c r="A122" s="27">
+      <c r="A122" s="29">
         <v>46161</v>
       </c>
-      <c r="B122" s="28">
+      <c r="B122" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A122,Journal[Temps])</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="C122" s="31"/>
+      <c r="C122" s="33"/>
     </row>
     <row r="123">
-      <c r="A123" s="27">
+      <c r="A123" s="29">
         <v>46162</v>
       </c>
-      <c r="B123" s="28">
+      <c r="B123" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A123,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C123" s="31"/>
+      <c r="C123" s="33"/>
     </row>
     <row r="124">
-      <c r="A124" s="27">
+      <c r="A124" s="29">
         <v>46163</v>
       </c>
-      <c r="B124" s="28">
+      <c r="B124" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A124,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C124" s="31"/>
+      <c r="C124" s="33"/>
     </row>
     <row r="125">
-      <c r="A125" s="27">
+      <c r="A125" s="29">
         <v>46164</v>
       </c>
-      <c r="B125" s="28">
+      <c r="B125" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A125,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C125" s="31"/>
+      <c r="C125" s="33"/>
     </row>
     <row r="126">
-      <c r="A126" s="27">
+      <c r="A126" s="29">
         <v>46165</v>
       </c>
-      <c r="B126" s="28">
+      <c r="B126" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A126,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C126" s="31"/>
+      <c r="C126" s="33"/>
     </row>
     <row r="127">
-      <c r="A127" s="27">
+      <c r="A127" s="29">
         <v>46166</v>
       </c>
-      <c r="B127" s="28">
+      <c r="B127" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A127,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C127" s="31"/>
+      <c r="C127" s="33"/>
     </row>
     <row r="128">
-      <c r="A128" s="27">
+      <c r="A128" s="29">
         <v>46167</v>
       </c>
-      <c r="B128" s="28">
+      <c r="B128" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A128,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C128" s="31"/>
+      <c r="C128" s="33"/>
     </row>
     <row r="129">
-      <c r="A129" s="27">
+      <c r="A129" s="29">
         <v>46168</v>
       </c>
-      <c r="B129" s="28">
+      <c r="B129" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A129,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C129" s="31"/>
+      <c r="C129" s="33"/>
     </row>
     <row r="130">
-      <c r="A130" s="27">
+      <c r="A130" s="29">
         <v>46169</v>
       </c>
-      <c r="B130" s="28">
+      <c r="B130" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A130,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C130" s="31"/>
+      <c r="C130" s="33"/>
     </row>
     <row r="131">
-      <c r="A131" s="27">
+      <c r="A131" s="29">
         <v>46170</v>
       </c>
-      <c r="B131" s="28">
+      <c r="B131" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A131,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C131" s="31"/>
+      <c r="C131" s="33"/>
     </row>
     <row r="132">
-      <c r="A132" s="27">
+      <c r="A132" s="29">
         <v>46171</v>
       </c>
-      <c r="B132" s="28">
+      <c r="B132" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A132,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C132" s="31"/>
+      <c r="C132" s="33"/>
     </row>
     <row r="133">
-      <c r="A133" s="27">
+      <c r="A133" s="29">
         <v>46172</v>
       </c>
-      <c r="B133" s="28">
+      <c r="B133" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A133,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C133" s="31"/>
+      <c r="C133" s="33"/>
     </row>
     <row r="134">
-      <c r="A134" s="27">
+      <c r="A134" s="29">
         <v>46173</v>
       </c>
-      <c r="B134" s="28">
+      <c r="B134" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A134,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C134" s="31"/>
+      <c r="C134" s="33"/>
     </row>
     <row r="135">
-      <c r="A135" s="27">
+      <c r="A135" s="29">
         <v>46174</v>
       </c>
-      <c r="B135" s="28">
+      <c r="B135" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A135,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C135" s="31"/>
+      <c r="C135" s="33"/>
     </row>
     <row r="136">
-      <c r="A136" s="27">
+      <c r="A136" s="29">
         <v>46175</v>
       </c>
-      <c r="B136" s="28">
+      <c r="B136" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A136,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C136" s="31"/>
+      <c r="C136" s="33"/>
     </row>
     <row r="137">
-      <c r="A137" s="27">
+      <c r="A137" s="29">
         <v>46176</v>
       </c>
-      <c r="B137" s="28">
+      <c r="B137" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A137,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C137" s="31"/>
+      <c r="C137" s="33"/>
     </row>
     <row r="138">
-      <c r="A138" s="27">
+      <c r="A138" s="29">
         <v>46177</v>
       </c>
-      <c r="B138" s="28">
+      <c r="B138" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A138,Journal[Temps])</f>
         <v>0.2986111111111111</v>
       </c>
-      <c r="C138" s="31"/>
+      <c r="C138" s="33"/>
     </row>
     <row r="139">
-      <c r="A139" s="27">
+      <c r="A139" s="29">
         <v>46178</v>
       </c>
-      <c r="B139" s="28">
+      <c r="B139" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A139,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C139" s="31"/>
+      <c r="C139" s="33"/>
     </row>
     <row r="140">
-      <c r="A140" s="27">
+      <c r="A140" s="29">
         <v>46179</v>
       </c>
-      <c r="B140" s="28">
+      <c r="B140" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A140,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C140" s="31"/>
+      <c r="C140" s="33"/>
     </row>
     <row r="141">
-      <c r="A141" s="27">
+      <c r="A141" s="29">
         <v>46180</v>
       </c>
-      <c r="B141" s="28">
+      <c r="B141" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A141,Journal[Temps])</f>
-        <v>4.1666666666666664e-002</v>
-      </c>
-      <c r="C141" s="31"/>
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="C141" s="33"/>
     </row>
     <row r="142">
-      <c r="A142" s="27">
+      <c r="A142" s="29">
         <v>46181</v>
       </c>
-      <c r="B142" s="28">
+      <c r="B142" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A142,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C142" s="31"/>
+      <c r="C142" s="33"/>
     </row>
     <row r="143">
-      <c r="A143" s="27">
+      <c r="A143" s="29">
         <v>46182</v>
       </c>
-      <c r="B143" s="28">
+      <c r="B143" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A143,Journal[Temps])</f>
-        <v>0</v>
-      </c>
-      <c r="C143" s="31"/>
+        <v>0.09375</v>
+      </c>
+      <c r="C143" s="33"/>
     </row>
     <row r="144">
-      <c r="A144" s="27">
+      <c r="A144" s="29">
         <v>46183</v>
       </c>
-      <c r="B144" s="28">
+      <c r="B144" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A144,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C144" s="31"/>
+      <c r="C144" s="33"/>
     </row>
     <row r="145">
-      <c r="A145" s="27">
+      <c r="A145" s="29">
         <v>46184</v>
       </c>
-      <c r="B145" s="28">
+      <c r="B145" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A145,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C145" s="31"/>
+      <c r="C145" s="33"/>
     </row>
     <row r="146">
-      <c r="A146" s="27">
+      <c r="A146" s="29">
         <v>46185</v>
       </c>
-      <c r="B146" s="28">
+      <c r="B146" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A146,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C146" s="31"/>
+      <c r="C146" s="33"/>
     </row>
     <row r="147">
-      <c r="A147" s="27">
+      <c r="A147" s="29">
         <v>46186</v>
       </c>
-      <c r="B147" s="28">
+      <c r="B147" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A147,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C147" s="31"/>
+      <c r="C147" s="33"/>
     </row>
     <row r="148">
-      <c r="A148" s="27">
+      <c r="A148" s="29">
         <v>46187</v>
       </c>
-      <c r="B148" s="28">
+      <c r="B148" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A148,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C148" s="31"/>
+      <c r="C148" s="33"/>
     </row>
     <row r="149">
-      <c r="A149" s="27">
+      <c r="A149" s="29">
         <v>46188</v>
       </c>
-      <c r="B149" s="28">
+      <c r="B149" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A149,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C149" s="31"/>
+      <c r="C149" s="33"/>
     </row>
     <row r="150">
-      <c r="A150" s="27">
+      <c r="A150" s="29">
         <v>46189</v>
       </c>
-      <c r="B150" s="28">
+      <c r="B150" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A150,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C150" s="31"/>
+      <c r="C150" s="33"/>
     </row>
     <row r="151">
-      <c r="A151" s="27">
+      <c r="A151" s="29">
         <v>46190</v>
       </c>
-      <c r="B151" s="28">
+      <c r="B151" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A151,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C151" s="31"/>
+      <c r="C151" s="33"/>
     </row>
     <row r="152">
-      <c r="A152" s="27">
+      <c r="A152" s="29">
         <v>46191</v>
       </c>
-      <c r="B152" s="28">
+      <c r="B152" s="30">
         <f>SUMIF(Journal[date],SommeParJours!A152,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C152" s="31"/>
+      <c r="C152" s="33"/>
     </row>
     <row r="153">
-      <c r="A153" s="27"/>
-      <c r="B153" s="32"/>
-      <c r="C153" s="31"/>
+      <c r="A153" s="29"/>
+      <c r="B153" s="34"/>
+      <c r="C153" s="33"/>
     </row>
     <row r="154">
-      <c r="A154" s="27"/>
-      <c r="B154" s="32"/>
-      <c r="C154" s="31"/>
+      <c r="A154" s="29"/>
+      <c r="B154" s="34"/>
+      <c r="C154" s="33"/>
     </row>
     <row r="155">
-      <c r="A155" s="27"/>
-      <c r="B155" s="32"/>
-      <c r="C155" s="31"/>
+      <c r="A155" s="29"/>
+      <c r="B155" s="34"/>
+      <c r="C155" s="33"/>
     </row>
     <row r="156">
-      <c r="A156" s="27"/>
-      <c r="B156" s="32"/>
-      <c r="C156" s="31"/>
+      <c r="A156" s="29"/>
+      <c r="B156" s="34"/>
+      <c r="C156" s="33"/>
     </row>
     <row r="157">
-      <c r="A157" s="27"/>
-      <c r="B157" s="32"/>
-      <c r="C157" s="31"/>
+      <c r="A157" s="29"/>
+      <c r="B157" s="34"/>
+      <c r="C157" s="33"/>
     </row>
     <row r="158">
-      <c r="A158" s="27"/>
-      <c r="B158" s="32"/>
-      <c r="C158" s="31"/>
+      <c r="A158" s="29"/>
+      <c r="B158" s="34"/>
+      <c r="C158" s="33"/>
     </row>
     <row r="159">
-      <c r="A159" s="27"/>
-      <c r="B159" s="32"/>
-      <c r="C159" s="31"/>
+      <c r="A159" s="29"/>
+      <c r="B159" s="34"/>
+      <c r="C159" s="33"/>
     </row>
     <row r="160">
-      <c r="A160" s="27"/>
-      <c r="B160" s="32"/>
+      <c r="A160" s="29"/>
+      <c r="B160" s="34"/>
     </row>
     <row r="161">
-      <c r="A161" s="27"/>
-      <c r="B161" s="32"/>
+      <c r="A161" s="29"/>
+      <c r="B161" s="34"/>
     </row>
     <row r="162">
-      <c r="A162" s="27"/>
-      <c r="B162" s="32"/>
+      <c r="A162" s="29"/>
+      <c r="B162" s="34"/>
     </row>
     <row r="163">
-      <c r="A163" s="27"/>
-      <c r="B163" s="32"/>
+      <c r="A163" s="29"/>
+      <c r="B163" s="34"/>
     </row>
     <row r="164">
-      <c r="A164" s="27"/>
-      <c r="B164" s="32"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="34"/>
     </row>
     <row r="165">
-      <c r="A165" s="27"/>
-      <c r="B165" s="32"/>
+      <c r="A165" s="29"/>
+      <c r="B165" s="34"/>
     </row>
     <row r="166">
-      <c r="A166" s="27"/>
-      <c r="B166" s="32"/>
+      <c r="A166" s="29"/>
+      <c r="B166" s="34"/>
     </row>
     <row r="167">
-      <c r="A167" s="27"/>
-      <c r="B167" s="32"/>
+      <c r="A167" s="29"/>
+      <c r="B167" s="34"/>
     </row>
     <row r="168">
-      <c r="A168" s="27"/>
-      <c r="B168" s="32"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="34"/>
     </row>
     <row r="169">
-      <c r="A169" s="27"/>
-      <c r="B169" s="32"/>
+      <c r="A169" s="29"/>
+      <c r="B169" s="34"/>
     </row>
     <row r="170">
-      <c r="A170" s="27"/>
-      <c r="B170" s="32"/>
+      <c r="A170" s="29"/>
+      <c r="B170" s="34"/>
     </row>
     <row r="171">
-      <c r="A171" s="27"/>
-      <c r="B171" s="32"/>
+      <c r="A171" s="29"/>
+      <c r="B171" s="34"/>
     </row>
     <row r="172">
-      <c r="A172" s="27"/>
-      <c r="B172" s="32"/>
+      <c r="A172" s="29"/>
+      <c r="B172" s="34"/>
     </row>
     <row r="173">
-      <c r="A173" s="27"/>
-      <c r="B173" s="32"/>
+      <c r="A173" s="29"/>
+      <c r="B173" s="34"/>
     </row>
     <row r="174">
-      <c r="A174" s="27"/>
-      <c r="B174" s="32"/>
+      <c r="A174" s="29"/>
+      <c r="B174" s="34"/>
     </row>
     <row r="175">
-      <c r="A175" s="27"/>
-      <c r="B175" s="32"/>
+      <c r="A175" s="29"/>
+      <c r="B175" s="34"/>
     </row>
     <row r="176">
-      <c r="A176" s="27"/>
-      <c r="B176" s="32"/>
+      <c r="A176" s="29"/>
+      <c r="B176" s="34"/>
     </row>
     <row r="177">
-      <c r="A177" s="27"/>
-      <c r="B177" s="32"/>
+      <c r="A177" s="29"/>
+      <c r="B177" s="34"/>
     </row>
     <row r="178">
-      <c r="A178" s="27"/>
-      <c r="B178" s="32"/>
+      <c r="A178" s="29"/>
+      <c r="B178" s="34"/>
     </row>
     <row r="179">
-      <c r="A179" s="27"/>
-      <c r="B179" s="32"/>
+      <c r="A179" s="29"/>
+      <c r="B179" s="34"/>
     </row>
     <row r="180">
-      <c r="A180" s="27"/>
-      <c r="B180" s="32"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="34"/>
     </row>
     <row r="181">
-      <c r="A181" s="27"/>
-      <c r="B181" s="32"/>
+      <c r="A181" s="29"/>
+      <c r="B181" s="34"/>
     </row>
     <row r="182">
-      <c r="A182" s="27"/>
-      <c r="B182" s="32"/>
+      <c r="A182" s="29"/>
+      <c r="B182" s="34"/>
     </row>
     <row r="183">
-      <c r="A183" s="27"/>
-      <c r="B183" s="32"/>
+      <c r="A183" s="29"/>
+      <c r="B183" s="34"/>
     </row>
     <row r="184">
-      <c r="A184" s="27"/>
-      <c r="B184" s="32"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="34"/>
     </row>
     <row r="185">
-      <c r="A185" s="27"/>
-      <c r="B185" s="32"/>
+      <c r="A185" s="29"/>
+      <c r="B185" s="34"/>
     </row>
     <row r="186">
-      <c r="A186" s="27"/>
-      <c r="B186" s="32"/>
+      <c r="A186" s="29"/>
+      <c r="B186" s="34"/>
     </row>
     <row r="187">
-      <c r="A187" s="27"/>
-      <c r="B187" s="32"/>
+      <c r="A187" s="29"/>
+      <c r="B187" s="34"/>
     </row>
     <row r="188">
-      <c r="A188" s="32"/>
-      <c r="B188" s="32"/>
+      <c r="A188" s="34"/>
+      <c r="B188" s="34"/>
     </row>
     <row r="189">
-      <c r="A189" s="32"/>
-      <c r="B189" s="32"/>
+      <c r="A189" s="34"/>
+      <c r="B189" s="34"/>
     </row>
     <row r="190">
-      <c r="A190" s="32"/>
-      <c r="B190" s="32"/>
+      <c r="A190" s="34"/>
+      <c r="B190" s="34"/>
     </row>
     <row r="191">
-      <c r="A191" s="32"/>
-      <c r="B191" s="32"/>
+      <c r="A191" s="34"/>
+      <c r="B191" s="34"/>
     </row>
     <row r="192">
-      <c r="A192" s="32"/>
-      <c r="B192" s="32"/>
+      <c r="A192" s="34"/>
+      <c r="B192" s="34"/>
     </row>
     <row r="193">
-      <c r="A193" s="32"/>
-      <c r="B193" s="32"/>
+      <c r="A193" s="34"/>
+      <c r="B193" s="34"/>
     </row>
     <row r="194">
-      <c r="A194" s="32"/>
-      <c r="B194" s="32"/>
+      <c r="A194" s="34"/>
+      <c r="B194" s="34"/>
     </row>
     <row r="195">
-      <c r="A195" s="32"/>
-      <c r="B195" s="32"/>
+      <c r="A195" s="34"/>
+      <c r="B195" s="34"/>
     </row>
     <row r="196">
-      <c r="A196" s="32"/>
-      <c r="B196" s="32"/>
+      <c r="A196" s="34"/>
+      <c r="B196" s="34"/>
     </row>
     <row r="197">
-      <c r="A197" s="32"/>
-      <c r="B197" s="32"/>
+      <c r="A197" s="34"/>
+      <c r="B197" s="34"/>
     </row>
     <row r="198">
-      <c r="A198" s="32"/>
-      <c r="B198" s="32"/>
+      <c r="A198" s="34"/>
+      <c r="B198" s="34"/>
     </row>
     <row r="199">
-      <c r="A199" s="32"/>
-      <c r="B199" s="32"/>
+      <c r="A199" s="34"/>
+      <c r="B199" s="34"/>
     </row>
     <row r="200">
-      <c r="A200" s="32"/>
-      <c r="B200" s="32"/>
+      <c r="A200" s="34"/>
+      <c r="B200" s="34"/>
     </row>
     <row r="201">
-      <c r="A201" s="32"/>
-      <c r="B201" s="32"/>
+      <c r="A201" s="34"/>
+      <c r="B201" s="34"/>
     </row>
     <row r="202">
-      <c r="A202" s="32"/>
-      <c r="B202" s="32"/>
+      <c r="A202" s="34"/>
+      <c r="B202" s="34"/>
     </row>
     <row r="203">
-      <c r="A203" s="32"/>
-      <c r="B203" s="32"/>
+      <c r="A203" s="34"/>
+      <c r="B203" s="34"/>
     </row>
     <row r="204">
-      <c r="A204" s="32"/>
-      <c r="B204" s="32"/>
+      <c r="A204" s="34"/>
+      <c r="B204" s="34"/>
     </row>
     <row r="205">
-      <c r="A205" s="32"/>
-      <c r="B205" s="32"/>
+      <c r="A205" s="34"/>
+      <c r="B205" s="34"/>
     </row>
     <row r="206">
-      <c r="A206" s="32"/>
-      <c r="B206" s="32"/>
+      <c r="A206" s="34"/>
+      <c r="B206" s="34"/>
     </row>
     <row r="207">
-      <c r="A207" s="32"/>
-      <c r="B207" s="32"/>
+      <c r="A207" s="34"/>
+      <c r="B207" s="34"/>
     </row>
     <row r="208">
-      <c r="A208" s="32"/>
-      <c r="B208" s="32"/>
+      <c r="A208" s="34"/>
+      <c r="B208" s="34"/>
     </row>
     <row r="209">
-      <c r="A209" s="32"/>
-      <c r="B209" s="32"/>
+      <c r="A209" s="34"/>
+      <c r="B209" s="34"/>
     </row>
     <row r="210">
-      <c r="A210" s="32"/>
-      <c r="B210" s="32"/>
+      <c r="A210" s="34"/>
+      <c r="B210" s="34"/>
     </row>
     <row r="211">
-      <c r="A211" s="32"/>
-      <c r="B211" s="32"/>
+      <c r="A211" s="34"/>
+      <c r="B211" s="34"/>
     </row>
     <row r="212">
-      <c r="A212" s="32"/>
-      <c r="B212" s="32"/>
+      <c r="A212" s="34"/>
+      <c r="B212" s="34"/>
     </row>
     <row r="213">
-      <c r="A213" s="32"/>
-      <c r="B213" s="32"/>
+      <c r="A213" s="34"/>
+      <c r="B213" s="34"/>
     </row>
     <row r="214">
-      <c r="A214" s="32"/>
-      <c r="B214" s="32"/>
+      <c r="A214" s="34"/>
+      <c r="B214" s="34"/>
     </row>
     <row r="215">
-      <c r="A215" s="32"/>
-      <c r="B215" s="32"/>
+      <c r="A215" s="34"/>
+      <c r="B215" s="34"/>
     </row>
     <row r="216">
-      <c r="A216" s="32"/>
-      <c r="B216" s="32"/>
+      <c r="A216" s="34"/>
+      <c r="B216" s="34"/>
     </row>
     <row r="217">
-      <c r="A217" s="32"/>
-      <c r="B217" s="32"/>
+      <c r="A217" s="34"/>
+      <c r="B217" s="34"/>
     </row>
     <row r="218">
-      <c r="A218" s="32"/>
-      <c r="B218" s="32"/>
+      <c r="A218" s="34"/>
+      <c r="B218" s="34"/>
     </row>
     <row r="219">
-      <c r="A219" s="32"/>
-      <c r="B219" s="32"/>
+      <c r="A219" s="34"/>
+      <c r="B219" s="34"/>
     </row>
     <row r="220">
-      <c r="A220" s="32"/>
-      <c r="B220" s="32"/>
+      <c r="A220" s="34"/>
+      <c r="B220" s="34"/>
     </row>
     <row r="221">
-      <c r="A221" s="32"/>
-      <c r="B221" s="32"/>
+      <c r="A221" s="34"/>
+      <c r="B221" s="34"/>
     </row>
     <row r="222">
-      <c r="A222" s="32"/>
-      <c r="B222" s="32"/>
+      <c r="A222" s="34"/>
+      <c r="B222" s="34"/>
     </row>
     <row r="223">
-      <c r="A223" s="32"/>
-      <c r="B223" s="32"/>
+      <c r="A223" s="34"/>
+      <c r="B223" s="34"/>
     </row>
     <row r="224">
-      <c r="A224" s="32"/>
-      <c r="B224" s="32"/>
+      <c r="A224" s="34"/>
+      <c r="B224" s="34"/>
     </row>
     <row r="225">
-      <c r="A225" s="32"/>
-      <c r="B225" s="32"/>
+      <c r="A225" s="34"/>
+      <c r="B225" s="34"/>
     </row>
     <row r="226">
-      <c r="A226" s="32"/>
-      <c r="B226" s="32"/>
+      <c r="A226" s="34"/>
+      <c r="B226" s="34"/>
     </row>
     <row r="227">
-      <c r="A227" s="32"/>
-      <c r="B227" s="32"/>
+      <c r="A227" s="34"/>
+      <c r="B227" s="34"/>
     </row>
     <row r="228">
-      <c r="A228" s="32"/>
-      <c r="B228" s="32"/>
+      <c r="A228" s="34"/>
+      <c r="B228" s="34"/>
     </row>
     <row r="229">
-      <c r="A229" s="32"/>
-      <c r="B229" s="32"/>
+      <c r="A229" s="34"/>
+      <c r="B229" s="34"/>
     </row>
     <row r="230">
-      <c r="A230" s="32"/>
-      <c r="B230" s="32"/>
+      <c r="A230" s="34"/>
+      <c r="B230" s="34"/>
     </row>
     <row r="231">
-      <c r="A231" s="32"/>
-      <c r="B231" s="32"/>
+      <c r="A231" s="34"/>
+      <c r="B231" s="34"/>
     </row>
     <row r="232">
-      <c r="A232" s="32"/>
-      <c r="B232" s="32"/>
+      <c r="A232" s="34"/>
+      <c r="B232" s="34"/>
     </row>
     <row r="233">
-      <c r="A233" s="32"/>
-      <c r="B233" s="32"/>
+      <c r="A233" s="34"/>
+      <c r="B233" s="34"/>
     </row>
     <row r="234">
-      <c r="A234" s="32"/>
-      <c r="B234" s="32"/>
+      <c r="A234" s="34"/>
+      <c r="B234" s="34"/>
     </row>
     <row r="235">
-      <c r="A235" s="32"/>
-      <c r="B235" s="32"/>
+      <c r="A235" s="34"/>
+      <c r="B235" s="34"/>
     </row>
     <row r="236">
-      <c r="A236" s="32"/>
-      <c r="B236" s="32"/>
+      <c r="A236" s="34"/>
+      <c r="B236" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8967,2034 +8995,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="33" width="6"/>
+    <col customWidth="1" min="12" max="12" style="35" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="33" width="6"/>
+    <col customWidth="1" min="23" max="23" style="35" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="33" width="6"/>
+    <col customWidth="1" min="30" max="30" style="35" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="34" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="C1" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="D1" s="37" t="s">
+    <row r="1" s="36" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="F1" s="38" t="s">
+      <c r="E1" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="F1" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="I1" s="37" t="s">
+      <c r="H1" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="L1" s="41" t="s">
-        <v>118</v>
-      </c>
-      <c r="M1" s="37" t="s">
+      <c r="K1" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="L1" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="N1" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="P1" s="37" t="s">
+      <c r="O1" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="P1" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="R1" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="S1" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="T1" s="37" t="s">
+      <c r="Q1" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="R1" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="U1" s="37" t="s">
+      <c r="S1" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="V1" s="39" t="s">
+      <c r="T1" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="W1" s="42" t="s">
+      <c r="U1" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="X1" s="37" t="s">
+      <c r="V1" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="Y1" s="37" t="s">
+      <c r="W1" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="Z1" s="39" t="s">
+      <c r="X1" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="AA1" s="43" t="s">
+      <c r="Y1" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="AB1" s="44" t="s">
+      <c r="Z1" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="AC1" s="44" t="s">
+      <c r="AA1" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="AD1" s="41" t="s">
+      <c r="AB1" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="AE1" s="45" t="s">
+      <c r="AC1" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="AF1" s="46" t="s">
+      <c r="AD1" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="AG1" s="47" t="s">
+      <c r="AE1" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF1" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG1" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="AH1" s="47" t="s">
-        <v>136</v>
-      </c>
-      <c r="AI1" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="AJ1" s="47" t="s">
+      <c r="AH1" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="AK1" s="44" t="s">
+      <c r="AI1" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="AL1" s="48"/>
-      <c r="AM1" s="48"/>
-      <c r="AN1" s="48"/>
-      <c r="AO1" s="48"/>
-      <c r="AP1" s="48"/>
-      <c r="AQ1" s="48"/>
-      <c r="AR1" s="48"/>
-      <c r="AS1" s="48"/>
-      <c r="AT1" s="48"/>
-      <c r="AU1" s="48"/>
+      <c r="AJ1" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="AK1" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="AL1" s="50"/>
+      <c r="AM1" s="50"/>
+      <c r="AN1" s="50"/>
+      <c r="AO1" s="50"/>
+      <c r="AP1" s="50"/>
+      <c r="AQ1" s="50"/>
+      <c r="AR1" s="50"/>
+      <c r="AS1" s="50"/>
+      <c r="AT1" s="50"/>
+      <c r="AU1" s="50"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="56"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="56"/>
-      <c r="AA2" s="57"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="56"/>
-      <c r="AF2" s="57"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="58"/>
+      <c r="AA2" s="59"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="58"/>
+      <c r="AF2" s="59"/>
+      <c r="AG2" s="53"/>
+      <c r="AH2" s="53"/>
+      <c r="AI2" s="53"/>
+      <c r="AJ2" s="53"/>
+      <c r="AK2" s="53"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="58"/>
-      <c r="X3" s="51"/>
-      <c r="Y3" s="51"/>
-      <c r="Z3" s="56"/>
-      <c r="AA3" s="57"/>
-      <c r="AB3" s="51"/>
-      <c r="AC3" s="51"/>
-      <c r="AD3" s="55"/>
-      <c r="AE3" s="56"/>
-      <c r="AF3" s="57"/>
-      <c r="AG3" s="51"/>
-      <c r="AH3" s="51"/>
-      <c r="AI3" s="51"/>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="62"/>
+      <c r="J3" s="62"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="58"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="53"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="53"/>
+      <c r="V3" s="58"/>
+      <c r="W3" s="60"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="53"/>
+      <c r="Z3" s="58"/>
+      <c r="AA3" s="59"/>
+      <c r="AB3" s="53"/>
+      <c r="AC3" s="53"/>
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="58"/>
+      <c r="AF3" s="59"/>
+      <c r="AG3" s="53"/>
+      <c r="AH3" s="53"/>
+      <c r="AI3" s="53"/>
+      <c r="AJ3" s="53"/>
+      <c r="AK3" s="53"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="49"/>
-      <c r="C4" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="57"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="58"/>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="57"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="55"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="57"/>
-      <c r="AG4" s="51"/>
-      <c r="AH4" s="51"/>
-      <c r="AI4" s="51"/>
-      <c r="AJ4" s="51"/>
-      <c r="AK4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="53"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="53"/>
+      <c r="T4" s="53"/>
+      <c r="U4" s="53"/>
+      <c r="V4" s="58"/>
+      <c r="W4" s="60"/>
+      <c r="X4" s="53"/>
+      <c r="Y4" s="53"/>
+      <c r="Z4" s="58"/>
+      <c r="AA4" s="59"/>
+      <c r="AB4" s="53"/>
+      <c r="AC4" s="53"/>
+      <c r="AD4" s="57"/>
+      <c r="AE4" s="58"/>
+      <c r="AF4" s="59"/>
+      <c r="AG4" s="53"/>
+      <c r="AH4" s="53"/>
+      <c r="AI4" s="53"/>
+      <c r="AJ4" s="53"/>
+      <c r="AK4" s="53"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="57"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="51"/>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="58"/>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="51"/>
-      <c r="Z5" s="56"/>
-      <c r="AA5" s="57"/>
-      <c r="AB5" s="51"/>
-      <c r="AC5" s="51"/>
-      <c r="AD5" s="55"/>
-      <c r="AE5" s="56"/>
-      <c r="AF5" s="57"/>
-      <c r="AG5" s="51"/>
-      <c r="AH5" s="51"/>
-      <c r="AI5" s="51"/>
-      <c r="AJ5" s="51"/>
-      <c r="AK5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="53"/>
+      <c r="T5" s="53"/>
+      <c r="U5" s="53"/>
+      <c r="V5" s="58"/>
+      <c r="W5" s="60"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="53"/>
+      <c r="Z5" s="58"/>
+      <c r="AA5" s="59"/>
+      <c r="AB5" s="53"/>
+      <c r="AC5" s="53"/>
+      <c r="AD5" s="57"/>
+      <c r="AE5" s="58"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="53"/>
+      <c r="AI5" s="53"/>
+      <c r="AJ5" s="53"/>
+      <c r="AK5" s="53"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="49"/>
-      <c r="C6" s="50" t="s">
+      <c r="B6" s="51"/>
+      <c r="C6" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="51"/>
-      <c r="V6" s="56"/>
-      <c r="W6" s="58"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="51"/>
-      <c r="Z6" s="56"/>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="51"/>
-      <c r="AC6" s="51"/>
-      <c r="AD6" s="55"/>
-      <c r="AE6" s="53"/>
-      <c r="AF6" s="54"/>
-      <c r="AG6" s="65"/>
-      <c r="AH6" s="65"/>
-      <c r="AI6" s="65"/>
-      <c r="AJ6" s="65"/>
-      <c r="AK6" s="65"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="53"/>
+      <c r="Q6" s="53"/>
+      <c r="R6" s="53"/>
+      <c r="S6" s="53"/>
+      <c r="T6" s="53"/>
+      <c r="U6" s="53"/>
+      <c r="V6" s="58"/>
+      <c r="W6" s="60"/>
+      <c r="X6" s="53"/>
+      <c r="Y6" s="53"/>
+      <c r="Z6" s="58"/>
+      <c r="AA6" s="59"/>
+      <c r="AB6" s="53"/>
+      <c r="AC6" s="53"/>
+      <c r="AD6" s="57"/>
+      <c r="AE6" s="55"/>
+      <c r="AF6" s="56"/>
+      <c r="AG6" s="67"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
+      <c r="AK6" s="67"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="49"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="63"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="58"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
-      <c r="Z7" s="56"/>
-      <c r="AA7" s="57"/>
-      <c r="AB7" s="51"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="55"/>
-      <c r="AE7" s="56"/>
-      <c r="AF7" s="57"/>
-      <c r="AG7" s="51"/>
-      <c r="AH7" s="51"/>
-      <c r="AI7" s="51"/>
-      <c r="AJ7" s="51"/>
-      <c r="AK7" s="51"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="65"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="65"/>
+      <c r="P7" s="53"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="53"/>
+      <c r="S7" s="53"/>
+      <c r="T7" s="53"/>
+      <c r="U7" s="53"/>
+      <c r="V7" s="58"/>
+      <c r="W7" s="60"/>
+      <c r="X7" s="53"/>
+      <c r="Y7" s="53"/>
+      <c r="Z7" s="58"/>
+      <c r="AA7" s="59"/>
+      <c r="AB7" s="53"/>
+      <c r="AC7" s="53"/>
+      <c r="AD7" s="57"/>
+      <c r="AE7" s="58"/>
+      <c r="AF7" s="59"/>
+      <c r="AG7" s="53"/>
+      <c r="AH7" s="53"/>
+      <c r="AI7" s="53"/>
+      <c r="AJ7" s="53"/>
+      <c r="AK7" s="53"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="49"/>
-      <c r="C8" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="65"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="65"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="65"/>
-      <c r="Q8" s="65"/>
-      <c r="R8" s="65"/>
-      <c r="S8" s="65"/>
-      <c r="T8" s="65"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="53"/>
-      <c r="W8" s="58"/>
-      <c r="X8" s="65"/>
-      <c r="Y8" s="65"/>
-      <c r="Z8" s="53"/>
-      <c r="AA8" s="54"/>
-      <c r="AB8" s="65"/>
-      <c r="AC8" s="65"/>
-      <c r="AD8" s="55"/>
-      <c r="AE8" s="53"/>
-      <c r="AF8" s="54"/>
-      <c r="AG8" s="65"/>
-      <c r="AH8" s="65"/>
-      <c r="AI8" s="65"/>
-      <c r="AJ8" s="65"/>
-      <c r="AK8" s="65"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="52" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="67"/>
+      <c r="N8" s="55"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="67"/>
+      <c r="U8" s="67"/>
+      <c r="V8" s="55"/>
+      <c r="W8" s="60"/>
+      <c r="X8" s="67"/>
+      <c r="Y8" s="67"/>
+      <c r="Z8" s="55"/>
+      <c r="AA8" s="56"/>
+      <c r="AB8" s="67"/>
+      <c r="AC8" s="67"/>
+      <c r="AD8" s="57"/>
+      <c r="AE8" s="55"/>
+      <c r="AF8" s="56"/>
+      <c r="AG8" s="67"/>
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="67"/>
+      <c r="AJ8" s="67"/>
+      <c r="AK8" s="67"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="49"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="64"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="64"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="66"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="62"/>
-      <c r="W9" s="58"/>
-      <c r="X9" s="64"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="62"/>
-      <c r="AA9" s="63"/>
-      <c r="AB9" s="51"/>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="64"/>
-      <c r="AE9" s="56"/>
-      <c r="AF9" s="57"/>
-      <c r="AG9" s="51"/>
-      <c r="AH9" s="51"/>
-      <c r="AI9" s="51"/>
-      <c r="AJ9" s="51"/>
-      <c r="AK9" s="51"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="53"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="66"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="65"/>
+      <c r="P9" s="53"/>
+      <c r="Q9" s="66"/>
+      <c r="R9" s="53"/>
+      <c r="S9" s="68"/>
+      <c r="T9" s="53"/>
+      <c r="U9" s="53"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="60"/>
+      <c r="X9" s="66"/>
+      <c r="Y9" s="53"/>
+      <c r="Z9" s="64"/>
+      <c r="AA9" s="65"/>
+      <c r="AB9" s="53"/>
+      <c r="AC9" s="53"/>
+      <c r="AD9" s="66"/>
+      <c r="AE9" s="58"/>
+      <c r="AF9" s="59"/>
+      <c r="AG9" s="53"/>
+      <c r="AH9" s="53"/>
+      <c r="AI9" s="53"/>
+      <c r="AJ9" s="53"/>
+      <c r="AK9" s="53"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="49"/>
-      <c r="C10" s="50" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="57"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="51"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="51"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="58"/>
-      <c r="X10" s="65"/>
-      <c r="Y10" s="65"/>
-      <c r="Z10" s="53"/>
-      <c r="AA10" s="57"/>
-      <c r="AB10" s="51"/>
-      <c r="AC10" s="51"/>
-      <c r="AD10" s="55"/>
-      <c r="AE10" s="56"/>
-      <c r="AF10" s="57"/>
-      <c r="AG10" s="51"/>
-      <c r="AH10" s="51"/>
-      <c r="AI10" s="51"/>
-      <c r="AJ10" s="51"/>
-      <c r="AK10" s="51"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="53"/>
+      <c r="K10" s="53"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="58"/>
+      <c r="O10" s="59"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="53"/>
+      <c r="U10" s="53"/>
+      <c r="V10" s="55"/>
+      <c r="W10" s="60"/>
+      <c r="X10" s="67"/>
+      <c r="Y10" s="67"/>
+      <c r="Z10" s="55"/>
+      <c r="AA10" s="59"/>
+      <c r="AB10" s="53"/>
+      <c r="AC10" s="53"/>
+      <c r="AD10" s="57"/>
+      <c r="AE10" s="58"/>
+      <c r="AF10" s="59"/>
+      <c r="AG10" s="53"/>
+      <c r="AH10" s="53"/>
+      <c r="AI10" s="53"/>
+      <c r="AJ10" s="53"/>
+      <c r="AK10" s="53"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="56"/>
-      <c r="O11" s="57"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="56"/>
-      <c r="W11" s="58"/>
-      <c r="X11" s="51"/>
-      <c r="Y11" s="51"/>
-      <c r="Z11" s="56"/>
-      <c r="AA11" s="57"/>
-      <c r="AB11" s="51"/>
-      <c r="AC11" s="51"/>
-      <c r="AD11" s="67"/>
-      <c r="AE11" s="56"/>
-      <c r="AF11" s="57"/>
-      <c r="AG11" s="51"/>
-      <c r="AH11" s="51"/>
-      <c r="AI11" s="51"/>
-      <c r="AJ11" s="51"/>
-      <c r="AK11" s="51"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="53"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="53"/>
+      <c r="N11" s="58"/>
+      <c r="O11" s="59"/>
+      <c r="P11" s="53"/>
+      <c r="Q11" s="53"/>
+      <c r="R11" s="53"/>
+      <c r="S11" s="53"/>
+      <c r="T11" s="53"/>
+      <c r="U11" s="53"/>
+      <c r="V11" s="58"/>
+      <c r="W11" s="60"/>
+      <c r="X11" s="53"/>
+      <c r="Y11" s="53"/>
+      <c r="Z11" s="58"/>
+      <c r="AA11" s="59"/>
+      <c r="AB11" s="53"/>
+      <c r="AC11" s="53"/>
+      <c r="AD11" s="69"/>
+      <c r="AE11" s="58"/>
+      <c r="AF11" s="59"/>
+      <c r="AG11" s="53"/>
+      <c r="AH11" s="53"/>
+      <c r="AI11" s="53"/>
+      <c r="AJ11" s="53"/>
+      <c r="AK11" s="53"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="49"/>
-      <c r="C12" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="56"/>
-      <c r="O12" s="57"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="51"/>
-      <c r="U12" s="51"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="58"/>
-      <c r="X12" s="51"/>
-      <c r="Y12" s="51"/>
-      <c r="Z12" s="56"/>
-      <c r="AA12" s="57"/>
-      <c r="AB12" s="51"/>
-      <c r="AC12" s="51"/>
-      <c r="AD12" s="55"/>
-      <c r="AE12" s="56"/>
-      <c r="AF12" s="54"/>
-      <c r="AG12" s="65"/>
-      <c r="AH12" s="65"/>
-      <c r="AI12" s="65"/>
-      <c r="AJ12" s="65"/>
-      <c r="AK12" s="65"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="59"/>
+      <c r="P12" s="53"/>
+      <c r="Q12" s="53"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="53"/>
+      <c r="T12" s="53"/>
+      <c r="U12" s="53"/>
+      <c r="V12" s="58"/>
+      <c r="W12" s="60"/>
+      <c r="X12" s="53"/>
+      <c r="Y12" s="53"/>
+      <c r="Z12" s="58"/>
+      <c r="AA12" s="59"/>
+      <c r="AB12" s="53"/>
+      <c r="AC12" s="53"/>
+      <c r="AD12" s="57"/>
+      <c r="AE12" s="58"/>
+      <c r="AF12" s="56"/>
+      <c r="AG12" s="67"/>
+      <c r="AH12" s="67"/>
+      <c r="AI12" s="67"/>
+      <c r="AJ12" s="67"/>
+      <c r="AK12" s="67"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="51"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="57"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="51"/>
-      <c r="U13" s="51"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="58"/>
-      <c r="X13" s="51"/>
-      <c r="Y13" s="51"/>
-      <c r="Z13" s="56"/>
-      <c r="AA13" s="57"/>
-      <c r="AB13" s="51"/>
-      <c r="AC13" s="51"/>
-      <c r="AD13" s="55"/>
-      <c r="AE13" s="56"/>
-      <c r="AF13" s="57"/>
-      <c r="AG13" s="51"/>
-      <c r="AH13" s="51"/>
-      <c r="AI13" s="51"/>
-      <c r="AJ13" s="51"/>
-      <c r="AK13" s="51"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="53"/>
+      <c r="K13" s="53"/>
+      <c r="L13" s="57"/>
+      <c r="M13" s="53"/>
+      <c r="N13" s="58"/>
+      <c r="O13" s="59"/>
+      <c r="P13" s="53"/>
+      <c r="Q13" s="53"/>
+      <c r="R13" s="53"/>
+      <c r="S13" s="53"/>
+      <c r="T13" s="53"/>
+      <c r="U13" s="53"/>
+      <c r="V13" s="58"/>
+      <c r="W13" s="60"/>
+      <c r="X13" s="53"/>
+      <c r="Y13" s="53"/>
+      <c r="Z13" s="58"/>
+      <c r="AA13" s="59"/>
+      <c r="AB13" s="53"/>
+      <c r="AC13" s="53"/>
+      <c r="AD13" s="57"/>
+      <c r="AE13" s="58"/>
+      <c r="AF13" s="59"/>
+      <c r="AG13" s="53"/>
+      <c r="AH13" s="53"/>
+      <c r="AI13" s="53"/>
+      <c r="AJ13" s="53"/>
+      <c r="AK13" s="53"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="68" t="s">
-        <v>144</v>
-      </c>
-      <c r="C14" s="69" t="s">
-        <v>145</v>
-      </c>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="71"/>
-      <c r="T14" s="71"/>
-      <c r="U14" s="71"/>
-      <c r="V14" s="72"/>
-      <c r="W14" s="58"/>
-      <c r="X14" s="71"/>
-      <c r="Y14" s="71"/>
-      <c r="Z14" s="72"/>
-      <c r="AA14" s="70"/>
-      <c r="AB14" s="71"/>
-      <c r="AC14" s="71"/>
-      <c r="AD14" s="55"/>
-      <c r="AE14" s="72"/>
-      <c r="AF14" s="70"/>
-      <c r="AG14" s="71"/>
-      <c r="AH14" s="71"/>
-      <c r="AI14" s="71"/>
-      <c r="AJ14" s="71"/>
-      <c r="AK14" s="71"/>
+      <c r="B14" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="54"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="74"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="73"/>
+      <c r="Q14" s="73"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="73"/>
+      <c r="T14" s="73"/>
+      <c r="U14" s="73"/>
+      <c r="V14" s="74"/>
+      <c r="W14" s="60"/>
+      <c r="X14" s="73"/>
+      <c r="Y14" s="73"/>
+      <c r="Z14" s="74"/>
+      <c r="AA14" s="72"/>
+      <c r="AB14" s="73"/>
+      <c r="AC14" s="73"/>
+      <c r="AD14" s="57"/>
+      <c r="AE14" s="74"/>
+      <c r="AF14" s="72"/>
+      <c r="AG14" s="73"/>
+      <c r="AH14" s="73"/>
+      <c r="AI14" s="73"/>
+      <c r="AJ14" s="73"/>
+      <c r="AK14" s="73"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="68"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-      <c r="T15" s="71"/>
-      <c r="U15" s="71"/>
-      <c r="V15" s="72"/>
-      <c r="W15" s="58"/>
-      <c r="X15" s="71"/>
-      <c r="Y15" s="71"/>
-      <c r="Z15" s="72"/>
-      <c r="AA15" s="70"/>
-      <c r="AB15" s="71"/>
-      <c r="AC15" s="71"/>
-      <c r="AD15" s="55"/>
-      <c r="AE15" s="72"/>
-      <c r="AF15" s="70"/>
-      <c r="AG15" s="71"/>
-      <c r="AH15" s="71"/>
-      <c r="AI15" s="71"/>
-      <c r="AJ15" s="71"/>
-      <c r="AK15" s="71"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="73"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="73"/>
+      <c r="T15" s="73"/>
+      <c r="U15" s="73"/>
+      <c r="V15" s="74"/>
+      <c r="W15" s="60"/>
+      <c r="X15" s="73"/>
+      <c r="Y15" s="73"/>
+      <c r="Z15" s="74"/>
+      <c r="AA15" s="72"/>
+      <c r="AB15" s="73"/>
+      <c r="AC15" s="73"/>
+      <c r="AD15" s="57"/>
+      <c r="AE15" s="74"/>
+      <c r="AF15" s="72"/>
+      <c r="AG15" s="73"/>
+      <c r="AH15" s="73"/>
+      <c r="AI15" s="73"/>
+      <c r="AJ15" s="73"/>
+      <c r="AK15" s="73"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="68"/>
-      <c r="C16" s="69" t="s">
-        <v>146</v>
-      </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="71"/>
-      <c r="T16" s="71"/>
-      <c r="U16" s="71"/>
-      <c r="V16" s="72"/>
-      <c r="W16" s="58"/>
-      <c r="X16" s="71"/>
-      <c r="Y16" s="71"/>
-      <c r="Z16" s="72"/>
-      <c r="AA16" s="70"/>
-      <c r="AB16" s="71"/>
-      <c r="AC16" s="71"/>
-      <c r="AD16" s="55"/>
-      <c r="AE16" s="72"/>
-      <c r="AF16" s="70"/>
-      <c r="AG16" s="71"/>
-      <c r="AH16" s="71"/>
-      <c r="AI16" s="71"/>
-      <c r="AJ16" s="71"/>
-      <c r="AK16" s="71"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="71" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="74"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="73"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="73"/>
+      <c r="T16" s="73"/>
+      <c r="U16" s="73"/>
+      <c r="V16" s="74"/>
+      <c r="W16" s="60"/>
+      <c r="X16" s="73"/>
+      <c r="Y16" s="73"/>
+      <c r="Z16" s="74"/>
+      <c r="AA16" s="72"/>
+      <c r="AB16" s="73"/>
+      <c r="AC16" s="73"/>
+      <c r="AD16" s="57"/>
+      <c r="AE16" s="74"/>
+      <c r="AF16" s="72"/>
+      <c r="AG16" s="73"/>
+      <c r="AH16" s="73"/>
+      <c r="AI16" s="73"/>
+      <c r="AJ16" s="73"/>
+      <c r="AK16" s="73"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="68"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="71"/>
-      <c r="U17" s="71"/>
-      <c r="V17" s="72"/>
-      <c r="W17" s="58"/>
-      <c r="X17" s="71"/>
-      <c r="Y17" s="71"/>
-      <c r="Z17" s="72"/>
-      <c r="AA17" s="70"/>
-      <c r="AB17" s="71"/>
-      <c r="AC17" s="71"/>
-      <c r="AD17" s="55"/>
-      <c r="AE17" s="72"/>
-      <c r="AF17" s="70"/>
-      <c r="AG17" s="71"/>
-      <c r="AH17" s="71"/>
-      <c r="AI17" s="71"/>
-      <c r="AJ17" s="71"/>
-      <c r="AK17" s="71"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="74"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="73"/>
+      <c r="Q17" s="73"/>
+      <c r="R17" s="73"/>
+      <c r="S17" s="73"/>
+      <c r="T17" s="73"/>
+      <c r="U17" s="73"/>
+      <c r="V17" s="74"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="73"/>
+      <c r="Y17" s="73"/>
+      <c r="Z17" s="74"/>
+      <c r="AA17" s="72"/>
+      <c r="AB17" s="73"/>
+      <c r="AC17" s="73"/>
+      <c r="AD17" s="57"/>
+      <c r="AE17" s="74"/>
+      <c r="AF17" s="72"/>
+      <c r="AG17" s="73"/>
+      <c r="AH17" s="73"/>
+      <c r="AI17" s="73"/>
+      <c r="AJ17" s="73"/>
+      <c r="AK17" s="73"/>
       <c r="AN17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="68"/>
-      <c r="C18" s="69" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="71"/>
-      <c r="S18" s="71"/>
-      <c r="T18" s="71"/>
-      <c r="U18" s="71"/>
-      <c r="V18" s="72"/>
-      <c r="W18" s="58"/>
-      <c r="X18" s="71"/>
-      <c r="Y18" s="71"/>
-      <c r="Z18" s="72"/>
-      <c r="AA18" s="70"/>
-      <c r="AB18" s="71"/>
-      <c r="AC18" s="71"/>
-      <c r="AD18" s="55"/>
-      <c r="AE18" s="72"/>
-      <c r="AF18" s="70"/>
-      <c r="AG18" s="71"/>
-      <c r="AH18" s="71"/>
-      <c r="AI18" s="71"/>
-      <c r="AJ18" s="71"/>
-      <c r="AK18" s="71"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="71" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="73"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="57"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="74"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="73"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="73"/>
+      <c r="T18" s="73"/>
+      <c r="U18" s="73"/>
+      <c r="V18" s="74"/>
+      <c r="W18" s="60"/>
+      <c r="X18" s="73"/>
+      <c r="Y18" s="73"/>
+      <c r="Z18" s="74"/>
+      <c r="AA18" s="72"/>
+      <c r="AB18" s="73"/>
+      <c r="AC18" s="73"/>
+      <c r="AD18" s="57"/>
+      <c r="AE18" s="74"/>
+      <c r="AF18" s="72"/>
+      <c r="AG18" s="73"/>
+      <c r="AH18" s="73"/>
+      <c r="AI18" s="73"/>
+      <c r="AJ18" s="73"/>
+      <c r="AK18" s="73"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="68"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="75"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
-      <c r="T19" s="71"/>
-      <c r="U19" s="71"/>
-      <c r="V19" s="72"/>
-      <c r="W19" s="58"/>
-      <c r="X19" s="71"/>
-      <c r="Y19" s="71"/>
-      <c r="Z19" s="72"/>
-      <c r="AA19" s="70"/>
-      <c r="AB19" s="71"/>
-      <c r="AC19" s="71"/>
-      <c r="AD19" s="55"/>
-      <c r="AE19" s="72"/>
-      <c r="AF19" s="70"/>
-      <c r="AG19" s="71"/>
-      <c r="AH19" s="71"/>
-      <c r="AI19" s="71"/>
-      <c r="AJ19" s="71"/>
-      <c r="AK19" s="71"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="73"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="74"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="73"/>
+      <c r="Q19" s="73"/>
+      <c r="R19" s="73"/>
+      <c r="S19" s="73"/>
+      <c r="T19" s="73"/>
+      <c r="U19" s="73"/>
+      <c r="V19" s="74"/>
+      <c r="W19" s="60"/>
+      <c r="X19" s="73"/>
+      <c r="Y19" s="73"/>
+      <c r="Z19" s="74"/>
+      <c r="AA19" s="72"/>
+      <c r="AB19" s="73"/>
+      <c r="AC19" s="73"/>
+      <c r="AD19" s="57"/>
+      <c r="AE19" s="74"/>
+      <c r="AF19" s="72"/>
+      <c r="AG19" s="73"/>
+      <c r="AH19" s="73"/>
+      <c r="AI19" s="73"/>
+      <c r="AJ19" s="73"/>
+      <c r="AK19" s="73"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="68"/>
-      <c r="C20" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="70"/>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="71"/>
-      <c r="S20" s="71"/>
-      <c r="T20" s="71"/>
-      <c r="U20" s="71"/>
-      <c r="V20" s="72"/>
-      <c r="W20" s="58"/>
-      <c r="X20" s="71"/>
-      <c r="Y20" s="71"/>
-      <c r="Z20" s="72"/>
-      <c r="AA20" s="70"/>
-      <c r="AB20" s="71"/>
-      <c r="AC20" s="71"/>
-      <c r="AD20" s="55"/>
-      <c r="AE20" s="72"/>
-      <c r="AF20" s="70"/>
-      <c r="AG20" s="71"/>
-      <c r="AH20" s="71"/>
-      <c r="AI20" s="71"/>
-      <c r="AJ20" s="71"/>
-      <c r="AK20" s="71"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="71" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="67"/>
+      <c r="J20" s="73"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="74"/>
+      <c r="O20" s="72"/>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="73"/>
+      <c r="R20" s="73"/>
+      <c r="S20" s="73"/>
+      <c r="T20" s="73"/>
+      <c r="U20" s="73"/>
+      <c r="V20" s="74"/>
+      <c r="W20" s="60"/>
+      <c r="X20" s="73"/>
+      <c r="Y20" s="73"/>
+      <c r="Z20" s="74"/>
+      <c r="AA20" s="72"/>
+      <c r="AB20" s="73"/>
+      <c r="AC20" s="73"/>
+      <c r="AD20" s="57"/>
+      <c r="AE20" s="74"/>
+      <c r="AF20" s="72"/>
+      <c r="AG20" s="73"/>
+      <c r="AH20" s="73"/>
+      <c r="AI20" s="73"/>
+      <c r="AJ20" s="73"/>
+      <c r="AK20" s="73"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="68"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="71"/>
-      <c r="T21" s="71"/>
-      <c r="U21" s="71"/>
-      <c r="V21" s="72"/>
-      <c r="W21" s="58"/>
-      <c r="X21" s="71"/>
-      <c r="Y21" s="71"/>
-      <c r="Z21" s="72"/>
-      <c r="AA21" s="70"/>
-      <c r="AB21" s="71"/>
-      <c r="AC21" s="71"/>
-      <c r="AD21" s="55"/>
-      <c r="AE21" s="72"/>
-      <c r="AF21" s="70"/>
-      <c r="AG21" s="71"/>
-      <c r="AH21" s="71"/>
-      <c r="AI21" s="71"/>
-      <c r="AJ21" s="71"/>
-      <c r="AK21" s="71"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="73"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="74"/>
+      <c r="O21" s="72"/>
+      <c r="P21" s="73"/>
+      <c r="Q21" s="73"/>
+      <c r="R21" s="73"/>
+      <c r="S21" s="73"/>
+      <c r="T21" s="73"/>
+      <c r="U21" s="73"/>
+      <c r="V21" s="74"/>
+      <c r="W21" s="60"/>
+      <c r="X21" s="73"/>
+      <c r="Y21" s="73"/>
+      <c r="Z21" s="74"/>
+      <c r="AA21" s="72"/>
+      <c r="AB21" s="73"/>
+      <c r="AC21" s="73"/>
+      <c r="AD21" s="57"/>
+      <c r="AE21" s="74"/>
+      <c r="AF21" s="72"/>
+      <c r="AG21" s="73"/>
+      <c r="AH21" s="73"/>
+      <c r="AI21" s="73"/>
+      <c r="AJ21" s="73"/>
+      <c r="AK21" s="73"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="68"/>
-      <c r="C22" s="69" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="71"/>
-      <c r="T22" s="71"/>
-      <c r="U22" s="71"/>
-      <c r="V22" s="72"/>
-      <c r="W22" s="58"/>
-      <c r="X22" s="71"/>
-      <c r="Y22" s="71"/>
-      <c r="Z22" s="72"/>
-      <c r="AA22" s="70"/>
-      <c r="AB22" s="71"/>
-      <c r="AC22" s="71"/>
-      <c r="AD22" s="55"/>
-      <c r="AE22" s="72"/>
-      <c r="AF22" s="70"/>
-      <c r="AG22" s="71"/>
-      <c r="AH22" s="71"/>
-      <c r="AI22" s="71"/>
-      <c r="AJ22" s="71"/>
-      <c r="AK22" s="71"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="71" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="56"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="57"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="73"/>
+      <c r="Q22" s="73"/>
+      <c r="R22" s="73"/>
+      <c r="S22" s="73"/>
+      <c r="T22" s="73"/>
+      <c r="U22" s="73"/>
+      <c r="V22" s="74"/>
+      <c r="W22" s="60"/>
+      <c r="X22" s="73"/>
+      <c r="Y22" s="73"/>
+      <c r="Z22" s="74"/>
+      <c r="AA22" s="72"/>
+      <c r="AB22" s="73"/>
+      <c r="AC22" s="73"/>
+      <c r="AD22" s="57"/>
+      <c r="AE22" s="74"/>
+      <c r="AF22" s="72"/>
+      <c r="AG22" s="73"/>
+      <c r="AH22" s="73"/>
+      <c r="AI22" s="73"/>
+      <c r="AJ22" s="73"/>
+      <c r="AK22" s="73"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="68"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="70"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="71"/>
-      <c r="S23" s="71"/>
-      <c r="T23" s="71"/>
-      <c r="U23" s="71"/>
-      <c r="V23" s="72"/>
-      <c r="W23" s="58"/>
-      <c r="X23" s="71"/>
-      <c r="Y23" s="71"/>
-      <c r="Z23" s="72"/>
-      <c r="AA23" s="70"/>
-      <c r="AB23" s="71"/>
-      <c r="AC23" s="71"/>
-      <c r="AD23" s="55"/>
-      <c r="AE23" s="72"/>
-      <c r="AF23" s="70"/>
-      <c r="AG23" s="71"/>
-      <c r="AH23" s="71"/>
-      <c r="AI23" s="71"/>
-      <c r="AJ23" s="71"/>
-      <c r="AK23" s="71"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="66"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="73"/>
+      <c r="Q23" s="73"/>
+      <c r="R23" s="73"/>
+      <c r="S23" s="73"/>
+      <c r="T23" s="73"/>
+      <c r="U23" s="73"/>
+      <c r="V23" s="74"/>
+      <c r="W23" s="60"/>
+      <c r="X23" s="73"/>
+      <c r="Y23" s="73"/>
+      <c r="Z23" s="74"/>
+      <c r="AA23" s="72"/>
+      <c r="AB23" s="73"/>
+      <c r="AC23" s="73"/>
+      <c r="AD23" s="57"/>
+      <c r="AE23" s="74"/>
+      <c r="AF23" s="72"/>
+      <c r="AG23" s="73"/>
+      <c r="AH23" s="73"/>
+      <c r="AI23" s="73"/>
+      <c r="AJ23" s="73"/>
+      <c r="AK23" s="73"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="68"/>
-      <c r="C24" s="69" t="s">
-        <v>151</v>
-      </c>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="71"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
-      <c r="R24" s="71"/>
-      <c r="S24" s="71"/>
-      <c r="T24" s="71"/>
-      <c r="U24" s="71"/>
-      <c r="V24" s="72"/>
-      <c r="W24" s="58"/>
-      <c r="X24" s="71"/>
-      <c r="Y24" s="71"/>
-      <c r="Z24" s="72"/>
-      <c r="AA24" s="70"/>
-      <c r="AB24" s="71"/>
-      <c r="AC24" s="71"/>
-      <c r="AD24" s="55"/>
-      <c r="AE24" s="72"/>
-      <c r="AF24" s="70"/>
-      <c r="AG24" s="71"/>
-      <c r="AH24" s="71"/>
-      <c r="AI24" s="71"/>
-      <c r="AJ24" s="71"/>
-      <c r="AK24" s="71"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="67"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="74"/>
+      <c r="O24" s="72"/>
+      <c r="P24" s="73"/>
+      <c r="Q24" s="73"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="73"/>
+      <c r="T24" s="73"/>
+      <c r="U24" s="73"/>
+      <c r="V24" s="74"/>
+      <c r="W24" s="60"/>
+      <c r="X24" s="73"/>
+      <c r="Y24" s="73"/>
+      <c r="Z24" s="74"/>
+      <c r="AA24" s="72"/>
+      <c r="AB24" s="73"/>
+      <c r="AC24" s="73"/>
+      <c r="AD24" s="57"/>
+      <c r="AE24" s="74"/>
+      <c r="AF24" s="72"/>
+      <c r="AG24" s="73"/>
+      <c r="AH24" s="73"/>
+      <c r="AI24" s="73"/>
+      <c r="AJ24" s="73"/>
+      <c r="AK24" s="73"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="68"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="60"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="70"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="71"/>
-      <c r="S25" s="71"/>
-      <c r="T25" s="71"/>
-      <c r="U25" s="71"/>
-      <c r="V25" s="72"/>
-      <c r="W25" s="58"/>
-      <c r="X25" s="71"/>
-      <c r="Y25" s="71"/>
-      <c r="Z25" s="72"/>
-      <c r="AA25" s="70"/>
-      <c r="AB25" s="71"/>
-      <c r="AC25" s="71"/>
-      <c r="AD25" s="55"/>
-      <c r="AE25" s="72"/>
-      <c r="AF25" s="70"/>
-      <c r="AG25" s="71"/>
-      <c r="AH25" s="71"/>
-      <c r="AI25" s="71"/>
-      <c r="AJ25" s="71"/>
-      <c r="AK25" s="71"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="74"/>
+      <c r="O25" s="72"/>
+      <c r="P25" s="73"/>
+      <c r="Q25" s="73"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="73"/>
+      <c r="T25" s="73"/>
+      <c r="U25" s="73"/>
+      <c r="V25" s="74"/>
+      <c r="W25" s="60"/>
+      <c r="X25" s="73"/>
+      <c r="Y25" s="73"/>
+      <c r="Z25" s="74"/>
+      <c r="AA25" s="72"/>
+      <c r="AB25" s="73"/>
+      <c r="AC25" s="73"/>
+      <c r="AD25" s="57"/>
+      <c r="AE25" s="74"/>
+      <c r="AF25" s="72"/>
+      <c r="AG25" s="73"/>
+      <c r="AH25" s="73"/>
+      <c r="AI25" s="73"/>
+      <c r="AJ25" s="73"/>
+      <c r="AK25" s="73"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="49" t="s">
-        <v>152</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="51"/>
-      <c r="N26" s="56"/>
-      <c r="O26" s="57"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="51"/>
-      <c r="R26" s="51"/>
-      <c r="S26" s="51"/>
-      <c r="T26" s="51"/>
-      <c r="U26" s="51"/>
-      <c r="V26" s="56"/>
-      <c r="W26" s="58"/>
-      <c r="X26" s="51"/>
-      <c r="Y26" s="51"/>
-      <c r="Z26" s="56"/>
-      <c r="AA26" s="57"/>
-      <c r="AB26" s="51"/>
-      <c r="AC26" s="51"/>
-      <c r="AD26" s="55"/>
-      <c r="AE26" s="56"/>
-      <c r="AF26" s="57"/>
-      <c r="AG26" s="51"/>
-      <c r="AH26" s="51"/>
-      <c r="AI26" s="51"/>
-      <c r="AJ26" s="51"/>
-      <c r="AK26" s="51"/>
+      <c r="B26" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="67"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="53"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="59"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
+      <c r="T26" s="53"/>
+      <c r="U26" s="53"/>
+      <c r="V26" s="58"/>
+      <c r="W26" s="60"/>
+      <c r="X26" s="53"/>
+      <c r="Y26" s="53"/>
+      <c r="Z26" s="58"/>
+      <c r="AA26" s="59"/>
+      <c r="AB26" s="53"/>
+      <c r="AC26" s="53"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="58"/>
+      <c r="AF26" s="59"/>
+      <c r="AG26" s="53"/>
+      <c r="AH26" s="53"/>
+      <c r="AI26" s="53"/>
+      <c r="AJ26" s="53"/>
+      <c r="AK26" s="53"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="49"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="51"/>
-      <c r="L27" s="55"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="57"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="51"/>
-      <c r="S27" s="51"/>
-      <c r="T27" s="51"/>
-      <c r="U27" s="51"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="58"/>
-      <c r="X27" s="51"/>
-      <c r="Y27" s="51"/>
-      <c r="Z27" s="56"/>
-      <c r="AA27" s="57"/>
-      <c r="AB27" s="51"/>
-      <c r="AC27" s="51"/>
-      <c r="AD27" s="55"/>
-      <c r="AE27" s="56"/>
-      <c r="AF27" s="57"/>
-      <c r="AG27" s="51"/>
-      <c r="AH27" s="51"/>
-      <c r="AI27" s="51"/>
-      <c r="AJ27" s="51"/>
-      <c r="AK27" s="51"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="57"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="59"/>
+      <c r="P27" s="53"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="53"/>
+      <c r="S27" s="53"/>
+      <c r="T27" s="53"/>
+      <c r="U27" s="53"/>
+      <c r="V27" s="58"/>
+      <c r="W27" s="60"/>
+      <c r="X27" s="53"/>
+      <c r="Y27" s="53"/>
+      <c r="Z27" s="58"/>
+      <c r="AA27" s="59"/>
+      <c r="AB27" s="53"/>
+      <c r="AC27" s="53"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="58"/>
+      <c r="AF27" s="59"/>
+      <c r="AG27" s="53"/>
+      <c r="AH27" s="53"/>
+      <c r="AI27" s="53"/>
+      <c r="AJ27" s="53"/>
+      <c r="AK27" s="53"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="49"/>
-      <c r="C28" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="55"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="57"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="51"/>
-      <c r="R28" s="51"/>
-      <c r="S28" s="51"/>
-      <c r="T28" s="51"/>
-      <c r="U28" s="51"/>
-      <c r="V28" s="56"/>
-      <c r="W28" s="58"/>
-      <c r="X28" s="51"/>
-      <c r="Y28" s="51"/>
-      <c r="Z28" s="56"/>
-      <c r="AA28" s="57"/>
-      <c r="AB28" s="51"/>
-      <c r="AC28" s="51"/>
-      <c r="AD28" s="55"/>
-      <c r="AE28" s="56"/>
-      <c r="AF28" s="57"/>
-      <c r="AG28" s="51"/>
-      <c r="AH28" s="51"/>
-      <c r="AI28" s="51"/>
-      <c r="AJ28" s="51"/>
-      <c r="AK28" s="51"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="57"/>
+      <c r="M28" s="53"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="59"/>
+      <c r="P28" s="53"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="53"/>
+      <c r="S28" s="53"/>
+      <c r="T28" s="53"/>
+      <c r="U28" s="53"/>
+      <c r="V28" s="58"/>
+      <c r="W28" s="60"/>
+      <c r="X28" s="53"/>
+      <c r="Y28" s="53"/>
+      <c r="Z28" s="58"/>
+      <c r="AA28" s="59"/>
+      <c r="AB28" s="53"/>
+      <c r="AC28" s="53"/>
+      <c r="AD28" s="57"/>
+      <c r="AE28" s="58"/>
+      <c r="AF28" s="59"/>
+      <c r="AG28" s="53"/>
+      <c r="AH28" s="53"/>
+      <c r="AI28" s="53"/>
+      <c r="AJ28" s="53"/>
+      <c r="AK28" s="53"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="49"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="56"/>
-      <c r="O29" s="57"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="51"/>
-      <c r="S29" s="51"/>
-      <c r="T29" s="51"/>
-      <c r="U29" s="51"/>
-      <c r="V29" s="56"/>
-      <c r="W29" s="58"/>
-      <c r="X29" s="51"/>
-      <c r="Y29" s="51"/>
-      <c r="Z29" s="56"/>
-      <c r="AA29" s="57"/>
-      <c r="AB29" s="51"/>
-      <c r="AC29" s="51"/>
-      <c r="AD29" s="55"/>
-      <c r="AE29" s="56"/>
-      <c r="AF29" s="57"/>
-      <c r="AG29" s="51"/>
-      <c r="AH29" s="51"/>
-      <c r="AI29" s="51"/>
-      <c r="AJ29" s="51"/>
-      <c r="AK29" s="51"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="58"/>
+      <c r="O29" s="59"/>
+      <c r="P29" s="53"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="53"/>
+      <c r="S29" s="53"/>
+      <c r="T29" s="53"/>
+      <c r="U29" s="53"/>
+      <c r="V29" s="58"/>
+      <c r="W29" s="60"/>
+      <c r="X29" s="53"/>
+      <c r="Y29" s="53"/>
+      <c r="Z29" s="58"/>
+      <c r="AA29" s="59"/>
+      <c r="AB29" s="53"/>
+      <c r="AC29" s="53"/>
+      <c r="AD29" s="57"/>
+      <c r="AE29" s="58"/>
+      <c r="AF29" s="59"/>
+      <c r="AG29" s="53"/>
+      <c r="AH29" s="53"/>
+      <c r="AI29" s="53"/>
+      <c r="AJ29" s="53"/>
+      <c r="AK29" s="53"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="49"/>
-      <c r="C30" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="57"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="51"/>
-      <c r="S30" s="51"/>
-      <c r="T30" s="51"/>
-      <c r="U30" s="51"/>
-      <c r="V30" s="56"/>
-      <c r="W30" s="58"/>
-      <c r="X30" s="51"/>
-      <c r="Y30" s="51"/>
-      <c r="Z30" s="56"/>
-      <c r="AA30" s="57"/>
-      <c r="AB30" s="51"/>
-      <c r="AC30" s="51"/>
-      <c r="AD30" s="55"/>
-      <c r="AE30" s="56"/>
-      <c r="AF30" s="57"/>
-      <c r="AG30" s="51"/>
-      <c r="AH30" s="51"/>
-      <c r="AI30" s="51"/>
-      <c r="AJ30" s="51"/>
-      <c r="AK30" s="51"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="67"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="67"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="59"/>
+      <c r="P30" s="53"/>
+      <c r="Q30" s="53"/>
+      <c r="R30" s="53"/>
+      <c r="S30" s="53"/>
+      <c r="T30" s="53"/>
+      <c r="U30" s="53"/>
+      <c r="V30" s="58"/>
+      <c r="W30" s="60"/>
+      <c r="X30" s="53"/>
+      <c r="Y30" s="53"/>
+      <c r="Z30" s="58"/>
+      <c r="AA30" s="59"/>
+      <c r="AB30" s="53"/>
+      <c r="AC30" s="53"/>
+      <c r="AD30" s="57"/>
+      <c r="AE30" s="58"/>
+      <c r="AF30" s="59"/>
+      <c r="AG30" s="53"/>
+      <c r="AH30" s="53"/>
+      <c r="AI30" s="53"/>
+      <c r="AJ30" s="53"/>
+      <c r="AK30" s="53"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="49"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="66"/>
-      <c r="K31" s="66"/>
-      <c r="L31" s="76"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="62"/>
-      <c r="O31" s="57"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-      <c r="R31" s="51"/>
-      <c r="S31" s="51"/>
-      <c r="T31" s="51"/>
-      <c r="U31" s="51"/>
-      <c r="V31" s="56"/>
-      <c r="W31" s="58"/>
-      <c r="X31" s="51"/>
-      <c r="Y31" s="51"/>
-      <c r="Z31" s="56"/>
-      <c r="AA31" s="57"/>
-      <c r="AB31" s="51"/>
-      <c r="AC31" s="51"/>
-      <c r="AD31" s="55"/>
-      <c r="AE31" s="56"/>
-      <c r="AF31" s="57"/>
-      <c r="AG31" s="51"/>
-      <c r="AH31" s="51"/>
-      <c r="AI31" s="51"/>
-      <c r="AJ31" s="51"/>
-      <c r="AK31" s="51"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="63"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="68"/>
+      <c r="L31" s="78"/>
+      <c r="M31" s="53"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="59"/>
+      <c r="P31" s="53"/>
+      <c r="Q31" s="53"/>
+      <c r="R31" s="53"/>
+      <c r="S31" s="53"/>
+      <c r="T31" s="53"/>
+      <c r="U31" s="53"/>
+      <c r="V31" s="58"/>
+      <c r="W31" s="60"/>
+      <c r="X31" s="53"/>
+      <c r="Y31" s="53"/>
+      <c r="Z31" s="58"/>
+      <c r="AA31" s="59"/>
+      <c r="AB31" s="53"/>
+      <c r="AC31" s="53"/>
+      <c r="AD31" s="57"/>
+      <c r="AE31" s="58"/>
+      <c r="AF31" s="59"/>
+      <c r="AG31" s="53"/>
+      <c r="AH31" s="53"/>
+      <c r="AI31" s="53"/>
+      <c r="AJ31" s="53"/>
+      <c r="AK31" s="53"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="49"/>
-      <c r="C32" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="51"/>
-      <c r="K32" s="51"/>
-      <c r="L32" s="55"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="53"/>
-      <c r="O32" s="57"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="51"/>
-      <c r="R32" s="51"/>
-      <c r="S32" s="51"/>
-      <c r="T32" s="51"/>
-      <c r="U32" s="51"/>
-      <c r="V32" s="56"/>
-      <c r="W32" s="58"/>
-      <c r="X32" s="51"/>
-      <c r="Y32" s="51"/>
-      <c r="Z32" s="56"/>
-      <c r="AA32" s="57"/>
-      <c r="AB32" s="51"/>
-      <c r="AC32" s="51"/>
-      <c r="AD32" s="55"/>
-      <c r="AE32" s="56"/>
-      <c r="AF32" s="57"/>
-      <c r="AG32" s="51"/>
-      <c r="AH32" s="51"/>
-      <c r="AI32" s="51"/>
-      <c r="AJ32" s="51"/>
-      <c r="AK32" s="51"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="57"/>
+      <c r="M32" s="67"/>
+      <c r="N32" s="55"/>
+      <c r="O32" s="59"/>
+      <c r="P32" s="53"/>
+      <c r="Q32" s="53"/>
+      <c r="R32" s="53"/>
+      <c r="S32" s="53"/>
+      <c r="T32" s="53"/>
+      <c r="U32" s="53"/>
+      <c r="V32" s="58"/>
+      <c r="W32" s="60"/>
+      <c r="X32" s="53"/>
+      <c r="Y32" s="53"/>
+      <c r="Z32" s="58"/>
+      <c r="AA32" s="59"/>
+      <c r="AB32" s="53"/>
+      <c r="AC32" s="53"/>
+      <c r="AD32" s="57"/>
+      <c r="AE32" s="58"/>
+      <c r="AF32" s="59"/>
+      <c r="AG32" s="53"/>
+      <c r="AH32" s="53"/>
+      <c r="AI32" s="53"/>
+      <c r="AJ32" s="53"/>
+      <c r="AK32" s="53"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="49"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="51"/>
-      <c r="N33" s="62"/>
-      <c r="O33" s="57"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="51"/>
-      <c r="R33" s="51"/>
-      <c r="S33" s="51"/>
-      <c r="T33" s="51"/>
-      <c r="U33" s="51"/>
-      <c r="V33" s="56"/>
-      <c r="W33" s="58"/>
-      <c r="X33" s="51"/>
-      <c r="Y33" s="51"/>
-      <c r="Z33" s="56"/>
-      <c r="AA33" s="57"/>
-      <c r="AB33" s="51"/>
-      <c r="AC33" s="51"/>
-      <c r="AD33" s="55"/>
-      <c r="AE33" s="56"/>
-      <c r="AF33" s="57"/>
-      <c r="AG33" s="51"/>
-      <c r="AH33" s="51"/>
-      <c r="AI33" s="51"/>
-      <c r="AJ33" s="51"/>
-      <c r="AK33" s="51"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="57"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="64"/>
+      <c r="O33" s="59"/>
+      <c r="P33" s="53"/>
+      <c r="Q33" s="53"/>
+      <c r="R33" s="53"/>
+      <c r="S33" s="53"/>
+      <c r="T33" s="53"/>
+      <c r="U33" s="53"/>
+      <c r="V33" s="58"/>
+      <c r="W33" s="60"/>
+      <c r="X33" s="53"/>
+      <c r="Y33" s="53"/>
+      <c r="Z33" s="58"/>
+      <c r="AA33" s="59"/>
+      <c r="AB33" s="53"/>
+      <c r="AC33" s="53"/>
+      <c r="AD33" s="57"/>
+      <c r="AE33" s="58"/>
+      <c r="AF33" s="59"/>
+      <c r="AG33" s="53"/>
+      <c r="AH33" s="53"/>
+      <c r="AI33" s="53"/>
+      <c r="AJ33" s="53"/>
+      <c r="AK33" s="53"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="68" t="s">
-        <v>157</v>
-      </c>
-      <c r="C34" s="77" t="s">
-        <v>158</v>
-      </c>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="55"/>
-      <c r="M34" s="65"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="54"/>
-      <c r="P34" s="65"/>
-      <c r="Q34" s="65"/>
-      <c r="R34" s="65"/>
-      <c r="S34" s="71"/>
-      <c r="T34" s="71"/>
-      <c r="U34" s="71"/>
-      <c r="V34" s="72"/>
-      <c r="W34" s="58"/>
-      <c r="X34" s="71"/>
-      <c r="Y34" s="71"/>
-      <c r="Z34" s="72"/>
-      <c r="AA34" s="70"/>
-      <c r="AB34" s="71"/>
-      <c r="AC34" s="71"/>
-      <c r="AD34" s="55"/>
-      <c r="AE34" s="72"/>
-      <c r="AF34" s="70"/>
-      <c r="AG34" s="71"/>
-      <c r="AH34" s="71"/>
-      <c r="AI34" s="71"/>
-      <c r="AJ34" s="71"/>
-      <c r="AK34" s="71"/>
+      <c r="B34" s="70" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="73"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="57"/>
+      <c r="M34" s="67"/>
+      <c r="N34" s="55"/>
+      <c r="O34" s="56"/>
+      <c r="P34" s="67"/>
+      <c r="Q34" s="67"/>
+      <c r="R34" s="67"/>
+      <c r="S34" s="73"/>
+      <c r="T34" s="73"/>
+      <c r="U34" s="73"/>
+      <c r="V34" s="74"/>
+      <c r="W34" s="60"/>
+      <c r="X34" s="73"/>
+      <c r="Y34" s="73"/>
+      <c r="Z34" s="74"/>
+      <c r="AA34" s="72"/>
+      <c r="AB34" s="73"/>
+      <c r="AC34" s="73"/>
+      <c r="AD34" s="57"/>
+      <c r="AE34" s="74"/>
+      <c r="AF34" s="72"/>
+      <c r="AG34" s="73"/>
+      <c r="AH34" s="73"/>
+      <c r="AI34" s="73"/>
+      <c r="AJ34" s="73"/>
+      <c r="AK34" s="73"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="68"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="78"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="62"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="64"/>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="79"/>
-      <c r="S35" s="79"/>
-      <c r="T35" s="60"/>
-      <c r="U35" s="71"/>
-      <c r="V35" s="72"/>
-      <c r="W35" s="58"/>
-      <c r="X35" s="71"/>
-      <c r="Y35" s="71"/>
-      <c r="Z35" s="72"/>
-      <c r="AA35" s="70"/>
-      <c r="AB35" s="71"/>
-      <c r="AC35" s="71"/>
-      <c r="AD35" s="55"/>
-      <c r="AE35" s="72"/>
-      <c r="AF35" s="70"/>
-      <c r="AG35" s="71"/>
-      <c r="AH35" s="71"/>
-      <c r="AI35" s="71"/>
-      <c r="AJ35" s="71"/>
-      <c r="AK35" s="71"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="72"/>
+      <c r="I35" s="73"/>
+      <c r="J35" s="73"/>
+      <c r="K35" s="80"/>
+      <c r="L35" s="57"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="72"/>
+      <c r="P35" s="66"/>
+      <c r="Q35" s="73"/>
+      <c r="R35" s="81"/>
+      <c r="S35" s="81"/>
+      <c r="T35" s="62"/>
+      <c r="U35" s="73"/>
+      <c r="V35" s="74"/>
+      <c r="W35" s="60"/>
+      <c r="X35" s="73"/>
+      <c r="Y35" s="73"/>
+      <c r="Z35" s="74"/>
+      <c r="AA35" s="72"/>
+      <c r="AB35" s="73"/>
+      <c r="AC35" s="73"/>
+      <c r="AD35" s="57"/>
+      <c r="AE35" s="74"/>
+      <c r="AF35" s="72"/>
+      <c r="AG35" s="73"/>
+      <c r="AH35" s="73"/>
+      <c r="AI35" s="73"/>
+      <c r="AJ35" s="73"/>
+      <c r="AK35" s="73"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="68"/>
-      <c r="C36" s="77" t="s">
-        <v>159</v>
-      </c>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="53"/>
-      <c r="O36" s="54"/>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="71"/>
-      <c r="R36" s="71"/>
-      <c r="S36" s="71"/>
-      <c r="T36" s="71"/>
-      <c r="U36" s="71"/>
-      <c r="V36" s="72"/>
-      <c r="W36" s="58"/>
-      <c r="X36" s="71"/>
-      <c r="Y36" s="71"/>
-      <c r="Z36" s="72"/>
-      <c r="AA36" s="70"/>
-      <c r="AB36" s="71"/>
-      <c r="AC36" s="71"/>
-      <c r="AD36" s="55"/>
-      <c r="AE36" s="72"/>
-      <c r="AF36" s="70"/>
-      <c r="AG36" s="71"/>
-      <c r="AH36" s="71"/>
-      <c r="AI36" s="71"/>
-      <c r="AJ36" s="71"/>
-      <c r="AK36" s="71"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="79" t="s">
+        <v>161</v>
+      </c>
+      <c r="D36" s="73"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="73"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="67"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="56"/>
+      <c r="P36" s="67"/>
+      <c r="Q36" s="73"/>
+      <c r="R36" s="73"/>
+      <c r="S36" s="73"/>
+      <c r="T36" s="73"/>
+      <c r="U36" s="73"/>
+      <c r="V36" s="74"/>
+      <c r="W36" s="60"/>
+      <c r="X36" s="73"/>
+      <c r="Y36" s="73"/>
+      <c r="Z36" s="74"/>
+      <c r="AA36" s="72"/>
+      <c r="AB36" s="73"/>
+      <c r="AC36" s="73"/>
+      <c r="AD36" s="57"/>
+      <c r="AE36" s="74"/>
+      <c r="AF36" s="72"/>
+      <c r="AG36" s="73"/>
+      <c r="AH36" s="73"/>
+      <c r="AI36" s="73"/>
+      <c r="AJ36" s="73"/>
+      <c r="AK36" s="73"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="68"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="71"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="71"/>
-      <c r="N37" s="72"/>
-      <c r="O37" s="70"/>
-      <c r="P37" s="64"/>
-      <c r="Q37" s="71"/>
-      <c r="R37" s="79"/>
-      <c r="S37" s="79"/>
-      <c r="T37" s="60"/>
-      <c r="U37" s="71"/>
-      <c r="V37" s="72"/>
-      <c r="W37" s="58"/>
-      <c r="X37" s="71"/>
-      <c r="Y37" s="71"/>
-      <c r="Z37" s="72"/>
-      <c r="AA37" s="70"/>
-      <c r="AB37" s="71"/>
-      <c r="AC37" s="71"/>
-      <c r="AD37" s="55"/>
-      <c r="AE37" s="72"/>
-      <c r="AF37" s="70"/>
-      <c r="AG37" s="71"/>
-      <c r="AH37" s="71"/>
-      <c r="AI37" s="71"/>
-      <c r="AJ37" s="71"/>
-      <c r="AK37" s="71"/>
+      <c r="B37" s="70"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="72"/>
+      <c r="I37" s="73"/>
+      <c r="J37" s="73"/>
+      <c r="K37" s="80"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="73"/>
+      <c r="N37" s="74"/>
+      <c r="O37" s="72"/>
+      <c r="P37" s="66"/>
+      <c r="Q37" s="73"/>
+      <c r="R37" s="81"/>
+      <c r="S37" s="81"/>
+      <c r="T37" s="62"/>
+      <c r="U37" s="73"/>
+      <c r="V37" s="74"/>
+      <c r="W37" s="60"/>
+      <c r="X37" s="73"/>
+      <c r="Y37" s="73"/>
+      <c r="Z37" s="74"/>
+      <c r="AA37" s="72"/>
+      <c r="AB37" s="73"/>
+      <c r="AC37" s="73"/>
+      <c r="AD37" s="57"/>
+      <c r="AE37" s="74"/>
+      <c r="AF37" s="72"/>
+      <c r="AG37" s="73"/>
+      <c r="AH37" s="73"/>
+      <c r="AI37" s="73"/>
+      <c r="AJ37" s="73"/>
+      <c r="AK37" s="73"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="68"/>
-      <c r="C38" s="77" t="s">
-        <v>160</v>
-      </c>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="71"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="71"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="54"/>
-      <c r="P38" s="65"/>
-      <c r="Q38" s="65"/>
-      <c r="R38" s="65"/>
-      <c r="S38" s="65"/>
-      <c r="T38" s="65"/>
-      <c r="U38" s="65"/>
-      <c r="V38" s="53"/>
-      <c r="W38" s="58"/>
-      <c r="X38" s="65"/>
-      <c r="Y38" s="65"/>
-      <c r="Z38" s="72"/>
-      <c r="AA38" s="70"/>
-      <c r="AB38" s="71"/>
-      <c r="AC38" s="71"/>
-      <c r="AD38" s="55"/>
-      <c r="AE38" s="72"/>
-      <c r="AF38" s="70"/>
-      <c r="AG38" s="71"/>
-      <c r="AH38" s="71"/>
-      <c r="AI38" s="71"/>
-      <c r="AJ38" s="71"/>
-      <c r="AK38" s="71"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="74"/>
+      <c r="H38" s="72"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="73"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="74"/>
+      <c r="O38" s="56"/>
+      <c r="P38" s="67"/>
+      <c r="Q38" s="67"/>
+      <c r="R38" s="67"/>
+      <c r="S38" s="67"/>
+      <c r="T38" s="67"/>
+      <c r="U38" s="67"/>
+      <c r="V38" s="55"/>
+      <c r="W38" s="60"/>
+      <c r="X38" s="67"/>
+      <c r="Y38" s="67"/>
+      <c r="Z38" s="74"/>
+      <c r="AA38" s="72"/>
+      <c r="AB38" s="73"/>
+      <c r="AC38" s="73"/>
+      <c r="AD38" s="57"/>
+      <c r="AE38" s="74"/>
+      <c r="AF38" s="72"/>
+      <c r="AG38" s="73"/>
+      <c r="AH38" s="73"/>
+      <c r="AI38" s="73"/>
+      <c r="AJ38" s="73"/>
+      <c r="AK38" s="73"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="68"/>
-      <c r="C39" s="77"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="72"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="71"/>
-      <c r="N39" s="72"/>
-      <c r="O39" s="70"/>
-      <c r="P39" s="71"/>
-      <c r="Q39" s="71"/>
-      <c r="R39" s="78"/>
-      <c r="S39" s="78"/>
-      <c r="T39" s="71"/>
-      <c r="U39" s="71"/>
-      <c r="V39" s="72"/>
-      <c r="W39" s="58"/>
-      <c r="X39" s="71"/>
-      <c r="Y39" s="71"/>
-      <c r="Z39" s="72"/>
-      <c r="AA39" s="70"/>
-      <c r="AB39" s="71"/>
-      <c r="AC39" s="71"/>
-      <c r="AD39" s="55"/>
-      <c r="AE39" s="72"/>
-      <c r="AF39" s="70"/>
-      <c r="AG39" s="71"/>
-      <c r="AH39" s="71"/>
-      <c r="AI39" s="71"/>
-      <c r="AJ39" s="71"/>
-      <c r="AK39" s="71"/>
+      <c r="B39" s="70"/>
+      <c r="C39" s="79"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="74"/>
+      <c r="H39" s="72"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="73"/>
+      <c r="K39" s="73"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="74"/>
+      <c r="O39" s="72"/>
+      <c r="P39" s="73"/>
+      <c r="Q39" s="73"/>
+      <c r="R39" s="80"/>
+      <c r="S39" s="80"/>
+      <c r="T39" s="73"/>
+      <c r="U39" s="73"/>
+      <c r="V39" s="74"/>
+      <c r="W39" s="60"/>
+      <c r="X39" s="73"/>
+      <c r="Y39" s="73"/>
+      <c r="Z39" s="74"/>
+      <c r="AA39" s="72"/>
+      <c r="AB39" s="73"/>
+      <c r="AC39" s="73"/>
+      <c r="AD39" s="57"/>
+      <c r="AE39" s="74"/>
+      <c r="AF39" s="72"/>
+      <c r="AG39" s="73"/>
+      <c r="AH39" s="73"/>
+      <c r="AI39" s="73"/>
+      <c r="AJ39" s="73"/>
+      <c r="AK39" s="73"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="68"/>
-      <c r="C40" s="77" t="s">
-        <v>161</v>
-      </c>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="71"/>
-      <c r="K40" s="71"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="71"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="70"/>
-      <c r="P40" s="71"/>
-      <c r="Q40" s="71"/>
-      <c r="R40" s="65"/>
-      <c r="S40" s="65"/>
-      <c r="T40" s="65"/>
-      <c r="U40" s="65"/>
-      <c r="V40" s="53"/>
-      <c r="W40" s="58"/>
-      <c r="X40" s="65"/>
-      <c r="Y40" s="65"/>
-      <c r="Z40" s="53"/>
-      <c r="AA40" s="54"/>
-      <c r="AB40" s="65"/>
-      <c r="AC40" s="65"/>
-      <c r="AD40" s="55"/>
-      <c r="AE40" s="72"/>
-      <c r="AF40" s="70"/>
-      <c r="AG40" s="71"/>
-      <c r="AH40" s="71"/>
-      <c r="AI40" s="71"/>
-      <c r="AJ40" s="71"/>
-      <c r="AK40" s="71"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="D40" s="73"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="74"/>
+      <c r="H40" s="72"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="73"/>
+      <c r="K40" s="73"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="73"/>
+      <c r="N40" s="74"/>
+      <c r="O40" s="72"/>
+      <c r="P40" s="73"/>
+      <c r="Q40" s="73"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="67"/>
+      <c r="T40" s="67"/>
+      <c r="U40" s="67"/>
+      <c r="V40" s="55"/>
+      <c r="W40" s="60"/>
+      <c r="X40" s="67"/>
+      <c r="Y40" s="67"/>
+      <c r="Z40" s="55"/>
+      <c r="AA40" s="56"/>
+      <c r="AB40" s="67"/>
+      <c r="AC40" s="67"/>
+      <c r="AD40" s="57"/>
+      <c r="AE40" s="74"/>
+      <c r="AF40" s="72"/>
+      <c r="AG40" s="73"/>
+      <c r="AH40" s="73"/>
+      <c r="AI40" s="73"/>
+      <c r="AJ40" s="73"/>
+      <c r="AK40" s="73"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="68"/>
-      <c r="C41" s="77"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="72"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="71"/>
-      <c r="K41" s="71"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="72"/>
-      <c r="O41" s="70"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="64"/>
-      <c r="R41" s="78"/>
-      <c r="S41" s="78"/>
-      <c r="T41" s="64"/>
-      <c r="U41" s="71"/>
-      <c r="V41" s="72"/>
-      <c r="W41" s="58"/>
-      <c r="X41" s="71"/>
-      <c r="Y41" s="71"/>
-      <c r="Z41" s="72"/>
-      <c r="AA41" s="70"/>
-      <c r="AB41" s="71"/>
-      <c r="AC41" s="71"/>
-      <c r="AD41" s="55"/>
-      <c r="AE41" s="72"/>
-      <c r="AF41" s="70"/>
-      <c r="AG41" s="71"/>
-      <c r="AH41" s="71"/>
-      <c r="AI41" s="71"/>
-      <c r="AJ41" s="71"/>
-      <c r="AK41" s="71"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="74"/>
+      <c r="H41" s="72"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="73"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="74"/>
+      <c r="O41" s="72"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="66"/>
+      <c r="R41" s="80"/>
+      <c r="S41" s="80"/>
+      <c r="T41" s="66"/>
+      <c r="U41" s="73"/>
+      <c r="V41" s="74"/>
+      <c r="W41" s="60"/>
+      <c r="X41" s="73"/>
+      <c r="Y41" s="73"/>
+      <c r="Z41" s="74"/>
+      <c r="AA41" s="72"/>
+      <c r="AB41" s="73"/>
+      <c r="AC41" s="73"/>
+      <c r="AD41" s="57"/>
+      <c r="AE41" s="74"/>
+      <c r="AF41" s="72"/>
+      <c r="AG41" s="73"/>
+      <c r="AH41" s="73"/>
+      <c r="AI41" s="73"/>
+      <c r="AJ41" s="73"/>
+      <c r="AK41" s="73"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="49" t="s">
+      <c r="B42" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="80" t="s">
-        <v>162</v>
-      </c>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="55"/>
-      <c r="M42" s="51"/>
-      <c r="N42" s="56"/>
-      <c r="O42" s="57"/>
-      <c r="P42" s="65"/>
-      <c r="Q42" s="65"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="51"/>
-      <c r="T42" s="64"/>
-      <c r="U42" s="51"/>
-      <c r="V42" s="53"/>
-      <c r="W42" s="58"/>
-      <c r="X42" s="65"/>
-      <c r="Y42" s="65"/>
-      <c r="Z42" s="53"/>
-      <c r="AA42" s="54"/>
-      <c r="AB42" s="65"/>
-      <c r="AC42" s="65"/>
-      <c r="AD42" s="55"/>
-      <c r="AE42" s="56"/>
-      <c r="AF42" s="57"/>
-      <c r="AG42" s="51"/>
-      <c r="AH42" s="51"/>
-      <c r="AI42" s="51"/>
-      <c r="AJ42" s="51"/>
-      <c r="AK42" s="51"/>
+      <c r="C42" s="82" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="53"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="61"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="53"/>
+      <c r="J42" s="53"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="53"/>
+      <c r="N42" s="58"/>
+      <c r="O42" s="59"/>
+      <c r="P42" s="67"/>
+      <c r="Q42" s="67"/>
+      <c r="R42" s="53"/>
+      <c r="S42" s="53"/>
+      <c r="T42" s="66"/>
+      <c r="U42" s="53"/>
+      <c r="V42" s="55"/>
+      <c r="W42" s="60"/>
+      <c r="X42" s="67"/>
+      <c r="Y42" s="67"/>
+      <c r="Z42" s="55"/>
+      <c r="AA42" s="56"/>
+      <c r="AB42" s="67"/>
+      <c r="AC42" s="67"/>
+      <c r="AD42" s="57"/>
+      <c r="AE42" s="58"/>
+      <c r="AF42" s="59"/>
+      <c r="AG42" s="53"/>
+      <c r="AH42" s="53"/>
+      <c r="AI42" s="53"/>
+      <c r="AJ42" s="53"/>
+      <c r="AK42" s="53"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="49"/>
-      <c r="C43" s="80"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="51"/>
-      <c r="K43" s="51"/>
-      <c r="L43" s="55"/>
-      <c r="M43" s="51"/>
-      <c r="N43" s="56"/>
-      <c r="O43" s="57"/>
-      <c r="P43" s="51"/>
-      <c r="Q43" s="64"/>
-      <c r="R43" s="51"/>
-      <c r="S43" s="66"/>
-      <c r="T43" s="51"/>
-      <c r="U43" s="51"/>
-      <c r="V43" s="56"/>
-      <c r="W43" s="58"/>
-      <c r="X43" s="51"/>
-      <c r="Y43" s="51"/>
-      <c r="Z43" s="56"/>
-      <c r="AA43" s="57"/>
-      <c r="AB43" s="51"/>
-      <c r="AC43" s="51"/>
-      <c r="AD43" s="55"/>
-      <c r="AE43" s="56"/>
-      <c r="AF43" s="57"/>
-      <c r="AG43" s="51"/>
-      <c r="AH43" s="51"/>
-      <c r="AI43" s="51"/>
-      <c r="AJ43" s="51"/>
-      <c r="AK43" s="51"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="82"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="61"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="53"/>
+      <c r="N43" s="58"/>
+      <c r="O43" s="59"/>
+      <c r="P43" s="53"/>
+      <c r="Q43" s="66"/>
+      <c r="R43" s="53"/>
+      <c r="S43" s="68"/>
+      <c r="T43" s="53"/>
+      <c r="U43" s="53"/>
+      <c r="V43" s="58"/>
+      <c r="W43" s="60"/>
+      <c r="X43" s="53"/>
+      <c r="Y43" s="53"/>
+      <c r="Z43" s="58"/>
+      <c r="AA43" s="59"/>
+      <c r="AB43" s="53"/>
+      <c r="AC43" s="53"/>
+      <c r="AD43" s="57"/>
+      <c r="AE43" s="58"/>
+      <c r="AF43" s="59"/>
+      <c r="AG43" s="53"/>
+      <c r="AH43" s="53"/>
+      <c r="AI43" s="53"/>
+      <c r="AJ43" s="53"/>
+      <c r="AK43" s="53"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="49"/>
-      <c r="C44" s="80" t="s">
-        <v>163</v>
-      </c>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="51"/>
-      <c r="J44" s="51"/>
-      <c r="K44" s="51"/>
-      <c r="L44" s="55"/>
-      <c r="M44" s="51"/>
-      <c r="N44" s="56"/>
-      <c r="O44" s="57"/>
-      <c r="P44" s="65"/>
-      <c r="Q44" s="65"/>
-      <c r="R44" s="51"/>
-      <c r="S44" s="51"/>
-      <c r="T44" s="51"/>
-      <c r="U44" s="51"/>
-      <c r="V44" s="56"/>
-      <c r="W44" s="58"/>
-      <c r="X44" s="65"/>
-      <c r="Y44" s="65"/>
-      <c r="Z44" s="56"/>
-      <c r="AA44" s="57"/>
-      <c r="AB44" s="51"/>
-      <c r="AC44" s="65"/>
-      <c r="AD44" s="55"/>
-      <c r="AE44" s="53"/>
-      <c r="AF44" s="54"/>
-      <c r="AG44" s="51"/>
-      <c r="AH44" s="51"/>
-      <c r="AI44" s="65"/>
-      <c r="AJ44" s="51"/>
-      <c r="AK44" s="51"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="82" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="61"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="53"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="53"/>
+      <c r="N44" s="58"/>
+      <c r="O44" s="59"/>
+      <c r="P44" s="67"/>
+      <c r="Q44" s="67"/>
+      <c r="R44" s="53"/>
+      <c r="S44" s="53"/>
+      <c r="T44" s="53"/>
+      <c r="U44" s="53"/>
+      <c r="V44" s="58"/>
+      <c r="W44" s="60"/>
+      <c r="X44" s="67"/>
+      <c r="Y44" s="67"/>
+      <c r="Z44" s="58"/>
+      <c r="AA44" s="59"/>
+      <c r="AB44" s="53"/>
+      <c r="AC44" s="67"/>
+      <c r="AD44" s="57"/>
+      <c r="AE44" s="55"/>
+      <c r="AF44" s="56"/>
+      <c r="AG44" s="53"/>
+      <c r="AH44" s="53"/>
+      <c r="AI44" s="67"/>
+      <c r="AJ44" s="53"/>
+      <c r="AK44" s="53"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="49"/>
-      <c r="C45" s="80"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="51"/>
-      <c r="J45" s="51"/>
-      <c r="K45" s="51"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="51"/>
-      <c r="N45" s="56"/>
-      <c r="O45" s="57"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="51"/>
-      <c r="R45" s="51"/>
-      <c r="S45" s="51"/>
-      <c r="T45" s="51"/>
-      <c r="U45" s="51"/>
-      <c r="V45" s="56"/>
-      <c r="W45" s="58"/>
-      <c r="X45" s="51"/>
-      <c r="Y45" s="64"/>
-      <c r="Z45" s="81"/>
-      <c r="AA45" s="57"/>
-      <c r="AB45" s="51"/>
-      <c r="AC45" s="51"/>
-      <c r="AD45" s="55"/>
-      <c r="AE45" s="56"/>
-      <c r="AF45" s="57"/>
-      <c r="AG45" s="51"/>
-      <c r="AH45" s="51"/>
-      <c r="AI45" s="51"/>
-      <c r="AJ45" s="51"/>
-      <c r="AK45" s="51"/>
+      <c r="B45" s="51"/>
+      <c r="C45" s="82"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="61"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="53"/>
+      <c r="N45" s="58"/>
+      <c r="O45" s="59"/>
+      <c r="P45" s="53"/>
+      <c r="Q45" s="53"/>
+      <c r="R45" s="53"/>
+      <c r="S45" s="53"/>
+      <c r="T45" s="53"/>
+      <c r="U45" s="53"/>
+      <c r="V45" s="58"/>
+      <c r="W45" s="60"/>
+      <c r="X45" s="53"/>
+      <c r="Y45" s="66"/>
+      <c r="Z45" s="83"/>
+      <c r="AA45" s="59"/>
+      <c r="AB45" s="53"/>
+      <c r="AC45" s="53"/>
+      <c r="AD45" s="57"/>
+      <c r="AE45" s="58"/>
+      <c r="AF45" s="59"/>
+      <c r="AG45" s="53"/>
+      <c r="AH45" s="53"/>
+      <c r="AI45" s="53"/>
+      <c r="AJ45" s="53"/>
+      <c r="AK45" s="53"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="C46" s="69" t="s">
+      <c r="B46" s="70" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="72"/>
-      <c r="H46" s="70"/>
-      <c r="I46" s="71"/>
-      <c r="J46" s="71"/>
-      <c r="K46" s="71"/>
-      <c r="L46" s="55"/>
-      <c r="M46" s="71"/>
-      <c r="N46" s="72"/>
-      <c r="O46" s="70"/>
-      <c r="P46" s="71"/>
-      <c r="Q46" s="71"/>
-      <c r="R46" s="71"/>
-      <c r="S46" s="71"/>
-      <c r="T46" s="71"/>
-      <c r="U46" s="71"/>
-      <c r="V46" s="72"/>
-      <c r="W46" s="58"/>
-      <c r="X46" s="71"/>
-      <c r="Y46" s="71"/>
-      <c r="Z46" s="72"/>
-      <c r="AA46" s="70"/>
-      <c r="AB46" s="71"/>
-      <c r="AC46" s="71"/>
-      <c r="AD46" s="55"/>
-      <c r="AE46" s="72"/>
-      <c r="AF46" s="70"/>
-      <c r="AG46" s="71"/>
-      <c r="AH46" s="71"/>
-      <c r="AI46" s="71"/>
-      <c r="AJ46" s="65"/>
-      <c r="AK46" s="71"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="74"/>
+      <c r="H46" s="72"/>
+      <c r="I46" s="73"/>
+      <c r="J46" s="73"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="57"/>
+      <c r="M46" s="73"/>
+      <c r="N46" s="74"/>
+      <c r="O46" s="72"/>
+      <c r="P46" s="73"/>
+      <c r="Q46" s="73"/>
+      <c r="R46" s="73"/>
+      <c r="S46" s="73"/>
+      <c r="T46" s="73"/>
+      <c r="U46" s="73"/>
+      <c r="V46" s="74"/>
+      <c r="W46" s="60"/>
+      <c r="X46" s="73"/>
+      <c r="Y46" s="73"/>
+      <c r="Z46" s="74"/>
+      <c r="AA46" s="72"/>
+      <c r="AB46" s="73"/>
+      <c r="AC46" s="73"/>
+      <c r="AD46" s="57"/>
+      <c r="AE46" s="74"/>
+      <c r="AF46" s="72"/>
+      <c r="AG46" s="73"/>
+      <c r="AH46" s="73"/>
+      <c r="AI46" s="73"/>
+      <c r="AJ46" s="67"/>
+      <c r="AK46" s="73"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="68"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="71"/>
-      <c r="E47" s="71"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="72"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="71"/>
-      <c r="J47" s="71"/>
-      <c r="K47" s="71"/>
-      <c r="L47" s="55"/>
-      <c r="M47" s="71"/>
-      <c r="N47" s="72"/>
-      <c r="O47" s="70"/>
-      <c r="P47" s="71"/>
-      <c r="Q47" s="71"/>
-      <c r="R47" s="71"/>
-      <c r="S47" s="71"/>
-      <c r="T47" s="71"/>
-      <c r="U47" s="71"/>
-      <c r="V47" s="72"/>
-      <c r="W47" s="58"/>
-      <c r="X47" s="71"/>
-      <c r="Y47" s="71"/>
-      <c r="Z47" s="72"/>
-      <c r="AA47" s="70"/>
-      <c r="AB47" s="71"/>
-      <c r="AC47" s="71"/>
-      <c r="AD47" s="55"/>
-      <c r="AE47" s="72"/>
-      <c r="AF47" s="70"/>
-      <c r="AG47" s="71"/>
-      <c r="AH47" s="71"/>
-      <c r="AI47" s="71"/>
-      <c r="AJ47" s="71"/>
-      <c r="AK47" s="71"/>
-      <c r="AN47" s="82" t="s">
-        <v>165</v>
-      </c>
-      <c r="AO47" s="65"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="74"/>
+      <c r="H47" s="72"/>
+      <c r="I47" s="73"/>
+      <c r="J47" s="73"/>
+      <c r="K47" s="73"/>
+      <c r="L47" s="57"/>
+      <c r="M47" s="73"/>
+      <c r="N47" s="74"/>
+      <c r="O47" s="72"/>
+      <c r="P47" s="73"/>
+      <c r="Q47" s="73"/>
+      <c r="R47" s="73"/>
+      <c r="S47" s="73"/>
+      <c r="T47" s="73"/>
+      <c r="U47" s="73"/>
+      <c r="V47" s="74"/>
+      <c r="W47" s="60"/>
+      <c r="X47" s="73"/>
+      <c r="Y47" s="73"/>
+      <c r="Z47" s="74"/>
+      <c r="AA47" s="72"/>
+      <c r="AB47" s="73"/>
+      <c r="AC47" s="73"/>
+      <c r="AD47" s="57"/>
+      <c r="AE47" s="74"/>
+      <c r="AF47" s="72"/>
+      <c r="AG47" s="73"/>
+      <c r="AH47" s="73"/>
+      <c r="AI47" s="73"/>
+      <c r="AJ47" s="73"/>
+      <c r="AK47" s="73"/>
+      <c r="AN47" s="84" t="s">
+        <v>167</v>
+      </c>
+      <c r="AO47" s="67"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="68"/>
-      <c r="C48" s="69" t="s">
-        <v>166</v>
-      </c>
-      <c r="D48" s="71"/>
-      <c r="E48" s="71"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="72"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="71"/>
-      <c r="J48" s="71"/>
-      <c r="K48" s="71"/>
-      <c r="L48" s="55"/>
-      <c r="M48" s="71"/>
-      <c r="N48" s="72"/>
-      <c r="O48" s="70"/>
-      <c r="P48" s="71"/>
-      <c r="Q48" s="71"/>
-      <c r="R48" s="71"/>
-      <c r="S48" s="71"/>
-      <c r="T48" s="71"/>
-      <c r="U48" s="71"/>
-      <c r="V48" s="72"/>
-      <c r="W48" s="58"/>
-      <c r="X48" s="71"/>
-      <c r="Y48" s="71"/>
-      <c r="Z48" s="72"/>
-      <c r="AA48" s="70"/>
-      <c r="AB48" s="71"/>
-      <c r="AC48" s="71"/>
-      <c r="AD48" s="55"/>
-      <c r="AE48" s="72"/>
-      <c r="AF48" s="70"/>
-      <c r="AG48" s="71"/>
-      <c r="AH48" s="71"/>
-      <c r="AI48" s="71"/>
-      <c r="AJ48" s="71"/>
-      <c r="AK48" s="83"/>
-      <c r="AN48" s="82" t="s">
-        <v>167</v>
-      </c>
-      <c r="AO48" s="64"/>
+      <c r="B48" s="70"/>
+      <c r="C48" s="71" t="s">
+        <v>168</v>
+      </c>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="72"/>
+      <c r="I48" s="73"/>
+      <c r="J48" s="73"/>
+      <c r="K48" s="73"/>
+      <c r="L48" s="57"/>
+      <c r="M48" s="73"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="72"/>
+      <c r="P48" s="73"/>
+      <c r="Q48" s="73"/>
+      <c r="R48" s="73"/>
+      <c r="S48" s="73"/>
+      <c r="T48" s="73"/>
+      <c r="U48" s="73"/>
+      <c r="V48" s="74"/>
+      <c r="W48" s="60"/>
+      <c r="X48" s="73"/>
+      <c r="Y48" s="73"/>
+      <c r="Z48" s="74"/>
+      <c r="AA48" s="72"/>
+      <c r="AB48" s="73"/>
+      <c r="AC48" s="73"/>
+      <c r="AD48" s="57"/>
+      <c r="AE48" s="74"/>
+      <c r="AF48" s="72"/>
+      <c r="AG48" s="73"/>
+      <c r="AH48" s="73"/>
+      <c r="AI48" s="73"/>
+      <c r="AJ48" s="73"/>
+      <c r="AK48" s="85"/>
+      <c r="AN48" s="84" t="s">
+        <v>169</v>
+      </c>
+      <c r="AO48" s="66"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="68"/>
-      <c r="C49" s="69"/>
-      <c r="D49" s="71"/>
-      <c r="E49" s="71"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="72"/>
-      <c r="H49" s="70"/>
-      <c r="I49" s="71"/>
-      <c r="J49" s="71"/>
-      <c r="K49" s="71"/>
-      <c r="L49" s="55"/>
-      <c r="M49" s="71"/>
-      <c r="N49" s="72"/>
-      <c r="O49" s="70"/>
-      <c r="P49" s="71"/>
-      <c r="Q49" s="71"/>
-      <c r="R49" s="71"/>
-      <c r="S49" s="71"/>
-      <c r="T49" s="71"/>
-      <c r="U49" s="71"/>
-      <c r="V49" s="72"/>
-      <c r="W49" s="58"/>
-      <c r="X49" s="71"/>
-      <c r="Y49" s="71"/>
-      <c r="Z49" s="72"/>
-      <c r="AA49" s="70"/>
-      <c r="AB49" s="71"/>
-      <c r="AC49" s="71"/>
-      <c r="AD49" s="55"/>
-      <c r="AE49" s="72"/>
-      <c r="AF49" s="70"/>
-      <c r="AG49" s="71"/>
-      <c r="AH49" s="71"/>
-      <c r="AI49" s="71"/>
-      <c r="AJ49" s="71"/>
-      <c r="AK49" s="71"/>
-      <c r="AN49" s="82" t="s">
-        <v>168</v>
-      </c>
-      <c r="AO49" s="60"/>
+      <c r="B49" s="70"/>
+      <c r="C49" s="71"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="72"/>
+      <c r="I49" s="73"/>
+      <c r="J49" s="73"/>
+      <c r="K49" s="73"/>
+      <c r="L49" s="57"/>
+      <c r="M49" s="73"/>
+      <c r="N49" s="74"/>
+      <c r="O49" s="72"/>
+      <c r="P49" s="73"/>
+      <c r="Q49" s="73"/>
+      <c r="R49" s="73"/>
+      <c r="S49" s="73"/>
+      <c r="T49" s="73"/>
+      <c r="U49" s="73"/>
+      <c r="V49" s="74"/>
+      <c r="W49" s="60"/>
+      <c r="X49" s="73"/>
+      <c r="Y49" s="73"/>
+      <c r="Z49" s="74"/>
+      <c r="AA49" s="72"/>
+      <c r="AB49" s="73"/>
+      <c r="AC49" s="73"/>
+      <c r="AD49" s="57"/>
+      <c r="AE49" s="74"/>
+      <c r="AF49" s="72"/>
+      <c r="AG49" s="73"/>
+      <c r="AH49" s="73"/>
+      <c r="AI49" s="73"/>
+      <c r="AJ49" s="73"/>
+      <c r="AK49" s="73"/>
+      <c r="AN49" s="84" t="s">
+        <v>170</v>
+      </c>
+      <c r="AO49" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -11057,801 +11085,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="84"/>
+      <c r="B1" s="86"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="85" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="86" t="s">
-        <v>114</v>
-      </c>
-      <c r="D2" s="87" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2" s="88" t="s">
-        <v>170</v>
-      </c>
-      <c r="F2" s="89" t="s">
+      <c r="B2" s="87" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="88" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="89" t="s">
         <v>171</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="89" t="s">
+      <c r="E2" s="90" t="s">
         <v>172</v>
       </c>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89" t="s">
-        <v>107</v>
-      </c>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="89" t="s">
-        <v>108</v>
-      </c>
-      <c r="S2" s="90"/>
-      <c r="AD2" s="91"/>
+      <c r="F2" s="91" t="s">
+        <v>173</v>
+      </c>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="91" t="s">
+        <v>174</v>
+      </c>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="90"/>
+      <c r="N2" s="91" t="s">
+        <v>109</v>
+      </c>
+      <c r="O2" s="91"/>
+      <c r="P2" s="91"/>
+      <c r="Q2" s="90"/>
+      <c r="R2" s="91" t="s">
+        <v>110</v>
+      </c>
+      <c r="S2" s="92"/>
+      <c r="AD2" s="93"/>
     </row>
     <row r="3">
-      <c r="B3" s="92"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="94" t="s">
-        <v>173</v>
-      </c>
-      <c r="E3" s="95">
+      <c r="B3" s="94"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="96" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" s="97">
         <v>4</v>
       </c>
-      <c r="F3" s="96">
+      <c r="F3" s="98">
         <v>1</v>
       </c>
-      <c r="G3" s="97">
+      <c r="G3" s="99">
         <v>2</v>
       </c>
-      <c r="H3" s="97">
+      <c r="H3" s="99">
         <v>3</v>
       </c>
-      <c r="I3" s="95">
+      <c r="I3" s="97">
         <v>4</v>
       </c>
-      <c r="J3" s="96">
+      <c r="J3" s="98">
         <v>1</v>
       </c>
-      <c r="K3" s="97">
+      <c r="K3" s="99">
         <v>2</v>
       </c>
-      <c r="L3" s="97">
+      <c r="L3" s="99">
         <v>3</v>
       </c>
-      <c r="M3" s="95">
+      <c r="M3" s="97">
         <v>4</v>
       </c>
-      <c r="N3" s="96">
+      <c r="N3" s="98">
         <v>1</v>
       </c>
-      <c r="O3" s="97">
+      <c r="O3" s="99">
         <v>2</v>
       </c>
-      <c r="P3" s="97">
+      <c r="P3" s="99">
         <v>3</v>
       </c>
-      <c r="Q3" s="95">
+      <c r="Q3" s="97">
         <v>4</v>
       </c>
-      <c r="R3" s="96">
+      <c r="R3" s="98">
         <v>1</v>
       </c>
-      <c r="S3" s="98">
+      <c r="S3" s="100">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="99" t="s">
-        <v>175</v>
-      </c>
-      <c r="C4" s="86" t="s">
-        <v>176</v>
-      </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="103"/>
-      <c r="L4" s="103"/>
-      <c r="M4" s="101"/>
-      <c r="N4" s="104"/>
-      <c r="O4" s="103"/>
-      <c r="P4" s="103"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="104"/>
-      <c r="S4" s="105"/>
+      <c r="B4" s="101" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="88" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="102"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="105"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="106"/>
+      <c r="O4" s="105"/>
+      <c r="P4" s="105"/>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="107"/>
       <c r="U4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="99"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="112"/>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="112"/>
-      <c r="S5" s="113"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="114"/>
+      <c r="K5" s="113"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="114"/>
+      <c r="O5" s="113"/>
+      <c r="P5" s="113"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="114"/>
+      <c r="S5" s="115"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="99"/>
-      <c r="C6" s="114" t="s">
-        <v>178</v>
-      </c>
-      <c r="D6" s="115"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="118"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="119"/>
-      <c r="L6" s="119"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="120"/>
-      <c r="O6" s="119"/>
-      <c r="P6" s="119"/>
-      <c r="Q6" s="116"/>
-      <c r="R6" s="120"/>
-      <c r="S6" s="121"/>
-      <c r="U6" s="122" t="s">
-        <v>179</v>
-      </c>
-      <c r="V6" s="122"/>
+      <c r="B6" s="101"/>
+      <c r="C6" s="116" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="117"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="121"/>
+      <c r="I6" s="118"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="121"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="122"/>
+      <c r="O6" s="121"/>
+      <c r="P6" s="121"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="122"/>
+      <c r="S6" s="123"/>
+      <c r="U6" s="124" t="s">
+        <v>181</v>
+      </c>
+      <c r="V6" s="124"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="99"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="108"/>
-      <c r="N7" s="112"/>
-      <c r="O7" s="111"/>
-      <c r="P7" s="111"/>
-      <c r="Q7" s="108"/>
-      <c r="R7" s="112"/>
-      <c r="S7" s="113"/>
+      <c r="B7" s="101"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="113"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="114"/>
+      <c r="O7" s="113"/>
+      <c r="P7" s="113"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="114"/>
+      <c r="S7" s="115"/>
       <c r="U7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="99"/>
-      <c r="C8" s="114" t="s">
-        <v>181</v>
-      </c>
-      <c r="D8" s="115"/>
-      <c r="E8" s="116"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="116"/>
-      <c r="J8" s="120"/>
-      <c r="K8" s="119"/>
-      <c r="L8" s="119"/>
-      <c r="M8" s="116"/>
-      <c r="N8" s="120"/>
-      <c r="O8" s="119"/>
-      <c r="P8" s="119"/>
-      <c r="Q8" s="116"/>
-      <c r="R8" s="120"/>
-      <c r="S8" s="121"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="116" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="117"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="122"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="118"/>
+      <c r="N8" s="122"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="118"/>
+      <c r="R8" s="122"/>
+      <c r="S8" s="123"/>
       <c r="U8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="99"/>
-      <c r="C9" s="106"/>
-      <c r="D9" s="107"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="111"/>
-      <c r="L9" s="111"/>
-      <c r="M9" s="108"/>
-      <c r="N9" s="112"/>
-      <c r="O9" s="111"/>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="108"/>
-      <c r="R9" s="112"/>
-      <c r="S9" s="113"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="109"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="114"/>
+      <c r="K9" s="113"/>
+      <c r="L9" s="113"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="114"/>
+      <c r="O9" s="113"/>
+      <c r="P9" s="113"/>
+      <c r="Q9" s="110"/>
+      <c r="R9" s="114"/>
+      <c r="S9" s="115"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="99"/>
-      <c r="C10" s="114" t="s">
-        <v>183</v>
-      </c>
-      <c r="D10" s="115"/>
-      <c r="E10" s="116"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="118"/>
-      <c r="H10" s="118"/>
-      <c r="I10" s="116"/>
-      <c r="J10" s="120"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="116"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="119"/>
-      <c r="P10" s="119"/>
-      <c r="Q10" s="116"/>
-      <c r="R10" s="120"/>
-      <c r="S10" s="121"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="116" t="s">
+        <v>185</v>
+      </c>
+      <c r="D10" s="117"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="122"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="118"/>
+      <c r="J10" s="122"/>
+      <c r="K10" s="121"/>
+      <c r="L10" s="121"/>
+      <c r="M10" s="118"/>
+      <c r="N10" s="122"/>
+      <c r="O10" s="121"/>
+      <c r="P10" s="121"/>
+      <c r="Q10" s="118"/>
+      <c r="R10" s="122"/>
+      <c r="S10" s="123"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="123"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="126"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="129"/>
-      <c r="M11" s="126"/>
-      <c r="N11" s="127"/>
-      <c r="O11" s="129"/>
-      <c r="P11" s="129"/>
-      <c r="Q11" s="126"/>
-      <c r="R11" s="127"/>
-      <c r="S11" s="130"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="126"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="128"/>
+      <c r="J11" s="129"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="128"/>
+      <c r="N11" s="129"/>
+      <c r="O11" s="131"/>
+      <c r="P11" s="131"/>
+      <c r="Q11" s="128"/>
+      <c r="R11" s="129"/>
+      <c r="S11" s="132"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="85" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="86" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="100"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="103"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="104"/>
-      <c r="O12" s="103"/>
-      <c r="P12" s="103"/>
-      <c r="Q12" s="101"/>
-      <c r="R12" s="104"/>
-      <c r="S12" s="105"/>
+      <c r="B12" s="87" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="88" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" s="102"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="106"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="133"/>
+      <c r="I12" s="134"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="105"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="106"/>
+      <c r="O12" s="105"/>
+      <c r="P12" s="105"/>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="106"/>
+      <c r="S12" s="107"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="99"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="112"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="108"/>
-      <c r="N13" s="112"/>
-      <c r="O13" s="111"/>
-      <c r="P13" s="111"/>
-      <c r="Q13" s="108"/>
-      <c r="R13" s="112"/>
-      <c r="S13" s="113"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="109"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="111"/>
+      <c r="K13" s="113"/>
+      <c r="L13" s="113"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="114"/>
+      <c r="O13" s="113"/>
+      <c r="P13" s="113"/>
+      <c r="Q13" s="110"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="115"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="99"/>
-      <c r="C14" s="114" t="s">
-        <v>186</v>
-      </c>
-      <c r="D14" s="133"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="120"/>
-      <c r="K14" s="119"/>
-      <c r="L14" s="119"/>
-      <c r="M14" s="116"/>
-      <c r="N14" s="120"/>
-      <c r="O14" s="119"/>
-      <c r="P14" s="119"/>
-      <c r="Q14" s="116"/>
-      <c r="R14" s="120"/>
-      <c r="S14" s="121"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="116" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="135"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="122"/>
+      <c r="K14" s="121"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="118"/>
+      <c r="N14" s="122"/>
+      <c r="O14" s="121"/>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="118"/>
+      <c r="R14" s="122"/>
+      <c r="S14" s="123"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="99"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="112"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="134"/>
-      <c r="J15" s="109"/>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="108"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="111"/>
-      <c r="P15" s="111"/>
-      <c r="Q15" s="108"/>
-      <c r="R15" s="112"/>
-      <c r="S15" s="113"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="114"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="113"/>
+      <c r="I15" s="136"/>
+      <c r="J15" s="111"/>
+      <c r="K15" s="113"/>
+      <c r="L15" s="113"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="113"/>
+      <c r="P15" s="113"/>
+      <c r="Q15" s="110"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="115"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="99"/>
-      <c r="C16" s="114" t="s">
-        <v>187</v>
-      </c>
-      <c r="D16" s="115"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="119"/>
-      <c r="L16" s="119"/>
-      <c r="M16" s="116"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="116"/>
-      <c r="R16" s="120"/>
-      <c r="S16" s="121"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="116" t="s">
+        <v>189</v>
+      </c>
+      <c r="D16" s="117"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="122"/>
+      <c r="G16" s="121"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="137"/>
+      <c r="J16" s="122"/>
+      <c r="K16" s="121"/>
+      <c r="L16" s="121"/>
+      <c r="M16" s="118"/>
+      <c r="N16" s="122"/>
+      <c r="O16" s="121"/>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="118"/>
+      <c r="R16" s="122"/>
+      <c r="S16" s="123"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="123"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="128"/>
-      <c r="L17" s="129"/>
-      <c r="M17" s="126"/>
-      <c r="N17" s="127"/>
-      <c r="O17" s="129"/>
-      <c r="P17" s="129"/>
-      <c r="Q17" s="126"/>
-      <c r="R17" s="127"/>
-      <c r="S17" s="130"/>
+      <c r="B17" s="125"/>
+      <c r="C17" s="126"/>
+      <c r="D17" s="127"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="131"/>
+      <c r="I17" s="128"/>
+      <c r="J17" s="138"/>
+      <c r="K17" s="130"/>
+      <c r="L17" s="131"/>
+      <c r="M17" s="128"/>
+      <c r="N17" s="129"/>
+      <c r="O17" s="131"/>
+      <c r="P17" s="131"/>
+      <c r="Q17" s="128"/>
+      <c r="R17" s="129"/>
+      <c r="S17" s="132"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="87" t="s">
-        <v>188</v>
-      </c>
-      <c r="C18" s="86" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="100"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="132"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="103"/>
-      <c r="L18" s="103"/>
-      <c r="M18" s="101"/>
-      <c r="N18" s="104"/>
-      <c r="O18" s="103"/>
-      <c r="P18" s="103"/>
-      <c r="Q18" s="101"/>
-      <c r="R18" s="104"/>
-      <c r="S18" s="105"/>
+      <c r="B18" s="89" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" s="88" t="s">
+        <v>191</v>
+      </c>
+      <c r="D18" s="102"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="105"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="106"/>
+      <c r="O18" s="105"/>
+      <c r="P18" s="105"/>
+      <c r="Q18" s="103"/>
+      <c r="R18" s="106"/>
+      <c r="S18" s="107"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="99"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="111"/>
-      <c r="M19" s="108"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="111"/>
-      <c r="P19" s="111"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="113"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="109"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="112"/>
+      <c r="H19" s="113"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="113"/>
+      <c r="L19" s="113"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="114"/>
+      <c r="O19" s="113"/>
+      <c r="P19" s="113"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="114"/>
+      <c r="S19" s="115"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="99"/>
-      <c r="C20" s="114" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="115"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="119"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="135"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="116"/>
-      <c r="N20" s="120"/>
-      <c r="O20" s="119"/>
-      <c r="P20" s="119"/>
-      <c r="Q20" s="116"/>
-      <c r="R20" s="120"/>
-      <c r="S20" s="121"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="116" t="s">
+        <v>192</v>
+      </c>
+      <c r="D20" s="117"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="121"/>
+      <c r="H20" s="121"/>
+      <c r="I20" s="137"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="120"/>
+      <c r="L20" s="120"/>
+      <c r="M20" s="118"/>
+      <c r="N20" s="122"/>
+      <c r="O20" s="121"/>
+      <c r="P20" s="121"/>
+      <c r="Q20" s="118"/>
+      <c r="R20" s="122"/>
+      <c r="S20" s="123"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="99"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="112"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="112"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="108"/>
-      <c r="N21" s="137"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="111"/>
-      <c r="Q21" s="108"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="113"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="109"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="113"/>
+      <c r="L21" s="113"/>
+      <c r="M21" s="110"/>
+      <c r="N21" s="139"/>
+      <c r="O21" s="113"/>
+      <c r="P21" s="113"/>
+      <c r="Q21" s="110"/>
+      <c r="R21" s="114"/>
+      <c r="S21" s="115"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="99"/>
-      <c r="C22" s="114" t="s">
-        <v>191</v>
-      </c>
-      <c r="D22" s="115"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="120"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="116"/>
-      <c r="J22" s="120"/>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="116"/>
-      <c r="N22" s="120"/>
-      <c r="O22" s="119"/>
-      <c r="P22" s="119"/>
-      <c r="Q22" s="116"/>
-      <c r="R22" s="120"/>
-      <c r="S22" s="121"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="116" t="s">
+        <v>193</v>
+      </c>
+      <c r="D22" s="117"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="121"/>
+      <c r="H22" s="121"/>
+      <c r="I22" s="118"/>
+      <c r="J22" s="122"/>
+      <c r="K22" s="120"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="118"/>
+      <c r="N22" s="122"/>
+      <c r="O22" s="121"/>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="118"/>
+      <c r="R22" s="122"/>
+      <c r="S22" s="123"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="123"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="127"/>
-      <c r="K23" s="129"/>
-      <c r="L23" s="129"/>
-      <c r="M23" s="126"/>
-      <c r="N23" s="127"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="129"/>
-      <c r="Q23" s="126"/>
-      <c r="R23" s="127"/>
-      <c r="S23" s="130"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="126"/>
+      <c r="D23" s="127"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="129"/>
+      <c r="G23" s="131"/>
+      <c r="H23" s="131"/>
+      <c r="I23" s="128"/>
+      <c r="J23" s="129"/>
+      <c r="K23" s="131"/>
+      <c r="L23" s="131"/>
+      <c r="M23" s="128"/>
+      <c r="N23" s="129"/>
+      <c r="O23" s="131"/>
+      <c r="P23" s="131"/>
+      <c r="Q23" s="128"/>
+      <c r="R23" s="129"/>
+      <c r="S23" s="132"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="87" t="s">
-        <v>192</v>
-      </c>
-      <c r="C24" s="86" t="s">
-        <v>193</v>
-      </c>
-      <c r="D24" s="100"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="101"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="103"/>
-      <c r="L24" s="103"/>
-      <c r="M24" s="132"/>
-      <c r="N24" s="102"/>
-      <c r="O24" s="131"/>
-      <c r="P24" s="131"/>
-      <c r="Q24" s="101"/>
-      <c r="R24" s="104"/>
-      <c r="S24" s="105"/>
+      <c r="B24" s="89" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="88" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24" s="102"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="105"/>
+      <c r="M24" s="134"/>
+      <c r="N24" s="104"/>
+      <c r="O24" s="133"/>
+      <c r="P24" s="133"/>
+      <c r="Q24" s="103"/>
+      <c r="R24" s="106"/>
+      <c r="S24" s="107"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="99"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="107"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="112"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="108"/>
-      <c r="N25" s="112"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="108"/>
-      <c r="R25" s="112"/>
-      <c r="S25" s="113"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="114"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="113"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="114"/>
+      <c r="K25" s="113"/>
+      <c r="L25" s="113"/>
+      <c r="M25" s="110"/>
+      <c r="N25" s="114"/>
+      <c r="O25" s="113"/>
+      <c r="P25" s="113"/>
+      <c r="Q25" s="110"/>
+      <c r="R25" s="114"/>
+      <c r="S25" s="115"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="99"/>
-      <c r="C26" s="114" t="s">
-        <v>194</v>
-      </c>
-      <c r="D26" s="115"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="116"/>
-      <c r="J26" s="120"/>
-      <c r="K26" s="119"/>
-      <c r="L26" s="119"/>
-      <c r="M26" s="116"/>
-      <c r="N26" s="120"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="118"/>
-      <c r="Q26" s="116"/>
-      <c r="R26" s="120"/>
-      <c r="S26" s="121"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="116" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" s="117"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="122"/>
+      <c r="G26" s="121"/>
+      <c r="H26" s="121"/>
+      <c r="I26" s="118"/>
+      <c r="J26" s="122"/>
+      <c r="K26" s="121"/>
+      <c r="L26" s="121"/>
+      <c r="M26" s="118"/>
+      <c r="N26" s="122"/>
+      <c r="O26" s="120"/>
+      <c r="P26" s="120"/>
+      <c r="Q26" s="118"/>
+      <c r="R26" s="122"/>
+      <c r="S26" s="123"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="99"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="108"/>
-      <c r="J27" s="112"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="108"/>
-      <c r="N27" s="112"/>
-      <c r="O27" s="111"/>
-      <c r="P27" s="111"/>
-      <c r="Q27" s="108"/>
-      <c r="R27" s="112"/>
-      <c r="S27" s="113"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="114"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="113"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="114"/>
+      <c r="K27" s="113"/>
+      <c r="L27" s="113"/>
+      <c r="M27" s="110"/>
+      <c r="N27" s="114"/>
+      <c r="O27" s="113"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="110"/>
+      <c r="R27" s="114"/>
+      <c r="S27" s="115"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="99"/>
-      <c r="C28" s="114" t="s">
-        <v>195</v>
-      </c>
-      <c r="D28" s="115"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="116"/>
-      <c r="J28" s="120"/>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="120"/>
-      <c r="O28" s="119"/>
-      <c r="P28" s="118"/>
-      <c r="Q28" s="135"/>
-      <c r="R28" s="120"/>
-      <c r="S28" s="121"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="116" t="s">
+        <v>197</v>
+      </c>
+      <c r="D28" s="117"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="122"/>
+      <c r="G28" s="121"/>
+      <c r="H28" s="121"/>
+      <c r="I28" s="118"/>
+      <c r="J28" s="122"/>
+      <c r="K28" s="121"/>
+      <c r="L28" s="121"/>
+      <c r="M28" s="118"/>
+      <c r="N28" s="122"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="120"/>
+      <c r="Q28" s="137"/>
+      <c r="R28" s="122"/>
+      <c r="S28" s="123"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="99"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="140"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="142"/>
-      <c r="I29" s="139"/>
-      <c r="J29" s="140"/>
-      <c r="K29" s="141"/>
-      <c r="L29" s="142"/>
-      <c r="M29" s="139"/>
-      <c r="N29" s="143"/>
-      <c r="O29" s="142"/>
-      <c r="P29" s="141"/>
-      <c r="Q29" s="139"/>
-      <c r="R29" s="140"/>
-      <c r="S29" s="144"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="140"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="143"/>
+      <c r="H29" s="144"/>
+      <c r="I29" s="141"/>
+      <c r="J29" s="142"/>
+      <c r="K29" s="143"/>
+      <c r="L29" s="144"/>
+      <c r="M29" s="141"/>
+      <c r="N29" s="145"/>
+      <c r="O29" s="144"/>
+      <c r="P29" s="143"/>
+      <c r="Q29" s="141"/>
+      <c r="R29" s="142"/>
+      <c r="S29" s="146"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="145" t="s">
+      <c r="B30" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="146" t="s">
-        <v>141</v>
-      </c>
-      <c r="D30" s="100"/>
-      <c r="E30" s="147"/>
-      <c r="F30" s="148"/>
-      <c r="G30" s="148"/>
-      <c r="H30" s="149"/>
-      <c r="I30" s="150"/>
-      <c r="J30" s="148"/>
-      <c r="K30" s="148"/>
-      <c r="L30" s="149"/>
-      <c r="M30" s="150"/>
-      <c r="N30" s="148"/>
-      <c r="O30" s="149"/>
-      <c r="P30" s="148"/>
-      <c r="Q30" s="150"/>
-      <c r="R30" s="148"/>
-      <c r="S30" s="151"/>
+      <c r="C30" s="148" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="102"/>
+      <c r="E30" s="149"/>
+      <c r="F30" s="150"/>
+      <c r="G30" s="150"/>
+      <c r="H30" s="151"/>
+      <c r="I30" s="152"/>
+      <c r="J30" s="150"/>
+      <c r="K30" s="150"/>
+      <c r="L30" s="151"/>
+      <c r="M30" s="152"/>
+      <c r="N30" s="150"/>
+      <c r="O30" s="151"/>
+      <c r="P30" s="150"/>
+      <c r="Q30" s="152"/>
+      <c r="R30" s="150"/>
+      <c r="S30" s="153"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="152"/>
-      <c r="C31" s="153"/>
-      <c r="D31" s="107"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="155"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="156"/>
-      <c r="I31" s="157"/>
-      <c r="J31" s="155"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="156"/>
-      <c r="M31" s="157"/>
-      <c r="N31" s="155"/>
-      <c r="O31" s="156"/>
-      <c r="P31" s="155"/>
-      <c r="Q31" s="157"/>
-      <c r="R31" s="155"/>
-      <c r="S31" s="113"/>
+      <c r="B31" s="154"/>
+      <c r="C31" s="155"/>
+      <c r="D31" s="109"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="157"/>
+      <c r="G31" s="157"/>
+      <c r="H31" s="158"/>
+      <c r="I31" s="159"/>
+      <c r="J31" s="157"/>
+      <c r="K31" s="160"/>
+      <c r="L31" s="158"/>
+      <c r="M31" s="159"/>
+      <c r="N31" s="157"/>
+      <c r="O31" s="158"/>
+      <c r="P31" s="157"/>
+      <c r="Q31" s="159"/>
+      <c r="R31" s="157"/>
+      <c r="S31" s="115"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="152"/>
-      <c r="C32" s="153" t="s">
+      <c r="B32" s="154"/>
+      <c r="C32" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="115"/>
-      <c r="E32" s="159"/>
-      <c r="F32" s="160"/>
-      <c r="G32" s="160"/>
-      <c r="H32" s="161"/>
-      <c r="I32" s="162"/>
-      <c r="J32" s="160"/>
-      <c r="K32" s="160"/>
-      <c r="L32" s="161"/>
-      <c r="M32" s="162"/>
-      <c r="N32" s="160"/>
-      <c r="O32" s="161"/>
-      <c r="P32" s="160"/>
-      <c r="Q32" s="162"/>
-      <c r="R32" s="160"/>
-      <c r="S32" s="163"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="161"/>
+      <c r="F32" s="162"/>
+      <c r="G32" s="162"/>
+      <c r="H32" s="163"/>
+      <c r="I32" s="164"/>
+      <c r="J32" s="162"/>
+      <c r="K32" s="162"/>
+      <c r="L32" s="163"/>
+      <c r="M32" s="164"/>
+      <c r="N32" s="162"/>
+      <c r="O32" s="163"/>
+      <c r="P32" s="162"/>
+      <c r="Q32" s="164"/>
+      <c r="R32" s="162"/>
+      <c r="S32" s="165"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="152"/>
-      <c r="C33" s="153"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="154"/>
-      <c r="F33" s="158"/>
-      <c r="G33" s="155"/>
-      <c r="H33" s="164"/>
-      <c r="I33" s="165"/>
-      <c r="J33" s="155"/>
-      <c r="K33" s="158"/>
-      <c r="L33" s="156"/>
-      <c r="M33" s="157"/>
-      <c r="N33" s="155"/>
-      <c r="O33" s="156"/>
-      <c r="P33" s="155"/>
-      <c r="Q33" s="157"/>
-      <c r="R33" s="155"/>
-      <c r="S33" s="113"/>
+      <c r="B33" s="154"/>
+      <c r="C33" s="155"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="160"/>
+      <c r="G33" s="157"/>
+      <c r="H33" s="166"/>
+      <c r="I33" s="167"/>
+      <c r="J33" s="157"/>
+      <c r="K33" s="160"/>
+      <c r="L33" s="158"/>
+      <c r="M33" s="159"/>
+      <c r="N33" s="157"/>
+      <c r="O33" s="158"/>
+      <c r="P33" s="157"/>
+      <c r="Q33" s="159"/>
+      <c r="R33" s="157"/>
+      <c r="S33" s="115"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="152"/>
-      <c r="C34" s="106" t="s">
-        <v>196</v>
-      </c>
-      <c r="D34" s="138"/>
-      <c r="E34" s="166"/>
-      <c r="F34" s="167"/>
-      <c r="G34" s="167"/>
-      <c r="H34" s="168"/>
-      <c r="I34" s="169"/>
-      <c r="J34" s="167"/>
-      <c r="K34" s="167"/>
-      <c r="L34" s="168"/>
-      <c r="M34" s="169"/>
-      <c r="N34" s="167"/>
-      <c r="O34" s="168"/>
-      <c r="P34" s="167"/>
-      <c r="Q34" s="169"/>
-      <c r="R34" s="167"/>
-      <c r="S34" s="170"/>
-      <c r="U34" s="171"/>
-      <c r="V34" s="172" t="s">
-        <v>197</v>
+      <c r="B34" s="154"/>
+      <c r="C34" s="108" t="s">
+        <v>198</v>
+      </c>
+      <c r="D34" s="140"/>
+      <c r="E34" s="168"/>
+      <c r="F34" s="169"/>
+      <c r="G34" s="169"/>
+      <c r="H34" s="170"/>
+      <c r="I34" s="171"/>
+      <c r="J34" s="169"/>
+      <c r="K34" s="169"/>
+      <c r="L34" s="170"/>
+      <c r="M34" s="171"/>
+      <c r="N34" s="169"/>
+      <c r="O34" s="170"/>
+      <c r="P34" s="169"/>
+      <c r="Q34" s="171"/>
+      <c r="R34" s="169"/>
+      <c r="S34" s="172"/>
+      <c r="U34" s="173"/>
+      <c r="V34" s="174" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="173"/>
-      <c r="C35" s="174"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="175"/>
-      <c r="F35" s="176"/>
-      <c r="G35" s="176"/>
-      <c r="H35" s="177"/>
-      <c r="I35" s="178"/>
-      <c r="J35" s="176"/>
-      <c r="K35" s="176"/>
-      <c r="L35" s="177"/>
-      <c r="M35" s="178"/>
-      <c r="N35" s="176"/>
-      <c r="O35" s="177"/>
-      <c r="P35" s="176"/>
-      <c r="Q35" s="178"/>
-      <c r="R35" s="176"/>
-      <c r="S35" s="130"/>
-      <c r="U35" s="179"/>
-      <c r="V35" s="180" t="s">
-        <v>198</v>
+      <c r="B35" s="175"/>
+      <c r="C35" s="176"/>
+      <c r="D35" s="127"/>
+      <c r="E35" s="177"/>
+      <c r="F35" s="178"/>
+      <c r="G35" s="178"/>
+      <c r="H35" s="179"/>
+      <c r="I35" s="180"/>
+      <c r="J35" s="178"/>
+      <c r="K35" s="178"/>
+      <c r="L35" s="179"/>
+      <c r="M35" s="180"/>
+      <c r="N35" s="178"/>
+      <c r="O35" s="179"/>
+      <c r="P35" s="178"/>
+      <c r="Q35" s="180"/>
+      <c r="R35" s="178"/>
+      <c r="S35" s="132"/>
+      <c r="U35" s="181"/>
+      <c r="V35" s="182" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/LHO - M5 - JournalPlanif.xlsx
+++ b/Documentation/LHO - M5 - JournalPlanif.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="203">
   <si>
     <t>date</t>
   </si>
@@ -345,6 +345,12 @@
   </si>
   <si>
     <t xml:space="preserve">Documentation des résultats des tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction des bug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout Licence dans la documentation</t>
   </si>
   <si>
     <t xml:space="preserve">Par jour</t>
@@ -1614,7 +1620,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="181">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1668,12 +1674,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4918,8 +4918,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E78">
-  <autoFilter ref="B2:E78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E80">
+  <autoFilter ref="B2:E80"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.016925246826516218</v>
+        <v>1.678321678321678e-002</v>
       </c>
       <c r="J3" s="12" t="str">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -5499,7 +5499,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.016925246826516218</v>
+        <v>1.678321678321678e-002</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.05359661495063469</v>
+        <v>5.3146853146853142e-002</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -5565,7 +5565,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.095909732016925237</v>
+        <v>9.5104895104895087e-002</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -5598,7 +5598,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>8</v>
@@ -5611,11 +5611,11 @@
       </c>
       <c r="H7" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>60.25</v>
+        <v>60.75</v>
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.33991537376586739</v>
+        <v>0.3398601398601398</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="K7" s="13">
         <f/>
-        <v>60.25</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="8" ht="28.5">
@@ -5644,11 +5644,11 @@
       </c>
       <c r="H8" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>75.666666666666671</v>
+        <v>77.166666666666671</v>
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.4268923366243535</v>
+        <v>0.43170163170163167</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="K8" s="13">
         <f/>
-        <v>75.666666666666671</v>
+        <v>77.166666666666671</v>
       </c>
     </row>
     <row r="9">
@@ -5677,11 +5677,11 @@
       </c>
       <c r="H9" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>8.3333333333333321</v>
+        <v>7.8333333333333339</v>
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.047014574518100594</v>
+        <v>4.3822843822843821e-002</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="K9" s="14">
         <f/>
-        <v>8.3333333333333321</v>
+        <v>7.8333333333333339</v>
       </c>
     </row>
     <row r="10">
@@ -5697,7 +5697,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>12</v>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.0028208744710860362</v>
+        <v>2.7972027972027968e-003</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -5724,7 +5724,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>12</v>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>177.25000000000003</v>
+        <v>178.75000000000003</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -5747,7 +5747,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>10</v>
@@ -5762,7 +5762,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>12</v>
@@ -5777,7 +5777,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>12</v>
@@ -5833,7 +5833,7 @@
         <v>35</v>
       </c>
       <c r="C18" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>10</v>
@@ -5847,7 +5847,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>12</v>
@@ -5861,7 +5861,7 @@
         <v>39</v>
       </c>
       <c r="C20" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>19</v>
@@ -5875,7 +5875,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>15</v>
@@ -5903,7 +5903,7 @@
         <v>43</v>
       </c>
       <c r="C23" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>15</v>
@@ -5917,7 +5917,7 @@
         <v>45</v>
       </c>
       <c r="C24" s="6">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>15</v>
@@ -5959,7 +5959,7 @@
         <v>49</v>
       </c>
       <c r="C27" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>12</v>
@@ -5973,7 +5973,7 @@
         <v>52</v>
       </c>
       <c r="C28" s="6">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>15</v>
@@ -6015,7 +6015,7 @@
         <v>46087</v>
       </c>
       <c r="C31" s="6">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>21</v>
@@ -6043,7 +6043,7 @@
         <v>46091</v>
       </c>
       <c r="C33" s="6">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>12</v>
@@ -6071,7 +6071,7 @@
         <v>46091</v>
       </c>
       <c r="C35" s="6">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>19</v>
@@ -6099,7 +6099,7 @@
         <v>46093</v>
       </c>
       <c r="C37" s="6">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>19</v>
@@ -6127,7 +6127,7 @@
         <v>46087</v>
       </c>
       <c r="C39" s="6">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>21</v>
@@ -6214,7 +6214,7 @@
         <v>46100</v>
       </c>
       <c r="C45" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>8</v>
@@ -6228,7 +6228,7 @@
         <v>46100</v>
       </c>
       <c r="C46" s="6">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>19</v>
@@ -6256,7 +6256,7 @@
         <v>46102</v>
       </c>
       <c r="C48" s="21">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>8</v>
@@ -6312,7 +6312,7 @@
         <v>46104</v>
       </c>
       <c r="C52" s="21">
-        <v>0.013888888888888888</v>
+        <v>1.3888888888888888e-002</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>21</v>
@@ -6340,7 +6340,7 @@
         <v>46118</v>
       </c>
       <c r="C54" s="21">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>19</v>
@@ -6354,7 +6354,7 @@
         <v>46119</v>
       </c>
       <c r="C55" s="21">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>8</v>
@@ -6368,7 +6368,7 @@
         <v>46119</v>
       </c>
       <c r="C56" s="21">
-        <v>0.0625</v>
+        <v>6.25e-002</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>19</v>
@@ -6410,7 +6410,7 @@
         <v>46134</v>
       </c>
       <c r="C59" s="21">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>12</v>
@@ -6424,7 +6424,7 @@
         <v>46134</v>
       </c>
       <c r="C60" s="21">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>19</v>
@@ -6438,7 +6438,7 @@
         <v>46135</v>
       </c>
       <c r="C61" s="21">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D61" s="7" t="s">
         <v>19</v>
@@ -6480,7 +6480,7 @@
         <v>46140</v>
       </c>
       <c r="C64" s="21">
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
       <c r="D64" s="7" t="s">
         <v>21</v>
@@ -6489,7 +6489,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="65" ht="28.800000000000001">
+    <row r="65" ht="28.5">
       <c r="B65" s="5">
         <v>46140</v>
       </c>
@@ -6503,7 +6503,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="66" ht="28.800000000000001">
+    <row r="66" ht="28.5">
       <c r="B66" s="5">
         <v>46160</v>
       </c>
@@ -6531,12 +6531,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" ht="28.800000000000001">
+    <row r="68" ht="28.5">
       <c r="B68" s="5">
         <v>46161</v>
       </c>
       <c r="C68" s="21">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>24</v>
@@ -6564,7 +6564,7 @@
         <v>46177</v>
       </c>
       <c r="C70" s="21">
-        <v>0.013888888888888888</v>
+        <v>1.3888888888888888e-002</v>
       </c>
       <c r="D70" s="7" t="s">
         <v>19</v>
@@ -6578,7 +6578,7 @@
         <v>46177</v>
       </c>
       <c r="C71" s="21">
-        <v>0.034722222222222224</v>
+        <v>3.4722222222222224e-002</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>19</v>
@@ -6594,14 +6594,14 @@
       <c r="C72" s="23">
         <v>0.125</v>
       </c>
-      <c r="D72" s="24" t="s">
+      <c r="D72" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E72" s="25" t="s">
+      <c r="E72" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="28.5">
       <c r="B73" s="5">
         <v>46177</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>46180</v>
       </c>
       <c r="C74" s="21">
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
       <c r="D74" s="7" t="s">
         <v>12</v>
@@ -6647,11 +6647,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="26">
+      <c r="B76" s="24">
         <v>46181</v>
       </c>
       <c r="C76" s="21">
-        <v>0.020833333333333332</v>
+        <v>2.0833333333333332e-002</v>
       </c>
       <c r="D76" s="7" t="s">
         <v>12</v>
@@ -6661,44 +6661,60 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="26">
+      <c r="B77" s="24">
         <v>46182</v>
       </c>
       <c r="C77" s="21">
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="D77" s="27" t="s">
+        <v>6.25e-002</v>
+      </c>
+      <c r="D77" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E77" s="28" t="s">
+      <c r="E77" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="26">
+      <c r="B78" s="24">
         <v>46182</v>
       </c>
       <c r="C78" s="21">
-        <v>0.010416666666666666</v>
-      </c>
-      <c r="D78" s="27" t="s">
+        <v>1.0416666666666666e-002</v>
+      </c>
+      <c r="D78" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E78" s="28" t="s">
+      <c r="E78" s="8" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="8"/>
+      <c r="B79" s="24">
+        <v>46182</v>
+      </c>
+      <c r="C79" s="21">
+        <v>6.25e-002</v>
+      </c>
+      <c r="D79" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" s="26" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="80">
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="8"/>
+      <c r="B80" s="24">
+        <v>46182</v>
+      </c>
+      <c r="C80" s="21">
+        <v>2.0833333333333332e-002</v>
+      </c>
+      <c r="D80" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" s="26" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="7"/>
@@ -6722,7 +6738,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00CF000C-009D-400F-A118-00DF00C800FB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{BEC242A8-24BE-4A6A-A6B7-4038FDA54160}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6746,11 +6762,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -6764,47 +6780,47 @@
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29">
+      <c r="A3" s="27">
         <v>46042</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C3" s="30"/>
+      <c r="C3" s="28"/>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="31">
+        <v>111</v>
+      </c>
+      <c r="F3" s="29">
         <f t="shared" ref="F3:F8" si="0">SUMPRODUCT((MONTH($A$3:$A$152)=D3)*($A$3:$A$152&lt;&gt;"")*$B$3:$B$152)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="30">
         <f t="shared" ref="G3:G8" si="1">F3*24</f>
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29">
+      <c r="A4" s="27">
         <v>46043</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6813,22 +6829,22 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F4" s="31">
+        <v>112</v>
+      </c>
+      <c r="F4" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="32">
+      <c r="G4" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29">
+      <c r="A5" s="27">
         <v>46044</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6837,22 +6853,22 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F5" s="31">
+        <v>113</v>
+      </c>
+      <c r="F5" s="29">
         <f t="shared" si="0"/>
         <v>2.6805555555555558</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="30">
         <f t="shared" si="1"/>
         <v>64.333333333333343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29">
+      <c r="A6" s="27">
         <v>46045</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6861,22 +6877,22 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="31">
+        <v>114</v>
+      </c>
+      <c r="F6" s="29">
         <f t="shared" si="0"/>
         <v>1.2083333333333333</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="30">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29">
+      <c r="A7" s="27">
         <v>46046</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6885,22 +6901,22 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F7" s="31">
+        <v>115</v>
+      </c>
+      <c r="F7" s="29">
         <f t="shared" si="0"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="G7" s="32">
+      <c r="G7" s="30">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29">
+      <c r="A8" s="27">
         <v>46047</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6909,2071 +6925,2071 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="31">
+        <v>116</v>
+      </c>
+      <c r="F8" s="29">
         <f t="shared" si="0"/>
-        <v>0.57986111111111116</v>
-      </c>
-      <c r="G8" s="32">
+        <v>0.64236111111111116</v>
+      </c>
+      <c r="G8" s="30">
         <f t="shared" si="1"/>
-        <v>13.916666666666668</v>
+        <v>15.416666666666668</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29">
+      <c r="A9" s="27">
         <v>46048</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
-      <c r="G9" s="32">
+      <c r="G9" s="30">
         <f>SUM(G3:G8)</f>
-        <v>114.25000000000001</v>
+        <v>115.75000000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29">
+      <c r="A10" s="27">
         <v>46049</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="29">
+      <c r="A11" s="27">
         <v>46050</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="29">
+      <c r="A12" s="27">
         <v>46051</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="29">
+      <c r="A13" s="27">
         <v>46052</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="29">
+      <c r="A14" s="27">
         <v>46053</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="29">
+      <c r="A15" s="27">
         <v>46054</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="29">
+      <c r="A16" s="27">
         <v>46055</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="29">
+      <c r="A17" s="27">
         <v>46056</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="29">
+      <c r="A18" s="27">
         <v>46057</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="29">
+      <c r="A19" s="27">
         <v>46058</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="29">
+      <c r="A20" s="27">
         <v>46059</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="29">
+      <c r="A21" s="27">
         <v>46060</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="29">
+      <c r="A22" s="27">
         <v>46061</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="29">
+      <c r="A23" s="27">
         <v>46062</v>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="29">
+      <c r="A24" s="27">
         <v>46063</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="29">
+      <c r="A25" s="27">
         <v>46064</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
     </row>
     <row r="26">
-      <c r="A26" s="29">
+      <c r="A26" s="27">
         <v>46065</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C26"/>
-      <c r="F26" s="32"/>
+      <c r="F26" s="30"/>
     </row>
     <row r="27">
-      <c r="A27" s="29">
+      <c r="A27" s="27">
         <v>46066</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29">
+      <c r="A28" s="27">
         <v>46067</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29">
+      <c r="A29" s="27">
         <v>46068</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29">
+      <c r="A30" s="27">
         <v>46069</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29">
+      <c r="A31" s="27">
         <v>46070</v>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29">
+      <c r="A32" s="27">
         <v>46071</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C32" s="33">
+      <c r="C32" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29">
+      <c r="A33" s="27">
         <v>46072</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29">
+      <c r="A34" s="27">
         <v>46073</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29">
+      <c r="A35" s="27">
         <v>46074</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="29">
+      <c r="A36" s="27">
         <v>46075</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29">
+      <c r="A37" s="27">
         <v>46076</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C37" s="33">
+      <c r="C37" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29">
+      <c r="A38" s="27">
         <v>46077</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29">
+      <c r="A39" s="27">
         <v>46078</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29">
+      <c r="A40" s="27">
         <v>46079</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C40" s="33">
+      <c r="C40" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29">
+      <c r="A41" s="27">
         <v>46080</v>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29">
+      <c r="A42" s="27">
         <v>46081</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29">
+      <c r="A43" s="27">
         <v>46082</v>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C43" s="33">
+      <c r="C43" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29">
+      <c r="A44" s="27">
         <v>46083</v>
       </c>
-      <c r="B44" s="30">
+      <c r="B44" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29">
+      <c r="A45" s="27">
         <v>46084</v>
       </c>
-      <c r="B45" s="30">
+      <c r="B45" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29">
+      <c r="A46" s="27">
         <v>46085</v>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29">
+      <c r="A47" s="27">
         <v>46086</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29">
+      <c r="A48" s="27">
         <v>46087</v>
       </c>
-      <c r="B48" s="30">
+      <c r="B48" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29">
+      <c r="A49" s="27">
         <v>46088</v>
       </c>
-      <c r="B49" s="30">
+      <c r="B49" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
-      <c r="C49" s="33">
+      <c r="C49" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29">
+      <c r="A50" s="27">
         <v>46089</v>
       </c>
-      <c r="B50" s="30">
+      <c r="B50" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29">
+      <c r="A51" s="27">
         <v>46090</v>
       </c>
-      <c r="B51" s="30">
+      <c r="B51" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29">
+      <c r="A52" s="27">
         <v>46091</v>
       </c>
-      <c r="B52" s="30">
+      <c r="B52" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C52" s="33">
+      <c r="C52" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29">
+      <c r="A53" s="27">
         <v>46092</v>
       </c>
-      <c r="B53" s="30">
+      <c r="B53" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29">
+      <c r="A54" s="27">
         <v>46093</v>
       </c>
-      <c r="B54" s="30">
+      <c r="B54" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="C54" s="33">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="C54" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29">
+      <c r="A55" s="27">
         <v>46094</v>
       </c>
-      <c r="B55" s="30">
+      <c r="B55" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C55" s="33">
+      <c r="C55" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29">
+      <c r="A56" s="27">
         <v>46095</v>
       </c>
-      <c r="B56" s="30">
+      <c r="B56" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29">
+      <c r="A57" s="27">
         <v>46096</v>
       </c>
-      <c r="B57" s="30">
+      <c r="B57" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29">
+      <c r="A58" s="27">
         <v>46097</v>
       </c>
-      <c r="B58" s="30">
+      <c r="B58" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C58" s="33">
+      <c r="C58" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="29">
+      <c r="A59" s="27">
         <v>46098</v>
       </c>
-      <c r="B59" s="30">
+      <c r="B59" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="29">
+      <c r="A60" s="27">
         <v>46099</v>
       </c>
-      <c r="B60" s="30">
+      <c r="B60" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C60" s="33">
+      <c r="C60" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="29">
+      <c r="A61" s="27">
         <v>46100</v>
       </c>
-      <c r="B61" s="30">
+      <c r="B61" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="C61" s="33">
+      <c r="C61" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29">
+      <c r="A62" s="27">
         <v>46101</v>
       </c>
-      <c r="B62" s="30">
+      <c r="B62" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29">
+      <c r="A63" s="27">
         <v>46102</v>
       </c>
-      <c r="B63" s="30">
+      <c r="B63" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="29">
+      <c r="A64" s="27">
         <v>46103</v>
       </c>
-      <c r="B64" s="30">
+      <c r="B64" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C64" s="33">
+      <c r="C64" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="29">
+      <c r="A65" s="27">
         <v>46104</v>
       </c>
-      <c r="B65" s="30">
+      <c r="B65" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
-        <v>0.013888888888888888</v>
-      </c>
-      <c r="C65" s="33">
+        <v>1.3888888888888888e-002</v>
+      </c>
+      <c r="C65" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
-        <v>0.013888888888888888</v>
+        <v>1.3888888888888888e-002</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="29">
+      <c r="A66" s="27">
         <v>46105</v>
       </c>
-      <c r="B66" s="30">
+      <c r="B66" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29">
+      <c r="A67" s="27">
         <v>46106</v>
       </c>
-      <c r="B67" s="30">
+      <c r="B67" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C67" s="33">
+      <c r="C67" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29">
+      <c r="A68" s="27">
         <v>46107</v>
       </c>
-      <c r="B68" s="30">
+      <c r="B68" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29">
+      <c r="A69" s="27">
         <v>46108</v>
       </c>
-      <c r="B69" s="30">
+      <c r="B69" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29">
+      <c r="A70" s="27">
         <v>46109</v>
       </c>
-      <c r="B70" s="30">
+      <c r="B70" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C70" s="33">
+      <c r="C70" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29">
+      <c r="A71" s="27">
         <v>46110</v>
       </c>
-      <c r="B71" s="30">
+      <c r="B71" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C71" s="33">
+      <c r="C71" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29">
+      <c r="A72" s="27">
         <v>46111</v>
       </c>
-      <c r="B72" s="30">
+      <c r="B72" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C72" s="33">
+      <c r="C72" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="29">
+      <c r="A73" s="27">
         <v>46112</v>
       </c>
-      <c r="B73" s="30">
+      <c r="B73" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C73" s="33">
+      <c r="C73" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29">
+      <c r="A74" s="27">
         <v>46113</v>
       </c>
-      <c r="B74" s="30">
+      <c r="B74" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C74" s="33">
+      <c r="C74" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29">
+      <c r="A75" s="27">
         <v>46114</v>
       </c>
-      <c r="B75" s="30">
+      <c r="B75" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C75" s="33">
+      <c r="C75" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29">
+      <c r="A76" s="27">
         <v>46115</v>
       </c>
-      <c r="B76" s="30">
+      <c r="B76" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C76" s="33">
+      <c r="C76" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29">
+      <c r="A77" s="27">
         <v>46116</v>
       </c>
-      <c r="B77" s="30">
+      <c r="B77" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C77" s="33">
+      <c r="C77" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29">
+      <c r="A78" s="27">
         <v>46117</v>
       </c>
-      <c r="B78" s="30">
+      <c r="B78" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C78" s="33">
+      <c r="C78" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29">
+      <c r="A79" s="27">
         <v>46118</v>
       </c>
-      <c r="B79" s="30">
+      <c r="B79" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="C79" s="33">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="C79" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="29">
+      <c r="A80" s="27">
         <v>46119</v>
       </c>
-      <c r="B80" s="30">
+      <c r="B80" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
-      </c>
-      <c r="C80" s="33">
+        <v>8.3333333333333329e-002</v>
+      </c>
+      <c r="C80" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
-        <v>0.083333333333333329</v>
+        <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="29">
+      <c r="A81" s="27">
         <v>46120</v>
       </c>
-      <c r="B81" s="30">
+      <c r="B81" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C81" s="33">
+      <c r="C81" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="29">
+      <c r="A82" s="27">
         <v>46121</v>
       </c>
-      <c r="B82" s="30">
+      <c r="B82" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C82" s="33">
+      <c r="C82" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="29">
+      <c r="A83" s="27">
         <v>46122</v>
       </c>
-      <c r="B83" s="30">
+      <c r="B83" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C83" s="33">
+      <c r="C83" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="29">
+      <c r="A84" s="27">
         <v>46123</v>
       </c>
-      <c r="B84" s="30">
+      <c r="B84" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C84" s="33">
+      <c r="C84" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="29">
+      <c r="A85" s="27">
         <v>46124</v>
       </c>
-      <c r="B85" s="30">
+      <c r="B85" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C85" s="33">
+      <c r="C85" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="29">
+      <c r="A86" s="27">
         <v>46125</v>
       </c>
-      <c r="B86" s="30">
+      <c r="B86" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C86" s="33">
+      <c r="C86" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="29">
+      <c r="A87" s="27">
         <v>46126</v>
       </c>
-      <c r="B87" s="30">
+      <c r="B87" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C87" s="33">
+      <c r="C87" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="29">
+      <c r="A88" s="27">
         <v>46127</v>
       </c>
-      <c r="B88" s="30">
+      <c r="B88" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C88" s="33">
+      <c r="C88" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="29">
+      <c r="A89" s="27">
         <v>46128</v>
       </c>
-      <c r="B89" s="30">
+      <c r="B89" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C89" s="33">
+      <c r="C89" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29">
+      <c r="A90" s="27">
         <v>46129</v>
       </c>
-      <c r="B90" s="30">
+      <c r="B90" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C90" s="33">
+      <c r="C90" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29">
+      <c r="A91" s="27">
         <v>46130</v>
       </c>
-      <c r="B91" s="30">
+      <c r="B91" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C91" s="33">
+      <c r="C91" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="29">
+      <c r="A92" s="27">
         <v>46131</v>
       </c>
-      <c r="B92" s="30">
+      <c r="B92" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C92" s="33">
+      <c r="C92" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29">
+      <c r="A93" s="27">
         <v>46132</v>
       </c>
-      <c r="B93" s="30">
+      <c r="B93" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C93" s="33">
+      <c r="C93" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="29">
+      <c r="A94" s="27">
         <v>46133</v>
       </c>
-      <c r="B94" s="30">
+      <c r="B94" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C94" s="33">
+      <c r="C94" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29">
+      <c r="A95" s="27">
         <v>46134</v>
       </c>
-      <c r="B95" s="30">
+      <c r="B95" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
-      <c r="C95" s="33">
+      <c r="C95" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="29">
+      <c r="A96" s="27">
         <v>46135</v>
       </c>
-      <c r="B96" s="30">
+      <c r="B96" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="C96" s="33">
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="C96" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
-        <v>0.041666666666666664</v>
+        <v>4.1666666666666664e-002</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29">
+      <c r="A97" s="27">
         <v>46136</v>
       </c>
-      <c r="B97" s="30">
+      <c r="B97" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C97" s="33">
+      <c r="C97" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="29">
+      <c r="A98" s="27">
         <v>46137</v>
       </c>
-      <c r="B98" s="30">
+      <c r="B98" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C98" s="33">
+      <c r="C98" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="29">
+      <c r="A99" s="27">
         <v>46138</v>
       </c>
-      <c r="B99" s="30">
+      <c r="B99" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C99" s="33">
+      <c r="C99" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="29">
+      <c r="A100" s="27">
         <v>46139</v>
       </c>
-      <c r="B100" s="30">
+      <c r="B100" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C100" s="33">
+      <c r="C100" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="29">
+      <c r="A101" s="27">
         <v>46140</v>
       </c>
-      <c r="B101" s="30">
+      <c r="B101" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
-      <c r="C101" s="33">
+      <c r="C101" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="29">
+      <c r="A102" s="27">
         <v>46141</v>
       </c>
-      <c r="B102" s="30">
+      <c r="B102" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C102" s="33">
+      <c r="C102" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="29">
+      <c r="A103" s="27">
         <v>46142</v>
       </c>
-      <c r="B103" s="30">
+      <c r="B103" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C103" s="33">
+      <c r="C103" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="29">
+      <c r="A104" s="27">
         <v>46143</v>
       </c>
-      <c r="B104" s="30">
+      <c r="B104" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C104" s="33">
+      <c r="C104" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="29">
+      <c r="A105" s="27">
         <v>46144</v>
       </c>
-      <c r="B105" s="30">
+      <c r="B105" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C105" s="33">
+      <c r="C105" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="29">
+      <c r="A106" s="27">
         <v>46145</v>
       </c>
-      <c r="B106" s="30">
+      <c r="B106" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C106" s="33">
+      <c r="C106" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="29">
+      <c r="A107" s="27">
         <v>46146</v>
       </c>
-      <c r="B107" s="30">
+      <c r="B107" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C107" s="33">
+      <c r="C107" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="29">
+      <c r="A108" s="27">
         <v>46147</v>
       </c>
-      <c r="B108" s="30">
+      <c r="B108" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C108" s="33">
+      <c r="C108" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="29">
+      <c r="A109" s="27">
         <v>46148</v>
       </c>
-      <c r="B109" s="30">
+      <c r="B109" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C109" s="33">
+      <c r="C109" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="29">
+      <c r="A110" s="27">
         <v>46149</v>
       </c>
-      <c r="B110" s="30">
+      <c r="B110" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C110" s="33">
+      <c r="C110" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="29">
+      <c r="A111" s="27">
         <v>46150</v>
       </c>
-      <c r="B111" s="30">
+      <c r="B111" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C111" s="33">
+      <c r="C111" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="29">
+      <c r="A112" s="27">
         <v>46151</v>
       </c>
-      <c r="B112" s="30">
+      <c r="B112" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C112" s="33">
+      <c r="C112" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="29">
+      <c r="A113" s="27">
         <v>46152</v>
       </c>
-      <c r="B113" s="30">
+      <c r="B113" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C113" s="33">
+      <c r="C113" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="29">
+      <c r="A114" s="27">
         <v>46153</v>
       </c>
-      <c r="B114" s="30">
+      <c r="B114" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C114" s="33">
+      <c r="C114" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="29">
+      <c r="A115" s="27">
         <v>46154</v>
       </c>
-      <c r="B115" s="30">
+      <c r="B115" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C115" s="33">
+      <c r="C115" s="31">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="29">
+      <c r="A116" s="27">
         <v>46155</v>
       </c>
-      <c r="B116" s="30">
+      <c r="B116" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A116,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C116" s="33"/>
+      <c r="C116" s="31"/>
     </row>
     <row r="117">
-      <c r="A117" s="29">
+      <c r="A117" s="27">
         <v>46156</v>
       </c>
-      <c r="B117" s="30">
+      <c r="B117" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A117,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C117" s="33"/>
+      <c r="C117" s="31"/>
     </row>
     <row r="118">
-      <c r="A118" s="29">
+      <c r="A118" s="27">
         <v>46157</v>
       </c>
-      <c r="B118" s="30">
+      <c r="B118" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A118,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C118" s="33"/>
+      <c r="C118" s="31"/>
     </row>
     <row r="119">
-      <c r="A119" s="29">
+      <c r="A119" s="27">
         <v>46158</v>
       </c>
-      <c r="B119" s="30">
+      <c r="B119" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A119,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C119" s="33"/>
+      <c r="C119" s="31"/>
     </row>
     <row r="120">
-      <c r="A120" s="29">
+      <c r="A120" s="27">
         <v>46159</v>
       </c>
-      <c r="B120" s="30">
+      <c r="B120" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A120,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C120" s="33"/>
+      <c r="C120" s="31"/>
     </row>
     <row r="121">
-      <c r="A121" s="29">
+      <c r="A121" s="27">
         <v>46160</v>
       </c>
-      <c r="B121" s="30">
+      <c r="B121" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A121,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C121" s="33"/>
+      <c r="C121" s="31"/>
     </row>
     <row r="122">
-      <c r="A122" s="29">
+      <c r="A122" s="27">
         <v>46161</v>
       </c>
-      <c r="B122" s="30">
+      <c r="B122" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A122,Journal[Temps])</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="C122" s="33"/>
+      <c r="C122" s="31"/>
     </row>
     <row r="123">
-      <c r="A123" s="29">
+      <c r="A123" s="27">
         <v>46162</v>
       </c>
-      <c r="B123" s="30">
+      <c r="B123" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A123,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C123" s="33"/>
+      <c r="C123" s="31"/>
     </row>
     <row r="124">
-      <c r="A124" s="29">
+      <c r="A124" s="27">
         <v>46163</v>
       </c>
-      <c r="B124" s="30">
+      <c r="B124" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A124,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C124" s="33"/>
+      <c r="C124" s="31"/>
     </row>
     <row r="125">
-      <c r="A125" s="29">
+      <c r="A125" s="27">
         <v>46164</v>
       </c>
-      <c r="B125" s="30">
+      <c r="B125" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A125,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C125" s="33"/>
+      <c r="C125" s="31"/>
     </row>
     <row r="126">
-      <c r="A126" s="29">
+      <c r="A126" s="27">
         <v>46165</v>
       </c>
-      <c r="B126" s="30">
+      <c r="B126" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A126,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C126" s="33"/>
+      <c r="C126" s="31"/>
     </row>
     <row r="127">
-      <c r="A127" s="29">
+      <c r="A127" s="27">
         <v>46166</v>
       </c>
-      <c r="B127" s="30">
+      <c r="B127" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A127,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C127" s="33"/>
+      <c r="C127" s="31"/>
     </row>
     <row r="128">
-      <c r="A128" s="29">
+      <c r="A128" s="27">
         <v>46167</v>
       </c>
-      <c r="B128" s="30">
+      <c r="B128" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A128,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C128" s="33"/>
+      <c r="C128" s="31"/>
     </row>
     <row r="129">
-      <c r="A129" s="29">
+      <c r="A129" s="27">
         <v>46168</v>
       </c>
-      <c r="B129" s="30">
+      <c r="B129" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A129,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C129" s="33"/>
+      <c r="C129" s="31"/>
     </row>
     <row r="130">
-      <c r="A130" s="29">
+      <c r="A130" s="27">
         <v>46169</v>
       </c>
-      <c r="B130" s="30">
+      <c r="B130" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A130,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C130" s="33"/>
+      <c r="C130" s="31"/>
     </row>
     <row r="131">
-      <c r="A131" s="29">
+      <c r="A131" s="27">
         <v>46170</v>
       </c>
-      <c r="B131" s="30">
+      <c r="B131" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A131,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C131" s="33"/>
+      <c r="C131" s="31"/>
     </row>
     <row r="132">
-      <c r="A132" s="29">
+      <c r="A132" s="27">
         <v>46171</v>
       </c>
-      <c r="B132" s="30">
+      <c r="B132" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A132,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C132" s="33"/>
+      <c r="C132" s="31"/>
     </row>
     <row r="133">
-      <c r="A133" s="29">
+      <c r="A133" s="27">
         <v>46172</v>
       </c>
-      <c r="B133" s="30">
+      <c r="B133" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A133,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C133" s="33"/>
+      <c r="C133" s="31"/>
     </row>
     <row r="134">
-      <c r="A134" s="29">
+      <c r="A134" s="27">
         <v>46173</v>
       </c>
-      <c r="B134" s="30">
+      <c r="B134" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A134,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C134" s="33"/>
+      <c r="C134" s="31"/>
     </row>
     <row r="135">
-      <c r="A135" s="29">
+      <c r="A135" s="27">
         <v>46174</v>
       </c>
-      <c r="B135" s="30">
+      <c r="B135" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A135,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C135" s="33"/>
+      <c r="C135" s="31"/>
     </row>
     <row r="136">
-      <c r="A136" s="29">
+      <c r="A136" s="27">
         <v>46175</v>
       </c>
-      <c r="B136" s="30">
+      <c r="B136" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A136,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C136" s="33"/>
+      <c r="C136" s="31"/>
     </row>
     <row r="137">
-      <c r="A137" s="29">
+      <c r="A137" s="27">
         <v>46176</v>
       </c>
-      <c r="B137" s="30">
+      <c r="B137" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A137,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C137" s="33"/>
+      <c r="C137" s="31"/>
     </row>
     <row r="138">
-      <c r="A138" s="29">
+      <c r="A138" s="27">
         <v>46177</v>
       </c>
-      <c r="B138" s="30">
+      <c r="B138" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A138,Journal[Temps])</f>
         <v>0.2986111111111111</v>
       </c>
-      <c r="C138" s="33"/>
+      <c r="C138" s="31"/>
     </row>
     <row r="139">
-      <c r="A139" s="29">
+      <c r="A139" s="27">
         <v>46178</v>
       </c>
-      <c r="B139" s="30">
+      <c r="B139" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A139,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C139" s="33"/>
+      <c r="C139" s="31"/>
     </row>
     <row r="140">
-      <c r="A140" s="29">
+      <c r="A140" s="27">
         <v>46179</v>
       </c>
-      <c r="B140" s="30">
+      <c r="B140" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A140,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C140" s="33"/>
+      <c r="C140" s="31"/>
     </row>
     <row r="141">
-      <c r="A141" s="29">
+      <c r="A141" s="27">
         <v>46180</v>
       </c>
-      <c r="B141" s="30">
+      <c r="B141" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A141,Journal[Temps])</f>
-        <v>0.041666666666666664</v>
-      </c>
-      <c r="C141" s="33"/>
+        <v>4.1666666666666664e-002</v>
+      </c>
+      <c r="C141" s="31"/>
     </row>
     <row r="142">
-      <c r="A142" s="29">
+      <c r="A142" s="27">
         <v>46181</v>
       </c>
-      <c r="B142" s="30">
+      <c r="B142" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A142,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C142" s="33"/>
+      <c r="C142" s="31"/>
     </row>
     <row r="143">
-      <c r="A143" s="29">
+      <c r="A143" s="27">
         <v>46182</v>
       </c>
-      <c r="B143" s="30">
+      <c r="B143" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A143,Journal[Temps])</f>
-        <v>0.09375</v>
-      </c>
-      <c r="C143" s="33"/>
+        <v>0.15625000000000003</v>
+      </c>
+      <c r="C143" s="31"/>
     </row>
     <row r="144">
-      <c r="A144" s="29">
+      <c r="A144" s="27">
         <v>46183</v>
       </c>
-      <c r="B144" s="30">
+      <c r="B144" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A144,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C144" s="33"/>
+      <c r="C144" s="31"/>
     </row>
     <row r="145">
-      <c r="A145" s="29">
+      <c r="A145" s="27">
         <v>46184</v>
       </c>
-      <c r="B145" s="30">
+      <c r="B145" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A145,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C145" s="33"/>
+      <c r="C145" s="31"/>
     </row>
     <row r="146">
-      <c r="A146" s="29">
+      <c r="A146" s="27">
         <v>46185</v>
       </c>
-      <c r="B146" s="30">
+      <c r="B146" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A146,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C146" s="33"/>
+      <c r="C146" s="31"/>
     </row>
     <row r="147">
-      <c r="A147" s="29">
+      <c r="A147" s="27">
         <v>46186</v>
       </c>
-      <c r="B147" s="30">
+      <c r="B147" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A147,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C147" s="33"/>
+      <c r="C147" s="31"/>
     </row>
     <row r="148">
-      <c r="A148" s="29">
+      <c r="A148" s="27">
         <v>46187</v>
       </c>
-      <c r="B148" s="30">
+      <c r="B148" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A148,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C148" s="33"/>
+      <c r="C148" s="31"/>
     </row>
     <row r="149">
-      <c r="A149" s="29">
+      <c r="A149" s="27">
         <v>46188</v>
       </c>
-      <c r="B149" s="30">
+      <c r="B149" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A149,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C149" s="33"/>
+      <c r="C149" s="31"/>
     </row>
     <row r="150">
-      <c r="A150" s="29">
+      <c r="A150" s="27">
         <v>46189</v>
       </c>
-      <c r="B150" s="30">
+      <c r="B150" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A150,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C150" s="33"/>
+      <c r="C150" s="31"/>
     </row>
     <row r="151">
-      <c r="A151" s="29">
+      <c r="A151" s="27">
         <v>46190</v>
       </c>
-      <c r="B151" s="30">
+      <c r="B151" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A151,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C151" s="33"/>
+      <c r="C151" s="31"/>
     </row>
     <row r="152">
-      <c r="A152" s="29">
+      <c r="A152" s="27">
         <v>46191</v>
       </c>
-      <c r="B152" s="30">
+      <c r="B152" s="28">
         <f>SUMIF(Journal[date],SommeParJours!A152,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C152" s="33"/>
+      <c r="C152" s="31"/>
     </row>
     <row r="153">
-      <c r="A153" s="29"/>
-      <c r="B153" s="34"/>
-      <c r="C153" s="33"/>
+      <c r="A153" s="27"/>
+      <c r="B153" s="32"/>
+      <c r="C153" s="31"/>
     </row>
     <row r="154">
-      <c r="A154" s="29"/>
-      <c r="B154" s="34"/>
-      <c r="C154" s="33"/>
+      <c r="A154" s="27"/>
+      <c r="B154" s="32"/>
+      <c r="C154" s="31"/>
     </row>
     <row r="155">
-      <c r="A155" s="29"/>
-      <c r="B155" s="34"/>
-      <c r="C155" s="33"/>
+      <c r="A155" s="27"/>
+      <c r="B155" s="32"/>
+      <c r="C155" s="31"/>
     </row>
     <row r="156">
-      <c r="A156" s="29"/>
-      <c r="B156" s="34"/>
-      <c r="C156" s="33"/>
+      <c r="A156" s="27"/>
+      <c r="B156" s="32"/>
+      <c r="C156" s="31"/>
     </row>
     <row r="157">
-      <c r="A157" s="29"/>
-      <c r="B157" s="34"/>
-      <c r="C157" s="33"/>
+      <c r="A157" s="27"/>
+      <c r="B157" s="32"/>
+      <c r="C157" s="31"/>
     </row>
     <row r="158">
-      <c r="A158" s="29"/>
-      <c r="B158" s="34"/>
-      <c r="C158" s="33"/>
+      <c r="A158" s="27"/>
+      <c r="B158" s="32"/>
+      <c r="C158" s="31"/>
     </row>
     <row r="159">
-      <c r="A159" s="29"/>
-      <c r="B159" s="34"/>
-      <c r="C159" s="33"/>
+      <c r="A159" s="27"/>
+      <c r="B159" s="32"/>
+      <c r="C159" s="31"/>
     </row>
     <row r="160">
-      <c r="A160" s="29"/>
-      <c r="B160" s="34"/>
+      <c r="A160" s="27"/>
+      <c r="B160" s="32"/>
     </row>
     <row r="161">
-      <c r="A161" s="29"/>
-      <c r="B161" s="34"/>
+      <c r="A161" s="27"/>
+      <c r="B161" s="32"/>
     </row>
     <row r="162">
-      <c r="A162" s="29"/>
-      <c r="B162" s="34"/>
+      <c r="A162" s="27"/>
+      <c r="B162" s="32"/>
     </row>
     <row r="163">
-      <c r="A163" s="29"/>
-      <c r="B163" s="34"/>
+      <c r="A163" s="27"/>
+      <c r="B163" s="32"/>
     </row>
     <row r="164">
-      <c r="A164" s="29"/>
-      <c r="B164" s="34"/>
+      <c r="A164" s="27"/>
+      <c r="B164" s="32"/>
     </row>
     <row r="165">
-      <c r="A165" s="29"/>
-      <c r="B165" s="34"/>
+      <c r="A165" s="27"/>
+      <c r="B165" s="32"/>
     </row>
     <row r="166">
-      <c r="A166" s="29"/>
-      <c r="B166" s="34"/>
+      <c r="A166" s="27"/>
+      <c r="B166" s="32"/>
     </row>
     <row r="167">
-      <c r="A167" s="29"/>
-      <c r="B167" s="34"/>
+      <c r="A167" s="27"/>
+      <c r="B167" s="32"/>
     </row>
     <row r="168">
-      <c r="A168" s="29"/>
-      <c r="B168" s="34"/>
+      <c r="A168" s="27"/>
+      <c r="B168" s="32"/>
     </row>
     <row r="169">
-      <c r="A169" s="29"/>
-      <c r="B169" s="34"/>
+      <c r="A169" s="27"/>
+      <c r="B169" s="32"/>
     </row>
     <row r="170">
-      <c r="A170" s="29"/>
-      <c r="B170" s="34"/>
+      <c r="A170" s="27"/>
+      <c r="B170" s="32"/>
     </row>
     <row r="171">
-      <c r="A171" s="29"/>
-      <c r="B171" s="34"/>
+      <c r="A171" s="27"/>
+      <c r="B171" s="32"/>
     </row>
     <row r="172">
-      <c r="A172" s="29"/>
-      <c r="B172" s="34"/>
+      <c r="A172" s="27"/>
+      <c r="B172" s="32"/>
     </row>
     <row r="173">
-      <c r="A173" s="29"/>
-      <c r="B173" s="34"/>
+      <c r="A173" s="27"/>
+      <c r="B173" s="32"/>
     </row>
     <row r="174">
-      <c r="A174" s="29"/>
-      <c r="B174" s="34"/>
+      <c r="A174" s="27"/>
+      <c r="B174" s="32"/>
     </row>
     <row r="175">
-      <c r="A175" s="29"/>
-      <c r="B175" s="34"/>
+      <c r="A175" s="27"/>
+      <c r="B175" s="32"/>
     </row>
     <row r="176">
-      <c r="A176" s="29"/>
-      <c r="B176" s="34"/>
+      <c r="A176" s="27"/>
+      <c r="B176" s="32"/>
     </row>
     <row r="177">
-      <c r="A177" s="29"/>
-      <c r="B177" s="34"/>
+      <c r="A177" s="27"/>
+      <c r="B177" s="32"/>
     </row>
     <row r="178">
-      <c r="A178" s="29"/>
-      <c r="B178" s="34"/>
+      <c r="A178" s="27"/>
+      <c r="B178" s="32"/>
     </row>
     <row r="179">
-      <c r="A179" s="29"/>
-      <c r="B179" s="34"/>
+      <c r="A179" s="27"/>
+      <c r="B179" s="32"/>
     </row>
     <row r="180">
-      <c r="A180" s="29"/>
-      <c r="B180" s="34"/>
+      <c r="A180" s="27"/>
+      <c r="B180" s="32"/>
     </row>
     <row r="181">
-      <c r="A181" s="29"/>
-      <c r="B181" s="34"/>
+      <c r="A181" s="27"/>
+      <c r="B181" s="32"/>
     </row>
     <row r="182">
-      <c r="A182" s="29"/>
-      <c r="B182" s="34"/>
+      <c r="A182" s="27"/>
+      <c r="B182" s="32"/>
     </row>
     <row r="183">
-      <c r="A183" s="29"/>
-      <c r="B183" s="34"/>
+      <c r="A183" s="27"/>
+      <c r="B183" s="32"/>
     </row>
     <row r="184">
-      <c r="A184" s="29"/>
-      <c r="B184" s="34"/>
+      <c r="A184" s="27"/>
+      <c r="B184" s="32"/>
     </row>
     <row r="185">
-      <c r="A185" s="29"/>
-      <c r="B185" s="34"/>
+      <c r="A185" s="27"/>
+      <c r="B185" s="32"/>
     </row>
     <row r="186">
-      <c r="A186" s="29"/>
-      <c r="B186" s="34"/>
+      <c r="A186" s="27"/>
+      <c r="B186" s="32"/>
     </row>
     <row r="187">
-      <c r="A187" s="29"/>
-      <c r="B187" s="34"/>
+      <c r="A187" s="27"/>
+      <c r="B187" s="32"/>
     </row>
     <row r="188">
-      <c r="A188" s="34"/>
-      <c r="B188" s="34"/>
+      <c r="A188" s="32"/>
+      <c r="B188" s="32"/>
     </row>
     <row r="189">
-      <c r="A189" s="34"/>
-      <c r="B189" s="34"/>
+      <c r="A189" s="32"/>
+      <c r="B189" s="32"/>
     </row>
     <row r="190">
-      <c r="A190" s="34"/>
-      <c r="B190" s="34"/>
+      <c r="A190" s="32"/>
+      <c r="B190" s="32"/>
     </row>
     <row r="191">
-      <c r="A191" s="34"/>
-      <c r="B191" s="34"/>
+      <c r="A191" s="32"/>
+      <c r="B191" s="32"/>
     </row>
     <row r="192">
-      <c r="A192" s="34"/>
-      <c r="B192" s="34"/>
+      <c r="A192" s="32"/>
+      <c r="B192" s="32"/>
     </row>
     <row r="193">
-      <c r="A193" s="34"/>
-      <c r="B193" s="34"/>
+      <c r="A193" s="32"/>
+      <c r="B193" s="32"/>
     </row>
     <row r="194">
-      <c r="A194" s="34"/>
-      <c r="B194" s="34"/>
+      <c r="A194" s="32"/>
+      <c r="B194" s="32"/>
     </row>
     <row r="195">
-      <c r="A195" s="34"/>
-      <c r="B195" s="34"/>
+      <c r="A195" s="32"/>
+      <c r="B195" s="32"/>
     </row>
     <row r="196">
-      <c r="A196" s="34"/>
-      <c r="B196" s="34"/>
+      <c r="A196" s="32"/>
+      <c r="B196" s="32"/>
     </row>
     <row r="197">
-      <c r="A197" s="34"/>
-      <c r="B197" s="34"/>
+      <c r="A197" s="32"/>
+      <c r="B197" s="32"/>
     </row>
     <row r="198">
-      <c r="A198" s="34"/>
-      <c r="B198" s="34"/>
+      <c r="A198" s="32"/>
+      <c r="B198" s="32"/>
     </row>
     <row r="199">
-      <c r="A199" s="34"/>
-      <c r="B199" s="34"/>
+      <c r="A199" s="32"/>
+      <c r="B199" s="32"/>
     </row>
     <row r="200">
-      <c r="A200" s="34"/>
-      <c r="B200" s="34"/>
+      <c r="A200" s="32"/>
+      <c r="B200" s="32"/>
     </row>
     <row r="201">
-      <c r="A201" s="34"/>
-      <c r="B201" s="34"/>
+      <c r="A201" s="32"/>
+      <c r="B201" s="32"/>
     </row>
     <row r="202">
-      <c r="A202" s="34"/>
-      <c r="B202" s="34"/>
+      <c r="A202" s="32"/>
+      <c r="B202" s="32"/>
     </row>
     <row r="203">
-      <c r="A203" s="34"/>
-      <c r="B203" s="34"/>
+      <c r="A203" s="32"/>
+      <c r="B203" s="32"/>
     </row>
     <row r="204">
-      <c r="A204" s="34"/>
-      <c r="B204" s="34"/>
+      <c r="A204" s="32"/>
+      <c r="B204" s="32"/>
     </row>
     <row r="205">
-      <c r="A205" s="34"/>
-      <c r="B205" s="34"/>
+      <c r="A205" s="32"/>
+      <c r="B205" s="32"/>
     </row>
     <row r="206">
-      <c r="A206" s="34"/>
-      <c r="B206" s="34"/>
+      <c r="A206" s="32"/>
+      <c r="B206" s="32"/>
     </row>
     <row r="207">
-      <c r="A207" s="34"/>
-      <c r="B207" s="34"/>
+      <c r="A207" s="32"/>
+      <c r="B207" s="32"/>
     </row>
     <row r="208">
-      <c r="A208" s="34"/>
-      <c r="B208" s="34"/>
+      <c r="A208" s="32"/>
+      <c r="B208" s="32"/>
     </row>
     <row r="209">
-      <c r="A209" s="34"/>
-      <c r="B209" s="34"/>
+      <c r="A209" s="32"/>
+      <c r="B209" s="32"/>
     </row>
     <row r="210">
-      <c r="A210" s="34"/>
-      <c r="B210" s="34"/>
+      <c r="A210" s="32"/>
+      <c r="B210" s="32"/>
     </row>
     <row r="211">
-      <c r="A211" s="34"/>
-      <c r="B211" s="34"/>
+      <c r="A211" s="32"/>
+      <c r="B211" s="32"/>
     </row>
     <row r="212">
-      <c r="A212" s="34"/>
-      <c r="B212" s="34"/>
+      <c r="A212" s="32"/>
+      <c r="B212" s="32"/>
     </row>
     <row r="213">
-      <c r="A213" s="34"/>
-      <c r="B213" s="34"/>
+      <c r="A213" s="32"/>
+      <c r="B213" s="32"/>
     </row>
     <row r="214">
-      <c r="A214" s="34"/>
-      <c r="B214" s="34"/>
+      <c r="A214" s="32"/>
+      <c r="B214" s="32"/>
     </row>
     <row r="215">
-      <c r="A215" s="34"/>
-      <c r="B215" s="34"/>
+      <c r="A215" s="32"/>
+      <c r="B215" s="32"/>
     </row>
     <row r="216">
-      <c r="A216" s="34"/>
-      <c r="B216" s="34"/>
+      <c r="A216" s="32"/>
+      <c r="B216" s="32"/>
     </row>
     <row r="217">
-      <c r="A217" s="34"/>
-      <c r="B217" s="34"/>
+      <c r="A217" s="32"/>
+      <c r="B217" s="32"/>
     </row>
     <row r="218">
-      <c r="A218" s="34"/>
-      <c r="B218" s="34"/>
+      <c r="A218" s="32"/>
+      <c r="B218" s="32"/>
     </row>
     <row r="219">
-      <c r="A219" s="34"/>
-      <c r="B219" s="34"/>
+      <c r="A219" s="32"/>
+      <c r="B219" s="32"/>
     </row>
     <row r="220">
-      <c r="A220" s="34"/>
-      <c r="B220" s="34"/>
+      <c r="A220" s="32"/>
+      <c r="B220" s="32"/>
     </row>
     <row r="221">
-      <c r="A221" s="34"/>
-      <c r="B221" s="34"/>
+      <c r="A221" s="32"/>
+      <c r="B221" s="32"/>
     </row>
     <row r="222">
-      <c r="A222" s="34"/>
-      <c r="B222" s="34"/>
+      <c r="A222" s="32"/>
+      <c r="B222" s="32"/>
     </row>
     <row r="223">
-      <c r="A223" s="34"/>
-      <c r="B223" s="34"/>
+      <c r="A223" s="32"/>
+      <c r="B223" s="32"/>
     </row>
     <row r="224">
-      <c r="A224" s="34"/>
-      <c r="B224" s="34"/>
+      <c r="A224" s="32"/>
+      <c r="B224" s="32"/>
     </row>
     <row r="225">
-      <c r="A225" s="34"/>
-      <c r="B225" s="34"/>
+      <c r="A225" s="32"/>
+      <c r="B225" s="32"/>
     </row>
     <row r="226">
-      <c r="A226" s="34"/>
-      <c r="B226" s="34"/>
+      <c r="A226" s="32"/>
+      <c r="B226" s="32"/>
     </row>
     <row r="227">
-      <c r="A227" s="34"/>
-      <c r="B227" s="34"/>
+      <c r="A227" s="32"/>
+      <c r="B227" s="32"/>
     </row>
     <row r="228">
-      <c r="A228" s="34"/>
-      <c r="B228" s="34"/>
+      <c r="A228" s="32"/>
+      <c r="B228" s="32"/>
     </row>
     <row r="229">
-      <c r="A229" s="34"/>
-      <c r="B229" s="34"/>
+      <c r="A229" s="32"/>
+      <c r="B229" s="32"/>
     </row>
     <row r="230">
-      <c r="A230" s="34"/>
-      <c r="B230" s="34"/>
+      <c r="A230" s="32"/>
+      <c r="B230" s="32"/>
     </row>
     <row r="231">
-      <c r="A231" s="34"/>
-      <c r="B231" s="34"/>
+      <c r="A231" s="32"/>
+      <c r="B231" s="32"/>
     </row>
     <row r="232">
-      <c r="A232" s="34"/>
-      <c r="B232" s="34"/>
+      <c r="A232" s="32"/>
+      <c r="B232" s="32"/>
     </row>
     <row r="233">
-      <c r="A233" s="34"/>
-      <c r="B233" s="34"/>
+      <c r="A233" s="32"/>
+      <c r="B233" s="32"/>
     </row>
     <row r="234">
-      <c r="A234" s="34"/>
-      <c r="B234" s="34"/>
+      <c r="A234" s="32"/>
+      <c r="B234" s="32"/>
     </row>
     <row r="235">
-      <c r="A235" s="34"/>
-      <c r="B235" s="34"/>
+      <c r="A235" s="32"/>
+      <c r="B235" s="32"/>
     </row>
     <row r="236">
-      <c r="A236" s="34"/>
-      <c r="B236" s="34"/>
+      <c r="A236" s="32"/>
+      <c r="B236" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8995,2034 +9011,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="35" width="6"/>
+    <col customWidth="1" min="12" max="12" style="33" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="35" width="6"/>
+    <col customWidth="1" min="23" max="23" style="33" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="35" width="6"/>
+    <col customWidth="1" min="30" max="30" style="33" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="36" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="39" t="s">
+    <row r="1" s="34" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="F1" s="40" t="s">
+      <c r="E1" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="I1" s="39" t="s">
+      <c r="H1" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="L1" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="M1" s="39" t="s">
+      <c r="K1" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="N1" s="41" t="s">
+      <c r="L1" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="M1" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="N1" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="P1" s="39" t="s">
+      <c r="O1" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="P1" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="R1" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="S1" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="T1" s="39" t="s">
+      <c r="Q1" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="R1" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="U1" s="39" t="s">
+      <c r="S1" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="V1" s="41" t="s">
+      <c r="T1" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="W1" s="44" t="s">
+      <c r="U1" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="X1" s="39" t="s">
+      <c r="V1" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="Y1" s="39" t="s">
+      <c r="W1" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="Z1" s="41" t="s">
+      <c r="X1" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="AA1" s="45" t="s">
+      <c r="Y1" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="AB1" s="46" t="s">
+      <c r="Z1" s="39" t="s">
         <v>133</v>
       </c>
-      <c r="AC1" s="46" t="s">
+      <c r="AA1" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="AD1" s="43" t="s">
+      <c r="AB1" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="AE1" s="47" t="s">
+      <c r="AC1" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="AF1" s="48" t="s">
+      <c r="AD1" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="AG1" s="49" t="s">
+      <c r="AE1" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF1" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG1" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="AH1" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="AI1" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="AJ1" s="49" t="s">
+      <c r="AH1" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="AK1" s="46" t="s">
+      <c r="AI1" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="AL1" s="50"/>
-      <c r="AM1" s="50"/>
-      <c r="AN1" s="50"/>
-      <c r="AO1" s="50"/>
-      <c r="AP1" s="50"/>
-      <c r="AQ1" s="50"/>
-      <c r="AR1" s="50"/>
-      <c r="AS1" s="50"/>
-      <c r="AT1" s="50"/>
-      <c r="AU1" s="50"/>
+      <c r="AJ1" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="AK1" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="AL1" s="48"/>
+      <c r="AM1" s="48"/>
+      <c r="AN1" s="48"/>
+      <c r="AO1" s="48"/>
+      <c r="AP1" s="48"/>
+      <c r="AQ1" s="48"/>
+      <c r="AR1" s="48"/>
+      <c r="AS1" s="48"/>
+      <c r="AT1" s="48"/>
+      <c r="AU1" s="48"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="53"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="60"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="58"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="53"/>
-      <c r="AC2" s="53"/>
-      <c r="AD2" s="57"/>
-      <c r="AE2" s="58"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="53"/>
-      <c r="AH2" s="53"/>
-      <c r="AI2" s="53"/>
-      <c r="AJ2" s="53"/>
-      <c r="AK2" s="53"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="58"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="57"/>
+      <c r="AB2" s="51"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="56"/>
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="51"/>
+      <c r="AH2" s="51"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="51"/>
+      <c r="AK2" s="51"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="51"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="53"/>
-      <c r="Q3" s="53"/>
-      <c r="R3" s="53"/>
-      <c r="S3" s="53"/>
-      <c r="T3" s="53"/>
-      <c r="U3" s="53"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="53"/>
-      <c r="Y3" s="53"/>
-      <c r="Z3" s="58"/>
-      <c r="AA3" s="59"/>
-      <c r="AB3" s="53"/>
-      <c r="AC3" s="53"/>
-      <c r="AD3" s="57"/>
-      <c r="AE3" s="58"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="53"/>
-      <c r="AH3" s="53"/>
-      <c r="AI3" s="53"/>
-      <c r="AJ3" s="53"/>
-      <c r="AK3" s="53"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="60"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="V3" s="56"/>
+      <c r="W3" s="58"/>
+      <c r="X3" s="51"/>
+      <c r="Y3" s="51"/>
+      <c r="Z3" s="56"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="51"/>
+      <c r="AC3" s="51"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="56"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="51"/>
+      <c r="AH3" s="51"/>
+      <c r="AI3" s="51"/>
+      <c r="AJ3" s="51"/>
+      <c r="AK3" s="51"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="51"/>
-      <c r="C4" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="57"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="53"/>
-      <c r="R4" s="53"/>
-      <c r="S4" s="53"/>
-      <c r="T4" s="53"/>
-      <c r="U4" s="53"/>
-      <c r="V4" s="58"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="53"/>
-      <c r="Y4" s="53"/>
-      <c r="Z4" s="58"/>
-      <c r="AA4" s="59"/>
-      <c r="AB4" s="53"/>
-      <c r="AC4" s="53"/>
-      <c r="AD4" s="57"/>
-      <c r="AE4" s="58"/>
-      <c r="AF4" s="59"/>
-      <c r="AG4" s="53"/>
-      <c r="AH4" s="53"/>
-      <c r="AI4" s="53"/>
-      <c r="AJ4" s="53"/>
-      <c r="AK4" s="53"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="57"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="56"/>
+      <c r="W4" s="58"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="57"/>
+      <c r="AB4" s="51"/>
+      <c r="AC4" s="51"/>
+      <c r="AD4" s="55"/>
+      <c r="AE4" s="56"/>
+      <c r="AF4" s="57"/>
+      <c r="AG4" s="51"/>
+      <c r="AH4" s="51"/>
+      <c r="AI4" s="51"/>
+      <c r="AJ4" s="51"/>
+      <c r="AK4" s="51"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="51"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="53"/>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="53"/>
-      <c r="T5" s="53"/>
-      <c r="U5" s="53"/>
-      <c r="V5" s="58"/>
-      <c r="W5" s="60"/>
-      <c r="X5" s="53"/>
-      <c r="Y5" s="53"/>
-      <c r="Z5" s="58"/>
-      <c r="AA5" s="59"/>
-      <c r="AB5" s="53"/>
-      <c r="AC5" s="53"/>
-      <c r="AD5" s="57"/>
-      <c r="AE5" s="58"/>
-      <c r="AF5" s="59"/>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="53"/>
-      <c r="AK5" s="53"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="51"/>
+      <c r="R5" s="51"/>
+      <c r="S5" s="51"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="51"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="58"/>
+      <c r="X5" s="51"/>
+      <c r="Y5" s="51"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="57"/>
+      <c r="AB5" s="51"/>
+      <c r="AC5" s="51"/>
+      <c r="AD5" s="55"/>
+      <c r="AE5" s="56"/>
+      <c r="AF5" s="57"/>
+      <c r="AG5" s="51"/>
+      <c r="AH5" s="51"/>
+      <c r="AI5" s="51"/>
+      <c r="AJ5" s="51"/>
+      <c r="AK5" s="51"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="51"/>
-      <c r="C6" s="52" t="s">
+      <c r="B6" s="49"/>
+      <c r="C6" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="53"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="53"/>
-      <c r="Q6" s="53"/>
-      <c r="R6" s="53"/>
-      <c r="S6" s="53"/>
-      <c r="T6" s="53"/>
-      <c r="U6" s="53"/>
-      <c r="V6" s="58"/>
-      <c r="W6" s="60"/>
-      <c r="X6" s="53"/>
-      <c r="Y6" s="53"/>
-      <c r="Z6" s="58"/>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="53"/>
-      <c r="AC6" s="53"/>
-      <c r="AD6" s="57"/>
-      <c r="AE6" s="55"/>
-      <c r="AF6" s="56"/>
-      <c r="AG6" s="67"/>
-      <c r="AH6" s="67"/>
-      <c r="AI6" s="67"/>
-      <c r="AJ6" s="67"/>
-      <c r="AK6" s="67"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="51"/>
+      <c r="U6" s="51"/>
+      <c r="V6" s="56"/>
+      <c r="W6" s="58"/>
+      <c r="X6" s="51"/>
+      <c r="Y6" s="51"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="57"/>
+      <c r="AB6" s="51"/>
+      <c r="AC6" s="51"/>
+      <c r="AD6" s="55"/>
+      <c r="AE6" s="53"/>
+      <c r="AF6" s="54"/>
+      <c r="AG6" s="65"/>
+      <c r="AH6" s="65"/>
+      <c r="AI6" s="65"/>
+      <c r="AJ6" s="65"/>
+      <c r="AK6" s="65"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="51"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="65"/>
-      <c r="P7" s="53"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="53"/>
-      <c r="T7" s="53"/>
-      <c r="U7" s="53"/>
-      <c r="V7" s="58"/>
-      <c r="W7" s="60"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="53"/>
-      <c r="Z7" s="58"/>
-      <c r="AA7" s="59"/>
-      <c r="AB7" s="53"/>
-      <c r="AC7" s="53"/>
-      <c r="AD7" s="57"/>
-      <c r="AE7" s="58"/>
-      <c r="AF7" s="59"/>
-      <c r="AG7" s="53"/>
-      <c r="AH7" s="53"/>
-      <c r="AI7" s="53"/>
-      <c r="AJ7" s="53"/>
-      <c r="AK7" s="53"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="51"/>
+      <c r="T7" s="51"/>
+      <c r="U7" s="51"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="58"/>
+      <c r="X7" s="51"/>
+      <c r="Y7" s="51"/>
+      <c r="Z7" s="56"/>
+      <c r="AA7" s="57"/>
+      <c r="AB7" s="51"/>
+      <c r="AC7" s="51"/>
+      <c r="AD7" s="55"/>
+      <c r="AE7" s="56"/>
+      <c r="AF7" s="57"/>
+      <c r="AG7" s="51"/>
+      <c r="AH7" s="51"/>
+      <c r="AI7" s="51"/>
+      <c r="AJ7" s="51"/>
+      <c r="AK7" s="51"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="51"/>
-      <c r="C8" s="52" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="57"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
-      <c r="R8" s="67"/>
-      <c r="S8" s="67"/>
-      <c r="T8" s="67"/>
-      <c r="U8" s="67"/>
-      <c r="V8" s="55"/>
-      <c r="W8" s="60"/>
-      <c r="X8" s="67"/>
-      <c r="Y8" s="67"/>
-      <c r="Z8" s="55"/>
-      <c r="AA8" s="56"/>
-      <c r="AB8" s="67"/>
-      <c r="AC8" s="67"/>
-      <c r="AD8" s="57"/>
-      <c r="AE8" s="55"/>
-      <c r="AF8" s="56"/>
-      <c r="AG8" s="67"/>
-      <c r="AH8" s="67"/>
-      <c r="AI8" s="67"/>
-      <c r="AJ8" s="67"/>
-      <c r="AK8" s="67"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="53"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="53"/>
+      <c r="W8" s="58"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65"/>
+      <c r="Z8" s="53"/>
+      <c r="AA8" s="54"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="55"/>
+      <c r="AE8" s="53"/>
+      <c r="AF8" s="54"/>
+      <c r="AG8" s="65"/>
+      <c r="AH8" s="65"/>
+      <c r="AI8" s="65"/>
+      <c r="AJ8" s="65"/>
+      <c r="AK8" s="65"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="51"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="66"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="66"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="66"/>
-      <c r="N9" s="58"/>
-      <c r="O9" s="65"/>
-      <c r="P9" s="53"/>
-      <c r="Q9" s="66"/>
-      <c r="R9" s="53"/>
-      <c r="S9" s="68"/>
-      <c r="T9" s="53"/>
-      <c r="U9" s="53"/>
-      <c r="V9" s="64"/>
-      <c r="W9" s="60"/>
-      <c r="X9" s="66"/>
-      <c r="Y9" s="53"/>
-      <c r="Z9" s="64"/>
-      <c r="AA9" s="65"/>
-      <c r="AB9" s="53"/>
-      <c r="AC9" s="53"/>
-      <c r="AD9" s="66"/>
-      <c r="AE9" s="58"/>
-      <c r="AF9" s="59"/>
-      <c r="AG9" s="53"/>
-      <c r="AH9" s="53"/>
-      <c r="AI9" s="53"/>
-      <c r="AJ9" s="53"/>
-      <c r="AK9" s="53"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="63"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="64"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="51"/>
+      <c r="U9" s="51"/>
+      <c r="V9" s="62"/>
+      <c r="W9" s="58"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="51"/>
+      <c r="Z9" s="62"/>
+      <c r="AA9" s="63"/>
+      <c r="AB9" s="51"/>
+      <c r="AC9" s="51"/>
+      <c r="AD9" s="64"/>
+      <c r="AE9" s="56"/>
+      <c r="AF9" s="57"/>
+      <c r="AG9" s="51"/>
+      <c r="AH9" s="51"/>
+      <c r="AI9" s="51"/>
+      <c r="AJ9" s="51"/>
+      <c r="AK9" s="51"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="51"/>
-      <c r="C10" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="58"/>
-      <c r="O10" s="59"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="55"/>
-      <c r="W10" s="60"/>
-      <c r="X10" s="67"/>
-      <c r="Y10" s="67"/>
-      <c r="Z10" s="55"/>
-      <c r="AA10" s="59"/>
-      <c r="AB10" s="53"/>
-      <c r="AC10" s="53"/>
-      <c r="AD10" s="57"/>
-      <c r="AE10" s="58"/>
-      <c r="AF10" s="59"/>
-      <c r="AG10" s="53"/>
-      <c r="AH10" s="53"/>
-      <c r="AI10" s="53"/>
-      <c r="AJ10" s="53"/>
-      <c r="AK10" s="53"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="51"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="51"/>
+      <c r="U10" s="51"/>
+      <c r="V10" s="53"/>
+      <c r="W10" s="58"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="65"/>
+      <c r="Z10" s="53"/>
+      <c r="AA10" s="57"/>
+      <c r="AB10" s="51"/>
+      <c r="AC10" s="51"/>
+      <c r="AD10" s="55"/>
+      <c r="AE10" s="56"/>
+      <c r="AF10" s="57"/>
+      <c r="AG10" s="51"/>
+      <c r="AH10" s="51"/>
+      <c r="AI10" s="51"/>
+      <c r="AJ10" s="51"/>
+      <c r="AK10" s="51"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="51"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="53"/>
-      <c r="L11" s="57"/>
-      <c r="M11" s="53"/>
-      <c r="N11" s="58"/>
-      <c r="O11" s="59"/>
-      <c r="P11" s="53"/>
-      <c r="Q11" s="53"/>
-      <c r="R11" s="53"/>
-      <c r="S11" s="53"/>
-      <c r="T11" s="53"/>
-      <c r="U11" s="53"/>
-      <c r="V11" s="58"/>
-      <c r="W11" s="60"/>
-      <c r="X11" s="53"/>
-      <c r="Y11" s="53"/>
-      <c r="Z11" s="58"/>
-      <c r="AA11" s="59"/>
-      <c r="AB11" s="53"/>
-      <c r="AC11" s="53"/>
-      <c r="AD11" s="69"/>
-      <c r="AE11" s="58"/>
-      <c r="AF11" s="59"/>
-      <c r="AG11" s="53"/>
-      <c r="AH11" s="53"/>
-      <c r="AI11" s="53"/>
-      <c r="AJ11" s="53"/>
-      <c r="AK11" s="53"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="57"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="51"/>
+      <c r="U11" s="51"/>
+      <c r="V11" s="56"/>
+      <c r="W11" s="58"/>
+      <c r="X11" s="51"/>
+      <c r="Y11" s="51"/>
+      <c r="Z11" s="56"/>
+      <c r="AA11" s="57"/>
+      <c r="AB11" s="51"/>
+      <c r="AC11" s="51"/>
+      <c r="AD11" s="67"/>
+      <c r="AE11" s="56"/>
+      <c r="AF11" s="57"/>
+      <c r="AG11" s="51"/>
+      <c r="AH11" s="51"/>
+      <c r="AI11" s="51"/>
+      <c r="AJ11" s="51"/>
+      <c r="AK11" s="51"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="51"/>
-      <c r="C12" s="52" t="s">
-        <v>145</v>
-      </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="53"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="59"/>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="53"/>
-      <c r="R12" s="53"/>
-      <c r="S12" s="53"/>
-      <c r="T12" s="53"/>
-      <c r="U12" s="53"/>
-      <c r="V12" s="58"/>
-      <c r="W12" s="60"/>
-      <c r="X12" s="53"/>
-      <c r="Y12" s="53"/>
-      <c r="Z12" s="58"/>
-      <c r="AA12" s="59"/>
-      <c r="AB12" s="53"/>
-      <c r="AC12" s="53"/>
-      <c r="AD12" s="57"/>
-      <c r="AE12" s="58"/>
-      <c r="AF12" s="56"/>
-      <c r="AG12" s="67"/>
-      <c r="AH12" s="67"/>
-      <c r="AI12" s="67"/>
-      <c r="AJ12" s="67"/>
-      <c r="AK12" s="67"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="57"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="51"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="51"/>
+      <c r="U12" s="51"/>
+      <c r="V12" s="56"/>
+      <c r="W12" s="58"/>
+      <c r="X12" s="51"/>
+      <c r="Y12" s="51"/>
+      <c r="Z12" s="56"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="51"/>
+      <c r="AC12" s="51"/>
+      <c r="AD12" s="55"/>
+      <c r="AE12" s="56"/>
+      <c r="AF12" s="54"/>
+      <c r="AG12" s="65"/>
+      <c r="AH12" s="65"/>
+      <c r="AI12" s="65"/>
+      <c r="AJ12" s="65"/>
+      <c r="AK12" s="65"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="51"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="57"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="59"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="53"/>
-      <c r="T13" s="53"/>
-      <c r="U13" s="53"/>
-      <c r="V13" s="58"/>
-      <c r="W13" s="60"/>
-      <c r="X13" s="53"/>
-      <c r="Y13" s="53"/>
-      <c r="Z13" s="58"/>
-      <c r="AA13" s="59"/>
-      <c r="AB13" s="53"/>
-      <c r="AC13" s="53"/>
-      <c r="AD13" s="57"/>
-      <c r="AE13" s="58"/>
-      <c r="AF13" s="59"/>
-      <c r="AG13" s="53"/>
-      <c r="AH13" s="53"/>
-      <c r="AI13" s="53"/>
-      <c r="AJ13" s="53"/>
-      <c r="AK13" s="53"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="50"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="57"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="51"/>
+      <c r="S13" s="51"/>
+      <c r="T13" s="51"/>
+      <c r="U13" s="51"/>
+      <c r="V13" s="56"/>
+      <c r="W13" s="58"/>
+      <c r="X13" s="51"/>
+      <c r="Y13" s="51"/>
+      <c r="Z13" s="56"/>
+      <c r="AA13" s="57"/>
+      <c r="AB13" s="51"/>
+      <c r="AC13" s="51"/>
+      <c r="AD13" s="55"/>
+      <c r="AE13" s="56"/>
+      <c r="AF13" s="57"/>
+      <c r="AG13" s="51"/>
+      <c r="AH13" s="51"/>
+      <c r="AI13" s="51"/>
+      <c r="AJ13" s="51"/>
+      <c r="AK13" s="51"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="70" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="71" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="54"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="73"/>
-      <c r="K14" s="73"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="73"/>
-      <c r="N14" s="74"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="73"/>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="73"/>
-      <c r="S14" s="73"/>
-      <c r="T14" s="73"/>
-      <c r="U14" s="73"/>
-      <c r="V14" s="74"/>
-      <c r="W14" s="60"/>
-      <c r="X14" s="73"/>
-      <c r="Y14" s="73"/>
-      <c r="Z14" s="74"/>
-      <c r="AA14" s="72"/>
-      <c r="AB14" s="73"/>
-      <c r="AC14" s="73"/>
-      <c r="AD14" s="57"/>
-      <c r="AE14" s="74"/>
-      <c r="AF14" s="72"/>
-      <c r="AG14" s="73"/>
-      <c r="AH14" s="73"/>
-      <c r="AI14" s="73"/>
-      <c r="AJ14" s="73"/>
-      <c r="AK14" s="73"/>
+      <c r="B14" s="68" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="69" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="71"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="71"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="70"/>
+      <c r="P14" s="71"/>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="71"/>
+      <c r="S14" s="71"/>
+      <c r="T14" s="71"/>
+      <c r="U14" s="71"/>
+      <c r="V14" s="72"/>
+      <c r="W14" s="58"/>
+      <c r="X14" s="71"/>
+      <c r="Y14" s="71"/>
+      <c r="Z14" s="72"/>
+      <c r="AA14" s="70"/>
+      <c r="AB14" s="71"/>
+      <c r="AC14" s="71"/>
+      <c r="AD14" s="55"/>
+      <c r="AE14" s="72"/>
+      <c r="AF14" s="70"/>
+      <c r="AG14" s="71"/>
+      <c r="AH14" s="71"/>
+      <c r="AI14" s="71"/>
+      <c r="AJ14" s="71"/>
+      <c r="AK14" s="71"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="70"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
-      <c r="K15" s="73"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="73"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="73"/>
-      <c r="Q15" s="73"/>
-      <c r="R15" s="73"/>
-      <c r="S15" s="73"/>
-      <c r="T15" s="73"/>
-      <c r="U15" s="73"/>
-      <c r="V15" s="74"/>
-      <c r="W15" s="60"/>
-      <c r="X15" s="73"/>
-      <c r="Y15" s="73"/>
-      <c r="Z15" s="74"/>
-      <c r="AA15" s="72"/>
-      <c r="AB15" s="73"/>
-      <c r="AC15" s="73"/>
-      <c r="AD15" s="57"/>
-      <c r="AE15" s="74"/>
-      <c r="AF15" s="72"/>
-      <c r="AG15" s="73"/>
-      <c r="AH15" s="73"/>
-      <c r="AI15" s="73"/>
-      <c r="AJ15" s="73"/>
-      <c r="AK15" s="73"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="70"/>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
+      <c r="V15" s="72"/>
+      <c r="W15" s="58"/>
+      <c r="X15" s="71"/>
+      <c r="Y15" s="71"/>
+      <c r="Z15" s="72"/>
+      <c r="AA15" s="70"/>
+      <c r="AB15" s="71"/>
+      <c r="AC15" s="71"/>
+      <c r="AD15" s="55"/>
+      <c r="AE15" s="72"/>
+      <c r="AF15" s="70"/>
+      <c r="AG15" s="71"/>
+      <c r="AH15" s="71"/>
+      <c r="AI15" s="71"/>
+      <c r="AJ15" s="71"/>
+      <c r="AK15" s="71"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="70"/>
-      <c r="C16" s="71" t="s">
-        <v>148</v>
-      </c>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="73"/>
-      <c r="K16" s="73"/>
-      <c r="L16" s="57"/>
-      <c r="M16" s="73"/>
-      <c r="N16" s="74"/>
-      <c r="O16" s="72"/>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="73"/>
-      <c r="R16" s="73"/>
-      <c r="S16" s="73"/>
-      <c r="T16" s="73"/>
-      <c r="U16" s="73"/>
-      <c r="V16" s="74"/>
-      <c r="W16" s="60"/>
-      <c r="X16" s="73"/>
-      <c r="Y16" s="73"/>
-      <c r="Z16" s="74"/>
-      <c r="AA16" s="72"/>
-      <c r="AB16" s="73"/>
-      <c r="AC16" s="73"/>
-      <c r="AD16" s="57"/>
-      <c r="AE16" s="74"/>
-      <c r="AF16" s="72"/>
-      <c r="AG16" s="73"/>
-      <c r="AH16" s="73"/>
-      <c r="AI16" s="73"/>
-      <c r="AJ16" s="73"/>
-      <c r="AK16" s="73"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="72"/>
+      <c r="O16" s="70"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="71"/>
+      <c r="S16" s="71"/>
+      <c r="T16" s="71"/>
+      <c r="U16" s="71"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="58"/>
+      <c r="X16" s="71"/>
+      <c r="Y16" s="71"/>
+      <c r="Z16" s="72"/>
+      <c r="AA16" s="70"/>
+      <c r="AB16" s="71"/>
+      <c r="AC16" s="71"/>
+      <c r="AD16" s="55"/>
+      <c r="AE16" s="72"/>
+      <c r="AF16" s="70"/>
+      <c r="AG16" s="71"/>
+      <c r="AH16" s="71"/>
+      <c r="AI16" s="71"/>
+      <c r="AJ16" s="71"/>
+      <c r="AK16" s="71"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="70"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="73"/>
-      <c r="K17" s="73"/>
-      <c r="L17" s="57"/>
-      <c r="M17" s="73"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="73"/>
-      <c r="Q17" s="73"/>
-      <c r="R17" s="73"/>
-      <c r="S17" s="73"/>
-      <c r="T17" s="73"/>
-      <c r="U17" s="73"/>
-      <c r="V17" s="74"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="73"/>
-      <c r="Y17" s="73"/>
-      <c r="Z17" s="74"/>
-      <c r="AA17" s="72"/>
-      <c r="AB17" s="73"/>
-      <c r="AC17" s="73"/>
-      <c r="AD17" s="57"/>
-      <c r="AE17" s="74"/>
-      <c r="AF17" s="72"/>
-      <c r="AG17" s="73"/>
-      <c r="AH17" s="73"/>
-      <c r="AI17" s="73"/>
-      <c r="AJ17" s="73"/>
-      <c r="AK17" s="73"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="72"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="55"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="70"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="71"/>
+      <c r="U17" s="71"/>
+      <c r="V17" s="72"/>
+      <c r="W17" s="58"/>
+      <c r="X17" s="71"/>
+      <c r="Y17" s="71"/>
+      <c r="Z17" s="72"/>
+      <c r="AA17" s="70"/>
+      <c r="AB17" s="71"/>
+      <c r="AC17" s="71"/>
+      <c r="AD17" s="55"/>
+      <c r="AE17" s="72"/>
+      <c r="AF17" s="70"/>
+      <c r="AG17" s="71"/>
+      <c r="AH17" s="71"/>
+      <c r="AI17" s="71"/>
+      <c r="AJ17" s="71"/>
+      <c r="AK17" s="71"/>
       <c r="AN17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="70"/>
-      <c r="C18" s="71" t="s">
-        <v>150</v>
-      </c>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="73"/>
-      <c r="K18" s="73"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="73"/>
-      <c r="N18" s="74"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="73"/>
-      <c r="Q18" s="73"/>
-      <c r="R18" s="73"/>
-      <c r="S18" s="73"/>
-      <c r="T18" s="73"/>
-      <c r="U18" s="73"/>
-      <c r="V18" s="74"/>
-      <c r="W18" s="60"/>
-      <c r="X18" s="73"/>
-      <c r="Y18" s="73"/>
-      <c r="Z18" s="74"/>
-      <c r="AA18" s="72"/>
-      <c r="AB18" s="73"/>
-      <c r="AC18" s="73"/>
-      <c r="AD18" s="57"/>
-      <c r="AE18" s="74"/>
-      <c r="AF18" s="72"/>
-      <c r="AG18" s="73"/>
-      <c r="AH18" s="73"/>
-      <c r="AI18" s="73"/>
-      <c r="AJ18" s="73"/>
-      <c r="AK18" s="73"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="71"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="55"/>
+      <c r="M18" s="71"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="71"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="71"/>
+      <c r="S18" s="71"/>
+      <c r="T18" s="71"/>
+      <c r="U18" s="71"/>
+      <c r="V18" s="72"/>
+      <c r="W18" s="58"/>
+      <c r="X18" s="71"/>
+      <c r="Y18" s="71"/>
+      <c r="Z18" s="72"/>
+      <c r="AA18" s="70"/>
+      <c r="AB18" s="71"/>
+      <c r="AC18" s="71"/>
+      <c r="AD18" s="55"/>
+      <c r="AE18" s="72"/>
+      <c r="AF18" s="70"/>
+      <c r="AG18" s="71"/>
+      <c r="AH18" s="71"/>
+      <c r="AI18" s="71"/>
+      <c r="AJ18" s="71"/>
+      <c r="AK18" s="71"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="70"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="73"/>
-      <c r="K19" s="73"/>
-      <c r="L19" s="57"/>
-      <c r="M19" s="73"/>
-      <c r="N19" s="74"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="73"/>
-      <c r="R19" s="73"/>
-      <c r="S19" s="73"/>
-      <c r="T19" s="73"/>
-      <c r="U19" s="73"/>
-      <c r="V19" s="74"/>
-      <c r="W19" s="60"/>
-      <c r="X19" s="73"/>
-      <c r="Y19" s="73"/>
-      <c r="Z19" s="74"/>
-      <c r="AA19" s="72"/>
-      <c r="AB19" s="73"/>
-      <c r="AC19" s="73"/>
-      <c r="AD19" s="57"/>
-      <c r="AE19" s="74"/>
-      <c r="AF19" s="72"/>
-      <c r="AG19" s="73"/>
-      <c r="AH19" s="73"/>
-      <c r="AI19" s="73"/>
-      <c r="AJ19" s="73"/>
-      <c r="AK19" s="73"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="72"/>
+      <c r="O19" s="70"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
+      <c r="U19" s="71"/>
+      <c r="V19" s="72"/>
+      <c r="W19" s="58"/>
+      <c r="X19" s="71"/>
+      <c r="Y19" s="71"/>
+      <c r="Z19" s="72"/>
+      <c r="AA19" s="70"/>
+      <c r="AB19" s="71"/>
+      <c r="AC19" s="71"/>
+      <c r="AD19" s="55"/>
+      <c r="AE19" s="72"/>
+      <c r="AF19" s="70"/>
+      <c r="AG19" s="71"/>
+      <c r="AH19" s="71"/>
+      <c r="AI19" s="71"/>
+      <c r="AJ19" s="71"/>
+      <c r="AK19" s="71"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="70"/>
-      <c r="C20" s="71" t="s">
-        <v>151</v>
-      </c>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="76"/>
-      <c r="G20" s="55"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="73"/>
-      <c r="K20" s="73"/>
-      <c r="L20" s="57"/>
-      <c r="M20" s="73"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="72"/>
-      <c r="P20" s="73"/>
-      <c r="Q20" s="73"/>
-      <c r="R20" s="73"/>
-      <c r="S20" s="73"/>
-      <c r="T20" s="73"/>
-      <c r="U20" s="73"/>
-      <c r="V20" s="74"/>
-      <c r="W20" s="60"/>
-      <c r="X20" s="73"/>
-      <c r="Y20" s="73"/>
-      <c r="Z20" s="74"/>
-      <c r="AA20" s="72"/>
-      <c r="AB20" s="73"/>
-      <c r="AC20" s="73"/>
-      <c r="AD20" s="57"/>
-      <c r="AE20" s="74"/>
-      <c r="AF20" s="72"/>
-      <c r="AG20" s="73"/>
-      <c r="AH20" s="73"/>
-      <c r="AI20" s="73"/>
-      <c r="AJ20" s="73"/>
-      <c r="AK20" s="73"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="72"/>
+      <c r="O20" s="70"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="71"/>
+      <c r="S20" s="71"/>
+      <c r="T20" s="71"/>
+      <c r="U20" s="71"/>
+      <c r="V20" s="72"/>
+      <c r="W20" s="58"/>
+      <c r="X20" s="71"/>
+      <c r="Y20" s="71"/>
+      <c r="Z20" s="72"/>
+      <c r="AA20" s="70"/>
+      <c r="AB20" s="71"/>
+      <c r="AC20" s="71"/>
+      <c r="AD20" s="55"/>
+      <c r="AE20" s="72"/>
+      <c r="AF20" s="70"/>
+      <c r="AG20" s="71"/>
+      <c r="AH20" s="71"/>
+      <c r="AI20" s="71"/>
+      <c r="AJ20" s="71"/>
+      <c r="AK20" s="71"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="70"/>
-      <c r="C21" s="71"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="73"/>
-      <c r="K21" s="73"/>
-      <c r="L21" s="57"/>
-      <c r="M21" s="73"/>
-      <c r="N21" s="74"/>
-      <c r="O21" s="72"/>
-      <c r="P21" s="73"/>
-      <c r="Q21" s="73"/>
-      <c r="R21" s="73"/>
-      <c r="S21" s="73"/>
-      <c r="T21" s="73"/>
-      <c r="U21" s="73"/>
-      <c r="V21" s="74"/>
-      <c r="W21" s="60"/>
-      <c r="X21" s="73"/>
-      <c r="Y21" s="73"/>
-      <c r="Z21" s="74"/>
-      <c r="AA21" s="72"/>
-      <c r="AB21" s="73"/>
-      <c r="AC21" s="73"/>
-      <c r="AD21" s="57"/>
-      <c r="AE21" s="74"/>
-      <c r="AF21" s="72"/>
-      <c r="AG21" s="73"/>
-      <c r="AH21" s="73"/>
-      <c r="AI21" s="73"/>
-      <c r="AJ21" s="73"/>
-      <c r="AK21" s="73"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="72"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="71"/>
+      <c r="T21" s="71"/>
+      <c r="U21" s="71"/>
+      <c r="V21" s="72"/>
+      <c r="W21" s="58"/>
+      <c r="X21" s="71"/>
+      <c r="Y21" s="71"/>
+      <c r="Z21" s="72"/>
+      <c r="AA21" s="70"/>
+      <c r="AB21" s="71"/>
+      <c r="AC21" s="71"/>
+      <c r="AD21" s="55"/>
+      <c r="AE21" s="72"/>
+      <c r="AF21" s="70"/>
+      <c r="AG21" s="71"/>
+      <c r="AH21" s="71"/>
+      <c r="AI21" s="71"/>
+      <c r="AJ21" s="71"/>
+      <c r="AK21" s="71"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="70"/>
-      <c r="C22" s="71" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="73"/>
-      <c r="K22" s="73"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="73"/>
-      <c r="N22" s="74"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="73"/>
-      <c r="Q22" s="73"/>
-      <c r="R22" s="73"/>
-      <c r="S22" s="73"/>
-      <c r="T22" s="73"/>
-      <c r="U22" s="73"/>
-      <c r="V22" s="74"/>
-      <c r="W22" s="60"/>
-      <c r="X22" s="73"/>
-      <c r="Y22" s="73"/>
-      <c r="Z22" s="74"/>
-      <c r="AA22" s="72"/>
-      <c r="AB22" s="73"/>
-      <c r="AC22" s="73"/>
-      <c r="AD22" s="57"/>
-      <c r="AE22" s="74"/>
-      <c r="AF22" s="72"/>
-      <c r="AG22" s="73"/>
-      <c r="AH22" s="73"/>
-      <c r="AI22" s="73"/>
-      <c r="AJ22" s="73"/>
-      <c r="AK22" s="73"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="69" t="s">
+        <v>154</v>
+      </c>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="71"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="71"/>
+      <c r="S22" s="71"/>
+      <c r="T22" s="71"/>
+      <c r="U22" s="71"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="58"/>
+      <c r="X22" s="71"/>
+      <c r="Y22" s="71"/>
+      <c r="Z22" s="72"/>
+      <c r="AA22" s="70"/>
+      <c r="AB22" s="71"/>
+      <c r="AC22" s="71"/>
+      <c r="AD22" s="55"/>
+      <c r="AE22" s="72"/>
+      <c r="AF22" s="70"/>
+      <c r="AG22" s="71"/>
+      <c r="AH22" s="71"/>
+      <c r="AI22" s="71"/>
+      <c r="AJ22" s="71"/>
+      <c r="AK22" s="71"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="70"/>
-      <c r="C23" s="71"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="72"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="73"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="73"/>
-      <c r="N23" s="74"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="73"/>
-      <c r="Q23" s="73"/>
-      <c r="R23" s="73"/>
-      <c r="S23" s="73"/>
-      <c r="T23" s="73"/>
-      <c r="U23" s="73"/>
-      <c r="V23" s="74"/>
-      <c r="W23" s="60"/>
-      <c r="X23" s="73"/>
-      <c r="Y23" s="73"/>
-      <c r="Z23" s="74"/>
-      <c r="AA23" s="72"/>
-      <c r="AB23" s="73"/>
-      <c r="AC23" s="73"/>
-      <c r="AD23" s="57"/>
-      <c r="AE23" s="74"/>
-      <c r="AF23" s="72"/>
-      <c r="AG23" s="73"/>
-      <c r="AH23" s="73"/>
-      <c r="AI23" s="73"/>
-      <c r="AJ23" s="73"/>
-      <c r="AK23" s="73"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="72"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="71"/>
+      <c r="T23" s="71"/>
+      <c r="U23" s="71"/>
+      <c r="V23" s="72"/>
+      <c r="W23" s="58"/>
+      <c r="X23" s="71"/>
+      <c r="Y23" s="71"/>
+      <c r="Z23" s="72"/>
+      <c r="AA23" s="70"/>
+      <c r="AB23" s="71"/>
+      <c r="AC23" s="71"/>
+      <c r="AD23" s="55"/>
+      <c r="AE23" s="72"/>
+      <c r="AF23" s="70"/>
+      <c r="AG23" s="71"/>
+      <c r="AH23" s="71"/>
+      <c r="AI23" s="71"/>
+      <c r="AJ23" s="71"/>
+      <c r="AK23" s="71"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="70"/>
-      <c r="C24" s="71" t="s">
-        <v>153</v>
-      </c>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="73"/>
-      <c r="K24" s="73"/>
-      <c r="L24" s="57"/>
-      <c r="M24" s="73"/>
-      <c r="N24" s="74"/>
-      <c r="O24" s="72"/>
-      <c r="P24" s="73"/>
-      <c r="Q24" s="73"/>
-      <c r="R24" s="73"/>
-      <c r="S24" s="73"/>
-      <c r="T24" s="73"/>
-      <c r="U24" s="73"/>
-      <c r="V24" s="74"/>
-      <c r="W24" s="60"/>
-      <c r="X24" s="73"/>
-      <c r="Y24" s="73"/>
-      <c r="Z24" s="74"/>
-      <c r="AA24" s="72"/>
-      <c r="AB24" s="73"/>
-      <c r="AC24" s="73"/>
-      <c r="AD24" s="57"/>
-      <c r="AE24" s="74"/>
-      <c r="AF24" s="72"/>
-      <c r="AG24" s="73"/>
-      <c r="AH24" s="73"/>
-      <c r="AI24" s="73"/>
-      <c r="AJ24" s="73"/>
-      <c r="AK24" s="73"/>
+      <c r="B24" s="68"/>
+      <c r="C24" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="71"/>
+      <c r="S24" s="71"/>
+      <c r="T24" s="71"/>
+      <c r="U24" s="71"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="58"/>
+      <c r="X24" s="71"/>
+      <c r="Y24" s="71"/>
+      <c r="Z24" s="72"/>
+      <c r="AA24" s="70"/>
+      <c r="AB24" s="71"/>
+      <c r="AC24" s="71"/>
+      <c r="AD24" s="55"/>
+      <c r="AE24" s="72"/>
+      <c r="AF24" s="70"/>
+      <c r="AG24" s="71"/>
+      <c r="AH24" s="71"/>
+      <c r="AI24" s="71"/>
+      <c r="AJ24" s="71"/>
+      <c r="AK24" s="71"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="70"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="73"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="73"/>
-      <c r="N25" s="74"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="73"/>
-      <c r="Q25" s="73"/>
-      <c r="R25" s="73"/>
-      <c r="S25" s="73"/>
-      <c r="T25" s="73"/>
-      <c r="U25" s="73"/>
-      <c r="V25" s="74"/>
-      <c r="W25" s="60"/>
-      <c r="X25" s="73"/>
-      <c r="Y25" s="73"/>
-      <c r="Z25" s="74"/>
-      <c r="AA25" s="72"/>
-      <c r="AB25" s="73"/>
-      <c r="AC25" s="73"/>
-      <c r="AD25" s="57"/>
-      <c r="AE25" s="74"/>
-      <c r="AF25" s="72"/>
-      <c r="AG25" s="73"/>
-      <c r="AH25" s="73"/>
-      <c r="AI25" s="73"/>
-      <c r="AJ25" s="73"/>
-      <c r="AK25" s="73"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="60"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="55"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="71"/>
+      <c r="T25" s="71"/>
+      <c r="U25" s="71"/>
+      <c r="V25" s="72"/>
+      <c r="W25" s="58"/>
+      <c r="X25" s="71"/>
+      <c r="Y25" s="71"/>
+      <c r="Z25" s="72"/>
+      <c r="AA25" s="70"/>
+      <c r="AB25" s="71"/>
+      <c r="AC25" s="71"/>
+      <c r="AD25" s="55"/>
+      <c r="AE25" s="72"/>
+      <c r="AF25" s="70"/>
+      <c r="AG25" s="71"/>
+      <c r="AH25" s="71"/>
+      <c r="AI25" s="71"/>
+      <c r="AJ25" s="71"/>
+      <c r="AK25" s="71"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="C26" s="52" t="s">
-        <v>155</v>
-      </c>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="67"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="57"/>
-      <c r="M26" s="53"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="59"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
-      <c r="R26" s="53"/>
-      <c r="S26" s="53"/>
-      <c r="T26" s="53"/>
-      <c r="U26" s="53"/>
-      <c r="V26" s="58"/>
-      <c r="W26" s="60"/>
-      <c r="X26" s="53"/>
-      <c r="Y26" s="53"/>
-      <c r="Z26" s="58"/>
-      <c r="AA26" s="59"/>
-      <c r="AB26" s="53"/>
-      <c r="AC26" s="53"/>
-      <c r="AD26" s="57"/>
-      <c r="AE26" s="58"/>
-      <c r="AF26" s="59"/>
-      <c r="AG26" s="53"/>
-      <c r="AH26" s="53"/>
-      <c r="AI26" s="53"/>
-      <c r="AJ26" s="53"/>
-      <c r="AK26" s="53"/>
+      <c r="B26" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="55"/>
+      <c r="M26" s="51"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="51"/>
+      <c r="R26" s="51"/>
+      <c r="S26" s="51"/>
+      <c r="T26" s="51"/>
+      <c r="U26" s="51"/>
+      <c r="V26" s="56"/>
+      <c r="W26" s="58"/>
+      <c r="X26" s="51"/>
+      <c r="Y26" s="51"/>
+      <c r="Z26" s="56"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="51"/>
+      <c r="AC26" s="51"/>
+      <c r="AD26" s="55"/>
+      <c r="AE26" s="56"/>
+      <c r="AF26" s="57"/>
+      <c r="AG26" s="51"/>
+      <c r="AH26" s="51"/>
+      <c r="AI26" s="51"/>
+      <c r="AJ26" s="51"/>
+      <c r="AK26" s="51"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="51"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="64"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="53"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="57"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="59"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="53"/>
-      <c r="T27" s="53"/>
-      <c r="U27" s="53"/>
-      <c r="V27" s="58"/>
-      <c r="W27" s="60"/>
-      <c r="X27" s="53"/>
-      <c r="Y27" s="53"/>
-      <c r="Z27" s="58"/>
-      <c r="AA27" s="59"/>
-      <c r="AB27" s="53"/>
-      <c r="AC27" s="53"/>
-      <c r="AD27" s="57"/>
-      <c r="AE27" s="58"/>
-      <c r="AF27" s="59"/>
-      <c r="AG27" s="53"/>
-      <c r="AH27" s="53"/>
-      <c r="AI27" s="53"/>
-      <c r="AJ27" s="53"/>
-      <c r="AK27" s="53"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+      <c r="K27" s="51"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="51"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="57"/>
+      <c r="P27" s="51"/>
+      <c r="Q27" s="51"/>
+      <c r="R27" s="51"/>
+      <c r="S27" s="51"/>
+      <c r="T27" s="51"/>
+      <c r="U27" s="51"/>
+      <c r="V27" s="56"/>
+      <c r="W27" s="58"/>
+      <c r="X27" s="51"/>
+      <c r="Y27" s="51"/>
+      <c r="Z27" s="56"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="51"/>
+      <c r="AC27" s="51"/>
+      <c r="AD27" s="55"/>
+      <c r="AE27" s="56"/>
+      <c r="AF27" s="57"/>
+      <c r="AG27" s="51"/>
+      <c r="AH27" s="51"/>
+      <c r="AI27" s="51"/>
+      <c r="AJ27" s="51"/>
+      <c r="AK27" s="51"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="51"/>
-      <c r="C28" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="67"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="53"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="59"/>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="53"/>
-      <c r="U28" s="53"/>
-      <c r="V28" s="58"/>
-      <c r="W28" s="60"/>
-      <c r="X28" s="53"/>
-      <c r="Y28" s="53"/>
-      <c r="Z28" s="58"/>
-      <c r="AA28" s="59"/>
-      <c r="AB28" s="53"/>
-      <c r="AC28" s="53"/>
-      <c r="AD28" s="57"/>
-      <c r="AE28" s="58"/>
-      <c r="AF28" s="59"/>
-      <c r="AG28" s="53"/>
-      <c r="AH28" s="53"/>
-      <c r="AI28" s="53"/>
-      <c r="AJ28" s="53"/>
-      <c r="AK28" s="53"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="55"/>
+      <c r="M28" s="51"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="57"/>
+      <c r="P28" s="51"/>
+      <c r="Q28" s="51"/>
+      <c r="R28" s="51"/>
+      <c r="S28" s="51"/>
+      <c r="T28" s="51"/>
+      <c r="U28" s="51"/>
+      <c r="V28" s="56"/>
+      <c r="W28" s="58"/>
+      <c r="X28" s="51"/>
+      <c r="Y28" s="51"/>
+      <c r="Z28" s="56"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="51"/>
+      <c r="AC28" s="51"/>
+      <c r="AD28" s="55"/>
+      <c r="AE28" s="56"/>
+      <c r="AF28" s="57"/>
+      <c r="AG28" s="51"/>
+      <c r="AH28" s="51"/>
+      <c r="AI28" s="51"/>
+      <c r="AJ28" s="51"/>
+      <c r="AK28" s="51"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="51"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="64"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="68"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="57"/>
-      <c r="M29" s="53"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="59"/>
-      <c r="P29" s="53"/>
-      <c r="Q29" s="53"/>
-      <c r="R29" s="53"/>
-      <c r="S29" s="53"/>
-      <c r="T29" s="53"/>
-      <c r="U29" s="53"/>
-      <c r="V29" s="58"/>
-      <c r="W29" s="60"/>
-      <c r="X29" s="53"/>
-      <c r="Y29" s="53"/>
-      <c r="Z29" s="58"/>
-      <c r="AA29" s="59"/>
-      <c r="AB29" s="53"/>
-      <c r="AC29" s="53"/>
-      <c r="AD29" s="57"/>
-      <c r="AE29" s="58"/>
-      <c r="AF29" s="59"/>
-      <c r="AG29" s="53"/>
-      <c r="AH29" s="53"/>
-      <c r="AI29" s="53"/>
-      <c r="AJ29" s="53"/>
-      <c r="AK29" s="53"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="51"/>
+      <c r="L29" s="55"/>
+      <c r="M29" s="51"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="51"/>
+      <c r="Q29" s="51"/>
+      <c r="R29" s="51"/>
+      <c r="S29" s="51"/>
+      <c r="T29" s="51"/>
+      <c r="U29" s="51"/>
+      <c r="V29" s="56"/>
+      <c r="W29" s="58"/>
+      <c r="X29" s="51"/>
+      <c r="Y29" s="51"/>
+      <c r="Z29" s="56"/>
+      <c r="AA29" s="57"/>
+      <c r="AB29" s="51"/>
+      <c r="AC29" s="51"/>
+      <c r="AD29" s="55"/>
+      <c r="AE29" s="56"/>
+      <c r="AF29" s="57"/>
+      <c r="AG29" s="51"/>
+      <c r="AH29" s="51"/>
+      <c r="AI29" s="51"/>
+      <c r="AJ29" s="51"/>
+      <c r="AK29" s="51"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="51"/>
-      <c r="C30" s="52" t="s">
-        <v>157</v>
-      </c>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="57"/>
-      <c r="M30" s="67"/>
-      <c r="N30" s="58"/>
-      <c r="O30" s="59"/>
-      <c r="P30" s="53"/>
-      <c r="Q30" s="53"/>
-      <c r="R30" s="53"/>
-      <c r="S30" s="53"/>
-      <c r="T30" s="53"/>
-      <c r="U30" s="53"/>
-      <c r="V30" s="58"/>
-      <c r="W30" s="60"/>
-      <c r="X30" s="53"/>
-      <c r="Y30" s="53"/>
-      <c r="Z30" s="58"/>
-      <c r="AA30" s="59"/>
-      <c r="AB30" s="53"/>
-      <c r="AC30" s="53"/>
-      <c r="AD30" s="57"/>
-      <c r="AE30" s="58"/>
-      <c r="AF30" s="59"/>
-      <c r="AG30" s="53"/>
-      <c r="AH30" s="53"/>
-      <c r="AI30" s="53"/>
-      <c r="AJ30" s="53"/>
-      <c r="AK30" s="53"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="65"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="55"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="51"/>
+      <c r="Q30" s="51"/>
+      <c r="R30" s="51"/>
+      <c r="S30" s="51"/>
+      <c r="T30" s="51"/>
+      <c r="U30" s="51"/>
+      <c r="V30" s="56"/>
+      <c r="W30" s="58"/>
+      <c r="X30" s="51"/>
+      <c r="Y30" s="51"/>
+      <c r="Z30" s="56"/>
+      <c r="AA30" s="57"/>
+      <c r="AB30" s="51"/>
+      <c r="AC30" s="51"/>
+      <c r="AD30" s="55"/>
+      <c r="AE30" s="56"/>
+      <c r="AF30" s="57"/>
+      <c r="AG30" s="51"/>
+      <c r="AH30" s="51"/>
+      <c r="AI30" s="51"/>
+      <c r="AJ30" s="51"/>
+      <c r="AK30" s="51"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="51"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
-      <c r="L31" s="78"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="59"/>
-      <c r="P31" s="53"/>
-      <c r="Q31" s="53"/>
-      <c r="R31" s="53"/>
-      <c r="S31" s="53"/>
-      <c r="T31" s="53"/>
-      <c r="U31" s="53"/>
-      <c r="V31" s="58"/>
-      <c r="W31" s="60"/>
-      <c r="X31" s="53"/>
-      <c r="Y31" s="53"/>
-      <c r="Z31" s="58"/>
-      <c r="AA31" s="59"/>
-      <c r="AB31" s="53"/>
-      <c r="AC31" s="53"/>
-      <c r="AD31" s="57"/>
-      <c r="AE31" s="58"/>
-      <c r="AF31" s="59"/>
-      <c r="AG31" s="53"/>
-      <c r="AH31" s="53"/>
-      <c r="AI31" s="53"/>
-      <c r="AJ31" s="53"/>
-      <c r="AK31" s="53"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="76"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="57"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="51"/>
+      <c r="R31" s="51"/>
+      <c r="S31" s="51"/>
+      <c r="T31" s="51"/>
+      <c r="U31" s="51"/>
+      <c r="V31" s="56"/>
+      <c r="W31" s="58"/>
+      <c r="X31" s="51"/>
+      <c r="Y31" s="51"/>
+      <c r="Z31" s="56"/>
+      <c r="AA31" s="57"/>
+      <c r="AB31" s="51"/>
+      <c r="AC31" s="51"/>
+      <c r="AD31" s="55"/>
+      <c r="AE31" s="56"/>
+      <c r="AF31" s="57"/>
+      <c r="AG31" s="51"/>
+      <c r="AH31" s="51"/>
+      <c r="AI31" s="51"/>
+      <c r="AJ31" s="51"/>
+      <c r="AK31" s="51"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="51"/>
-      <c r="C32" s="52" t="s">
-        <v>158</v>
-      </c>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="59"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="53"/>
-      <c r="K32" s="53"/>
-      <c r="L32" s="57"/>
-      <c r="M32" s="67"/>
-      <c r="N32" s="55"/>
-      <c r="O32" s="59"/>
-      <c r="P32" s="53"/>
-      <c r="Q32" s="53"/>
-      <c r="R32" s="53"/>
-      <c r="S32" s="53"/>
-      <c r="T32" s="53"/>
-      <c r="U32" s="53"/>
-      <c r="V32" s="58"/>
-      <c r="W32" s="60"/>
-      <c r="X32" s="53"/>
-      <c r="Y32" s="53"/>
-      <c r="Z32" s="58"/>
-      <c r="AA32" s="59"/>
-      <c r="AB32" s="53"/>
-      <c r="AC32" s="53"/>
-      <c r="AD32" s="57"/>
-      <c r="AE32" s="58"/>
-      <c r="AF32" s="59"/>
-      <c r="AG32" s="53"/>
-      <c r="AH32" s="53"/>
-      <c r="AI32" s="53"/>
-      <c r="AJ32" s="53"/>
-      <c r="AK32" s="53"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
+      <c r="K32" s="51"/>
+      <c r="L32" s="55"/>
+      <c r="M32" s="65"/>
+      <c r="N32" s="53"/>
+      <c r="O32" s="57"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="51"/>
+      <c r="R32" s="51"/>
+      <c r="S32" s="51"/>
+      <c r="T32" s="51"/>
+      <c r="U32" s="51"/>
+      <c r="V32" s="56"/>
+      <c r="W32" s="58"/>
+      <c r="X32" s="51"/>
+      <c r="Y32" s="51"/>
+      <c r="Z32" s="56"/>
+      <c r="AA32" s="57"/>
+      <c r="AB32" s="51"/>
+      <c r="AC32" s="51"/>
+      <c r="AD32" s="55"/>
+      <c r="AE32" s="56"/>
+      <c r="AF32" s="57"/>
+      <c r="AG32" s="51"/>
+      <c r="AH32" s="51"/>
+      <c r="AI32" s="51"/>
+      <c r="AJ32" s="51"/>
+      <c r="AK32" s="51"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="51"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="59"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="57"/>
-      <c r="M33" s="53"/>
-      <c r="N33" s="64"/>
-      <c r="O33" s="59"/>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
-      <c r="V33" s="58"/>
-      <c r="W33" s="60"/>
-      <c r="X33" s="53"/>
-      <c r="Y33" s="53"/>
-      <c r="Z33" s="58"/>
-      <c r="AA33" s="59"/>
-      <c r="AB33" s="53"/>
-      <c r="AC33" s="53"/>
-      <c r="AD33" s="57"/>
-      <c r="AE33" s="58"/>
-      <c r="AF33" s="59"/>
-      <c r="AG33" s="53"/>
-      <c r="AH33" s="53"/>
-      <c r="AI33" s="53"/>
-      <c r="AJ33" s="53"/>
-      <c r="AK33" s="53"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+      <c r="L33" s="55"/>
+      <c r="M33" s="51"/>
+      <c r="N33" s="62"/>
+      <c r="O33" s="57"/>
+      <c r="P33" s="51"/>
+      <c r="Q33" s="51"/>
+      <c r="R33" s="51"/>
+      <c r="S33" s="51"/>
+      <c r="T33" s="51"/>
+      <c r="U33" s="51"/>
+      <c r="V33" s="56"/>
+      <c r="W33" s="58"/>
+      <c r="X33" s="51"/>
+      <c r="Y33" s="51"/>
+      <c r="Z33" s="56"/>
+      <c r="AA33" s="57"/>
+      <c r="AB33" s="51"/>
+      <c r="AC33" s="51"/>
+      <c r="AD33" s="55"/>
+      <c r="AE33" s="56"/>
+      <c r="AF33" s="57"/>
+      <c r="AG33" s="51"/>
+      <c r="AH33" s="51"/>
+      <c r="AI33" s="51"/>
+      <c r="AJ33" s="51"/>
+      <c r="AK33" s="51"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="70" t="s">
-        <v>159</v>
-      </c>
-      <c r="C34" s="79" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="73"/>
-      <c r="J34" s="73"/>
-      <c r="K34" s="73"/>
-      <c r="L34" s="57"/>
-      <c r="M34" s="67"/>
-      <c r="N34" s="55"/>
-      <c r="O34" s="56"/>
-      <c r="P34" s="67"/>
-      <c r="Q34" s="67"/>
-      <c r="R34" s="67"/>
-      <c r="S34" s="73"/>
-      <c r="T34" s="73"/>
-      <c r="U34" s="73"/>
-      <c r="V34" s="74"/>
-      <c r="W34" s="60"/>
-      <c r="X34" s="73"/>
-      <c r="Y34" s="73"/>
-      <c r="Z34" s="74"/>
-      <c r="AA34" s="72"/>
-      <c r="AB34" s="73"/>
-      <c r="AC34" s="73"/>
-      <c r="AD34" s="57"/>
-      <c r="AE34" s="74"/>
-      <c r="AF34" s="72"/>
-      <c r="AG34" s="73"/>
-      <c r="AH34" s="73"/>
-      <c r="AI34" s="73"/>
-      <c r="AJ34" s="73"/>
-      <c r="AK34" s="73"/>
+      <c r="B34" s="68" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="77" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="71"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="65"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="54"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="65"/>
+      <c r="R34" s="65"/>
+      <c r="S34" s="71"/>
+      <c r="T34" s="71"/>
+      <c r="U34" s="71"/>
+      <c r="V34" s="72"/>
+      <c r="W34" s="58"/>
+      <c r="X34" s="71"/>
+      <c r="Y34" s="71"/>
+      <c r="Z34" s="72"/>
+      <c r="AA34" s="70"/>
+      <c r="AB34" s="71"/>
+      <c r="AC34" s="71"/>
+      <c r="AD34" s="55"/>
+      <c r="AE34" s="72"/>
+      <c r="AF34" s="70"/>
+      <c r="AG34" s="71"/>
+      <c r="AH34" s="71"/>
+      <c r="AI34" s="71"/>
+      <c r="AJ34" s="71"/>
+      <c r="AK34" s="71"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="70"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="73"/>
-      <c r="J35" s="73"/>
-      <c r="K35" s="80"/>
-      <c r="L35" s="57"/>
-      <c r="M35" s="73"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="72"/>
-      <c r="P35" s="66"/>
-      <c r="Q35" s="73"/>
-      <c r="R35" s="81"/>
-      <c r="S35" s="81"/>
-      <c r="T35" s="62"/>
-      <c r="U35" s="73"/>
-      <c r="V35" s="74"/>
-      <c r="W35" s="60"/>
-      <c r="X35" s="73"/>
-      <c r="Y35" s="73"/>
-      <c r="Z35" s="74"/>
-      <c r="AA35" s="72"/>
-      <c r="AB35" s="73"/>
-      <c r="AC35" s="73"/>
-      <c r="AD35" s="57"/>
-      <c r="AE35" s="74"/>
-      <c r="AF35" s="72"/>
-      <c r="AG35" s="73"/>
-      <c r="AH35" s="73"/>
-      <c r="AI35" s="73"/>
-      <c r="AJ35" s="73"/>
-      <c r="AK35" s="73"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="78"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="71"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="70"/>
+      <c r="P35" s="64"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="79"/>
+      <c r="S35" s="79"/>
+      <c r="T35" s="60"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="72"/>
+      <c r="W35" s="58"/>
+      <c r="X35" s="71"/>
+      <c r="Y35" s="71"/>
+      <c r="Z35" s="72"/>
+      <c r="AA35" s="70"/>
+      <c r="AB35" s="71"/>
+      <c r="AC35" s="71"/>
+      <c r="AD35" s="55"/>
+      <c r="AE35" s="72"/>
+      <c r="AF35" s="70"/>
+      <c r="AG35" s="71"/>
+      <c r="AH35" s="71"/>
+      <c r="AI35" s="71"/>
+      <c r="AJ35" s="71"/>
+      <c r="AK35" s="71"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="70"/>
-      <c r="C36" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="D36" s="73"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="73"/>
-      <c r="J36" s="73"/>
-      <c r="K36" s="73"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="67"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="56"/>
-      <c r="P36" s="67"/>
-      <c r="Q36" s="73"/>
-      <c r="R36" s="73"/>
-      <c r="S36" s="73"/>
-      <c r="T36" s="73"/>
-      <c r="U36" s="73"/>
-      <c r="V36" s="74"/>
-      <c r="W36" s="60"/>
-      <c r="X36" s="73"/>
-      <c r="Y36" s="73"/>
-      <c r="Z36" s="74"/>
-      <c r="AA36" s="72"/>
-      <c r="AB36" s="73"/>
-      <c r="AC36" s="73"/>
-      <c r="AD36" s="57"/>
-      <c r="AE36" s="74"/>
-      <c r="AF36" s="72"/>
-      <c r="AG36" s="73"/>
-      <c r="AH36" s="73"/>
-      <c r="AI36" s="73"/>
-      <c r="AJ36" s="73"/>
-      <c r="AK36" s="73"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="77" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="71"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="72"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="53"/>
+      <c r="O36" s="54"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="71"/>
+      <c r="S36" s="71"/>
+      <c r="T36" s="71"/>
+      <c r="U36" s="71"/>
+      <c r="V36" s="72"/>
+      <c r="W36" s="58"/>
+      <c r="X36" s="71"/>
+      <c r="Y36" s="71"/>
+      <c r="Z36" s="72"/>
+      <c r="AA36" s="70"/>
+      <c r="AB36" s="71"/>
+      <c r="AC36" s="71"/>
+      <c r="AD36" s="55"/>
+      <c r="AE36" s="72"/>
+      <c r="AF36" s="70"/>
+      <c r="AG36" s="71"/>
+      <c r="AH36" s="71"/>
+      <c r="AI36" s="71"/>
+      <c r="AJ36" s="71"/>
+      <c r="AK36" s="71"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="70"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="73"/>
-      <c r="E37" s="73"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="73"/>
-      <c r="J37" s="73"/>
-      <c r="K37" s="80"/>
-      <c r="L37" s="57"/>
-      <c r="M37" s="73"/>
-      <c r="N37" s="74"/>
-      <c r="O37" s="72"/>
-      <c r="P37" s="66"/>
-      <c r="Q37" s="73"/>
-      <c r="R37" s="81"/>
-      <c r="S37" s="81"/>
-      <c r="T37" s="62"/>
-      <c r="U37" s="73"/>
-      <c r="V37" s="74"/>
-      <c r="W37" s="60"/>
-      <c r="X37" s="73"/>
-      <c r="Y37" s="73"/>
-      <c r="Z37" s="74"/>
-      <c r="AA37" s="72"/>
-      <c r="AB37" s="73"/>
-      <c r="AC37" s="73"/>
-      <c r="AD37" s="57"/>
-      <c r="AE37" s="74"/>
-      <c r="AF37" s="72"/>
-      <c r="AG37" s="73"/>
-      <c r="AH37" s="73"/>
-      <c r="AI37" s="73"/>
-      <c r="AJ37" s="73"/>
-      <c r="AK37" s="73"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="72"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="78"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="72"/>
+      <c r="O37" s="70"/>
+      <c r="P37" s="64"/>
+      <c r="Q37" s="71"/>
+      <c r="R37" s="79"/>
+      <c r="S37" s="79"/>
+      <c r="T37" s="60"/>
+      <c r="U37" s="71"/>
+      <c r="V37" s="72"/>
+      <c r="W37" s="58"/>
+      <c r="X37" s="71"/>
+      <c r="Y37" s="71"/>
+      <c r="Z37" s="72"/>
+      <c r="AA37" s="70"/>
+      <c r="AB37" s="71"/>
+      <c r="AC37" s="71"/>
+      <c r="AD37" s="55"/>
+      <c r="AE37" s="72"/>
+      <c r="AF37" s="70"/>
+      <c r="AG37" s="71"/>
+      <c r="AH37" s="71"/>
+      <c r="AI37" s="71"/>
+      <c r="AJ37" s="71"/>
+      <c r="AK37" s="71"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="70"/>
-      <c r="C38" s="79" t="s">
-        <v>162</v>
-      </c>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="72"/>
-      <c r="I38" s="73"/>
-      <c r="J38" s="73"/>
-      <c r="K38" s="73"/>
-      <c r="L38" s="57"/>
-      <c r="M38" s="73"/>
-      <c r="N38" s="74"/>
-      <c r="O38" s="56"/>
-      <c r="P38" s="67"/>
-      <c r="Q38" s="67"/>
-      <c r="R38" s="67"/>
-      <c r="S38" s="67"/>
-      <c r="T38" s="67"/>
-      <c r="U38" s="67"/>
-      <c r="V38" s="55"/>
-      <c r="W38" s="60"/>
-      <c r="X38" s="67"/>
-      <c r="Y38" s="67"/>
-      <c r="Z38" s="74"/>
-      <c r="AA38" s="72"/>
-      <c r="AB38" s="73"/>
-      <c r="AC38" s="73"/>
-      <c r="AD38" s="57"/>
-      <c r="AE38" s="74"/>
-      <c r="AF38" s="72"/>
-      <c r="AG38" s="73"/>
-      <c r="AH38" s="73"/>
-      <c r="AI38" s="73"/>
-      <c r="AJ38" s="73"/>
-      <c r="AK38" s="73"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="77" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="71"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="72"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="71"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="54"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="65"/>
+      <c r="R38" s="65"/>
+      <c r="S38" s="65"/>
+      <c r="T38" s="65"/>
+      <c r="U38" s="65"/>
+      <c r="V38" s="53"/>
+      <c r="W38" s="58"/>
+      <c r="X38" s="65"/>
+      <c r="Y38" s="65"/>
+      <c r="Z38" s="72"/>
+      <c r="AA38" s="70"/>
+      <c r="AB38" s="71"/>
+      <c r="AC38" s="71"/>
+      <c r="AD38" s="55"/>
+      <c r="AE38" s="72"/>
+      <c r="AF38" s="70"/>
+      <c r="AG38" s="71"/>
+      <c r="AH38" s="71"/>
+      <c r="AI38" s="71"/>
+      <c r="AJ38" s="71"/>
+      <c r="AK38" s="71"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="70"/>
-      <c r="C39" s="79"/>
-      <c r="D39" s="73"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="74"/>
-      <c r="H39" s="72"/>
-      <c r="I39" s="73"/>
-      <c r="J39" s="73"/>
-      <c r="K39" s="73"/>
-      <c r="L39" s="57"/>
-      <c r="M39" s="73"/>
-      <c r="N39" s="74"/>
-      <c r="O39" s="72"/>
-      <c r="P39" s="73"/>
-      <c r="Q39" s="73"/>
-      <c r="R39" s="80"/>
-      <c r="S39" s="80"/>
-      <c r="T39" s="73"/>
-      <c r="U39" s="73"/>
-      <c r="V39" s="74"/>
-      <c r="W39" s="60"/>
-      <c r="X39" s="73"/>
-      <c r="Y39" s="73"/>
-      <c r="Z39" s="74"/>
-      <c r="AA39" s="72"/>
-      <c r="AB39" s="73"/>
-      <c r="AC39" s="73"/>
-      <c r="AD39" s="57"/>
-      <c r="AE39" s="74"/>
-      <c r="AF39" s="72"/>
-      <c r="AG39" s="73"/>
-      <c r="AH39" s="73"/>
-      <c r="AI39" s="73"/>
-      <c r="AJ39" s="73"/>
-      <c r="AK39" s="73"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="74"/>
+      <c r="G39" s="72"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="72"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="78"/>
+      <c r="S39" s="78"/>
+      <c r="T39" s="71"/>
+      <c r="U39" s="71"/>
+      <c r="V39" s="72"/>
+      <c r="W39" s="58"/>
+      <c r="X39" s="71"/>
+      <c r="Y39" s="71"/>
+      <c r="Z39" s="72"/>
+      <c r="AA39" s="70"/>
+      <c r="AB39" s="71"/>
+      <c r="AC39" s="71"/>
+      <c r="AD39" s="55"/>
+      <c r="AE39" s="72"/>
+      <c r="AF39" s="70"/>
+      <c r="AG39" s="71"/>
+      <c r="AH39" s="71"/>
+      <c r="AI39" s="71"/>
+      <c r="AJ39" s="71"/>
+      <c r="AK39" s="71"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="70"/>
-      <c r="C40" s="79" t="s">
-        <v>163</v>
-      </c>
-      <c r="D40" s="73"/>
-      <c r="E40" s="73"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="74"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="73"/>
-      <c r="J40" s="73"/>
-      <c r="K40" s="73"/>
-      <c r="L40" s="57"/>
-      <c r="M40" s="73"/>
-      <c r="N40" s="74"/>
-      <c r="O40" s="72"/>
-      <c r="P40" s="73"/>
-      <c r="Q40" s="73"/>
-      <c r="R40" s="67"/>
-      <c r="S40" s="67"/>
-      <c r="T40" s="67"/>
-      <c r="U40" s="67"/>
-      <c r="V40" s="55"/>
-      <c r="W40" s="60"/>
-      <c r="X40" s="67"/>
-      <c r="Y40" s="67"/>
-      <c r="Z40" s="55"/>
-      <c r="AA40" s="56"/>
-      <c r="AB40" s="67"/>
-      <c r="AC40" s="67"/>
-      <c r="AD40" s="57"/>
-      <c r="AE40" s="74"/>
-      <c r="AF40" s="72"/>
-      <c r="AG40" s="73"/>
-      <c r="AH40" s="73"/>
-      <c r="AI40" s="73"/>
-      <c r="AJ40" s="73"/>
-      <c r="AK40" s="73"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="74"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="71"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="70"/>
+      <c r="P40" s="71"/>
+      <c r="Q40" s="71"/>
+      <c r="R40" s="65"/>
+      <c r="S40" s="65"/>
+      <c r="T40" s="65"/>
+      <c r="U40" s="65"/>
+      <c r="V40" s="53"/>
+      <c r="W40" s="58"/>
+      <c r="X40" s="65"/>
+      <c r="Y40" s="65"/>
+      <c r="Z40" s="53"/>
+      <c r="AA40" s="54"/>
+      <c r="AB40" s="65"/>
+      <c r="AC40" s="65"/>
+      <c r="AD40" s="55"/>
+      <c r="AE40" s="72"/>
+      <c r="AF40" s="70"/>
+      <c r="AG40" s="71"/>
+      <c r="AH40" s="71"/>
+      <c r="AI40" s="71"/>
+      <c r="AJ40" s="71"/>
+      <c r="AK40" s="71"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="70"/>
-      <c r="C41" s="79"/>
-      <c r="D41" s="73"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="72"/>
-      <c r="I41" s="73"/>
-      <c r="J41" s="73"/>
-      <c r="K41" s="73"/>
-      <c r="L41" s="57"/>
-      <c r="M41" s="73"/>
-      <c r="N41" s="74"/>
-      <c r="O41" s="72"/>
-      <c r="P41" s="73"/>
-      <c r="Q41" s="66"/>
-      <c r="R41" s="80"/>
-      <c r="S41" s="80"/>
-      <c r="T41" s="66"/>
-      <c r="U41" s="73"/>
-      <c r="V41" s="74"/>
-      <c r="W41" s="60"/>
-      <c r="X41" s="73"/>
-      <c r="Y41" s="73"/>
-      <c r="Z41" s="74"/>
-      <c r="AA41" s="72"/>
-      <c r="AB41" s="73"/>
-      <c r="AC41" s="73"/>
-      <c r="AD41" s="57"/>
-      <c r="AE41" s="74"/>
-      <c r="AF41" s="72"/>
-      <c r="AG41" s="73"/>
-      <c r="AH41" s="73"/>
-      <c r="AI41" s="73"/>
-      <c r="AJ41" s="73"/>
-      <c r="AK41" s="73"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="74"/>
+      <c r="G41" s="72"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="71"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="71"/>
+      <c r="N41" s="72"/>
+      <c r="O41" s="70"/>
+      <c r="P41" s="71"/>
+      <c r="Q41" s="64"/>
+      <c r="R41" s="78"/>
+      <c r="S41" s="78"/>
+      <c r="T41" s="64"/>
+      <c r="U41" s="71"/>
+      <c r="V41" s="72"/>
+      <c r="W41" s="58"/>
+      <c r="X41" s="71"/>
+      <c r="Y41" s="71"/>
+      <c r="Z41" s="72"/>
+      <c r="AA41" s="70"/>
+      <c r="AB41" s="71"/>
+      <c r="AC41" s="71"/>
+      <c r="AD41" s="55"/>
+      <c r="AE41" s="72"/>
+      <c r="AF41" s="70"/>
+      <c r="AG41" s="71"/>
+      <c r="AH41" s="71"/>
+      <c r="AI41" s="71"/>
+      <c r="AJ41" s="71"/>
+      <c r="AK41" s="71"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="51" t="s">
+      <c r="B42" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="82" t="s">
-        <v>164</v>
-      </c>
-      <c r="D42" s="53"/>
-      <c r="E42" s="53"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="53"/>
-      <c r="K42" s="53"/>
-      <c r="L42" s="57"/>
-      <c r="M42" s="53"/>
-      <c r="N42" s="58"/>
-      <c r="O42" s="59"/>
-      <c r="P42" s="67"/>
-      <c r="Q42" s="67"/>
-      <c r="R42" s="53"/>
-      <c r="S42" s="53"/>
-      <c r="T42" s="66"/>
-      <c r="U42" s="53"/>
-      <c r="V42" s="55"/>
-      <c r="W42" s="60"/>
-      <c r="X42" s="67"/>
-      <c r="Y42" s="67"/>
-      <c r="Z42" s="55"/>
-      <c r="AA42" s="56"/>
-      <c r="AB42" s="67"/>
-      <c r="AC42" s="67"/>
-      <c r="AD42" s="57"/>
-      <c r="AE42" s="58"/>
-      <c r="AF42" s="59"/>
-      <c r="AG42" s="53"/>
-      <c r="AH42" s="53"/>
-      <c r="AI42" s="53"/>
-      <c r="AJ42" s="53"/>
-      <c r="AK42" s="53"/>
+      <c r="C42" s="80" t="s">
+        <v>166</v>
+      </c>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="51"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="51"/>
+      <c r="N42" s="56"/>
+      <c r="O42" s="57"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="51"/>
+      <c r="S42" s="51"/>
+      <c r="T42" s="64"/>
+      <c r="U42" s="51"/>
+      <c r="V42" s="53"/>
+      <c r="W42" s="58"/>
+      <c r="X42" s="65"/>
+      <c r="Y42" s="65"/>
+      <c r="Z42" s="53"/>
+      <c r="AA42" s="54"/>
+      <c r="AB42" s="65"/>
+      <c r="AC42" s="65"/>
+      <c r="AD42" s="55"/>
+      <c r="AE42" s="56"/>
+      <c r="AF42" s="57"/>
+      <c r="AG42" s="51"/>
+      <c r="AH42" s="51"/>
+      <c r="AI42" s="51"/>
+      <c r="AJ42" s="51"/>
+      <c r="AK42" s="51"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="51"/>
-      <c r="C43" s="82"/>
-      <c r="D43" s="53"/>
-      <c r="E43" s="53"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="53"/>
-      <c r="J43" s="53"/>
-      <c r="K43" s="53"/>
-      <c r="L43" s="57"/>
-      <c r="M43" s="53"/>
-      <c r="N43" s="58"/>
-      <c r="O43" s="59"/>
-      <c r="P43" s="53"/>
-      <c r="Q43" s="66"/>
-      <c r="R43" s="53"/>
-      <c r="S43" s="68"/>
-      <c r="T43" s="53"/>
-      <c r="U43" s="53"/>
-      <c r="V43" s="58"/>
-      <c r="W43" s="60"/>
-      <c r="X43" s="53"/>
-      <c r="Y43" s="53"/>
-      <c r="Z43" s="58"/>
-      <c r="AA43" s="59"/>
-      <c r="AB43" s="53"/>
-      <c r="AC43" s="53"/>
-      <c r="AD43" s="57"/>
-      <c r="AE43" s="58"/>
-      <c r="AF43" s="59"/>
-      <c r="AG43" s="53"/>
-      <c r="AH43" s="53"/>
-      <c r="AI43" s="53"/>
-      <c r="AJ43" s="53"/>
-      <c r="AK43" s="53"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="80"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="51"/>
+      <c r="K43" s="51"/>
+      <c r="L43" s="55"/>
+      <c r="M43" s="51"/>
+      <c r="N43" s="56"/>
+      <c r="O43" s="57"/>
+      <c r="P43" s="51"/>
+      <c r="Q43" s="64"/>
+      <c r="R43" s="51"/>
+      <c r="S43" s="66"/>
+      <c r="T43" s="51"/>
+      <c r="U43" s="51"/>
+      <c r="V43" s="56"/>
+      <c r="W43" s="58"/>
+      <c r="X43" s="51"/>
+      <c r="Y43" s="51"/>
+      <c r="Z43" s="56"/>
+      <c r="AA43" s="57"/>
+      <c r="AB43" s="51"/>
+      <c r="AC43" s="51"/>
+      <c r="AD43" s="55"/>
+      <c r="AE43" s="56"/>
+      <c r="AF43" s="57"/>
+      <c r="AG43" s="51"/>
+      <c r="AH43" s="51"/>
+      <c r="AI43" s="51"/>
+      <c r="AJ43" s="51"/>
+      <c r="AK43" s="51"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="51"/>
-      <c r="C44" s="82" t="s">
-        <v>165</v>
-      </c>
-      <c r="D44" s="53"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="53"/>
-      <c r="J44" s="53"/>
-      <c r="K44" s="53"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="53"/>
-      <c r="N44" s="58"/>
-      <c r="O44" s="59"/>
-      <c r="P44" s="67"/>
-      <c r="Q44" s="67"/>
-      <c r="R44" s="53"/>
-      <c r="S44" s="53"/>
-      <c r="T44" s="53"/>
-      <c r="U44" s="53"/>
-      <c r="V44" s="58"/>
-      <c r="W44" s="60"/>
-      <c r="X44" s="67"/>
-      <c r="Y44" s="67"/>
-      <c r="Z44" s="58"/>
-      <c r="AA44" s="59"/>
-      <c r="AB44" s="53"/>
-      <c r="AC44" s="67"/>
-      <c r="AD44" s="57"/>
-      <c r="AE44" s="55"/>
-      <c r="AF44" s="56"/>
-      <c r="AG44" s="53"/>
-      <c r="AH44" s="53"/>
-      <c r="AI44" s="67"/>
-      <c r="AJ44" s="53"/>
-      <c r="AK44" s="53"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="80" t="s">
+        <v>167</v>
+      </c>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="51"/>
+      <c r="K44" s="51"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="51"/>
+      <c r="N44" s="56"/>
+      <c r="O44" s="57"/>
+      <c r="P44" s="65"/>
+      <c r="Q44" s="65"/>
+      <c r="R44" s="51"/>
+      <c r="S44" s="51"/>
+      <c r="T44" s="51"/>
+      <c r="U44" s="51"/>
+      <c r="V44" s="56"/>
+      <c r="W44" s="58"/>
+      <c r="X44" s="65"/>
+      <c r="Y44" s="65"/>
+      <c r="Z44" s="56"/>
+      <c r="AA44" s="57"/>
+      <c r="AB44" s="51"/>
+      <c r="AC44" s="65"/>
+      <c r="AD44" s="55"/>
+      <c r="AE44" s="53"/>
+      <c r="AF44" s="54"/>
+      <c r="AG44" s="51"/>
+      <c r="AH44" s="51"/>
+      <c r="AI44" s="65"/>
+      <c r="AJ44" s="51"/>
+      <c r="AK44" s="51"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="51"/>
-      <c r="C45" s="82"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="53"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="53"/>
-      <c r="J45" s="53"/>
-      <c r="K45" s="53"/>
-      <c r="L45" s="57"/>
-      <c r="M45" s="53"/>
-      <c r="N45" s="58"/>
-      <c r="O45" s="59"/>
-      <c r="P45" s="53"/>
-      <c r="Q45" s="53"/>
-      <c r="R45" s="53"/>
-      <c r="S45" s="53"/>
-      <c r="T45" s="53"/>
-      <c r="U45" s="53"/>
-      <c r="V45" s="58"/>
-      <c r="W45" s="60"/>
-      <c r="X45" s="53"/>
-      <c r="Y45" s="66"/>
-      <c r="Z45" s="83"/>
-      <c r="AA45" s="59"/>
-      <c r="AB45" s="53"/>
-      <c r="AC45" s="53"/>
-      <c r="AD45" s="57"/>
-      <c r="AE45" s="58"/>
-      <c r="AF45" s="59"/>
-      <c r="AG45" s="53"/>
-      <c r="AH45" s="53"/>
-      <c r="AI45" s="53"/>
-      <c r="AJ45" s="53"/>
-      <c r="AK45" s="53"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="80"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="51"/>
+      <c r="K45" s="51"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="51"/>
+      <c r="N45" s="56"/>
+      <c r="O45" s="57"/>
+      <c r="P45" s="51"/>
+      <c r="Q45" s="51"/>
+      <c r="R45" s="51"/>
+      <c r="S45" s="51"/>
+      <c r="T45" s="51"/>
+      <c r="U45" s="51"/>
+      <c r="V45" s="56"/>
+      <c r="W45" s="58"/>
+      <c r="X45" s="51"/>
+      <c r="Y45" s="64"/>
+      <c r="Z45" s="81"/>
+      <c r="AA45" s="57"/>
+      <c r="AB45" s="51"/>
+      <c r="AC45" s="51"/>
+      <c r="AD45" s="55"/>
+      <c r="AE45" s="56"/>
+      <c r="AF45" s="57"/>
+      <c r="AG45" s="51"/>
+      <c r="AH45" s="51"/>
+      <c r="AI45" s="51"/>
+      <c r="AJ45" s="51"/>
+      <c r="AK45" s="51"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="70" t="s">
-        <v>166</v>
-      </c>
-      <c r="C46" s="71" t="s">
+      <c r="B46" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="C46" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="74"/>
-      <c r="H46" s="72"/>
-      <c r="I46" s="73"/>
-      <c r="J46" s="73"/>
-      <c r="K46" s="73"/>
-      <c r="L46" s="57"/>
-      <c r="M46" s="73"/>
-      <c r="N46" s="74"/>
-      <c r="O46" s="72"/>
-      <c r="P46" s="73"/>
-      <c r="Q46" s="73"/>
-      <c r="R46" s="73"/>
-      <c r="S46" s="73"/>
-      <c r="T46" s="73"/>
-      <c r="U46" s="73"/>
-      <c r="V46" s="74"/>
-      <c r="W46" s="60"/>
-      <c r="X46" s="73"/>
-      <c r="Y46" s="73"/>
-      <c r="Z46" s="74"/>
-      <c r="AA46" s="72"/>
-      <c r="AB46" s="73"/>
-      <c r="AC46" s="73"/>
-      <c r="AD46" s="57"/>
-      <c r="AE46" s="74"/>
-      <c r="AF46" s="72"/>
-      <c r="AG46" s="73"/>
-      <c r="AH46" s="73"/>
-      <c r="AI46" s="73"/>
-      <c r="AJ46" s="67"/>
-      <c r="AK46" s="73"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="72"/>
+      <c r="H46" s="70"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="71"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="71"/>
+      <c r="N46" s="72"/>
+      <c r="O46" s="70"/>
+      <c r="P46" s="71"/>
+      <c r="Q46" s="71"/>
+      <c r="R46" s="71"/>
+      <c r="S46" s="71"/>
+      <c r="T46" s="71"/>
+      <c r="U46" s="71"/>
+      <c r="V46" s="72"/>
+      <c r="W46" s="58"/>
+      <c r="X46" s="71"/>
+      <c r="Y46" s="71"/>
+      <c r="Z46" s="72"/>
+      <c r="AA46" s="70"/>
+      <c r="AB46" s="71"/>
+      <c r="AC46" s="71"/>
+      <c r="AD46" s="55"/>
+      <c r="AE46" s="72"/>
+      <c r="AF46" s="70"/>
+      <c r="AG46" s="71"/>
+      <c r="AH46" s="71"/>
+      <c r="AI46" s="71"/>
+      <c r="AJ46" s="65"/>
+      <c r="AK46" s="71"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="70"/>
-      <c r="C47" s="71"/>
-      <c r="D47" s="73"/>
-      <c r="E47" s="73"/>
-      <c r="F47" s="76"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="72"/>
-      <c r="I47" s="73"/>
-      <c r="J47" s="73"/>
-      <c r="K47" s="73"/>
-      <c r="L47" s="57"/>
-      <c r="M47" s="73"/>
-      <c r="N47" s="74"/>
-      <c r="O47" s="72"/>
-      <c r="P47" s="73"/>
-      <c r="Q47" s="73"/>
-      <c r="R47" s="73"/>
-      <c r="S47" s="73"/>
-      <c r="T47" s="73"/>
-      <c r="U47" s="73"/>
-      <c r="V47" s="74"/>
-      <c r="W47" s="60"/>
-      <c r="X47" s="73"/>
-      <c r="Y47" s="73"/>
-      <c r="Z47" s="74"/>
-      <c r="AA47" s="72"/>
-      <c r="AB47" s="73"/>
-      <c r="AC47" s="73"/>
-      <c r="AD47" s="57"/>
-      <c r="AE47" s="74"/>
-      <c r="AF47" s="72"/>
-      <c r="AG47" s="73"/>
-      <c r="AH47" s="73"/>
-      <c r="AI47" s="73"/>
-      <c r="AJ47" s="73"/>
-      <c r="AK47" s="73"/>
-      <c r="AN47" s="84" t="s">
-        <v>167</v>
-      </c>
-      <c r="AO47" s="67"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="71"/>
+      <c r="E47" s="71"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="72"/>
+      <c r="H47" s="70"/>
+      <c r="I47" s="71"/>
+      <c r="J47" s="71"/>
+      <c r="K47" s="71"/>
+      <c r="L47" s="55"/>
+      <c r="M47" s="71"/>
+      <c r="N47" s="72"/>
+      <c r="O47" s="70"/>
+      <c r="P47" s="71"/>
+      <c r="Q47" s="71"/>
+      <c r="R47" s="71"/>
+      <c r="S47" s="71"/>
+      <c r="T47" s="71"/>
+      <c r="U47" s="71"/>
+      <c r="V47" s="72"/>
+      <c r="W47" s="58"/>
+      <c r="X47" s="71"/>
+      <c r="Y47" s="71"/>
+      <c r="Z47" s="72"/>
+      <c r="AA47" s="70"/>
+      <c r="AB47" s="71"/>
+      <c r="AC47" s="71"/>
+      <c r="AD47" s="55"/>
+      <c r="AE47" s="72"/>
+      <c r="AF47" s="70"/>
+      <c r="AG47" s="71"/>
+      <c r="AH47" s="71"/>
+      <c r="AI47" s="71"/>
+      <c r="AJ47" s="71"/>
+      <c r="AK47" s="71"/>
+      <c r="AN47" s="82" t="s">
+        <v>169</v>
+      </c>
+      <c r="AO47" s="65"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="70"/>
-      <c r="C48" s="71" t="s">
-        <v>168</v>
-      </c>
-      <c r="D48" s="73"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="74"/>
-      <c r="H48" s="72"/>
-      <c r="I48" s="73"/>
-      <c r="J48" s="73"/>
-      <c r="K48" s="73"/>
-      <c r="L48" s="57"/>
-      <c r="M48" s="73"/>
-      <c r="N48" s="74"/>
-      <c r="O48" s="72"/>
-      <c r="P48" s="73"/>
-      <c r="Q48" s="73"/>
-      <c r="R48" s="73"/>
-      <c r="S48" s="73"/>
-      <c r="T48" s="73"/>
-      <c r="U48" s="73"/>
-      <c r="V48" s="74"/>
-      <c r="W48" s="60"/>
-      <c r="X48" s="73"/>
-      <c r="Y48" s="73"/>
-      <c r="Z48" s="74"/>
-      <c r="AA48" s="72"/>
-      <c r="AB48" s="73"/>
-      <c r="AC48" s="73"/>
-      <c r="AD48" s="57"/>
-      <c r="AE48" s="74"/>
-      <c r="AF48" s="72"/>
-      <c r="AG48" s="73"/>
-      <c r="AH48" s="73"/>
-      <c r="AI48" s="73"/>
-      <c r="AJ48" s="73"/>
-      <c r="AK48" s="85"/>
-      <c r="AN48" s="84" t="s">
-        <v>169</v>
-      </c>
-      <c r="AO48" s="66"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="69" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" s="71"/>
+      <c r="E48" s="71"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="72"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="71"/>
+      <c r="J48" s="71"/>
+      <c r="K48" s="71"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="71"/>
+      <c r="N48" s="72"/>
+      <c r="O48" s="70"/>
+      <c r="P48" s="71"/>
+      <c r="Q48" s="71"/>
+      <c r="R48" s="71"/>
+      <c r="S48" s="71"/>
+      <c r="T48" s="71"/>
+      <c r="U48" s="71"/>
+      <c r="V48" s="72"/>
+      <c r="W48" s="58"/>
+      <c r="X48" s="71"/>
+      <c r="Y48" s="71"/>
+      <c r="Z48" s="72"/>
+      <c r="AA48" s="70"/>
+      <c r="AB48" s="71"/>
+      <c r="AC48" s="71"/>
+      <c r="AD48" s="55"/>
+      <c r="AE48" s="72"/>
+      <c r="AF48" s="70"/>
+      <c r="AG48" s="71"/>
+      <c r="AH48" s="71"/>
+      <c r="AI48" s="71"/>
+      <c r="AJ48" s="71"/>
+      <c r="AK48" s="83"/>
+      <c r="AN48" s="82" t="s">
+        <v>171</v>
+      </c>
+      <c r="AO48" s="64"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="70"/>
-      <c r="C49" s="71"/>
-      <c r="D49" s="73"/>
-      <c r="E49" s="73"/>
-      <c r="F49" s="76"/>
-      <c r="G49" s="74"/>
-      <c r="H49" s="72"/>
-      <c r="I49" s="73"/>
-      <c r="J49" s="73"/>
-      <c r="K49" s="73"/>
-      <c r="L49" s="57"/>
-      <c r="M49" s="73"/>
-      <c r="N49" s="74"/>
-      <c r="O49" s="72"/>
-      <c r="P49" s="73"/>
-      <c r="Q49" s="73"/>
-      <c r="R49" s="73"/>
-      <c r="S49" s="73"/>
-      <c r="T49" s="73"/>
-      <c r="U49" s="73"/>
-      <c r="V49" s="74"/>
-      <c r="W49" s="60"/>
-      <c r="X49" s="73"/>
-      <c r="Y49" s="73"/>
-      <c r="Z49" s="74"/>
-      <c r="AA49" s="72"/>
-      <c r="AB49" s="73"/>
-      <c r="AC49" s="73"/>
-      <c r="AD49" s="57"/>
-      <c r="AE49" s="74"/>
-      <c r="AF49" s="72"/>
-      <c r="AG49" s="73"/>
-      <c r="AH49" s="73"/>
-      <c r="AI49" s="73"/>
-      <c r="AJ49" s="73"/>
-      <c r="AK49" s="73"/>
-      <c r="AN49" s="84" t="s">
-        <v>170</v>
-      </c>
-      <c r="AO49" s="62"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="69"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="72"/>
+      <c r="H49" s="70"/>
+      <c r="I49" s="71"/>
+      <c r="J49" s="71"/>
+      <c r="K49" s="71"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="71"/>
+      <c r="N49" s="72"/>
+      <c r="O49" s="70"/>
+      <c r="P49" s="71"/>
+      <c r="Q49" s="71"/>
+      <c r="R49" s="71"/>
+      <c r="S49" s="71"/>
+      <c r="T49" s="71"/>
+      <c r="U49" s="71"/>
+      <c r="V49" s="72"/>
+      <c r="W49" s="58"/>
+      <c r="X49" s="71"/>
+      <c r="Y49" s="71"/>
+      <c r="Z49" s="72"/>
+      <c r="AA49" s="70"/>
+      <c r="AB49" s="71"/>
+      <c r="AC49" s="71"/>
+      <c r="AD49" s="55"/>
+      <c r="AE49" s="72"/>
+      <c r="AF49" s="70"/>
+      <c r="AG49" s="71"/>
+      <c r="AH49" s="71"/>
+      <c r="AI49" s="71"/>
+      <c r="AJ49" s="71"/>
+      <c r="AK49" s="71"/>
+      <c r="AN49" s="82" t="s">
+        <v>172</v>
+      </c>
+      <c r="AO49" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -11085,801 +11101,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="86"/>
+      <c r="B1" s="84"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="87" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="88" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="89" t="s">
-        <v>171</v>
-      </c>
-      <c r="E2" s="90" t="s">
-        <v>172</v>
-      </c>
-      <c r="F2" s="91" t="s">
+      <c r="B2" s="85" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="87" t="s">
         <v>173</v>
       </c>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="91" t="s">
+      <c r="E2" s="88" t="s">
         <v>174</v>
       </c>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="91" t="s">
-        <v>109</v>
-      </c>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="90"/>
-      <c r="R2" s="91" t="s">
-        <v>110</v>
-      </c>
-      <c r="S2" s="92"/>
-      <c r="AD2" s="93"/>
+      <c r="F2" s="89" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="89" t="s">
+        <v>176</v>
+      </c>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="O2" s="89"/>
+      <c r="P2" s="89"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="89" t="s">
+        <v>112</v>
+      </c>
+      <c r="S2" s="90"/>
+      <c r="AD2" s="91"/>
     </row>
     <row r="3">
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="E3" s="97">
+      <c r="B3" s="92"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="94" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" s="95">
         <v>4</v>
       </c>
-      <c r="F3" s="98">
+      <c r="F3" s="96">
         <v>1</v>
       </c>
-      <c r="G3" s="99">
+      <c r="G3" s="97">
         <v>2</v>
       </c>
-      <c r="H3" s="99">
+      <c r="H3" s="97">
         <v>3</v>
       </c>
-      <c r="I3" s="97">
+      <c r="I3" s="95">
         <v>4</v>
       </c>
-      <c r="J3" s="98">
+      <c r="J3" s="96">
         <v>1</v>
       </c>
-      <c r="K3" s="99">
+      <c r="K3" s="97">
         <v>2</v>
       </c>
-      <c r="L3" s="99">
+      <c r="L3" s="97">
         <v>3</v>
       </c>
-      <c r="M3" s="97">
+      <c r="M3" s="95">
         <v>4</v>
       </c>
-      <c r="N3" s="98">
+      <c r="N3" s="96">
         <v>1</v>
       </c>
-      <c r="O3" s="99">
+      <c r="O3" s="97">
         <v>2</v>
       </c>
-      <c r="P3" s="99">
+      <c r="P3" s="97">
         <v>3</v>
       </c>
-      <c r="Q3" s="97">
+      <c r="Q3" s="95">
         <v>4</v>
       </c>
-      <c r="R3" s="98">
+      <c r="R3" s="96">
         <v>1</v>
       </c>
-      <c r="S3" s="100">
+      <c r="S3" s="98">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="101" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4" s="88" t="s">
-        <v>178</v>
-      </c>
-      <c r="D4" s="102"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="103"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="103"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="105"/>
-      <c r="P4" s="105"/>
-      <c r="Q4" s="103"/>
-      <c r="R4" s="106"/>
-      <c r="S4" s="107"/>
+      <c r="B4" s="99" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="86" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="100"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="104"/>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="104"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="101"/>
+      <c r="R4" s="104"/>
+      <c r="S4" s="105"/>
       <c r="U4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="101"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="112"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="114"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="114"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="114"/>
-      <c r="S5" s="115"/>
+      <c r="B5" s="99"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="111"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="112"/>
+      <c r="O5" s="111"/>
+      <c r="P5" s="111"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="112"/>
+      <c r="S5" s="113"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="101"/>
-      <c r="C6" s="116" t="s">
-        <v>180</v>
-      </c>
-      <c r="D6" s="117"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="121"/>
-      <c r="M6" s="118"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="121"/>
-      <c r="P6" s="121"/>
-      <c r="Q6" s="118"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="123"/>
-      <c r="U6" s="124" t="s">
-        <v>181</v>
-      </c>
-      <c r="V6" s="124"/>
+      <c r="B6" s="99"/>
+      <c r="C6" s="114" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="115"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="118"/>
+      <c r="H6" s="119"/>
+      <c r="I6" s="116"/>
+      <c r="J6" s="120"/>
+      <c r="K6" s="119"/>
+      <c r="L6" s="119"/>
+      <c r="M6" s="116"/>
+      <c r="N6" s="120"/>
+      <c r="O6" s="119"/>
+      <c r="P6" s="119"/>
+      <c r="Q6" s="116"/>
+      <c r="R6" s="120"/>
+      <c r="S6" s="121"/>
+      <c r="U6" s="122" t="s">
+        <v>183</v>
+      </c>
+      <c r="V6" s="122"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="101"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="109"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="114"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="114"/>
-      <c r="K7" s="113"/>
-      <c r="L7" s="113"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="114"/>
-      <c r="O7" s="113"/>
-      <c r="P7" s="113"/>
-      <c r="Q7" s="110"/>
-      <c r="R7" s="114"/>
-      <c r="S7" s="115"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="108"/>
+      <c r="N7" s="112"/>
+      <c r="O7" s="111"/>
+      <c r="P7" s="111"/>
+      <c r="Q7" s="108"/>
+      <c r="R7" s="112"/>
+      <c r="S7" s="113"/>
       <c r="U7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="101"/>
-      <c r="C8" s="116" t="s">
-        <v>183</v>
-      </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="118"/>
-      <c r="J8" s="122"/>
-      <c r="K8" s="121"/>
-      <c r="L8" s="121"/>
-      <c r="M8" s="118"/>
-      <c r="N8" s="122"/>
-      <c r="O8" s="121"/>
-      <c r="P8" s="121"/>
-      <c r="Q8" s="118"/>
-      <c r="R8" s="122"/>
-      <c r="S8" s="123"/>
+      <c r="B8" s="99"/>
+      <c r="C8" s="114" t="s">
+        <v>185</v>
+      </c>
+      <c r="D8" s="115"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="119"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="120"/>
+      <c r="K8" s="119"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="116"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="119"/>
+      <c r="P8" s="119"/>
+      <c r="Q8" s="116"/>
+      <c r="R8" s="120"/>
+      <c r="S8" s="121"/>
       <c r="U8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="101"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="109"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="114"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="113"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="114"/>
-      <c r="K9" s="113"/>
-      <c r="L9" s="113"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="114"/>
-      <c r="O9" s="113"/>
-      <c r="P9" s="113"/>
-      <c r="Q9" s="110"/>
-      <c r="R9" s="114"/>
-      <c r="S9" s="115"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="111"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="112"/>
+      <c r="O9" s="111"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="108"/>
+      <c r="R9" s="112"/>
+      <c r="S9" s="113"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="101"/>
-      <c r="C10" s="116" t="s">
-        <v>185</v>
-      </c>
-      <c r="D10" s="117"/>
-      <c r="E10" s="118"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="118"/>
-      <c r="J10" s="122"/>
-      <c r="K10" s="121"/>
-      <c r="L10" s="121"/>
-      <c r="M10" s="118"/>
-      <c r="N10" s="122"/>
-      <c r="O10" s="121"/>
-      <c r="P10" s="121"/>
-      <c r="Q10" s="118"/>
-      <c r="R10" s="122"/>
-      <c r="S10" s="123"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="114" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" s="115"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="120"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="116"/>
+      <c r="N10" s="120"/>
+      <c r="O10" s="119"/>
+      <c r="P10" s="119"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="120"/>
+      <c r="S10" s="121"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="125"/>
-      <c r="C11" s="126"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="128"/>
-      <c r="J11" s="129"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="131"/>
-      <c r="M11" s="128"/>
-      <c r="N11" s="129"/>
-      <c r="O11" s="131"/>
-      <c r="P11" s="131"/>
-      <c r="Q11" s="128"/>
-      <c r="R11" s="129"/>
-      <c r="S11" s="132"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="126"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="129"/>
+      <c r="P11" s="129"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="127"/>
+      <c r="S11" s="130"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="87" t="s">
-        <v>186</v>
-      </c>
-      <c r="C12" s="88" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="102"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="105"/>
-      <c r="H12" s="133"/>
-      <c r="I12" s="134"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="105"/>
-      <c r="L12" s="105"/>
-      <c r="M12" s="103"/>
-      <c r="N12" s="106"/>
-      <c r="O12" s="105"/>
-      <c r="P12" s="105"/>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="106"/>
-      <c r="S12" s="107"/>
+      <c r="B12" s="85" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="100"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="132"/>
+      <c r="J12" s="104"/>
+      <c r="K12" s="103"/>
+      <c r="L12" s="103"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="104"/>
+      <c r="O12" s="103"/>
+      <c r="P12" s="103"/>
+      <c r="Q12" s="101"/>
+      <c r="R12" s="104"/>
+      <c r="S12" s="105"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="101"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="109"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="114"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="113"/>
-      <c r="L13" s="113"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="114"/>
-      <c r="O13" s="113"/>
-      <c r="P13" s="113"/>
-      <c r="Q13" s="110"/>
-      <c r="R13" s="114"/>
-      <c r="S13" s="115"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="109"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="108"/>
+      <c r="N13" s="112"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="108"/>
+      <c r="R13" s="112"/>
+      <c r="S13" s="113"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="101"/>
-      <c r="C14" s="116" t="s">
-        <v>188</v>
-      </c>
-      <c r="D14" s="135"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="120"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="122"/>
-      <c r="K14" s="121"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="118"/>
-      <c r="N14" s="122"/>
-      <c r="O14" s="121"/>
-      <c r="P14" s="121"/>
-      <c r="Q14" s="118"/>
-      <c r="R14" s="122"/>
-      <c r="S14" s="123"/>
+      <c r="B14" s="99"/>
+      <c r="C14" s="114" t="s">
+        <v>190</v>
+      </c>
+      <c r="D14" s="133"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="120"/>
+      <c r="K14" s="119"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="116"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="119"/>
+      <c r="P14" s="119"/>
+      <c r="Q14" s="116"/>
+      <c r="R14" s="120"/>
+      <c r="S14" s="121"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="101"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="114"/>
-      <c r="G15" s="113"/>
-      <c r="H15" s="113"/>
-      <c r="I15" s="136"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="113"/>
-      <c r="L15" s="113"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="113"/>
-      <c r="P15" s="113"/>
-      <c r="Q15" s="110"/>
-      <c r="R15" s="114"/>
-      <c r="S15" s="115"/>
+      <c r="B15" s="99"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="111"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="109"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="108"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="108"/>
+      <c r="R15" s="112"/>
+      <c r="S15" s="113"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="101"/>
-      <c r="C16" s="116" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" s="117"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="121"/>
-      <c r="H16" s="120"/>
-      <c r="I16" s="137"/>
-      <c r="J16" s="122"/>
-      <c r="K16" s="121"/>
-      <c r="L16" s="121"/>
-      <c r="M16" s="118"/>
-      <c r="N16" s="122"/>
-      <c r="O16" s="121"/>
-      <c r="P16" s="121"/>
-      <c r="Q16" s="118"/>
-      <c r="R16" s="122"/>
-      <c r="S16" s="123"/>
+      <c r="B16" s="99"/>
+      <c r="C16" s="114" t="s">
+        <v>191</v>
+      </c>
+      <c r="D16" s="115"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="116"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="119"/>
+      <c r="P16" s="119"/>
+      <c r="Q16" s="116"/>
+      <c r="R16" s="120"/>
+      <c r="S16" s="121"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="125"/>
-      <c r="C17" s="126"/>
-      <c r="D17" s="127"/>
-      <c r="E17" s="128"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="131"/>
-      <c r="H17" s="131"/>
-      <c r="I17" s="128"/>
-      <c r="J17" s="138"/>
-      <c r="K17" s="130"/>
-      <c r="L17" s="131"/>
-      <c r="M17" s="128"/>
-      <c r="N17" s="129"/>
-      <c r="O17" s="131"/>
-      <c r="P17" s="131"/>
-      <c r="Q17" s="128"/>
-      <c r="R17" s="129"/>
-      <c r="S17" s="132"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="125"/>
+      <c r="E17" s="126"/>
+      <c r="F17" s="127"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="129"/>
+      <c r="I17" s="126"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="128"/>
+      <c r="L17" s="129"/>
+      <c r="M17" s="126"/>
+      <c r="N17" s="127"/>
+      <c r="O17" s="129"/>
+      <c r="P17" s="129"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="127"/>
+      <c r="S17" s="130"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="89" t="s">
-        <v>190</v>
-      </c>
-      <c r="C18" s="88" t="s">
-        <v>191</v>
-      </c>
-      <c r="D18" s="102"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="105"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="105"/>
-      <c r="L18" s="105"/>
-      <c r="M18" s="103"/>
-      <c r="N18" s="106"/>
-      <c r="O18" s="105"/>
-      <c r="P18" s="105"/>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="106"/>
-      <c r="S18" s="107"/>
+      <c r="B18" s="87" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" s="100"/>
+      <c r="E18" s="101"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="104"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="101"/>
+      <c r="N18" s="104"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="101"/>
+      <c r="R18" s="104"/>
+      <c r="S18" s="105"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="101"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="109"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="114"/>
-      <c r="G19" s="112"/>
-      <c r="H19" s="113"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="114"/>
-      <c r="K19" s="113"/>
-      <c r="L19" s="113"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="114"/>
-      <c r="O19" s="113"/>
-      <c r="P19" s="113"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="114"/>
-      <c r="S19" s="115"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="106"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="111"/>
+      <c r="I19" s="108"/>
+      <c r="J19" s="112"/>
+      <c r="K19" s="111"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="108"/>
+      <c r="N19" s="112"/>
+      <c r="O19" s="111"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="108"/>
+      <c r="R19" s="112"/>
+      <c r="S19" s="113"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="101"/>
-      <c r="C20" s="116" t="s">
-        <v>192</v>
-      </c>
-      <c r="D20" s="117"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="121"/>
-      <c r="H20" s="121"/>
-      <c r="I20" s="137"/>
-      <c r="J20" s="119"/>
-      <c r="K20" s="120"/>
-      <c r="L20" s="120"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="122"/>
-      <c r="O20" s="121"/>
-      <c r="P20" s="121"/>
-      <c r="Q20" s="118"/>
-      <c r="R20" s="122"/>
-      <c r="S20" s="123"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="114" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" s="115"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="135"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="118"/>
+      <c r="L20" s="118"/>
+      <c r="M20" s="116"/>
+      <c r="N20" s="120"/>
+      <c r="O20" s="119"/>
+      <c r="P20" s="119"/>
+      <c r="Q20" s="116"/>
+      <c r="R20" s="120"/>
+      <c r="S20" s="121"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="101"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="109"/>
-      <c r="E21" s="110"/>
-      <c r="F21" s="114"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="110"/>
-      <c r="J21" s="114"/>
-      <c r="K21" s="113"/>
-      <c r="L21" s="113"/>
-      <c r="M21" s="110"/>
-      <c r="N21" s="139"/>
-      <c r="O21" s="113"/>
-      <c r="P21" s="113"/>
-      <c r="Q21" s="110"/>
-      <c r="R21" s="114"/>
-      <c r="S21" s="115"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="111"/>
+      <c r="I21" s="108"/>
+      <c r="J21" s="112"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="108"/>
+      <c r="N21" s="137"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="108"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="113"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="101"/>
-      <c r="C22" s="116" t="s">
-        <v>193</v>
-      </c>
-      <c r="D22" s="117"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="122"/>
-      <c r="G22" s="121"/>
-      <c r="H22" s="121"/>
-      <c r="I22" s="118"/>
-      <c r="J22" s="122"/>
-      <c r="K22" s="120"/>
-      <c r="L22" s="120"/>
-      <c r="M22" s="118"/>
-      <c r="N22" s="122"/>
-      <c r="O22" s="121"/>
-      <c r="P22" s="121"/>
-      <c r="Q22" s="118"/>
-      <c r="R22" s="122"/>
-      <c r="S22" s="123"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="114" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" s="115"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="116"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="118"/>
+      <c r="M22" s="116"/>
+      <c r="N22" s="120"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="119"/>
+      <c r="Q22" s="116"/>
+      <c r="R22" s="120"/>
+      <c r="S22" s="121"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="125"/>
-      <c r="C23" s="126"/>
-      <c r="D23" s="127"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="129"/>
-      <c r="G23" s="131"/>
-      <c r="H23" s="131"/>
-      <c r="I23" s="128"/>
-      <c r="J23" s="129"/>
-      <c r="K23" s="131"/>
-      <c r="L23" s="131"/>
-      <c r="M23" s="128"/>
-      <c r="N23" s="129"/>
-      <c r="O23" s="131"/>
-      <c r="P23" s="131"/>
-      <c r="Q23" s="128"/>
-      <c r="R23" s="129"/>
-      <c r="S23" s="132"/>
+      <c r="B23" s="123"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="125"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="126"/>
+      <c r="J23" s="127"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="129"/>
+      <c r="M23" s="126"/>
+      <c r="N23" s="127"/>
+      <c r="O23" s="129"/>
+      <c r="P23" s="129"/>
+      <c r="Q23" s="126"/>
+      <c r="R23" s="127"/>
+      <c r="S23" s="130"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="89" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24" s="88" t="s">
-        <v>195</v>
-      </c>
-      <c r="D24" s="102"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="106"/>
-      <c r="G24" s="105"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="103"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="105"/>
-      <c r="L24" s="105"/>
-      <c r="M24" s="134"/>
-      <c r="N24" s="104"/>
-      <c r="O24" s="133"/>
-      <c r="P24" s="133"/>
-      <c r="Q24" s="103"/>
-      <c r="R24" s="106"/>
-      <c r="S24" s="107"/>
+      <c r="B24" s="87" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" s="86" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" s="100"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="104"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="104"/>
+      <c r="K24" s="103"/>
+      <c r="L24" s="103"/>
+      <c r="M24" s="132"/>
+      <c r="N24" s="102"/>
+      <c r="O24" s="131"/>
+      <c r="P24" s="131"/>
+      <c r="Q24" s="101"/>
+      <c r="R24" s="104"/>
+      <c r="S24" s="105"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="101"/>
-      <c r="C25" s="108"/>
-      <c r="D25" s="109"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="114"/>
-      <c r="G25" s="113"/>
-      <c r="H25" s="113"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="114"/>
-      <c r="K25" s="113"/>
-      <c r="L25" s="113"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="114"/>
-      <c r="O25" s="113"/>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="110"/>
-      <c r="R25" s="114"/>
-      <c r="S25" s="115"/>
+      <c r="B25" s="99"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="111"/>
+      <c r="L25" s="111"/>
+      <c r="M25" s="108"/>
+      <c r="N25" s="112"/>
+      <c r="O25" s="111"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="108"/>
+      <c r="R25" s="112"/>
+      <c r="S25" s="113"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="101"/>
-      <c r="C26" s="116" t="s">
-        <v>196</v>
-      </c>
-      <c r="D26" s="117"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="122"/>
-      <c r="G26" s="121"/>
-      <c r="H26" s="121"/>
-      <c r="I26" s="118"/>
-      <c r="J26" s="122"/>
-      <c r="K26" s="121"/>
-      <c r="L26" s="121"/>
-      <c r="M26" s="118"/>
-      <c r="N26" s="122"/>
-      <c r="O26" s="120"/>
-      <c r="P26" s="120"/>
-      <c r="Q26" s="118"/>
-      <c r="R26" s="122"/>
-      <c r="S26" s="123"/>
+      <c r="B26" s="99"/>
+      <c r="C26" s="114" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="115"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
+      <c r="M26" s="116"/>
+      <c r="N26" s="120"/>
+      <c r="O26" s="118"/>
+      <c r="P26" s="118"/>
+      <c r="Q26" s="116"/>
+      <c r="R26" s="120"/>
+      <c r="S26" s="121"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="101"/>
-      <c r="C27" s="108"/>
-      <c r="D27" s="109"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="114"/>
-      <c r="G27" s="113"/>
-      <c r="H27" s="113"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="114"/>
-      <c r="K27" s="113"/>
-      <c r="L27" s="113"/>
-      <c r="M27" s="110"/>
-      <c r="N27" s="114"/>
-      <c r="O27" s="113"/>
-      <c r="P27" s="113"/>
-      <c r="Q27" s="110"/>
-      <c r="R27" s="114"/>
-      <c r="S27" s="115"/>
+      <c r="B27" s="99"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="108"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="108"/>
+      <c r="J27" s="112"/>
+      <c r="K27" s="111"/>
+      <c r="L27" s="111"/>
+      <c r="M27" s="108"/>
+      <c r="N27" s="112"/>
+      <c r="O27" s="111"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="108"/>
+      <c r="R27" s="112"/>
+      <c r="S27" s="113"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="101"/>
-      <c r="C28" s="116" t="s">
-        <v>197</v>
-      </c>
-      <c r="D28" s="117"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="122"/>
-      <c r="G28" s="121"/>
-      <c r="H28" s="121"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="122"/>
-      <c r="K28" s="121"/>
-      <c r="L28" s="121"/>
-      <c r="M28" s="118"/>
-      <c r="N28" s="122"/>
-      <c r="O28" s="121"/>
-      <c r="P28" s="120"/>
-      <c r="Q28" s="137"/>
-      <c r="R28" s="122"/>
-      <c r="S28" s="123"/>
+      <c r="B28" s="99"/>
+      <c r="C28" s="114" t="s">
+        <v>199</v>
+      </c>
+      <c r="D28" s="115"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="119"/>
+      <c r="H28" s="119"/>
+      <c r="I28" s="116"/>
+      <c r="J28" s="120"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="119"/>
+      <c r="M28" s="116"/>
+      <c r="N28" s="120"/>
+      <c r="O28" s="119"/>
+      <c r="P28" s="118"/>
+      <c r="Q28" s="135"/>
+      <c r="R28" s="120"/>
+      <c r="S28" s="121"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="101"/>
-      <c r="C29" s="95"/>
-      <c r="D29" s="140"/>
-      <c r="E29" s="141"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="143"/>
-      <c r="H29" s="144"/>
-      <c r="I29" s="141"/>
-      <c r="J29" s="142"/>
-      <c r="K29" s="143"/>
-      <c r="L29" s="144"/>
-      <c r="M29" s="141"/>
-      <c r="N29" s="145"/>
-      <c r="O29" s="144"/>
-      <c r="P29" s="143"/>
-      <c r="Q29" s="141"/>
-      <c r="R29" s="142"/>
-      <c r="S29" s="146"/>
+      <c r="B29" s="99"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="140"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="142"/>
+      <c r="I29" s="139"/>
+      <c r="J29" s="140"/>
+      <c r="K29" s="141"/>
+      <c r="L29" s="142"/>
+      <c r="M29" s="139"/>
+      <c r="N29" s="143"/>
+      <c r="O29" s="142"/>
+      <c r="P29" s="141"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="140"/>
+      <c r="S29" s="144"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="147" t="s">
+      <c r="B30" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="148" t="s">
-        <v>143</v>
-      </c>
-      <c r="D30" s="102"/>
-      <c r="E30" s="149"/>
-      <c r="F30" s="150"/>
-      <c r="G30" s="150"/>
-      <c r="H30" s="151"/>
-      <c r="I30" s="152"/>
-      <c r="J30" s="150"/>
-      <c r="K30" s="150"/>
-      <c r="L30" s="151"/>
-      <c r="M30" s="152"/>
-      <c r="N30" s="150"/>
-      <c r="O30" s="151"/>
-      <c r="P30" s="150"/>
-      <c r="Q30" s="152"/>
-      <c r="R30" s="150"/>
-      <c r="S30" s="153"/>
+      <c r="C30" s="146" t="s">
+        <v>145</v>
+      </c>
+      <c r="D30" s="100"/>
+      <c r="E30" s="147"/>
+      <c r="F30" s="148"/>
+      <c r="G30" s="148"/>
+      <c r="H30" s="149"/>
+      <c r="I30" s="150"/>
+      <c r="J30" s="148"/>
+      <c r="K30" s="148"/>
+      <c r="L30" s="149"/>
+      <c r="M30" s="150"/>
+      <c r="N30" s="148"/>
+      <c r="O30" s="149"/>
+      <c r="P30" s="148"/>
+      <c r="Q30" s="150"/>
+      <c r="R30" s="148"/>
+      <c r="S30" s="151"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="154"/>
-      <c r="C31" s="155"/>
-      <c r="D31" s="109"/>
-      <c r="E31" s="156"/>
-      <c r="F31" s="157"/>
-      <c r="G31" s="157"/>
-      <c r="H31" s="158"/>
-      <c r="I31" s="159"/>
-      <c r="J31" s="157"/>
-      <c r="K31" s="160"/>
-      <c r="L31" s="158"/>
-      <c r="M31" s="159"/>
-      <c r="N31" s="157"/>
-      <c r="O31" s="158"/>
-      <c r="P31" s="157"/>
-      <c r="Q31" s="159"/>
-      <c r="R31" s="157"/>
-      <c r="S31" s="115"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="107"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="155"/>
+      <c r="G31" s="155"/>
+      <c r="H31" s="156"/>
+      <c r="I31" s="157"/>
+      <c r="J31" s="155"/>
+      <c r="K31" s="158"/>
+      <c r="L31" s="156"/>
+      <c r="M31" s="157"/>
+      <c r="N31" s="155"/>
+      <c r="O31" s="156"/>
+      <c r="P31" s="155"/>
+      <c r="Q31" s="157"/>
+      <c r="R31" s="155"/>
+      <c r="S31" s="113"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="154"/>
-      <c r="C32" s="155" t="s">
+      <c r="B32" s="152"/>
+      <c r="C32" s="153" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="117"/>
-      <c r="E32" s="161"/>
-      <c r="F32" s="162"/>
-      <c r="G32" s="162"/>
-      <c r="H32" s="163"/>
-      <c r="I32" s="164"/>
-      <c r="J32" s="162"/>
-      <c r="K32" s="162"/>
-      <c r="L32" s="163"/>
-      <c r="M32" s="164"/>
-      <c r="N32" s="162"/>
-      <c r="O32" s="163"/>
-      <c r="P32" s="162"/>
-      <c r="Q32" s="164"/>
-      <c r="R32" s="162"/>
-      <c r="S32" s="165"/>
+      <c r="D32" s="115"/>
+      <c r="E32" s="159"/>
+      <c r="F32" s="160"/>
+      <c r="G32" s="160"/>
+      <c r="H32" s="161"/>
+      <c r="I32" s="162"/>
+      <c r="J32" s="160"/>
+      <c r="K32" s="160"/>
+      <c r="L32" s="161"/>
+      <c r="M32" s="162"/>
+      <c r="N32" s="160"/>
+      <c r="O32" s="161"/>
+      <c r="P32" s="160"/>
+      <c r="Q32" s="162"/>
+      <c r="R32" s="160"/>
+      <c r="S32" s="163"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="154"/>
-      <c r="C33" s="155"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="160"/>
-      <c r="G33" s="157"/>
-      <c r="H33" s="166"/>
-      <c r="I33" s="167"/>
-      <c r="J33" s="157"/>
-      <c r="K33" s="160"/>
-      <c r="L33" s="158"/>
-      <c r="M33" s="159"/>
-      <c r="N33" s="157"/>
-      <c r="O33" s="158"/>
-      <c r="P33" s="157"/>
-      <c r="Q33" s="159"/>
-      <c r="R33" s="157"/>
-      <c r="S33" s="115"/>
+      <c r="B33" s="152"/>
+      <c r="C33" s="153"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="154"/>
+      <c r="F33" s="158"/>
+      <c r="G33" s="155"/>
+      <c r="H33" s="164"/>
+      <c r="I33" s="165"/>
+      <c r="J33" s="155"/>
+      <c r="K33" s="158"/>
+      <c r="L33" s="156"/>
+      <c r="M33" s="157"/>
+      <c r="N33" s="155"/>
+      <c r="O33" s="156"/>
+      <c r="P33" s="155"/>
+      <c r="Q33" s="157"/>
+      <c r="R33" s="155"/>
+      <c r="S33" s="113"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="154"/>
-      <c r="C34" s="108" t="s">
-        <v>198</v>
-      </c>
-      <c r="D34" s="140"/>
-      <c r="E34" s="168"/>
-      <c r="F34" s="169"/>
-      <c r="G34" s="169"/>
-      <c r="H34" s="170"/>
-      <c r="I34" s="171"/>
-      <c r="J34" s="169"/>
-      <c r="K34" s="169"/>
-      <c r="L34" s="170"/>
-      <c r="M34" s="171"/>
-      <c r="N34" s="169"/>
-      <c r="O34" s="170"/>
-      <c r="P34" s="169"/>
-      <c r="Q34" s="171"/>
-      <c r="R34" s="169"/>
-      <c r="S34" s="172"/>
-      <c r="U34" s="173"/>
-      <c r="V34" s="174" t="s">
-        <v>199</v>
+      <c r="B34" s="152"/>
+      <c r="C34" s="106" t="s">
+        <v>200</v>
+      </c>
+      <c r="D34" s="138"/>
+      <c r="E34" s="166"/>
+      <c r="F34" s="167"/>
+      <c r="G34" s="167"/>
+      <c r="H34" s="168"/>
+      <c r="I34" s="169"/>
+      <c r="J34" s="167"/>
+      <c r="K34" s="167"/>
+      <c r="L34" s="168"/>
+      <c r="M34" s="169"/>
+      <c r="N34" s="167"/>
+      <c r="O34" s="168"/>
+      <c r="P34" s="167"/>
+      <c r="Q34" s="169"/>
+      <c r="R34" s="167"/>
+      <c r="S34" s="170"/>
+      <c r="U34" s="171"/>
+      <c r="V34" s="172" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="175"/>
-      <c r="C35" s="176"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="177"/>
-      <c r="F35" s="178"/>
-      <c r="G35" s="178"/>
-      <c r="H35" s="179"/>
-      <c r="I35" s="180"/>
-      <c r="J35" s="178"/>
-      <c r="K35" s="178"/>
-      <c r="L35" s="179"/>
-      <c r="M35" s="180"/>
-      <c r="N35" s="178"/>
-      <c r="O35" s="179"/>
-      <c r="P35" s="178"/>
-      <c r="Q35" s="180"/>
-      <c r="R35" s="178"/>
-      <c r="S35" s="132"/>
-      <c r="U35" s="181"/>
-      <c r="V35" s="182" t="s">
-        <v>200</v>
+      <c r="B35" s="173"/>
+      <c r="C35" s="174"/>
+      <c r="D35" s="125"/>
+      <c r="E35" s="175"/>
+      <c r="F35" s="176"/>
+      <c r="G35" s="176"/>
+      <c r="H35" s="177"/>
+      <c r="I35" s="178"/>
+      <c r="J35" s="176"/>
+      <c r="K35" s="176"/>
+      <c r="L35" s="177"/>
+      <c r="M35" s="178"/>
+      <c r="N35" s="176"/>
+      <c r="O35" s="177"/>
+      <c r="P35" s="176"/>
+      <c r="Q35" s="178"/>
+      <c r="R35" s="176"/>
+      <c r="S35" s="130"/>
+      <c r="U35" s="179"/>
+      <c r="V35" s="180" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/LHO - M5 - JournalPlanif.xlsx
+++ b/Documentation/LHO - M5 - JournalPlanif.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId3"/>
@@ -1620,7 +1620,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="179">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1677,12 +1677,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -6695,10 +6689,10 @@
       <c r="C79" s="21">
         <v>6.25e-002</v>
       </c>
-      <c r="D79" s="25" t="s">
+      <c r="D79" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E79" s="26" t="s">
+      <c r="E79" s="8" t="s">
         <v>104</v>
       </c>
     </row>
@@ -6709,10 +6703,10 @@
       <c r="C80" s="21">
         <v>2.0833333333333332e-002</v>
       </c>
-      <c r="D80" s="25" t="s">
+      <c r="D80" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E80" s="26" t="s">
+      <c r="E80" s="8" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6738,7 +6732,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{BEC242A8-24BE-4A6A-A6B7-4038FDA54160}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{FB648811-ECE8-4492-836D-196A61C7A278}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6793,34 +6787,34 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27">
+      <c r="A3" s="25">
         <v>46042</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C3" s="28"/>
+      <c r="C3" s="26"/>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>111</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="27">
         <f t="shared" ref="F3:F8" si="0">SUMPRODUCT((MONTH($A$3:$A$152)=D3)*($A$3:$A$152&lt;&gt;"")*$B$3:$B$152)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="30">
+      <c r="G3" s="28">
         <f t="shared" ref="G3:G8" si="1">F3*24</f>
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27">
+      <c r="A4" s="25">
         <v>46043</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6831,20 +6825,20 @@
       <c r="E4" t="s">
         <v>112</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27">
+      <c r="A5" s="25">
         <v>46044</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6855,20 +6849,20 @@
       <c r="E5" t="s">
         <v>113</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="27">
         <f t="shared" si="0"/>
         <v>2.6805555555555558</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="28">
         <f t="shared" si="1"/>
         <v>64.333333333333343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27">
+      <c r="A6" s="25">
         <v>46045</v>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6879,20 +6873,20 @@
       <c r="E6" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="27">
         <f t="shared" si="0"/>
         <v>1.2083333333333333</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="28">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27">
+      <c r="A7" s="25">
         <v>46046</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6903,20 +6897,20 @@
       <c r="E7" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="27">
         <f t="shared" si="0"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="28">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27">
+      <c r="A8" s="25">
         <v>46047</v>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6927,2069 +6921,2069 @@
       <c r="E8" t="s">
         <v>116</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="27">
         <f t="shared" si="0"/>
         <v>0.64236111111111116</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="28">
         <f t="shared" si="1"/>
         <v>15.416666666666668</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27">
+      <c r="A9" s="25">
         <v>46048</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
-      <c r="G9" s="30">
+      <c r="G9" s="28">
         <f>SUM(G3:G8)</f>
         <v>115.75000000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27">
+      <c r="A10" s="25">
         <v>46049</v>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="27">
+      <c r="A11" s="25">
         <v>46050</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="27">
+      <c r="A12" s="25">
         <v>46051</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="27">
+      <c r="A13" s="25">
         <v>46052</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="27">
+      <c r="A14" s="25">
         <v>46053</v>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="27">
+      <c r="A15" s="25">
         <v>46054</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="27">
+      <c r="A16" s="25">
         <v>46055</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="27">
+      <c r="A17" s="25">
         <v>46056</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="27">
+      <c r="A18" s="25">
         <v>46057</v>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="27">
+      <c r="A19" s="25">
         <v>46058</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="27">
+      <c r="A20" s="25">
         <v>46059</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="27">
+      <c r="A21" s="25">
         <v>46060</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="27">
+      <c r="A22" s="25">
         <v>46061</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="27">
+      <c r="A23" s="25">
         <v>46062</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="27">
+      <c r="A24" s="25">
         <v>46063</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="27">
+      <c r="A25" s="25">
         <v>46064</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
     </row>
     <row r="26">
-      <c r="A26" s="27">
+      <c r="A26" s="25">
         <v>46065</v>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C26"/>
-      <c r="F26" s="30"/>
+      <c r="F26" s="28"/>
     </row>
     <row r="27">
-      <c r="A27" s="27">
+      <c r="A27" s="25">
         <v>46066</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27">
+      <c r="A28" s="25">
         <v>46067</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27">
+      <c r="A29" s="25">
         <v>46068</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27">
+      <c r="A30" s="25">
         <v>46069</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27">
+      <c r="A31" s="25">
         <v>46070</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27">
+      <c r="A32" s="25">
         <v>46071</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27">
+      <c r="A33" s="25">
         <v>46072</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27">
+      <c r="A34" s="25">
         <v>46073</v>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27">
+      <c r="A35" s="25">
         <v>46074</v>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27">
+      <c r="A36" s="25">
         <v>46075</v>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27">
+      <c r="A37" s="25">
         <v>46076</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27">
+      <c r="A38" s="25">
         <v>46077</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="27">
+      <c r="A39" s="25">
         <v>46078</v>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="27">
+      <c r="A40" s="25">
         <v>46079</v>
       </c>
-      <c r="B40" s="28">
+      <c r="B40" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="27">
+      <c r="A41" s="25">
         <v>46080</v>
       </c>
-      <c r="B41" s="28">
+      <c r="B41" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="27">
+      <c r="A42" s="25">
         <v>46081</v>
       </c>
-      <c r="B42" s="28">
+      <c r="B42" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="27">
+      <c r="A43" s="25">
         <v>46082</v>
       </c>
-      <c r="B43" s="28">
+      <c r="B43" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="27">
+      <c r="A44" s="25">
         <v>46083</v>
       </c>
-      <c r="B44" s="28">
+      <c r="B44" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="27">
+      <c r="A45" s="25">
         <v>46084</v>
       </c>
-      <c r="B45" s="28">
+      <c r="B45" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="27">
+      <c r="A46" s="25">
         <v>46085</v>
       </c>
-      <c r="B46" s="28">
+      <c r="B46" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="27">
+      <c r="A47" s="25">
         <v>46086</v>
       </c>
-      <c r="B47" s="28">
+      <c r="B47" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="27">
+      <c r="A48" s="25">
         <v>46087</v>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="27">
+      <c r="A49" s="25">
         <v>46088</v>
       </c>
-      <c r="B49" s="28">
+      <c r="B49" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="27">
+      <c r="A50" s="25">
         <v>46089</v>
       </c>
-      <c r="B50" s="28">
+      <c r="B50" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="27">
+      <c r="A51" s="25">
         <v>46090</v>
       </c>
-      <c r="B51" s="28">
+      <c r="B51" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="27">
+      <c r="A52" s="25">
         <v>46091</v>
       </c>
-      <c r="B52" s="28">
+      <c r="B52" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="27">
+      <c r="A53" s="25">
         <v>46092</v>
       </c>
-      <c r="B53" s="28">
+      <c r="B53" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="27">
+      <c r="A54" s="25">
         <v>46093</v>
       </c>
-      <c r="B54" s="28">
+      <c r="B54" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="27">
+      <c r="A55" s="25">
         <v>46094</v>
       </c>
-      <c r="B55" s="28">
+      <c r="B55" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="27">
+      <c r="A56" s="25">
         <v>46095</v>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="27">
+      <c r="A57" s="25">
         <v>46096</v>
       </c>
-      <c r="B57" s="28">
+      <c r="B57" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="27">
+      <c r="A58" s="25">
         <v>46097</v>
       </c>
-      <c r="B58" s="28">
+      <c r="B58" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="27">
+      <c r="A59" s="25">
         <v>46098</v>
       </c>
-      <c r="B59" s="28">
+      <c r="B59" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="27">
+      <c r="A60" s="25">
         <v>46099</v>
       </c>
-      <c r="B60" s="28">
+      <c r="B60" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="27">
+      <c r="A61" s="25">
         <v>46100</v>
       </c>
-      <c r="B61" s="28">
+      <c r="B61" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="27">
+      <c r="A62" s="25">
         <v>46101</v>
       </c>
-      <c r="B62" s="28">
+      <c r="B62" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="27">
+      <c r="A63" s="25">
         <v>46102</v>
       </c>
-      <c r="B63" s="28">
+      <c r="B63" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="27">
+      <c r="A64" s="25">
         <v>46103</v>
       </c>
-      <c r="B64" s="28">
+      <c r="B64" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C64" s="31">
+      <c r="C64" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="27">
+      <c r="A65" s="25">
         <v>46104</v>
       </c>
-      <c r="B65" s="28">
+      <c r="B65" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="27">
+      <c r="A66" s="25">
         <v>46105</v>
       </c>
-      <c r="B66" s="28">
+      <c r="B66" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="27">
+      <c r="A67" s="25">
         <v>46106</v>
       </c>
-      <c r="B67" s="28">
+      <c r="B67" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C67" s="31">
+      <c r="C67" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="27">
+      <c r="A68" s="25">
         <v>46107</v>
       </c>
-      <c r="B68" s="28">
+      <c r="B68" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="27">
+      <c r="A69" s="25">
         <v>46108</v>
       </c>
-      <c r="B69" s="28">
+      <c r="B69" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="27">
+      <c r="A70" s="25">
         <v>46109</v>
       </c>
-      <c r="B70" s="28">
+      <c r="B70" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C70" s="31">
+      <c r="C70" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="27">
+      <c r="A71" s="25">
         <v>46110</v>
       </c>
-      <c r="B71" s="28">
+      <c r="B71" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C71" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="27">
+      <c r="A72" s="25">
         <v>46111</v>
       </c>
-      <c r="B72" s="28">
+      <c r="B72" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C72" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="27">
+      <c r="A73" s="25">
         <v>46112</v>
       </c>
-      <c r="B73" s="28">
+      <c r="B73" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C73" s="31">
+      <c r="C73" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="27">
+      <c r="A74" s="25">
         <v>46113</v>
       </c>
-      <c r="B74" s="28">
+      <c r="B74" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C74" s="31">
+      <c r="C74" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="27">
+      <c r="A75" s="25">
         <v>46114</v>
       </c>
-      <c r="B75" s="28">
+      <c r="B75" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C75" s="31">
+      <c r="C75" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="27">
+      <c r="A76" s="25">
         <v>46115</v>
       </c>
-      <c r="B76" s="28">
+      <c r="B76" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C76" s="31">
+      <c r="C76" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="27">
+      <c r="A77" s="25">
         <v>46116</v>
       </c>
-      <c r="B77" s="28">
+      <c r="B77" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C77" s="31">
+      <c r="C77" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="27">
+      <c r="A78" s="25">
         <v>46117</v>
       </c>
-      <c r="B78" s="28">
+      <c r="B78" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C78" s="31">
+      <c r="C78" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="27">
+      <c r="A79" s="25">
         <v>46118</v>
       </c>
-      <c r="B79" s="28">
+      <c r="B79" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C79" s="31">
+      <c r="C79" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="27">
+      <c r="A80" s="25">
         <v>46119</v>
       </c>
-      <c r="B80" s="28">
+      <c r="B80" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C80" s="31">
+      <c r="C80" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="27">
+      <c r="A81" s="25">
         <v>46120</v>
       </c>
-      <c r="B81" s="28">
+      <c r="B81" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C81" s="31">
+      <c r="C81" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="27">
+      <c r="A82" s="25">
         <v>46121</v>
       </c>
-      <c r="B82" s="28">
+      <c r="B82" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C82" s="31">
+      <c r="C82" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="27">
+      <c r="A83" s="25">
         <v>46122</v>
       </c>
-      <c r="B83" s="28">
+      <c r="B83" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C83" s="31">
+      <c r="C83" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="27">
+      <c r="A84" s="25">
         <v>46123</v>
       </c>
-      <c r="B84" s="28">
+      <c r="B84" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C84" s="31">
+      <c r="C84" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="27">
+      <c r="A85" s="25">
         <v>46124</v>
       </c>
-      <c r="B85" s="28">
+      <c r="B85" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C85" s="31">
+      <c r="C85" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="27">
+      <c r="A86" s="25">
         <v>46125</v>
       </c>
-      <c r="B86" s="28">
+      <c r="B86" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C86" s="31">
+      <c r="C86" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="27">
+      <c r="A87" s="25">
         <v>46126</v>
       </c>
-      <c r="B87" s="28">
+      <c r="B87" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C87" s="31">
+      <c r="C87" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="27">
+      <c r="A88" s="25">
         <v>46127</v>
       </c>
-      <c r="B88" s="28">
+      <c r="B88" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C88" s="31">
+      <c r="C88" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="27">
+      <c r="A89" s="25">
         <v>46128</v>
       </c>
-      <c r="B89" s="28">
+      <c r="B89" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C89" s="31">
+      <c r="C89" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="27">
+      <c r="A90" s="25">
         <v>46129</v>
       </c>
-      <c r="B90" s="28">
+      <c r="B90" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C90" s="31">
+      <c r="C90" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="27">
+      <c r="A91" s="25">
         <v>46130</v>
       </c>
-      <c r="B91" s="28">
+      <c r="B91" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C91" s="31">
+      <c r="C91" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="27">
+      <c r="A92" s="25">
         <v>46131</v>
       </c>
-      <c r="B92" s="28">
+      <c r="B92" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C92" s="31">
+      <c r="C92" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="27">
+      <c r="A93" s="25">
         <v>46132</v>
       </c>
-      <c r="B93" s="28">
+      <c r="B93" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C93" s="31">
+      <c r="C93" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="27">
+      <c r="A94" s="25">
         <v>46133</v>
       </c>
-      <c r="B94" s="28">
+      <c r="B94" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C94" s="31">
+      <c r="C94" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="27">
+      <c r="A95" s="25">
         <v>46134</v>
       </c>
-      <c r="B95" s="28">
+      <c r="B95" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
-      <c r="C95" s="31">
+      <c r="C95" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="27">
+      <c r="A96" s="25">
         <v>46135</v>
       </c>
-      <c r="B96" s="28">
+      <c r="B96" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
-      <c r="C96" s="31">
+      <c r="C96" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="27">
+      <c r="A97" s="25">
         <v>46136</v>
       </c>
-      <c r="B97" s="28">
+      <c r="B97" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C97" s="31">
+      <c r="C97" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="27">
+      <c r="A98" s="25">
         <v>46137</v>
       </c>
-      <c r="B98" s="28">
+      <c r="B98" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C98" s="31">
+      <c r="C98" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="27">
+      <c r="A99" s="25">
         <v>46138</v>
       </c>
-      <c r="B99" s="28">
+      <c r="B99" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C99" s="31">
+      <c r="C99" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="27">
+      <c r="A100" s="25">
         <v>46139</v>
       </c>
-      <c r="B100" s="28">
+      <c r="B100" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C100" s="31">
+      <c r="C100" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="27">
+      <c r="A101" s="25">
         <v>46140</v>
       </c>
-      <c r="B101" s="28">
+      <c r="B101" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
-      <c r="C101" s="31">
+      <c r="C101" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="27">
+      <c r="A102" s="25">
         <v>46141</v>
       </c>
-      <c r="B102" s="28">
+      <c r="B102" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C102" s="31">
+      <c r="C102" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="27">
+      <c r="A103" s="25">
         <v>46142</v>
       </c>
-      <c r="B103" s="28">
+      <c r="B103" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C103" s="31">
+      <c r="C103" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="27">
+      <c r="A104" s="25">
         <v>46143</v>
       </c>
-      <c r="B104" s="28">
+      <c r="B104" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C104" s="31">
+      <c r="C104" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="27">
+      <c r="A105" s="25">
         <v>46144</v>
       </c>
-      <c r="B105" s="28">
+      <c r="B105" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C105" s="31">
+      <c r="C105" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="27">
+      <c r="A106" s="25">
         <v>46145</v>
       </c>
-      <c r="B106" s="28">
+      <c r="B106" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C106" s="31">
+      <c r="C106" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="27">
+      <c r="A107" s="25">
         <v>46146</v>
       </c>
-      <c r="B107" s="28">
+      <c r="B107" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C107" s="31">
+      <c r="C107" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="27">
+      <c r="A108" s="25">
         <v>46147</v>
       </c>
-      <c r="B108" s="28">
+      <c r="B108" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C108" s="31">
+      <c r="C108" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="27">
+      <c r="A109" s="25">
         <v>46148</v>
       </c>
-      <c r="B109" s="28">
+      <c r="B109" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C109" s="31">
+      <c r="C109" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="27">
+      <c r="A110" s="25">
         <v>46149</v>
       </c>
-      <c r="B110" s="28">
+      <c r="B110" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C110" s="31">
+      <c r="C110" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="27">
+      <c r="A111" s="25">
         <v>46150</v>
       </c>
-      <c r="B111" s="28">
+      <c r="B111" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C111" s="31">
+      <c r="C111" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="27">
+      <c r="A112" s="25">
         <v>46151</v>
       </c>
-      <c r="B112" s="28">
+      <c r="B112" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C112" s="31">
+      <c r="C112" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="27">
+      <c r="A113" s="25">
         <v>46152</v>
       </c>
-      <c r="B113" s="28">
+      <c r="B113" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C113" s="31">
+      <c r="C113" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="27">
+      <c r="A114" s="25">
         <v>46153</v>
       </c>
-      <c r="B114" s="28">
+      <c r="B114" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C114" s="31">
+      <c r="C114" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="27">
+      <c r="A115" s="25">
         <v>46154</v>
       </c>
-      <c r="B115" s="28">
+      <c r="B115" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C115" s="31">
+      <c r="C115" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="27">
+      <c r="A116" s="25">
         <v>46155</v>
       </c>
-      <c r="B116" s="28">
+      <c r="B116" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A116,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C116" s="31"/>
+      <c r="C116" s="29"/>
     </row>
     <row r="117">
-      <c r="A117" s="27">
+      <c r="A117" s="25">
         <v>46156</v>
       </c>
-      <c r="B117" s="28">
+      <c r="B117" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A117,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C117" s="31"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118">
-      <c r="A118" s="27">
+      <c r="A118" s="25">
         <v>46157</v>
       </c>
-      <c r="B118" s="28">
+      <c r="B118" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A118,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C118" s="31"/>
+      <c r="C118" s="29"/>
     </row>
     <row r="119">
-      <c r="A119" s="27">
+      <c r="A119" s="25">
         <v>46158</v>
       </c>
-      <c r="B119" s="28">
+      <c r="B119" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A119,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C119" s="31"/>
+      <c r="C119" s="29"/>
     </row>
     <row r="120">
-      <c r="A120" s="27">
+      <c r="A120" s="25">
         <v>46159</v>
       </c>
-      <c r="B120" s="28">
+      <c r="B120" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A120,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C120" s="31"/>
+      <c r="C120" s="29"/>
     </row>
     <row r="121">
-      <c r="A121" s="27">
+      <c r="A121" s="25">
         <v>46160</v>
       </c>
-      <c r="B121" s="28">
+      <c r="B121" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A121,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C121" s="31"/>
+      <c r="C121" s="29"/>
     </row>
     <row r="122">
-      <c r="A122" s="27">
+      <c r="A122" s="25">
         <v>46161</v>
       </c>
-      <c r="B122" s="28">
+      <c r="B122" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A122,Journal[Temps])</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="C122" s="31"/>
+      <c r="C122" s="29"/>
     </row>
     <row r="123">
-      <c r="A123" s="27">
+      <c r="A123" s="25">
         <v>46162</v>
       </c>
-      <c r="B123" s="28">
+      <c r="B123" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A123,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C123" s="31"/>
+      <c r="C123" s="29"/>
     </row>
     <row r="124">
-      <c r="A124" s="27">
+      <c r="A124" s="25">
         <v>46163</v>
       </c>
-      <c r="B124" s="28">
+      <c r="B124" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A124,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C124" s="31"/>
+      <c r="C124" s="29"/>
     </row>
     <row r="125">
-      <c r="A125" s="27">
+      <c r="A125" s="25">
         <v>46164</v>
       </c>
-      <c r="B125" s="28">
+      <c r="B125" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A125,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C125" s="31"/>
+      <c r="C125" s="29"/>
     </row>
     <row r="126">
-      <c r="A126" s="27">
+      <c r="A126" s="25">
         <v>46165</v>
       </c>
-      <c r="B126" s="28">
+      <c r="B126" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A126,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C126" s="31"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127">
-      <c r="A127" s="27">
+      <c r="A127" s="25">
         <v>46166</v>
       </c>
-      <c r="B127" s="28">
+      <c r="B127" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A127,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C127" s="31"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128">
-      <c r="A128" s="27">
+      <c r="A128" s="25">
         <v>46167</v>
       </c>
-      <c r="B128" s="28">
+      <c r="B128" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A128,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C128" s="31"/>
+      <c r="C128" s="29"/>
     </row>
     <row r="129">
-      <c r="A129" s="27">
+      <c r="A129" s="25">
         <v>46168</v>
       </c>
-      <c r="B129" s="28">
+      <c r="B129" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A129,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C129" s="31"/>
+      <c r="C129" s="29"/>
     </row>
     <row r="130">
-      <c r="A130" s="27">
+      <c r="A130" s="25">
         <v>46169</v>
       </c>
-      <c r="B130" s="28">
+      <c r="B130" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A130,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C130" s="31"/>
+      <c r="C130" s="29"/>
     </row>
     <row r="131">
-      <c r="A131" s="27">
+      <c r="A131" s="25">
         <v>46170</v>
       </c>
-      <c r="B131" s="28">
+      <c r="B131" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A131,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C131" s="31"/>
+      <c r="C131" s="29"/>
     </row>
     <row r="132">
-      <c r="A132" s="27">
+      <c r="A132" s="25">
         <v>46171</v>
       </c>
-      <c r="B132" s="28">
+      <c r="B132" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A132,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C132" s="31"/>
+      <c r="C132" s="29"/>
     </row>
     <row r="133">
-      <c r="A133" s="27">
+      <c r="A133" s="25">
         <v>46172</v>
       </c>
-      <c r="B133" s="28">
+      <c r="B133" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A133,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C133" s="31"/>
+      <c r="C133" s="29"/>
     </row>
     <row r="134">
-      <c r="A134" s="27">
+      <c r="A134" s="25">
         <v>46173</v>
       </c>
-      <c r="B134" s="28">
+      <c r="B134" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A134,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C134" s="31"/>
+      <c r="C134" s="29"/>
     </row>
     <row r="135">
-      <c r="A135" s="27">
+      <c r="A135" s="25">
         <v>46174</v>
       </c>
-      <c r="B135" s="28">
+      <c r="B135" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A135,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C135" s="31"/>
+      <c r="C135" s="29"/>
     </row>
     <row r="136">
-      <c r="A136" s="27">
+      <c r="A136" s="25">
         <v>46175</v>
       </c>
-      <c r="B136" s="28">
+      <c r="B136" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A136,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C136" s="31"/>
+      <c r="C136" s="29"/>
     </row>
     <row r="137">
-      <c r="A137" s="27">
+      <c r="A137" s="25">
         <v>46176</v>
       </c>
-      <c r="B137" s="28">
+      <c r="B137" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A137,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C137" s="31"/>
+      <c r="C137" s="29"/>
     </row>
     <row r="138">
-      <c r="A138" s="27">
+      <c r="A138" s="25">
         <v>46177</v>
       </c>
-      <c r="B138" s="28">
+      <c r="B138" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A138,Journal[Temps])</f>
         <v>0.2986111111111111</v>
       </c>
-      <c r="C138" s="31"/>
+      <c r="C138" s="29"/>
     </row>
     <row r="139">
-      <c r="A139" s="27">
+      <c r="A139" s="25">
         <v>46178</v>
       </c>
-      <c r="B139" s="28">
+      <c r="B139" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A139,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C139" s="31"/>
+      <c r="C139" s="29"/>
     </row>
     <row r="140">
-      <c r="A140" s="27">
+      <c r="A140" s="25">
         <v>46179</v>
       </c>
-      <c r="B140" s="28">
+      <c r="B140" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A140,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C140" s="31"/>
+      <c r="C140" s="29"/>
     </row>
     <row r="141">
-      <c r="A141" s="27">
+      <c r="A141" s="25">
         <v>46180</v>
       </c>
-      <c r="B141" s="28">
+      <c r="B141" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A141,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
-      <c r="C141" s="31"/>
+      <c r="C141" s="29"/>
     </row>
     <row r="142">
-      <c r="A142" s="27">
+      <c r="A142" s="25">
         <v>46181</v>
       </c>
-      <c r="B142" s="28">
+      <c r="B142" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A142,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C142" s="31"/>
+      <c r="C142" s="29"/>
     </row>
     <row r="143">
-      <c r="A143" s="27">
+      <c r="A143" s="25">
         <v>46182</v>
       </c>
-      <c r="B143" s="28">
+      <c r="B143" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A143,Journal[Temps])</f>
         <v>0.15625000000000003</v>
       </c>
-      <c r="C143" s="31"/>
+      <c r="C143" s="29"/>
     </row>
     <row r="144">
-      <c r="A144" s="27">
+      <c r="A144" s="25">
         <v>46183</v>
       </c>
-      <c r="B144" s="28">
+      <c r="B144" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A144,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C144" s="31"/>
+      <c r="C144" s="29"/>
     </row>
     <row r="145">
-      <c r="A145" s="27">
+      <c r="A145" s="25">
         <v>46184</v>
       </c>
-      <c r="B145" s="28">
+      <c r="B145" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A145,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C145" s="31"/>
+      <c r="C145" s="29"/>
     </row>
     <row r="146">
-      <c r="A146" s="27">
+      <c r="A146" s="25">
         <v>46185</v>
       </c>
-      <c r="B146" s="28">
+      <c r="B146" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A146,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C146" s="31"/>
+      <c r="C146" s="29"/>
     </row>
     <row r="147">
-      <c r="A147" s="27">
+      <c r="A147" s="25">
         <v>46186</v>
       </c>
-      <c r="B147" s="28">
+      <c r="B147" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A147,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C147" s="31"/>
+      <c r="C147" s="29"/>
     </row>
     <row r="148">
-      <c r="A148" s="27">
+      <c r="A148" s="25">
         <v>46187</v>
       </c>
-      <c r="B148" s="28">
+      <c r="B148" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A148,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C148" s="31"/>
+      <c r="C148" s="29"/>
     </row>
     <row r="149">
-      <c r="A149" s="27">
+      <c r="A149" s="25">
         <v>46188</v>
       </c>
-      <c r="B149" s="28">
+      <c r="B149" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A149,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C149" s="31"/>
+      <c r="C149" s="29"/>
     </row>
     <row r="150">
-      <c r="A150" s="27">
+      <c r="A150" s="25">
         <v>46189</v>
       </c>
-      <c r="B150" s="28">
+      <c r="B150" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A150,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C150" s="31"/>
+      <c r="C150" s="29"/>
     </row>
     <row r="151">
-      <c r="A151" s="27">
+      <c r="A151" s="25">
         <v>46190</v>
       </c>
-      <c r="B151" s="28">
+      <c r="B151" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A151,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C151" s="31"/>
+      <c r="C151" s="29"/>
     </row>
     <row r="152">
-      <c r="A152" s="27">
+      <c r="A152" s="25">
         <v>46191</v>
       </c>
-      <c r="B152" s="28">
+      <c r="B152" s="26">
         <f>SUMIF(Journal[date],SommeParJours!A152,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C152" s="31"/>
+      <c r="C152" s="29"/>
     </row>
     <row r="153">
-      <c r="A153" s="27"/>
-      <c r="B153" s="32"/>
-      <c r="C153" s="31"/>
+      <c r="A153" s="25"/>
+      <c r="B153" s="30"/>
+      <c r="C153" s="29"/>
     </row>
     <row r="154">
-      <c r="A154" s="27"/>
-      <c r="B154" s="32"/>
-      <c r="C154" s="31"/>
+      <c r="A154" s="25"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="29"/>
     </row>
     <row r="155">
-      <c r="A155" s="27"/>
-      <c r="B155" s="32"/>
-      <c r="C155" s="31"/>
+      <c r="A155" s="25"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="29"/>
     </row>
     <row r="156">
-      <c r="A156" s="27"/>
-      <c r="B156" s="32"/>
-      <c r="C156" s="31"/>
+      <c r="A156" s="25"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="29"/>
     </row>
     <row r="157">
-      <c r="A157" s="27"/>
-      <c r="B157" s="32"/>
-      <c r="C157" s="31"/>
+      <c r="A157" s="25"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="29"/>
     </row>
     <row r="158">
-      <c r="A158" s="27"/>
-      <c r="B158" s="32"/>
-      <c r="C158" s="31"/>
+      <c r="A158" s="25"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="29"/>
     </row>
     <row r="159">
-      <c r="A159" s="27"/>
-      <c r="B159" s="32"/>
-      <c r="C159" s="31"/>
+      <c r="A159" s="25"/>
+      <c r="B159" s="30"/>
+      <c r="C159" s="29"/>
     </row>
     <row r="160">
-      <c r="A160" s="27"/>
-      <c r="B160" s="32"/>
+      <c r="A160" s="25"/>
+      <c r="B160" s="30"/>
     </row>
     <row r="161">
-      <c r="A161" s="27"/>
-      <c r="B161" s="32"/>
+      <c r="A161" s="25"/>
+      <c r="B161" s="30"/>
     </row>
     <row r="162">
-      <c r="A162" s="27"/>
-      <c r="B162" s="32"/>
+      <c r="A162" s="25"/>
+      <c r="B162" s="30"/>
     </row>
     <row r="163">
-      <c r="A163" s="27"/>
-      <c r="B163" s="32"/>
+      <c r="A163" s="25"/>
+      <c r="B163" s="30"/>
     </row>
     <row r="164">
-      <c r="A164" s="27"/>
-      <c r="B164" s="32"/>
+      <c r="A164" s="25"/>
+      <c r="B164" s="30"/>
     </row>
     <row r="165">
-      <c r="A165" s="27"/>
-      <c r="B165" s="32"/>
+      <c r="A165" s="25"/>
+      <c r="B165" s="30"/>
     </row>
     <row r="166">
-      <c r="A166" s="27"/>
-      <c r="B166" s="32"/>
+      <c r="A166" s="25"/>
+      <c r="B166" s="30"/>
     </row>
     <row r="167">
-      <c r="A167" s="27"/>
-      <c r="B167" s="32"/>
+      <c r="A167" s="25"/>
+      <c r="B167" s="30"/>
     </row>
     <row r="168">
-      <c r="A168" s="27"/>
-      <c r="B168" s="32"/>
+      <c r="A168" s="25"/>
+      <c r="B168" s="30"/>
     </row>
     <row r="169">
-      <c r="A169" s="27"/>
-      <c r="B169" s="32"/>
+      <c r="A169" s="25"/>
+      <c r="B169" s="30"/>
     </row>
     <row r="170">
-      <c r="A170" s="27"/>
-      <c r="B170" s="32"/>
+      <c r="A170" s="25"/>
+      <c r="B170" s="30"/>
     </row>
     <row r="171">
-      <c r="A171" s="27"/>
-      <c r="B171" s="32"/>
+      <c r="A171" s="25"/>
+      <c r="B171" s="30"/>
     </row>
     <row r="172">
-      <c r="A172" s="27"/>
-      <c r="B172" s="32"/>
+      <c r="A172" s="25"/>
+      <c r="B172" s="30"/>
     </row>
     <row r="173">
-      <c r="A173" s="27"/>
-      <c r="B173" s="32"/>
+      <c r="A173" s="25"/>
+      <c r="B173" s="30"/>
     </row>
     <row r="174">
-      <c r="A174" s="27"/>
-      <c r="B174" s="32"/>
+      <c r="A174" s="25"/>
+      <c r="B174" s="30"/>
     </row>
     <row r="175">
-      <c r="A175" s="27"/>
-      <c r="B175" s="32"/>
+      <c r="A175" s="25"/>
+      <c r="B175" s="30"/>
     </row>
     <row r="176">
-      <c r="A176" s="27"/>
-      <c r="B176" s="32"/>
+      <c r="A176" s="25"/>
+      <c r="B176" s="30"/>
     </row>
     <row r="177">
-      <c r="A177" s="27"/>
-      <c r="B177" s="32"/>
+      <c r="A177" s="25"/>
+      <c r="B177" s="30"/>
     </row>
     <row r="178">
-      <c r="A178" s="27"/>
-      <c r="B178" s="32"/>
+      <c r="A178" s="25"/>
+      <c r="B178" s="30"/>
     </row>
     <row r="179">
-      <c r="A179" s="27"/>
-      <c r="B179" s="32"/>
+      <c r="A179" s="25"/>
+      <c r="B179" s="30"/>
     </row>
     <row r="180">
-      <c r="A180" s="27"/>
-      <c r="B180" s="32"/>
+      <c r="A180" s="25"/>
+      <c r="B180" s="30"/>
     </row>
     <row r="181">
-      <c r="A181" s="27"/>
-      <c r="B181" s="32"/>
+      <c r="A181" s="25"/>
+      <c r="B181" s="30"/>
     </row>
     <row r="182">
-      <c r="A182" s="27"/>
-      <c r="B182" s="32"/>
+      <c r="A182" s="25"/>
+      <c r="B182" s="30"/>
     </row>
     <row r="183">
-      <c r="A183" s="27"/>
-      <c r="B183" s="32"/>
+      <c r="A183" s="25"/>
+      <c r="B183" s="30"/>
     </row>
     <row r="184">
-      <c r="A184" s="27"/>
-      <c r="B184" s="32"/>
+      <c r="A184" s="25"/>
+      <c r="B184" s="30"/>
     </row>
     <row r="185">
-      <c r="A185" s="27"/>
-      <c r="B185" s="32"/>
+      <c r="A185" s="25"/>
+      <c r="B185" s="30"/>
     </row>
     <row r="186">
-      <c r="A186" s="27"/>
-      <c r="B186" s="32"/>
+      <c r="A186" s="25"/>
+      <c r="B186" s="30"/>
     </row>
     <row r="187">
-      <c r="A187" s="27"/>
-      <c r="B187" s="32"/>
+      <c r="A187" s="25"/>
+      <c r="B187" s="30"/>
     </row>
     <row r="188">
-      <c r="A188" s="32"/>
-      <c r="B188" s="32"/>
+      <c r="A188" s="30"/>
+      <c r="B188" s="30"/>
     </row>
     <row r="189">
-      <c r="A189" s="32"/>
-      <c r="B189" s="32"/>
+      <c r="A189" s="30"/>
+      <c r="B189" s="30"/>
     </row>
     <row r="190">
-      <c r="A190" s="32"/>
-      <c r="B190" s="32"/>
+      <c r="A190" s="30"/>
+      <c r="B190" s="30"/>
     </row>
     <row r="191">
-      <c r="A191" s="32"/>
-      <c r="B191" s="32"/>
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
     </row>
     <row r="192">
-      <c r="A192" s="32"/>
-      <c r="B192" s="32"/>
+      <c r="A192" s="30"/>
+      <c r="B192" s="30"/>
     </row>
     <row r="193">
-      <c r="A193" s="32"/>
-      <c r="B193" s="32"/>
+      <c r="A193" s="30"/>
+      <c r="B193" s="30"/>
     </row>
     <row r="194">
-      <c r="A194" s="32"/>
-      <c r="B194" s="32"/>
+      <c r="A194" s="30"/>
+      <c r="B194" s="30"/>
     </row>
     <row r="195">
-      <c r="A195" s="32"/>
-      <c r="B195" s="32"/>
+      <c r="A195" s="30"/>
+      <c r="B195" s="30"/>
     </row>
     <row r="196">
-      <c r="A196" s="32"/>
-      <c r="B196" s="32"/>
+      <c r="A196" s="30"/>
+      <c r="B196" s="30"/>
     </row>
     <row r="197">
-      <c r="A197" s="32"/>
-      <c r="B197" s="32"/>
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
     </row>
     <row r="198">
-      <c r="A198" s="32"/>
-      <c r="B198" s="32"/>
+      <c r="A198" s="30"/>
+      <c r="B198" s="30"/>
     </row>
     <row r="199">
-      <c r="A199" s="32"/>
-      <c r="B199" s="32"/>
+      <c r="A199" s="30"/>
+      <c r="B199" s="30"/>
     </row>
     <row r="200">
-      <c r="A200" s="32"/>
-      <c r="B200" s="32"/>
+      <c r="A200" s="30"/>
+      <c r="B200" s="30"/>
     </row>
     <row r="201">
-      <c r="A201" s="32"/>
-      <c r="B201" s="32"/>
+      <c r="A201" s="30"/>
+      <c r="B201" s="30"/>
     </row>
     <row r="202">
-      <c r="A202" s="32"/>
-      <c r="B202" s="32"/>
+      <c r="A202" s="30"/>
+      <c r="B202" s="30"/>
     </row>
     <row r="203">
-      <c r="A203" s="32"/>
-      <c r="B203" s="32"/>
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
     </row>
     <row r="204">
-      <c r="A204" s="32"/>
-      <c r="B204" s="32"/>
+      <c r="A204" s="30"/>
+      <c r="B204" s="30"/>
     </row>
     <row r="205">
-      <c r="A205" s="32"/>
-      <c r="B205" s="32"/>
+      <c r="A205" s="30"/>
+      <c r="B205" s="30"/>
     </row>
     <row r="206">
-      <c r="A206" s="32"/>
-      <c r="B206" s="32"/>
+      <c r="A206" s="30"/>
+      <c r="B206" s="30"/>
     </row>
     <row r="207">
-      <c r="A207" s="32"/>
-      <c r="B207" s="32"/>
+      <c r="A207" s="30"/>
+      <c r="B207" s="30"/>
     </row>
     <row r="208">
-      <c r="A208" s="32"/>
-      <c r="B208" s="32"/>
+      <c r="A208" s="30"/>
+      <c r="B208" s="30"/>
     </row>
     <row r="209">
-      <c r="A209" s="32"/>
-      <c r="B209" s="32"/>
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
     </row>
     <row r="210">
-      <c r="A210" s="32"/>
-      <c r="B210" s="32"/>
+      <c r="A210" s="30"/>
+      <c r="B210" s="30"/>
     </row>
     <row r="211">
-      <c r="A211" s="32"/>
-      <c r="B211" s="32"/>
+      <c r="A211" s="30"/>
+      <c r="B211" s="30"/>
     </row>
     <row r="212">
-      <c r="A212" s="32"/>
-      <c r="B212" s="32"/>
+      <c r="A212" s="30"/>
+      <c r="B212" s="30"/>
     </row>
     <row r="213">
-      <c r="A213" s="32"/>
-      <c r="B213" s="32"/>
+      <c r="A213" s="30"/>
+      <c r="B213" s="30"/>
     </row>
     <row r="214">
-      <c r="A214" s="32"/>
-      <c r="B214" s="32"/>
+      <c r="A214" s="30"/>
+      <c r="B214" s="30"/>
     </row>
     <row r="215">
-      <c r="A215" s="32"/>
-      <c r="B215" s="32"/>
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
     </row>
     <row r="216">
-      <c r="A216" s="32"/>
-      <c r="B216" s="32"/>
+      <c r="A216" s="30"/>
+      <c r="B216" s="30"/>
     </row>
     <row r="217">
-      <c r="A217" s="32"/>
-      <c r="B217" s="32"/>
+      <c r="A217" s="30"/>
+      <c r="B217" s="30"/>
     </row>
     <row r="218">
-      <c r="A218" s="32"/>
-      <c r="B218" s="32"/>
+      <c r="A218" s="30"/>
+      <c r="B218" s="30"/>
     </row>
     <row r="219">
-      <c r="A219" s="32"/>
-      <c r="B219" s="32"/>
+      <c r="A219" s="30"/>
+      <c r="B219" s="30"/>
     </row>
     <row r="220">
-      <c r="A220" s="32"/>
-      <c r="B220" s="32"/>
+      <c r="A220" s="30"/>
+      <c r="B220" s="30"/>
     </row>
     <row r="221">
-      <c r="A221" s="32"/>
-      <c r="B221" s="32"/>
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
     </row>
     <row r="222">
-      <c r="A222" s="32"/>
-      <c r="B222" s="32"/>
+      <c r="A222" s="30"/>
+      <c r="B222" s="30"/>
     </row>
     <row r="223">
-      <c r="A223" s="32"/>
-      <c r="B223" s="32"/>
+      <c r="A223" s="30"/>
+      <c r="B223" s="30"/>
     </row>
     <row r="224">
-      <c r="A224" s="32"/>
-      <c r="B224" s="32"/>
+      <c r="A224" s="30"/>
+      <c r="B224" s="30"/>
     </row>
     <row r="225">
-      <c r="A225" s="32"/>
-      <c r="B225" s="32"/>
+      <c r="A225" s="30"/>
+      <c r="B225" s="30"/>
     </row>
     <row r="226">
-      <c r="A226" s="32"/>
-      <c r="B226" s="32"/>
+      <c r="A226" s="30"/>
+      <c r="B226" s="30"/>
     </row>
     <row r="227">
-      <c r="A227" s="32"/>
-      <c r="B227" s="32"/>
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
     </row>
     <row r="228">
-      <c r="A228" s="32"/>
-      <c r="B228" s="32"/>
+      <c r="A228" s="30"/>
+      <c r="B228" s="30"/>
     </row>
     <row r="229">
-      <c r="A229" s="32"/>
-      <c r="B229" s="32"/>
+      <c r="A229" s="30"/>
+      <c r="B229" s="30"/>
     </row>
     <row r="230">
-      <c r="A230" s="32"/>
-      <c r="B230" s="32"/>
+      <c r="A230" s="30"/>
+      <c r="B230" s="30"/>
     </row>
     <row r="231">
-      <c r="A231" s="32"/>
-      <c r="B231" s="32"/>
+      <c r="A231" s="30"/>
+      <c r="B231" s="30"/>
     </row>
     <row r="232">
-      <c r="A232" s="32"/>
-      <c r="B232" s="32"/>
+      <c r="A232" s="30"/>
+      <c r="B232" s="30"/>
     </row>
     <row r="233">
-      <c r="A233" s="32"/>
-      <c r="B233" s="32"/>
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
     </row>
     <row r="234">
-      <c r="A234" s="32"/>
-      <c r="B234" s="32"/>
+      <c r="A234" s="30"/>
+      <c r="B234" s="30"/>
     </row>
     <row r="235">
-      <c r="A235" s="32"/>
-      <c r="B235" s="32"/>
+      <c r="A235" s="30"/>
+      <c r="B235" s="30"/>
     </row>
     <row r="236">
-      <c r="A236" s="32"/>
-      <c r="B236" s="32"/>
+      <c r="A236" s="30"/>
+      <c r="B236" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9011,2034 +9005,2034 @@
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="33" width="6"/>
+    <col customWidth="1" min="12" max="12" style="31" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="33" width="6"/>
+    <col customWidth="1" min="23" max="23" style="31" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="33" width="6"/>
+    <col customWidth="1" min="30" max="30" style="31" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="34" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="35" t="s">
+    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="L1" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="40" t="s">
+      <c r="O1" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="P1" s="37" t="s">
+      <c r="P1" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="37" t="s">
+      <c r="Q1" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="R1" s="37" t="s">
+      <c r="R1" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="S1" s="37" t="s">
+      <c r="S1" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="T1" s="37" t="s">
+      <c r="T1" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="U1" s="37" t="s">
+      <c r="U1" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="V1" s="39" t="s">
+      <c r="V1" s="37" t="s">
         <v>129</v>
       </c>
-      <c r="W1" s="42" t="s">
+      <c r="W1" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="X1" s="37" t="s">
+      <c r="X1" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="Y1" s="37" t="s">
+      <c r="Y1" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="Z1" s="39" t="s">
+      <c r="Z1" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="AA1" s="43" t="s">
+      <c r="AA1" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="AB1" s="44" t="s">
+      <c r="AB1" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="AC1" s="44" t="s">
+      <c r="AC1" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="AD1" s="41" t="s">
+      <c r="AD1" s="39" t="s">
         <v>137</v>
       </c>
-      <c r="AE1" s="45" t="s">
+      <c r="AE1" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="AF1" s="46" t="s">
+      <c r="AF1" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="AG1" s="47" t="s">
+      <c r="AG1" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="AH1" s="47" t="s">
+      <c r="AH1" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="AI1" s="47" t="s">
+      <c r="AI1" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="AJ1" s="47" t="s">
+      <c r="AJ1" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="AK1" s="44" t="s">
+      <c r="AK1" s="42" t="s">
         <v>143</v>
       </c>
-      <c r="AL1" s="48"/>
-      <c r="AM1" s="48"/>
-      <c r="AN1" s="48"/>
-      <c r="AO1" s="48"/>
-      <c r="AP1" s="48"/>
-      <c r="AQ1" s="48"/>
-      <c r="AR1" s="48"/>
-      <c r="AS1" s="48"/>
-      <c r="AT1" s="48"/>
-      <c r="AU1" s="48"/>
+      <c r="AL1" s="46"/>
+      <c r="AM1" s="46"/>
+      <c r="AN1" s="46"/>
+      <c r="AO1" s="46"/>
+      <c r="AP1" s="46"/>
+      <c r="AQ1" s="46"/>
+      <c r="AR1" s="46"/>
+      <c r="AS1" s="46"/>
+      <c r="AT1" s="46"/>
+      <c r="AU1" s="46"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="56"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="56"/>
-      <c r="AA2" s="57"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="56"/>
-      <c r="AF2" s="57"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="51"/>
-      <c r="AI2" s="51"/>
-      <c r="AJ2" s="51"/>
-      <c r="AK2" s="51"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="54"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="49"/>
+      <c r="AH2" s="49"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="49"/>
+      <c r="AK2" s="49"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="58"/>
-      <c r="X3" s="51"/>
-      <c r="Y3" s="51"/>
-      <c r="Z3" s="56"/>
-      <c r="AA3" s="57"/>
-      <c r="AB3" s="51"/>
-      <c r="AC3" s="51"/>
-      <c r="AD3" s="55"/>
-      <c r="AE3" s="56"/>
-      <c r="AF3" s="57"/>
-      <c r="AG3" s="51"/>
-      <c r="AH3" s="51"/>
-      <c r="AI3" s="51"/>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="51"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="54"/>
+      <c r="W3" s="56"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="53"/>
+      <c r="AE3" s="54"/>
+      <c r="AF3" s="55"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="49"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="49"/>
-      <c r="C4" s="50" t="s">
+      <c r="B4" s="47"/>
+      <c r="C4" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="57"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="56"/>
-      <c r="W4" s="58"/>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="57"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="55"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="57"/>
-      <c r="AG4" s="51"/>
-      <c r="AH4" s="51"/>
-      <c r="AI4" s="51"/>
-      <c r="AJ4" s="51"/>
-      <c r="AK4" s="51"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="54"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="54"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="53"/>
+      <c r="AE4" s="54"/>
+      <c r="AF4" s="55"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="49"/>
+      <c r="AI4" s="49"/>
+      <c r="AJ4" s="49"/>
+      <c r="AK4" s="49"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="57"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="51"/>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="58"/>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="51"/>
-      <c r="Z5" s="56"/>
-      <c r="AA5" s="57"/>
-      <c r="AB5" s="51"/>
-      <c r="AC5" s="51"/>
-      <c r="AD5" s="55"/>
-      <c r="AE5" s="56"/>
-      <c r="AF5" s="57"/>
-      <c r="AG5" s="51"/>
-      <c r="AH5" s="51"/>
-      <c r="AI5" s="51"/>
-      <c r="AJ5" s="51"/>
-      <c r="AK5" s="51"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="49"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="54"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="54"/>
+      <c r="AA5" s="55"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="53"/>
+      <c r="AE5" s="54"/>
+      <c r="AF5" s="55"/>
+      <c r="AG5" s="49"/>
+      <c r="AH5" s="49"/>
+      <c r="AI5" s="49"/>
+      <c r="AJ5" s="49"/>
+      <c r="AK5" s="49"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="49"/>
-      <c r="C6" s="50" t="s">
+      <c r="B6" s="47"/>
+      <c r="C6" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="51"/>
-      <c r="V6" s="56"/>
-      <c r="W6" s="58"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="51"/>
-      <c r="Z6" s="56"/>
-      <c r="AA6" s="57"/>
-      <c r="AB6" s="51"/>
-      <c r="AC6" s="51"/>
-      <c r="AD6" s="55"/>
-      <c r="AE6" s="53"/>
-      <c r="AF6" s="54"/>
-      <c r="AG6" s="65"/>
-      <c r="AH6" s="65"/>
-      <c r="AI6" s="65"/>
-      <c r="AJ6" s="65"/>
-      <c r="AK6" s="65"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="55"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="54"/>
+      <c r="W6" s="56"/>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="54"/>
+      <c r="AA6" s="55"/>
+      <c r="AB6" s="49"/>
+      <c r="AC6" s="49"/>
+      <c r="AD6" s="53"/>
+      <c r="AE6" s="51"/>
+      <c r="AF6" s="52"/>
+      <c r="AG6" s="63"/>
+      <c r="AH6" s="63"/>
+      <c r="AI6" s="63"/>
+      <c r="AJ6" s="63"/>
+      <c r="AK6" s="63"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="49"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="63"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="58"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
-      <c r="Z7" s="56"/>
-      <c r="AA7" s="57"/>
-      <c r="AB7" s="51"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="55"/>
-      <c r="AE7" s="56"/>
-      <c r="AF7" s="57"/>
-      <c r="AG7" s="51"/>
-      <c r="AH7" s="51"/>
-      <c r="AI7" s="51"/>
-      <c r="AJ7" s="51"/>
-      <c r="AK7" s="51"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="53"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="61"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="54"/>
+      <c r="AA7" s="55"/>
+      <c r="AB7" s="49"/>
+      <c r="AC7" s="49"/>
+      <c r="AD7" s="53"/>
+      <c r="AE7" s="54"/>
+      <c r="AF7" s="55"/>
+      <c r="AG7" s="49"/>
+      <c r="AH7" s="49"/>
+      <c r="AI7" s="49"/>
+      <c r="AJ7" s="49"/>
+      <c r="AK7" s="49"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="49"/>
-      <c r="C8" s="50" t="s">
+      <c r="B8" s="47"/>
+      <c r="C8" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="65"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="65"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="65"/>
-      <c r="Q8" s="65"/>
-      <c r="R8" s="65"/>
-      <c r="S8" s="65"/>
-      <c r="T8" s="65"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="53"/>
-      <c r="W8" s="58"/>
-      <c r="X8" s="65"/>
-      <c r="Y8" s="65"/>
-      <c r="Z8" s="53"/>
-      <c r="AA8" s="54"/>
-      <c r="AB8" s="65"/>
-      <c r="AC8" s="65"/>
-      <c r="AD8" s="55"/>
-      <c r="AE8" s="53"/>
-      <c r="AF8" s="54"/>
-      <c r="AG8" s="65"/>
-      <c r="AH8" s="65"/>
-      <c r="AI8" s="65"/>
-      <c r="AJ8" s="65"/>
-      <c r="AK8" s="65"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="63"/>
+      <c r="J8" s="63"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="53"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="63"/>
+      <c r="S8" s="63"/>
+      <c r="T8" s="63"/>
+      <c r="U8" s="63"/>
+      <c r="V8" s="51"/>
+      <c r="W8" s="56"/>
+      <c r="X8" s="63"/>
+      <c r="Y8" s="63"/>
+      <c r="Z8" s="51"/>
+      <c r="AA8" s="52"/>
+      <c r="AB8" s="63"/>
+      <c r="AC8" s="63"/>
+      <c r="AD8" s="53"/>
+      <c r="AE8" s="51"/>
+      <c r="AF8" s="52"/>
+      <c r="AG8" s="63"/>
+      <c r="AH8" s="63"/>
+      <c r="AI8" s="63"/>
+      <c r="AJ8" s="63"/>
+      <c r="AK8" s="63"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="49"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="64"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="64"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="66"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="62"/>
-      <c r="W9" s="58"/>
-      <c r="X9" s="64"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="62"/>
-      <c r="AA9" s="63"/>
-      <c r="AB9" s="51"/>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="64"/>
-      <c r="AE9" s="56"/>
-      <c r="AF9" s="57"/>
-      <c r="AG9" s="51"/>
-      <c r="AH9" s="51"/>
-      <c r="AI9" s="51"/>
-      <c r="AJ9" s="51"/>
-      <c r="AK9" s="51"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="62"/>
+      <c r="N9" s="54"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="62"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="62"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="60"/>
+      <c r="AA9" s="61"/>
+      <c r="AB9" s="49"/>
+      <c r="AC9" s="49"/>
+      <c r="AD9" s="62"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="55"/>
+      <c r="AG9" s="49"/>
+      <c r="AH9" s="49"/>
+      <c r="AI9" s="49"/>
+      <c r="AJ9" s="49"/>
+      <c r="AK9" s="49"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="49"/>
-      <c r="C10" s="50" t="s">
+      <c r="B10" s="47"/>
+      <c r="C10" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="51"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="57"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="51"/>
-      <c r="S10" s="51"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="51"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="58"/>
-      <c r="X10" s="65"/>
-      <c r="Y10" s="65"/>
-      <c r="Z10" s="53"/>
-      <c r="AA10" s="57"/>
-      <c r="AB10" s="51"/>
-      <c r="AC10" s="51"/>
-      <c r="AD10" s="55"/>
-      <c r="AE10" s="56"/>
-      <c r="AF10" s="57"/>
-      <c r="AG10" s="51"/>
-      <c r="AH10" s="51"/>
-      <c r="AI10" s="51"/>
-      <c r="AJ10" s="51"/>
-      <c r="AK10" s="51"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="55"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="51"/>
+      <c r="W10" s="56"/>
+      <c r="X10" s="63"/>
+      <c r="Y10" s="63"/>
+      <c r="Z10" s="51"/>
+      <c r="AA10" s="55"/>
+      <c r="AB10" s="49"/>
+      <c r="AC10" s="49"/>
+      <c r="AD10" s="53"/>
+      <c r="AE10" s="54"/>
+      <c r="AF10" s="55"/>
+      <c r="AG10" s="49"/>
+      <c r="AH10" s="49"/>
+      <c r="AI10" s="49"/>
+      <c r="AJ10" s="49"/>
+      <c r="AK10" s="49"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="49"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="55"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="56"/>
-      <c r="O11" s="57"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="56"/>
-      <c r="W11" s="58"/>
-      <c r="X11" s="51"/>
-      <c r="Y11" s="51"/>
-      <c r="Z11" s="56"/>
-      <c r="AA11" s="57"/>
-      <c r="AB11" s="51"/>
-      <c r="AC11" s="51"/>
-      <c r="AD11" s="67"/>
-      <c r="AE11" s="56"/>
-      <c r="AF11" s="57"/>
-      <c r="AG11" s="51"/>
-      <c r="AH11" s="51"/>
-      <c r="AI11" s="51"/>
-      <c r="AJ11" s="51"/>
-      <c r="AK11" s="51"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="49"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="55"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="55"/>
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="65"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="55"/>
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="49"/>
+      <c r="AI11" s="49"/>
+      <c r="AJ11" s="49"/>
+      <c r="AK11" s="49"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="49"/>
-      <c r="C12" s="50" t="s">
+      <c r="B12" s="47"/>
+      <c r="C12" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="59"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="55"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="56"/>
-      <c r="O12" s="57"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="51"/>
-      <c r="U12" s="51"/>
-      <c r="V12" s="56"/>
-      <c r="W12" s="58"/>
-      <c r="X12" s="51"/>
-      <c r="Y12" s="51"/>
-      <c r="Z12" s="56"/>
-      <c r="AA12" s="57"/>
-      <c r="AB12" s="51"/>
-      <c r="AC12" s="51"/>
-      <c r="AD12" s="55"/>
-      <c r="AE12" s="56"/>
-      <c r="AF12" s="54"/>
-      <c r="AG12" s="65"/>
-      <c r="AH12" s="65"/>
-      <c r="AI12" s="65"/>
-      <c r="AJ12" s="65"/>
-      <c r="AK12" s="65"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="53"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="55"/>
+      <c r="AB12" s="49"/>
+      <c r="AC12" s="49"/>
+      <c r="AD12" s="53"/>
+      <c r="AE12" s="54"/>
+      <c r="AF12" s="52"/>
+      <c r="AG12" s="63"/>
+      <c r="AH12" s="63"/>
+      <c r="AI12" s="63"/>
+      <c r="AJ12" s="63"/>
+      <c r="AK12" s="63"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="49"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="56"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="51"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="57"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="51"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="51"/>
-      <c r="U13" s="51"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="58"/>
-      <c r="X13" s="51"/>
-      <c r="Y13" s="51"/>
-      <c r="Z13" s="56"/>
-      <c r="AA13" s="57"/>
-      <c r="AB13" s="51"/>
-      <c r="AC13" s="51"/>
-      <c r="AD13" s="55"/>
-      <c r="AE13" s="56"/>
-      <c r="AF13" s="57"/>
-      <c r="AG13" s="51"/>
-      <c r="AH13" s="51"/>
-      <c r="AI13" s="51"/>
-      <c r="AJ13" s="51"/>
-      <c r="AK13" s="51"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="49"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="53"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="54"/>
+      <c r="W13" s="56"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="54"/>
+      <c r="AA13" s="55"/>
+      <c r="AB13" s="49"/>
+      <c r="AC13" s="49"/>
+      <c r="AD13" s="53"/>
+      <c r="AE13" s="54"/>
+      <c r="AF13" s="55"/>
+      <c r="AG13" s="49"/>
+      <c r="AH13" s="49"/>
+      <c r="AI13" s="49"/>
+      <c r="AJ13" s="49"/>
+      <c r="AK13" s="49"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="68" t="s">
+      <c r="B14" s="66" t="s">
         <v>148</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="67" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="71"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="71"/>
-      <c r="R14" s="71"/>
-      <c r="S14" s="71"/>
-      <c r="T14" s="71"/>
-      <c r="U14" s="71"/>
-      <c r="V14" s="72"/>
-      <c r="W14" s="58"/>
-      <c r="X14" s="71"/>
-      <c r="Y14" s="71"/>
-      <c r="Z14" s="72"/>
-      <c r="AA14" s="70"/>
-      <c r="AB14" s="71"/>
-      <c r="AC14" s="71"/>
-      <c r="AD14" s="55"/>
-      <c r="AE14" s="72"/>
-      <c r="AF14" s="70"/>
-      <c r="AG14" s="71"/>
-      <c r="AH14" s="71"/>
-      <c r="AI14" s="71"/>
-      <c r="AJ14" s="71"/>
-      <c r="AK14" s="71"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="53"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="69"/>
+      <c r="Q14" s="69"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="69"/>
+      <c r="T14" s="69"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="70"/>
+      <c r="W14" s="56"/>
+      <c r="X14" s="69"/>
+      <c r="Y14" s="69"/>
+      <c r="Z14" s="70"/>
+      <c r="AA14" s="68"/>
+      <c r="AB14" s="69"/>
+      <c r="AC14" s="69"/>
+      <c r="AD14" s="53"/>
+      <c r="AE14" s="70"/>
+      <c r="AF14" s="68"/>
+      <c r="AG14" s="69"/>
+      <c r="AH14" s="69"/>
+      <c r="AI14" s="69"/>
+      <c r="AJ14" s="69"/>
+      <c r="AK14" s="69"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="68"/>
-      <c r="C15" s="69"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="70"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="70"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-      <c r="T15" s="71"/>
-      <c r="U15" s="71"/>
-      <c r="V15" s="72"/>
-      <c r="W15" s="58"/>
-      <c r="X15" s="71"/>
-      <c r="Y15" s="71"/>
-      <c r="Z15" s="72"/>
-      <c r="AA15" s="70"/>
-      <c r="AB15" s="71"/>
-      <c r="AC15" s="71"/>
-      <c r="AD15" s="55"/>
-      <c r="AE15" s="72"/>
-      <c r="AF15" s="70"/>
-      <c r="AG15" s="71"/>
-      <c r="AH15" s="71"/>
-      <c r="AI15" s="71"/>
-      <c r="AJ15" s="71"/>
-      <c r="AK15" s="71"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="68"/>
+      <c r="P15" s="69"/>
+      <c r="Q15" s="69"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="69"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="70"/>
+      <c r="W15" s="56"/>
+      <c r="X15" s="69"/>
+      <c r="Y15" s="69"/>
+      <c r="Z15" s="70"/>
+      <c r="AA15" s="68"/>
+      <c r="AB15" s="69"/>
+      <c r="AC15" s="69"/>
+      <c r="AD15" s="53"/>
+      <c r="AE15" s="70"/>
+      <c r="AF15" s="68"/>
+      <c r="AG15" s="69"/>
+      <c r="AH15" s="69"/>
+      <c r="AI15" s="69"/>
+      <c r="AJ15" s="69"/>
+      <c r="AK15" s="69"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="68"/>
-      <c r="C16" s="69" t="s">
+      <c r="B16" s="66"/>
+      <c r="C16" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="70"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="71"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="70"/>
-      <c r="P16" s="71"/>
-      <c r="Q16" s="71"/>
-      <c r="R16" s="71"/>
-      <c r="S16" s="71"/>
-      <c r="T16" s="71"/>
-      <c r="U16" s="71"/>
-      <c r="V16" s="72"/>
-      <c r="W16" s="58"/>
-      <c r="X16" s="71"/>
-      <c r="Y16" s="71"/>
-      <c r="Z16" s="72"/>
-      <c r="AA16" s="70"/>
-      <c r="AB16" s="71"/>
-      <c r="AC16" s="71"/>
-      <c r="AD16" s="55"/>
-      <c r="AE16" s="72"/>
-      <c r="AF16" s="70"/>
-      <c r="AG16" s="71"/>
-      <c r="AH16" s="71"/>
-      <c r="AI16" s="71"/>
-      <c r="AJ16" s="71"/>
-      <c r="AK16" s="71"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="53"/>
+      <c r="M16" s="69"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="69"/>
+      <c r="Q16" s="69"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="69"/>
+      <c r="T16" s="69"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="70"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="69"/>
+      <c r="Y16" s="69"/>
+      <c r="Z16" s="70"/>
+      <c r="AA16" s="68"/>
+      <c r="AB16" s="69"/>
+      <c r="AC16" s="69"/>
+      <c r="AD16" s="53"/>
+      <c r="AE16" s="70"/>
+      <c r="AF16" s="68"/>
+      <c r="AG16" s="69"/>
+      <c r="AH16" s="69"/>
+      <c r="AI16" s="69"/>
+      <c r="AJ16" s="69"/>
+      <c r="AK16" s="69"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="68"/>
-      <c r="C17" s="69"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="70"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="71"/>
-      <c r="U17" s="71"/>
-      <c r="V17" s="72"/>
-      <c r="W17" s="58"/>
-      <c r="X17" s="71"/>
-      <c r="Y17" s="71"/>
-      <c r="Z17" s="72"/>
-      <c r="AA17" s="70"/>
-      <c r="AB17" s="71"/>
-      <c r="AC17" s="71"/>
-      <c r="AD17" s="55"/>
-      <c r="AE17" s="72"/>
-      <c r="AF17" s="70"/>
-      <c r="AG17" s="71"/>
-      <c r="AH17" s="71"/>
-      <c r="AI17" s="71"/>
-      <c r="AJ17" s="71"/>
-      <c r="AK17" s="71"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="53"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="69"/>
+      <c r="Q17" s="69"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="69"/>
+      <c r="U17" s="69"/>
+      <c r="V17" s="70"/>
+      <c r="W17" s="56"/>
+      <c r="X17" s="69"/>
+      <c r="Y17" s="69"/>
+      <c r="Z17" s="70"/>
+      <c r="AA17" s="68"/>
+      <c r="AB17" s="69"/>
+      <c r="AC17" s="69"/>
+      <c r="AD17" s="53"/>
+      <c r="AE17" s="70"/>
+      <c r="AF17" s="68"/>
+      <c r="AG17" s="69"/>
+      <c r="AH17" s="69"/>
+      <c r="AI17" s="69"/>
+      <c r="AJ17" s="69"/>
+      <c r="AK17" s="69"/>
       <c r="AN17" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="68"/>
-      <c r="C18" s="69" t="s">
+      <c r="B18" s="66"/>
+      <c r="C18" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="D18" s="65"/>
-      <c r="E18" s="65"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="70"/>
-      <c r="I18" s="71"/>
-      <c r="J18" s="71"/>
-      <c r="K18" s="71"/>
-      <c r="L18" s="55"/>
-      <c r="M18" s="71"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="70"/>
-      <c r="P18" s="71"/>
-      <c r="Q18" s="71"/>
-      <c r="R18" s="71"/>
-      <c r="S18" s="71"/>
-      <c r="T18" s="71"/>
-      <c r="U18" s="71"/>
-      <c r="V18" s="72"/>
-      <c r="W18" s="58"/>
-      <c r="X18" s="71"/>
-      <c r="Y18" s="71"/>
-      <c r="Z18" s="72"/>
-      <c r="AA18" s="70"/>
-      <c r="AB18" s="71"/>
-      <c r="AC18" s="71"/>
-      <c r="AD18" s="55"/>
-      <c r="AE18" s="72"/>
-      <c r="AF18" s="70"/>
-      <c r="AG18" s="71"/>
-      <c r="AH18" s="71"/>
-      <c r="AI18" s="71"/>
-      <c r="AJ18" s="71"/>
-      <c r="AK18" s="71"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="53"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="70"/>
+      <c r="O18" s="68"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="69"/>
+      <c r="R18" s="69"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="69"/>
+      <c r="U18" s="69"/>
+      <c r="V18" s="70"/>
+      <c r="W18" s="56"/>
+      <c r="X18" s="69"/>
+      <c r="Y18" s="69"/>
+      <c r="Z18" s="70"/>
+      <c r="AA18" s="68"/>
+      <c r="AB18" s="69"/>
+      <c r="AC18" s="69"/>
+      <c r="AD18" s="53"/>
+      <c r="AE18" s="70"/>
+      <c r="AF18" s="68"/>
+      <c r="AG18" s="69"/>
+      <c r="AH18" s="69"/>
+      <c r="AI18" s="69"/>
+      <c r="AJ18" s="69"/>
+      <c r="AK18" s="69"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="68"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="75"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="70"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="70"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
-      <c r="T19" s="71"/>
-      <c r="U19" s="71"/>
-      <c r="V19" s="72"/>
-      <c r="W19" s="58"/>
-      <c r="X19" s="71"/>
-      <c r="Y19" s="71"/>
-      <c r="Z19" s="72"/>
-      <c r="AA19" s="70"/>
-      <c r="AB19" s="71"/>
-      <c r="AC19" s="71"/>
-      <c r="AD19" s="55"/>
-      <c r="AE19" s="72"/>
-      <c r="AF19" s="70"/>
-      <c r="AG19" s="71"/>
-      <c r="AH19" s="71"/>
-      <c r="AI19" s="71"/>
-      <c r="AJ19" s="71"/>
-      <c r="AK19" s="71"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="53"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="68"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="69"/>
+      <c r="R19" s="69"/>
+      <c r="S19" s="69"/>
+      <c r="T19" s="69"/>
+      <c r="U19" s="69"/>
+      <c r="V19" s="70"/>
+      <c r="W19" s="56"/>
+      <c r="X19" s="69"/>
+      <c r="Y19" s="69"/>
+      <c r="Z19" s="70"/>
+      <c r="AA19" s="68"/>
+      <c r="AB19" s="69"/>
+      <c r="AC19" s="69"/>
+      <c r="AD19" s="53"/>
+      <c r="AE19" s="70"/>
+      <c r="AF19" s="68"/>
+      <c r="AG19" s="69"/>
+      <c r="AH19" s="69"/>
+      <c r="AI19" s="69"/>
+      <c r="AJ19" s="69"/>
+      <c r="AK19" s="69"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="68"/>
-      <c r="C20" s="69" t="s">
+      <c r="B20" s="66"/>
+      <c r="C20" s="67" t="s">
         <v>153</v>
       </c>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="71"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="55"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="70"/>
-      <c r="P20" s="71"/>
-      <c r="Q20" s="71"/>
-      <c r="R20" s="71"/>
-      <c r="S20" s="71"/>
-      <c r="T20" s="71"/>
-      <c r="U20" s="71"/>
-      <c r="V20" s="72"/>
-      <c r="W20" s="58"/>
-      <c r="X20" s="71"/>
-      <c r="Y20" s="71"/>
-      <c r="Z20" s="72"/>
-      <c r="AA20" s="70"/>
-      <c r="AB20" s="71"/>
-      <c r="AC20" s="71"/>
-      <c r="AD20" s="55"/>
-      <c r="AE20" s="72"/>
-      <c r="AF20" s="70"/>
-      <c r="AG20" s="71"/>
-      <c r="AH20" s="71"/>
-      <c r="AI20" s="71"/>
-      <c r="AJ20" s="71"/>
-      <c r="AK20" s="71"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="72"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="53"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="68"/>
+      <c r="P20" s="69"/>
+      <c r="Q20" s="69"/>
+      <c r="R20" s="69"/>
+      <c r="S20" s="69"/>
+      <c r="T20" s="69"/>
+      <c r="U20" s="69"/>
+      <c r="V20" s="70"/>
+      <c r="W20" s="56"/>
+      <c r="X20" s="69"/>
+      <c r="Y20" s="69"/>
+      <c r="Z20" s="70"/>
+      <c r="AA20" s="68"/>
+      <c r="AB20" s="69"/>
+      <c r="AC20" s="69"/>
+      <c r="AD20" s="53"/>
+      <c r="AE20" s="70"/>
+      <c r="AF20" s="68"/>
+      <c r="AG20" s="69"/>
+      <c r="AH20" s="69"/>
+      <c r="AI20" s="69"/>
+      <c r="AJ20" s="69"/>
+      <c r="AK20" s="69"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="68"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="72"/>
-      <c r="H21" s="70"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="55"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="72"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="71"/>
-      <c r="T21" s="71"/>
-      <c r="U21" s="71"/>
-      <c r="V21" s="72"/>
-      <c r="W21" s="58"/>
-      <c r="X21" s="71"/>
-      <c r="Y21" s="71"/>
-      <c r="Z21" s="72"/>
-      <c r="AA21" s="70"/>
-      <c r="AB21" s="71"/>
-      <c r="AC21" s="71"/>
-      <c r="AD21" s="55"/>
-      <c r="AE21" s="72"/>
-      <c r="AF21" s="70"/>
-      <c r="AG21" s="71"/>
-      <c r="AH21" s="71"/>
-      <c r="AI21" s="71"/>
-      <c r="AJ21" s="71"/>
-      <c r="AK21" s="71"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="72"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="69"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="69"/>
+      <c r="Q21" s="69"/>
+      <c r="R21" s="69"/>
+      <c r="S21" s="69"/>
+      <c r="T21" s="69"/>
+      <c r="U21" s="69"/>
+      <c r="V21" s="70"/>
+      <c r="W21" s="56"/>
+      <c r="X21" s="69"/>
+      <c r="Y21" s="69"/>
+      <c r="Z21" s="70"/>
+      <c r="AA21" s="68"/>
+      <c r="AB21" s="69"/>
+      <c r="AC21" s="69"/>
+      <c r="AD21" s="53"/>
+      <c r="AE21" s="70"/>
+      <c r="AF21" s="68"/>
+      <c r="AG21" s="69"/>
+      <c r="AH21" s="69"/>
+      <c r="AI21" s="69"/>
+      <c r="AJ21" s="69"/>
+      <c r="AK21" s="69"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="68"/>
-      <c r="C22" s="69" t="s">
+      <c r="B22" s="66"/>
+      <c r="C22" s="67" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="71"/>
-      <c r="Q22" s="71"/>
-      <c r="R22" s="71"/>
-      <c r="S22" s="71"/>
-      <c r="T22" s="71"/>
-      <c r="U22" s="71"/>
-      <c r="V22" s="72"/>
-      <c r="W22" s="58"/>
-      <c r="X22" s="71"/>
-      <c r="Y22" s="71"/>
-      <c r="Z22" s="72"/>
-      <c r="AA22" s="70"/>
-      <c r="AB22" s="71"/>
-      <c r="AC22" s="71"/>
-      <c r="AD22" s="55"/>
-      <c r="AE22" s="72"/>
-      <c r="AF22" s="70"/>
-      <c r="AG22" s="71"/>
-      <c r="AH22" s="71"/>
-      <c r="AI22" s="71"/>
-      <c r="AJ22" s="71"/>
-      <c r="AK22" s="71"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="53"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="69"/>
+      <c r="Q22" s="69"/>
+      <c r="R22" s="69"/>
+      <c r="S22" s="69"/>
+      <c r="T22" s="69"/>
+      <c r="U22" s="69"/>
+      <c r="V22" s="70"/>
+      <c r="W22" s="56"/>
+      <c r="X22" s="69"/>
+      <c r="Y22" s="69"/>
+      <c r="Z22" s="70"/>
+      <c r="AA22" s="68"/>
+      <c r="AB22" s="69"/>
+      <c r="AC22" s="69"/>
+      <c r="AD22" s="53"/>
+      <c r="AE22" s="70"/>
+      <c r="AF22" s="68"/>
+      <c r="AG22" s="69"/>
+      <c r="AH22" s="69"/>
+      <c r="AI22" s="69"/>
+      <c r="AJ22" s="69"/>
+      <c r="AK22" s="69"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="68"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="72"/>
-      <c r="O23" s="70"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="71"/>
-      <c r="S23" s="71"/>
-      <c r="T23" s="71"/>
-      <c r="U23" s="71"/>
-      <c r="V23" s="72"/>
-      <c r="W23" s="58"/>
-      <c r="X23" s="71"/>
-      <c r="Y23" s="71"/>
-      <c r="Z23" s="72"/>
-      <c r="AA23" s="70"/>
-      <c r="AB23" s="71"/>
-      <c r="AC23" s="71"/>
-      <c r="AD23" s="55"/>
-      <c r="AE23" s="72"/>
-      <c r="AF23" s="70"/>
-      <c r="AG23" s="71"/>
-      <c r="AH23" s="71"/>
-      <c r="AI23" s="71"/>
-      <c r="AJ23" s="71"/>
-      <c r="AK23" s="71"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="68"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="69"/>
+      <c r="R23" s="69"/>
+      <c r="S23" s="69"/>
+      <c r="T23" s="69"/>
+      <c r="U23" s="69"/>
+      <c r="V23" s="70"/>
+      <c r="W23" s="56"/>
+      <c r="X23" s="69"/>
+      <c r="Y23" s="69"/>
+      <c r="Z23" s="70"/>
+      <c r="AA23" s="68"/>
+      <c r="AB23" s="69"/>
+      <c r="AC23" s="69"/>
+      <c r="AD23" s="53"/>
+      <c r="AE23" s="70"/>
+      <c r="AF23" s="68"/>
+      <c r="AG23" s="69"/>
+      <c r="AH23" s="69"/>
+      <c r="AI23" s="69"/>
+      <c r="AJ23" s="69"/>
+      <c r="AK23" s="69"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="68"/>
-      <c r="C24" s="69" t="s">
+      <c r="B24" s="66"/>
+      <c r="C24" s="67" t="s">
         <v>155</v>
       </c>
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="71"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
-      <c r="R24" s="71"/>
-      <c r="S24" s="71"/>
-      <c r="T24" s="71"/>
-      <c r="U24" s="71"/>
-      <c r="V24" s="72"/>
-      <c r="W24" s="58"/>
-      <c r="X24" s="71"/>
-      <c r="Y24" s="71"/>
-      <c r="Z24" s="72"/>
-      <c r="AA24" s="70"/>
-      <c r="AB24" s="71"/>
-      <c r="AC24" s="71"/>
-      <c r="AD24" s="55"/>
-      <c r="AE24" s="72"/>
-      <c r="AF24" s="70"/>
-      <c r="AG24" s="71"/>
-      <c r="AH24" s="71"/>
-      <c r="AI24" s="71"/>
-      <c r="AJ24" s="71"/>
-      <c r="AK24" s="71"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="72"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="53"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="68"/>
+      <c r="P24" s="69"/>
+      <c r="Q24" s="69"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="69"/>
+      <c r="U24" s="69"/>
+      <c r="V24" s="70"/>
+      <c r="W24" s="56"/>
+      <c r="X24" s="69"/>
+      <c r="Y24" s="69"/>
+      <c r="Z24" s="70"/>
+      <c r="AA24" s="68"/>
+      <c r="AB24" s="69"/>
+      <c r="AC24" s="69"/>
+      <c r="AD24" s="53"/>
+      <c r="AE24" s="70"/>
+      <c r="AF24" s="68"/>
+      <c r="AG24" s="69"/>
+      <c r="AH24" s="69"/>
+      <c r="AI24" s="69"/>
+      <c r="AJ24" s="69"/>
+      <c r="AK24" s="69"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="68"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="60"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="70"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="71"/>
-      <c r="S25" s="71"/>
-      <c r="T25" s="71"/>
-      <c r="U25" s="71"/>
-      <c r="V25" s="72"/>
-      <c r="W25" s="58"/>
-      <c r="X25" s="71"/>
-      <c r="Y25" s="71"/>
-      <c r="Z25" s="72"/>
-      <c r="AA25" s="70"/>
-      <c r="AB25" s="71"/>
-      <c r="AC25" s="71"/>
-      <c r="AD25" s="55"/>
-      <c r="AE25" s="72"/>
-      <c r="AF25" s="70"/>
-      <c r="AG25" s="71"/>
-      <c r="AH25" s="71"/>
-      <c r="AI25" s="71"/>
-      <c r="AJ25" s="71"/>
-      <c r="AK25" s="71"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="69"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="70"/>
+      <c r="O25" s="68"/>
+      <c r="P25" s="69"/>
+      <c r="Q25" s="69"/>
+      <c r="R25" s="69"/>
+      <c r="S25" s="69"/>
+      <c r="T25" s="69"/>
+      <c r="U25" s="69"/>
+      <c r="V25" s="70"/>
+      <c r="W25" s="56"/>
+      <c r="X25" s="69"/>
+      <c r="Y25" s="69"/>
+      <c r="Z25" s="70"/>
+      <c r="AA25" s="68"/>
+      <c r="AB25" s="69"/>
+      <c r="AC25" s="69"/>
+      <c r="AD25" s="53"/>
+      <c r="AE25" s="70"/>
+      <c r="AF25" s="68"/>
+      <c r="AG25" s="69"/>
+      <c r="AH25" s="69"/>
+      <c r="AI25" s="69"/>
+      <c r="AJ25" s="69"/>
+      <c r="AK25" s="69"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="51"/>
-      <c r="N26" s="56"/>
-      <c r="O26" s="57"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="51"/>
-      <c r="R26" s="51"/>
-      <c r="S26" s="51"/>
-      <c r="T26" s="51"/>
-      <c r="U26" s="51"/>
-      <c r="V26" s="56"/>
-      <c r="W26" s="58"/>
-      <c r="X26" s="51"/>
-      <c r="Y26" s="51"/>
-      <c r="Z26" s="56"/>
-      <c r="AA26" s="57"/>
-      <c r="AB26" s="51"/>
-      <c r="AC26" s="51"/>
-      <c r="AD26" s="55"/>
-      <c r="AE26" s="56"/>
-      <c r="AF26" s="57"/>
-      <c r="AG26" s="51"/>
-      <c r="AH26" s="51"/>
-      <c r="AI26" s="51"/>
-      <c r="AJ26" s="51"/>
-      <c r="AK26" s="51"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="54"/>
+      <c r="O26" s="55"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="54"/>
+      <c r="W26" s="56"/>
+      <c r="X26" s="49"/>
+      <c r="Y26" s="49"/>
+      <c r="Z26" s="54"/>
+      <c r="AA26" s="55"/>
+      <c r="AB26" s="49"/>
+      <c r="AC26" s="49"/>
+      <c r="AD26" s="53"/>
+      <c r="AE26" s="54"/>
+      <c r="AF26" s="55"/>
+      <c r="AG26" s="49"/>
+      <c r="AH26" s="49"/>
+      <c r="AI26" s="49"/>
+      <c r="AJ26" s="49"/>
+      <c r="AK26" s="49"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="49"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="63"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
-      <c r="K27" s="51"/>
-      <c r="L27" s="55"/>
-      <c r="M27" s="51"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="57"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="51"/>
-      <c r="S27" s="51"/>
-      <c r="T27" s="51"/>
-      <c r="U27" s="51"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="58"/>
-      <c r="X27" s="51"/>
-      <c r="Y27" s="51"/>
-      <c r="Z27" s="56"/>
-      <c r="AA27" s="57"/>
-      <c r="AB27" s="51"/>
-      <c r="AC27" s="51"/>
-      <c r="AD27" s="55"/>
-      <c r="AE27" s="56"/>
-      <c r="AF27" s="57"/>
-      <c r="AG27" s="51"/>
-      <c r="AH27" s="51"/>
-      <c r="AI27" s="51"/>
-      <c r="AJ27" s="51"/>
-      <c r="AK27" s="51"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="55"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
+      <c r="U27" s="49"/>
+      <c r="V27" s="54"/>
+      <c r="W27" s="56"/>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="54"/>
+      <c r="AA27" s="55"/>
+      <c r="AB27" s="49"/>
+      <c r="AC27" s="49"/>
+      <c r="AD27" s="53"/>
+      <c r="AE27" s="54"/>
+      <c r="AF27" s="55"/>
+      <c r="AG27" s="49"/>
+      <c r="AH27" s="49"/>
+      <c r="AI27" s="49"/>
+      <c r="AJ27" s="49"/>
+      <c r="AK27" s="49"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="49"/>
-      <c r="C28" s="50" t="s">
+      <c r="B28" s="47"/>
+      <c r="C28" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="55"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="57"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="51"/>
-      <c r="R28" s="51"/>
-      <c r="S28" s="51"/>
-      <c r="T28" s="51"/>
-      <c r="U28" s="51"/>
-      <c r="V28" s="56"/>
-      <c r="W28" s="58"/>
-      <c r="X28" s="51"/>
-      <c r="Y28" s="51"/>
-      <c r="Z28" s="56"/>
-      <c r="AA28" s="57"/>
-      <c r="AB28" s="51"/>
-      <c r="AC28" s="51"/>
-      <c r="AD28" s="55"/>
-      <c r="AE28" s="56"/>
-      <c r="AF28" s="57"/>
-      <c r="AG28" s="51"/>
-      <c r="AH28" s="51"/>
-      <c r="AI28" s="51"/>
-      <c r="AJ28" s="51"/>
-      <c r="AK28" s="51"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" s="63"/>
+      <c r="L28" s="53"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="54"/>
+      <c r="O28" s="55"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="54"/>
+      <c r="W28" s="56"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="54"/>
+      <c r="AA28" s="55"/>
+      <c r="AB28" s="49"/>
+      <c r="AC28" s="49"/>
+      <c r="AD28" s="53"/>
+      <c r="AE28" s="54"/>
+      <c r="AF28" s="55"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="49"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="59"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="51"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="51"/>
-      <c r="N29" s="56"/>
-      <c r="O29" s="57"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="51"/>
-      <c r="S29" s="51"/>
-      <c r="T29" s="51"/>
-      <c r="U29" s="51"/>
-      <c r="V29" s="56"/>
-      <c r="W29" s="58"/>
-      <c r="X29" s="51"/>
-      <c r="Y29" s="51"/>
-      <c r="Z29" s="56"/>
-      <c r="AA29" s="57"/>
-      <c r="AB29" s="51"/>
-      <c r="AC29" s="51"/>
-      <c r="AD29" s="55"/>
-      <c r="AE29" s="56"/>
-      <c r="AF29" s="57"/>
-      <c r="AG29" s="51"/>
-      <c r="AH29" s="51"/>
-      <c r="AI29" s="51"/>
-      <c r="AJ29" s="51"/>
-      <c r="AK29" s="51"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="55"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="49"/>
+      <c r="R29" s="49"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
+      <c r="U29" s="49"/>
+      <c r="V29" s="54"/>
+      <c r="W29" s="56"/>
+      <c r="X29" s="49"/>
+      <c r="Y29" s="49"/>
+      <c r="Z29" s="54"/>
+      <c r="AA29" s="55"/>
+      <c r="AB29" s="49"/>
+      <c r="AC29" s="49"/>
+      <c r="AD29" s="53"/>
+      <c r="AE29" s="54"/>
+      <c r="AF29" s="55"/>
+      <c r="AG29" s="49"/>
+      <c r="AH29" s="49"/>
+      <c r="AI29" s="49"/>
+      <c r="AJ29" s="49"/>
+      <c r="AK29" s="49"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="49"/>
-      <c r="C30" s="50" t="s">
+      <c r="B30" s="47"/>
+      <c r="C30" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="54"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="65"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="57"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="51"/>
-      <c r="S30" s="51"/>
-      <c r="T30" s="51"/>
-      <c r="U30" s="51"/>
-      <c r="V30" s="56"/>
-      <c r="W30" s="58"/>
-      <c r="X30" s="51"/>
-      <c r="Y30" s="51"/>
-      <c r="Z30" s="56"/>
-      <c r="AA30" s="57"/>
-      <c r="AB30" s="51"/>
-      <c r="AC30" s="51"/>
-      <c r="AD30" s="55"/>
-      <c r="AE30" s="56"/>
-      <c r="AF30" s="57"/>
-      <c r="AG30" s="51"/>
-      <c r="AH30" s="51"/>
-      <c r="AI30" s="51"/>
-      <c r="AJ30" s="51"/>
-      <c r="AK30" s="51"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
+      <c r="K30" s="63"/>
+      <c r="L30" s="53"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="55"/>
+      <c r="P30" s="49"/>
+      <c r="Q30" s="49"/>
+      <c r="R30" s="49"/>
+      <c r="S30" s="49"/>
+      <c r="T30" s="49"/>
+      <c r="U30" s="49"/>
+      <c r="V30" s="54"/>
+      <c r="W30" s="56"/>
+      <c r="X30" s="49"/>
+      <c r="Y30" s="49"/>
+      <c r="Z30" s="54"/>
+      <c r="AA30" s="55"/>
+      <c r="AB30" s="49"/>
+      <c r="AC30" s="49"/>
+      <c r="AD30" s="53"/>
+      <c r="AE30" s="54"/>
+      <c r="AF30" s="55"/>
+      <c r="AG30" s="49"/>
+      <c r="AH30" s="49"/>
+      <c r="AI30" s="49"/>
+      <c r="AJ30" s="49"/>
+      <c r="AK30" s="49"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="49"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="66"/>
-      <c r="K31" s="66"/>
-      <c r="L31" s="76"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="62"/>
-      <c r="O31" s="57"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-      <c r="R31" s="51"/>
-      <c r="S31" s="51"/>
-      <c r="T31" s="51"/>
-      <c r="U31" s="51"/>
-      <c r="V31" s="56"/>
-      <c r="W31" s="58"/>
-      <c r="X31" s="51"/>
-      <c r="Y31" s="51"/>
-      <c r="Z31" s="56"/>
-      <c r="AA31" s="57"/>
-      <c r="AB31" s="51"/>
-      <c r="AC31" s="51"/>
-      <c r="AD31" s="55"/>
-      <c r="AE31" s="56"/>
-      <c r="AF31" s="57"/>
-      <c r="AG31" s="51"/>
-      <c r="AH31" s="51"/>
-      <c r="AI31" s="51"/>
-      <c r="AJ31" s="51"/>
-      <c r="AK31" s="51"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="49"/>
+      <c r="J31" s="64"/>
+      <c r="K31" s="64"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="49"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="49"/>
+      <c r="Q31" s="49"/>
+      <c r="R31" s="49"/>
+      <c r="S31" s="49"/>
+      <c r="T31" s="49"/>
+      <c r="U31" s="49"/>
+      <c r="V31" s="54"/>
+      <c r="W31" s="56"/>
+      <c r="X31" s="49"/>
+      <c r="Y31" s="49"/>
+      <c r="Z31" s="54"/>
+      <c r="AA31" s="55"/>
+      <c r="AB31" s="49"/>
+      <c r="AC31" s="49"/>
+      <c r="AD31" s="53"/>
+      <c r="AE31" s="54"/>
+      <c r="AF31" s="55"/>
+      <c r="AG31" s="49"/>
+      <c r="AH31" s="49"/>
+      <c r="AI31" s="49"/>
+      <c r="AJ31" s="49"/>
+      <c r="AK31" s="49"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="49"/>
-      <c r="C32" s="50" t="s">
+      <c r="B32" s="47"/>
+      <c r="C32" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="57"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="51"/>
-      <c r="K32" s="51"/>
-      <c r="L32" s="55"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="53"/>
-      <c r="O32" s="57"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="51"/>
-      <c r="R32" s="51"/>
-      <c r="S32" s="51"/>
-      <c r="T32" s="51"/>
-      <c r="U32" s="51"/>
-      <c r="V32" s="56"/>
-      <c r="W32" s="58"/>
-      <c r="X32" s="51"/>
-      <c r="Y32" s="51"/>
-      <c r="Z32" s="56"/>
-      <c r="AA32" s="57"/>
-      <c r="AB32" s="51"/>
-      <c r="AC32" s="51"/>
-      <c r="AD32" s="55"/>
-      <c r="AE32" s="56"/>
-      <c r="AF32" s="57"/>
-      <c r="AG32" s="51"/>
-      <c r="AH32" s="51"/>
-      <c r="AI32" s="51"/>
-      <c r="AJ32" s="51"/>
-      <c r="AK32" s="51"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="54"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="51"/>
+      <c r="O32" s="55"/>
+      <c r="P32" s="49"/>
+      <c r="Q32" s="49"/>
+      <c r="R32" s="49"/>
+      <c r="S32" s="49"/>
+      <c r="T32" s="49"/>
+      <c r="U32" s="49"/>
+      <c r="V32" s="54"/>
+      <c r="W32" s="56"/>
+      <c r="X32" s="49"/>
+      <c r="Y32" s="49"/>
+      <c r="Z32" s="54"/>
+      <c r="AA32" s="55"/>
+      <c r="AB32" s="49"/>
+      <c r="AC32" s="49"/>
+      <c r="AD32" s="53"/>
+      <c r="AE32" s="54"/>
+      <c r="AF32" s="55"/>
+      <c r="AG32" s="49"/>
+      <c r="AH32" s="49"/>
+      <c r="AI32" s="49"/>
+      <c r="AJ32" s="49"/>
+      <c r="AK32" s="49"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="49"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="57"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="55"/>
-      <c r="M33" s="51"/>
-      <c r="N33" s="62"/>
-      <c r="O33" s="57"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="51"/>
-      <c r="R33" s="51"/>
-      <c r="S33" s="51"/>
-      <c r="T33" s="51"/>
-      <c r="U33" s="51"/>
-      <c r="V33" s="56"/>
-      <c r="W33" s="58"/>
-      <c r="X33" s="51"/>
-      <c r="Y33" s="51"/>
-      <c r="Z33" s="56"/>
-      <c r="AA33" s="57"/>
-      <c r="AB33" s="51"/>
-      <c r="AC33" s="51"/>
-      <c r="AD33" s="55"/>
-      <c r="AE33" s="56"/>
-      <c r="AF33" s="57"/>
-      <c r="AG33" s="51"/>
-      <c r="AH33" s="51"/>
-      <c r="AI33" s="51"/>
-      <c r="AJ33" s="51"/>
-      <c r="AK33" s="51"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
+      <c r="K33" s="49"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="60"/>
+      <c r="O33" s="55"/>
+      <c r="P33" s="49"/>
+      <c r="Q33" s="49"/>
+      <c r="R33" s="49"/>
+      <c r="S33" s="49"/>
+      <c r="T33" s="49"/>
+      <c r="U33" s="49"/>
+      <c r="V33" s="54"/>
+      <c r="W33" s="56"/>
+      <c r="X33" s="49"/>
+      <c r="Y33" s="49"/>
+      <c r="Z33" s="54"/>
+      <c r="AA33" s="55"/>
+      <c r="AB33" s="49"/>
+      <c r="AC33" s="49"/>
+      <c r="AD33" s="53"/>
+      <c r="AE33" s="54"/>
+      <c r="AF33" s="55"/>
+      <c r="AG33" s="49"/>
+      <c r="AH33" s="49"/>
+      <c r="AI33" s="49"/>
+      <c r="AJ33" s="49"/>
+      <c r="AK33" s="49"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="68" t="s">
+      <c r="B34" s="66" t="s">
         <v>161</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C34" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="55"/>
-      <c r="M34" s="65"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="54"/>
-      <c r="P34" s="65"/>
-      <c r="Q34" s="65"/>
-      <c r="R34" s="65"/>
-      <c r="S34" s="71"/>
-      <c r="T34" s="71"/>
-      <c r="U34" s="71"/>
-      <c r="V34" s="72"/>
-      <c r="W34" s="58"/>
-      <c r="X34" s="71"/>
-      <c r="Y34" s="71"/>
-      <c r="Z34" s="72"/>
-      <c r="AA34" s="70"/>
-      <c r="AB34" s="71"/>
-      <c r="AC34" s="71"/>
-      <c r="AD34" s="55"/>
-      <c r="AE34" s="72"/>
-      <c r="AF34" s="70"/>
-      <c r="AG34" s="71"/>
-      <c r="AH34" s="71"/>
-      <c r="AI34" s="71"/>
-      <c r="AJ34" s="71"/>
-      <c r="AK34" s="71"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="68"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="69"/>
+      <c r="K34" s="69"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="63"/>
+      <c r="N34" s="51"/>
+      <c r="O34" s="52"/>
+      <c r="P34" s="63"/>
+      <c r="Q34" s="63"/>
+      <c r="R34" s="63"/>
+      <c r="S34" s="69"/>
+      <c r="T34" s="69"/>
+      <c r="U34" s="69"/>
+      <c r="V34" s="70"/>
+      <c r="W34" s="56"/>
+      <c r="X34" s="69"/>
+      <c r="Y34" s="69"/>
+      <c r="Z34" s="70"/>
+      <c r="AA34" s="68"/>
+      <c r="AB34" s="69"/>
+      <c r="AC34" s="69"/>
+      <c r="AD34" s="53"/>
+      <c r="AE34" s="70"/>
+      <c r="AF34" s="68"/>
+      <c r="AG34" s="69"/>
+      <c r="AH34" s="69"/>
+      <c r="AI34" s="69"/>
+      <c r="AJ34" s="69"/>
+      <c r="AK34" s="69"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="68"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="78"/>
-      <c r="L35" s="55"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="62"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="64"/>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="79"/>
-      <c r="S35" s="79"/>
-      <c r="T35" s="60"/>
-      <c r="U35" s="71"/>
-      <c r="V35" s="72"/>
-      <c r="W35" s="58"/>
-      <c r="X35" s="71"/>
-      <c r="Y35" s="71"/>
-      <c r="Z35" s="72"/>
-      <c r="AA35" s="70"/>
-      <c r="AB35" s="71"/>
-      <c r="AC35" s="71"/>
-      <c r="AD35" s="55"/>
-      <c r="AE35" s="72"/>
-      <c r="AF35" s="70"/>
-      <c r="AG35" s="71"/>
-      <c r="AH35" s="71"/>
-      <c r="AI35" s="71"/>
-      <c r="AJ35" s="71"/>
-      <c r="AK35" s="71"/>
+      <c r="B35" s="66"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="68"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="76"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="69"/>
+      <c r="N35" s="60"/>
+      <c r="O35" s="68"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="69"/>
+      <c r="R35" s="77"/>
+      <c r="S35" s="77"/>
+      <c r="T35" s="58"/>
+      <c r="U35" s="69"/>
+      <c r="V35" s="70"/>
+      <c r="W35" s="56"/>
+      <c r="X35" s="69"/>
+      <c r="Y35" s="69"/>
+      <c r="Z35" s="70"/>
+      <c r="AA35" s="68"/>
+      <c r="AB35" s="69"/>
+      <c r="AC35" s="69"/>
+      <c r="AD35" s="53"/>
+      <c r="AE35" s="70"/>
+      <c r="AF35" s="68"/>
+      <c r="AG35" s="69"/>
+      <c r="AH35" s="69"/>
+      <c r="AI35" s="69"/>
+      <c r="AJ35" s="69"/>
+      <c r="AK35" s="69"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="68"/>
-      <c r="C36" s="77" t="s">
+      <c r="B36" s="66"/>
+      <c r="C36" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="65"/>
-      <c r="N36" s="53"/>
-      <c r="O36" s="54"/>
-      <c r="P36" s="65"/>
-      <c r="Q36" s="71"/>
-      <c r="R36" s="71"/>
-      <c r="S36" s="71"/>
-      <c r="T36" s="71"/>
-      <c r="U36" s="71"/>
-      <c r="V36" s="72"/>
-      <c r="W36" s="58"/>
-      <c r="X36" s="71"/>
-      <c r="Y36" s="71"/>
-      <c r="Z36" s="72"/>
-      <c r="AA36" s="70"/>
-      <c r="AB36" s="71"/>
-      <c r="AC36" s="71"/>
-      <c r="AD36" s="55"/>
-      <c r="AE36" s="72"/>
-      <c r="AF36" s="70"/>
-      <c r="AG36" s="71"/>
-      <c r="AH36" s="71"/>
-      <c r="AI36" s="71"/>
-      <c r="AJ36" s="71"/>
-      <c r="AK36" s="71"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="69"/>
+      <c r="L36" s="53"/>
+      <c r="M36" s="63"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="52"/>
+      <c r="P36" s="63"/>
+      <c r="Q36" s="69"/>
+      <c r="R36" s="69"/>
+      <c r="S36" s="69"/>
+      <c r="T36" s="69"/>
+      <c r="U36" s="69"/>
+      <c r="V36" s="70"/>
+      <c r="W36" s="56"/>
+      <c r="X36" s="69"/>
+      <c r="Y36" s="69"/>
+      <c r="Z36" s="70"/>
+      <c r="AA36" s="68"/>
+      <c r="AB36" s="69"/>
+      <c r="AC36" s="69"/>
+      <c r="AD36" s="53"/>
+      <c r="AE36" s="70"/>
+      <c r="AF36" s="68"/>
+      <c r="AG36" s="69"/>
+      <c r="AH36" s="69"/>
+      <c r="AI36" s="69"/>
+      <c r="AJ36" s="69"/>
+      <c r="AK36" s="69"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="68"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="71"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="71"/>
-      <c r="N37" s="72"/>
-      <c r="O37" s="70"/>
-      <c r="P37" s="64"/>
-      <c r="Q37" s="71"/>
-      <c r="R37" s="79"/>
-      <c r="S37" s="79"/>
-      <c r="T37" s="60"/>
-      <c r="U37" s="71"/>
-      <c r="V37" s="72"/>
-      <c r="W37" s="58"/>
-      <c r="X37" s="71"/>
-      <c r="Y37" s="71"/>
-      <c r="Z37" s="72"/>
-      <c r="AA37" s="70"/>
-      <c r="AB37" s="71"/>
-      <c r="AC37" s="71"/>
-      <c r="AD37" s="55"/>
-      <c r="AE37" s="72"/>
-      <c r="AF37" s="70"/>
-      <c r="AG37" s="71"/>
-      <c r="AH37" s="71"/>
-      <c r="AI37" s="71"/>
-      <c r="AJ37" s="71"/>
-      <c r="AK37" s="71"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="72"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="68"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="69"/>
+      <c r="N37" s="70"/>
+      <c r="O37" s="68"/>
+      <c r="P37" s="62"/>
+      <c r="Q37" s="69"/>
+      <c r="R37" s="77"/>
+      <c r="S37" s="77"/>
+      <c r="T37" s="58"/>
+      <c r="U37" s="69"/>
+      <c r="V37" s="70"/>
+      <c r="W37" s="56"/>
+      <c r="X37" s="69"/>
+      <c r="Y37" s="69"/>
+      <c r="Z37" s="70"/>
+      <c r="AA37" s="68"/>
+      <c r="AB37" s="69"/>
+      <c r="AC37" s="69"/>
+      <c r="AD37" s="53"/>
+      <c r="AE37" s="70"/>
+      <c r="AF37" s="68"/>
+      <c r="AG37" s="69"/>
+      <c r="AH37" s="69"/>
+      <c r="AI37" s="69"/>
+      <c r="AJ37" s="69"/>
+      <c r="AK37" s="69"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="68"/>
-      <c r="C38" s="77" t="s">
+      <c r="B38" s="66"/>
+      <c r="C38" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="D38" s="71"/>
-      <c r="E38" s="71"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="72"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="71"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="71"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="54"/>
-      <c r="P38" s="65"/>
-      <c r="Q38" s="65"/>
-      <c r="R38" s="65"/>
-      <c r="S38" s="65"/>
-      <c r="T38" s="65"/>
-      <c r="U38" s="65"/>
-      <c r="V38" s="53"/>
-      <c r="W38" s="58"/>
-      <c r="X38" s="65"/>
-      <c r="Y38" s="65"/>
-      <c r="Z38" s="72"/>
-      <c r="AA38" s="70"/>
-      <c r="AB38" s="71"/>
-      <c r="AC38" s="71"/>
-      <c r="AD38" s="55"/>
-      <c r="AE38" s="72"/>
-      <c r="AF38" s="70"/>
-      <c r="AG38" s="71"/>
-      <c r="AH38" s="71"/>
-      <c r="AI38" s="71"/>
-      <c r="AJ38" s="71"/>
-      <c r="AK38" s="71"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="53"/>
+      <c r="M38" s="69"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="63"/>
+      <c r="Q38" s="63"/>
+      <c r="R38" s="63"/>
+      <c r="S38" s="63"/>
+      <c r="T38" s="63"/>
+      <c r="U38" s="63"/>
+      <c r="V38" s="51"/>
+      <c r="W38" s="56"/>
+      <c r="X38" s="63"/>
+      <c r="Y38" s="63"/>
+      <c r="Z38" s="70"/>
+      <c r="AA38" s="68"/>
+      <c r="AB38" s="69"/>
+      <c r="AC38" s="69"/>
+      <c r="AD38" s="53"/>
+      <c r="AE38" s="70"/>
+      <c r="AF38" s="68"/>
+      <c r="AG38" s="69"/>
+      <c r="AH38" s="69"/>
+      <c r="AI38" s="69"/>
+      <c r="AJ38" s="69"/>
+      <c r="AK38" s="69"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="68"/>
-      <c r="C39" s="77"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="71"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="72"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="71"/>
-      <c r="N39" s="72"/>
-      <c r="O39" s="70"/>
-      <c r="P39" s="71"/>
-      <c r="Q39" s="71"/>
-      <c r="R39" s="78"/>
-      <c r="S39" s="78"/>
-      <c r="T39" s="71"/>
-      <c r="U39" s="71"/>
-      <c r="V39" s="72"/>
-      <c r="W39" s="58"/>
-      <c r="X39" s="71"/>
-      <c r="Y39" s="71"/>
-      <c r="Z39" s="72"/>
-      <c r="AA39" s="70"/>
-      <c r="AB39" s="71"/>
-      <c r="AC39" s="71"/>
-      <c r="AD39" s="55"/>
-      <c r="AE39" s="72"/>
-      <c r="AF39" s="70"/>
-      <c r="AG39" s="71"/>
-      <c r="AH39" s="71"/>
-      <c r="AI39" s="71"/>
-      <c r="AJ39" s="71"/>
-      <c r="AK39" s="71"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="75"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="72"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="69"/>
+      <c r="L39" s="53"/>
+      <c r="M39" s="69"/>
+      <c r="N39" s="70"/>
+      <c r="O39" s="68"/>
+      <c r="P39" s="69"/>
+      <c r="Q39" s="69"/>
+      <c r="R39" s="76"/>
+      <c r="S39" s="76"/>
+      <c r="T39" s="69"/>
+      <c r="U39" s="69"/>
+      <c r="V39" s="70"/>
+      <c r="W39" s="56"/>
+      <c r="X39" s="69"/>
+      <c r="Y39" s="69"/>
+      <c r="Z39" s="70"/>
+      <c r="AA39" s="68"/>
+      <c r="AB39" s="69"/>
+      <c r="AC39" s="69"/>
+      <c r="AD39" s="53"/>
+      <c r="AE39" s="70"/>
+      <c r="AF39" s="68"/>
+      <c r="AG39" s="69"/>
+      <c r="AH39" s="69"/>
+      <c r="AI39" s="69"/>
+      <c r="AJ39" s="69"/>
+      <c r="AK39" s="69"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="68"/>
-      <c r="C40" s="77" t="s">
+      <c r="B40" s="66"/>
+      <c r="C40" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="71"/>
-      <c r="K40" s="71"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="71"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="70"/>
-      <c r="P40" s="71"/>
-      <c r="Q40" s="71"/>
-      <c r="R40" s="65"/>
-      <c r="S40" s="65"/>
-      <c r="T40" s="65"/>
-      <c r="U40" s="65"/>
-      <c r="V40" s="53"/>
-      <c r="W40" s="58"/>
-      <c r="X40" s="65"/>
-      <c r="Y40" s="65"/>
-      <c r="Z40" s="53"/>
-      <c r="AA40" s="54"/>
-      <c r="AB40" s="65"/>
-      <c r="AC40" s="65"/>
-      <c r="AD40" s="55"/>
-      <c r="AE40" s="72"/>
-      <c r="AF40" s="70"/>
-      <c r="AG40" s="71"/>
-      <c r="AH40" s="71"/>
-      <c r="AI40" s="71"/>
-      <c r="AJ40" s="71"/>
-      <c r="AK40" s="71"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="69"/>
+      <c r="L40" s="53"/>
+      <c r="M40" s="69"/>
+      <c r="N40" s="70"/>
+      <c r="O40" s="68"/>
+      <c r="P40" s="69"/>
+      <c r="Q40" s="69"/>
+      <c r="R40" s="63"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="63"/>
+      <c r="U40" s="63"/>
+      <c r="V40" s="51"/>
+      <c r="W40" s="56"/>
+      <c r="X40" s="63"/>
+      <c r="Y40" s="63"/>
+      <c r="Z40" s="51"/>
+      <c r="AA40" s="52"/>
+      <c r="AB40" s="63"/>
+      <c r="AC40" s="63"/>
+      <c r="AD40" s="53"/>
+      <c r="AE40" s="70"/>
+      <c r="AF40" s="68"/>
+      <c r="AG40" s="69"/>
+      <c r="AH40" s="69"/>
+      <c r="AI40" s="69"/>
+      <c r="AJ40" s="69"/>
+      <c r="AK40" s="69"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="68"/>
-      <c r="C41" s="77"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="72"/>
-      <c r="H41" s="70"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="71"/>
-      <c r="K41" s="71"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="72"/>
-      <c r="O41" s="70"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="64"/>
-      <c r="R41" s="78"/>
-      <c r="S41" s="78"/>
-      <c r="T41" s="64"/>
-      <c r="U41" s="71"/>
-      <c r="V41" s="72"/>
-      <c r="W41" s="58"/>
-      <c r="X41" s="71"/>
-      <c r="Y41" s="71"/>
-      <c r="Z41" s="72"/>
-      <c r="AA41" s="70"/>
-      <c r="AB41" s="71"/>
-      <c r="AC41" s="71"/>
-      <c r="AD41" s="55"/>
-      <c r="AE41" s="72"/>
-      <c r="AF41" s="70"/>
-      <c r="AG41" s="71"/>
-      <c r="AH41" s="71"/>
-      <c r="AI41" s="71"/>
-      <c r="AJ41" s="71"/>
-      <c r="AK41" s="71"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="75"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="69"/>
+      <c r="N41" s="70"/>
+      <c r="O41" s="68"/>
+      <c r="P41" s="69"/>
+      <c r="Q41" s="62"/>
+      <c r="R41" s="76"/>
+      <c r="S41" s="76"/>
+      <c r="T41" s="62"/>
+      <c r="U41" s="69"/>
+      <c r="V41" s="70"/>
+      <c r="W41" s="56"/>
+      <c r="X41" s="69"/>
+      <c r="Y41" s="69"/>
+      <c r="Z41" s="70"/>
+      <c r="AA41" s="68"/>
+      <c r="AB41" s="69"/>
+      <c r="AC41" s="69"/>
+      <c r="AD41" s="53"/>
+      <c r="AE41" s="70"/>
+      <c r="AF41" s="68"/>
+      <c r="AG41" s="69"/>
+      <c r="AH41" s="69"/>
+      <c r="AI41" s="69"/>
+      <c r="AJ41" s="69"/>
+      <c r="AK41" s="69"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="49" t="s">
+      <c r="B42" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="80" t="s">
+      <c r="C42" s="78" t="s">
         <v>166</v>
       </c>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="55"/>
-      <c r="M42" s="51"/>
-      <c r="N42" s="56"/>
-      <c r="O42" s="57"/>
-      <c r="P42" s="65"/>
-      <c r="Q42" s="65"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="51"/>
-      <c r="T42" s="64"/>
-      <c r="U42" s="51"/>
-      <c r="V42" s="53"/>
-      <c r="W42" s="58"/>
-      <c r="X42" s="65"/>
-      <c r="Y42" s="65"/>
-      <c r="Z42" s="53"/>
-      <c r="AA42" s="54"/>
-      <c r="AB42" s="65"/>
-      <c r="AC42" s="65"/>
-      <c r="AD42" s="55"/>
-      <c r="AE42" s="56"/>
-      <c r="AF42" s="57"/>
-      <c r="AG42" s="51"/>
-      <c r="AH42" s="51"/>
-      <c r="AI42" s="51"/>
-      <c r="AJ42" s="51"/>
-      <c r="AK42" s="51"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="53"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="54"/>
+      <c r="O42" s="55"/>
+      <c r="P42" s="63"/>
+      <c r="Q42" s="63"/>
+      <c r="R42" s="49"/>
+      <c r="S42" s="49"/>
+      <c r="T42" s="62"/>
+      <c r="U42" s="49"/>
+      <c r="V42" s="51"/>
+      <c r="W42" s="56"/>
+      <c r="X42" s="63"/>
+      <c r="Y42" s="63"/>
+      <c r="Z42" s="51"/>
+      <c r="AA42" s="52"/>
+      <c r="AB42" s="63"/>
+      <c r="AC42" s="63"/>
+      <c r="AD42" s="53"/>
+      <c r="AE42" s="54"/>
+      <c r="AF42" s="55"/>
+      <c r="AG42" s="49"/>
+      <c r="AH42" s="49"/>
+      <c r="AI42" s="49"/>
+      <c r="AJ42" s="49"/>
+      <c r="AK42" s="49"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="49"/>
-      <c r="C43" s="80"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="57"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="51"/>
-      <c r="K43" s="51"/>
-      <c r="L43" s="55"/>
-      <c r="M43" s="51"/>
-      <c r="N43" s="56"/>
-      <c r="O43" s="57"/>
-      <c r="P43" s="51"/>
-      <c r="Q43" s="64"/>
-      <c r="R43" s="51"/>
-      <c r="S43" s="66"/>
-      <c r="T43" s="51"/>
-      <c r="U43" s="51"/>
-      <c r="V43" s="56"/>
-      <c r="W43" s="58"/>
-      <c r="X43" s="51"/>
-      <c r="Y43" s="51"/>
-      <c r="Z43" s="56"/>
-      <c r="AA43" s="57"/>
-      <c r="AB43" s="51"/>
-      <c r="AC43" s="51"/>
-      <c r="AD43" s="55"/>
-      <c r="AE43" s="56"/>
-      <c r="AF43" s="57"/>
-      <c r="AG43" s="51"/>
-      <c r="AH43" s="51"/>
-      <c r="AI43" s="51"/>
-      <c r="AJ43" s="51"/>
-      <c r="AK43" s="51"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="78"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="49"/>
+      <c r="L43" s="53"/>
+      <c r="M43" s="49"/>
+      <c r="N43" s="54"/>
+      <c r="O43" s="55"/>
+      <c r="P43" s="49"/>
+      <c r="Q43" s="62"/>
+      <c r="R43" s="49"/>
+      <c r="S43" s="64"/>
+      <c r="T43" s="49"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="54"/>
+      <c r="W43" s="56"/>
+      <c r="X43" s="49"/>
+      <c r="Y43" s="49"/>
+      <c r="Z43" s="54"/>
+      <c r="AA43" s="55"/>
+      <c r="AB43" s="49"/>
+      <c r="AC43" s="49"/>
+      <c r="AD43" s="53"/>
+      <c r="AE43" s="54"/>
+      <c r="AF43" s="55"/>
+      <c r="AG43" s="49"/>
+      <c r="AH43" s="58"/>
+      <c r="AI43" s="58"/>
+      <c r="AJ43" s="49"/>
+      <c r="AK43" s="49"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="49"/>
-      <c r="C44" s="80" t="s">
+      <c r="B44" s="47"/>
+      <c r="C44" s="78" t="s">
         <v>167</v>
       </c>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="51"/>
-      <c r="J44" s="51"/>
-      <c r="K44" s="51"/>
-      <c r="L44" s="55"/>
-      <c r="M44" s="51"/>
-      <c r="N44" s="56"/>
-      <c r="O44" s="57"/>
-      <c r="P44" s="65"/>
-      <c r="Q44" s="65"/>
-      <c r="R44" s="51"/>
-      <c r="S44" s="51"/>
-      <c r="T44" s="51"/>
-      <c r="U44" s="51"/>
-      <c r="V44" s="56"/>
-      <c r="W44" s="58"/>
-      <c r="X44" s="65"/>
-      <c r="Y44" s="65"/>
-      <c r="Z44" s="56"/>
-      <c r="AA44" s="57"/>
-      <c r="AB44" s="51"/>
-      <c r="AC44" s="65"/>
-      <c r="AD44" s="55"/>
-      <c r="AE44" s="53"/>
-      <c r="AF44" s="54"/>
-      <c r="AG44" s="51"/>
-      <c r="AH44" s="51"/>
-      <c r="AI44" s="65"/>
-      <c r="AJ44" s="51"/>
-      <c r="AK44" s="51"/>
+      <c r="D44" s="49"/>
+      <c r="E44" s="49"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="54"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="49"/>
+      <c r="L44" s="53"/>
+      <c r="M44" s="49"/>
+      <c r="N44" s="54"/>
+      <c r="O44" s="55"/>
+      <c r="P44" s="63"/>
+      <c r="Q44" s="63"/>
+      <c r="R44" s="49"/>
+      <c r="S44" s="49"/>
+      <c r="T44" s="49"/>
+      <c r="U44" s="49"/>
+      <c r="V44" s="54"/>
+      <c r="W44" s="56"/>
+      <c r="X44" s="63"/>
+      <c r="Y44" s="63"/>
+      <c r="Z44" s="54"/>
+      <c r="AA44" s="55"/>
+      <c r="AB44" s="49"/>
+      <c r="AC44" s="63"/>
+      <c r="AD44" s="53"/>
+      <c r="AE44" s="51"/>
+      <c r="AF44" s="52"/>
+      <c r="AG44" s="49"/>
+      <c r="AH44" s="49"/>
+      <c r="AI44" s="63"/>
+      <c r="AJ44" s="49"/>
+      <c r="AK44" s="49"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="49"/>
-      <c r="C45" s="80"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="51"/>
-      <c r="J45" s="51"/>
-      <c r="K45" s="51"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="51"/>
-      <c r="N45" s="56"/>
-      <c r="O45" s="57"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="51"/>
-      <c r="R45" s="51"/>
-      <c r="S45" s="51"/>
-      <c r="T45" s="51"/>
-      <c r="U45" s="51"/>
-      <c r="V45" s="56"/>
-      <c r="W45" s="58"/>
-      <c r="X45" s="51"/>
-      <c r="Y45" s="64"/>
-      <c r="Z45" s="81"/>
-      <c r="AA45" s="57"/>
-      <c r="AB45" s="51"/>
-      <c r="AC45" s="51"/>
-      <c r="AD45" s="55"/>
-      <c r="AE45" s="56"/>
-      <c r="AF45" s="57"/>
-      <c r="AG45" s="51"/>
-      <c r="AH45" s="51"/>
-      <c r="AI45" s="51"/>
-      <c r="AJ45" s="51"/>
-      <c r="AK45" s="51"/>
+      <c r="B45" s="47"/>
+      <c r="C45" s="78"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="49"/>
+      <c r="J45" s="49"/>
+      <c r="K45" s="49"/>
+      <c r="L45" s="53"/>
+      <c r="M45" s="49"/>
+      <c r="N45" s="54"/>
+      <c r="O45" s="55"/>
+      <c r="P45" s="49"/>
+      <c r="Q45" s="49"/>
+      <c r="R45" s="49"/>
+      <c r="S45" s="49"/>
+      <c r="T45" s="49"/>
+      <c r="U45" s="49"/>
+      <c r="V45" s="54"/>
+      <c r="W45" s="56"/>
+      <c r="X45" s="49"/>
+      <c r="Y45" s="62"/>
+      <c r="Z45" s="79"/>
+      <c r="AA45" s="55"/>
+      <c r="AB45" s="49"/>
+      <c r="AC45" s="49"/>
+      <c r="AD45" s="53"/>
+      <c r="AE45" s="54"/>
+      <c r="AF45" s="55"/>
+      <c r="AG45" s="49"/>
+      <c r="AH45" s="62"/>
+      <c r="AI45" s="62"/>
+      <c r="AJ45" s="49"/>
+      <c r="AK45" s="49"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="68" t="s">
+      <c r="B46" s="66" t="s">
         <v>168</v>
       </c>
-      <c r="C46" s="69" t="s">
+      <c r="C46" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="71"/>
-      <c r="E46" s="71"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="72"/>
-      <c r="H46" s="70"/>
-      <c r="I46" s="71"/>
-      <c r="J46" s="71"/>
-      <c r="K46" s="71"/>
-      <c r="L46" s="55"/>
-      <c r="M46" s="71"/>
-      <c r="N46" s="72"/>
-      <c r="O46" s="70"/>
-      <c r="P46" s="71"/>
-      <c r="Q46" s="71"/>
-      <c r="R46" s="71"/>
-      <c r="S46" s="71"/>
-      <c r="T46" s="71"/>
-      <c r="U46" s="71"/>
-      <c r="V46" s="72"/>
-      <c r="W46" s="58"/>
-      <c r="X46" s="71"/>
-      <c r="Y46" s="71"/>
-      <c r="Z46" s="72"/>
-      <c r="AA46" s="70"/>
-      <c r="AB46" s="71"/>
-      <c r="AC46" s="71"/>
-      <c r="AD46" s="55"/>
-      <c r="AE46" s="72"/>
-      <c r="AF46" s="70"/>
-      <c r="AG46" s="71"/>
-      <c r="AH46" s="71"/>
-      <c r="AI46" s="71"/>
-      <c r="AJ46" s="65"/>
-      <c r="AK46" s="71"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="72"/>
+      <c r="G46" s="70"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
+      <c r="L46" s="53"/>
+      <c r="M46" s="69"/>
+      <c r="N46" s="70"/>
+      <c r="O46" s="68"/>
+      <c r="P46" s="69"/>
+      <c r="Q46" s="69"/>
+      <c r="R46" s="69"/>
+      <c r="S46" s="69"/>
+      <c r="T46" s="69"/>
+      <c r="U46" s="69"/>
+      <c r="V46" s="70"/>
+      <c r="W46" s="56"/>
+      <c r="X46" s="69"/>
+      <c r="Y46" s="69"/>
+      <c r="Z46" s="70"/>
+      <c r="AA46" s="68"/>
+      <c r="AB46" s="69"/>
+      <c r="AC46" s="69"/>
+      <c r="AD46" s="53"/>
+      <c r="AE46" s="70"/>
+      <c r="AF46" s="68"/>
+      <c r="AG46" s="69"/>
+      <c r="AH46" s="69"/>
+      <c r="AI46" s="69"/>
+      <c r="AJ46" s="63"/>
+      <c r="AK46" s="69"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="68"/>
-      <c r="C47" s="69"/>
-      <c r="D47" s="71"/>
-      <c r="E47" s="71"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="72"/>
-      <c r="H47" s="70"/>
-      <c r="I47" s="71"/>
-      <c r="J47" s="71"/>
-      <c r="K47" s="71"/>
-      <c r="L47" s="55"/>
-      <c r="M47" s="71"/>
-      <c r="N47" s="72"/>
-      <c r="O47" s="70"/>
-      <c r="P47" s="71"/>
-      <c r="Q47" s="71"/>
-      <c r="R47" s="71"/>
-      <c r="S47" s="71"/>
-      <c r="T47" s="71"/>
-      <c r="U47" s="71"/>
-      <c r="V47" s="72"/>
-      <c r="W47" s="58"/>
-      <c r="X47" s="71"/>
-      <c r="Y47" s="71"/>
-      <c r="Z47" s="72"/>
-      <c r="AA47" s="70"/>
-      <c r="AB47" s="71"/>
-      <c r="AC47" s="71"/>
-      <c r="AD47" s="55"/>
-      <c r="AE47" s="72"/>
-      <c r="AF47" s="70"/>
-      <c r="AG47" s="71"/>
-      <c r="AH47" s="71"/>
-      <c r="AI47" s="71"/>
-      <c r="AJ47" s="71"/>
-      <c r="AK47" s="71"/>
-      <c r="AN47" s="82" t="s">
+      <c r="B47" s="66"/>
+      <c r="C47" s="67"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="72"/>
+      <c r="G47" s="70"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="53"/>
+      <c r="M47" s="69"/>
+      <c r="N47" s="70"/>
+      <c r="O47" s="68"/>
+      <c r="P47" s="69"/>
+      <c r="Q47" s="69"/>
+      <c r="R47" s="69"/>
+      <c r="S47" s="69"/>
+      <c r="T47" s="69"/>
+      <c r="U47" s="69"/>
+      <c r="V47" s="70"/>
+      <c r="W47" s="56"/>
+      <c r="X47" s="69"/>
+      <c r="Y47" s="69"/>
+      <c r="Z47" s="70"/>
+      <c r="AA47" s="68"/>
+      <c r="AB47" s="69"/>
+      <c r="AC47" s="69"/>
+      <c r="AD47" s="53"/>
+      <c r="AE47" s="70"/>
+      <c r="AF47" s="68"/>
+      <c r="AG47" s="69"/>
+      <c r="AH47" s="69"/>
+      <c r="AI47" s="69"/>
+      <c r="AJ47" s="69"/>
+      <c r="AK47" s="69"/>
+      <c r="AN47" s="80" t="s">
         <v>169</v>
       </c>
-      <c r="AO47" s="65"/>
+      <c r="AO47" s="63"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="68"/>
-      <c r="C48" s="69" t="s">
+      <c r="B48" s="66"/>
+      <c r="C48" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="D48" s="71"/>
-      <c r="E48" s="71"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="72"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="71"/>
-      <c r="J48" s="71"/>
-      <c r="K48" s="71"/>
-      <c r="L48" s="55"/>
-      <c r="M48" s="71"/>
-      <c r="N48" s="72"/>
-      <c r="O48" s="70"/>
-      <c r="P48" s="71"/>
-      <c r="Q48" s="71"/>
-      <c r="R48" s="71"/>
-      <c r="S48" s="71"/>
-      <c r="T48" s="71"/>
-      <c r="U48" s="71"/>
-      <c r="V48" s="72"/>
-      <c r="W48" s="58"/>
-      <c r="X48" s="71"/>
-      <c r="Y48" s="71"/>
-      <c r="Z48" s="72"/>
-      <c r="AA48" s="70"/>
-      <c r="AB48" s="71"/>
-      <c r="AC48" s="71"/>
-      <c r="AD48" s="55"/>
-      <c r="AE48" s="72"/>
-      <c r="AF48" s="70"/>
-      <c r="AG48" s="71"/>
-      <c r="AH48" s="71"/>
-      <c r="AI48" s="71"/>
-      <c r="AJ48" s="71"/>
-      <c r="AK48" s="83"/>
-      <c r="AN48" s="82" t="s">
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="72"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="68"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
+      <c r="L48" s="53"/>
+      <c r="M48" s="69"/>
+      <c r="N48" s="70"/>
+      <c r="O48" s="68"/>
+      <c r="P48" s="69"/>
+      <c r="Q48" s="69"/>
+      <c r="R48" s="69"/>
+      <c r="S48" s="69"/>
+      <c r="T48" s="69"/>
+      <c r="U48" s="69"/>
+      <c r="V48" s="70"/>
+      <c r="W48" s="56"/>
+      <c r="X48" s="69"/>
+      <c r="Y48" s="69"/>
+      <c r="Z48" s="70"/>
+      <c r="AA48" s="68"/>
+      <c r="AB48" s="69"/>
+      <c r="AC48" s="69"/>
+      <c r="AD48" s="53"/>
+      <c r="AE48" s="70"/>
+      <c r="AF48" s="68"/>
+      <c r="AG48" s="69"/>
+      <c r="AH48" s="69"/>
+      <c r="AI48" s="69"/>
+      <c r="AJ48" s="69"/>
+      <c r="AK48" s="81"/>
+      <c r="AN48" s="80" t="s">
         <v>171</v>
       </c>
-      <c r="AO48" s="64"/>
+      <c r="AO48" s="62"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="68"/>
-      <c r="C49" s="69"/>
-      <c r="D49" s="71"/>
-      <c r="E49" s="71"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="72"/>
-      <c r="H49" s="70"/>
-      <c r="I49" s="71"/>
-      <c r="J49" s="71"/>
-      <c r="K49" s="71"/>
-      <c r="L49" s="55"/>
-      <c r="M49" s="71"/>
-      <c r="N49" s="72"/>
-      <c r="O49" s="70"/>
-      <c r="P49" s="71"/>
-      <c r="Q49" s="71"/>
-      <c r="R49" s="71"/>
-      <c r="S49" s="71"/>
-      <c r="T49" s="71"/>
-      <c r="U49" s="71"/>
-      <c r="V49" s="72"/>
-      <c r="W49" s="58"/>
-      <c r="X49" s="71"/>
-      <c r="Y49" s="71"/>
-      <c r="Z49" s="72"/>
-      <c r="AA49" s="70"/>
-      <c r="AB49" s="71"/>
-      <c r="AC49" s="71"/>
-      <c r="AD49" s="55"/>
-      <c r="AE49" s="72"/>
-      <c r="AF49" s="70"/>
-      <c r="AG49" s="71"/>
-      <c r="AH49" s="71"/>
-      <c r="AI49" s="71"/>
-      <c r="AJ49" s="71"/>
-      <c r="AK49" s="71"/>
-      <c r="AN49" s="82" t="s">
+      <c r="B49" s="66"/>
+      <c r="C49" s="67"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="72"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="68"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="53"/>
+      <c r="M49" s="69"/>
+      <c r="N49" s="70"/>
+      <c r="O49" s="68"/>
+      <c r="P49" s="69"/>
+      <c r="Q49" s="69"/>
+      <c r="R49" s="69"/>
+      <c r="S49" s="69"/>
+      <c r="T49" s="69"/>
+      <c r="U49" s="69"/>
+      <c r="V49" s="70"/>
+      <c r="W49" s="56"/>
+      <c r="X49" s="69"/>
+      <c r="Y49" s="69"/>
+      <c r="Z49" s="70"/>
+      <c r="AA49" s="68"/>
+      <c r="AB49" s="69"/>
+      <c r="AC49" s="69"/>
+      <c r="AD49" s="53"/>
+      <c r="AE49" s="70"/>
+      <c r="AF49" s="68"/>
+      <c r="AG49" s="69"/>
+      <c r="AH49" s="69"/>
+      <c r="AI49" s="69"/>
+      <c r="AJ49" s="69"/>
+      <c r="AK49" s="69"/>
+      <c r="AN49" s="80" t="s">
         <v>172</v>
       </c>
-      <c r="AO49" s="60"/>
+      <c r="AO49" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -11101,94 +11095,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="84"/>
+      <c r="B1" s="82"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="83" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="84" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="87" t="s">
+      <c r="D2" s="85" t="s">
         <v>173</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="86" t="s">
         <v>174</v>
       </c>
-      <c r="F2" s="89" t="s">
+      <c r="F2" s="87" t="s">
         <v>175</v>
       </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="88"/>
-      <c r="J2" s="89" t="s">
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="87" t="s">
         <v>176</v>
       </c>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="89" t="s">
+      <c r="K2" s="87"/>
+      <c r="L2" s="87"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="88"/>
-      <c r="R2" s="89" t="s">
+      <c r="O2" s="87"/>
+      <c r="P2" s="87"/>
+      <c r="Q2" s="86"/>
+      <c r="R2" s="87" t="s">
         <v>112</v>
       </c>
-      <c r="S2" s="90"/>
-      <c r="AD2" s="91"/>
+      <c r="S2" s="88"/>
+      <c r="AD2" s="89"/>
     </row>
     <row r="3">
-      <c r="B3" s="92"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="94" t="s">
+      <c r="B3" s="90"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="92" t="s">
         <v>177</v>
       </c>
-      <c r="E3" s="95">
+      <c r="E3" s="93">
         <v>4</v>
       </c>
-      <c r="F3" s="96">
+      <c r="F3" s="94">
         <v>1</v>
       </c>
-      <c r="G3" s="97">
+      <c r="G3" s="95">
         <v>2</v>
       </c>
-      <c r="H3" s="97">
+      <c r="H3" s="95">
         <v>3</v>
       </c>
-      <c r="I3" s="95">
+      <c r="I3" s="93">
         <v>4</v>
       </c>
-      <c r="J3" s="96">
+      <c r="J3" s="94">
         <v>1</v>
       </c>
-      <c r="K3" s="97">
+      <c r="K3" s="95">
         <v>2</v>
       </c>
-      <c r="L3" s="97">
+      <c r="L3" s="95">
         <v>3</v>
       </c>
-      <c r="M3" s="95">
+      <c r="M3" s="93">
         <v>4</v>
       </c>
-      <c r="N3" s="96">
+      <c r="N3" s="94">
         <v>1</v>
       </c>
-      <c r="O3" s="97">
+      <c r="O3" s="95">
         <v>2</v>
       </c>
-      <c r="P3" s="97">
+      <c r="P3" s="95">
         <v>3</v>
       </c>
-      <c r="Q3" s="95">
+      <c r="Q3" s="93">
         <v>4</v>
       </c>
-      <c r="R3" s="96">
+      <c r="R3" s="94">
         <v>1</v>
       </c>
-      <c r="S3" s="98">
+      <c r="S3" s="96">
         <v>2</v>
       </c>
       <c r="U3" t="s">
@@ -11196,705 +11190,705 @@
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="97" t="s">
         <v>179</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="84" t="s">
         <v>180</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="103"/>
-      <c r="L4" s="103"/>
-      <c r="M4" s="101"/>
-      <c r="N4" s="104"/>
-      <c r="O4" s="103"/>
-      <c r="P4" s="103"/>
-      <c r="Q4" s="101"/>
-      <c r="R4" s="104"/>
-      <c r="S4" s="105"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="103"/>
       <c r="U4" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="99"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="107"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="112"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="108"/>
-      <c r="N5" s="112"/>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="108"/>
-      <c r="R5" s="112"/>
-      <c r="S5" s="113"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="109"/>
+      <c r="L5" s="109"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="106"/>
+      <c r="R5" s="110"/>
+      <c r="S5" s="111"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="99"/>
-      <c r="C6" s="114" t="s">
+      <c r="B6" s="97"/>
+      <c r="C6" s="112" t="s">
         <v>182</v>
       </c>
-      <c r="D6" s="115"/>
-      <c r="E6" s="116"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="118"/>
-      <c r="H6" s="119"/>
-      <c r="I6" s="116"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="119"/>
-      <c r="L6" s="119"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="120"/>
-      <c r="O6" s="119"/>
-      <c r="P6" s="119"/>
-      <c r="Q6" s="116"/>
-      <c r="R6" s="120"/>
-      <c r="S6" s="121"/>
-      <c r="U6" s="122" t="s">
+      <c r="D6" s="113"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="116"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="118"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="114"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="117"/>
+      <c r="P6" s="117"/>
+      <c r="Q6" s="114"/>
+      <c r="R6" s="118"/>
+      <c r="S6" s="119"/>
+      <c r="U6" s="120" t="s">
         <v>183</v>
       </c>
-      <c r="V6" s="122"/>
+      <c r="V6" s="120"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="99"/>
-      <c r="C7" s="106"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="111"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="108"/>
-      <c r="N7" s="112"/>
-      <c r="O7" s="111"/>
-      <c r="P7" s="111"/>
-      <c r="Q7" s="108"/>
-      <c r="R7" s="112"/>
-      <c r="S7" s="113"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="108"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="109"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="109"/>
+      <c r="Q7" s="106"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="111"/>
       <c r="U7" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="99"/>
-      <c r="C8" s="114" t="s">
+      <c r="B8" s="97"/>
+      <c r="C8" s="112" t="s">
         <v>185</v>
       </c>
-      <c r="D8" s="115"/>
-      <c r="E8" s="116"/>
-      <c r="F8" s="117"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="116"/>
-      <c r="J8" s="120"/>
-      <c r="K8" s="119"/>
-      <c r="L8" s="119"/>
-      <c r="M8" s="116"/>
-      <c r="N8" s="120"/>
-      <c r="O8" s="119"/>
-      <c r="P8" s="119"/>
-      <c r="Q8" s="116"/>
-      <c r="R8" s="120"/>
-      <c r="S8" s="121"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="114"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="114"/>
+      <c r="J8" s="118"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="117"/>
+      <c r="M8" s="114"/>
+      <c r="N8" s="118"/>
+      <c r="O8" s="117"/>
+      <c r="P8" s="117"/>
+      <c r="Q8" s="114"/>
+      <c r="R8" s="118"/>
+      <c r="S8" s="119"/>
       <c r="U8" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="99"/>
-      <c r="C9" s="106"/>
-      <c r="D9" s="107"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="108"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="111"/>
-      <c r="L9" s="111"/>
-      <c r="M9" s="108"/>
-      <c r="N9" s="112"/>
-      <c r="O9" s="111"/>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="108"/>
-      <c r="R9" s="112"/>
-      <c r="S9" s="113"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="110"/>
+      <c r="K9" s="109"/>
+      <c r="L9" s="109"/>
+      <c r="M9" s="106"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="109"/>
+      <c r="P9" s="109"/>
+      <c r="Q9" s="106"/>
+      <c r="R9" s="110"/>
+      <c r="S9" s="111"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="99"/>
-      <c r="C10" s="114" t="s">
+      <c r="B10" s="97"/>
+      <c r="C10" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="115"/>
-      <c r="E10" s="116"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="118"/>
-      <c r="H10" s="118"/>
-      <c r="I10" s="116"/>
-      <c r="J10" s="120"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="116"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="119"/>
-      <c r="P10" s="119"/>
-      <c r="Q10" s="116"/>
-      <c r="R10" s="120"/>
-      <c r="S10" s="121"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="114"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="116"/>
+      <c r="H10" s="116"/>
+      <c r="I10" s="114"/>
+      <c r="J10" s="118"/>
+      <c r="K10" s="117"/>
+      <c r="L10" s="117"/>
+      <c r="M10" s="114"/>
+      <c r="N10" s="118"/>
+      <c r="O10" s="117"/>
+      <c r="P10" s="117"/>
+      <c r="Q10" s="114"/>
+      <c r="R10" s="118"/>
+      <c r="S10" s="119"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="123"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="126"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="126"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="129"/>
-      <c r="M11" s="126"/>
-      <c r="N11" s="127"/>
-      <c r="O11" s="129"/>
-      <c r="P11" s="129"/>
-      <c r="Q11" s="126"/>
-      <c r="R11" s="127"/>
-      <c r="S11" s="130"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="125"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="124"/>
+      <c r="N11" s="125"/>
+      <c r="O11" s="127"/>
+      <c r="P11" s="127"/>
+      <c r="Q11" s="124"/>
+      <c r="R11" s="125"/>
+      <c r="S11" s="128"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="83" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="86" t="s">
+      <c r="C12" s="84" t="s">
         <v>189</v>
       </c>
-      <c r="D12" s="100"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="132"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="103"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="101"/>
-      <c r="N12" s="104"/>
-      <c r="O12" s="103"/>
-      <c r="P12" s="103"/>
-      <c r="Q12" s="101"/>
-      <c r="R12" s="104"/>
-      <c r="S12" s="105"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="129"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="102"/>
+      <c r="K12" s="101"/>
+      <c r="L12" s="101"/>
+      <c r="M12" s="99"/>
+      <c r="N12" s="102"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="101"/>
+      <c r="Q12" s="99"/>
+      <c r="R12" s="102"/>
+      <c r="S12" s="103"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="99"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="112"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="108"/>
-      <c r="N13" s="112"/>
-      <c r="O13" s="111"/>
-      <c r="P13" s="111"/>
-      <c r="Q13" s="108"/>
-      <c r="R13" s="112"/>
-      <c r="S13" s="113"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="104"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="106"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="109"/>
+      <c r="L13" s="109"/>
+      <c r="M13" s="106"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="109"/>
+      <c r="P13" s="109"/>
+      <c r="Q13" s="106"/>
+      <c r="R13" s="110"/>
+      <c r="S13" s="111"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="99"/>
-      <c r="C14" s="114" t="s">
+      <c r="B14" s="97"/>
+      <c r="C14" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="D14" s="133"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="116"/>
-      <c r="J14" s="120"/>
-      <c r="K14" s="119"/>
-      <c r="L14" s="119"/>
-      <c r="M14" s="116"/>
-      <c r="N14" s="120"/>
-      <c r="O14" s="119"/>
-      <c r="P14" s="119"/>
-      <c r="Q14" s="116"/>
-      <c r="R14" s="120"/>
-      <c r="S14" s="121"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="118"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="118"/>
+      <c r="O14" s="117"/>
+      <c r="P14" s="117"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="118"/>
+      <c r="S14" s="119"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="99"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="112"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="134"/>
-      <c r="J15" s="109"/>
-      <c r="K15" s="111"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="108"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="111"/>
-      <c r="P15" s="111"/>
-      <c r="Q15" s="108"/>
-      <c r="R15" s="112"/>
-      <c r="S15" s="113"/>
+      <c r="B15" s="97"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="106"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="109"/>
+      <c r="L15" s="109"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="110"/>
+      <c r="O15" s="109"/>
+      <c r="P15" s="109"/>
+      <c r="Q15" s="106"/>
+      <c r="R15" s="110"/>
+      <c r="S15" s="111"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="99"/>
-      <c r="C16" s="114" t="s">
+      <c r="B16" s="97"/>
+      <c r="C16" s="112" t="s">
         <v>191</v>
       </c>
-      <c r="D16" s="115"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="119"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="120"/>
-      <c r="K16" s="119"/>
-      <c r="L16" s="119"/>
-      <c r="M16" s="116"/>
-      <c r="N16" s="120"/>
-      <c r="O16" s="119"/>
-      <c r="P16" s="119"/>
-      <c r="Q16" s="116"/>
-      <c r="R16" s="120"/>
-      <c r="S16" s="121"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="116"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="118"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="114"/>
+      <c r="N16" s="118"/>
+      <c r="O16" s="117"/>
+      <c r="P16" s="117"/>
+      <c r="Q16" s="114"/>
+      <c r="R16" s="118"/>
+      <c r="S16" s="119"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="123"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="129"/>
-      <c r="H17" s="129"/>
-      <c r="I17" s="126"/>
-      <c r="J17" s="136"/>
-      <c r="K17" s="128"/>
-      <c r="L17" s="129"/>
-      <c r="M17" s="126"/>
-      <c r="N17" s="127"/>
-      <c r="O17" s="129"/>
-      <c r="P17" s="129"/>
-      <c r="Q17" s="126"/>
-      <c r="R17" s="127"/>
-      <c r="S17" s="130"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="123"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="127"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="124"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="126"/>
+      <c r="L17" s="127"/>
+      <c r="M17" s="124"/>
+      <c r="N17" s="125"/>
+      <c r="O17" s="127"/>
+      <c r="P17" s="127"/>
+      <c r="Q17" s="124"/>
+      <c r="R17" s="125"/>
+      <c r="S17" s="128"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="85" t="s">
         <v>192</v>
       </c>
-      <c r="C18" s="86" t="s">
+      <c r="C18" s="84" t="s">
         <v>193</v>
       </c>
-      <c r="D18" s="100"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="132"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="103"/>
-      <c r="L18" s="103"/>
-      <c r="M18" s="101"/>
-      <c r="N18" s="104"/>
-      <c r="O18" s="103"/>
-      <c r="P18" s="103"/>
-      <c r="Q18" s="101"/>
-      <c r="R18" s="104"/>
-      <c r="S18" s="105"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="102"/>
+      <c r="G18" s="101"/>
+      <c r="H18" s="101"/>
+      <c r="I18" s="130"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="101"/>
+      <c r="L18" s="101"/>
+      <c r="M18" s="99"/>
+      <c r="N18" s="102"/>
+      <c r="O18" s="101"/>
+      <c r="P18" s="101"/>
+      <c r="Q18" s="99"/>
+      <c r="R18" s="102"/>
+      <c r="S18" s="103"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="99"/>
-      <c r="C19" s="106"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="112"/>
-      <c r="G19" s="110"/>
-      <c r="H19" s="111"/>
-      <c r="I19" s="108"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="111"/>
-      <c r="L19" s="111"/>
-      <c r="M19" s="108"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="111"/>
-      <c r="P19" s="111"/>
-      <c r="Q19" s="108"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="113"/>
+      <c r="B19" s="97"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="108"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="106"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="109"/>
+      <c r="M19" s="106"/>
+      <c r="N19" s="110"/>
+      <c r="O19" s="109"/>
+      <c r="P19" s="109"/>
+      <c r="Q19" s="106"/>
+      <c r="R19" s="110"/>
+      <c r="S19" s="111"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="99"/>
-      <c r="C20" s="114" t="s">
+      <c r="B20" s="97"/>
+      <c r="C20" s="112" t="s">
         <v>194</v>
       </c>
-      <c r="D20" s="115"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="119"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="135"/>
-      <c r="J20" s="117"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="116"/>
-      <c r="N20" s="120"/>
-      <c r="O20" s="119"/>
-      <c r="P20" s="119"/>
-      <c r="Q20" s="116"/>
-      <c r="R20" s="120"/>
-      <c r="S20" s="121"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="133"/>
+      <c r="J20" s="115"/>
+      <c r="K20" s="116"/>
+      <c r="L20" s="116"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="118"/>
+      <c r="O20" s="117"/>
+      <c r="P20" s="117"/>
+      <c r="Q20" s="114"/>
+      <c r="R20" s="118"/>
+      <c r="S20" s="119"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="99"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="112"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="111"/>
-      <c r="I21" s="108"/>
-      <c r="J21" s="112"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="108"/>
-      <c r="N21" s="137"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="111"/>
-      <c r="Q21" s="108"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="113"/>
+      <c r="B21" s="97"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="110"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="109"/>
+      <c r="L21" s="109"/>
+      <c r="M21" s="106"/>
+      <c r="N21" s="135"/>
+      <c r="O21" s="109"/>
+      <c r="P21" s="109"/>
+      <c r="Q21" s="106"/>
+      <c r="R21" s="110"/>
+      <c r="S21" s="111"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="99"/>
-      <c r="C22" s="114" t="s">
+      <c r="B22" s="97"/>
+      <c r="C22" s="112" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="115"/>
-      <c r="E22" s="116"/>
-      <c r="F22" s="120"/>
-      <c r="G22" s="119"/>
-      <c r="H22" s="119"/>
-      <c r="I22" s="116"/>
-      <c r="J22" s="120"/>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="116"/>
-      <c r="N22" s="120"/>
-      <c r="O22" s="119"/>
-      <c r="P22" s="119"/>
-      <c r="Q22" s="116"/>
-      <c r="R22" s="120"/>
-      <c r="S22" s="121"/>
+      <c r="D22" s="113"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="116"/>
+      <c r="L22" s="116"/>
+      <c r="M22" s="114"/>
+      <c r="N22" s="118"/>
+      <c r="O22" s="117"/>
+      <c r="P22" s="117"/>
+      <c r="Q22" s="114"/>
+      <c r="R22" s="118"/>
+      <c r="S22" s="119"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="123"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="126"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="126"/>
-      <c r="J23" s="127"/>
-      <c r="K23" s="129"/>
-      <c r="L23" s="129"/>
-      <c r="M23" s="126"/>
-      <c r="N23" s="127"/>
-      <c r="O23" s="129"/>
-      <c r="P23" s="129"/>
-      <c r="Q23" s="126"/>
-      <c r="R23" s="127"/>
-      <c r="S23" s="130"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="127"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="124"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="127"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="124"/>
+      <c r="N23" s="125"/>
+      <c r="O23" s="127"/>
+      <c r="P23" s="127"/>
+      <c r="Q23" s="124"/>
+      <c r="R23" s="125"/>
+      <c r="S23" s="128"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="87" t="s">
+      <c r="B24" s="85" t="s">
         <v>196</v>
       </c>
-      <c r="C24" s="86" t="s">
+      <c r="C24" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="D24" s="100"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="101"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="103"/>
-      <c r="L24" s="103"/>
-      <c r="M24" s="132"/>
-      <c r="N24" s="102"/>
-      <c r="O24" s="131"/>
-      <c r="P24" s="131"/>
-      <c r="Q24" s="101"/>
-      <c r="R24" s="104"/>
-      <c r="S24" s="105"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="102"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="102"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="130"/>
+      <c r="N24" s="100"/>
+      <c r="O24" s="129"/>
+      <c r="P24" s="129"/>
+      <c r="Q24" s="99"/>
+      <c r="R24" s="102"/>
+      <c r="S24" s="103"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="99"/>
-      <c r="C25" s="106"/>
-      <c r="D25" s="107"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="108"/>
-      <c r="J25" s="112"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="108"/>
-      <c r="N25" s="112"/>
-      <c r="O25" s="111"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="108"/>
-      <c r="R25" s="112"/>
-      <c r="S25" s="113"/>
+      <c r="B25" s="97"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="109"/>
+      <c r="H25" s="109"/>
+      <c r="I25" s="106"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="106"/>
+      <c r="N25" s="110"/>
+      <c r="O25" s="109"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="106"/>
+      <c r="R25" s="110"/>
+      <c r="S25" s="111"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="99"/>
-      <c r="C26" s="114" t="s">
+      <c r="B26" s="97"/>
+      <c r="C26" s="112" t="s">
         <v>198</v>
       </c>
-      <c r="D26" s="115"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="119"/>
-      <c r="H26" s="119"/>
-      <c r="I26" s="116"/>
-      <c r="J26" s="120"/>
-      <c r="K26" s="119"/>
-      <c r="L26" s="119"/>
-      <c r="M26" s="116"/>
-      <c r="N26" s="120"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="118"/>
-      <c r="Q26" s="116"/>
-      <c r="R26" s="120"/>
-      <c r="S26" s="121"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="114"/>
+      <c r="F26" s="118"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="114"/>
+      <c r="J26" s="118"/>
+      <c r="K26" s="117"/>
+      <c r="L26" s="117"/>
+      <c r="M26" s="114"/>
+      <c r="N26" s="118"/>
+      <c r="O26" s="116"/>
+      <c r="P26" s="116"/>
+      <c r="Q26" s="114"/>
+      <c r="R26" s="118"/>
+      <c r="S26" s="119"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="99"/>
-      <c r="C27" s="106"/>
-      <c r="D27" s="107"/>
-      <c r="E27" s="108"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="108"/>
-      <c r="J27" s="112"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="111"/>
-      <c r="M27" s="108"/>
-      <c r="N27" s="112"/>
-      <c r="O27" s="111"/>
-      <c r="P27" s="111"/>
-      <c r="Q27" s="108"/>
-      <c r="R27" s="112"/>
-      <c r="S27" s="113"/>
+      <c r="B27" s="97"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="106"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="109"/>
+      <c r="L27" s="109"/>
+      <c r="M27" s="106"/>
+      <c r="N27" s="110"/>
+      <c r="O27" s="109"/>
+      <c r="P27" s="109"/>
+      <c r="Q27" s="106"/>
+      <c r="R27" s="110"/>
+      <c r="S27" s="111"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="99"/>
-      <c r="C28" s="114" t="s">
+      <c r="B28" s="97"/>
+      <c r="C28" s="112" t="s">
         <v>199</v>
       </c>
-      <c r="D28" s="115"/>
-      <c r="E28" s="116"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="119"/>
-      <c r="H28" s="119"/>
-      <c r="I28" s="116"/>
-      <c r="J28" s="120"/>
-      <c r="K28" s="119"/>
-      <c r="L28" s="119"/>
-      <c r="M28" s="116"/>
-      <c r="N28" s="120"/>
-      <c r="O28" s="119"/>
-      <c r="P28" s="118"/>
-      <c r="Q28" s="135"/>
-      <c r="R28" s="120"/>
-      <c r="S28" s="121"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="118"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="118"/>
+      <c r="K28" s="117"/>
+      <c r="L28" s="117"/>
+      <c r="M28" s="114"/>
+      <c r="N28" s="118"/>
+      <c r="O28" s="117"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="133"/>
+      <c r="R28" s="118"/>
+      <c r="S28" s="119"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="99"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="140"/>
-      <c r="G29" s="141"/>
-      <c r="H29" s="142"/>
-      <c r="I29" s="139"/>
-      <c r="J29" s="140"/>
-      <c r="K29" s="141"/>
-      <c r="L29" s="142"/>
-      <c r="M29" s="139"/>
-      <c r="N29" s="143"/>
-      <c r="O29" s="142"/>
-      <c r="P29" s="141"/>
-      <c r="Q29" s="139"/>
-      <c r="R29" s="140"/>
-      <c r="S29" s="144"/>
+      <c r="B29" s="97"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="136"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="139"/>
+      <c r="H29" s="140"/>
+      <c r="I29" s="137"/>
+      <c r="J29" s="138"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="140"/>
+      <c r="M29" s="137"/>
+      <c r="N29" s="141"/>
+      <c r="O29" s="140"/>
+      <c r="P29" s="139"/>
+      <c r="Q29" s="137"/>
+      <c r="R29" s="138"/>
+      <c r="S29" s="142"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="145" t="s">
+      <c r="B30" s="143" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="146" t="s">
+      <c r="C30" s="144" t="s">
         <v>145</v>
       </c>
-      <c r="D30" s="100"/>
-      <c r="E30" s="147"/>
-      <c r="F30" s="148"/>
-      <c r="G30" s="148"/>
-      <c r="H30" s="149"/>
-      <c r="I30" s="150"/>
-      <c r="J30" s="148"/>
-      <c r="K30" s="148"/>
-      <c r="L30" s="149"/>
-      <c r="M30" s="150"/>
-      <c r="N30" s="148"/>
-      <c r="O30" s="149"/>
-      <c r="P30" s="148"/>
-      <c r="Q30" s="150"/>
-      <c r="R30" s="148"/>
-      <c r="S30" s="151"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="145"/>
+      <c r="F30" s="146"/>
+      <c r="G30" s="146"/>
+      <c r="H30" s="147"/>
+      <c r="I30" s="148"/>
+      <c r="J30" s="146"/>
+      <c r="K30" s="146"/>
+      <c r="L30" s="147"/>
+      <c r="M30" s="148"/>
+      <c r="N30" s="146"/>
+      <c r="O30" s="147"/>
+      <c r="P30" s="146"/>
+      <c r="Q30" s="148"/>
+      <c r="R30" s="146"/>
+      <c r="S30" s="149"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="152"/>
-      <c r="C31" s="153"/>
-      <c r="D31" s="107"/>
-      <c r="E31" s="154"/>
-      <c r="F31" s="155"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="156"/>
-      <c r="I31" s="157"/>
-      <c r="J31" s="155"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="156"/>
-      <c r="M31" s="157"/>
-      <c r="N31" s="155"/>
-      <c r="O31" s="156"/>
-      <c r="P31" s="155"/>
-      <c r="Q31" s="157"/>
-      <c r="R31" s="155"/>
-      <c r="S31" s="113"/>
+      <c r="B31" s="150"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="152"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="153"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="155"/>
+      <c r="J31" s="153"/>
+      <c r="K31" s="156"/>
+      <c r="L31" s="154"/>
+      <c r="M31" s="155"/>
+      <c r="N31" s="153"/>
+      <c r="O31" s="154"/>
+      <c r="P31" s="153"/>
+      <c r="Q31" s="155"/>
+      <c r="R31" s="153"/>
+      <c r="S31" s="111"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="152"/>
-      <c r="C32" s="153" t="s">
+      <c r="B32" s="150"/>
+      <c r="C32" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="115"/>
-      <c r="E32" s="159"/>
-      <c r="F32" s="160"/>
-      <c r="G32" s="160"/>
-      <c r="H32" s="161"/>
-      <c r="I32" s="162"/>
-      <c r="J32" s="160"/>
-      <c r="K32" s="160"/>
-      <c r="L32" s="161"/>
-      <c r="M32" s="162"/>
-      <c r="N32" s="160"/>
-      <c r="O32" s="161"/>
-      <c r="P32" s="160"/>
-      <c r="Q32" s="162"/>
-      <c r="R32" s="160"/>
-      <c r="S32" s="163"/>
+      <c r="D32" s="113"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="158"/>
+      <c r="G32" s="158"/>
+      <c r="H32" s="159"/>
+      <c r="I32" s="160"/>
+      <c r="J32" s="158"/>
+      <c r="K32" s="158"/>
+      <c r="L32" s="159"/>
+      <c r="M32" s="160"/>
+      <c r="N32" s="158"/>
+      <c r="O32" s="159"/>
+      <c r="P32" s="158"/>
+      <c r="Q32" s="160"/>
+      <c r="R32" s="158"/>
+      <c r="S32" s="161"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="152"/>
-      <c r="C33" s="153"/>
-      <c r="D33" s="107"/>
-      <c r="E33" s="154"/>
-      <c r="F33" s="158"/>
-      <c r="G33" s="155"/>
-      <c r="H33" s="164"/>
-      <c r="I33" s="165"/>
-      <c r="J33" s="155"/>
-      <c r="K33" s="158"/>
-      <c r="L33" s="156"/>
-      <c r="M33" s="157"/>
-      <c r="N33" s="155"/>
-      <c r="O33" s="156"/>
-      <c r="P33" s="155"/>
-      <c r="Q33" s="157"/>
-      <c r="R33" s="155"/>
-      <c r="S33" s="113"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="151"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="152"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="153"/>
+      <c r="H33" s="162"/>
+      <c r="I33" s="163"/>
+      <c r="J33" s="153"/>
+      <c r="K33" s="156"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="155"/>
+      <c r="N33" s="153"/>
+      <c r="O33" s="154"/>
+      <c r="P33" s="153"/>
+      <c r="Q33" s="155"/>
+      <c r="R33" s="153"/>
+      <c r="S33" s="111"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="152"/>
-      <c r="C34" s="106" t="s">
+      <c r="B34" s="150"/>
+      <c r="C34" s="104" t="s">
         <v>200</v>
       </c>
-      <c r="D34" s="138"/>
-      <c r="E34" s="166"/>
-      <c r="F34" s="167"/>
-      <c r="G34" s="167"/>
-      <c r="H34" s="168"/>
-      <c r="I34" s="169"/>
-      <c r="J34" s="167"/>
-      <c r="K34" s="167"/>
-      <c r="L34" s="168"/>
-      <c r="M34" s="169"/>
-      <c r="N34" s="167"/>
-      <c r="O34" s="168"/>
-      <c r="P34" s="167"/>
-      <c r="Q34" s="169"/>
-      <c r="R34" s="167"/>
-      <c r="S34" s="170"/>
-      <c r="U34" s="171"/>
-      <c r="V34" s="172" t="s">
+      <c r="D34" s="136"/>
+      <c r="E34" s="164"/>
+      <c r="F34" s="165"/>
+      <c r="G34" s="165"/>
+      <c r="H34" s="166"/>
+      <c r="I34" s="167"/>
+      <c r="J34" s="165"/>
+      <c r="K34" s="165"/>
+      <c r="L34" s="166"/>
+      <c r="M34" s="167"/>
+      <c r="N34" s="165"/>
+      <c r="O34" s="166"/>
+      <c r="P34" s="165"/>
+      <c r="Q34" s="167"/>
+      <c r="R34" s="165"/>
+      <c r="S34" s="168"/>
+      <c r="U34" s="169"/>
+      <c r="V34" s="170" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="173"/>
-      <c r="C35" s="174"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="175"/>
-      <c r="F35" s="176"/>
-      <c r="G35" s="176"/>
-      <c r="H35" s="177"/>
-      <c r="I35" s="178"/>
-      <c r="J35" s="176"/>
-      <c r="K35" s="176"/>
-      <c r="L35" s="177"/>
-      <c r="M35" s="178"/>
-      <c r="N35" s="176"/>
-      <c r="O35" s="177"/>
-      <c r="P35" s="176"/>
-      <c r="Q35" s="178"/>
-      <c r="R35" s="176"/>
-      <c r="S35" s="130"/>
-      <c r="U35" s="179"/>
-      <c r="V35" s="180" t="s">
+      <c r="B35" s="171"/>
+      <c r="C35" s="172"/>
+      <c r="D35" s="123"/>
+      <c r="E35" s="173"/>
+      <c r="F35" s="174"/>
+      <c r="G35" s="174"/>
+      <c r="H35" s="175"/>
+      <c r="I35" s="176"/>
+      <c r="J35" s="174"/>
+      <c r="K35" s="174"/>
+      <c r="L35" s="175"/>
+      <c r="M35" s="176"/>
+      <c r="N35" s="174"/>
+      <c r="O35" s="175"/>
+      <c r="P35" s="174"/>
+      <c r="Q35" s="176"/>
+      <c r="R35" s="174"/>
+      <c r="S35" s="128"/>
+      <c r="U35" s="177"/>
+      <c r="V35" s="178" t="s">
         <v>202</v>
       </c>
     </row>

--- a/Documentation/LHO - M5 - JournalPlanif.xlsx
+++ b/Documentation/LHO - M5 - JournalPlanif.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="2"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" state="visible" r:id="rId3"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
   <si>
     <t>date</t>
   </si>
@@ -329,18 +329,18 @@
     <t xml:space="preserve">Déploiement de la première version sur Windows, Linux et MacOS. Avec Installateur universel pour windows Inno Setup.</t>
   </si>
   <si>
+    <t xml:space="preserve">Documentation du processus de déploiement multiplateforme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création des différents test pour l'application. pas encore testé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relecture et correction de la documentation</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;-- A jour avec la BDD</t>
   </si>
   <si>
-    <t xml:space="preserve">Documentation du processus de déploiement multiplateforme.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création des différents test pour l'application. pas encore testé.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relecture et correction de la documentation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Test complet de l'application</t>
   </si>
   <si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ajout Licence dans la documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création et finalisation de la présentation</t>
   </si>
   <si>
     <t xml:space="preserve">Par jour</t>
@@ -1620,7 +1623,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="182">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1677,6 +1680,15 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="169" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2294,10 +2306,10 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>55.5</c:v>
+                  <c:v>60.75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>75.66666666666667</c:v>
+                  <c:v>77.16666666666667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4912,8 +4924,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E80">
-  <autoFilter ref="B2:E80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E81">
+  <autoFilter ref="B2:E81"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5477,7 +5489,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.678321678321678e-002</v>
+        <v>1.6506189821182942e-002</v>
       </c>
       <c r="J3" s="12" t="str">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -5510,7 +5522,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.678321678321678e-002</v>
+        <v>1.6506189821182942e-002</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -5543,7 +5555,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>5.3146853146853142e-002</v>
+        <v>5.2269601100412649e-002</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -5576,7 +5588,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>9.5104895104895087e-002</v>
+        <v>9.3535075653369992e-002</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -5609,7 +5621,7 @@
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.3398601398601398</v>
+        <v>0.33425034387895458</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -5642,7 +5654,7 @@
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.43170163170163167</v>
+        <v>0.42457588262265011</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -5675,7 +5687,7 @@
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>4.3822843822843821e-002</v>
+        <v>4.3099495644199903e-002</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -5704,11 +5716,11 @@
       </c>
       <c r="H10" s="16">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>2.7972027972027968e-003</v>
+        <v>1.9257221458046765e-002</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -5731,7 +5743,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>178.75000000000003</v>
+        <v>181.75000000000003</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -6608,9 +6620,6 @@
       <c r="E73" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G73" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="74">
       <c r="B74" s="5">
@@ -6623,7 +6632,7 @@
         <v>12</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75">
@@ -6637,7 +6646,7 @@
         <v>21</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76">
@@ -6651,6 +6660,9 @@
         <v>12</v>
       </c>
       <c r="E76" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G76" s="25" t="s">
         <v>101</v>
       </c>
     </row>
@@ -6711,10 +6723,18 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="8"/>
+      <c r="B81" s="24">
+        <v>46184</v>
+      </c>
+      <c r="C81" s="21">
+        <v>0.125</v>
+      </c>
+      <c r="D81" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>106</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -6732,7 +6752,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{FB648811-ECE8-4492-836D-196A61C7A278}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{A40C2A4D-6AB0-4D36-9062-8784943F8D47}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6756,11 +6776,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -6774,47 +6794,47 @@
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25">
+      <c r="A3" s="28">
         <v>46042</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A3,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C3" s="26"/>
+      <c r="C3" s="29"/>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F3" s="27">
+        <v>112</v>
+      </c>
+      <c r="F3" s="30">
         <f t="shared" ref="F3:F8" si="0">SUMPRODUCT((MONTH($A$3:$A$152)=D3)*($A$3:$A$152&lt;&gt;"")*$B$3:$B$152)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="31">
         <f t="shared" ref="G3:G8" si="1">F3*24</f>
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25">
+      <c r="A4" s="28">
         <v>46043</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A4,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6823,22 +6843,22 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F4" s="27">
+        <v>113</v>
+      </c>
+      <c r="F4" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25">
+      <c r="A5" s="28">
         <v>46044</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A5,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6847,22 +6867,22 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F5" s="27">
+        <v>114</v>
+      </c>
+      <c r="F5" s="30">
         <f t="shared" si="0"/>
         <v>2.6805555555555558</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="31">
         <f t="shared" si="1"/>
         <v>64.333333333333343</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25">
+      <c r="A6" s="28">
         <v>46045</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A6,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6871,22 +6891,22 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="27">
+        <v>115</v>
+      </c>
+      <c r="F6" s="30">
         <f t="shared" si="0"/>
         <v>1.2083333333333333</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="31">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25">
+      <c r="A7" s="28">
         <v>46046</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A7,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6895,22 +6915,22 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" s="27">
+        <v>116</v>
+      </c>
+      <c r="F7" s="30">
         <f t="shared" si="0"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="31">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25">
+      <c r="A8" s="28">
         <v>46047</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A8,Journal[Temps])</f>
         <v>0</v>
       </c>
@@ -6919,2071 +6939,2071 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F8" s="27">
+        <v>117</v>
+      </c>
+      <c r="F8" s="30">
         <f t="shared" si="0"/>
-        <v>0.64236111111111116</v>
-      </c>
-      <c r="G8" s="28">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="G8" s="31">
         <f t="shared" si="1"/>
-        <v>15.416666666666668</v>
+        <v>18.416666666666668</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25">
+      <c r="A9" s="28">
         <v>46048</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A9,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C9"/>
-      <c r="G9" s="28">
+      <c r="G9" s="31">
         <f>SUM(G3:G8)</f>
-        <v>115.75000000000001</v>
+        <v>118.75000000000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25">
+      <c r="A10" s="28">
         <v>46049</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A10,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11">
-      <c r="A11" s="25">
+      <c r="A11" s="28">
         <v>46050</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A11,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C11"/>
     </row>
     <row r="12">
-      <c r="A12" s="25">
+      <c r="A12" s="28">
         <v>46051</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A12,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C12"/>
     </row>
     <row r="13">
-      <c r="A13" s="25">
+      <c r="A13" s="28">
         <v>46052</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A13,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C13"/>
     </row>
     <row r="14">
-      <c r="A14" s="25">
+      <c r="A14" s="28">
         <v>46053</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A14,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C14"/>
     </row>
     <row r="15">
-      <c r="A15" s="25">
+      <c r="A15" s="28">
         <v>46054</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A15,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C15"/>
     </row>
     <row r="16">
-      <c r="A16" s="25">
+      <c r="A16" s="28">
         <v>46055</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A16,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C16"/>
     </row>
     <row r="17">
-      <c r="A17" s="25">
+      <c r="A17" s="28">
         <v>46056</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A17,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C17"/>
     </row>
     <row r="18">
-      <c r="A18" s="25">
+      <c r="A18" s="28">
         <v>46057</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A18,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C18"/>
     </row>
     <row r="19">
-      <c r="A19" s="25">
+      <c r="A19" s="28">
         <v>46058</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A19,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20">
-      <c r="A20" s="25">
+      <c r="A20" s="28">
         <v>46059</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A20,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C20"/>
     </row>
     <row r="21">
-      <c r="A21" s="25">
+      <c r="A21" s="28">
         <v>46060</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A21,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C21"/>
     </row>
     <row r="22">
-      <c r="A22" s="25">
+      <c r="A22" s="28">
         <v>46061</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A22,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C22"/>
     </row>
     <row r="23">
-      <c r="A23" s="25">
+      <c r="A23" s="28">
         <v>46062</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A23,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C23"/>
     </row>
     <row r="24">
-      <c r="A24" s="25">
+      <c r="A24" s="28">
         <v>46063</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A24,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C24"/>
     </row>
     <row r="25">
-      <c r="A25" s="25">
+      <c r="A25" s="28">
         <v>46064</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A25,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C25"/>
     </row>
     <row r="26">
-      <c r="A26" s="25">
+      <c r="A26" s="28">
         <v>46065</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A26,Journal[Temps])</f>
         <v>0</v>
       </c>
       <c r="C26"/>
-      <c r="F26" s="28"/>
+      <c r="F26" s="31"/>
     </row>
     <row r="27">
-      <c r="A27" s="25">
+      <c r="A27" s="28">
         <v>46066</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A27,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25">
+      <c r="A28" s="28">
         <v>46067</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A28,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25">
+      <c r="A29" s="28">
         <v>46068</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A29,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25">
+      <c r="A30" s="28">
         <v>46069</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A30,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25">
+      <c r="A31" s="28">
         <v>46070</v>
       </c>
-      <c r="B31" s="26">
+      <c r="B31" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A31,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25">
+      <c r="A32" s="28">
         <v>46071</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A32,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25">
+      <c r="A33" s="28">
         <v>46072</v>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A33,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25">
+      <c r="A34" s="28">
         <v>46073</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A34,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="25">
+      <c r="A35" s="28">
         <v>46074</v>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A35,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25">
+      <c r="A36" s="28">
         <v>46075</v>
       </c>
-      <c r="B36" s="26">
+      <c r="B36" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A36,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="25">
+      <c r="A37" s="28">
         <v>46076</v>
       </c>
-      <c r="B37" s="26">
+      <c r="B37" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A37,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="25">
+      <c r="A38" s="28">
         <v>46077</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A38,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="25">
+      <c r="A39" s="28">
         <v>46078</v>
       </c>
-      <c r="B39" s="26">
+      <c r="B39" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A39,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25">
+      <c r="A40" s="28">
         <v>46079</v>
       </c>
-      <c r="B40" s="26">
+      <c r="B40" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A40,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25">
+      <c r="A41" s="28">
         <v>46080</v>
       </c>
-      <c r="B41" s="26">
+      <c r="B41" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A41,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="25">
+      <c r="A42" s="28">
         <v>46081</v>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A42,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="25">
+      <c r="A43" s="28">
         <v>46082</v>
       </c>
-      <c r="B43" s="26">
+      <c r="B43" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A43,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="25">
+      <c r="A44" s="28">
         <v>46083</v>
       </c>
-      <c r="B44" s="26">
+      <c r="B44" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A44,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="25">
+      <c r="A45" s="28">
         <v>46084</v>
       </c>
-      <c r="B45" s="26">
+      <c r="B45" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A45,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="25">
+      <c r="A46" s="28">
         <v>46085</v>
       </c>
-      <c r="B46" s="26">
+      <c r="B46" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A46,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="25">
+      <c r="A47" s="28">
         <v>46086</v>
       </c>
-      <c r="B47" s="26">
+      <c r="B47" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A47,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="25">
+      <c r="A48" s="28">
         <v>46087</v>
       </c>
-      <c r="B48" s="26">
+      <c r="B48" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A48,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="25">
+      <c r="A49" s="28">
         <v>46088</v>
       </c>
-      <c r="B49" s="26">
+      <c r="B49" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A49,Journal[Temps])</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="25">
+      <c r="A50" s="28">
         <v>46089</v>
       </c>
-      <c r="B50" s="26">
+      <c r="B50" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A50,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="25">
+      <c r="A51" s="28">
         <v>46090</v>
       </c>
-      <c r="B51" s="26">
+      <c r="B51" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A51,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="25">
+      <c r="A52" s="28">
         <v>46091</v>
       </c>
-      <c r="B52" s="26">
+      <c r="B52" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A52,Journal[Temps])</f>
         <v>0.29166666666666669</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="25">
+      <c r="A53" s="28">
         <v>46092</v>
       </c>
-      <c r="B53" s="26">
+      <c r="B53" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A53,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="25">
+      <c r="A54" s="28">
         <v>46093</v>
       </c>
-      <c r="B54" s="26">
+      <c r="B54" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A54,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="25">
+      <c r="A55" s="28">
         <v>46094</v>
       </c>
-      <c r="B55" s="26">
+      <c r="B55" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A55,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="25">
+      <c r="A56" s="28">
         <v>46095</v>
       </c>
-      <c r="B56" s="26">
+      <c r="B56" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A56,Journal[Temps])</f>
         <v>0.1875</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="25">
+      <c r="A57" s="28">
         <v>46096</v>
       </c>
-      <c r="B57" s="26">
+      <c r="B57" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A57,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="25">
+      <c r="A58" s="28">
         <v>46097</v>
       </c>
-      <c r="B58" s="26">
+      <c r="B58" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A58,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="25">
+      <c r="A59" s="28">
         <v>46098</v>
       </c>
-      <c r="B59" s="26">
+      <c r="B59" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A59,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="25">
+      <c r="A60" s="28">
         <v>46099</v>
       </c>
-      <c r="B60" s="26">
+      <c r="B60" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C60" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A60,Journal[Temps])</f>
         <v>0.20833333333333334</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="25">
+      <c r="A61" s="28">
         <v>46100</v>
       </c>
-      <c r="B61" s="26">
+      <c r="B61" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A61,Journal[Temps])</f>
         <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="25">
+      <c r="A62" s="28">
         <v>46101</v>
       </c>
-      <c r="B62" s="26">
+      <c r="B62" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C62" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A62,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="25">
+      <c r="A63" s="28">
         <v>46102</v>
       </c>
-      <c r="B63" s="26">
+      <c r="B63" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C63" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A63,Journal[Temps])</f>
         <v>0.20833333333333331</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="25">
+      <c r="A64" s="28">
         <v>46103</v>
       </c>
-      <c r="B64" s="26">
+      <c r="B64" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C64" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A64,Journal[Temps])</f>
         <v>0.375</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="25">
+      <c r="A65" s="28">
         <v>46104</v>
       </c>
-      <c r="B65" s="26">
+      <c r="B65" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C65" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A65,Journal[Temps])</f>
         <v>1.3888888888888888e-002</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="25">
+      <c r="A66" s="28">
         <v>46105</v>
       </c>
-      <c r="B66" s="26">
+      <c r="B66" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C66" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A66,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="25">
+      <c r="A67" s="28">
         <v>46106</v>
       </c>
-      <c r="B67" s="26">
+      <c r="B67" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C67" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A67,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="25">
+      <c r="A68" s="28">
         <v>46107</v>
       </c>
-      <c r="B68" s="26">
+      <c r="B68" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C68" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A68,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="25">
+      <c r="A69" s="28">
         <v>46108</v>
       </c>
-      <c r="B69" s="26">
+      <c r="B69" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C69" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A69,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="25">
+      <c r="A70" s="28">
         <v>46109</v>
       </c>
-      <c r="B70" s="26">
+      <c r="B70" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C70" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A70,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="25">
+      <c r="A71" s="28">
         <v>46110</v>
       </c>
-      <c r="B71" s="26">
+      <c r="B71" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C71" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A71,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="25">
+      <c r="A72" s="28">
         <v>46111</v>
       </c>
-      <c r="B72" s="26">
+      <c r="B72" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C72" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A72,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="25">
+      <c r="A73" s="28">
         <v>46112</v>
       </c>
-      <c r="B73" s="26">
+      <c r="B73" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C73" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A73,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="25">
+      <c r="A74" s="28">
         <v>46113</v>
       </c>
-      <c r="B74" s="26">
+      <c r="B74" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C74" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A74,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="25">
+      <c r="A75" s="28">
         <v>46114</v>
       </c>
-      <c r="B75" s="26">
+      <c r="B75" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C75" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A75,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="25">
+      <c r="A76" s="28">
         <v>46115</v>
       </c>
-      <c r="B76" s="26">
+      <c r="B76" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C76" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A76,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="25">
+      <c r="A77" s="28">
         <v>46116</v>
       </c>
-      <c r="B77" s="26">
+      <c r="B77" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C77" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A77,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="25">
+      <c r="A78" s="28">
         <v>46117</v>
       </c>
-      <c r="B78" s="26">
+      <c r="B78" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C78" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A78,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="25">
+      <c r="A79" s="28">
         <v>46118</v>
       </c>
-      <c r="B79" s="26">
+      <c r="B79" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C79" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A79,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="25">
+      <c r="A80" s="28">
         <v>46119</v>
       </c>
-      <c r="B80" s="26">
+      <c r="B80" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C80" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A80,Journal[Temps])</f>
         <v>8.3333333333333329e-002</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="25">
+      <c r="A81" s="28">
         <v>46120</v>
       </c>
-      <c r="B81" s="26">
+      <c r="B81" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C81" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A81,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="25">
+      <c r="A82" s="28">
         <v>46121</v>
       </c>
-      <c r="B82" s="26">
+      <c r="B82" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C82" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A82,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="25">
+      <c r="A83" s="28">
         <v>46122</v>
       </c>
-      <c r="B83" s="26">
+      <c r="B83" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C83" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A83,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="25">
+      <c r="A84" s="28">
         <v>46123</v>
       </c>
-      <c r="B84" s="26">
+      <c r="B84" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C84" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A84,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="25">
+      <c r="A85" s="28">
         <v>46124</v>
       </c>
-      <c r="B85" s="26">
+      <c r="B85" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C85" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A85,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="25">
+      <c r="A86" s="28">
         <v>46125</v>
       </c>
-      <c r="B86" s="26">
+      <c r="B86" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A86,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="25">
+      <c r="A87" s="28">
         <v>46126</v>
       </c>
-      <c r="B87" s="26">
+      <c r="B87" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C87" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A87,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="25">
+      <c r="A88" s="28">
         <v>46127</v>
       </c>
-      <c r="B88" s="26">
+      <c r="B88" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C88" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A88,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="25">
+      <c r="A89" s="28">
         <v>46128</v>
       </c>
-      <c r="B89" s="26">
+      <c r="B89" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C89" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A89,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="25">
+      <c r="A90" s="28">
         <v>46129</v>
       </c>
-      <c r="B90" s="26">
+      <c r="B90" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C90" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A90,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="25">
+      <c r="A91" s="28">
         <v>46130</v>
       </c>
-      <c r="B91" s="26">
+      <c r="B91" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C91" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A91,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="25">
+      <c r="A92" s="28">
         <v>46131</v>
       </c>
-      <c r="B92" s="26">
+      <c r="B92" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C92" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A92,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="25">
+      <c r="A93" s="28">
         <v>46132</v>
       </c>
-      <c r="B93" s="26">
+      <c r="B93" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C93" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A93,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="25">
+      <c r="A94" s="28">
         <v>46133</v>
       </c>
-      <c r="B94" s="26">
+      <c r="B94" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C94" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A94,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="25">
+      <c r="A95" s="28">
         <v>46134</v>
       </c>
-      <c r="B95" s="26">
+      <c r="B95" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C95" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A95,Journal[Temps])</f>
         <v>0.10416666666666666</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="25">
+      <c r="A96" s="28">
         <v>46135</v>
       </c>
-      <c r="B96" s="26">
+      <c r="B96" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C96" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A96,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="25">
+      <c r="A97" s="28">
         <v>46136</v>
       </c>
-      <c r="B97" s="26">
+      <c r="B97" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C97" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A97,Journal[Temps])</f>
         <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="25">
+      <c r="A98" s="28">
         <v>46137</v>
       </c>
-      <c r="B98" s="26">
+      <c r="B98" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C98" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A98,Journal[Temps])</f>
         <v>0.125</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="25">
+      <c r="A99" s="28">
         <v>46138</v>
       </c>
-      <c r="B99" s="26">
+      <c r="B99" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C99" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A99,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="25">
+      <c r="A100" s="28">
         <v>46139</v>
       </c>
-      <c r="B100" s="26">
+      <c r="B100" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C100" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A100,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="25">
+      <c r="A101" s="28">
         <v>46140</v>
       </c>
-      <c r="B101" s="26">
+      <c r="B101" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C101" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A101,Journal[Temps])</f>
         <v>0.22916666666666669</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="25">
+      <c r="A102" s="28">
         <v>46141</v>
       </c>
-      <c r="B102" s="26">
+      <c r="B102" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C102" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A102,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="25">
+      <c r="A103" s="28">
         <v>46142</v>
       </c>
-      <c r="B103" s="26">
+      <c r="B103" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C103" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A103,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="25">
+      <c r="A104" s="28">
         <v>46143</v>
       </c>
-      <c r="B104" s="26">
+      <c r="B104" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C104" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A104,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="25">
+      <c r="A105" s="28">
         <v>46144</v>
       </c>
-      <c r="B105" s="26">
+      <c r="B105" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C105" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A105,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="25">
+      <c r="A106" s="28">
         <v>46145</v>
       </c>
-      <c r="B106" s="26">
+      <c r="B106" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C106" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A106,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="25">
+      <c r="A107" s="28">
         <v>46146</v>
       </c>
-      <c r="B107" s="26">
+      <c r="B107" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C107" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A107,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="25">
+      <c r="A108" s="28">
         <v>46147</v>
       </c>
-      <c r="B108" s="26">
+      <c r="B108" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C108" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A108,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="25">
+      <c r="A109" s="28">
         <v>46148</v>
       </c>
-      <c r="B109" s="26">
+      <c r="B109" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C109" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A109,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="25">
+      <c r="A110" s="28">
         <v>46149</v>
       </c>
-      <c r="B110" s="26">
+      <c r="B110" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C110" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A110,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="25">
+      <c r="A111" s="28">
         <v>46150</v>
       </c>
-      <c r="B111" s="26">
+      <c r="B111" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C111" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A111,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="25">
+      <c r="A112" s="28">
         <v>46151</v>
       </c>
-      <c r="B112" s="26">
+      <c r="B112" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C112" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A112,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="25">
+      <c r="A113" s="28">
         <v>46152</v>
       </c>
-      <c r="B113" s="26">
+      <c r="B113" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C113" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A113,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="25">
+      <c r="A114" s="28">
         <v>46153</v>
       </c>
-      <c r="B114" s="26">
+      <c r="B114" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C114" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A114,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="25">
+      <c r="A115" s="28">
         <v>46154</v>
       </c>
-      <c r="B115" s="26">
+      <c r="B115" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C115" s="32">
         <f>SUMIF(Journal[date],SommeParJours!A115,Journal[Temps])</f>
         <v>0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="25">
+      <c r="A116" s="28">
         <v>46155</v>
       </c>
-      <c r="B116" s="26">
+      <c r="B116" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A116,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C116" s="29"/>
+      <c r="C116" s="32"/>
     </row>
     <row r="117">
-      <c r="A117" s="25">
+      <c r="A117" s="28">
         <v>46156</v>
       </c>
-      <c r="B117" s="26">
+      <c r="B117" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A117,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C117" s="29"/>
+      <c r="C117" s="32"/>
     </row>
     <row r="118">
-      <c r="A118" s="25">
+      <c r="A118" s="28">
         <v>46157</v>
       </c>
-      <c r="B118" s="26">
+      <c r="B118" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A118,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C118" s="29"/>
+      <c r="C118" s="32"/>
     </row>
     <row r="119">
-      <c r="A119" s="25">
+      <c r="A119" s="28">
         <v>46158</v>
       </c>
-      <c r="B119" s="26">
+      <c r="B119" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A119,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C119" s="29"/>
+      <c r="C119" s="32"/>
     </row>
     <row r="120">
-      <c r="A120" s="25">
+      <c r="A120" s="28">
         <v>46159</v>
       </c>
-      <c r="B120" s="26">
+      <c r="B120" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A120,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C120" s="29"/>
+      <c r="C120" s="32"/>
     </row>
     <row r="121">
-      <c r="A121" s="25">
+      <c r="A121" s="28">
         <v>46160</v>
       </c>
-      <c r="B121" s="26">
+      <c r="B121" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A121,Journal[Temps])</f>
         <v>0.125</v>
       </c>
-      <c r="C121" s="29"/>
+      <c r="C121" s="32"/>
     </row>
     <row r="122">
-      <c r="A122" s="25">
+      <c r="A122" s="28">
         <v>46161</v>
       </c>
-      <c r="B122" s="26">
+      <c r="B122" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A122,Journal[Temps])</f>
         <v>0.16666666666666669</v>
       </c>
-      <c r="C122" s="29"/>
+      <c r="C122" s="32"/>
     </row>
     <row r="123">
-      <c r="A123" s="25">
+      <c r="A123" s="28">
         <v>46162</v>
       </c>
-      <c r="B123" s="26">
+      <c r="B123" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A123,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C123" s="29"/>
+      <c r="C123" s="32"/>
     </row>
     <row r="124">
-      <c r="A124" s="25">
+      <c r="A124" s="28">
         <v>46163</v>
       </c>
-      <c r="B124" s="26">
+      <c r="B124" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A124,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C124" s="29"/>
+      <c r="C124" s="32"/>
     </row>
     <row r="125">
-      <c r="A125" s="25">
+      <c r="A125" s="28">
         <v>46164</v>
       </c>
-      <c r="B125" s="26">
+      <c r="B125" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A125,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C125" s="29"/>
+      <c r="C125" s="32"/>
     </row>
     <row r="126">
-      <c r="A126" s="25">
+      <c r="A126" s="28">
         <v>46165</v>
       </c>
-      <c r="B126" s="26">
+      <c r="B126" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A126,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C126" s="29"/>
+      <c r="C126" s="32"/>
     </row>
     <row r="127">
-      <c r="A127" s="25">
+      <c r="A127" s="28">
         <v>46166</v>
       </c>
-      <c r="B127" s="26">
+      <c r="B127" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A127,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C127" s="29"/>
+      <c r="C127" s="32"/>
     </row>
     <row r="128">
-      <c r="A128" s="25">
+      <c r="A128" s="28">
         <v>46167</v>
       </c>
-      <c r="B128" s="26">
+      <c r="B128" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A128,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C128" s="29"/>
+      <c r="C128" s="32"/>
     </row>
     <row r="129">
-      <c r="A129" s="25">
+      <c r="A129" s="28">
         <v>46168</v>
       </c>
-      <c r="B129" s="26">
+      <c r="B129" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A129,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C129" s="29"/>
+      <c r="C129" s="32"/>
     </row>
     <row r="130">
-      <c r="A130" s="25">
+      <c r="A130" s="28">
         <v>46169</v>
       </c>
-      <c r="B130" s="26">
+      <c r="B130" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A130,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C130" s="29"/>
+      <c r="C130" s="32"/>
     </row>
     <row r="131">
-      <c r="A131" s="25">
+      <c r="A131" s="28">
         <v>46170</v>
       </c>
-      <c r="B131" s="26">
+      <c r="B131" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A131,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C131" s="29"/>
+      <c r="C131" s="32"/>
     </row>
     <row r="132">
-      <c r="A132" s="25">
+      <c r="A132" s="28">
         <v>46171</v>
       </c>
-      <c r="B132" s="26">
+      <c r="B132" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A132,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C132" s="29"/>
+      <c r="C132" s="32"/>
     </row>
     <row r="133">
-      <c r="A133" s="25">
+      <c r="A133" s="28">
         <v>46172</v>
       </c>
-      <c r="B133" s="26">
+      <c r="B133" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A133,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C133" s="29"/>
+      <c r="C133" s="32"/>
     </row>
     <row r="134">
-      <c r="A134" s="25">
+      <c r="A134" s="28">
         <v>46173</v>
       </c>
-      <c r="B134" s="26">
+      <c r="B134" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A134,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C134" s="29"/>
+      <c r="C134" s="32"/>
     </row>
     <row r="135">
-      <c r="A135" s="25">
+      <c r="A135" s="28">
         <v>46174</v>
       </c>
-      <c r="B135" s="26">
+      <c r="B135" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A135,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C135" s="29"/>
+      <c r="C135" s="32"/>
     </row>
     <row r="136">
-      <c r="A136" s="25">
+      <c r="A136" s="28">
         <v>46175</v>
       </c>
-      <c r="B136" s="26">
+      <c r="B136" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A136,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C136" s="29"/>
+      <c r="C136" s="32"/>
     </row>
     <row r="137">
-      <c r="A137" s="25">
+      <c r="A137" s="28">
         <v>46176</v>
       </c>
-      <c r="B137" s="26">
+      <c r="B137" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A137,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C137" s="29"/>
+      <c r="C137" s="32"/>
     </row>
     <row r="138">
-      <c r="A138" s="25">
+      <c r="A138" s="28">
         <v>46177</v>
       </c>
-      <c r="B138" s="26">
+      <c r="B138" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A138,Journal[Temps])</f>
         <v>0.2986111111111111</v>
       </c>
-      <c r="C138" s="29"/>
+      <c r="C138" s="32"/>
     </row>
     <row r="139">
-      <c r="A139" s="25">
+      <c r="A139" s="28">
         <v>46178</v>
       </c>
-      <c r="B139" s="26">
+      <c r="B139" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A139,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C139" s="29"/>
+      <c r="C139" s="32"/>
     </row>
     <row r="140">
-      <c r="A140" s="25">
+      <c r="A140" s="28">
         <v>46179</v>
       </c>
-      <c r="B140" s="26">
+      <c r="B140" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A140,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C140" s="29"/>
+      <c r="C140" s="32"/>
     </row>
     <row r="141">
-      <c r="A141" s="25">
+      <c r="A141" s="28">
         <v>46180</v>
       </c>
-      <c r="B141" s="26">
+      <c r="B141" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A141,Journal[Temps])</f>
         <v>4.1666666666666664e-002</v>
       </c>
-      <c r="C141" s="29"/>
+      <c r="C141" s="32"/>
     </row>
     <row r="142">
-      <c r="A142" s="25">
+      <c r="A142" s="28">
         <v>46181</v>
       </c>
-      <c r="B142" s="26">
+      <c r="B142" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A142,Journal[Temps])</f>
         <v>0.14583333333333334</v>
       </c>
-      <c r="C142" s="29"/>
+      <c r="C142" s="32"/>
     </row>
     <row r="143">
-      <c r="A143" s="25">
+      <c r="A143" s="28">
         <v>46182</v>
       </c>
-      <c r="B143" s="26">
+      <c r="B143" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A143,Journal[Temps])</f>
         <v>0.15625000000000003</v>
       </c>
-      <c r="C143" s="29"/>
+      <c r="C143" s="32"/>
     </row>
     <row r="144">
-      <c r="A144" s="25">
+      <c r="A144" s="28">
         <v>46183</v>
       </c>
-      <c r="B144" s="26">
+      <c r="B144" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A144,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C144" s="29"/>
+      <c r="C144" s="32"/>
     </row>
     <row r="145">
-      <c r="A145" s="25">
+      <c r="A145" s="28">
         <v>46184</v>
       </c>
-      <c r="B145" s="26">
+      <c r="B145" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A145,Journal[Temps])</f>
-        <v>0</v>
-      </c>
-      <c r="C145" s="29"/>
+        <v>0.125</v>
+      </c>
+      <c r="C145" s="32"/>
     </row>
     <row r="146">
-      <c r="A146" s="25">
+      <c r="A146" s="28">
         <v>46185</v>
       </c>
-      <c r="B146" s="26">
+      <c r="B146" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A146,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C146" s="29"/>
+      <c r="C146" s="32"/>
     </row>
     <row r="147">
-      <c r="A147" s="25">
+      <c r="A147" s="28">
         <v>46186</v>
       </c>
-      <c r="B147" s="26">
+      <c r="B147" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A147,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C147" s="29"/>
+      <c r="C147" s="32"/>
     </row>
     <row r="148">
-      <c r="A148" s="25">
+      <c r="A148" s="28">
         <v>46187</v>
       </c>
-      <c r="B148" s="26">
+      <c r="B148" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A148,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C148" s="29"/>
+      <c r="C148" s="32"/>
     </row>
     <row r="149">
-      <c r="A149" s="25">
+      <c r="A149" s="28">
         <v>46188</v>
       </c>
-      <c r="B149" s="26">
+      <c r="B149" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A149,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C149" s="29"/>
+      <c r="C149" s="32"/>
     </row>
     <row r="150">
-      <c r="A150" s="25">
+      <c r="A150" s="28">
         <v>46189</v>
       </c>
-      <c r="B150" s="26">
+      <c r="B150" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A150,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C150" s="29"/>
+      <c r="C150" s="32"/>
     </row>
     <row r="151">
-      <c r="A151" s="25">
+      <c r="A151" s="28">
         <v>46190</v>
       </c>
-      <c r="B151" s="26">
+      <c r="B151" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A151,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C151" s="29"/>
+      <c r="C151" s="32"/>
     </row>
     <row r="152">
-      <c r="A152" s="25">
+      <c r="A152" s="28">
         <v>46191</v>
       </c>
-      <c r="B152" s="26">
+      <c r="B152" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A152,Journal[Temps])</f>
         <v>0</v>
       </c>
-      <c r="C152" s="29"/>
+      <c r="C152" s="32"/>
     </row>
     <row r="153">
-      <c r="A153" s="25"/>
-      <c r="B153" s="30"/>
-      <c r="C153" s="29"/>
+      <c r="A153" s="28"/>
+      <c r="B153" s="33"/>
+      <c r="C153" s="32"/>
     </row>
     <row r="154">
-      <c r="A154" s="25"/>
-      <c r="B154" s="30"/>
-      <c r="C154" s="29"/>
+      <c r="A154" s="28"/>
+      <c r="B154" s="33"/>
+      <c r="C154" s="32"/>
     </row>
     <row r="155">
-      <c r="A155" s="25"/>
-      <c r="B155" s="30"/>
-      <c r="C155" s="29"/>
+      <c r="A155" s="28"/>
+      <c r="B155" s="33"/>
+      <c r="C155" s="32"/>
     </row>
     <row r="156">
-      <c r="A156" s="25"/>
-      <c r="B156" s="30"/>
-      <c r="C156" s="29"/>
+      <c r="A156" s="28"/>
+      <c r="B156" s="33"/>
+      <c r="C156" s="32"/>
     </row>
     <row r="157">
-      <c r="A157" s="25"/>
-      <c r="B157" s="30"/>
-      <c r="C157" s="29"/>
+      <c r="A157" s="28"/>
+      <c r="B157" s="33"/>
+      <c r="C157" s="32"/>
     </row>
     <row r="158">
-      <c r="A158" s="25"/>
-      <c r="B158" s="30"/>
-      <c r="C158" s="29"/>
+      <c r="A158" s="28"/>
+      <c r="B158" s="33"/>
+      <c r="C158" s="32"/>
     </row>
     <row r="159">
-      <c r="A159" s="25"/>
-      <c r="B159" s="30"/>
-      <c r="C159" s="29"/>
+      <c r="A159" s="28"/>
+      <c r="B159" s="33"/>
+      <c r="C159" s="32"/>
     </row>
     <row r="160">
-      <c r="A160" s="25"/>
-      <c r="B160" s="30"/>
+      <c r="A160" s="28"/>
+      <c r="B160" s="33"/>
     </row>
     <row r="161">
-      <c r="A161" s="25"/>
-      <c r="B161" s="30"/>
+      <c r="A161" s="28"/>
+      <c r="B161" s="33"/>
     </row>
     <row r="162">
-      <c r="A162" s="25"/>
-      <c r="B162" s="30"/>
+      <c r="A162" s="28"/>
+      <c r="B162" s="33"/>
     </row>
     <row r="163">
-      <c r="A163" s="25"/>
-      <c r="B163" s="30"/>
+      <c r="A163" s="28"/>
+      <c r="B163" s="33"/>
     </row>
     <row r="164">
-      <c r="A164" s="25"/>
-      <c r="B164" s="30"/>
+      <c r="A164" s="28"/>
+      <c r="B164" s="33"/>
     </row>
     <row r="165">
-      <c r="A165" s="25"/>
-      <c r="B165" s="30"/>
+      <c r="A165" s="28"/>
+      <c r="B165" s="33"/>
     </row>
     <row r="166">
-      <c r="A166" s="25"/>
-      <c r="B166" s="30"/>
+      <c r="A166" s="28"/>
+      <c r="B166" s="33"/>
     </row>
     <row r="167">
-      <c r="A167" s="25"/>
-      <c r="B167" s="30"/>
+      <c r="A167" s="28"/>
+      <c r="B167" s="33"/>
     </row>
     <row r="168">
-      <c r="A168" s="25"/>
-      <c r="B168" s="30"/>
+      <c r="A168" s="28"/>
+      <c r="B168" s="33"/>
     </row>
     <row r="169">
-      <c r="A169" s="25"/>
-      <c r="B169" s="30"/>
+      <c r="A169" s="28"/>
+      <c r="B169" s="33"/>
     </row>
     <row r="170">
-      <c r="A170" s="25"/>
-      <c r="B170" s="30"/>
+      <c r="A170" s="28"/>
+      <c r="B170" s="33"/>
     </row>
     <row r="171">
-      <c r="A171" s="25"/>
-      <c r="B171" s="30"/>
+      <c r="A171" s="28"/>
+      <c r="B171" s="33"/>
     </row>
     <row r="172">
-      <c r="A172" s="25"/>
-      <c r="B172" s="30"/>
+      <c r="A172" s="28"/>
+      <c r="B172" s="33"/>
     </row>
     <row r="173">
-      <c r="A173" s="25"/>
-      <c r="B173" s="30"/>
+      <c r="A173" s="28"/>
+      <c r="B173" s="33"/>
     </row>
     <row r="174">
-      <c r="A174" s="25"/>
-      <c r="B174" s="30"/>
+      <c r="A174" s="28"/>
+      <c r="B174" s="33"/>
     </row>
     <row r="175">
-      <c r="A175" s="25"/>
-      <c r="B175" s="30"/>
+      <c r="A175" s="28"/>
+      <c r="B175" s="33"/>
     </row>
     <row r="176">
-      <c r="A176" s="25"/>
-      <c r="B176" s="30"/>
+      <c r="A176" s="28"/>
+      <c r="B176" s="33"/>
     </row>
     <row r="177">
-      <c r="A177" s="25"/>
-      <c r="B177" s="30"/>
+      <c r="A177" s="28"/>
+      <c r="B177" s="33"/>
     </row>
     <row r="178">
-      <c r="A178" s="25"/>
-      <c r="B178" s="30"/>
+      <c r="A178" s="28"/>
+      <c r="B178" s="33"/>
     </row>
     <row r="179">
-      <c r="A179" s="25"/>
-      <c r="B179" s="30"/>
+      <c r="A179" s="28"/>
+      <c r="B179" s="33"/>
     </row>
     <row r="180">
-      <c r="A180" s="25"/>
-      <c r="B180" s="30"/>
+      <c r="A180" s="28"/>
+      <c r="B180" s="33"/>
     </row>
     <row r="181">
-      <c r="A181" s="25"/>
-      <c r="B181" s="30"/>
+      <c r="A181" s="28"/>
+      <c r="B181" s="33"/>
     </row>
     <row r="182">
-      <c r="A182" s="25"/>
-      <c r="B182" s="30"/>
+      <c r="A182" s="28"/>
+      <c r="B182" s="33"/>
     </row>
     <row r="183">
-      <c r="A183" s="25"/>
-      <c r="B183" s="30"/>
+      <c r="A183" s="28"/>
+      <c r="B183" s="33"/>
     </row>
     <row r="184">
-      <c r="A184" s="25"/>
-      <c r="B184" s="30"/>
+      <c r="A184" s="28"/>
+      <c r="B184" s="33"/>
     </row>
     <row r="185">
-      <c r="A185" s="25"/>
-      <c r="B185" s="30"/>
+      <c r="A185" s="28"/>
+      <c r="B185" s="33"/>
     </row>
     <row r="186">
-      <c r="A186" s="25"/>
-      <c r="B186" s="30"/>
+      <c r="A186" s="28"/>
+      <c r="B186" s="33"/>
     </row>
     <row r="187">
-      <c r="A187" s="25"/>
-      <c r="B187" s="30"/>
+      <c r="A187" s="28"/>
+      <c r="B187" s="33"/>
     </row>
     <row r="188">
-      <c r="A188" s="30"/>
-      <c r="B188" s="30"/>
+      <c r="A188" s="33"/>
+      <c r="B188" s="33"/>
     </row>
     <row r="189">
-      <c r="A189" s="30"/>
-      <c r="B189" s="30"/>
+      <c r="A189" s="33"/>
+      <c r="B189" s="33"/>
     </row>
     <row r="190">
-      <c r="A190" s="30"/>
-      <c r="B190" s="30"/>
+      <c r="A190" s="33"/>
+      <c r="B190" s="33"/>
     </row>
     <row r="191">
-      <c r="A191" s="30"/>
-      <c r="B191" s="30"/>
+      <c r="A191" s="33"/>
+      <c r="B191" s="33"/>
     </row>
     <row r="192">
-      <c r="A192" s="30"/>
-      <c r="B192" s="30"/>
+      <c r="A192" s="33"/>
+      <c r="B192" s="33"/>
     </row>
     <row r="193">
-      <c r="A193" s="30"/>
-      <c r="B193" s="30"/>
+      <c r="A193" s="33"/>
+      <c r="B193" s="33"/>
     </row>
     <row r="194">
-      <c r="A194" s="30"/>
-      <c r="B194" s="30"/>
+      <c r="A194" s="33"/>
+      <c r="B194" s="33"/>
     </row>
     <row r="195">
-      <c r="A195" s="30"/>
-      <c r="B195" s="30"/>
+      <c r="A195" s="33"/>
+      <c r="B195" s="33"/>
     </row>
     <row r="196">
-      <c r="A196" s="30"/>
-      <c r="B196" s="30"/>
+      <c r="A196" s="33"/>
+      <c r="B196" s="33"/>
     </row>
     <row r="197">
-      <c r="A197" s="30"/>
-      <c r="B197" s="30"/>
+      <c r="A197" s="33"/>
+      <c r="B197" s="33"/>
     </row>
     <row r="198">
-      <c r="A198" s="30"/>
-      <c r="B198" s="30"/>
+      <c r="A198" s="33"/>
+      <c r="B198" s="33"/>
     </row>
     <row r="199">
-      <c r="A199" s="30"/>
-      <c r="B199" s="30"/>
+      <c r="A199" s="33"/>
+      <c r="B199" s="33"/>
     </row>
     <row r="200">
-      <c r="A200" s="30"/>
-      <c r="B200" s="30"/>
+      <c r="A200" s="33"/>
+      <c r="B200" s="33"/>
     </row>
     <row r="201">
-      <c r="A201" s="30"/>
-      <c r="B201" s="30"/>
+      <c r="A201" s="33"/>
+      <c r="B201" s="33"/>
     </row>
     <row r="202">
-      <c r="A202" s="30"/>
-      <c r="B202" s="30"/>
+      <c r="A202" s="33"/>
+      <c r="B202" s="33"/>
     </row>
     <row r="203">
-      <c r="A203" s="30"/>
-      <c r="B203" s="30"/>
+      <c r="A203" s="33"/>
+      <c r="B203" s="33"/>
     </row>
     <row r="204">
-      <c r="A204" s="30"/>
-      <c r="B204" s="30"/>
+      <c r="A204" s="33"/>
+      <c r="B204" s="33"/>
     </row>
     <row r="205">
-      <c r="A205" s="30"/>
-      <c r="B205" s="30"/>
+      <c r="A205" s="33"/>
+      <c r="B205" s="33"/>
     </row>
     <row r="206">
-      <c r="A206" s="30"/>
-      <c r="B206" s="30"/>
+      <c r="A206" s="33"/>
+      <c r="B206" s="33"/>
     </row>
     <row r="207">
-      <c r="A207" s="30"/>
-      <c r="B207" s="30"/>
+      <c r="A207" s="33"/>
+      <c r="B207" s="33"/>
     </row>
     <row r="208">
-      <c r="A208" s="30"/>
-      <c r="B208" s="30"/>
+      <c r="A208" s="33"/>
+      <c r="B208" s="33"/>
     </row>
     <row r="209">
-      <c r="A209" s="30"/>
-      <c r="B209" s="30"/>
+      <c r="A209" s="33"/>
+      <c r="B209" s="33"/>
     </row>
     <row r="210">
-      <c r="A210" s="30"/>
-      <c r="B210" s="30"/>
+      <c r="A210" s="33"/>
+      <c r="B210" s="33"/>
     </row>
     <row r="211">
-      <c r="A211" s="30"/>
-      <c r="B211" s="30"/>
+      <c r="A211" s="33"/>
+      <c r="B211" s="33"/>
     </row>
     <row r="212">
-      <c r="A212" s="30"/>
-      <c r="B212" s="30"/>
+      <c r="A212" s="33"/>
+      <c r="B212" s="33"/>
     </row>
     <row r="213">
-      <c r="A213" s="30"/>
-      <c r="B213" s="30"/>
+      <c r="A213" s="33"/>
+      <c r="B213" s="33"/>
     </row>
     <row r="214">
-      <c r="A214" s="30"/>
-      <c r="B214" s="30"/>
+      <c r="A214" s="33"/>
+      <c r="B214" s="33"/>
     </row>
     <row r="215">
-      <c r="A215" s="30"/>
-      <c r="B215" s="30"/>
+      <c r="A215" s="33"/>
+      <c r="B215" s="33"/>
     </row>
     <row r="216">
-      <c r="A216" s="30"/>
-      <c r="B216" s="30"/>
+      <c r="A216" s="33"/>
+      <c r="B216" s="33"/>
     </row>
     <row r="217">
-      <c r="A217" s="30"/>
-      <c r="B217" s="30"/>
+      <c r="A217" s="33"/>
+      <c r="B217" s="33"/>
     </row>
     <row r="218">
-      <c r="A218" s="30"/>
-      <c r="B218" s="30"/>
+      <c r="A218" s="33"/>
+      <c r="B218" s="33"/>
     </row>
     <row r="219">
-      <c r="A219" s="30"/>
-      <c r="B219" s="30"/>
+      <c r="A219" s="33"/>
+      <c r="B219" s="33"/>
     </row>
     <row r="220">
-      <c r="A220" s="30"/>
-      <c r="B220" s="30"/>
+      <c r="A220" s="33"/>
+      <c r="B220" s="33"/>
     </row>
     <row r="221">
-      <c r="A221" s="30"/>
-      <c r="B221" s="30"/>
+      <c r="A221" s="33"/>
+      <c r="B221" s="33"/>
     </row>
     <row r="222">
-      <c r="A222" s="30"/>
-      <c r="B222" s="30"/>
+      <c r="A222" s="33"/>
+      <c r="B222" s="33"/>
     </row>
     <row r="223">
-      <c r="A223" s="30"/>
-      <c r="B223" s="30"/>
+      <c r="A223" s="33"/>
+      <c r="B223" s="33"/>
     </row>
     <row r="224">
-      <c r="A224" s="30"/>
-      <c r="B224" s="30"/>
+      <c r="A224" s="33"/>
+      <c r="B224" s="33"/>
     </row>
     <row r="225">
-      <c r="A225" s="30"/>
-      <c r="B225" s="30"/>
+      <c r="A225" s="33"/>
+      <c r="B225" s="33"/>
     </row>
     <row r="226">
-      <c r="A226" s="30"/>
-      <c r="B226" s="30"/>
+      <c r="A226" s="33"/>
+      <c r="B226" s="33"/>
     </row>
     <row r="227">
-      <c r="A227" s="30"/>
-      <c r="B227" s="30"/>
+      <c r="A227" s="33"/>
+      <c r="B227" s="33"/>
     </row>
     <row r="228">
-      <c r="A228" s="30"/>
-      <c r="B228" s="30"/>
+      <c r="A228" s="33"/>
+      <c r="B228" s="33"/>
     </row>
     <row r="229">
-      <c r="A229" s="30"/>
-      <c r="B229" s="30"/>
+      <c r="A229" s="33"/>
+      <c r="B229" s="33"/>
     </row>
     <row r="230">
-      <c r="A230" s="30"/>
-      <c r="B230" s="30"/>
+      <c r="A230" s="33"/>
+      <c r="B230" s="33"/>
     </row>
     <row r="231">
-      <c r="A231" s="30"/>
-      <c r="B231" s="30"/>
+      <c r="A231" s="33"/>
+      <c r="B231" s="33"/>
     </row>
     <row r="232">
-      <c r="A232" s="30"/>
-      <c r="B232" s="30"/>
+      <c r="A232" s="33"/>
+      <c r="B232" s="33"/>
     </row>
     <row r="233">
-      <c r="A233" s="30"/>
-      <c r="B233" s="30"/>
+      <c r="A233" s="33"/>
+      <c r="B233" s="33"/>
     </row>
     <row r="234">
-      <c r="A234" s="30"/>
-      <c r="B234" s="30"/>
+      <c r="A234" s="33"/>
+      <c r="B234" s="33"/>
     </row>
     <row r="235">
-      <c r="A235" s="30"/>
-      <c r="B235" s="30"/>
+      <c r="A235" s="33"/>
+      <c r="B235" s="33"/>
     </row>
     <row r="236">
-      <c r="A236" s="30"/>
-      <c r="B236" s="30"/>
+      <c r="A236" s="33"/>
+      <c r="B236" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9000,2058 +9020,2049 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="4.33203125"/>
     <col bestFit="1" min="3" max="3" width="35.77734375"/>
     <col customWidth="1" min="4" max="11" width="3.44140625"/>
-    <col customWidth="1" min="12" max="12" style="31" width="6"/>
+    <col customWidth="1" min="12" max="12" style="34" width="6"/>
     <col customWidth="1" min="13" max="22" width="3.44140625"/>
-    <col customWidth="1" min="23" max="23" style="31" width="6"/>
+    <col customWidth="1" min="23" max="23" style="34" width="6"/>
     <col customWidth="1" min="24" max="29" width="3.44140625"/>
-    <col customWidth="1" min="30" max="30" style="31" width="6"/>
+    <col customWidth="1" min="30" max="30" style="34" width="6"/>
     <col customWidth="1" min="31" max="39" width="3.44140625"/>
     <col bestFit="1" customWidth="1" min="40" max="40" width="13.88671875"/>
     <col customWidth="1" min="41" max="47" width="3.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="1" ht="66.599999999999994" customHeight="1">
-      <c r="B1" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="34" t="s">
+    <row r="1" s="35" customFormat="1" ht="66.599999999999994" customHeight="1">
+      <c r="B1" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="C1" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1" s="36" t="s">
+      <c r="E1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="I1" s="35" t="s">
+      <c r="H1" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="J1" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="L1" s="39" t="s">
+      <c r="K1" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="L1" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="M1" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="N1" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="38" t="s">
-        <v>124</v>
-      </c>
-      <c r="P1" s="35" t="s">
+      <c r="O1" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="P1" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="R1" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="S1" s="35" t="s">
+      <c r="Q1" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="R1" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="T1" s="35" t="s">
+      <c r="S1" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="U1" s="35" t="s">
+      <c r="T1" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="V1" s="37" t="s">
+      <c r="U1" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="W1" s="40" t="s">
+      <c r="V1" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="X1" s="35" t="s">
+      <c r="W1" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="Y1" s="35" t="s">
+      <c r="X1" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="Z1" s="37" t="s">
+      <c r="Y1" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="AA1" s="41" t="s">
+      <c r="Z1" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="AB1" s="42" t="s">
+      <c r="AA1" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="AC1" s="42" t="s">
+      <c r="AB1" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="AD1" s="39" t="s">
+      <c r="AC1" s="45" t="s">
         <v>137</v>
       </c>
-      <c r="AE1" s="43" t="s">
+      <c r="AD1" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="AF1" s="44" t="s">
+      <c r="AE1" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="AG1" s="45" t="s">
+      <c r="AF1" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG1" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="AH1" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="AI1" s="45" t="s">
+      <c r="AH1" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="AJ1" s="45" t="s">
+      <c r="AI1" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="AK1" s="42" t="s">
+      <c r="AJ1" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="AL1" s="46"/>
-      <c r="AM1" s="46"/>
-      <c r="AN1" s="46"/>
-      <c r="AO1" s="46"/>
-      <c r="AP1" s="46"/>
-      <c r="AQ1" s="46"/>
-      <c r="AR1" s="46"/>
-      <c r="AS1" s="46"/>
-      <c r="AT1" s="46"/>
-      <c r="AU1" s="46"/>
+      <c r="AK1" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="AL1" s="49"/>
+      <c r="AM1" s="49"/>
+      <c r="AN1" s="49"/>
+      <c r="AO1" s="49"/>
+      <c r="AP1" s="49"/>
+      <c r="AQ1" s="49"/>
+      <c r="AR1" s="49"/>
+      <c r="AS1" s="49"/>
+      <c r="AT1" s="49"/>
+      <c r="AU1" s="49"/>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
-      <c r="T2" s="49"/>
-      <c r="U2" s="49"/>
-      <c r="V2" s="54"/>
-      <c r="W2" s="56"/>
-      <c r="X2" s="49"/>
-      <c r="Y2" s="49"/>
-      <c r="Z2" s="54"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="49"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="53"/>
-      <c r="AE2" s="54"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="49"/>
-      <c r="AH2" s="49"/>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="49"/>
-      <c r="AK2" s="49"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="57"/>
+      <c r="AA2" s="58"/>
+      <c r="AB2" s="52"/>
+      <c r="AC2" s="52"/>
+      <c r="AD2" s="56"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="58"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="52"/>
+      <c r="AI2" s="52"/>
+      <c r="AJ2" s="52"/>
+      <c r="AK2" s="52"/>
     </row>
     <row r="3" ht="12" customHeight="1">
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="54"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="54"/>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="53"/>
-      <c r="AE3" s="54"/>
-      <c r="AF3" s="55"/>
-      <c r="AG3" s="49"/>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="49"/>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="60"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="58"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="59"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="52"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="58"/>
+      <c r="AB3" s="52"/>
+      <c r="AC3" s="52"/>
+      <c r="AD3" s="56"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="58"/>
+      <c r="AG3" s="52"/>
+      <c r="AH3" s="52"/>
+      <c r="AI3" s="52"/>
+      <c r="AJ3" s="52"/>
+      <c r="AK3" s="52"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="47"/>
-      <c r="C4" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="49"/>
-      <c r="Q4" s="49"/>
-      <c r="R4" s="49"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="49"/>
-      <c r="U4" s="49"/>
-      <c r="V4" s="54"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="49"/>
-      <c r="Y4" s="49"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="55"/>
-      <c r="AB4" s="49"/>
-      <c r="AC4" s="49"/>
-      <c r="AD4" s="53"/>
-      <c r="AE4" s="54"/>
-      <c r="AF4" s="55"/>
-      <c r="AG4" s="49"/>
-      <c r="AH4" s="49"/>
-      <c r="AI4" s="49"/>
-      <c r="AJ4" s="49"/>
-      <c r="AK4" s="49"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="57"/>
+      <c r="W4" s="59"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
+      <c r="Z4" s="57"/>
+      <c r="AA4" s="58"/>
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="52"/>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="57"/>
+      <c r="AF4" s="58"/>
+      <c r="AG4" s="52"/>
+      <c r="AH4" s="52"/>
+      <c r="AI4" s="52"/>
+      <c r="AJ4" s="52"/>
+      <c r="AK4" s="52"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="49"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="49"/>
-      <c r="T5" s="49"/>
-      <c r="U5" s="49"/>
-      <c r="V5" s="54"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="49"/>
-      <c r="Y5" s="49"/>
-      <c r="Z5" s="54"/>
-      <c r="AA5" s="55"/>
-      <c r="AB5" s="49"/>
-      <c r="AC5" s="49"/>
-      <c r="AD5" s="53"/>
-      <c r="AE5" s="54"/>
-      <c r="AF5" s="55"/>
-      <c r="AG5" s="49"/>
-      <c r="AH5" s="49"/>
-      <c r="AI5" s="49"/>
-      <c r="AJ5" s="49"/>
-      <c r="AK5" s="49"/>
+      <c r="B5" s="50"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="52"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="52"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="52"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="59"/>
+      <c r="X5" s="52"/>
+      <c r="Y5" s="52"/>
+      <c r="Z5" s="57"/>
+      <c r="AA5" s="58"/>
+      <c r="AB5" s="52"/>
+      <c r="AC5" s="52"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="57"/>
+      <c r="AF5" s="58"/>
+      <c r="AG5" s="52"/>
+      <c r="AH5" s="52"/>
+      <c r="AI5" s="52"/>
+      <c r="AJ5" s="52"/>
+      <c r="AK5" s="52"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="47"/>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="50"/>
+      <c r="C6" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="49"/>
-      <c r="T6" s="49"/>
-      <c r="U6" s="49"/>
-      <c r="V6" s="54"/>
-      <c r="W6" s="56"/>
-      <c r="X6" s="49"/>
-      <c r="Y6" s="49"/>
-      <c r="Z6" s="54"/>
-      <c r="AA6" s="55"/>
-      <c r="AB6" s="49"/>
-      <c r="AC6" s="49"/>
-      <c r="AD6" s="53"/>
-      <c r="AE6" s="51"/>
-      <c r="AF6" s="52"/>
-      <c r="AG6" s="63"/>
-      <c r="AH6" s="63"/>
-      <c r="AI6" s="63"/>
-      <c r="AJ6" s="63"/>
-      <c r="AK6" s="63"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="58"/>
+      <c r="P6" s="52"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
+      <c r="T6" s="52"/>
+      <c r="U6" s="52"/>
+      <c r="V6" s="57"/>
+      <c r="W6" s="59"/>
+      <c r="X6" s="52"/>
+      <c r="Y6" s="52"/>
+      <c r="Z6" s="57"/>
+      <c r="AA6" s="58"/>
+      <c r="AB6" s="52"/>
+      <c r="AC6" s="52"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="54"/>
+      <c r="AF6" s="55"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="66"/>
+      <c r="AI6" s="66"/>
+      <c r="AJ6" s="66"/>
+      <c r="AK6" s="66"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="47"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="49"/>
-      <c r="N7" s="54"/>
-      <c r="O7" s="61"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="49"/>
-      <c r="S7" s="49"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="54"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="49"/>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="54"/>
-      <c r="AA7" s="55"/>
-      <c r="AB7" s="49"/>
-      <c r="AC7" s="49"/>
-      <c r="AD7" s="53"/>
-      <c r="AE7" s="54"/>
-      <c r="AF7" s="55"/>
-      <c r="AG7" s="49"/>
-      <c r="AH7" s="49"/>
-      <c r="AI7" s="49"/>
-      <c r="AJ7" s="49"/>
-      <c r="AK7" s="49"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="64"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="52"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="57"/>
+      <c r="W7" s="59"/>
+      <c r="X7" s="52"/>
+      <c r="Y7" s="52"/>
+      <c r="Z7" s="57"/>
+      <c r="AA7" s="58"/>
+      <c r="AB7" s="52"/>
+      <c r="AC7" s="52"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="57"/>
+      <c r="AF7" s="58"/>
+      <c r="AG7" s="52"/>
+      <c r="AH7" s="52"/>
+      <c r="AI7" s="52"/>
+      <c r="AJ7" s="52"/>
+      <c r="AK7" s="52"/>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="47"/>
-      <c r="C8" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="52"/>
-      <c r="P8" s="63"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="63"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="63"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="63"/>
-      <c r="Y8" s="63"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="52"/>
-      <c r="AB8" s="63"/>
-      <c r="AC8" s="63"/>
-      <c r="AD8" s="53"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="52"/>
-      <c r="AG8" s="63"/>
-      <c r="AH8" s="63"/>
-      <c r="AI8" s="63"/>
-      <c r="AJ8" s="63"/>
-      <c r="AK8" s="63"/>
+      <c r="B8" s="50"/>
+      <c r="C8" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="66"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="55"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="66"/>
+      <c r="U8" s="66"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="59"/>
+      <c r="X8" s="66"/>
+      <c r="Y8" s="66"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="55"/>
+      <c r="AB8" s="66"/>
+      <c r="AC8" s="66"/>
+      <c r="AD8" s="56"/>
+      <c r="AE8" s="54"/>
+      <c r="AF8" s="55"/>
+      <c r="AG8" s="66"/>
+      <c r="AH8" s="66"/>
+      <c r="AI8" s="66"/>
+      <c r="AJ8" s="66"/>
+      <c r="AK8" s="66"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="47"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="62"/>
-      <c r="N9" s="54"/>
-      <c r="O9" s="61"/>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="62"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="64"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="60"/>
-      <c r="W9" s="56"/>
-      <c r="X9" s="62"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="60"/>
-      <c r="AA9" s="61"/>
-      <c r="AB9" s="49"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="62"/>
-      <c r="AE9" s="54"/>
-      <c r="AF9" s="55"/>
-      <c r="AG9" s="49"/>
-      <c r="AH9" s="49"/>
-      <c r="AI9" s="49"/>
-      <c r="AJ9" s="49"/>
-      <c r="AK9" s="49"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="57"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="52"/>
+      <c r="Q9" s="65"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="52"/>
+      <c r="V9" s="63"/>
+      <c r="W9" s="59"/>
+      <c r="X9" s="65"/>
+      <c r="Y9" s="52"/>
+      <c r="Z9" s="63"/>
+      <c r="AA9" s="64"/>
+      <c r="AB9" s="52"/>
+      <c r="AC9" s="52"/>
+      <c r="AD9" s="65"/>
+      <c r="AE9" s="57"/>
+      <c r="AF9" s="58"/>
+      <c r="AG9" s="52"/>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="52"/>
+      <c r="AK9" s="52"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="47"/>
-      <c r="C10" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="49"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49"/>
-      <c r="V10" s="51"/>
-      <c r="W10" s="56"/>
-      <c r="X10" s="63"/>
-      <c r="Y10" s="63"/>
-      <c r="Z10" s="51"/>
-      <c r="AA10" s="55"/>
-      <c r="AB10" s="49"/>
-      <c r="AC10" s="49"/>
-      <c r="AD10" s="53"/>
-      <c r="AE10" s="54"/>
-      <c r="AF10" s="55"/>
-      <c r="AG10" s="49"/>
-      <c r="AH10" s="49"/>
-      <c r="AI10" s="49"/>
-      <c r="AJ10" s="49"/>
-      <c r="AK10" s="49"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="58"/>
+      <c r="P10" s="52"/>
+      <c r="Q10" s="52"/>
+      <c r="R10" s="52"/>
+      <c r="S10" s="52"/>
+      <c r="T10" s="52"/>
+      <c r="U10" s="52"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="59"/>
+      <c r="X10" s="66"/>
+      <c r="Y10" s="66"/>
+      <c r="Z10" s="54"/>
+      <c r="AA10" s="58"/>
+      <c r="AB10" s="52"/>
+      <c r="AC10" s="52"/>
+      <c r="AD10" s="56"/>
+      <c r="AE10" s="57"/>
+      <c r="AF10" s="58"/>
+      <c r="AG10" s="52"/>
+      <c r="AH10" s="52"/>
+      <c r="AI10" s="52"/>
+      <c r="AJ10" s="52"/>
+      <c r="AK10" s="52"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="47"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="49"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="55"/>
-      <c r="P11" s="49"/>
-      <c r="Q11" s="49"/>
-      <c r="R11" s="49"/>
-      <c r="S11" s="49"/>
-      <c r="T11" s="49"/>
-      <c r="U11" s="49"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="56"/>
-      <c r="X11" s="49"/>
-      <c r="Y11" s="49"/>
-      <c r="Z11" s="54"/>
-      <c r="AA11" s="55"/>
-      <c r="AB11" s="49"/>
-      <c r="AC11" s="49"/>
-      <c r="AD11" s="65"/>
-      <c r="AE11" s="54"/>
-      <c r="AF11" s="55"/>
-      <c r="AG11" s="49"/>
-      <c r="AH11" s="49"/>
-      <c r="AI11" s="49"/>
-      <c r="AJ11" s="49"/>
-      <c r="AK11" s="49"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="52"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
+      <c r="T11" s="52"/>
+      <c r="U11" s="52"/>
+      <c r="V11" s="57"/>
+      <c r="W11" s="59"/>
+      <c r="X11" s="52"/>
+      <c r="Y11" s="52"/>
+      <c r="Z11" s="57"/>
+      <c r="AA11" s="58"/>
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="52"/>
+      <c r="AD11" s="68"/>
+      <c r="AE11" s="57"/>
+      <c r="AF11" s="58"/>
+      <c r="AG11" s="52"/>
+      <c r="AH11" s="52"/>
+      <c r="AI11" s="52"/>
+      <c r="AJ11" s="52"/>
+      <c r="AK11" s="52"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="47"/>
-      <c r="C12" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="54"/>
-      <c r="W12" s="56"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="54"/>
-      <c r="AA12" s="55"/>
-      <c r="AB12" s="49"/>
-      <c r="AC12" s="49"/>
-      <c r="AD12" s="53"/>
-      <c r="AE12" s="54"/>
-      <c r="AF12" s="52"/>
-      <c r="AG12" s="63"/>
-      <c r="AH12" s="63"/>
-      <c r="AI12" s="63"/>
-      <c r="AJ12" s="63"/>
-      <c r="AK12" s="63"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="56"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="57"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="52"/>
+      <c r="Q12" s="52"/>
+      <c r="R12" s="52"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="52"/>
+      <c r="U12" s="52"/>
+      <c r="V12" s="57"/>
+      <c r="W12" s="59"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="52"/>
+      <c r="Z12" s="57"/>
+      <c r="AA12" s="58"/>
+      <c r="AB12" s="52"/>
+      <c r="AC12" s="52"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="57"/>
+      <c r="AF12" s="55"/>
+      <c r="AG12" s="66"/>
+      <c r="AH12" s="66"/>
+      <c r="AI12" s="66"/>
+      <c r="AJ12" s="66"/>
+      <c r="AK12" s="66"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="47"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="49"/>
-      <c r="Q13" s="49"/>
-      <c r="R13" s="49"/>
-      <c r="S13" s="49"/>
-      <c r="T13" s="49"/>
-      <c r="U13" s="49"/>
-      <c r="V13" s="54"/>
-      <c r="W13" s="56"/>
-      <c r="X13" s="49"/>
-      <c r="Y13" s="49"/>
-      <c r="Z13" s="54"/>
-      <c r="AA13" s="55"/>
-      <c r="AB13" s="49"/>
-      <c r="AC13" s="49"/>
-      <c r="AD13" s="53"/>
-      <c r="AE13" s="54"/>
-      <c r="AF13" s="55"/>
-      <c r="AG13" s="49"/>
-      <c r="AH13" s="49"/>
-      <c r="AI13" s="49"/>
-      <c r="AJ13" s="49"/>
-      <c r="AK13" s="49"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="57"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="52"/>
+      <c r="Q13" s="52"/>
+      <c r="R13" s="52"/>
+      <c r="S13" s="52"/>
+      <c r="T13" s="52"/>
+      <c r="U13" s="52"/>
+      <c r="V13" s="57"/>
+      <c r="W13" s="59"/>
+      <c r="X13" s="52"/>
+      <c r="Y13" s="52"/>
+      <c r="Z13" s="57"/>
+      <c r="AA13" s="58"/>
+      <c r="AB13" s="52"/>
+      <c r="AC13" s="52"/>
+      <c r="AD13" s="56"/>
+      <c r="AE13" s="57"/>
+      <c r="AF13" s="58"/>
+      <c r="AG13" s="52"/>
+      <c r="AH13" s="52"/>
+      <c r="AI13" s="52"/>
+      <c r="AJ13" s="52"/>
+      <c r="AK13" s="52"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="66" t="s">
-        <v>148</v>
-      </c>
-      <c r="C14" s="67" t="s">
+      <c r="B14" s="69" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="69"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="70"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="69"/>
-      <c r="Q14" s="69"/>
-      <c r="R14" s="69"/>
-      <c r="S14" s="69"/>
-      <c r="T14" s="69"/>
-      <c r="U14" s="69"/>
-      <c r="V14" s="70"/>
-      <c r="W14" s="56"/>
-      <c r="X14" s="69"/>
-      <c r="Y14" s="69"/>
-      <c r="Z14" s="70"/>
-      <c r="AA14" s="68"/>
-      <c r="AB14" s="69"/>
-      <c r="AC14" s="69"/>
-      <c r="AD14" s="53"/>
-      <c r="AE14" s="70"/>
-      <c r="AF14" s="68"/>
-      <c r="AG14" s="69"/>
-      <c r="AH14" s="69"/>
-      <c r="AI14" s="69"/>
-      <c r="AJ14" s="69"/>
-      <c r="AK14" s="69"/>
+      <c r="C14" s="70" t="s">
+        <v>150</v>
+      </c>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="54"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="73"/>
+      <c r="W14" s="59"/>
+      <c r="X14" s="72"/>
+      <c r="Y14" s="72"/>
+      <c r="Z14" s="73"/>
+      <c r="AA14" s="71"/>
+      <c r="AB14" s="72"/>
+      <c r="AC14" s="72"/>
+      <c r="AD14" s="56"/>
+      <c r="AE14" s="73"/>
+      <c r="AF14" s="71"/>
+      <c r="AG14" s="72"/>
+      <c r="AH14" s="72"/>
+      <c r="AI14" s="72"/>
+      <c r="AJ14" s="72"/>
+      <c r="AK14" s="72"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="66"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="69"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="69"/>
-      <c r="Q15" s="69"/>
-      <c r="R15" s="69"/>
-      <c r="S15" s="69"/>
-      <c r="T15" s="69"/>
-      <c r="U15" s="69"/>
-      <c r="V15" s="70"/>
-      <c r="W15" s="56"/>
-      <c r="X15" s="69"/>
-      <c r="Y15" s="69"/>
-      <c r="Z15" s="70"/>
-      <c r="AA15" s="68"/>
-      <c r="AB15" s="69"/>
-      <c r="AC15" s="69"/>
-      <c r="AD15" s="53"/>
-      <c r="AE15" s="70"/>
-      <c r="AF15" s="68"/>
-      <c r="AG15" s="69"/>
-      <c r="AH15" s="69"/>
-      <c r="AI15" s="69"/>
-      <c r="AJ15" s="69"/>
-      <c r="AK15" s="69"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="71"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="72"/>
+      <c r="V15" s="73"/>
+      <c r="W15" s="59"/>
+      <c r="X15" s="72"/>
+      <c r="Y15" s="72"/>
+      <c r="Z15" s="73"/>
+      <c r="AA15" s="71"/>
+      <c r="AB15" s="72"/>
+      <c r="AC15" s="72"/>
+      <c r="AD15" s="56"/>
+      <c r="AE15" s="73"/>
+      <c r="AF15" s="71"/>
+      <c r="AG15" s="72"/>
+      <c r="AH15" s="72"/>
+      <c r="AI15" s="72"/>
+      <c r="AJ15" s="72"/>
+      <c r="AK15" s="72"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="66"/>
-      <c r="C16" s="67" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="70"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="69"/>
-      <c r="Q16" s="69"/>
-      <c r="R16" s="69"/>
-      <c r="S16" s="69"/>
-      <c r="T16" s="69"/>
-      <c r="U16" s="69"/>
-      <c r="V16" s="70"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="69"/>
-      <c r="Y16" s="69"/>
-      <c r="Z16" s="70"/>
-      <c r="AA16" s="68"/>
-      <c r="AB16" s="69"/>
-      <c r="AC16" s="69"/>
-      <c r="AD16" s="53"/>
-      <c r="AE16" s="70"/>
-      <c r="AF16" s="68"/>
-      <c r="AG16" s="69"/>
-      <c r="AH16" s="69"/>
-      <c r="AI16" s="69"/>
-      <c r="AJ16" s="69"/>
-      <c r="AK16" s="69"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="56"/>
+      <c r="M16" s="72"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="72"/>
+      <c r="V16" s="73"/>
+      <c r="W16" s="59"/>
+      <c r="X16" s="72"/>
+      <c r="Y16" s="72"/>
+      <c r="Z16" s="73"/>
+      <c r="AA16" s="71"/>
+      <c r="AB16" s="72"/>
+      <c r="AC16" s="72"/>
+      <c r="AD16" s="56"/>
+      <c r="AE16" s="73"/>
+      <c r="AF16" s="71"/>
+      <c r="AG16" s="72"/>
+      <c r="AH16" s="72"/>
+      <c r="AI16" s="72"/>
+      <c r="AJ16" s="72"/>
+      <c r="AK16" s="72"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="66"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="70"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="69"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="69"/>
-      <c r="L17" s="53"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="69"/>
-      <c r="Q17" s="69"/>
-      <c r="R17" s="69"/>
-      <c r="S17" s="69"/>
-      <c r="T17" s="69"/>
-      <c r="U17" s="69"/>
-      <c r="V17" s="70"/>
-      <c r="W17" s="56"/>
-      <c r="X17" s="69"/>
-      <c r="Y17" s="69"/>
-      <c r="Z17" s="70"/>
-      <c r="AA17" s="68"/>
-      <c r="AB17" s="69"/>
-      <c r="AC17" s="69"/>
-      <c r="AD17" s="53"/>
-      <c r="AE17" s="70"/>
-      <c r="AF17" s="68"/>
-      <c r="AG17" s="69"/>
-      <c r="AH17" s="69"/>
-      <c r="AI17" s="69"/>
-      <c r="AJ17" s="69"/>
-      <c r="AK17" s="69"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="75"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="72"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="72"/>
+      <c r="V17" s="73"/>
+      <c r="W17" s="59"/>
+      <c r="X17" s="72"/>
+      <c r="Y17" s="72"/>
+      <c r="Z17" s="73"/>
+      <c r="AA17" s="71"/>
+      <c r="AB17" s="72"/>
+      <c r="AC17" s="72"/>
+      <c r="AD17" s="56"/>
+      <c r="AE17" s="73"/>
+      <c r="AF17" s="71"/>
+      <c r="AG17" s="72"/>
+      <c r="AH17" s="72"/>
+      <c r="AI17" s="72"/>
+      <c r="AJ17" s="72"/>
+      <c r="AK17" s="72"/>
       <c r="AN17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="66"/>
-      <c r="C18" s="67" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="70"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="69"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="69"/>
-      <c r="N18" s="70"/>
-      <c r="O18" s="68"/>
-      <c r="P18" s="69"/>
-      <c r="Q18" s="69"/>
-      <c r="R18" s="69"/>
-      <c r="S18" s="69"/>
-      <c r="T18" s="69"/>
-      <c r="U18" s="69"/>
-      <c r="V18" s="70"/>
-      <c r="W18" s="56"/>
-      <c r="X18" s="69"/>
-      <c r="Y18" s="69"/>
-      <c r="Z18" s="70"/>
-      <c r="AA18" s="68"/>
-      <c r="AB18" s="69"/>
-      <c r="AC18" s="69"/>
-      <c r="AD18" s="53"/>
-      <c r="AE18" s="70"/>
-      <c r="AF18" s="68"/>
-      <c r="AG18" s="69"/>
-      <c r="AH18" s="69"/>
-      <c r="AI18" s="69"/>
-      <c r="AJ18" s="69"/>
-      <c r="AK18" s="69"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="70" t="s">
+        <v>153</v>
+      </c>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="56"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="73"/>
+      <c r="O18" s="71"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="72"/>
+      <c r="U18" s="72"/>
+      <c r="V18" s="73"/>
+      <c r="W18" s="59"/>
+      <c r="X18" s="72"/>
+      <c r="Y18" s="72"/>
+      <c r="Z18" s="73"/>
+      <c r="AA18" s="71"/>
+      <c r="AB18" s="72"/>
+      <c r="AC18" s="72"/>
+      <c r="AD18" s="56"/>
+      <c r="AE18" s="73"/>
+      <c r="AF18" s="71"/>
+      <c r="AG18" s="72"/>
+      <c r="AH18" s="72"/>
+      <c r="AI18" s="72"/>
+      <c r="AJ18" s="72"/>
+      <c r="AK18" s="72"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="66"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="70"/>
-      <c r="O19" s="68"/>
-      <c r="P19" s="69"/>
-      <c r="Q19" s="69"/>
-      <c r="R19" s="69"/>
-      <c r="S19" s="69"/>
-      <c r="T19" s="69"/>
-      <c r="U19" s="69"/>
-      <c r="V19" s="70"/>
-      <c r="W19" s="56"/>
-      <c r="X19" s="69"/>
-      <c r="Y19" s="69"/>
-      <c r="Z19" s="70"/>
-      <c r="AA19" s="68"/>
-      <c r="AB19" s="69"/>
-      <c r="AC19" s="69"/>
-      <c r="AD19" s="53"/>
-      <c r="AE19" s="70"/>
-      <c r="AF19" s="68"/>
-      <c r="AG19" s="69"/>
-      <c r="AH19" s="69"/>
-      <c r="AI19" s="69"/>
-      <c r="AJ19" s="69"/>
-      <c r="AK19" s="69"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="72"/>
+      <c r="J19" s="72"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="56"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="73"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="72"/>
+      <c r="S19" s="72"/>
+      <c r="T19" s="72"/>
+      <c r="U19" s="72"/>
+      <c r="V19" s="73"/>
+      <c r="W19" s="59"/>
+      <c r="X19" s="72"/>
+      <c r="Y19" s="72"/>
+      <c r="Z19" s="73"/>
+      <c r="AA19" s="71"/>
+      <c r="AB19" s="72"/>
+      <c r="AC19" s="72"/>
+      <c r="AD19" s="56"/>
+      <c r="AE19" s="73"/>
+      <c r="AF19" s="71"/>
+      <c r="AG19" s="72"/>
+      <c r="AH19" s="72"/>
+      <c r="AI19" s="72"/>
+      <c r="AJ19" s="72"/>
+      <c r="AK19" s="72"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="66"/>
-      <c r="C20" s="67" t="s">
-        <v>153</v>
-      </c>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="63"/>
-      <c r="J20" s="69"/>
-      <c r="K20" s="69"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="68"/>
-      <c r="P20" s="69"/>
-      <c r="Q20" s="69"/>
-      <c r="R20" s="69"/>
-      <c r="S20" s="69"/>
-      <c r="T20" s="69"/>
-      <c r="U20" s="69"/>
-      <c r="V20" s="70"/>
-      <c r="W20" s="56"/>
-      <c r="X20" s="69"/>
-      <c r="Y20" s="69"/>
-      <c r="Z20" s="70"/>
-      <c r="AA20" s="68"/>
-      <c r="AB20" s="69"/>
-      <c r="AC20" s="69"/>
-      <c r="AD20" s="53"/>
-      <c r="AE20" s="70"/>
-      <c r="AF20" s="68"/>
-      <c r="AG20" s="69"/>
-      <c r="AH20" s="69"/>
-      <c r="AI20" s="69"/>
-      <c r="AJ20" s="69"/>
-      <c r="AK20" s="69"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="70" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="72"/>
+      <c r="E20" s="72"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="72"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="56"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="73"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="72"/>
+      <c r="V20" s="73"/>
+      <c r="W20" s="59"/>
+      <c r="X20" s="72"/>
+      <c r="Y20" s="72"/>
+      <c r="Z20" s="73"/>
+      <c r="AA20" s="71"/>
+      <c r="AB20" s="72"/>
+      <c r="AC20" s="72"/>
+      <c r="AD20" s="56"/>
+      <c r="AE20" s="73"/>
+      <c r="AF20" s="71"/>
+      <c r="AG20" s="72"/>
+      <c r="AH20" s="72"/>
+      <c r="AI20" s="72"/>
+      <c r="AJ20" s="72"/>
+      <c r="AK20" s="72"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="66"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="72"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="69"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="69"/>
-      <c r="N21" s="70"/>
-      <c r="O21" s="68"/>
-      <c r="P21" s="69"/>
-      <c r="Q21" s="69"/>
-      <c r="R21" s="69"/>
-      <c r="S21" s="69"/>
-      <c r="T21" s="69"/>
-      <c r="U21" s="69"/>
-      <c r="V21" s="70"/>
-      <c r="W21" s="56"/>
-      <c r="X21" s="69"/>
-      <c r="Y21" s="69"/>
-      <c r="Z21" s="70"/>
-      <c r="AA21" s="68"/>
-      <c r="AB21" s="69"/>
-      <c r="AC21" s="69"/>
-      <c r="AD21" s="53"/>
-      <c r="AE21" s="70"/>
-      <c r="AF21" s="68"/>
-      <c r="AG21" s="69"/>
-      <c r="AH21" s="69"/>
-      <c r="AI21" s="69"/>
-      <c r="AJ21" s="69"/>
-      <c r="AK21" s="69"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="72"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="72"/>
+      <c r="K21" s="72"/>
+      <c r="L21" s="56"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="73"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="72"/>
+      <c r="V21" s="73"/>
+      <c r="W21" s="59"/>
+      <c r="X21" s="72"/>
+      <c r="Y21" s="72"/>
+      <c r="Z21" s="73"/>
+      <c r="AA21" s="71"/>
+      <c r="AB21" s="72"/>
+      <c r="AC21" s="72"/>
+      <c r="AD21" s="56"/>
+      <c r="AE21" s="73"/>
+      <c r="AF21" s="71"/>
+      <c r="AG21" s="72"/>
+      <c r="AH21" s="72"/>
+      <c r="AI21" s="72"/>
+      <c r="AJ21" s="72"/>
+      <c r="AK21" s="72"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="66"/>
-      <c r="C22" s="67" t="s">
-        <v>154</v>
-      </c>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="68"/>
-      <c r="P22" s="69"/>
-      <c r="Q22" s="69"/>
-      <c r="R22" s="69"/>
-      <c r="S22" s="69"/>
-      <c r="T22" s="69"/>
-      <c r="U22" s="69"/>
-      <c r="V22" s="70"/>
-      <c r="W22" s="56"/>
-      <c r="X22" s="69"/>
-      <c r="Y22" s="69"/>
-      <c r="Z22" s="70"/>
-      <c r="AA22" s="68"/>
-      <c r="AB22" s="69"/>
-      <c r="AC22" s="69"/>
-      <c r="AD22" s="53"/>
-      <c r="AE22" s="70"/>
-      <c r="AF22" s="68"/>
-      <c r="AG22" s="69"/>
-      <c r="AH22" s="69"/>
-      <c r="AI22" s="69"/>
-      <c r="AJ22" s="69"/>
-      <c r="AK22" s="69"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="70" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="75"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="73"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="72"/>
+      <c r="Y22" s="72"/>
+      <c r="Z22" s="73"/>
+      <c r="AA22" s="71"/>
+      <c r="AB22" s="72"/>
+      <c r="AC22" s="72"/>
+      <c r="AD22" s="56"/>
+      <c r="AE22" s="73"/>
+      <c r="AF22" s="71"/>
+      <c r="AG22" s="72"/>
+      <c r="AH22" s="72"/>
+      <c r="AI22" s="72"/>
+      <c r="AJ22" s="72"/>
+      <c r="AK22" s="72"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="66"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="72"/>
-      <c r="G23" s="70"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="68"/>
-      <c r="P23" s="69"/>
-      <c r="Q23" s="69"/>
-      <c r="R23" s="69"/>
-      <c r="S23" s="69"/>
-      <c r="T23" s="69"/>
-      <c r="U23" s="69"/>
-      <c r="V23" s="70"/>
-      <c r="W23" s="56"/>
-      <c r="X23" s="69"/>
-      <c r="Y23" s="69"/>
-      <c r="Z23" s="70"/>
-      <c r="AA23" s="68"/>
-      <c r="AB23" s="69"/>
-      <c r="AC23" s="69"/>
-      <c r="AD23" s="53"/>
-      <c r="AE23" s="70"/>
-      <c r="AF23" s="68"/>
-      <c r="AG23" s="69"/>
-      <c r="AH23" s="69"/>
-      <c r="AI23" s="69"/>
-      <c r="AJ23" s="69"/>
-      <c r="AK23" s="69"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="72"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="61"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="72"/>
+      <c r="N23" s="73"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="72"/>
+      <c r="Q23" s="72"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="72"/>
+      <c r="T23" s="72"/>
+      <c r="U23" s="72"/>
+      <c r="V23" s="73"/>
+      <c r="W23" s="59"/>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="72"/>
+      <c r="Z23" s="73"/>
+      <c r="AA23" s="71"/>
+      <c r="AB23" s="72"/>
+      <c r="AC23" s="72"/>
+      <c r="AD23" s="56"/>
+      <c r="AE23" s="73"/>
+      <c r="AF23" s="71"/>
+      <c r="AG23" s="72"/>
+      <c r="AH23" s="72"/>
+      <c r="AI23" s="72"/>
+      <c r="AJ23" s="72"/>
+      <c r="AK23" s="72"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="66"/>
-      <c r="C24" s="67" t="s">
-        <v>155</v>
-      </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="70"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="63"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="69"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="68"/>
-      <c r="P24" s="69"/>
-      <c r="Q24" s="69"/>
-      <c r="R24" s="69"/>
-      <c r="S24" s="69"/>
-      <c r="T24" s="69"/>
-      <c r="U24" s="69"/>
-      <c r="V24" s="70"/>
-      <c r="W24" s="56"/>
-      <c r="X24" s="69"/>
-      <c r="Y24" s="69"/>
-      <c r="Z24" s="70"/>
-      <c r="AA24" s="68"/>
-      <c r="AB24" s="69"/>
-      <c r="AC24" s="69"/>
-      <c r="AD24" s="53"/>
-      <c r="AE24" s="70"/>
-      <c r="AF24" s="68"/>
-      <c r="AG24" s="69"/>
-      <c r="AH24" s="69"/>
-      <c r="AI24" s="69"/>
-      <c r="AJ24" s="69"/>
-      <c r="AK24" s="69"/>
+      <c r="B24" s="69"/>
+      <c r="C24" s="70" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="72"/>
+      <c r="E24" s="72"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="66"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="73"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72"/>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="72"/>
+      <c r="V24" s="73"/>
+      <c r="W24" s="59"/>
+      <c r="X24" s="72"/>
+      <c r="Y24" s="72"/>
+      <c r="Z24" s="73"/>
+      <c r="AA24" s="71"/>
+      <c r="AB24" s="72"/>
+      <c r="AC24" s="72"/>
+      <c r="AD24" s="56"/>
+      <c r="AE24" s="73"/>
+      <c r="AF24" s="71"/>
+      <c r="AG24" s="72"/>
+      <c r="AH24" s="72"/>
+      <c r="AI24" s="72"/>
+      <c r="AJ24" s="72"/>
+      <c r="AK24" s="72"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="66"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="69"/>
-      <c r="L25" s="53"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="68"/>
-      <c r="P25" s="69"/>
-      <c r="Q25" s="69"/>
-      <c r="R25" s="69"/>
-      <c r="S25" s="69"/>
-      <c r="T25" s="69"/>
-      <c r="U25" s="69"/>
-      <c r="V25" s="70"/>
-      <c r="W25" s="56"/>
-      <c r="X25" s="69"/>
-      <c r="Y25" s="69"/>
-      <c r="Z25" s="70"/>
-      <c r="AA25" s="68"/>
-      <c r="AB25" s="69"/>
-      <c r="AC25" s="69"/>
-      <c r="AD25" s="53"/>
-      <c r="AE25" s="70"/>
-      <c r="AF25" s="68"/>
-      <c r="AG25" s="69"/>
-      <c r="AH25" s="69"/>
-      <c r="AI25" s="69"/>
-      <c r="AJ25" s="69"/>
-      <c r="AK25" s="69"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="70"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="61"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="73"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="72"/>
+      <c r="U25" s="72"/>
+      <c r="V25" s="73"/>
+      <c r="W25" s="59"/>
+      <c r="X25" s="72"/>
+      <c r="Y25" s="72"/>
+      <c r="Z25" s="73"/>
+      <c r="AA25" s="71"/>
+      <c r="AB25" s="72"/>
+      <c r="AC25" s="72"/>
+      <c r="AD25" s="56"/>
+      <c r="AE25" s="73"/>
+      <c r="AF25" s="71"/>
+      <c r="AG25" s="72"/>
+      <c r="AH25" s="72"/>
+      <c r="AI25" s="72"/>
+      <c r="AJ25" s="72"/>
+      <c r="AK25" s="72"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="47" t="s">
-        <v>156</v>
-      </c>
-      <c r="C26" s="48" t="s">
+      <c r="B26" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="54"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="54"/>
-      <c r="O26" s="55"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
-      <c r="U26" s="49"/>
-      <c r="V26" s="54"/>
-      <c r="W26" s="56"/>
-      <c r="X26" s="49"/>
-      <c r="Y26" s="49"/>
-      <c r="Z26" s="54"/>
-      <c r="AA26" s="55"/>
-      <c r="AB26" s="49"/>
-      <c r="AC26" s="49"/>
-      <c r="AD26" s="53"/>
-      <c r="AE26" s="54"/>
-      <c r="AF26" s="55"/>
-      <c r="AG26" s="49"/>
-      <c r="AH26" s="49"/>
-      <c r="AI26" s="49"/>
-      <c r="AJ26" s="49"/>
-      <c r="AK26" s="49"/>
+      <c r="C26" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="60"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="52"/>
+      <c r="Q26" s="52"/>
+      <c r="R26" s="52"/>
+      <c r="S26" s="52"/>
+      <c r="T26" s="52"/>
+      <c r="U26" s="52"/>
+      <c r="V26" s="57"/>
+      <c r="W26" s="59"/>
+      <c r="X26" s="52"/>
+      <c r="Y26" s="52"/>
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="58"/>
+      <c r="AB26" s="52"/>
+      <c r="AC26" s="52"/>
+      <c r="AD26" s="56"/>
+      <c r="AE26" s="57"/>
+      <c r="AF26" s="58"/>
+      <c r="AG26" s="52"/>
+      <c r="AH26" s="52"/>
+      <c r="AI26" s="52"/>
+      <c r="AJ26" s="52"/>
+      <c r="AK26" s="52"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="47"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="53"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="49"/>
-      <c r="R27" s="49"/>
-      <c r="S27" s="49"/>
-      <c r="T27" s="49"/>
-      <c r="U27" s="49"/>
-      <c r="V27" s="54"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="49"/>
-      <c r="Y27" s="49"/>
-      <c r="Z27" s="54"/>
-      <c r="AA27" s="55"/>
-      <c r="AB27" s="49"/>
-      <c r="AC27" s="49"/>
-      <c r="AD27" s="53"/>
-      <c r="AE27" s="54"/>
-      <c r="AF27" s="55"/>
-      <c r="AG27" s="49"/>
-      <c r="AH27" s="49"/>
-      <c r="AI27" s="49"/>
-      <c r="AJ27" s="49"/>
-      <c r="AK27" s="49"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="64"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="52"/>
+      <c r="R27" s="52"/>
+      <c r="S27" s="52"/>
+      <c r="T27" s="52"/>
+      <c r="U27" s="52"/>
+      <c r="V27" s="57"/>
+      <c r="W27" s="59"/>
+      <c r="X27" s="52"/>
+      <c r="Y27" s="52"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="58"/>
+      <c r="AB27" s="52"/>
+      <c r="AC27" s="52"/>
+      <c r="AD27" s="56"/>
+      <c r="AE27" s="57"/>
+      <c r="AF27" s="58"/>
+      <c r="AG27" s="52"/>
+      <c r="AH27" s="52"/>
+      <c r="AI27" s="52"/>
+      <c r="AJ27" s="52"/>
+      <c r="AK27" s="52"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="47"/>
-      <c r="C28" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="53"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="54"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="49"/>
-      <c r="T28" s="49"/>
-      <c r="U28" s="49"/>
-      <c r="V28" s="54"/>
-      <c r="W28" s="56"/>
-      <c r="X28" s="49"/>
-      <c r="Y28" s="49"/>
-      <c r="Z28" s="54"/>
-      <c r="AA28" s="55"/>
-      <c r="AB28" s="49"/>
-      <c r="AC28" s="49"/>
-      <c r="AD28" s="53"/>
-      <c r="AE28" s="54"/>
-      <c r="AF28" s="55"/>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="60"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="57"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="52"/>
+      <c r="R28" s="52"/>
+      <c r="S28" s="52"/>
+      <c r="T28" s="52"/>
+      <c r="U28" s="52"/>
+      <c r="V28" s="57"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="52"/>
+      <c r="Y28" s="52"/>
+      <c r="Z28" s="57"/>
+      <c r="AA28" s="58"/>
+      <c r="AB28" s="52"/>
+      <c r="AC28" s="52"/>
+      <c r="AD28" s="56"/>
+      <c r="AE28" s="57"/>
+      <c r="AF28" s="58"/>
+      <c r="AG28" s="52"/>
+      <c r="AH28" s="52"/>
+      <c r="AI28" s="52"/>
+      <c r="AJ28" s="52"/>
+      <c r="AK28" s="52"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="64"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="53"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="55"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="49"/>
-      <c r="R29" s="49"/>
-      <c r="S29" s="49"/>
-      <c r="T29" s="49"/>
-      <c r="U29" s="49"/>
-      <c r="V29" s="54"/>
-      <c r="W29" s="56"/>
-      <c r="X29" s="49"/>
-      <c r="Y29" s="49"/>
-      <c r="Z29" s="54"/>
-      <c r="AA29" s="55"/>
-      <c r="AB29" s="49"/>
-      <c r="AC29" s="49"/>
-      <c r="AD29" s="53"/>
-      <c r="AE29" s="54"/>
-      <c r="AF29" s="55"/>
-      <c r="AG29" s="49"/>
-      <c r="AH29" s="49"/>
-      <c r="AI29" s="49"/>
-      <c r="AJ29" s="49"/>
-      <c r="AK29" s="49"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="52"/>
+      <c r="Q29" s="52"/>
+      <c r="R29" s="52"/>
+      <c r="S29" s="52"/>
+      <c r="T29" s="52"/>
+      <c r="U29" s="52"/>
+      <c r="V29" s="57"/>
+      <c r="W29" s="59"/>
+      <c r="X29" s="52"/>
+      <c r="Y29" s="52"/>
+      <c r="Z29" s="57"/>
+      <c r="AA29" s="58"/>
+      <c r="AB29" s="52"/>
+      <c r="AC29" s="52"/>
+      <c r="AD29" s="56"/>
+      <c r="AE29" s="57"/>
+      <c r="AF29" s="58"/>
+      <c r="AG29" s="52"/>
+      <c r="AH29" s="52"/>
+      <c r="AI29" s="52"/>
+      <c r="AJ29" s="52"/>
+      <c r="AK29" s="52"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="47"/>
-      <c r="C30" s="48" t="s">
-        <v>159</v>
-      </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="63"/>
-      <c r="K30" s="63"/>
-      <c r="L30" s="53"/>
-      <c r="M30" s="63"/>
-      <c r="N30" s="54"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="49"/>
-      <c r="R30" s="49"/>
-      <c r="S30" s="49"/>
-      <c r="T30" s="49"/>
-      <c r="U30" s="49"/>
-      <c r="V30" s="54"/>
-      <c r="W30" s="56"/>
-      <c r="X30" s="49"/>
-      <c r="Y30" s="49"/>
-      <c r="Z30" s="54"/>
-      <c r="AA30" s="55"/>
-      <c r="AB30" s="49"/>
-      <c r="AC30" s="49"/>
-      <c r="AD30" s="53"/>
-      <c r="AE30" s="54"/>
-      <c r="AF30" s="55"/>
-      <c r="AG30" s="49"/>
-      <c r="AH30" s="49"/>
-      <c r="AI30" s="49"/>
-      <c r="AJ30" s="49"/>
-      <c r="AK30" s="49"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="52"/>
+      <c r="R30" s="52"/>
+      <c r="S30" s="52"/>
+      <c r="T30" s="52"/>
+      <c r="U30" s="52"/>
+      <c r="V30" s="57"/>
+      <c r="W30" s="59"/>
+      <c r="X30" s="52"/>
+      <c r="Y30" s="52"/>
+      <c r="Z30" s="57"/>
+      <c r="AA30" s="58"/>
+      <c r="AB30" s="52"/>
+      <c r="AC30" s="52"/>
+      <c r="AD30" s="56"/>
+      <c r="AE30" s="57"/>
+      <c r="AF30" s="58"/>
+      <c r="AG30" s="52"/>
+      <c r="AH30" s="52"/>
+      <c r="AI30" s="52"/>
+      <c r="AJ30" s="52"/>
+      <c r="AK30" s="52"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="47"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="60"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="74"/>
-      <c r="M31" s="49"/>
-      <c r="N31" s="60"/>
-      <c r="O31" s="55"/>
-      <c r="P31" s="49"/>
-      <c r="Q31" s="49"/>
-      <c r="R31" s="49"/>
-      <c r="S31" s="49"/>
-      <c r="T31" s="49"/>
-      <c r="U31" s="49"/>
-      <c r="V31" s="54"/>
-      <c r="W31" s="56"/>
-      <c r="X31" s="49"/>
-      <c r="Y31" s="49"/>
-      <c r="Z31" s="54"/>
-      <c r="AA31" s="55"/>
-      <c r="AB31" s="49"/>
-      <c r="AC31" s="49"/>
-      <c r="AD31" s="53"/>
-      <c r="AE31" s="54"/>
-      <c r="AF31" s="55"/>
-      <c r="AG31" s="49"/>
-      <c r="AH31" s="49"/>
-      <c r="AI31" s="49"/>
-      <c r="AJ31" s="49"/>
-      <c r="AK31" s="49"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="64"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="77"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="52"/>
+      <c r="Q31" s="52"/>
+      <c r="R31" s="52"/>
+      <c r="S31" s="52"/>
+      <c r="T31" s="52"/>
+      <c r="U31" s="52"/>
+      <c r="V31" s="57"/>
+      <c r="W31" s="59"/>
+      <c r="X31" s="52"/>
+      <c r="Y31" s="52"/>
+      <c r="Z31" s="57"/>
+      <c r="AA31" s="58"/>
+      <c r="AB31" s="52"/>
+      <c r="AC31" s="52"/>
+      <c r="AD31" s="56"/>
+      <c r="AE31" s="57"/>
+      <c r="AF31" s="58"/>
+      <c r="AG31" s="52"/>
+      <c r="AH31" s="52"/>
+      <c r="AI31" s="52"/>
+      <c r="AJ31" s="52"/>
+      <c r="AK31" s="52"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="47"/>
-      <c r="C32" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="54"/>
-      <c r="H32" s="55"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="53"/>
-      <c r="M32" s="63"/>
-      <c r="N32" s="51"/>
-      <c r="O32" s="55"/>
-      <c r="P32" s="49"/>
-      <c r="Q32" s="49"/>
-      <c r="R32" s="49"/>
-      <c r="S32" s="49"/>
-      <c r="T32" s="49"/>
-      <c r="U32" s="49"/>
-      <c r="V32" s="54"/>
-      <c r="W32" s="56"/>
-      <c r="X32" s="49"/>
-      <c r="Y32" s="49"/>
-      <c r="Z32" s="54"/>
-      <c r="AA32" s="55"/>
-      <c r="AB32" s="49"/>
-      <c r="AC32" s="49"/>
-      <c r="AD32" s="53"/>
-      <c r="AE32" s="54"/>
-      <c r="AF32" s="55"/>
-      <c r="AG32" s="49"/>
-      <c r="AH32" s="49"/>
-      <c r="AI32" s="49"/>
-      <c r="AJ32" s="49"/>
-      <c r="AK32" s="49"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="66"/>
+      <c r="N32" s="54"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="52"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="52"/>
+      <c r="T32" s="52"/>
+      <c r="U32" s="52"/>
+      <c r="V32" s="57"/>
+      <c r="W32" s="59"/>
+      <c r="X32" s="52"/>
+      <c r="Y32" s="52"/>
+      <c r="Z32" s="57"/>
+      <c r="AA32" s="58"/>
+      <c r="AB32" s="52"/>
+      <c r="AC32" s="52"/>
+      <c r="AD32" s="56"/>
+      <c r="AE32" s="57"/>
+      <c r="AF32" s="58"/>
+      <c r="AG32" s="52"/>
+      <c r="AH32" s="52"/>
+      <c r="AI32" s="52"/>
+      <c r="AJ32" s="52"/>
+      <c r="AK32" s="52"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="47"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="55"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49"/>
-      <c r="L33" s="53"/>
-      <c r="M33" s="49"/>
-      <c r="N33" s="60"/>
-      <c r="O33" s="55"/>
-      <c r="P33" s="49"/>
-      <c r="Q33" s="49"/>
-      <c r="R33" s="49"/>
-      <c r="S33" s="49"/>
-      <c r="T33" s="49"/>
-      <c r="U33" s="49"/>
-      <c r="V33" s="54"/>
-      <c r="W33" s="56"/>
-      <c r="X33" s="49"/>
-      <c r="Y33" s="49"/>
-      <c r="Z33" s="54"/>
-      <c r="AA33" s="55"/>
-      <c r="AB33" s="49"/>
-      <c r="AC33" s="49"/>
-      <c r="AD33" s="53"/>
-      <c r="AE33" s="54"/>
-      <c r="AF33" s="55"/>
-      <c r="AG33" s="49"/>
-      <c r="AH33" s="49"/>
-      <c r="AI33" s="49"/>
-      <c r="AJ33" s="49"/>
-      <c r="AK33" s="49"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="63"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="52"/>
+      <c r="Q33" s="52"/>
+      <c r="R33" s="52"/>
+      <c r="S33" s="52"/>
+      <c r="T33" s="52"/>
+      <c r="U33" s="52"/>
+      <c r="V33" s="57"/>
+      <c r="W33" s="59"/>
+      <c r="X33" s="52"/>
+      <c r="Y33" s="52"/>
+      <c r="Z33" s="57"/>
+      <c r="AA33" s="58"/>
+      <c r="AB33" s="52"/>
+      <c r="AC33" s="52"/>
+      <c r="AD33" s="56"/>
+      <c r="AE33" s="57"/>
+      <c r="AF33" s="58"/>
+      <c r="AG33" s="52"/>
+      <c r="AH33" s="52"/>
+      <c r="AI33" s="52"/>
+      <c r="AJ33" s="52"/>
+      <c r="AK33" s="52"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="66" t="s">
-        <v>161</v>
-      </c>
-      <c r="C34" s="75" t="s">
+      <c r="B34" s="69" t="s">
         <v>162</v>
       </c>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="68"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="63"/>
-      <c r="N34" s="51"/>
-      <c r="O34" s="52"/>
-      <c r="P34" s="63"/>
-      <c r="Q34" s="63"/>
-      <c r="R34" s="63"/>
-      <c r="S34" s="69"/>
-      <c r="T34" s="69"/>
-      <c r="U34" s="69"/>
-      <c r="V34" s="70"/>
-      <c r="W34" s="56"/>
-      <c r="X34" s="69"/>
-      <c r="Y34" s="69"/>
-      <c r="Z34" s="70"/>
-      <c r="AA34" s="68"/>
-      <c r="AB34" s="69"/>
-      <c r="AC34" s="69"/>
-      <c r="AD34" s="53"/>
-      <c r="AE34" s="70"/>
-      <c r="AF34" s="68"/>
-      <c r="AG34" s="69"/>
-      <c r="AH34" s="69"/>
-      <c r="AI34" s="69"/>
-      <c r="AJ34" s="69"/>
-      <c r="AK34" s="69"/>
+      <c r="C34" s="78" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="66"/>
+      <c r="N34" s="54"/>
+      <c r="O34" s="55"/>
+      <c r="P34" s="66"/>
+      <c r="Q34" s="66"/>
+      <c r="R34" s="66"/>
+      <c r="S34" s="72"/>
+      <c r="T34" s="72"/>
+      <c r="U34" s="72"/>
+      <c r="V34" s="73"/>
+      <c r="W34" s="59"/>
+      <c r="X34" s="72"/>
+      <c r="Y34" s="72"/>
+      <c r="Z34" s="73"/>
+      <c r="AA34" s="71"/>
+      <c r="AB34" s="72"/>
+      <c r="AC34" s="72"/>
+      <c r="AD34" s="56"/>
+      <c r="AE34" s="73"/>
+      <c r="AF34" s="71"/>
+      <c r="AG34" s="72"/>
+      <c r="AH34" s="72"/>
+      <c r="AI34" s="72"/>
+      <c r="AJ34" s="72"/>
+      <c r="AK34" s="72"/>
     </row>
     <row r="35" ht="12" customHeight="1">
-      <c r="B35" s="66"/>
-      <c r="C35" s="75"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="68"/>
-      <c r="I35" s="69"/>
-      <c r="J35" s="69"/>
-      <c r="K35" s="76"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="69"/>
-      <c r="N35" s="60"/>
-      <c r="O35" s="68"/>
-      <c r="P35" s="62"/>
-      <c r="Q35" s="69"/>
-      <c r="R35" s="77"/>
-      <c r="S35" s="77"/>
-      <c r="T35" s="58"/>
-      <c r="U35" s="69"/>
-      <c r="V35" s="70"/>
-      <c r="W35" s="56"/>
-      <c r="X35" s="69"/>
-      <c r="Y35" s="69"/>
-      <c r="Z35" s="70"/>
-      <c r="AA35" s="68"/>
-      <c r="AB35" s="69"/>
-      <c r="AC35" s="69"/>
-      <c r="AD35" s="53"/>
-      <c r="AE35" s="70"/>
-      <c r="AF35" s="68"/>
-      <c r="AG35" s="69"/>
-      <c r="AH35" s="69"/>
-      <c r="AI35" s="69"/>
-      <c r="AJ35" s="69"/>
-      <c r="AK35" s="69"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="72"/>
+      <c r="J35" s="72"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="72"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="65"/>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="80"/>
+      <c r="S35" s="80"/>
+      <c r="T35" s="61"/>
+      <c r="U35" s="72"/>
+      <c r="V35" s="73"/>
+      <c r="W35" s="59"/>
+      <c r="X35" s="72"/>
+      <c r="Y35" s="72"/>
+      <c r="Z35" s="73"/>
+      <c r="AA35" s="71"/>
+      <c r="AB35" s="72"/>
+      <c r="AC35" s="72"/>
+      <c r="AD35" s="56"/>
+      <c r="AE35" s="73"/>
+      <c r="AF35" s="71"/>
+      <c r="AG35" s="72"/>
+      <c r="AH35" s="72"/>
+      <c r="AI35" s="72"/>
+      <c r="AJ35" s="72"/>
+      <c r="AK35" s="72"/>
     </row>
     <row r="36" ht="12" customHeight="1">
-      <c r="B36" s="66"/>
-      <c r="C36" s="75" t="s">
-        <v>163</v>
-      </c>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="69"/>
-      <c r="K36" s="69"/>
-      <c r="L36" s="53"/>
-      <c r="M36" s="63"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="63"/>
-      <c r="Q36" s="69"/>
-      <c r="R36" s="69"/>
-      <c r="S36" s="69"/>
-      <c r="T36" s="69"/>
-      <c r="U36" s="69"/>
-      <c r="V36" s="70"/>
-      <c r="W36" s="56"/>
-      <c r="X36" s="69"/>
-      <c r="Y36" s="69"/>
-      <c r="Z36" s="70"/>
-      <c r="AA36" s="68"/>
-      <c r="AB36" s="69"/>
-      <c r="AC36" s="69"/>
-      <c r="AD36" s="53"/>
-      <c r="AE36" s="70"/>
-      <c r="AF36" s="68"/>
-      <c r="AG36" s="69"/>
-      <c r="AH36" s="69"/>
-      <c r="AI36" s="69"/>
-      <c r="AJ36" s="69"/>
-      <c r="AK36" s="69"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="78" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="72"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="66"/>
+      <c r="N36" s="54"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="66"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="72"/>
+      <c r="T36" s="72"/>
+      <c r="U36" s="72"/>
+      <c r="V36" s="73"/>
+      <c r="W36" s="59"/>
+      <c r="X36" s="72"/>
+      <c r="Y36" s="72"/>
+      <c r="Z36" s="73"/>
+      <c r="AA36" s="71"/>
+      <c r="AB36" s="72"/>
+      <c r="AC36" s="72"/>
+      <c r="AD36" s="56"/>
+      <c r="AE36" s="73"/>
+      <c r="AF36" s="71"/>
+      <c r="AG36" s="72"/>
+      <c r="AH36" s="72"/>
+      <c r="AI36" s="72"/>
+      <c r="AJ36" s="72"/>
+      <c r="AK36" s="72"/>
     </row>
     <row r="37" ht="12" customHeight="1">
-      <c r="B37" s="66"/>
-      <c r="C37" s="75"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="68"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="76"/>
-      <c r="L37" s="53"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="70"/>
-      <c r="O37" s="68"/>
-      <c r="P37" s="62"/>
-      <c r="Q37" s="69"/>
-      <c r="R37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="58"/>
-      <c r="U37" s="69"/>
-      <c r="V37" s="70"/>
-      <c r="W37" s="56"/>
-      <c r="X37" s="69"/>
-      <c r="Y37" s="69"/>
-      <c r="Z37" s="70"/>
-      <c r="AA37" s="68"/>
-      <c r="AB37" s="69"/>
-      <c r="AC37" s="69"/>
-      <c r="AD37" s="53"/>
-      <c r="AE37" s="70"/>
-      <c r="AF37" s="68"/>
-      <c r="AG37" s="69"/>
-      <c r="AH37" s="69"/>
-      <c r="AI37" s="69"/>
-      <c r="AJ37" s="69"/>
-      <c r="AK37" s="69"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="78"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="72"/>
+      <c r="J37" s="72"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="73"/>
+      <c r="O37" s="71"/>
+      <c r="P37" s="65"/>
+      <c r="Q37" s="72"/>
+      <c r="R37" s="80"/>
+      <c r="S37" s="80"/>
+      <c r="T37" s="61"/>
+      <c r="U37" s="72"/>
+      <c r="V37" s="73"/>
+      <c r="W37" s="59"/>
+      <c r="X37" s="72"/>
+      <c r="Y37" s="72"/>
+      <c r="Z37" s="73"/>
+      <c r="AA37" s="71"/>
+      <c r="AB37" s="72"/>
+      <c r="AC37" s="72"/>
+      <c r="AD37" s="56"/>
+      <c r="AE37" s="73"/>
+      <c r="AF37" s="71"/>
+      <c r="AG37" s="72"/>
+      <c r="AH37" s="72"/>
+      <c r="AI37" s="72"/>
+      <c r="AJ37" s="72"/>
+      <c r="AK37" s="72"/>
     </row>
     <row r="38" ht="12" customHeight="1">
-      <c r="B38" s="66"/>
-      <c r="C38" s="75" t="s">
-        <v>164</v>
-      </c>
-      <c r="D38" s="69"/>
-      <c r="E38" s="69"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="69"/>
-      <c r="K38" s="69"/>
-      <c r="L38" s="53"/>
-      <c r="M38" s="69"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="52"/>
-      <c r="P38" s="63"/>
-      <c r="Q38" s="63"/>
-      <c r="R38" s="63"/>
-      <c r="S38" s="63"/>
-      <c r="T38" s="63"/>
-      <c r="U38" s="63"/>
-      <c r="V38" s="51"/>
-      <c r="W38" s="56"/>
-      <c r="X38" s="63"/>
-      <c r="Y38" s="63"/>
-      <c r="Z38" s="70"/>
-      <c r="AA38" s="68"/>
-      <c r="AB38" s="69"/>
-      <c r="AC38" s="69"/>
-      <c r="AD38" s="53"/>
-      <c r="AE38" s="70"/>
-      <c r="AF38" s="68"/>
-      <c r="AG38" s="69"/>
-      <c r="AH38" s="69"/>
-      <c r="AI38" s="69"/>
-      <c r="AJ38" s="69"/>
-      <c r="AK38" s="69"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="78" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="73"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="72"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="73"/>
+      <c r="O38" s="55"/>
+      <c r="P38" s="66"/>
+      <c r="Q38" s="66"/>
+      <c r="R38" s="66"/>
+      <c r="S38" s="66"/>
+      <c r="T38" s="66"/>
+      <c r="U38" s="66"/>
+      <c r="V38" s="54"/>
+      <c r="W38" s="59"/>
+      <c r="X38" s="66"/>
+      <c r="Y38" s="66"/>
+      <c r="Z38" s="73"/>
+      <c r="AA38" s="71"/>
+      <c r="AB38" s="72"/>
+      <c r="AC38" s="72"/>
+      <c r="AD38" s="56"/>
+      <c r="AE38" s="73"/>
+      <c r="AF38" s="71"/>
+      <c r="AG38" s="72"/>
+      <c r="AH38" s="72"/>
+      <c r="AI38" s="72"/>
+      <c r="AJ38" s="72"/>
+      <c r="AK38" s="72"/>
     </row>
     <row r="39" ht="12" customHeight="1">
-      <c r="B39" s="66"/>
-      <c r="C39" s="75"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="72"/>
-      <c r="G39" s="70"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="69"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="69"/>
-      <c r="N39" s="70"/>
-      <c r="O39" s="68"/>
-      <c r="P39" s="69"/>
-      <c r="Q39" s="69"/>
-      <c r="R39" s="76"/>
-      <c r="S39" s="76"/>
-      <c r="T39" s="69"/>
-      <c r="U39" s="69"/>
-      <c r="V39" s="70"/>
-      <c r="W39" s="56"/>
-      <c r="X39" s="69"/>
-      <c r="Y39" s="69"/>
-      <c r="Z39" s="70"/>
-      <c r="AA39" s="68"/>
-      <c r="AB39" s="69"/>
-      <c r="AC39" s="69"/>
-      <c r="AD39" s="53"/>
-      <c r="AE39" s="70"/>
-      <c r="AF39" s="68"/>
-      <c r="AG39" s="69"/>
-      <c r="AH39" s="69"/>
-      <c r="AI39" s="69"/>
-      <c r="AJ39" s="69"/>
-      <c r="AK39" s="69"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="72"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="72"/>
+      <c r="J39" s="72"/>
+      <c r="K39" s="72"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="72"/>
+      <c r="N39" s="73"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="79"/>
+      <c r="S39" s="79"/>
+      <c r="T39" s="72"/>
+      <c r="U39" s="72"/>
+      <c r="V39" s="73"/>
+      <c r="W39" s="59"/>
+      <c r="X39" s="72"/>
+      <c r="Y39" s="72"/>
+      <c r="Z39" s="73"/>
+      <c r="AA39" s="71"/>
+      <c r="AB39" s="72"/>
+      <c r="AC39" s="72"/>
+      <c r="AD39" s="56"/>
+      <c r="AE39" s="73"/>
+      <c r="AF39" s="71"/>
+      <c r="AG39" s="72"/>
+      <c r="AH39" s="72"/>
+      <c r="AI39" s="72"/>
+      <c r="AJ39" s="72"/>
+      <c r="AK39" s="72"/>
     </row>
     <row r="40" ht="12" customHeight="1">
-      <c r="B40" s="66"/>
-      <c r="C40" s="75" t="s">
-        <v>165</v>
-      </c>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="70"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="69"/>
-      <c r="L40" s="53"/>
-      <c r="M40" s="69"/>
-      <c r="N40" s="70"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="69"/>
-      <c r="Q40" s="69"/>
-      <c r="R40" s="63"/>
-      <c r="S40" s="63"/>
-      <c r="T40" s="63"/>
-      <c r="U40" s="63"/>
-      <c r="V40" s="51"/>
-      <c r="W40" s="56"/>
-      <c r="X40" s="63"/>
-      <c r="Y40" s="63"/>
-      <c r="Z40" s="51"/>
-      <c r="AA40" s="52"/>
-      <c r="AB40" s="63"/>
-      <c r="AC40" s="63"/>
-      <c r="AD40" s="53"/>
-      <c r="AE40" s="70"/>
-      <c r="AF40" s="68"/>
-      <c r="AG40" s="69"/>
-      <c r="AH40" s="69"/>
-      <c r="AI40" s="69"/>
-      <c r="AJ40" s="69"/>
-      <c r="AK40" s="69"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="78" t="s">
+        <v>166</v>
+      </c>
+      <c r="D40" s="72"/>
+      <c r="E40" s="72"/>
+      <c r="F40" s="75"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="72"/>
+      <c r="J40" s="72"/>
+      <c r="K40" s="72"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="72"/>
+      <c r="N40" s="73"/>
+      <c r="O40" s="71"/>
+      <c r="P40" s="72"/>
+      <c r="Q40" s="72"/>
+      <c r="R40" s="66"/>
+      <c r="S40" s="66"/>
+      <c r="T40" s="66"/>
+      <c r="U40" s="66"/>
+      <c r="V40" s="54"/>
+      <c r="W40" s="59"/>
+      <c r="X40" s="66"/>
+      <c r="Y40" s="66"/>
+      <c r="Z40" s="54"/>
+      <c r="AA40" s="55"/>
+      <c r="AB40" s="66"/>
+      <c r="AC40" s="66"/>
+      <c r="AD40" s="56"/>
+      <c r="AE40" s="73"/>
+      <c r="AF40" s="71"/>
+      <c r="AG40" s="72"/>
+      <c r="AH40" s="72"/>
+      <c r="AI40" s="72"/>
+      <c r="AJ40" s="72"/>
+      <c r="AK40" s="72"/>
     </row>
     <row r="41" ht="12" customHeight="1">
-      <c r="B41" s="66"/>
-      <c r="C41" s="75"/>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="72"/>
-      <c r="G41" s="70"/>
-      <c r="H41" s="68"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="53"/>
-      <c r="M41" s="69"/>
-      <c r="N41" s="70"/>
-      <c r="O41" s="68"/>
-      <c r="P41" s="69"/>
-      <c r="Q41" s="62"/>
-      <c r="R41" s="76"/>
-      <c r="S41" s="76"/>
-      <c r="T41" s="62"/>
-      <c r="U41" s="69"/>
-      <c r="V41" s="70"/>
-      <c r="W41" s="56"/>
-      <c r="X41" s="69"/>
-      <c r="Y41" s="69"/>
-      <c r="Z41" s="70"/>
-      <c r="AA41" s="68"/>
-      <c r="AB41" s="69"/>
-      <c r="AC41" s="69"/>
-      <c r="AD41" s="53"/>
-      <c r="AE41" s="70"/>
-      <c r="AF41" s="68"/>
-      <c r="AG41" s="69"/>
-      <c r="AH41" s="69"/>
-      <c r="AI41" s="69"/>
-      <c r="AJ41" s="69"/>
-      <c r="AK41" s="69"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="72"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="72"/>
+      <c r="K41" s="72"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="72"/>
+      <c r="N41" s="73"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="72"/>
+      <c r="Q41" s="65"/>
+      <c r="R41" s="79"/>
+      <c r="S41" s="79"/>
+      <c r="T41" s="65"/>
+      <c r="U41" s="72"/>
+      <c r="V41" s="73"/>
+      <c r="W41" s="59"/>
+      <c r="X41" s="72"/>
+      <c r="Y41" s="72"/>
+      <c r="Z41" s="73"/>
+      <c r="AA41" s="71"/>
+      <c r="AB41" s="72"/>
+      <c r="AC41" s="72"/>
+      <c r="AD41" s="56"/>
+      <c r="AE41" s="73"/>
+      <c r="AF41" s="71"/>
+      <c r="AG41" s="72"/>
+      <c r="AH41" s="72"/>
+      <c r="AI41" s="72"/>
+      <c r="AJ41" s="72"/>
+      <c r="AK41" s="72"/>
     </row>
     <row r="42" ht="12" customHeight="1">
-      <c r="B42" s="47" t="s">
+      <c r="B42" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="78" t="s">
-        <v>166</v>
-      </c>
-      <c r="D42" s="49"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="54"/>
-      <c r="H42" s="55"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
-      <c r="K42" s="49"/>
-      <c r="L42" s="53"/>
-      <c r="M42" s="49"/>
-      <c r="N42" s="54"/>
-      <c r="O42" s="55"/>
-      <c r="P42" s="63"/>
-      <c r="Q42" s="63"/>
-      <c r="R42" s="49"/>
-      <c r="S42" s="49"/>
-      <c r="T42" s="62"/>
-      <c r="U42" s="49"/>
-      <c r="V42" s="51"/>
-      <c r="W42" s="56"/>
-      <c r="X42" s="63"/>
-      <c r="Y42" s="63"/>
-      <c r="Z42" s="51"/>
-      <c r="AA42" s="52"/>
-      <c r="AB42" s="63"/>
-      <c r="AC42" s="63"/>
-      <c r="AD42" s="53"/>
-      <c r="AE42" s="54"/>
-      <c r="AF42" s="55"/>
-      <c r="AG42" s="49"/>
-      <c r="AH42" s="49"/>
-      <c r="AI42" s="49"/>
-      <c r="AJ42" s="49"/>
-      <c r="AK42" s="49"/>
+      <c r="C42" s="81" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="57"/>
+      <c r="O42" s="58"/>
+      <c r="P42" s="66"/>
+      <c r="Q42" s="66"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="52"/>
+      <c r="T42" s="65"/>
+      <c r="U42" s="52"/>
+      <c r="V42" s="54"/>
+      <c r="W42" s="59"/>
+      <c r="X42" s="66"/>
+      <c r="Y42" s="66"/>
+      <c r="Z42" s="54"/>
+      <c r="AA42" s="55"/>
+      <c r="AB42" s="66"/>
+      <c r="AC42" s="66"/>
+      <c r="AD42" s="56"/>
+      <c r="AE42" s="57"/>
+      <c r="AF42" s="58"/>
+      <c r="AG42" s="52"/>
+      <c r="AH42" s="52"/>
+      <c r="AI42" s="52"/>
+      <c r="AJ42" s="52"/>
+      <c r="AK42" s="52"/>
     </row>
     <row r="43" ht="12" customHeight="1">
-      <c r="B43" s="47"/>
-      <c r="C43" s="78"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="49"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="54"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="K43" s="49"/>
-      <c r="L43" s="53"/>
-      <c r="M43" s="49"/>
-      <c r="N43" s="54"/>
-      <c r="O43" s="55"/>
-      <c r="P43" s="49"/>
-      <c r="Q43" s="62"/>
-      <c r="R43" s="49"/>
-      <c r="S43" s="64"/>
-      <c r="T43" s="49"/>
-      <c r="U43" s="49"/>
-      <c r="V43" s="54"/>
-      <c r="W43" s="56"/>
-      <c r="X43" s="49"/>
-      <c r="Y43" s="49"/>
-      <c r="Z43" s="54"/>
-      <c r="AA43" s="55"/>
-      <c r="AB43" s="49"/>
-      <c r="AC43" s="49"/>
-      <c r="AD43" s="53"/>
-      <c r="AE43" s="54"/>
-      <c r="AF43" s="55"/>
-      <c r="AG43" s="49"/>
-      <c r="AH43" s="58"/>
-      <c r="AI43" s="58"/>
-      <c r="AJ43" s="49"/>
-      <c r="AK43" s="49"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
+      <c r="K43" s="52"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="52"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="58"/>
+      <c r="P43" s="52"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="67"/>
+      <c r="T43" s="52"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="57"/>
+      <c r="W43" s="59"/>
+      <c r="X43" s="52"/>
+      <c r="Y43" s="52"/>
+      <c r="Z43" s="57"/>
+      <c r="AA43" s="58"/>
+      <c r="AB43" s="52"/>
+      <c r="AC43" s="52"/>
+      <c r="AD43" s="56"/>
+      <c r="AE43" s="57"/>
+      <c r="AF43" s="58"/>
+      <c r="AG43" s="52"/>
+      <c r="AH43" s="61"/>
+      <c r="AI43" s="61"/>
+      <c r="AJ43" s="52"/>
+      <c r="AK43" s="52"/>
     </row>
     <row r="44" ht="12" customHeight="1">
-      <c r="B44" s="47"/>
-      <c r="C44" s="78" t="s">
-        <v>167</v>
-      </c>
-      <c r="D44" s="49"/>
-      <c r="E44" s="49"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="54"/>
-      <c r="H44" s="55"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="K44" s="49"/>
-      <c r="L44" s="53"/>
-      <c r="M44" s="49"/>
-      <c r="N44" s="54"/>
-      <c r="O44" s="55"/>
-      <c r="P44" s="63"/>
-      <c r="Q44" s="63"/>
-      <c r="R44" s="49"/>
-      <c r="S44" s="49"/>
-      <c r="T44" s="49"/>
-      <c r="U44" s="49"/>
-      <c r="V44" s="54"/>
-      <c r="W44" s="56"/>
-      <c r="X44" s="63"/>
-      <c r="Y44" s="63"/>
-      <c r="Z44" s="54"/>
-      <c r="AA44" s="55"/>
-      <c r="AB44" s="49"/>
-      <c r="AC44" s="63"/>
-      <c r="AD44" s="53"/>
-      <c r="AE44" s="51"/>
-      <c r="AF44" s="52"/>
-      <c r="AG44" s="49"/>
-      <c r="AH44" s="49"/>
-      <c r="AI44" s="63"/>
-      <c r="AJ44" s="49"/>
-      <c r="AK44" s="49"/>
+      <c r="B44" s="50"/>
+      <c r="C44" s="81" t="s">
+        <v>168</v>
+      </c>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="52"/>
+      <c r="N44" s="57"/>
+      <c r="O44" s="58"/>
+      <c r="P44" s="66"/>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="52"/>
+      <c r="S44" s="52"/>
+      <c r="T44" s="52"/>
+      <c r="U44" s="52"/>
+      <c r="V44" s="57"/>
+      <c r="W44" s="59"/>
+      <c r="X44" s="66"/>
+      <c r="Y44" s="66"/>
+      <c r="Z44" s="57"/>
+      <c r="AA44" s="58"/>
+      <c r="AB44" s="52"/>
+      <c r="AC44" s="66"/>
+      <c r="AD44" s="56"/>
+      <c r="AE44" s="54"/>
+      <c r="AF44" s="55"/>
+      <c r="AG44" s="52"/>
+      <c r="AH44" s="52"/>
+      <c r="AI44" s="66"/>
+      <c r="AJ44" s="52"/>
+      <c r="AK44" s="52"/>
     </row>
     <row r="45" ht="12" customHeight="1">
-      <c r="B45" s="47"/>
-      <c r="C45" s="78"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="K45" s="49"/>
-      <c r="L45" s="53"/>
-      <c r="M45" s="49"/>
-      <c r="N45" s="54"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="49"/>
-      <c r="Q45" s="49"/>
-      <c r="R45" s="49"/>
-      <c r="S45" s="49"/>
-      <c r="T45" s="49"/>
-      <c r="U45" s="49"/>
-      <c r="V45" s="54"/>
-      <c r="W45" s="56"/>
-      <c r="X45" s="49"/>
-      <c r="Y45" s="62"/>
-      <c r="Z45" s="79"/>
-      <c r="AA45" s="55"/>
-      <c r="AB45" s="49"/>
-      <c r="AC45" s="49"/>
-      <c r="AD45" s="53"/>
-      <c r="AE45" s="54"/>
-      <c r="AF45" s="55"/>
-      <c r="AG45" s="49"/>
-      <c r="AH45" s="62"/>
-      <c r="AI45" s="62"/>
-      <c r="AJ45" s="49"/>
-      <c r="AK45" s="49"/>
+      <c r="B45" s="50"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="58"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="58"/>
+      <c r="P45" s="52"/>
+      <c r="Q45" s="52"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="52"/>
+      <c r="T45" s="52"/>
+      <c r="U45" s="52"/>
+      <c r="V45" s="57"/>
+      <c r="W45" s="59"/>
+      <c r="X45" s="52"/>
+      <c r="Y45" s="65"/>
+      <c r="Z45" s="82"/>
+      <c r="AA45" s="58"/>
+      <c r="AB45" s="52"/>
+      <c r="AC45" s="52"/>
+      <c r="AD45" s="56"/>
+      <c r="AE45" s="57"/>
+      <c r="AF45" s="58"/>
+      <c r="AG45" s="52"/>
+      <c r="AH45" s="65"/>
+      <c r="AI45" s="65"/>
+      <c r="AJ45" s="52"/>
+      <c r="AK45" s="52"/>
     </row>
     <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="66" t="s">
-        <v>168</v>
-      </c>
-      <c r="C46" s="67" t="s">
+      <c r="B46" s="69" t="s">
+        <v>169</v>
+      </c>
+      <c r="C46" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
-      <c r="F46" s="72"/>
-      <c r="G46" s="70"/>
-      <c r="H46" s="68"/>
-      <c r="I46" s="69"/>
-      <c r="J46" s="69"/>
-      <c r="K46" s="69"/>
-      <c r="L46" s="53"/>
-      <c r="M46" s="69"/>
-      <c r="N46" s="70"/>
-      <c r="O46" s="68"/>
-      <c r="P46" s="69"/>
-      <c r="Q46" s="69"/>
-      <c r="R46" s="69"/>
-      <c r="S46" s="69"/>
-      <c r="T46" s="69"/>
-      <c r="U46" s="69"/>
-      <c r="V46" s="70"/>
-      <c r="W46" s="56"/>
-      <c r="X46" s="69"/>
-      <c r="Y46" s="69"/>
-      <c r="Z46" s="70"/>
-      <c r="AA46" s="68"/>
-      <c r="AB46" s="69"/>
-      <c r="AC46" s="69"/>
-      <c r="AD46" s="53"/>
-      <c r="AE46" s="70"/>
-      <c r="AF46" s="68"/>
-      <c r="AG46" s="69"/>
-      <c r="AH46" s="69"/>
-      <c r="AI46" s="69"/>
-      <c r="AJ46" s="63"/>
-      <c r="AK46" s="69"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="72"/>
+      <c r="F46" s="75"/>
+      <c r="G46" s="73"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="72"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="72"/>
+      <c r="N46" s="73"/>
+      <c r="O46" s="71"/>
+      <c r="P46" s="72"/>
+      <c r="Q46" s="72"/>
+      <c r="R46" s="72"/>
+      <c r="S46" s="72"/>
+      <c r="T46" s="72"/>
+      <c r="U46" s="72"/>
+      <c r="V46" s="73"/>
+      <c r="W46" s="59"/>
+      <c r="X46" s="72"/>
+      <c r="Y46" s="72"/>
+      <c r="Z46" s="73"/>
+      <c r="AA46" s="71"/>
+      <c r="AB46" s="72"/>
+      <c r="AC46" s="72"/>
+      <c r="AD46" s="56"/>
+      <c r="AE46" s="73"/>
+      <c r="AF46" s="71"/>
+      <c r="AG46" s="72"/>
+      <c r="AH46" s="72"/>
+      <c r="AI46" s="72"/>
+      <c r="AJ46" s="66"/>
+      <c r="AK46" s="72"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="B47" s="66"/>
-      <c r="C47" s="67"/>
-      <c r="D47" s="69"/>
-      <c r="E47" s="69"/>
-      <c r="F47" s="72"/>
-      <c r="G47" s="70"/>
-      <c r="H47" s="68"/>
-      <c r="I47" s="69"/>
-      <c r="J47" s="69"/>
-      <c r="K47" s="69"/>
-      <c r="L47" s="53"/>
-      <c r="M47" s="69"/>
-      <c r="N47" s="70"/>
-      <c r="O47" s="68"/>
-      <c r="P47" s="69"/>
-      <c r="Q47" s="69"/>
-      <c r="R47" s="69"/>
-      <c r="S47" s="69"/>
-      <c r="T47" s="69"/>
-      <c r="U47" s="69"/>
-      <c r="V47" s="70"/>
-      <c r="W47" s="56"/>
-      <c r="X47" s="69"/>
-      <c r="Y47" s="69"/>
-      <c r="Z47" s="70"/>
-      <c r="AA47" s="68"/>
-      <c r="AB47" s="69"/>
-      <c r="AC47" s="69"/>
-      <c r="AD47" s="53"/>
-      <c r="AE47" s="70"/>
-      <c r="AF47" s="68"/>
-      <c r="AG47" s="69"/>
-      <c r="AH47" s="69"/>
-      <c r="AI47" s="69"/>
-      <c r="AJ47" s="69"/>
-      <c r="AK47" s="69"/>
-      <c r="AN47" s="80" t="s">
-        <v>169</v>
-      </c>
-      <c r="AO47" s="63"/>
+      <c r="B47" s="69"/>
+      <c r="C47" s="70"/>
+      <c r="D47" s="72"/>
+      <c r="E47" s="72"/>
+      <c r="F47" s="75"/>
+      <c r="G47" s="73"/>
+      <c r="H47" s="71"/>
+      <c r="I47" s="72"/>
+      <c r="J47" s="72"/>
+      <c r="K47" s="72"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="72"/>
+      <c r="N47" s="73"/>
+      <c r="O47" s="71"/>
+      <c r="P47" s="72"/>
+      <c r="Q47" s="72"/>
+      <c r="R47" s="72"/>
+      <c r="S47" s="72"/>
+      <c r="T47" s="72"/>
+      <c r="U47" s="72"/>
+      <c r="V47" s="73"/>
+      <c r="W47" s="59"/>
+      <c r="X47" s="72"/>
+      <c r="Y47" s="72"/>
+      <c r="Z47" s="73"/>
+      <c r="AA47" s="71"/>
+      <c r="AB47" s="72"/>
+      <c r="AC47" s="72"/>
+      <c r="AD47" s="56"/>
+      <c r="AE47" s="73"/>
+      <c r="AF47" s="71"/>
+      <c r="AG47" s="72"/>
+      <c r="AH47" s="72"/>
+      <c r="AI47" s="72"/>
+      <c r="AJ47" s="65"/>
+      <c r="AK47" s="72"/>
+      <c r="AN47" s="83" t="s">
+        <v>170</v>
+      </c>
+      <c r="AO47" s="66"/>
     </row>
     <row r="48" ht="12" customHeight="1">
-      <c r="B48" s="66"/>
-      <c r="C48" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
-      <c r="F48" s="72"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="68"/>
-      <c r="I48" s="69"/>
-      <c r="J48" s="69"/>
-      <c r="K48" s="69"/>
-      <c r="L48" s="53"/>
-      <c r="M48" s="69"/>
-      <c r="N48" s="70"/>
-      <c r="O48" s="68"/>
-      <c r="P48" s="69"/>
-      <c r="Q48" s="69"/>
-      <c r="R48" s="69"/>
-      <c r="S48" s="69"/>
-      <c r="T48" s="69"/>
-      <c r="U48" s="69"/>
-      <c r="V48" s="70"/>
-      <c r="W48" s="56"/>
-      <c r="X48" s="69"/>
-      <c r="Y48" s="69"/>
-      <c r="Z48" s="70"/>
-      <c r="AA48" s="68"/>
-      <c r="AB48" s="69"/>
-      <c r="AC48" s="69"/>
-      <c r="AD48" s="53"/>
-      <c r="AE48" s="70"/>
-      <c r="AF48" s="68"/>
-      <c r="AG48" s="69"/>
-      <c r="AH48" s="69"/>
-      <c r="AI48" s="69"/>
-      <c r="AJ48" s="69"/>
-      <c r="AK48" s="81"/>
-      <c r="AN48" s="80" t="s">
+      <c r="B48" s="69"/>
+      <c r="C48" s="70" t="s">
         <v>171</v>
       </c>
-      <c r="AO48" s="62"/>
+      <c r="D48" s="72"/>
+      <c r="E48" s="72"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="71"/>
+      <c r="I48" s="72"/>
+      <c r="J48" s="72"/>
+      <c r="K48" s="72"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="72"/>
+      <c r="N48" s="73"/>
+      <c r="O48" s="71"/>
+      <c r="P48" s="72"/>
+      <c r="Q48" s="72"/>
+      <c r="R48" s="72"/>
+      <c r="S48" s="72"/>
+      <c r="T48" s="72"/>
+      <c r="U48" s="72"/>
+      <c r="V48" s="73"/>
+      <c r="W48" s="59"/>
+      <c r="X48" s="72"/>
+      <c r="Y48" s="72"/>
+      <c r="Z48" s="73"/>
+      <c r="AA48" s="71"/>
+      <c r="AB48" s="72"/>
+      <c r="AC48" s="72"/>
+      <c r="AD48" s="56"/>
+      <c r="AE48" s="73"/>
+      <c r="AF48" s="71"/>
+      <c r="AG48" s="72"/>
+      <c r="AH48" s="72"/>
+      <c r="AI48" s="72"/>
+      <c r="AJ48" s="72"/>
+      <c r="AK48" s="84"/>
+      <c r="AN48" s="83" t="s">
+        <v>172</v>
+      </c>
+      <c r="AO48" s="65"/>
     </row>
     <row r="49" ht="12" customHeight="1">
-      <c r="B49" s="66"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="69"/>
-      <c r="E49" s="69"/>
-      <c r="F49" s="72"/>
-      <c r="G49" s="70"/>
-      <c r="H49" s="68"/>
-      <c r="I49" s="69"/>
-      <c r="J49" s="69"/>
-      <c r="K49" s="69"/>
-      <c r="L49" s="53"/>
-      <c r="M49" s="69"/>
-      <c r="N49" s="70"/>
-      <c r="O49" s="68"/>
-      <c r="P49" s="69"/>
-      <c r="Q49" s="69"/>
-      <c r="R49" s="69"/>
-      <c r="S49" s="69"/>
-      <c r="T49" s="69"/>
-      <c r="U49" s="69"/>
-      <c r="V49" s="70"/>
-      <c r="W49" s="56"/>
-      <c r="X49" s="69"/>
-      <c r="Y49" s="69"/>
-      <c r="Z49" s="70"/>
-      <c r="AA49" s="68"/>
-      <c r="AB49" s="69"/>
-      <c r="AC49" s="69"/>
-      <c r="AD49" s="53"/>
-      <c r="AE49" s="70"/>
-      <c r="AF49" s="68"/>
-      <c r="AG49" s="69"/>
-      <c r="AH49" s="69"/>
-      <c r="AI49" s="69"/>
-      <c r="AJ49" s="69"/>
-      <c r="AK49" s="69"/>
-      <c r="AN49" s="80" t="s">
-        <v>172</v>
-      </c>
-      <c r="AO49" s="58"/>
+      <c r="B49" s="69"/>
+      <c r="C49" s="70"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="72"/>
+      <c r="F49" s="75"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="72"/>
+      <c r="J49" s="72"/>
+      <c r="K49" s="72"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="72"/>
+      <c r="N49" s="73"/>
+      <c r="O49" s="71"/>
+      <c r="P49" s="72"/>
+      <c r="Q49" s="72"/>
+      <c r="R49" s="72"/>
+      <c r="S49" s="72"/>
+      <c r="T49" s="72"/>
+      <c r="U49" s="72"/>
+      <c r="V49" s="73"/>
+      <c r="W49" s="59"/>
+      <c r="X49" s="72"/>
+      <c r="Y49" s="72"/>
+      <c r="Z49" s="73"/>
+      <c r="AA49" s="71"/>
+      <c r="AB49" s="72"/>
+      <c r="AC49" s="72"/>
+      <c r="AD49" s="56"/>
+      <c r="AE49" s="73"/>
+      <c r="AF49" s="71"/>
+      <c r="AG49" s="72"/>
+      <c r="AH49" s="72"/>
+      <c r="AI49" s="72"/>
+      <c r="AJ49" s="72"/>
+      <c r="AK49" s="72"/>
+      <c r="AN49" s="83" t="s">
+        <v>173</v>
+      </c>
+      <c r="AO49" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B34:B41"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B2:B13"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C12:C13"/>
     <mergeCell ref="B14:B25"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="C16:C17"/>
@@ -11059,13 +11070,22 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="C22:C23"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B2:B13"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B34:B41"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="C48:C49"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -11095,801 +11115,801 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="82"/>
+      <c r="B1" s="85"/>
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
-      <c r="B2" s="83" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="84" t="s">
+      <c r="B2" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="85" t="s">
-        <v>173</v>
-      </c>
-      <c r="E2" s="86" t="s">
+      <c r="C2" s="87" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="88" t="s">
         <v>174</v>
       </c>
-      <c r="F2" s="87" t="s">
+      <c r="E2" s="89" t="s">
         <v>175</v>
       </c>
-      <c r="G2" s="87"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="87" t="s">
+      <c r="F2" s="90" t="s">
         <v>176</v>
       </c>
-      <c r="K2" s="87"/>
-      <c r="L2" s="87"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="87" t="s">
-        <v>111</v>
-      </c>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="86"/>
-      <c r="R2" s="87" t="s">
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="90" t="s">
+        <v>177</v>
+      </c>
+      <c r="K2" s="90"/>
+      <c r="L2" s="90"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="90" t="s">
         <v>112</v>
       </c>
-      <c r="S2" s="88"/>
-      <c r="AD2" s="89"/>
+      <c r="O2" s="90"/>
+      <c r="P2" s="90"/>
+      <c r="Q2" s="89"/>
+      <c r="R2" s="90" t="s">
+        <v>113</v>
+      </c>
+      <c r="S2" s="91"/>
+      <c r="AD2" s="92"/>
     </row>
     <row r="3">
-      <c r="B3" s="90"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="92" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" s="93">
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="95" t="s">
+        <v>178</v>
+      </c>
+      <c r="E3" s="96">
         <v>4</v>
       </c>
-      <c r="F3" s="94">
+      <c r="F3" s="97">
         <v>1</v>
       </c>
-      <c r="G3" s="95">
+      <c r="G3" s="98">
         <v>2</v>
       </c>
-      <c r="H3" s="95">
+      <c r="H3" s="98">
         <v>3</v>
       </c>
-      <c r="I3" s="93">
+      <c r="I3" s="96">
         <v>4</v>
       </c>
-      <c r="J3" s="94">
+      <c r="J3" s="97">
         <v>1</v>
       </c>
-      <c r="K3" s="95">
+      <c r="K3" s="98">
         <v>2</v>
       </c>
-      <c r="L3" s="95">
+      <c r="L3" s="98">
         <v>3</v>
       </c>
-      <c r="M3" s="93">
+      <c r="M3" s="96">
         <v>4</v>
       </c>
-      <c r="N3" s="94">
+      <c r="N3" s="97">
         <v>1</v>
       </c>
-      <c r="O3" s="95">
+      <c r="O3" s="98">
         <v>2</v>
       </c>
-      <c r="P3" s="95">
+      <c r="P3" s="98">
         <v>3</v>
       </c>
-      <c r="Q3" s="93">
+      <c r="Q3" s="96">
         <v>4</v>
       </c>
-      <c r="R3" s="94">
+      <c r="R3" s="97">
         <v>1</v>
       </c>
-      <c r="S3" s="96">
+      <c r="S3" s="99">
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="B4" s="97" t="s">
-        <v>179</v>
-      </c>
-      <c r="C4" s="84" t="s">
+      <c r="B4" s="100" t="s">
         <v>180</v>
       </c>
-      <c r="D4" s="98"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="101"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="102"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="102"/>
-      <c r="S4" s="103"/>
+      <c r="C4" s="87" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="101"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="104"/>
+      <c r="L4" s="104"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="105"/>
+      <c r="O4" s="104"/>
+      <c r="P4" s="104"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="105"/>
+      <c r="S4" s="106"/>
       <c r="U4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="B5" s="97"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="109"/>
-      <c r="L5" s="109"/>
-      <c r="M5" s="106"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="106"/>
-      <c r="R5" s="110"/>
-      <c r="S5" s="111"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="109"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="109"/>
+      <c r="N5" s="113"/>
+      <c r="O5" s="112"/>
+      <c r="P5" s="112"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="114"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="B6" s="97"/>
-      <c r="C6" s="112" t="s">
-        <v>182</v>
-      </c>
-      <c r="D6" s="113"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="116"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="118"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
-      <c r="M6" s="114"/>
-      <c r="N6" s="118"/>
-      <c r="O6" s="117"/>
-      <c r="P6" s="117"/>
-      <c r="Q6" s="114"/>
-      <c r="R6" s="118"/>
-      <c r="S6" s="119"/>
-      <c r="U6" s="120" t="s">
+      <c r="B6" s="100"/>
+      <c r="C6" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="V6" s="120"/>
+      <c r="D6" s="116"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="121"/>
+      <c r="K6" s="120"/>
+      <c r="L6" s="120"/>
+      <c r="M6" s="117"/>
+      <c r="N6" s="121"/>
+      <c r="O6" s="120"/>
+      <c r="P6" s="120"/>
+      <c r="Q6" s="117"/>
+      <c r="R6" s="121"/>
+      <c r="S6" s="122"/>
+      <c r="U6" s="123" t="s">
+        <v>184</v>
+      </c>
+      <c r="V6" s="123"/>
     </row>
     <row r="7" ht="12" customHeight="1">
-      <c r="B7" s="97"/>
-      <c r="C7" s="104"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="109"/>
-      <c r="L7" s="109"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="109"/>
-      <c r="P7" s="109"/>
-      <c r="Q7" s="106"/>
-      <c r="R7" s="110"/>
-      <c r="S7" s="111"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="112"/>
+      <c r="M7" s="109"/>
+      <c r="N7" s="113"/>
+      <c r="O7" s="112"/>
+      <c r="P7" s="112"/>
+      <c r="Q7" s="109"/>
+      <c r="R7" s="113"/>
+      <c r="S7" s="114"/>
       <c r="U7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="B8" s="97"/>
-      <c r="C8" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="113"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="115"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="114"/>
-      <c r="J8" s="118"/>
-      <c r="K8" s="117"/>
-      <c r="L8" s="117"/>
-      <c r="M8" s="114"/>
-      <c r="N8" s="118"/>
-      <c r="O8" s="117"/>
-      <c r="P8" s="117"/>
-      <c r="Q8" s="114"/>
-      <c r="R8" s="118"/>
-      <c r="S8" s="119"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="115" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="116"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="120"/>
+      <c r="L8" s="120"/>
+      <c r="M8" s="117"/>
+      <c r="N8" s="121"/>
+      <c r="O8" s="120"/>
+      <c r="P8" s="120"/>
+      <c r="Q8" s="117"/>
+      <c r="R8" s="121"/>
+      <c r="S8" s="122"/>
       <c r="U8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="B9" s="97"/>
-      <c r="C9" s="104"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="108"/>
-      <c r="H9" s="109"/>
-      <c r="I9" s="106"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="109"/>
-      <c r="L9" s="109"/>
-      <c r="M9" s="106"/>
-      <c r="N9" s="110"/>
-      <c r="O9" s="109"/>
-      <c r="P9" s="109"/>
-      <c r="Q9" s="106"/>
-      <c r="R9" s="110"/>
-      <c r="S9" s="111"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="109"/>
+      <c r="F9" s="113"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="109"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="112"/>
+      <c r="M9" s="109"/>
+      <c r="N9" s="113"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="112"/>
+      <c r="Q9" s="109"/>
+      <c r="R9" s="113"/>
+      <c r="S9" s="114"/>
     </row>
     <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="97"/>
-      <c r="C10" s="112" t="s">
-        <v>187</v>
-      </c>
-      <c r="D10" s="113"/>
-      <c r="E10" s="114"/>
-      <c r="F10" s="118"/>
-      <c r="G10" s="116"/>
-      <c r="H10" s="116"/>
-      <c r="I10" s="114"/>
-      <c r="J10" s="118"/>
-      <c r="K10" s="117"/>
-      <c r="L10" s="117"/>
-      <c r="M10" s="114"/>
-      <c r="N10" s="118"/>
-      <c r="O10" s="117"/>
-      <c r="P10" s="117"/>
-      <c r="Q10" s="114"/>
-      <c r="R10" s="118"/>
-      <c r="S10" s="119"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="115" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="116"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="119"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="117"/>
+      <c r="J10" s="121"/>
+      <c r="K10" s="120"/>
+      <c r="L10" s="120"/>
+      <c r="M10" s="117"/>
+      <c r="N10" s="121"/>
+      <c r="O10" s="120"/>
+      <c r="P10" s="120"/>
+      <c r="Q10" s="117"/>
+      <c r="R10" s="121"/>
+      <c r="S10" s="122"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="B11" s="121"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="126"/>
-      <c r="H11" s="126"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="125"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="124"/>
-      <c r="N11" s="125"/>
-      <c r="O11" s="127"/>
-      <c r="P11" s="127"/>
-      <c r="Q11" s="124"/>
-      <c r="R11" s="125"/>
-      <c r="S11" s="128"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="126"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="128"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="128"/>
+      <c r="O11" s="130"/>
+      <c r="P11" s="130"/>
+      <c r="Q11" s="127"/>
+      <c r="R11" s="128"/>
+      <c r="S11" s="131"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="B12" s="83" t="s">
-        <v>188</v>
-      </c>
-      <c r="C12" s="84" t="s">
+      <c r="B12" s="86" t="s">
         <v>189</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="102"/>
-      <c r="K12" s="101"/>
-      <c r="L12" s="101"/>
-      <c r="M12" s="99"/>
-      <c r="N12" s="102"/>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
-      <c r="Q12" s="99"/>
-      <c r="R12" s="102"/>
-      <c r="S12" s="103"/>
+      <c r="C12" s="87" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" s="101"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="132"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="104"/>
+      <c r="M12" s="102"/>
+      <c r="N12" s="105"/>
+      <c r="O12" s="104"/>
+      <c r="P12" s="104"/>
+      <c r="Q12" s="102"/>
+      <c r="R12" s="105"/>
+      <c r="S12" s="106"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="B13" s="97"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="105"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="107"/>
-      <c r="K13" s="109"/>
-      <c r="L13" s="109"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="109"/>
-      <c r="P13" s="109"/>
-      <c r="Q13" s="106"/>
-      <c r="R13" s="110"/>
-      <c r="S13" s="111"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="107"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="112"/>
+      <c r="H13" s="112"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="112"/>
+      <c r="L13" s="112"/>
+      <c r="M13" s="109"/>
+      <c r="N13" s="113"/>
+      <c r="O13" s="112"/>
+      <c r="P13" s="112"/>
+      <c r="Q13" s="109"/>
+      <c r="R13" s="113"/>
+      <c r="S13" s="114"/>
     </row>
     <row r="14" ht="12" customHeight="1">
-      <c r="B14" s="97"/>
-      <c r="C14" s="112" t="s">
-        <v>190</v>
-      </c>
-      <c r="D14" s="131"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="116"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="117"/>
-      <c r="L14" s="117"/>
-      <c r="M14" s="114"/>
-      <c r="N14" s="118"/>
-      <c r="O14" s="117"/>
-      <c r="P14" s="117"/>
-      <c r="Q14" s="114"/>
-      <c r="R14" s="118"/>
-      <c r="S14" s="119"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="115" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" s="134"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="120"/>
+      <c r="L14" s="120"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="121"/>
+      <c r="O14" s="120"/>
+      <c r="P14" s="120"/>
+      <c r="Q14" s="117"/>
+      <c r="R14" s="121"/>
+      <c r="S14" s="122"/>
     </row>
     <row r="15" ht="12" customHeight="1">
-      <c r="B15" s="97"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="109"/>
-      <c r="H15" s="109"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="107"/>
-      <c r="K15" s="109"/>
-      <c r="L15" s="109"/>
-      <c r="M15" s="106"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="109"/>
-      <c r="P15" s="109"/>
-      <c r="Q15" s="106"/>
-      <c r="R15" s="110"/>
-      <c r="S15" s="111"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="107"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="109"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="112"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="135"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="109"/>
+      <c r="N15" s="113"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="109"/>
+      <c r="R15" s="113"/>
+      <c r="S15" s="114"/>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="B16" s="97"/>
-      <c r="C16" s="112" t="s">
-        <v>191</v>
-      </c>
-      <c r="D16" s="113"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="116"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="114"/>
-      <c r="N16" s="118"/>
-      <c r="O16" s="117"/>
-      <c r="P16" s="117"/>
-      <c r="Q16" s="114"/>
-      <c r="R16" s="118"/>
-      <c r="S16" s="119"/>
+      <c r="B16" s="100"/>
+      <c r="C16" s="115" t="s">
+        <v>192</v>
+      </c>
+      <c r="D16" s="116"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="121"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="117"/>
+      <c r="R16" s="121"/>
+      <c r="S16" s="122"/>
     </row>
     <row r="17" ht="12" customHeight="1">
-      <c r="B17" s="121"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="123"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="125"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="124"/>
-      <c r="J17" s="134"/>
-      <c r="K17" s="126"/>
-      <c r="L17" s="127"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="125"/>
-      <c r="O17" s="127"/>
-      <c r="P17" s="127"/>
-      <c r="Q17" s="124"/>
-      <c r="R17" s="125"/>
-      <c r="S17" s="128"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="125"/>
+      <c r="D17" s="126"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="137"/>
+      <c r="K17" s="129"/>
+      <c r="L17" s="130"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="128"/>
+      <c r="O17" s="130"/>
+      <c r="P17" s="130"/>
+      <c r="Q17" s="127"/>
+      <c r="R17" s="128"/>
+      <c r="S17" s="131"/>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="B18" s="85" t="s">
-        <v>192</v>
-      </c>
-      <c r="C18" s="84" t="s">
+      <c r="B18" s="88" t="s">
         <v>193</v>
       </c>
-      <c r="D18" s="98"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="101"/>
-      <c r="H18" s="101"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="102"/>
-      <c r="K18" s="101"/>
-      <c r="L18" s="101"/>
-      <c r="M18" s="99"/>
-      <c r="N18" s="102"/>
-      <c r="O18" s="101"/>
-      <c r="P18" s="101"/>
-      <c r="Q18" s="99"/>
-      <c r="R18" s="102"/>
-      <c r="S18" s="103"/>
+      <c r="C18" s="87" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18" s="101"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="104"/>
+      <c r="L18" s="104"/>
+      <c r="M18" s="102"/>
+      <c r="N18" s="105"/>
+      <c r="O18" s="104"/>
+      <c r="P18" s="104"/>
+      <c r="Q18" s="102"/>
+      <c r="R18" s="105"/>
+      <c r="S18" s="106"/>
     </row>
     <row r="19" ht="12" customHeight="1">
-      <c r="B19" s="97"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="105"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="108"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="109"/>
-      <c r="L19" s="109"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="109"/>
-      <c r="P19" s="109"/>
-      <c r="Q19" s="106"/>
-      <c r="R19" s="110"/>
-      <c r="S19" s="111"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="108"/>
+      <c r="E19" s="109"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="111"/>
+      <c r="H19" s="112"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112"/>
+      <c r="M19" s="109"/>
+      <c r="N19" s="113"/>
+      <c r="O19" s="112"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="109"/>
+      <c r="R19" s="113"/>
+      <c r="S19" s="114"/>
     </row>
     <row r="20" ht="12" customHeight="1">
-      <c r="B20" s="97"/>
-      <c r="C20" s="112" t="s">
-        <v>194</v>
-      </c>
-      <c r="D20" s="113"/>
-      <c r="E20" s="114"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="133"/>
-      <c r="J20" s="115"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="116"/>
-      <c r="M20" s="114"/>
-      <c r="N20" s="118"/>
-      <c r="O20" s="117"/>
-      <c r="P20" s="117"/>
-      <c r="Q20" s="114"/>
-      <c r="R20" s="118"/>
-      <c r="S20" s="119"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="115" t="s">
+        <v>195</v>
+      </c>
+      <c r="D20" s="116"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="121"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="136"/>
+      <c r="J20" s="118"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="117"/>
+      <c r="N20" s="121"/>
+      <c r="O20" s="120"/>
+      <c r="P20" s="120"/>
+      <c r="Q20" s="117"/>
+      <c r="R20" s="121"/>
+      <c r="S20" s="122"/>
     </row>
     <row r="21" ht="12" customHeight="1">
-      <c r="B21" s="97"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="110"/>
-      <c r="G21" s="109"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="106"/>
-      <c r="N21" s="135"/>
-      <c r="O21" s="109"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="106"/>
-      <c r="R21" s="110"/>
-      <c r="S21" s="111"/>
+      <c r="B21" s="100"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="109"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="112"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="112"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="109"/>
+      <c r="N21" s="138"/>
+      <c r="O21" s="112"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="109"/>
+      <c r="R21" s="113"/>
+      <c r="S21" s="114"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="B22" s="97"/>
-      <c r="C22" s="112" t="s">
-        <v>195</v>
-      </c>
-      <c r="D22" s="113"/>
-      <c r="E22" s="114"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="114"/>
-      <c r="J22" s="118"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
-      <c r="M22" s="114"/>
-      <c r="N22" s="118"/>
-      <c r="O22" s="117"/>
-      <c r="P22" s="117"/>
-      <c r="Q22" s="114"/>
-      <c r="R22" s="118"/>
-      <c r="S22" s="119"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="115" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" s="116"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="120"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="121"/>
+      <c r="O22" s="120"/>
+      <c r="P22" s="120"/>
+      <c r="Q22" s="117"/>
+      <c r="R22" s="121"/>
+      <c r="S22" s="122"/>
     </row>
     <row r="23" ht="12" customHeight="1">
-      <c r="B23" s="121"/>
-      <c r="C23" s="122"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="127"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="124"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="127"/>
-      <c r="L23" s="127"/>
-      <c r="M23" s="124"/>
-      <c r="N23" s="125"/>
-      <c r="O23" s="127"/>
-      <c r="P23" s="127"/>
-      <c r="Q23" s="124"/>
-      <c r="R23" s="125"/>
-      <c r="S23" s="128"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="130"/>
+      <c r="H23" s="130"/>
+      <c r="I23" s="127"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="130"/>
+      <c r="L23" s="130"/>
+      <c r="M23" s="127"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="130"/>
+      <c r="P23" s="130"/>
+      <c r="Q23" s="127"/>
+      <c r="R23" s="128"/>
+      <c r="S23" s="131"/>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="B24" s="85" t="s">
-        <v>196</v>
-      </c>
-      <c r="C24" s="84" t="s">
+      <c r="B24" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="D24" s="98"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="102"/>
-      <c r="G24" s="101"/>
-      <c r="H24" s="101"/>
-      <c r="I24" s="99"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="101"/>
-      <c r="L24" s="101"/>
-      <c r="M24" s="130"/>
-      <c r="N24" s="100"/>
-      <c r="O24" s="129"/>
-      <c r="P24" s="129"/>
-      <c r="Q24" s="99"/>
-      <c r="R24" s="102"/>
-      <c r="S24" s="103"/>
+      <c r="C24" s="87" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="101"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="104"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="102"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="104"/>
+      <c r="L24" s="104"/>
+      <c r="M24" s="133"/>
+      <c r="N24" s="103"/>
+      <c r="O24" s="132"/>
+      <c r="P24" s="132"/>
+      <c r="Q24" s="102"/>
+      <c r="R24" s="105"/>
+      <c r="S24" s="106"/>
     </row>
     <row r="25" ht="12" customHeight="1">
-      <c r="B25" s="97"/>
-      <c r="C25" s="104"/>
-      <c r="D25" s="105"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="109"/>
-      <c r="H25" s="109"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="109"/>
-      <c r="L25" s="109"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="110"/>
-      <c r="O25" s="109"/>
-      <c r="P25" s="109"/>
-      <c r="Q25" s="106"/>
-      <c r="R25" s="110"/>
-      <c r="S25" s="111"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="112"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="113"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="112"/>
+      <c r="Q25" s="109"/>
+      <c r="R25" s="113"/>
+      <c r="S25" s="114"/>
     </row>
     <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="97"/>
-      <c r="C26" s="112" t="s">
-        <v>198</v>
-      </c>
-      <c r="D26" s="113"/>
-      <c r="E26" s="114"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="114"/>
-      <c r="J26" s="118"/>
-      <c r="K26" s="117"/>
-      <c r="L26" s="117"/>
-      <c r="M26" s="114"/>
-      <c r="N26" s="118"/>
-      <c r="O26" s="116"/>
-      <c r="P26" s="116"/>
-      <c r="Q26" s="114"/>
-      <c r="R26" s="118"/>
-      <c r="S26" s="119"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="115" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="116"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="121"/>
+      <c r="K26" s="120"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="117"/>
+      <c r="N26" s="121"/>
+      <c r="O26" s="119"/>
+      <c r="P26" s="119"/>
+      <c r="Q26" s="117"/>
+      <c r="R26" s="121"/>
+      <c r="S26" s="122"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="B27" s="97"/>
-      <c r="C27" s="104"/>
-      <c r="D27" s="105"/>
-      <c r="E27" s="106"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="109"/>
-      <c r="H27" s="109"/>
-      <c r="I27" s="106"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="109"/>
-      <c r="L27" s="109"/>
-      <c r="M27" s="106"/>
-      <c r="N27" s="110"/>
-      <c r="O27" s="109"/>
-      <c r="P27" s="109"/>
-      <c r="Q27" s="106"/>
-      <c r="R27" s="110"/>
-      <c r="S27" s="111"/>
+      <c r="B27" s="100"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="109"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="112"/>
+      <c r="L27" s="112"/>
+      <c r="M27" s="109"/>
+      <c r="N27" s="113"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="112"/>
+      <c r="Q27" s="109"/>
+      <c r="R27" s="113"/>
+      <c r="S27" s="114"/>
     </row>
     <row r="28" ht="12" customHeight="1">
-      <c r="B28" s="97"/>
-      <c r="C28" s="112" t="s">
-        <v>199</v>
-      </c>
-      <c r="D28" s="113"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="117"/>
-      <c r="I28" s="114"/>
-      <c r="J28" s="118"/>
-      <c r="K28" s="117"/>
-      <c r="L28" s="117"/>
-      <c r="M28" s="114"/>
-      <c r="N28" s="118"/>
-      <c r="O28" s="117"/>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="133"/>
-      <c r="R28" s="118"/>
-      <c r="S28" s="119"/>
+      <c r="B28" s="100"/>
+      <c r="C28" s="115" t="s">
+        <v>200</v>
+      </c>
+      <c r="D28" s="116"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="121"/>
+      <c r="G28" s="120"/>
+      <c r="H28" s="120"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="121"/>
+      <c r="K28" s="120"/>
+      <c r="L28" s="120"/>
+      <c r="M28" s="117"/>
+      <c r="N28" s="121"/>
+      <c r="O28" s="120"/>
+      <c r="P28" s="119"/>
+      <c r="Q28" s="136"/>
+      <c r="R28" s="121"/>
+      <c r="S28" s="122"/>
     </row>
     <row r="29" ht="12" customHeight="1">
-      <c r="B29" s="97"/>
-      <c r="C29" s="91"/>
-      <c r="D29" s="136"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="139"/>
-      <c r="H29" s="140"/>
-      <c r="I29" s="137"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="139"/>
-      <c r="L29" s="140"/>
-      <c r="M29" s="137"/>
-      <c r="N29" s="141"/>
-      <c r="O29" s="140"/>
-      <c r="P29" s="139"/>
-      <c r="Q29" s="137"/>
-      <c r="R29" s="138"/>
-      <c r="S29" s="142"/>
+      <c r="B29" s="100"/>
+      <c r="C29" s="94"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="143"/>
+      <c r="I29" s="140"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="142"/>
+      <c r="L29" s="143"/>
+      <c r="M29" s="140"/>
+      <c r="N29" s="144"/>
+      <c r="O29" s="143"/>
+      <c r="P29" s="142"/>
+      <c r="Q29" s="140"/>
+      <c r="R29" s="141"/>
+      <c r="S29" s="145"/>
     </row>
     <row r="30" ht="12" customHeight="1">
-      <c r="B30" s="143" t="s">
+      <c r="B30" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="144" t="s">
-        <v>145</v>
-      </c>
-      <c r="D30" s="98"/>
-      <c r="E30" s="145"/>
-      <c r="F30" s="146"/>
-      <c r="G30" s="146"/>
-      <c r="H30" s="147"/>
-      <c r="I30" s="148"/>
-      <c r="J30" s="146"/>
-      <c r="K30" s="146"/>
-      <c r="L30" s="147"/>
-      <c r="M30" s="148"/>
-      <c r="N30" s="146"/>
-      <c r="O30" s="147"/>
-      <c r="P30" s="146"/>
-      <c r="Q30" s="148"/>
-      <c r="R30" s="146"/>
-      <c r="S30" s="149"/>
+      <c r="C30" s="147" t="s">
+        <v>146</v>
+      </c>
+      <c r="D30" s="101"/>
+      <c r="E30" s="148"/>
+      <c r="F30" s="149"/>
+      <c r="G30" s="149"/>
+      <c r="H30" s="150"/>
+      <c r="I30" s="151"/>
+      <c r="J30" s="149"/>
+      <c r="K30" s="149"/>
+      <c r="L30" s="150"/>
+      <c r="M30" s="151"/>
+      <c r="N30" s="149"/>
+      <c r="O30" s="150"/>
+      <c r="P30" s="149"/>
+      <c r="Q30" s="151"/>
+      <c r="R30" s="149"/>
+      <c r="S30" s="152"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="150"/>
-      <c r="C31" s="151"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="153"/>
-      <c r="G31" s="153"/>
-      <c r="H31" s="154"/>
-      <c r="I31" s="155"/>
-      <c r="J31" s="153"/>
-      <c r="K31" s="156"/>
-      <c r="L31" s="154"/>
-      <c r="M31" s="155"/>
-      <c r="N31" s="153"/>
-      <c r="O31" s="154"/>
-      <c r="P31" s="153"/>
-      <c r="Q31" s="155"/>
-      <c r="R31" s="153"/>
-      <c r="S31" s="111"/>
+      <c r="B31" s="153"/>
+      <c r="C31" s="154"/>
+      <c r="D31" s="108"/>
+      <c r="E31" s="155"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="156"/>
+      <c r="H31" s="157"/>
+      <c r="I31" s="158"/>
+      <c r="J31" s="156"/>
+      <c r="K31" s="159"/>
+      <c r="L31" s="157"/>
+      <c r="M31" s="158"/>
+      <c r="N31" s="156"/>
+      <c r="O31" s="157"/>
+      <c r="P31" s="156"/>
+      <c r="Q31" s="158"/>
+      <c r="R31" s="156"/>
+      <c r="S31" s="114"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="B32" s="150"/>
-      <c r="C32" s="151" t="s">
+      <c r="B32" s="153"/>
+      <c r="C32" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="113"/>
-      <c r="E32" s="157"/>
-      <c r="F32" s="158"/>
-      <c r="G32" s="158"/>
-      <c r="H32" s="159"/>
-      <c r="I32" s="160"/>
-      <c r="J32" s="158"/>
-      <c r="K32" s="158"/>
-      <c r="L32" s="159"/>
-      <c r="M32" s="160"/>
-      <c r="N32" s="158"/>
-      <c r="O32" s="159"/>
-      <c r="P32" s="158"/>
-      <c r="Q32" s="160"/>
-      <c r="R32" s="158"/>
-      <c r="S32" s="161"/>
+      <c r="D32" s="116"/>
+      <c r="E32" s="160"/>
+      <c r="F32" s="161"/>
+      <c r="G32" s="161"/>
+      <c r="H32" s="162"/>
+      <c r="I32" s="163"/>
+      <c r="J32" s="161"/>
+      <c r="K32" s="161"/>
+      <c r="L32" s="162"/>
+      <c r="M32" s="163"/>
+      <c r="N32" s="161"/>
+      <c r="O32" s="162"/>
+      <c r="P32" s="161"/>
+      <c r="Q32" s="163"/>
+      <c r="R32" s="161"/>
+      <c r="S32" s="164"/>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="B33" s="150"/>
-      <c r="C33" s="151"/>
-      <c r="D33" s="105"/>
-      <c r="E33" s="152"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="153"/>
-      <c r="H33" s="162"/>
-      <c r="I33" s="163"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="156"/>
-      <c r="L33" s="154"/>
-      <c r="M33" s="155"/>
-      <c r="N33" s="153"/>
-      <c r="O33" s="154"/>
-      <c r="P33" s="153"/>
-      <c r="Q33" s="155"/>
-      <c r="R33" s="153"/>
-      <c r="S33" s="111"/>
+      <c r="B33" s="153"/>
+      <c r="C33" s="154"/>
+      <c r="D33" s="108"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="159"/>
+      <c r="G33" s="156"/>
+      <c r="H33" s="165"/>
+      <c r="I33" s="166"/>
+      <c r="J33" s="156"/>
+      <c r="K33" s="159"/>
+      <c r="L33" s="157"/>
+      <c r="M33" s="158"/>
+      <c r="N33" s="156"/>
+      <c r="O33" s="157"/>
+      <c r="P33" s="156"/>
+      <c r="Q33" s="158"/>
+      <c r="R33" s="156"/>
+      <c r="S33" s="114"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="B34" s="150"/>
-      <c r="C34" s="104" t="s">
-        <v>200</v>
-      </c>
-      <c r="D34" s="136"/>
-      <c r="E34" s="164"/>
-      <c r="F34" s="165"/>
-      <c r="G34" s="165"/>
-      <c r="H34" s="166"/>
-      <c r="I34" s="167"/>
-      <c r="J34" s="165"/>
-      <c r="K34" s="165"/>
-      <c r="L34" s="166"/>
-      <c r="M34" s="167"/>
-      <c r="N34" s="165"/>
-      <c r="O34" s="166"/>
-      <c r="P34" s="165"/>
-      <c r="Q34" s="167"/>
-      <c r="R34" s="165"/>
-      <c r="S34" s="168"/>
-      <c r="U34" s="169"/>
-      <c r="V34" s="170" t="s">
+      <c r="B34" s="153"/>
+      <c r="C34" s="107" t="s">
         <v>201</v>
       </c>
+      <c r="D34" s="139"/>
+      <c r="E34" s="167"/>
+      <c r="F34" s="168"/>
+      <c r="G34" s="168"/>
+      <c r="H34" s="169"/>
+      <c r="I34" s="170"/>
+      <c r="J34" s="168"/>
+      <c r="K34" s="168"/>
+      <c r="L34" s="169"/>
+      <c r="M34" s="170"/>
+      <c r="N34" s="168"/>
+      <c r="O34" s="169"/>
+      <c r="P34" s="168"/>
+      <c r="Q34" s="170"/>
+      <c r="R34" s="168"/>
+      <c r="S34" s="171"/>
+      <c r="U34" s="172"/>
+      <c r="V34" s="173" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
-      <c r="B35" s="171"/>
-      <c r="C35" s="172"/>
-      <c r="D35" s="123"/>
-      <c r="E35" s="173"/>
-      <c r="F35" s="174"/>
-      <c r="G35" s="174"/>
-      <c r="H35" s="175"/>
-      <c r="I35" s="176"/>
-      <c r="J35" s="174"/>
-      <c r="K35" s="174"/>
-      <c r="L35" s="175"/>
-      <c r="M35" s="176"/>
-      <c r="N35" s="174"/>
-      <c r="O35" s="175"/>
-      <c r="P35" s="174"/>
-      <c r="Q35" s="176"/>
-      <c r="R35" s="174"/>
-      <c r="S35" s="128"/>
-      <c r="U35" s="177"/>
-      <c r="V35" s="178" t="s">
-        <v>202</v>
+      <c r="B35" s="174"/>
+      <c r="C35" s="175"/>
+      <c r="D35" s="126"/>
+      <c r="E35" s="176"/>
+      <c r="F35" s="177"/>
+      <c r="G35" s="177"/>
+      <c r="H35" s="178"/>
+      <c r="I35" s="179"/>
+      <c r="J35" s="177"/>
+      <c r="K35" s="177"/>
+      <c r="L35" s="178"/>
+      <c r="M35" s="179"/>
+      <c r="N35" s="177"/>
+      <c r="O35" s="178"/>
+      <c r="P35" s="177"/>
+      <c r="Q35" s="179"/>
+      <c r="R35" s="177"/>
+      <c r="S35" s="131"/>
+      <c r="U35" s="180"/>
+      <c r="V35" s="181" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/LHO - M5 - JournalPlanif.xlsx
+++ b/Documentation/LHO - M5 - JournalPlanif.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
   <si>
     <t>date</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t xml:space="preserve">Création et finalisation de la présentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout Git GitHub, Annexes</t>
   </si>
   <si>
     <t xml:space="preserve">Par jour</t>
@@ -1685,10 +1688,10 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4924,8 +4927,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E81">
-  <autoFilter ref="B2:E81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" displayName="Journal" ref="B2:E82">
+  <autoFilter ref="B2:E82"/>
   <tableColumns count="4">
     <tableColumn id="1" name="date" dataDxfId="0"/>
     <tableColumn id="2" name="Temps" dataDxfId="1"/>
@@ -5489,7 +5492,7 @@
       </c>
       <c r="I3" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.6506189821182942e-002</v>
+        <v>1.6371077762619368e-002</v>
       </c>
       <c r="J3" s="12" t="str">
         <f t="array" ref="J3:J9">_xlfn._xlws.FILTER(G3:G10,H3:H10&gt;0)</f>
@@ -5522,7 +5525,7 @@
       </c>
       <c r="I4" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.6506189821182942e-002</v>
+        <v>1.6371077762619368e-002</v>
       </c>
       <c r="J4" s="4" t="str">
         <f/>
@@ -5555,7 +5558,7 @@
       </c>
       <c r="I5" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>5.2269601100412649e-002</v>
+        <v>5.1841746248294671e-002</v>
       </c>
       <c r="J5" s="4" t="str">
         <f/>
@@ -5588,7 +5591,7 @@
       </c>
       <c r="I6" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>9.3535075653369992e-002</v>
+        <v>9.2769440654843091e-002</v>
       </c>
       <c r="J6" s="4" t="str">
         <f/>
@@ -5617,11 +5620,11 @@
       </c>
       <c r="H7" s="10">
         <f>SUMIF(Journal[type de travail],types[[#This Row],[type de travail]],Journal[Temps])*24</f>
-        <v>60.75</v>
+        <v>62.25</v>
       </c>
       <c r="I7" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.33425034387895458</v>
+        <v>0.33969986357435195</v>
       </c>
       <c r="J7" s="4" t="str">
         <f/>
@@ -5629,7 +5632,7 @@
       </c>
       <c r="K7" s="13">
         <f/>
-        <v>60.75</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="8" ht="28.5">
@@ -5654,7 +5657,7 @@
       </c>
       <c r="I8" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>0.42457588262265011</v>
+        <v>0.42110050022737605</v>
       </c>
       <c r="J8" s="4" t="str">
         <f/>
@@ -5687,7 +5690,7 @@
       </c>
       <c r="I9" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>4.3099495644199903e-002</v>
+        <v>4.2746703046839467e-002</v>
       </c>
       <c r="J9" s="4" t="str">
         <f/>
@@ -5720,7 +5723,7 @@
       </c>
       <c r="I10" s="11">
         <f>types[[#This Row],[somme]]/$H$11</f>
-        <v>1.9257221458046765e-002</v>
+        <v>1.9099590723055931e-002</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -5743,7 +5746,7 @@
       </c>
       <c r="H11" s="10">
         <f>SUM(H3:H10)</f>
-        <v>181.75000000000003</v>
+        <v>183.25000000000003</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -6729,11 +6732,25 @@
       <c r="C81" s="21">
         <v>0.125</v>
       </c>
-      <c r="D81" s="26" t="s">
+      <c r="D81" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E81" s="27" t="s">
+      <c r="E81" s="8" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="82" ht="14.25">
+      <c r="B82" s="22">
+        <v>46188</v>
+      </c>
+      <c r="C82" s="23">
+        <v>6.25e-002</v>
+      </c>
+      <c r="D82" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" s="27" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -6752,7 +6769,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{A40C2A4D-6AB0-4D36-9062-8784943F8D47}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{1EB892F3-1BAF-43C4-AAE4-FB64AFCD2FBA}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$G$3:$G$10</xm:f>
           </x14:formula1>
@@ -6776,11 +6793,11 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -6794,13 +6811,13 @@
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -6819,7 +6836,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F3" s="30">
         <f t="shared" ref="F3:F8" si="0">SUMPRODUCT((MONTH($A$3:$A$152)=D3)*($A$3:$A$152&lt;&gt;"")*$B$3:$B$152)</f>
@@ -6843,7 +6860,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F4" s="30">
         <f t="shared" si="0"/>
@@ -6867,7 +6884,7 @@
         <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F5" s="30">
         <f t="shared" si="0"/>
@@ -6891,7 +6908,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F6" s="30">
         <f t="shared" si="0"/>
@@ -6915,7 +6932,7 @@
         <v>5</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F7" s="30">
         <f t="shared" si="0"/>
@@ -6939,15 +6956,15 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F8" s="30">
         <f t="shared" si="0"/>
-        <v>0.76736111111111116</v>
+        <v>0.82986111111111116</v>
       </c>
       <c r="G8" s="31">
         <f t="shared" si="1"/>
-        <v>18.416666666666668</v>
+        <v>19.916666666666668</v>
       </c>
     </row>
     <row r="9">
@@ -6961,7 +6978,7 @@
       <c r="C9"/>
       <c r="G9" s="31">
         <f>SUM(G3:G8)</f>
-        <v>118.75000000000001</v>
+        <v>120.25000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -8628,7 +8645,7 @@
       </c>
       <c r="B149" s="29">
         <f>SUMIF(Journal[date],SommeParJours!A149,Journal[Temps])</f>
-        <v>0</v>
+        <v>6.25e-002</v>
       </c>
       <c r="C149" s="32"/>
     </row>
@@ -9037,16 +9054,16 @@
   <sheetData>
     <row r="1" s="35" customFormat="1" ht="66.599999999999994" customHeight="1">
       <c r="B1" s="36" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D1" s="38" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F1" s="39" t="s">
         <v>11</v>
@@ -9055,7 +9072,7 @@
         <v>17</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I1" s="38" t="s">
         <v>22</v>
@@ -9064,85 +9081,85 @@
         <v>37</v>
       </c>
       <c r="K1" s="38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L1" s="42" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M1" s="38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N1" s="40" t="s">
         <v>47</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P1" s="38" t="s">
         <v>49</v>
       </c>
       <c r="Q1" s="38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R1" s="38" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S1" s="38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="T1" s="38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="U1" s="38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="V1" s="40" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="W1" s="43" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="X1" s="38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Y1" s="38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z1" s="40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AA1" s="44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AB1" s="45" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AC1" s="45" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AD1" s="42" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AE1" s="46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AF1" s="47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG1" s="48" t="s">
         <v>92</v>
       </c>
       <c r="AH1" s="48" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AI1" s="48" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AJ1" s="48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK1" s="45" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL1" s="49"/>
       <c r="AM1" s="49"/>
@@ -9238,7 +9255,7 @@
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="50"/>
       <c r="C4" s="51" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D4" s="52"/>
       <c r="E4" s="52"/>
@@ -9394,7 +9411,7 @@
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="50"/>
       <c r="C8" s="51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D8" s="66"/>
       <c r="E8" s="66"/>
@@ -9472,7 +9489,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="50"/>
       <c r="C10" s="51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D10" s="52"/>
       <c r="E10" s="52"/>
@@ -9550,7 +9567,7 @@
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="50"/>
       <c r="C12" s="51" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D12" s="52"/>
       <c r="E12" s="52"/>
@@ -9627,10 +9644,10 @@
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="69" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D14" s="66"/>
       <c r="E14" s="66"/>
@@ -9708,7 +9725,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="69"/>
       <c r="C16" s="70" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D16" s="66"/>
       <c r="E16" s="66"/>
@@ -9783,13 +9800,13 @@
       <c r="AJ17" s="72"/>
       <c r="AK17" s="72"/>
       <c r="AN17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="69"/>
       <c r="C18" s="70" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D18" s="66"/>
       <c r="E18" s="66"/>
@@ -9867,7 +9884,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="69"/>
       <c r="C20" s="70" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D20" s="72"/>
       <c r="E20" s="72"/>
@@ -9945,7 +9962,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="69"/>
       <c r="C22" s="70" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D22" s="72"/>
       <c r="E22" s="72"/>
@@ -10023,7 +10040,7 @@
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="69"/>
       <c r="C24" s="70" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D24" s="72"/>
       <c r="E24" s="72"/>
@@ -10100,10 +10117,10 @@
     </row>
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D26" s="52"/>
       <c r="E26" s="52"/>
@@ -10181,7 +10198,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="50"/>
       <c r="C28" s="51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D28" s="52"/>
       <c r="E28" s="52"/>
@@ -10259,7 +10276,7 @@
     <row r="30" ht="12" customHeight="1">
       <c r="B30" s="50"/>
       <c r="C30" s="51" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D30" s="52"/>
       <c r="E30" s="52"/>
@@ -10337,7 +10354,7 @@
     <row r="32" ht="12" customHeight="1">
       <c r="B32" s="50"/>
       <c r="C32" s="51" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D32" s="52"/>
       <c r="E32" s="52"/>
@@ -10414,10 +10431,10 @@
     </row>
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="69" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C34" s="78" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D34" s="72"/>
       <c r="E34" s="72"/>
@@ -10495,7 +10512,7 @@
     <row r="36" ht="12" customHeight="1">
       <c r="B36" s="69"/>
       <c r="C36" s="78" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D36" s="72"/>
       <c r="E36" s="72"/>
@@ -10573,7 +10590,7 @@
     <row r="38" ht="12" customHeight="1">
       <c r="B38" s="69"/>
       <c r="C38" s="78" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D38" s="72"/>
       <c r="E38" s="72"/>
@@ -10651,7 +10668,7 @@
     <row r="40" ht="12" customHeight="1">
       <c r="B40" s="69"/>
       <c r="C40" s="78" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D40" s="72"/>
       <c r="E40" s="72"/>
@@ -10731,7 +10748,7 @@
         <v>21</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D42" s="52"/>
       <c r="E42" s="52"/>
@@ -10809,7 +10826,7 @@
     <row r="44" ht="12" customHeight="1">
       <c r="B44" s="50"/>
       <c r="C44" s="81" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="52"/>
@@ -10886,7 +10903,7 @@
     </row>
     <row r="46" ht="12" customHeight="1">
       <c r="B46" s="69" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C46" s="70" t="s">
         <v>24</v>
@@ -10964,14 +10981,14 @@
       <c r="AJ47" s="65"/>
       <c r="AK47" s="72"/>
       <c r="AN47" s="83" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AO47" s="66"/>
     </row>
     <row r="48" ht="12" customHeight="1">
       <c r="B48" s="69"/>
       <c r="C48" s="70" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D48" s="72"/>
       <c r="E48" s="72"/>
@@ -11008,7 +11025,7 @@
       <c r="AJ48" s="72"/>
       <c r="AK48" s="84"/>
       <c r="AN48" s="83" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AO48" s="65"/>
     </row>
@@ -11050,7 +11067,7 @@
       <c r="AJ49" s="72"/>
       <c r="AK49" s="72"/>
       <c r="AN49" s="83" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AO49" s="61"/>
     </row>
@@ -11119,37 +11136,37 @@
     </row>
     <row r="2" ht="56.399999999999999" customHeight="1">
       <c r="B2" s="86" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C2" s="87" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D2" s="88" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E2" s="89" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F2" s="90" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G2" s="90"/>
       <c r="H2" s="90"/>
       <c r="I2" s="89"/>
       <c r="J2" s="90" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K2" s="90"/>
       <c r="L2" s="90"/>
       <c r="M2" s="89"/>
       <c r="N2" s="90" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O2" s="90"/>
       <c r="P2" s="90"/>
       <c r="Q2" s="89"/>
       <c r="R2" s="90" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S2" s="91"/>
       <c r="AD2" s="92"/>
@@ -11158,7 +11175,7 @@
       <c r="B3" s="93"/>
       <c r="C3" s="94"/>
       <c r="D3" s="95" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E3" s="96">
         <v>4</v>
@@ -11206,15 +11223,15 @@
         <v>2</v>
       </c>
       <c r="U3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
       <c r="B4" s="100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D4" s="101"/>
       <c r="E4" s="102"/>
@@ -11233,7 +11250,7 @@
       <c r="R4" s="105"/>
       <c r="S4" s="106"/>
       <c r="U4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" ht="12" customHeight="1">
@@ -11259,7 +11276,7 @@
     <row r="6" ht="12" customHeight="1">
       <c r="B6" s="100"/>
       <c r="C6" s="115" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D6" s="116"/>
       <c r="E6" s="117"/>
@@ -11278,7 +11295,7 @@
       <c r="R6" s="121"/>
       <c r="S6" s="122"/>
       <c r="U6" s="123" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="V6" s="123"/>
     </row>
@@ -11302,13 +11319,13 @@
       <c r="R7" s="113"/>
       <c r="S7" s="114"/>
       <c r="U7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
       <c r="B8" s="100"/>
       <c r="C8" s="115" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D8" s="116"/>
       <c r="E8" s="117"/>
@@ -11327,7 +11344,7 @@
       <c r="R8" s="121"/>
       <c r="S8" s="122"/>
       <c r="U8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" ht="12" customHeight="1">
@@ -11353,7 +11370,7 @@
     <row r="10" ht="12" customHeight="1">
       <c r="B10" s="100"/>
       <c r="C10" s="115" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" s="116"/>
       <c r="E10" s="117"/>
@@ -11394,10 +11411,10 @@
     </row>
     <row r="12" ht="12" customHeight="1">
       <c r="B12" s="86" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D12" s="101"/>
       <c r="E12" s="102"/>
@@ -11439,7 +11456,7 @@
     <row r="14" ht="12" customHeight="1">
       <c r="B14" s="100"/>
       <c r="C14" s="115" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D14" s="134"/>
       <c r="E14" s="117"/>
@@ -11481,7 +11498,7 @@
     <row r="16" ht="12" customHeight="1">
       <c r="B16" s="100"/>
       <c r="C16" s="115" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D16" s="116"/>
       <c r="E16" s="117"/>
@@ -11522,10 +11539,10 @@
     </row>
     <row r="18" ht="12" customHeight="1">
       <c r="B18" s="88" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="87" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D18" s="101"/>
       <c r="E18" s="102"/>
@@ -11567,7 +11584,7 @@
     <row r="20" ht="12" customHeight="1">
       <c r="B20" s="100"/>
       <c r="C20" s="115" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D20" s="116"/>
       <c r="E20" s="117"/>
@@ -11609,7 +11626,7 @@
     <row r="22" ht="12" customHeight="1">
       <c r="B22" s="100"/>
       <c r="C22" s="115" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D22" s="116"/>
       <c r="E22" s="117"/>
@@ -11650,10 +11667,10 @@
     </row>
     <row r="24" ht="12" customHeight="1">
       <c r="B24" s="88" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D24" s="101"/>
       <c r="E24" s="102"/>
@@ -11695,7 +11712,7 @@
     <row r="26" ht="12" customHeight="1">
       <c r="B26" s="100"/>
       <c r="C26" s="115" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D26" s="116"/>
       <c r="E26" s="117"/>
@@ -11737,7 +11754,7 @@
     <row r="28" ht="12" customHeight="1">
       <c r="B28" s="100"/>
       <c r="C28" s="115" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D28" s="116"/>
       <c r="E28" s="117"/>
@@ -11781,7 +11798,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="147" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D30" s="101"/>
       <c r="E30" s="148"/>
@@ -11865,7 +11882,7 @@
     <row r="34" ht="12" customHeight="1">
       <c r="B34" s="153"/>
       <c r="C34" s="107" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D34" s="139"/>
       <c r="E34" s="167"/>
@@ -11885,7 +11902,7 @@
       <c r="S34" s="171"/>
       <c r="U34" s="172"/>
       <c r="V34" s="173" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" ht="13.800000000000001" customHeight="1">
@@ -11909,7 +11926,7 @@
       <c r="S35" s="131"/>
       <c r="U35" s="180"/>
       <c r="V35" s="181" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
